--- a/NSE_Sector_Monitor.xlsx
+++ b/NSE_Sector_Monitor.xlsx
@@ -571,19 +571,19 @@
         <v>8</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>14.87</v>
+        <v>14.77</v>
       </c>
       <c r="H2" s="1" t="n">
-        <v>1.64</v>
+        <v>1.23</v>
       </c>
       <c r="I2" s="1" t="n">
-        <v>3.51</v>
+        <v>2.81</v>
       </c>
       <c r="J2" s="1" t="n">
-        <v>6.99</v>
+        <v>6.27</v>
       </c>
       <c r="K2" s="1" t="n">
-        <v>22.78</v>
+        <v>21.95</v>
       </c>
       <c r="L2" s="1" t="inlineStr">
         <is>
@@ -617,46 +617,46 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Digital</t>
+          <t>Realty</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
         <v>2</v>
       </c>
       <c r="C3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D3" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>2</v>
-      </c>
       <c r="F3" s="2" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>88.36</v>
+        <v>85.69</v>
       </c>
       <c r="H3" s="1" t="n">
-        <v>-0.08</v>
+        <v>-2.09</v>
       </c>
       <c r="I3" s="1" t="n">
-        <v>-1.19</v>
+        <v>-4.07</v>
       </c>
       <c r="J3" s="1" t="n">
-        <v>0.32</v>
+        <v>-1.43</v>
       </c>
       <c r="K3" s="1" t="n">
-        <v>9.720000000000001</v>
+        <v>10.1</v>
       </c>
       <c r="L3" s="1" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Down</t>
         </is>
       </c>
       <c r="M3" s="1" t="n">
-        <v>-8.460000000000001</v>
+        <v>-8.08</v>
       </c>
       <c r="N3" s="1" t="inlineStr">
         <is>
@@ -670,7 +670,7 @@
       </c>
       <c r="P3" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Q3" s="1" t="inlineStr">
@@ -682,46 +682,46 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Realty</t>
+          <t>Digital</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
         <v>3</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>85.20999999999999</v>
+        <v>87.55</v>
       </c>
       <c r="H4" s="1" t="n">
-        <v>-3.05</v>
+        <v>-1.19</v>
       </c>
       <c r="I4" s="1" t="n">
-        <v>-4.61</v>
+        <v>-2.1</v>
       </c>
       <c r="J4" s="1" t="n">
-        <v>-1.98</v>
+        <v>-0.6</v>
       </c>
       <c r="K4" s="1" t="n">
-        <v>9.49</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="L4" s="1" t="inlineStr">
         <is>
-          <t>Down</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="M4" s="1" t="n">
-        <v>-8.59</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="N4" s="1" t="inlineStr">
         <is>
@@ -766,19 +766,19 @@
         <v>1</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>27.29</v>
+        <v>27.38</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.4</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>1.58</v>
+        <v>1.92</v>
       </c>
       <c r="J5" s="1" t="n">
-        <v>2.86</v>
+        <v>3.2</v>
       </c>
       <c r="K5" s="1" t="n">
-        <v>7.84</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L5" s="1" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="M5" s="1" t="n">
-        <v>-0.36</v>
+        <v>-0.03</v>
       </c>
       <c r="N5" s="1" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
       </c>
       <c r="O5" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P5" s="1" t="inlineStr">
@@ -831,19 +831,19 @@
         <v>-1</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>106.73</v>
+        <v>106.8</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>-1.97</v>
+        <v>-0.76</v>
       </c>
       <c r="I6" s="1" t="n">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="J6" s="1" t="n">
-        <v>2.76</v>
+        <v>2.83</v>
       </c>
       <c r="K6" s="1" t="n">
-        <v>6.72</v>
+        <v>6.79</v>
       </c>
       <c r="L6" s="1" t="inlineStr">
         <is>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="M6" s="1" t="n">
-        <v>-1.71</v>
+        <v>-1.64</v>
       </c>
       <c r="N6" s="1" t="inlineStr">
         <is>
@@ -896,19 +896,19 @@
         <v>5</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>16.96</v>
+        <v>17</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>-0.53</v>
+        <v>0</v>
       </c>
       <c r="I7" s="1" t="n">
-        <v>2.42</v>
+        <v>2.66</v>
       </c>
       <c r="J7" s="1" t="n">
-        <v>2.86</v>
+        <v>3.1</v>
       </c>
       <c r="K7" s="1" t="n">
-        <v>4.76</v>
+        <v>5.01</v>
       </c>
       <c r="L7" s="1" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         </is>
       </c>
       <c r="M7" s="1" t="n">
-        <v>-0.15</v>
+        <v>0</v>
       </c>
       <c r="N7" s="1" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
       </c>
       <c r="P7" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Q7" s="1" t="inlineStr">
@@ -961,19 +961,19 @@
         <v>9</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>32.4</v>
+        <v>32.49</v>
       </c>
       <c r="H8" s="1" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>-0</v>
+        <v>0.28</v>
       </c>
       <c r="J8" s="1" t="n">
-        <v>0.06</v>
+        <v>0.34</v>
       </c>
       <c r="K8" s="1" t="n">
-        <v>3.56</v>
+        <v>3.85</v>
       </c>
       <c r="L8" s="1" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         </is>
       </c>
       <c r="M8" s="1" t="n">
-        <v>-0.97</v>
+        <v>-0.7</v>
       </c>
       <c r="N8" s="1" t="inlineStr">
         <is>
@@ -1026,19 +1026,19 @@
         <v>11</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>282.87</v>
+        <v>283.5</v>
       </c>
       <c r="H9" s="1" t="n">
-        <v>-0.92</v>
+        <v>-0.36</v>
       </c>
       <c r="I9" s="1" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.29</v>
       </c>
       <c r="J9" s="1" t="n">
-        <v>-3.8</v>
+        <v>-3.58</v>
       </c>
       <c r="K9" s="1" t="n">
-        <v>3.3</v>
+        <v>3.53</v>
       </c>
       <c r="L9" s="1" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="M9" s="1" t="n">
-        <v>-4.59</v>
+        <v>-4.37</v>
       </c>
       <c r="N9" s="1" t="inlineStr">
         <is>
@@ -1091,19 +1091,19 @@
         <v>18</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>32.17</v>
+        <v>32.26</v>
       </c>
       <c r="H10" s="1" t="n">
-        <v>0.06</v>
+        <v>0.62</v>
       </c>
       <c r="I10" s="1" t="n">
-        <v>-4.03</v>
+        <v>-3.76</v>
       </c>
       <c r="J10" s="1" t="n">
-        <v>-4.27</v>
+        <v>-4.01</v>
       </c>
       <c r="K10" s="1" t="n">
-        <v>2.93</v>
+        <v>3.22</v>
       </c>
       <c r="L10" s="1" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="M10" s="1" t="n">
-        <v>-24.48</v>
+        <v>-24.27</v>
       </c>
       <c r="N10" s="1" t="inlineStr">
         <is>
@@ -1137,46 +1137,46 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>Tourism</t>
+          <t>EV &amp; New Age Auto</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
         <v>10</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>-3</v>
+        <v>3</v>
       </c>
       <c r="D11" s="2" t="n">
+        <v>-4</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>-4</v>
+      </c>
+      <c r="F11" s="2" t="n">
         <v>-2</v>
       </c>
-      <c r="E11" s="2" t="n">
-        <v>-2</v>
-      </c>
-      <c r="F11" s="2" t="n">
-        <v>2</v>
-      </c>
       <c r="G11" s="1" t="n">
-        <v>76.84999999999999</v>
+        <v>31.99</v>
       </c>
       <c r="H11" s="1" t="n">
-        <v>-0.44</v>
+        <v>-0.4</v>
       </c>
       <c r="I11" s="1" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="J11" s="1" t="n">
-        <v>-0.82</v>
+        <v>-3.05</v>
       </c>
       <c r="K11" s="1" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="L11" s="1" t="inlineStr">
         <is>
-          <t>Down</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="M11" s="1" t="n">
-        <v>-16.11</v>
+        <v>-3.55</v>
       </c>
       <c r="N11" s="1" t="inlineStr">
         <is>
@@ -1195,53 +1195,53 @@
       </c>
       <c r="Q11" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>EV &amp; New Age Auto</t>
+          <t>Tourism</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
         <v>11</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>2</v>
+        <v>-4</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>-5</v>
+        <v>-3</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>-5</v>
+        <v>-3</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-3</v>
+        <v>1</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>31.91</v>
+        <v>76.36</v>
       </c>
       <c r="H12" s="1" t="n">
-        <v>-0.93</v>
+        <v>-0.29</v>
       </c>
       <c r="I12" s="1" t="n">
-        <v>0.25</v>
+        <v>-0.11</v>
       </c>
       <c r="J12" s="1" t="n">
-        <v>-3.3</v>
+        <v>-1.46</v>
       </c>
       <c r="K12" s="1" t="n">
-        <v>2.46</v>
+        <v>2.03</v>
       </c>
       <c r="L12" s="1" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Down</t>
         </is>
       </c>
       <c r="M12" s="1" t="n">
-        <v>-3.79</v>
+        <v>-16.64</v>
       </c>
       <c r="N12" s="1" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="Q12" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1286,19 +1286,19 @@
         <v>5</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>127.96</v>
+        <v>127.99</v>
       </c>
       <c r="H13" s="1" t="n">
-        <v>-0.3</v>
+        <v>-0.27</v>
       </c>
       <c r="I13" s="1" t="n">
-        <v>0.27</v>
+        <v>0.29</v>
       </c>
       <c r="J13" s="1" t="n">
-        <v>-1.98</v>
+        <v>-1.96</v>
       </c>
       <c r="K13" s="1" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="L13" s="1" t="inlineStr">
         <is>
@@ -1306,7 +1306,7 @@
         </is>
       </c>
       <c r="M13" s="1" t="n">
-        <v>-6.25</v>
+        <v>-6.23</v>
       </c>
       <c r="N13" s="1" t="inlineStr">
         <is>
@@ -1351,19 +1351,19 @@
         <v>1</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>162.79</v>
+        <v>162.8</v>
       </c>
       <c r="H14" s="1" t="n">
-        <v>-0.68</v>
+        <v>-0.67</v>
       </c>
       <c r="I14" s="1" t="n">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="J14" s="1" t="n">
-        <v>-0.29</v>
+        <v>-0.28</v>
       </c>
       <c r="K14" s="1" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="L14" s="1" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         </is>
       </c>
       <c r="M14" s="1" t="n">
-        <v>-1.11</v>
+        <v>-1.1</v>
       </c>
       <c r="N14" s="1" t="inlineStr">
         <is>
@@ -1416,19 +1416,19 @@
         <v>-11</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>29.87</v>
+        <v>29.99</v>
       </c>
       <c r="H15" s="1" t="n">
-        <v>-0.76</v>
+        <v>-0.2</v>
       </c>
       <c r="I15" s="1" t="n">
-        <v>0.45</v>
+        <v>0.85</v>
       </c>
       <c r="J15" s="1" t="n">
-        <v>0.11</v>
+        <v>0.51</v>
       </c>
       <c r="K15" s="1" t="n">
-        <v>0.52</v>
+        <v>0.92</v>
       </c>
       <c r="L15" s="1" t="inlineStr">
         <is>
@@ -1481,19 +1481,19 @@
         <v>-14</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>13.1</v>
+        <v>13.15</v>
       </c>
       <c r="H16" s="1" t="n">
-        <v>-2.53</v>
+        <v>-1.42</v>
       </c>
       <c r="I16" s="1" t="n">
-        <v>-0.58</v>
+        <v>-0.2</v>
       </c>
       <c r="J16" s="1" t="n">
-        <v>3.46</v>
+        <v>3.86</v>
       </c>
       <c r="K16" s="1" t="n">
-        <v>-0.02</v>
+        <v>0.36</v>
       </c>
       <c r="L16" s="1" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         </is>
       </c>
       <c r="M16" s="1" t="n">
-        <v>-5.56</v>
+        <v>-5.2</v>
       </c>
       <c r="N16" s="1" t="inlineStr">
         <is>
@@ -1546,19 +1546,19 @@
         <v>-6</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>32.71</v>
+        <v>32.78</v>
       </c>
       <c r="H17" s="1" t="n">
-        <v>-0.55</v>
+        <v>-0.36</v>
       </c>
       <c r="I17" s="1" t="n">
-        <v>0.16</v>
+        <v>0.38</v>
       </c>
       <c r="J17" s="1" t="n">
-        <v>-4.02</v>
+        <v>-3.82</v>
       </c>
       <c r="K17" s="1" t="n">
-        <v>-0.13</v>
+        <v>0.09</v>
       </c>
       <c r="L17" s="1" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         </is>
       </c>
       <c r="M17" s="1" t="n">
-        <v>-4.02</v>
+        <v>-3.82</v>
       </c>
       <c r="N17" s="1" t="inlineStr">
         <is>
@@ -1611,19 +1611,19 @@
         <v>7</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>30.33</v>
+        <v>30.35</v>
       </c>
       <c r="H18" s="1" t="n">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="I18" s="1" t="n">
-        <v>-0.21</v>
+        <v>-0.15</v>
       </c>
       <c r="J18" s="1" t="n">
-        <v>0.42</v>
+        <v>0.48</v>
       </c>
       <c r="K18" s="1" t="n">
-        <v>-0.48</v>
+        <v>-0.42</v>
       </c>
       <c r="L18" s="1" t="inlineStr">
         <is>
@@ -1676,19 +1676,19 @@
         <v>-11</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>53.99</v>
+        <v>54.04</v>
       </c>
       <c r="H19" s="1" t="n">
-        <v>0</v>
+        <v>0.76</v>
       </c>
       <c r="I19" s="1" t="n">
-        <v>0.74</v>
+        <v>0.84</v>
       </c>
       <c r="J19" s="1" t="n">
-        <v>3.98</v>
+        <v>4.08</v>
       </c>
       <c r="K19" s="1" t="n">
-        <v>-0.73</v>
+        <v>-0.63</v>
       </c>
       <c r="L19" s="1" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
       </c>
       <c r="P19" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Q19" s="1" t="inlineStr">
@@ -1722,38 +1722,38 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>Bank</t>
+          <t>Private Bank</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
         <v>19</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>-8</v>
+        <v>-6</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>-7</v>
+        <v>1</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>586.35</v>
+        <v>28.15</v>
       </c>
       <c r="H20" s="1" t="n">
-        <v>0.08</v>
+        <v>1.48</v>
       </c>
       <c r="I20" s="1" t="n">
-        <v>0.02</v>
+        <v>0.84</v>
       </c>
       <c r="J20" s="1" t="n">
-        <v>1.45</v>
+        <v>4.35</v>
       </c>
       <c r="K20" s="1" t="n">
-        <v>-1.01</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="L20" s="1" t="inlineStr">
         <is>
@@ -1761,64 +1761,64 @@
         </is>
       </c>
       <c r="M20" s="1" t="n">
-        <v>-5.23</v>
+        <v>-2.89</v>
       </c>
       <c r="N20" s="1" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O20" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P20" s="1" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="O20" s="1" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="P20" s="1" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="Q20" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas</t>
+          <t>Bank</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
         <v>20</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>1</v>
+        <v>-10</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>3</v>
+        <v>-9</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>2</v>
+        <v>-8</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>11.17</v>
+        <v>587.25</v>
       </c>
       <c r="H21" s="1" t="n">
-        <v>-0.62</v>
+        <v>0.64</v>
       </c>
       <c r="I21" s="1" t="n">
-        <v>-0.09</v>
+        <v>0.17</v>
       </c>
       <c r="J21" s="1" t="n">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="K21" s="1" t="n">
-        <v>-1.34</v>
+        <v>-0.86</v>
       </c>
       <c r="L21" s="1" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         </is>
       </c>
       <c r="M21" s="1" t="n">
-        <v>-8.9</v>
+        <v>-5.08</v>
       </c>
       <c r="N21" s="1" t="inlineStr">
         <is>
@@ -1852,38 +1852,38 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>Private Bank</t>
+          <t>Oil &amp; Gas</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
         <v>21</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>-12</v>
+        <v>0</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>-8</v>
+        <v>2</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>-6</v>
+        <v>5</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>27.94</v>
+        <v>11.19</v>
       </c>
       <c r="H22" s="1" t="n">
         <v>0.18</v>
       </c>
       <c r="I22" s="1" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="J22" s="1" t="n">
-        <v>3.57</v>
+        <v>1.73</v>
       </c>
       <c r="K22" s="1" t="n">
-        <v>-1.55</v>
+        <v>-1.17</v>
       </c>
       <c r="L22" s="1" t="inlineStr">
         <is>
@@ -1891,7 +1891,7 @@
         </is>
       </c>
       <c r="M22" s="1" t="n">
-        <v>-3.62</v>
+        <v>-8.74</v>
       </c>
       <c r="N22" s="1" t="inlineStr">
         <is>
@@ -1936,19 +1936,19 @@
         <v>-4</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>94.18000000000001</v>
+        <v>94.22</v>
       </c>
       <c r="H23" s="1" t="n">
-        <v>0.68</v>
+        <v>0.73</v>
       </c>
       <c r="I23" s="1" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="J23" s="1" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.74</v>
       </c>
       <c r="K23" s="1" t="n">
-        <v>-2.14</v>
+        <v>-2.1</v>
       </c>
       <c r="L23" s="1" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         </is>
       </c>
       <c r="M23" s="1" t="n">
-        <v>-3.89</v>
+        <v>-3.85</v>
       </c>
       <c r="N23" s="1" t="inlineStr">
         <is>
@@ -2001,19 +2001,19 @@
         <v>0</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>10.11</v>
+        <v>10.13</v>
       </c>
       <c r="H24" s="1" t="n">
-        <v>-0.79</v>
+        <v>-0.1</v>
       </c>
       <c r="I24" s="1" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J24" s="1" t="n">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="K24" s="1" t="n">
-        <v>-2.9</v>
+        <v>-2.7</v>
       </c>
       <c r="L24" s="1" t="inlineStr">
         <is>
@@ -2021,7 +2021,7 @@
         </is>
       </c>
       <c r="M24" s="1" t="n">
-        <v>-9.98</v>
+        <v>-9.800000000000001</v>
       </c>
       <c r="N24" s="1" t="inlineStr">
         <is>
@@ -2066,19 +2066,19 @@
         <v>1</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>93.22</v>
+        <v>93.36</v>
       </c>
       <c r="H25" s="1" t="n">
-        <v>-0.38</v>
+        <v>-0.19</v>
       </c>
       <c r="I25" s="1" t="n">
-        <v>-0.68</v>
+        <v>-0.53</v>
       </c>
       <c r="J25" s="1" t="n">
-        <v>-1.69</v>
+        <v>-1.55</v>
       </c>
       <c r="K25" s="1" t="n">
-        <v>-3.32</v>
+        <v>-3.18</v>
       </c>
       <c r="L25" s="1" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         </is>
       </c>
       <c r="M25" s="1" t="n">
-        <v>-13.48</v>
+        <v>-13.35</v>
       </c>
       <c r="N25" s="1" t="inlineStr">
         <is>
@@ -2131,19 +2131,19 @@
         <v>-12</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>98.26000000000001</v>
+        <v>98.33</v>
       </c>
       <c r="H26" s="1" t="n">
-        <v>-0.31</v>
+        <v>-0.24</v>
       </c>
       <c r="I26" s="1" t="n">
-        <v>-0.4</v>
+        <v>-0.33</v>
       </c>
       <c r="J26" s="1" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="K26" s="1" t="n">
-        <v>-3.67</v>
+        <v>-3.6</v>
       </c>
       <c r="L26" s="1" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="M26" s="1" t="n">
-        <v>-8.210000000000001</v>
+        <v>-8.140000000000001</v>
       </c>
       <c r="N26" s="1" t="inlineStr">
         <is>
@@ -2196,19 +2196,19 @@
         <v>-24</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>38.06</v>
+        <v>38.2</v>
       </c>
       <c r="H27" s="1" t="n">
-        <v>-1.65</v>
+        <v>0.13</v>
       </c>
       <c r="I27" s="1" t="n">
-        <v>0.74</v>
+        <v>1.11</v>
       </c>
       <c r="J27" s="1" t="n">
-        <v>1.41</v>
+        <v>1.78</v>
       </c>
       <c r="K27" s="1" t="n">
-        <v>-4.45</v>
+        <v>-4.1</v>
       </c>
       <c r="L27" s="1" t="inlineStr">
         <is>
@@ -2261,19 +2261,19 @@
         <v>-5</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>48.6</v>
+        <v>48.58</v>
       </c>
       <c r="H28" s="1" t="n">
-        <v>-0.1</v>
+        <v>-0.14</v>
       </c>
       <c r="I28" s="1" t="n">
-        <v>-0.09</v>
+        <v>-0.13</v>
       </c>
       <c r="J28" s="1" t="n">
-        <v>-4.1</v>
+        <v>-4.14</v>
       </c>
       <c r="K28" s="1" t="n">
-        <v>-8.25</v>
+        <v>-8.279999999999999</v>
       </c>
       <c r="L28" s="1" t="inlineStr">
         <is>
@@ -2281,7 +2281,7 @@
         </is>
       </c>
       <c r="M28" s="1" t="n">
-        <v>-19.11</v>
+        <v>-19.14</v>
       </c>
       <c r="N28" s="1" t="inlineStr">
         <is>
@@ -2576,10 +2576,10 @@
         <v>9</v>
       </c>
       <c r="C2" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="D2" s="1" t="n">
         <v>19</v>
-      </c>
-      <c r="D2" s="1" t="n">
-        <v>21</v>
       </c>
       <c r="E2" s="1" t="n">
         <v>24</v>
@@ -2600,7 +2600,7 @@
         <v>15</v>
       </c>
       <c r="K2" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L2" s="1" t="n">
         <v>7</v>
@@ -2627,7 +2627,7 @@
         <v>5</v>
       </c>
       <c r="T2" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="U2" s="1" t="n">
         <v>14</v>
@@ -2639,19 +2639,19 @@
         <v>18</v>
       </c>
       <c r="X2" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y2" s="1" t="n">
         <v>1</v>
       </c>
       <c r="Z2" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA2" s="1" t="n">
         <v>17</v>
       </c>
       <c r="AB2" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3">
@@ -2661,7 +2661,7 @@
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C3" s="1" t="n">
         <v>18</v>
@@ -2685,7 +2685,7 @@
         <v>10</v>
       </c>
       <c r="J3" s="1" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K3" s="1" t="n">
         <v>2</v>
@@ -2697,16 +2697,16 @@
         <v>23</v>
       </c>
       <c r="N3" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="O3" s="1" t="n">
         <v>24</v>
       </c>
       <c r="P3" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q3" s="1" t="n">
         <v>25</v>
-      </c>
-      <c r="Q3" s="1" t="n">
-        <v>26</v>
       </c>
       <c r="R3" s="1" t="n">
         <v>17</v>
@@ -2715,16 +2715,16 @@
         <v>4</v>
       </c>
       <c r="T3" s="1" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="U3" s="1" t="n">
         <v>13</v>
       </c>
       <c r="V3" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="W3" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="X3" s="1" t="n">
         <v>3</v>
@@ -2736,7 +2736,7 @@
         <v>8</v>
       </c>
       <c r="AA3" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AB3" s="1" t="n">
         <v>9</v>

--- a/NSE_Sector_Monitor.xlsx
+++ b/NSE_Sector_Monitor.xlsx
@@ -565,25 +565,25 @@
         <v>0</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>14.77</v>
+        <v>14.45</v>
       </c>
       <c r="H2" s="1" t="n">
-        <v>1.23</v>
+        <v>-2.82</v>
       </c>
       <c r="I2" s="1" t="n">
-        <v>2.81</v>
+        <v>1.74</v>
       </c>
       <c r="J2" s="1" t="n">
-        <v>6.27</v>
+        <v>5.57</v>
       </c>
       <c r="K2" s="1" t="n">
-        <v>21.95</v>
+        <v>20</v>
       </c>
       <c r="L2" s="1" t="inlineStr">
         <is>
@@ -591,16 +591,16 @@
         </is>
       </c>
       <c r="M2" s="1" t="n">
-        <v>0</v>
+        <v>-1.14</v>
       </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr">
@@ -617,46 +617,46 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Realty</t>
+          <t>Pharma</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
         <v>2</v>
       </c>
       <c r="C3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="G3" s="1" t="n">
+        <v>26.94</v>
+      </c>
+      <c r="H3" s="1" t="n">
+        <v>-1.28</v>
+      </c>
+      <c r="I3" s="1" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="J3" s="1" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="K3" s="1" t="n">
+        <v>11.14</v>
+      </c>
+      <c r="L3" s="1" t="inlineStr">
+        <is>
+          <t>Up</t>
+        </is>
+      </c>
+      <c r="M3" s="1" t="n">
         <v>0</v>
-      </c>
-      <c r="D3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="G3" s="1" t="n">
-        <v>85.69</v>
-      </c>
-      <c r="H3" s="1" t="n">
-        <v>-2.09</v>
-      </c>
-      <c r="I3" s="1" t="n">
-        <v>-4.07</v>
-      </c>
-      <c r="J3" s="1" t="n">
-        <v>-1.43</v>
-      </c>
-      <c r="K3" s="1" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>Down</t>
-        </is>
-      </c>
-      <c r="M3" s="1" t="n">
-        <v>-8.08</v>
       </c>
       <c r="N3" s="1" t="inlineStr">
         <is>
@@ -692,28 +692,28 @@
         <v>0</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>87.55</v>
+        <v>88.19</v>
       </c>
       <c r="H4" s="1" t="n">
-        <v>-1.19</v>
+        <v>-0.19</v>
       </c>
       <c r="I4" s="1" t="n">
-        <v>-2.1</v>
+        <v>1.1</v>
       </c>
       <c r="J4" s="1" t="n">
-        <v>-0.6</v>
+        <v>1.77</v>
       </c>
       <c r="K4" s="1" t="n">
-        <v>8.720000000000001</v>
+        <v>10.81</v>
       </c>
       <c r="L4" s="1" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
         </is>
       </c>
       <c r="M4" s="1" t="n">
-        <v>-9.300000000000001</v>
+        <v>-7.05</v>
       </c>
       <c r="N4" s="1" t="inlineStr">
         <is>
@@ -747,47 +747,47 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Pharma</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
         <v>4</v>
       </c>
       <c r="C5" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="G5" s="1" t="n">
+        <v>16.84</v>
+      </c>
+      <c r="H5" s="1" t="n">
+        <v>-0.71</v>
+      </c>
+      <c r="I5" s="1" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="J5" s="1" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="K5" s="1" t="n">
+        <v>8.57</v>
+      </c>
+      <c r="L5" s="1" t="inlineStr">
+        <is>
+          <t>Up</t>
+        </is>
+      </c>
+      <c r="M5" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="D5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" s="1" t="n">
-        <v>27.38</v>
-      </c>
-      <c r="H5" s="1" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="I5" s="1" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="J5" s="1" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="K5" s="1" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="L5" s="1" t="inlineStr">
-        <is>
-          <t>Up</t>
-        </is>
-      </c>
-      <c r="M5" s="1" t="n">
-        <v>-0.03</v>
-      </c>
       <c r="N5" s="1" t="inlineStr">
         <is>
           <t>No</t>
@@ -795,12 +795,12 @@
       </c>
       <c r="O5" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P5" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Q5" s="1" t="inlineStr">
@@ -812,38 +812,38 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Defence</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
         <v>5</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D6" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="E6" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="E6" s="2" t="n">
-        <v>9</v>
-      </c>
       <c r="F6" s="2" t="n">
-        <v>-1</v>
+        <v>22</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>106.8</v>
+        <v>32.87</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>-0.76</v>
+        <v>2.18</v>
       </c>
       <c r="I6" s="1" t="n">
-        <v>1.37</v>
+        <v>1.56</v>
       </c>
       <c r="J6" s="1" t="n">
-        <v>2.83</v>
+        <v>0.64</v>
       </c>
       <c r="K6" s="1" t="n">
-        <v>6.79</v>
+        <v>6.02</v>
       </c>
       <c r="L6" s="1" t="inlineStr">
         <is>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="M6" s="1" t="n">
-        <v>-1.64</v>
+        <v>-21.5</v>
       </c>
       <c r="N6" s="1" t="inlineStr">
         <is>
@@ -865,50 +865,50 @@
       </c>
       <c r="P6" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Q6" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>EV &amp; New Age Auto</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
         <v>6</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>1</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>9</v>
+        <v>-1</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>17</v>
+        <v>31.48</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>0</v>
+        <v>-1.35</v>
       </c>
       <c r="I7" s="1" t="n">
-        <v>2.66</v>
+        <v>0.4</v>
       </c>
       <c r="J7" s="1" t="n">
-        <v>3.1</v>
+        <v>-3.45</v>
       </c>
       <c r="K7" s="1" t="n">
-        <v>5.01</v>
+        <v>3.4</v>
       </c>
       <c r="L7" s="1" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         </is>
       </c>
       <c r="M7" s="1" t="n">
-        <v>0</v>
+        <v>-3.45</v>
       </c>
       <c r="N7" s="1" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
       </c>
       <c r="P7" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Q7" s="1" t="inlineStr">
@@ -942,46 +942,46 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Fin Services</t>
+          <t>Realty</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
         <v>7</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>-1</v>
+        <v>-5</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>10</v>
+        <v>-5</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>12</v>
+        <v>-6</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>9</v>
+        <v>-6</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>32.49</v>
+        <v>82.37</v>
       </c>
       <c r="H8" s="1" t="n">
-        <v>0.4</v>
+        <v>-3.33</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>0.28</v>
+        <v>-5.69</v>
       </c>
       <c r="J8" s="1" t="n">
-        <v>0.34</v>
+        <v>-5.57</v>
       </c>
       <c r="K8" s="1" t="n">
-        <v>3.85</v>
+        <v>3.35</v>
       </c>
       <c r="L8" s="1" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Down</t>
         </is>
       </c>
       <c r="M8" s="1" t="n">
-        <v>-0.7</v>
+        <v>-10.11</v>
       </c>
       <c r="N8" s="1" t="inlineStr">
         <is>
@@ -1000,45 +1000,45 @@
       </c>
       <c r="Q8" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>Defence</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
         <v>8</v>
       </c>
       <c r="C9" s="2" t="n">
+        <v>-3</v>
+      </c>
+      <c r="D9" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D9" s="2" t="n">
+      <c r="E9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" s="2" t="n">
         <v>-3</v>
       </c>
-      <c r="E9" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>11</v>
-      </c>
       <c r="G9" s="1" t="n">
-        <v>283.5</v>
+        <v>100.76</v>
       </c>
       <c r="H9" s="1" t="n">
-        <v>-0.36</v>
+        <v>-5.59</v>
       </c>
       <c r="I9" s="1" t="n">
-        <v>0.29</v>
+        <v>-5.6</v>
       </c>
       <c r="J9" s="1" t="n">
-        <v>-3.58</v>
+        <v>-2.39</v>
       </c>
       <c r="K9" s="1" t="n">
-        <v>3.53</v>
+        <v>3</v>
       </c>
       <c r="L9" s="1" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="M9" s="1" t="n">
-        <v>-4.37</v>
+        <v>-5.6</v>
       </c>
       <c r="N9" s="1" t="inlineStr">
         <is>
@@ -1072,38 +1072,38 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Auto</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
         <v>9</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>3</v>
+        <v>-3</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>-4</v>
+        <v>-7</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>32.26</v>
+        <v>278.31</v>
       </c>
       <c r="H10" s="1" t="n">
-        <v>0.62</v>
+        <v>-1.61</v>
       </c>
       <c r="I10" s="1" t="n">
-        <v>-3.76</v>
+        <v>-0.26</v>
       </c>
       <c r="J10" s="1" t="n">
-        <v>-4.01</v>
+        <v>-3.74</v>
       </c>
       <c r="K10" s="1" t="n">
-        <v>3.22</v>
+        <v>2.8</v>
       </c>
       <c r="L10" s="1" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="M10" s="1" t="n">
-        <v>-24.27</v>
+        <v>-4.5</v>
       </c>
       <c r="N10" s="1" t="inlineStr">
         <is>
@@ -1137,46 +1137,46 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>EV &amp; New Age Auto</t>
+          <t>Consumption</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
         <v>10</v>
       </c>
       <c r="C11" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F11" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D11" s="2" t="n">
-        <v>-4</v>
-      </c>
-      <c r="E11" s="2" t="n">
-        <v>-4</v>
-      </c>
-      <c r="F11" s="2" t="n">
-        <v>-2</v>
-      </c>
       <c r="G11" s="1" t="n">
-        <v>31.99</v>
+        <v>126.43</v>
       </c>
       <c r="H11" s="1" t="n">
-        <v>-0.4</v>
+        <v>-1.2</v>
       </c>
       <c r="I11" s="1" t="n">
-        <v>0.5</v>
+        <v>0.63</v>
       </c>
       <c r="J11" s="1" t="n">
-        <v>-3.05</v>
+        <v>-1.99</v>
       </c>
       <c r="K11" s="1" t="n">
-        <v>2.72</v>
+        <v>1.47</v>
       </c>
       <c r="L11" s="1" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Down</t>
         </is>
       </c>
       <c r="M11" s="1" t="n">
-        <v>-3.55</v>
+        <v>-5.4</v>
       </c>
       <c r="N11" s="1" t="inlineStr">
         <is>
@@ -1195,7 +1195,7 @@
       </c>
       <c r="Q11" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1209,31 +1209,31 @@
         <v>11</v>
       </c>
       <c r="C12" s="2" t="n">
+        <v>-3</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="E12" s="2" t="n">
         <v>-4</v>
       </c>
-      <c r="D12" s="2" t="n">
-        <v>-3</v>
-      </c>
-      <c r="E12" s="2" t="n">
-        <v>-3</v>
-      </c>
       <c r="F12" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>76.36</v>
+        <v>75.27</v>
       </c>
       <c r="H12" s="1" t="n">
-        <v>-0.29</v>
+        <v>-2.06</v>
       </c>
       <c r="I12" s="1" t="n">
-        <v>-0.11</v>
+        <v>-0.15</v>
       </c>
       <c r="J12" s="1" t="n">
-        <v>-1.46</v>
+        <v>-1.72</v>
       </c>
       <c r="K12" s="1" t="n">
-        <v>2.03</v>
+        <v>1.29</v>
       </c>
       <c r="L12" s="1" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="M12" s="1" t="n">
-        <v>-16.64</v>
+        <v>-16.41</v>
       </c>
       <c r="N12" s="1" t="inlineStr">
         <is>
@@ -1267,46 +1267,46 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>Consumption</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
         <v>12</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D13" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>-6</v>
+      </c>
+      <c r="G13" s="1" t="n">
+        <v>29.24</v>
+      </c>
+      <c r="H13" s="1" t="n">
+        <v>-2.11</v>
+      </c>
+      <c r="I13" s="1" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="J13" s="1" t="n">
+        <v>-0.28</v>
+      </c>
+      <c r="K13" s="1" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="L13" s="1" t="inlineStr">
+        <is>
+          <t>Up</t>
+        </is>
+      </c>
+      <c r="M13" s="1" t="n">
         <v>0</v>
-      </c>
-      <c r="E13" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F13" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="G13" s="1" t="n">
-        <v>127.99</v>
-      </c>
-      <c r="H13" s="1" t="n">
-        <v>-0.27</v>
-      </c>
-      <c r="I13" s="1" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="J13" s="1" t="n">
-        <v>-1.96</v>
-      </c>
-      <c r="K13" s="1" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="L13" s="1" t="inlineStr">
-        <is>
-          <t>Down</t>
-        </is>
-      </c>
-      <c r="M13" s="1" t="n">
-        <v>-6.23</v>
       </c>
       <c r="N13" s="1" t="inlineStr">
         <is>
@@ -1339,39 +1339,39 @@
         <v>13</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>162.8</v>
+        <v>158.97</v>
       </c>
       <c r="H14" s="1" t="n">
-        <v>-0.67</v>
+        <v>-2.35</v>
       </c>
       <c r="I14" s="1" t="n">
-        <v>0.2</v>
+        <v>-1.24</v>
       </c>
       <c r="J14" s="1" t="n">
-        <v>-0.28</v>
+        <v>-1.55</v>
       </c>
       <c r="K14" s="1" t="n">
-        <v>1.12</v>
+        <v>0.77</v>
       </c>
       <c r="L14" s="1" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Down</t>
         </is>
       </c>
       <c r="M14" s="1" t="n">
-        <v>-1.1</v>
+        <v>-1.76</v>
       </c>
       <c r="N14" s="1" t="inlineStr">
         <is>
@@ -1397,46 +1397,46 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Fin Services</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
         <v>14</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>2</v>
+        <v>-5</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>4</v>
+        <v>-1</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-11</v>
+        <v>-4</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>29.99</v>
+        <v>31.64</v>
       </c>
       <c r="H15" s="1" t="n">
-        <v>-0.2</v>
+        <v>-2.35</v>
       </c>
       <c r="I15" s="1" t="n">
-        <v>0.85</v>
+        <v>-0.11</v>
       </c>
       <c r="J15" s="1" t="n">
-        <v>0.51</v>
+        <v>-0.24</v>
       </c>
       <c r="K15" s="1" t="n">
-        <v>0.92</v>
+        <v>0.53</v>
       </c>
       <c r="L15" s="1" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Down</t>
         </is>
       </c>
       <c r="M15" s="1" t="n">
-        <v>0</v>
+        <v>-1.62</v>
       </c>
       <c r="N15" s="1" t="inlineStr">
         <is>
@@ -1469,31 +1469,31 @@
         <v>15</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-14</v>
+        <v>-8</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>13.15</v>
+        <v>12.77</v>
       </c>
       <c r="H16" s="1" t="n">
-        <v>-1.42</v>
+        <v>-2.52</v>
       </c>
       <c r="I16" s="1" t="n">
-        <v>-0.2</v>
+        <v>-0.93</v>
       </c>
       <c r="J16" s="1" t="n">
-        <v>3.86</v>
+        <v>1.11</v>
       </c>
       <c r="K16" s="1" t="n">
-        <v>0.36</v>
+        <v>0.5</v>
       </c>
       <c r="L16" s="1" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         </is>
       </c>
       <c r="M16" s="1" t="n">
-        <v>-5.2</v>
+        <v>-6.35</v>
       </c>
       <c r="N16" s="1" t="inlineStr">
         <is>
@@ -1515,7 +1515,7 @@
       </c>
       <c r="P16" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Q16" s="1" t="inlineStr">
@@ -1527,46 +1527,46 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>MNC</t>
+          <t>Bank</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
         <v>16</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>3</v>
+        <v>-6</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-6</v>
+        <v>5</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>32.78</v>
+        <v>579.33</v>
       </c>
       <c r="H17" s="1" t="n">
-        <v>-0.36</v>
+        <v>-1.2</v>
       </c>
       <c r="I17" s="1" t="n">
-        <v>0.38</v>
+        <v>1.09</v>
       </c>
       <c r="J17" s="1" t="n">
-        <v>-3.82</v>
+        <v>1.49</v>
       </c>
       <c r="K17" s="1" t="n">
-        <v>0.09</v>
+        <v>0.36</v>
       </c>
       <c r="L17" s="1" t="inlineStr">
         <is>
-          <t>Down</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="M17" s="1" t="n">
-        <v>-3.82</v>
+        <v>-4.74</v>
       </c>
       <c r="N17" s="1" t="inlineStr">
         <is>
@@ -1585,7 +1585,7 @@
       </c>
       <c r="Q17" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1599,35 +1599,35 @@
         <v>17</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>30.35</v>
+        <v>30</v>
       </c>
       <c r="H18" s="1" t="n">
-        <v>0.73</v>
+        <v>-1.09</v>
       </c>
       <c r="I18" s="1" t="n">
-        <v>-0.15</v>
+        <v>1.28</v>
       </c>
       <c r="J18" s="1" t="n">
         <v>0.48</v>
       </c>
       <c r="K18" s="1" t="n">
-        <v>-0.42</v>
+        <v>0.34</v>
       </c>
       <c r="L18" s="1" t="inlineStr">
         <is>
-          <t>Down</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="M18" s="1" t="n">
@@ -1657,38 +1657,38 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>Capital Market</t>
+          <t>Private Bank</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
         <v>18</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>3</v>
+        <v>-7</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>-17</v>
+        <v>-1</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>-11</v>
+        <v>-6</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>54.04</v>
+        <v>27.76</v>
       </c>
       <c r="H19" s="1" t="n">
-        <v>0.76</v>
+        <v>-0.64</v>
       </c>
       <c r="I19" s="1" t="n">
-        <v>0.84</v>
+        <v>1.77</v>
       </c>
       <c r="J19" s="1" t="n">
-        <v>4.08</v>
+        <v>3.72</v>
       </c>
       <c r="K19" s="1" t="n">
-        <v>-0.63</v>
+        <v>0.11</v>
       </c>
       <c r="L19" s="1" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         </is>
       </c>
       <c r="M19" s="1" t="n">
-        <v>0</v>
+        <v>-2.58</v>
       </c>
       <c r="N19" s="1" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
       </c>
       <c r="P19" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Q19" s="1" t="inlineStr">
@@ -1722,55 +1722,55 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>Private Bank</t>
+          <t>MNC</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
         <v>19</v>
       </c>
       <c r="C20" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>-6</v>
+      </c>
+      <c r="F20" s="2" t="n">
         <v>-10</v>
       </c>
-      <c r="D20" s="2" t="n">
-        <v>-6</v>
-      </c>
-      <c r="E20" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F20" s="2" t="n">
-        <v>-4</v>
-      </c>
       <c r="G20" s="1" t="n">
-        <v>28.15</v>
+        <v>32.18</v>
       </c>
       <c r="H20" s="1" t="n">
-        <v>1.48</v>
+        <v>-1.62</v>
       </c>
       <c r="I20" s="1" t="n">
-        <v>0.84</v>
+        <v>-0.09</v>
       </c>
       <c r="J20" s="1" t="n">
-        <v>4.35</v>
+        <v>-2.95</v>
       </c>
       <c r="K20" s="1" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.71</v>
       </c>
       <c r="L20" s="1" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Down</t>
         </is>
       </c>
       <c r="M20" s="1" t="n">
-        <v>-2.89</v>
+        <v>-3.94</v>
       </c>
       <c r="N20" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O20" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P20" s="1" t="inlineStr">
@@ -1780,45 +1780,45 @@
       </c>
       <c r="Q20" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>Bank</t>
+          <t>Oil &amp; Gas</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
         <v>20</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>-10</v>
+        <v>2</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>-9</v>
+        <v>1</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>-8</v>
+        <v>2</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>587.25</v>
+        <v>11</v>
       </c>
       <c r="H21" s="1" t="n">
-        <v>0.64</v>
+        <v>-1.52</v>
       </c>
       <c r="I21" s="1" t="n">
-        <v>0.17</v>
+        <v>0.87</v>
       </c>
       <c r="J21" s="1" t="n">
-        <v>1.61</v>
+        <v>0.98</v>
       </c>
       <c r="K21" s="1" t="n">
-        <v>-0.86</v>
+        <v>-1.62</v>
       </c>
       <c r="L21" s="1" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         </is>
       </c>
       <c r="M21" s="1" t="n">
-        <v>-5.08</v>
+        <v>-8.73</v>
       </c>
       <c r="N21" s="1" t="inlineStr">
         <is>
@@ -1852,38 +1852,38 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas</t>
+          <t>PSE</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
         <v>21</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>11.19</v>
+        <v>9.93</v>
       </c>
       <c r="H22" s="1" t="n">
-        <v>0.18</v>
+        <v>-1.78</v>
       </c>
       <c r="I22" s="1" t="n">
-        <v>0.09</v>
+        <v>0.77</v>
       </c>
       <c r="J22" s="1" t="n">
-        <v>1.73</v>
+        <v>1.27</v>
       </c>
       <c r="K22" s="1" t="n">
-        <v>-1.17</v>
+        <v>-2.31</v>
       </c>
       <c r="L22" s="1" t="inlineStr">
         <is>
@@ -1891,7 +1891,7 @@
         </is>
       </c>
       <c r="M22" s="1" t="n">
-        <v>-8.74</v>
+        <v>-10.05</v>
       </c>
       <c r="N22" s="1" t="inlineStr">
         <is>
@@ -1917,46 +1917,46 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Capital Market</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
         <v>22</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="D23" s="2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>-19</v>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>-19</v>
+      </c>
+      <c r="G23" s="1" t="n">
+        <v>52.85</v>
+      </c>
+      <c r="H23" s="1" t="n">
+        <v>-2.11</v>
+      </c>
+      <c r="I23" s="1" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="J23" s="1" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="K23" s="1" t="n">
+        <v>-2.54</v>
+      </c>
+      <c r="L23" s="1" t="inlineStr">
+        <is>
+          <t>Up</t>
+        </is>
+      </c>
+      <c r="M23" s="1" t="n">
         <v>0</v>
-      </c>
-      <c r="E23" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="F23" s="2" t="n">
-        <v>-4</v>
-      </c>
-      <c r="G23" s="1" t="n">
-        <v>94.22</v>
-      </c>
-      <c r="H23" s="1" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="I23" s="1" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="J23" s="1" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="K23" s="1" t="n">
-        <v>-2.1</v>
-      </c>
-      <c r="L23" s="1" t="inlineStr">
-        <is>
-          <t>Up</t>
-        </is>
-      </c>
-      <c r="M23" s="1" t="n">
-        <v>-3.85</v>
       </c>
       <c r="N23" s="1" t="inlineStr">
         <is>
@@ -1982,46 +1982,46 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>PSE</t>
+          <t>PSU Bank</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
         <v>23</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>2</v>
+        <v>-9</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>4</v>
+        <v>-15</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>10.13</v>
+        <v>91.25</v>
       </c>
       <c r="H24" s="1" t="n">
-        <v>-0.1</v>
+        <v>-2.11</v>
       </c>
       <c r="I24" s="1" t="n">
-        <v>1.2</v>
+        <v>-0.18</v>
       </c>
       <c r="J24" s="1" t="n">
-        <v>1.95</v>
+        <v>-2.04</v>
       </c>
       <c r="K24" s="1" t="n">
-        <v>-2.7</v>
+        <v>-2.65</v>
       </c>
       <c r="L24" s="1" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Down</t>
         </is>
       </c>
       <c r="M24" s="1" t="n">
-        <v>-9.800000000000001</v>
+        <v>-13.84</v>
       </c>
       <c r="N24" s="1" t="inlineStr">
         <is>
@@ -2047,46 +2047,46 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>PSU Bank</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
         <v>24</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>-7</v>
+        <v>-3</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>-10</v>
+        <v>-2</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>-13</v>
+        <v>-3</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>1</v>
+        <v>-8</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>93.36</v>
+        <v>91.91</v>
       </c>
       <c r="H25" s="1" t="n">
-        <v>-0.19</v>
+        <v>-2.41</v>
       </c>
       <c r="I25" s="1" t="n">
-        <v>-0.53</v>
+        <v>-0.29</v>
       </c>
       <c r="J25" s="1" t="n">
-        <v>-1.55</v>
+        <v>-0.61</v>
       </c>
       <c r="K25" s="1" t="n">
-        <v>-3.18</v>
+        <v>-3.14</v>
       </c>
       <c r="L25" s="1" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Down</t>
         </is>
       </c>
       <c r="M25" s="1" t="n">
-        <v>-13.35</v>
+        <v>-4.58</v>
       </c>
       <c r="N25" s="1" t="inlineStr">
         <is>
@@ -2125,33 +2125,33 @@
         <v>1</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>-12</v>
+        <v>-11</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>98.33</v>
+        <v>96.23999999999999</v>
       </c>
       <c r="H26" s="1" t="n">
-        <v>-0.24</v>
+        <v>-2.06</v>
       </c>
       <c r="I26" s="1" t="n">
-        <v>-0.33</v>
+        <v>0.26</v>
       </c>
       <c r="J26" s="1" t="n">
-        <v>1.39</v>
+        <v>0.65</v>
       </c>
       <c r="K26" s="1" t="n">
-        <v>-3.6</v>
+        <v>-3.33</v>
       </c>
       <c r="L26" s="1" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Down</t>
         </is>
       </c>
       <c r="M26" s="1" t="n">
-        <v>-8.140000000000001</v>
+        <v>-8.539999999999999</v>
       </c>
       <c r="N26" s="1" t="inlineStr">
         <is>
@@ -2184,31 +2184,31 @@
         <v>26</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D27" s="2" t="n">
         <v>1</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="F27" s="2" t="n">
         <v>-24</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>38.2</v>
+        <v>37.48</v>
       </c>
       <c r="H27" s="1" t="n">
-        <v>0.13</v>
+        <v>-1.52</v>
       </c>
       <c r="I27" s="1" t="n">
-        <v>1.11</v>
+        <v>0.33</v>
       </c>
       <c r="J27" s="1" t="n">
-        <v>1.78</v>
+        <v>1.06</v>
       </c>
       <c r="K27" s="1" t="n">
-        <v>-4.1</v>
+        <v>-4.28</v>
       </c>
       <c r="L27" s="1" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
       </c>
       <c r="Q27" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2249,31 +2249,31 @@
         <v>27</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="F28" s="2" t="n">
         <v>-5</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>48.58</v>
+        <v>48.49</v>
       </c>
       <c r="H28" s="1" t="n">
-        <v>-0.14</v>
+        <v>-0.23</v>
       </c>
       <c r="I28" s="1" t="n">
-        <v>-0.13</v>
+        <v>1.09</v>
       </c>
       <c r="J28" s="1" t="n">
-        <v>-4.14</v>
+        <v>-2.2</v>
       </c>
       <c r="K28" s="1" t="n">
-        <v>-8.279999999999999</v>
+        <v>-6.61</v>
       </c>
       <c r="L28" s="1" t="inlineStr">
         <is>
@@ -2281,7 +2281,7 @@
         </is>
       </c>
       <c r="M28" s="1" t="n">
-        <v>-19.14</v>
+        <v>-17.08</v>
       </c>
       <c r="N28" s="1" t="inlineStr">
         <is>
@@ -2569,50 +2569,50 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B2" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="C2" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="D2" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="E2" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="F2" s="1" t="n">
         <v>9</v>
-      </c>
-      <c r="C2" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="D2" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="E2" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="F2" s="1" t="n">
-        <v>8</v>
       </c>
       <c r="G2" s="1" t="n">
         <v>27</v>
       </c>
       <c r="H2" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I2" s="1" t="n">
         <v>4</v>
-      </c>
-      <c r="I2" s="1" t="n">
-        <v>6</v>
       </c>
       <c r="J2" s="1" t="n">
         <v>15</v>
       </c>
       <c r="K2" s="1" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="L2" s="1" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="M2" s="1" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="N2" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="O2" s="1" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="P2" s="1" t="n">
         <v>26</v>
@@ -2621,22 +2621,22 @@
         <v>25</v>
       </c>
       <c r="R2" s="1" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="S2" s="1" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T2" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="U2" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="V2" s="1" t="n">
         <v>13</v>
       </c>
       <c r="W2" s="1" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="X2" s="1" t="n">
         <v>3</v>
@@ -2651,56 +2651,56 @@
         <v>17</v>
       </c>
       <c r="AB2" s="1" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="C3" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="D3" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="D3" s="1" t="n">
-        <v>21</v>
-      </c>
       <c r="E3" s="1" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G3" s="1" t="n">
         <v>27</v>
       </c>
       <c r="H3" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I3" s="1" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J3" s="1" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K3" s="1" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L3" s="1" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="M3" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N3" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O3" s="1" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="P3" s="1" t="n">
         <v>26</v>
@@ -2709,22 +2709,22 @@
         <v>25</v>
       </c>
       <c r="R3" s="1" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="S3" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T3" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="U3" s="1" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="V3" s="1" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="W3" s="1" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="X3" s="1" t="n">
         <v>3</v>
@@ -2733,35 +2733,35 @@
         <v>1</v>
       </c>
       <c r="Z3" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA3" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="AB3" s="1" t="n">
         <v>8</v>
-      </c>
-      <c r="AA3" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="AB3" s="1" t="n">
-        <v>9</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G4" s="1" t="n">
         <v>27</v>
@@ -2770,137 +2770,137 @@
         <v>4</v>
       </c>
       <c r="I4" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="J4" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="K4" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="L4" s="1" t="n">
         <v>7</v>
-      </c>
-      <c r="J4" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="K4" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="L4" s="1" t="n">
-        <v>8</v>
       </c>
       <c r="M4" s="1" t="n">
         <v>22</v>
       </c>
       <c r="N4" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="O4" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="P4" s="1" t="n">
         <v>26</v>
       </c>
-      <c r="P4" s="1" t="n">
+      <c r="Q4" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="Q4" s="1" t="n">
-        <v>24</v>
-      </c>
       <c r="R4" s="1" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="S4" s="1" t="n">
         <v>5</v>
       </c>
       <c r="T4" s="1" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="U4" s="1" t="n">
         <v>14</v>
       </c>
       <c r="V4" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="W4" s="1" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="X4" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y4" s="1" t="n">
         <v>1</v>
       </c>
       <c r="Z4" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA4" s="1" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AB4" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G5" s="1" t="n">
         <v>27</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J5" s="1" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="K5" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L5" s="1" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="M5" s="1" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N5" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="O5" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P5" s="1" t="n">
         <v>26</v>
       </c>
       <c r="Q5" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="R5" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="S5" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T5" s="1" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="U5" s="1" t="n">
         <v>13</v>
       </c>
       <c r="V5" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="W5" s="1" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="X5" s="1" t="n">
         <v>3</v>
@@ -2912,44 +2912,44 @@
         <v>8</v>
       </c>
       <c r="AA5" s="1" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AB5" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>6</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H6" s="1" t="n">
         <v>4</v>
       </c>
       <c r="I6" s="1" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J6" s="1" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="K6" s="1" t="n">
         <v>2</v>
@@ -2958,37 +2958,37 @@
         <v>8</v>
       </c>
       <c r="M6" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N6" s="1" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="O6" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="P6" s="1" t="n">
         <v>25</v>
-      </c>
-      <c r="P6" s="1" t="n">
-        <v>27</v>
       </c>
       <c r="Q6" s="1" t="n">
         <v>24</v>
       </c>
       <c r="R6" s="1" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="S6" s="1" t="n">
         <v>5</v>
       </c>
       <c r="T6" s="1" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="U6" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="V6" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="W6" s="1" t="n">
         <v>15</v>
-      </c>
-      <c r="W6" s="1" t="n">
-        <v>17</v>
       </c>
       <c r="X6" s="1" t="n">
         <v>3</v>
@@ -2997,83 +2997,83 @@
         <v>1</v>
       </c>
       <c r="Z6" s="1" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AA6" s="1" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AB6" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H7" s="1" t="n">
         <v>4</v>
       </c>
       <c r="I7" s="1" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="J7" s="1" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K7" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="M7" s="1" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N7" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O7" s="1" t="n">
         <v>25</v>
       </c>
       <c r="P7" s="1" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Q7" s="1" t="n">
         <v>24</v>
       </c>
       <c r="R7" s="1" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="S7" s="1" t="n">
         <v>5</v>
       </c>
       <c r="T7" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="U7" s="1" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="V7" s="1" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="W7" s="1" t="n">
         <v>19</v>
@@ -3085,32 +3085,32 @@
         <v>1</v>
       </c>
       <c r="Z7" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA7" s="1" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AB7" s="1" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C8" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D8" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="D8" s="1" t="n">
-        <v>12</v>
-      </c>
       <c r="E8" s="1" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>6</v>
@@ -3122,49 +3122,49 @@
         <v>4</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J8" s="1" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="K8" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M8" s="1" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="N8" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="O8" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="P8" s="1" t="n">
         <v>27</v>
       </c>
       <c r="Q8" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R8" s="1" t="n">
         <v>19</v>
       </c>
       <c r="S8" s="1" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T8" s="1" t="n">
         <v>22</v>
       </c>
       <c r="U8" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="V8" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="V8" s="1" t="n">
-        <v>18</v>
-      </c>
       <c r="W8" s="1" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="X8" s="1" t="n">
         <v>3</v>
@@ -3173,59 +3173,59 @@
         <v>1</v>
       </c>
       <c r="Z8" s="1" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AA8" s="1" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AB8" s="1" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D9" s="1" t="n">
         <v>9</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H9" s="1" t="n">
         <v>4</v>
       </c>
       <c r="I9" s="1" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="J9" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K9" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L9" s="1" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M9" s="1" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N9" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O9" s="1" t="n">
         <v>25</v>
@@ -3234,25 +3234,25 @@
         <v>27</v>
       </c>
       <c r="Q9" s="1" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="R9" s="1" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="S9" s="1" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" s="1" t="n">
         <v>21</v>
       </c>
       <c r="U9" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="V9" s="1" t="n">
         <v>18</v>
       </c>
       <c r="W9" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="X9" s="1" t="n">
         <v>3</v>
@@ -3261,41 +3261,41 @@
         <v>1</v>
       </c>
       <c r="Z9" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA9" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AB9" s="1" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F10" s="1" t="n">
         <v>6</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H10" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I10" s="1" t="n">
         <v>5</v>
@@ -3307,13 +3307,13 @@
         <v>2</v>
       </c>
       <c r="L10" s="1" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="M10" s="1" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="N10" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="O10" s="1" t="n">
         <v>24</v>
@@ -3322,37 +3322,37 @@
         <v>27</v>
       </c>
       <c r="Q10" s="1" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="R10" s="1" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="S10" s="1" t="n">
         <v>8</v>
       </c>
       <c r="T10" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="U10" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="V10" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="W10" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="U10" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="V10" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="W10" s="1" t="n">
-        <v>20</v>
-      </c>
       <c r="X10" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y10" s="1" t="n">
         <v>1</v>
       </c>
       <c r="Z10" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA10" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AB10" s="1" t="n">
         <v>7</v>
@@ -3361,32 +3361,32 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G11" s="1" t="n">
         <v>24</v>
       </c>
       <c r="H11" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="I11" s="1" t="n">
         <v>5</v>
-      </c>
-      <c r="I11" s="1" t="n">
-        <v>6</v>
       </c>
       <c r="J11" s="1" t="n">
         <v>23</v>
@@ -3395,43 +3395,43 @@
         <v>2</v>
       </c>
       <c r="L11" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="M11" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="N11" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="M11" s="1" t="n">
+      <c r="O11" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="P11" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q11" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="R11" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="S11" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="N11" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="O11" s="1" t="n">
-        <v>27</v>
-      </c>
-      <c r="P11" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="Q11" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="R11" s="1" t="n">
+      <c r="U11" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="V11" s="1" t="n">
         <v>18</v>
-      </c>
-      <c r="S11" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="T11" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="U11" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="V11" s="1" t="n">
-        <v>17</v>
       </c>
       <c r="W11" s="1" t="n">
         <v>20</v>
       </c>
       <c r="X11" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y11" s="1" t="n">
         <v>1</v>
@@ -3440,7 +3440,7 @@
         <v>8</v>
       </c>
       <c r="AA11" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AB11" s="1" t="n">
         <v>7</v>
@@ -3449,41 +3449,41 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="C12" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="D12" s="1" t="n">
         <v>11</v>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>13</v>
       </c>
       <c r="E12" s="1" t="n">
         <v>14</v>
       </c>
       <c r="F12" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="G12" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="H12" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="I12" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="G12" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="H12" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="I12" s="1" t="n">
-        <v>7</v>
-      </c>
       <c r="J12" s="1" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="K12" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="M12" s="1" t="n">
         <v>22</v>
@@ -3492,7 +3492,7 @@
         <v>12</v>
       </c>
       <c r="O12" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P12" s="1" t="n">
         <v>27</v>
@@ -3501,47 +3501,47 @@
         <v>26</v>
       </c>
       <c r="R12" s="1" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="S12" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T12" s="1" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="U12" s="1" t="n">
         <v>18</v>
       </c>
       <c r="V12" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="W12" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="X12" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y12" s="1" t="n">
         <v>1</v>
       </c>
       <c r="Z12" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA12" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AB12" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C13" s="1" t="n">
         <v>10</v>
@@ -3550,131 +3550,131 @@
         <v>12</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G13" s="1" t="n">
         <v>24</v>
       </c>
       <c r="H13" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I13" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J13" s="1" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K13" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L13" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="M13" s="1" t="n">
         <v>21</v>
       </c>
       <c r="N13" s="1" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="O13" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="P13" s="1" t="n">
         <v>26</v>
-      </c>
-      <c r="P13" s="1" t="n">
-        <v>27</v>
       </c>
       <c r="Q13" s="1" t="n">
         <v>25</v>
       </c>
       <c r="R13" s="1" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="S13" s="1" t="n">
         <v>9</v>
       </c>
       <c r="T13" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="U13" s="1" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="V13" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="W13" s="1" t="n">
         <v>20</v>
       </c>
       <c r="X13" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y13" s="1" t="n">
         <v>1</v>
       </c>
       <c r="Z13" s="1" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AA13" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AB13" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="C14" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="C14" s="1" t="n">
-        <v>9</v>
-      </c>
       <c r="D14" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="E14" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="E14" s="1" t="n">
-        <v>12</v>
-      </c>
       <c r="F14" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G14" s="1" t="n">
         <v>24</v>
       </c>
       <c r="H14" s="1" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I14" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J14" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K14" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M14" s="1" t="n">
         <v>22</v>
       </c>
       <c r="N14" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="O14" s="1" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P14" s="1" t="n">
         <v>27</v>
       </c>
       <c r="Q14" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="R14" s="1" t="n">
         <v>19</v>
@@ -3689,10 +3689,10 @@
         <v>18</v>
       </c>
       <c r="V14" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="W14" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="X14" s="1" t="n">
         <v>3</v>
@@ -3701,86 +3701,86 @@
         <v>1</v>
       </c>
       <c r="Z14" s="1" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AA14" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AB14" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="C15" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="D15" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="D15" s="1" t="n">
-        <v>17</v>
-      </c>
       <c r="E15" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G15" s="1" t="n">
         <v>24</v>
       </c>
       <c r="H15" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="I15" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="I15" s="1" t="n">
-        <v>11</v>
-      </c>
       <c r="J15" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K15" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L15" s="1" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="M15" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N15" s="1" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="O15" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="P15" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q15" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="P15" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="Q15" s="1" t="n">
-        <v>27</v>
-      </c>
       <c r="R15" s="1" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="S15" s="1" t="n">
         <v>9</v>
       </c>
       <c r="T15" s="1" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="U15" s="1" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="V15" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="W15" s="1" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="X15" s="1" t="n">
         <v>3</v>
@@ -3792,83 +3792,83 @@
         <v>6</v>
       </c>
       <c r="AA15" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AB15" s="1" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="C16" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="D16" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="E16" s="1" t="n">
         <v>12</v>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>15</v>
       </c>
       <c r="F16" s="1" t="n">
         <v>4</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H16" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I16" s="1" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J16" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K16" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L16" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="M16" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="N16" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="O16" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="P16" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q16" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="R16" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="S16" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="U16" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="M16" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="N16" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="O16" s="1" t="n">
-        <v>27</v>
-      </c>
-      <c r="P16" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="Q16" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="R16" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="S16" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="T16" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="U16" s="1" t="n">
-        <v>19</v>
-      </c>
       <c r="V16" s="1" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="W16" s="1" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="X16" s="1" t="n">
         <v>3</v>
@@ -3877,32 +3877,32 @@
         <v>1</v>
       </c>
       <c r="Z16" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA16" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AB16" s="1" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C17" s="1" t="n">
         <v>12</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F17" s="1" t="n">
         <v>4</v>
@@ -3911,113 +3911,113 @@
         <v>24</v>
       </c>
       <c r="H17" s="1" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I17" s="1" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J17" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K17" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L17" s="1" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M17" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="N17" s="1" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="O17" s="1" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="P17" s="1" t="n">
         <v>26</v>
       </c>
       <c r="Q17" s="1" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="R17" s="1" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="S17" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T17" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="U17" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="V17" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="W17" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="U17" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="V17" s="1" t="n">
+      <c r="X17" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y17" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z17" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA17" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="W17" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="X17" s="1" t="n">
+      <c r="AB17" s="1" t="n">
         <v>5</v>
-      </c>
-      <c r="Y17" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z17" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA17" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="AB17" s="1" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="F18" s="1" t="n">
         <v>4</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H18" s="1" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="I18" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="J18" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="J18" s="1" t="n">
-        <v>23</v>
-      </c>
       <c r="K18" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L18" s="1" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M18" s="1" t="n">
         <v>21</v>
       </c>
       <c r="N18" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O18" s="1" t="n">
         <v>27</v>
@@ -4026,13 +4026,13 @@
         <v>26</v>
       </c>
       <c r="Q18" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R18" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="S18" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T18" s="1" t="n">
         <v>22</v>
@@ -4041,22 +4041,22 @@
         <v>19</v>
       </c>
       <c r="V18" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="W18" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="X18" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y18" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="X18" s="1" t="n">
+      <c r="Z18" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="Y18" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z18" s="1" t="n">
-        <v>7</v>
-      </c>
       <c r="AA18" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AB18" s="1" t="n">
         <v>5</v>
@@ -4065,32 +4065,32 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C19" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="E19" s="1" t="n">
         <v>10</v>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>9</v>
       </c>
       <c r="F19" s="1" t="n">
         <v>4</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H19" s="1" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I19" s="1" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="J19" s="1" t="n">
         <v>22</v>
@@ -4099,7 +4099,7 @@
         <v>3</v>
       </c>
       <c r="L19" s="1" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="M19" s="1" t="n">
         <v>21</v>
@@ -4111,13 +4111,13 @@
         <v>27</v>
       </c>
       <c r="P19" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q19" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="Q19" s="1" t="n">
-        <v>24</v>
-      </c>
       <c r="R19" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="S19" s="1" t="n">
         <v>8</v>
@@ -4126,16 +4126,16 @@
         <v>23</v>
       </c>
       <c r="U19" s="1" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="V19" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="W19" s="1" t="n">
         <v>1</v>
       </c>
       <c r="X19" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y19" s="1" t="n">
         <v>2</v>
@@ -4144,50 +4144,50 @@
         <v>7</v>
       </c>
       <c r="AA19" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AB19" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D20" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E20" s="1" t="n">
         <v>9</v>
       </c>
       <c r="F20" s="1" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H20" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I20" s="1" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J20" s="1" t="n">
         <v>23</v>
       </c>
       <c r="K20" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L20" s="1" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="M20" s="1" t="n">
         <v>21</v>
@@ -4196,37 +4196,37 @@
         <v>11</v>
       </c>
       <c r="O20" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="P20" s="1" t="n">
         <v>26</v>
-      </c>
-      <c r="P20" s="1" t="n">
-        <v>24</v>
       </c>
       <c r="Q20" s="1" t="n">
         <v>25</v>
       </c>
       <c r="R20" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="S20" s="1" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T20" s="1" t="n">
         <v>22</v>
       </c>
       <c r="U20" s="1" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="V20" s="1" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="W20" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="X20" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Y20" s="1" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Z20" s="1" t="n">
         <v>7</v>
@@ -4241,38 +4241,38 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="C21" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="C21" s="1" t="n">
-        <v>11</v>
-      </c>
       <c r="D21" s="1" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F21" s="1" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H21" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I21" s="1" t="n">
         <v>19</v>
       </c>
       <c r="J21" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K21" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L21" s="1" t="n">
         <v>20</v>
@@ -4281,40 +4281,40 @@
         <v>21</v>
       </c>
       <c r="N21" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="O21" s="1" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P21" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q21" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="Q21" s="1" t="n">
-        <v>25</v>
-      </c>
       <c r="R21" s="1" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="S21" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T21" s="1" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="U21" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="V21" s="1" t="n">
         <v>14</v>
       </c>
       <c r="W21" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="X21" s="1" t="n">
         <v>6</v>
       </c>
       <c r="Y21" s="1" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Z21" s="1" t="n">
         <v>7</v>
@@ -4329,38 +4329,38 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D22" s="1" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F22" s="1" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H22" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I22" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J22" s="1" t="n">
         <v>23</v>
       </c>
       <c r="K22" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L22" s="1" t="n">
         <v>20</v>
@@ -4369,10 +4369,10 @@
         <v>21</v>
       </c>
       <c r="N22" s="1" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="O22" s="1" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P22" s="1" t="n">
         <v>24</v>
@@ -4384,31 +4384,31 @@
         <v>14</v>
       </c>
       <c r="S22" s="1" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T22" s="1" t="n">
         <v>22</v>
       </c>
       <c r="U22" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="V22" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="W22" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X22" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y22" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="Y22" s="1" t="n">
-        <v>2</v>
-      </c>
       <c r="Z22" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA22" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AB22" s="1" t="n">
         <v>5</v>
@@ -4417,62 +4417,62 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D23" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="E23" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="F23" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G23" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="H23" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="I23" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="J23" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="K23" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L23" s="1" t="n">
         <v>20</v>
-      </c>
-      <c r="E23" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="F23" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="G23" s="1" t="n">
-        <v>23</v>
-      </c>
-      <c r="H23" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="I23" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="J23" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="K23" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="L23" s="1" t="n">
-        <v>19</v>
       </c>
       <c r="M23" s="1" t="n">
         <v>21</v>
       </c>
       <c r="N23" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="O23" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="P23" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q23" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="R23" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="O23" s="1" t="n">
-        <v>27</v>
-      </c>
-      <c r="P23" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="Q23" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="R23" s="1" t="n">
-        <v>10</v>
-      </c>
       <c r="S23" s="1" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="T23" s="1" t="n">
         <v>22</v>
@@ -4481,65 +4481,65 @@
         <v>16</v>
       </c>
       <c r="V23" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="W23" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="X23" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y23" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z23" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA23" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="W23" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="X23" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y23" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z23" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="AA23" s="1" t="n">
-        <v>17</v>
-      </c>
       <c r="AB23" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D24" s="1" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E24" s="1" t="n">
         <v>10</v>
       </c>
       <c r="F24" s="1" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G24" s="1" t="n">
         <v>26</v>
       </c>
       <c r="H24" s="1" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I24" s="1" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="J24" s="1" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K24" s="1" t="n">
         <v>3</v>
       </c>
       <c r="L24" s="1" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="M24" s="1" t="n">
         <v>21</v>
@@ -4560,16 +4560,16 @@
         <v>14</v>
       </c>
       <c r="S24" s="1" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="T24" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="U24" s="1" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="V24" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="W24" s="1" t="n">
         <v>1</v>
@@ -4581,47 +4581,47 @@
         <v>2</v>
       </c>
       <c r="Z24" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA24" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AB24" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D25" s="1" t="n">
         <v>20</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F25" s="1" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="H25" s="1" t="n">
         <v>9</v>
       </c>
       <c r="I25" s="1" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="J25" s="1" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K25" s="1" t="n">
         <v>3</v>
@@ -4633,7 +4633,7 @@
         <v>21</v>
       </c>
       <c r="N25" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="O25" s="1" t="n">
         <v>27</v>
@@ -4642,22 +4642,22 @@
         <v>25</v>
       </c>
       <c r="Q25" s="1" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="R25" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="S25" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="T25" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="U25" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="V25" s="1" t="n">
         <v>18</v>
-      </c>
-      <c r="V25" s="1" t="n">
-        <v>17</v>
       </c>
       <c r="W25" s="1" t="n">
         <v>1</v>
@@ -4669,10 +4669,10 @@
         <v>2</v>
       </c>
       <c r="Z25" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA25" s="1" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AB25" s="1" t="n">
         <v>6</v>
@@ -4681,23 +4681,23 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D26" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F26" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G26" s="1" t="n">
         <v>26</v>
@@ -4706,31 +4706,31 @@
         <v>8</v>
       </c>
       <c r="I26" s="1" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J26" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K26" s="1" t="n">
         <v>3</v>
       </c>
       <c r="L26" s="1" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="M26" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N26" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="O26" s="1" t="n">
         <v>27</v>
       </c>
       <c r="P26" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q26" s="1" t="n">
         <v>25</v>
-      </c>
-      <c r="Q26" s="1" t="n">
-        <v>24</v>
       </c>
       <c r="R26" s="1" t="n">
         <v>14</v>
@@ -4742,25 +4742,25 @@
         <v>23</v>
       </c>
       <c r="U26" s="1" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="V26" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="W26" s="1" t="n">
         <v>1</v>
       </c>
       <c r="X26" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y26" s="1" t="n">
         <v>2</v>
       </c>
       <c r="Z26" s="1" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AA26" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AB26" s="1" t="n">
         <v>6</v>
@@ -4769,83 +4769,83 @@
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="C27" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="D27" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="E27" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="F27" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="G27" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="H27" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="C27" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="D27" s="1" t="n">
+      <c r="I27" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="J27" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="K27" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="L27" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="E27" s="1" t="n">
+      <c r="M27" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="N27" s="1" t="n">
         <v>11</v>
-      </c>
-      <c r="F27" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="G27" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="H27" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="I27" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="J27" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="K27" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="L27" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="M27" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="N27" s="1" t="n">
-        <v>12</v>
       </c>
       <c r="O27" s="1" t="n">
         <v>27</v>
       </c>
       <c r="P27" s="1" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Q27" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R27" s="1" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="S27" s="1" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="T27" s="1" t="n">
         <v>23</v>
       </c>
       <c r="U27" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="V27" s="1" t="n">
         <v>17</v>
-      </c>
-      <c r="V27" s="1" t="n">
-        <v>15</v>
       </c>
       <c r="W27" s="1" t="n">
         <v>1</v>
       </c>
       <c r="X27" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y27" s="1" t="n">
         <v>2</v>
       </c>
       <c r="Z27" s="1" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AA27" s="1" t="n">
         <v>14</v>
@@ -4857,41 +4857,41 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="C28" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D28" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="E28" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="F28" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="G28" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="H28" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="C28" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="D28" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="E28" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="F28" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="G28" s="1" t="n">
-        <v>23</v>
-      </c>
-      <c r="H28" s="1" t="n">
+      <c r="I28" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="J28" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="K28" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="I28" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="J28" s="1" t="n">
+      <c r="L28" s="1" t="n">
         <v>20</v>
-      </c>
-      <c r="K28" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="L28" s="1" t="n">
-        <v>18</v>
       </c>
       <c r="M28" s="1" t="n">
         <v>22</v>
@@ -4903,40 +4903,40 @@
         <v>27</v>
       </c>
       <c r="P28" s="1" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Q28" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R28" s="1" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="S28" s="1" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="T28" s="1" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="U28" s="1" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="V28" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="W28" s="1" t="n">
         <v>1</v>
       </c>
       <c r="X28" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y28" s="1" t="n">
         <v>2</v>
       </c>
       <c r="Z28" s="1" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AA28" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AB28" s="1" t="n">
         <v>6</v>
@@ -4945,47 +4945,47 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D29" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="E29" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="F29" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="G29" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="H29" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="I29" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="J29" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="K29" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="L29" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="M29" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="N29" s="1" t="n">
         <v>12</v>
-      </c>
-      <c r="E29" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="F29" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="G29" s="1" t="n">
-        <v>23</v>
-      </c>
-      <c r="H29" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="I29" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="J29" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="K29" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="L29" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="M29" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="N29" s="1" t="n">
-        <v>11</v>
       </c>
       <c r="O29" s="1" t="n">
         <v>27</v>
@@ -4994,62 +4994,62 @@
         <v>26</v>
       </c>
       <c r="Q29" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="R29" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="S29" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="T29" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="U29" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="V29" s="1" t="n">
         <v>15</v>
-      </c>
-      <c r="S29" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="T29" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="U29" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="V29" s="1" t="n">
-        <v>13</v>
       </c>
       <c r="W29" s="1" t="n">
         <v>1</v>
       </c>
       <c r="X29" s="1" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y29" s="1" t="n">
         <v>2</v>
       </c>
       <c r="Z29" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA29" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AB29" s="1" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D30" s="1" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F30" s="1" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G30" s="1" t="n">
         <v>23</v>
@@ -5058,22 +5058,22 @@
         <v>3</v>
       </c>
       <c r="I30" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="J30" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="K30" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="J30" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="K30" s="1" t="n">
-        <v>5</v>
-      </c>
       <c r="L30" s="1" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="M30" s="1" t="n">
         <v>22</v>
       </c>
       <c r="N30" s="1" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="O30" s="1" t="n">
         <v>27</v>
@@ -5082,22 +5082,22 @@
         <v>26</v>
       </c>
       <c r="Q30" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="R30" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="S30" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="T30" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="R30" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="S30" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="T30" s="1" t="n">
-        <v>25</v>
-      </c>
       <c r="U30" s="1" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="V30" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="W30" s="1" t="n">
         <v>1</v>
@@ -5109,32 +5109,32 @@
         <v>2</v>
       </c>
       <c r="Z30" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA30" s="1" t="n">
         <v>14</v>
       </c>
       <c r="AB30" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
         <v>10</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D31" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F31" s="1" t="n">
         <v>5</v>
@@ -5143,25 +5143,25 @@
         <v>23</v>
       </c>
       <c r="H31" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="I31" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="J31" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="K31" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="I31" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="J31" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="K31" s="1" t="n">
-        <v>6</v>
-      </c>
       <c r="L31" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M31" s="1" t="n">
         <v>21</v>
       </c>
       <c r="N31" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="O31" s="1" t="n">
         <v>27</v>
@@ -5173,25 +5173,25 @@
         <v>24</v>
       </c>
       <c r="R31" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="S31" s="1" t="n">
         <v>19</v>
-      </c>
-      <c r="S31" s="1" t="n">
-        <v>18</v>
       </c>
       <c r="T31" s="1" t="n">
         <v>25</v>
       </c>
       <c r="U31" s="1" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="V31" s="1" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="W31" s="1" t="n">
         <v>1</v>
       </c>
       <c r="X31" s="1" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Y31" s="1" t="n">
         <v>2</v>
@@ -5200,29 +5200,29 @@
         <v>9</v>
       </c>
       <c r="AA31" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AB31" s="1" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D32" s="1" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F32" s="1" t="n">
         <v>6</v>
@@ -5231,25 +5231,25 @@
         <v>23</v>
       </c>
       <c r="H32" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I32" s="1" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J32" s="1" t="n">
         <v>21</v>
       </c>
       <c r="K32" s="1" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L32" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="M32" s="1" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="N32" s="1" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="O32" s="1" t="n">
         <v>27</v>
@@ -5261,34 +5261,34 @@
         <v>24</v>
       </c>
       <c r="R32" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="S32" s="1" t="n">
         <v>19</v>
-      </c>
-      <c r="S32" s="1" t="n">
-        <v>18</v>
       </c>
       <c r="T32" s="1" t="n">
         <v>25</v>
       </c>
       <c r="U32" s="1" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="V32" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="W32" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="X32" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="X32" s="1" t="n">
-        <v>7</v>
-      </c>
       <c r="Y32" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Z32" s="1" t="n">
         <v>9</v>
       </c>
       <c r="AA32" s="1" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AB32" s="1" t="n">
         <v>8</v>
@@ -5297,41 +5297,41 @@
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
         <v>10</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D33" s="1" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F33" s="1" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G33" s="1" t="n">
         <v>23</v>
       </c>
       <c r="H33" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I33" s="1" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J33" s="1" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K33" s="1" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L33" s="1" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="M33" s="1" t="n">
         <v>21</v>
@@ -5349,77 +5349,77 @@
         <v>24</v>
       </c>
       <c r="R33" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="S33" s="1" t="n">
         <v>18</v>
-      </c>
-      <c r="S33" s="1" t="n">
-        <v>19</v>
       </c>
       <c r="T33" s="1" t="n">
         <v>25</v>
       </c>
       <c r="U33" s="1" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="V33" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="W33" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="X33" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="X33" s="1" t="n">
-        <v>6</v>
-      </c>
       <c r="Y33" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Z33" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA33" s="1" t="n">
         <v>17</v>
       </c>
       <c r="AB33" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C34" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="D34" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="D34" s="1" t="n">
-        <v>13</v>
-      </c>
       <c r="E34" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F34" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G34" s="1" t="n">
         <v>23</v>
       </c>
       <c r="H34" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I34" s="1" t="n">
         <v>3</v>
       </c>
       <c r="J34" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K34" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L34" s="1" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="M34" s="1" t="n">
         <v>20</v>
@@ -5449,41 +5449,41 @@
         <v>10</v>
       </c>
       <c r="V34" s="1" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="W34" s="1" t="n">
         <v>4</v>
       </c>
       <c r="X34" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y34" s="1" t="n">
         <v>5</v>
       </c>
       <c r="Z34" s="1" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AA34" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AB34" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D35" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E35" s="1" t="n">
         <v>22</v>
@@ -5492,25 +5492,25 @@
         <v>7</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H35" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I35" s="1" t="n">
         <v>3</v>
       </c>
       <c r="J35" s="1" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="K35" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L35" s="1" t="n">
         <v>16</v>
       </c>
       <c r="M35" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N35" s="1" t="n">
         <v>12</v>
@@ -5522,22 +5522,22 @@
         <v>26</v>
       </c>
       <c r="Q35" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R35" s="1" t="n">
         <v>18</v>
       </c>
       <c r="S35" s="1" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="T35" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="U35" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="V35" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="W35" s="1" t="n">
         <v>4</v>
@@ -5549,38 +5549,38 @@
         <v>5</v>
       </c>
       <c r="Z35" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA35" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="AB35" s="1" t="n">
         <v>9</v>
-      </c>
-      <c r="AA35" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="AB35" s="1" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B36" s="1" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D36" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F36" s="1" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H36" s="1" t="n">
         <v>2</v>
@@ -5589,13 +5589,13 @@
         <v>3</v>
       </c>
       <c r="J36" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K36" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L36" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="M36" s="1" t="n">
         <v>20</v>
@@ -5607,40 +5607,40 @@
         <v>27</v>
       </c>
       <c r="P36" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q36" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="Q36" s="1" t="n">
+      <c r="R36" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="S36" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="T36" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="R36" s="1" t="n">
+      <c r="U36" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="V36" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="W36" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="X36" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y36" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z36" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA36" s="1" t="n">
         <v>16</v>
-      </c>
-      <c r="S36" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="T36" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="U36" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="V36" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="W36" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="X36" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="Y36" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="Z36" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="AA36" s="1" t="n">
-        <v>18</v>
       </c>
       <c r="AB36" s="1" t="n">
         <v>9</v>
@@ -5649,11 +5649,11 @@
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B37" s="1" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C37" s="1" t="n">
         <v>15</v>
@@ -5662,13 +5662,13 @@
         <v>14</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F37" s="1" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="H37" s="1" t="n">
         <v>2</v>
@@ -5677,52 +5677,52 @@
         <v>3</v>
       </c>
       <c r="J37" s="1" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K37" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L37" s="1" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="M37" s="1" t="n">
         <v>20</v>
       </c>
       <c r="N37" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="O37" s="1" t="n">
         <v>27</v>
       </c>
       <c r="P37" s="1" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="Q37" s="1" t="n">
         <v>25</v>
       </c>
       <c r="R37" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="S37" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="T37" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="U37" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="V37" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="W37" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="X37" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="T37" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="U37" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="V37" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="W37" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="X37" s="1" t="n">
-        <v>11</v>
-      </c>
       <c r="Y37" s="1" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Z37" s="1" t="n">
         <v>9</v>
@@ -5737,14 +5737,14 @@
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B38" s="1" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D38" s="1" t="n">
         <v>14</v>
@@ -5756,7 +5756,7 @@
         <v>5</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="H38" s="1" t="n">
         <v>2</v>
@@ -5765,143 +5765,143 @@
         <v>3</v>
       </c>
       <c r="J38" s="1" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="K38" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L38" s="1" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="M38" s="1" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="N38" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O38" s="1" t="n">
         <v>27</v>
       </c>
       <c r="P38" s="1" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="Q38" s="1" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="R38" s="1" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="S38" s="1" t="n">
         <v>10</v>
       </c>
       <c r="T38" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="U38" s="1" t="n">
         <v>4</v>
       </c>
       <c r="V38" s="1" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="W38" s="1" t="n">
         <v>6</v>
       </c>
       <c r="X38" s="1" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="Y38" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z38" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="Z38" s="1" t="n">
+      <c r="AA38" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="AB38" s="1" t="n">
         <v>9</v>
-      </c>
-      <c r="AA38" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="AB38" s="1" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B39" s="1" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D39" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F39" s="1" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G39" s="1" t="n">
         <v>24</v>
       </c>
       <c r="H39" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I39" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="J39" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="K39" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="I39" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="J39" s="1" t="n">
+      <c r="L39" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="M39" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="N39" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="O39" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="P39" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="Q39" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="R39" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="S39" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="T39" s="1" t="n">
         <v>21</v>
-      </c>
-      <c r="K39" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="L39" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="M39" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="N39" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="O39" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="P39" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q39" s="1" t="n">
-        <v>23</v>
-      </c>
-      <c r="R39" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="S39" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="T39" s="1" t="n">
-        <v>22</v>
       </c>
       <c r="U39" s="1" t="n">
         <v>4</v>
       </c>
       <c r="V39" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="W39" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="X39" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="W39" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="X39" s="1" t="n">
-        <v>14</v>
-      </c>
       <c r="Y39" s="1" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Z39" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA39" s="1" t="n">
         <v>19</v>
@@ -5913,126 +5913,126 @@
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B40" s="1" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C40" s="1" t="n">
         <v>16</v>
       </c>
       <c r="D40" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F40" s="1" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="G40" s="1" t="n">
         <v>24</v>
       </c>
       <c r="H40" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I40" s="1" t="n">
         <v>3</v>
       </c>
       <c r="J40" s="1" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K40" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L40" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M40" s="1" t="n">
         <v>18</v>
       </c>
       <c r="N40" s="1" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="O40" s="1" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P40" s="1" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="Q40" s="1" t="n">
         <v>23</v>
       </c>
       <c r="R40" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="S40" s="1" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T40" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="U40" s="1" t="n">
         <v>4</v>
       </c>
       <c r="V40" s="1" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="W40" s="1" t="n">
         <v>6</v>
       </c>
       <c r="X40" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="Y40" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z40" s="1" t="n">
         <v>9</v>
       </c>
       <c r="AA40" s="1" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AB40" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B41" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="C41" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="D41" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="E41" s="1" t="n">
         <v>27</v>
       </c>
-      <c r="C41" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="D41" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="E41" s="1" t="n">
-        <v>25</v>
-      </c>
       <c r="F41" s="1" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H41" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I41" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="I41" s="1" t="n">
+      <c r="J41" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="K41" s="1" t="n">
         <v>3</v>
-      </c>
-      <c r="J41" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="K41" s="1" t="n">
-        <v>1</v>
       </c>
       <c r="L41" s="1" t="n">
         <v>16</v>
@@ -6047,83 +6047,83 @@
         <v>26</v>
       </c>
       <c r="P41" s="1" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q41" s="1" t="n">
         <v>23</v>
       </c>
       <c r="R41" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="S41" s="1" t="n">
         <v>5</v>
       </c>
       <c r="T41" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="U41" s="1" t="n">
         <v>4</v>
       </c>
       <c r="V41" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="W41" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="X41" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="W41" s="1" t="n">
+      <c r="Y41" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="X41" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="Y41" s="1" t="n">
+      <c r="Z41" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA41" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="AB41" s="1" t="n">
         <v>8</v>
-      </c>
-      <c r="Z41" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="AA41" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="AB41" s="1" t="n">
-        <v>10</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B42" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D42" s="1" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E42" s="1" t="n">
         <v>25</v>
       </c>
       <c r="F42" s="1" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H42" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I42" s="1" t="n">
         <v>3</v>
       </c>
       <c r="J42" s="1" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="K42" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L42" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M42" s="1" t="n">
         <v>18</v>
@@ -6135,49 +6135,49 @@
         <v>26</v>
       </c>
       <c r="P42" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Q42" s="1" t="n">
         <v>23</v>
       </c>
       <c r="R42" s="1" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="S42" s="1" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T42" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="U42" s="1" t="n">
         <v>4</v>
       </c>
       <c r="V42" s="1" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="W42" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="X42" s="1" t="n">
         <v>17</v>
       </c>
       <c r="Y42" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z42" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="Z42" s="1" t="n">
-        <v>10</v>
-      </c>
       <c r="AA42" s="1" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AB42" s="1" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B43" s="1" t="n">
@@ -6187,16 +6187,16 @@
         <v>13</v>
       </c>
       <c r="D43" s="1" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E43" s="1" t="n">
         <v>25</v>
       </c>
       <c r="F43" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H43" s="1" t="n">
         <v>2</v>
@@ -6214,46 +6214,46 @@
         <v>16</v>
       </c>
       <c r="M43" s="1" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N43" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="O43" s="1" t="n">
         <v>26</v>
       </c>
       <c r="P43" s="1" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="Q43" s="1" t="n">
         <v>23</v>
       </c>
       <c r="R43" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="S43" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="T43" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="U43" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="V43" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="W43" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="X43" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y43" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z43" s="1" t="n">
         <v>9</v>
-      </c>
-      <c r="S43" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="T43" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="U43" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="V43" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="W43" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="X43" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="Y43" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="Z43" s="1" t="n">
-        <v>7</v>
       </c>
       <c r="AA43" s="1" t="n">
         <v>20</v>
@@ -6265,26 +6265,26 @@
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B44" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D44" s="1" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E44" s="1" t="n">
         <v>25</v>
       </c>
       <c r="F44" s="1" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H44" s="1" t="n">
         <v>2</v>
@@ -6293,86 +6293,86 @@
         <v>3</v>
       </c>
       <c r="J44" s="1" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K44" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L44" s="1" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="M44" s="1" t="n">
         <v>18</v>
       </c>
       <c r="N44" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O44" s="1" t="n">
         <v>26</v>
       </c>
       <c r="P44" s="1" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="Q44" s="1" t="n">
         <v>23</v>
       </c>
       <c r="R44" s="1" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="S44" s="1" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="T44" s="1" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="U44" s="1" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="V44" s="1" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="W44" s="1" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="X44" s="1" t="n">
         <v>17</v>
       </c>
       <c r="Y44" s="1" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="Z44" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA44" s="1" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AB44" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B45" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C45" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="D45" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="E45" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="F45" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="D45" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="E45" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="F45" s="1" t="n">
+      <c r="G45" s="1" t="n">
         <v>21</v>
-      </c>
-      <c r="G45" s="1" t="n">
-        <v>20</v>
       </c>
       <c r="H45" s="1" t="n">
         <v>2</v>
@@ -6381,25 +6381,25 @@
         <v>3</v>
       </c>
       <c r="J45" s="1" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="K45" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L45" s="1" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="M45" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N45" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="O45" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="P45" s="1" t="n">
         <v>15</v>
-      </c>
-      <c r="O45" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="P45" s="1" t="n">
-        <v>13</v>
       </c>
       <c r="Q45" s="1" t="n">
         <v>23</v>
@@ -6408,13 +6408,13 @@
         <v>9</v>
       </c>
       <c r="S45" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="T45" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="U45" s="1" t="n">
         <v>6</v>
-      </c>
-      <c r="T45" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="U45" s="1" t="n">
-        <v>8</v>
       </c>
       <c r="V45" s="1" t="n">
         <v>12</v>
@@ -6423,7 +6423,7 @@
         <v>4</v>
       </c>
       <c r="X45" s="1" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="Y45" s="1" t="n">
         <v>5</v>
@@ -6432,7 +6432,7 @@
         <v>7</v>
       </c>
       <c r="AA45" s="1" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AB45" s="1" t="n">
         <v>10</v>
@@ -6441,7 +6441,7 @@
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B46" s="1" t="n">
@@ -6451,16 +6451,16 @@
         <v>16</v>
       </c>
       <c r="D46" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F46" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="G46" s="1" t="n">
         <v>20</v>
-      </c>
-      <c r="G46" s="1" t="n">
-        <v>22</v>
       </c>
       <c r="H46" s="1" t="n">
         <v>2</v>
@@ -6469,22 +6469,22 @@
         <v>3</v>
       </c>
       <c r="J46" s="1" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="K46" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L46" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="M46" s="1" t="n">
         <v>18</v>
       </c>
       <c r="N46" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="O46" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P46" s="1" t="n">
         <v>12</v>
@@ -6502,22 +6502,22 @@
         <v>24</v>
       </c>
       <c r="U46" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V46" s="1" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="W46" s="1" t="n">
         <v>4</v>
       </c>
       <c r="X46" s="1" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Y46" s="1" t="n">
         <v>5</v>
       </c>
       <c r="Z46" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA46" s="1" t="n">
         <v>21</v>
@@ -6529,23 +6529,23 @@
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B47" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C47" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="D47" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="D47" s="1" t="n">
-        <v>12</v>
-      </c>
       <c r="E47" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F47" s="1" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G47" s="1" t="n">
         <v>20</v>
@@ -6566,22 +6566,22 @@
         <v>11</v>
       </c>
       <c r="M47" s="1" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N47" s="1" t="n">
         <v>15</v>
       </c>
       <c r="O47" s="1" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P47" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Q47" s="1" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="R47" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="S47" s="1" t="n">
         <v>6</v>
@@ -6593,13 +6593,13 @@
         <v>8</v>
       </c>
       <c r="V47" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="W47" s="1" t="n">
         <v>4</v>
       </c>
       <c r="X47" s="1" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="Y47" s="1" t="n">
         <v>5</v>
@@ -6611,23 +6611,23 @@
         <v>22</v>
       </c>
       <c r="AB47" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B48" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D48" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E48" s="1" t="n">
         <v>26</v>
@@ -6636,43 +6636,43 @@
         <v>20</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="H48" s="1" t="n">
         <v>2</v>
       </c>
       <c r="I48" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J48" s="1" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K48" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L48" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="M48" s="1" t="n">
         <v>18</v>
       </c>
       <c r="N48" s="1" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="O48" s="1" t="n">
         <v>25</v>
       </c>
       <c r="P48" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Q48" s="1" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="R48" s="1" t="n">
         <v>9</v>
       </c>
       <c r="S48" s="1" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T48" s="1" t="n">
         <v>24</v>
@@ -6681,22 +6681,22 @@
         <v>8</v>
       </c>
       <c r="V48" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="W48" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="X48" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y48" s="1" t="n">
         <v>5</v>
-      </c>
-      <c r="X48" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="Y48" s="1" t="n">
-        <v>6</v>
       </c>
       <c r="Z48" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AA48" s="1" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AB48" s="1" t="n">
         <v>10</v>
@@ -6705,29 +6705,29 @@
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B49" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D49" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F49" s="1" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G49" s="1" t="n">
         <v>20</v>
       </c>
       <c r="H49" s="1" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I49" s="1" t="n">
         <v>3</v>
@@ -6742,16 +6742,16 @@
         <v>11</v>
       </c>
       <c r="M49" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N49" s="1" t="n">
         <v>15</v>
       </c>
       <c r="O49" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P49" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="Q49" s="1" t="n">
         <v>21</v>
@@ -6760,13 +6760,13 @@
         <v>10</v>
       </c>
       <c r="S49" s="1" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="T49" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="U49" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V49" s="1" t="n">
         <v>13</v>
@@ -6775,7 +6775,7 @@
         <v>4</v>
       </c>
       <c r="X49" s="1" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Y49" s="1" t="n">
         <v>5</v>
@@ -6787,68 +6787,68 @@
         <v>22</v>
       </c>
       <c r="AB49" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B50" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D50" s="1" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E50" s="1" t="n">
         <v>26</v>
       </c>
       <c r="F50" s="1" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H50" s="1" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I50" s="1" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J50" s="1" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="K50" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L50" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M50" s="1" t="n">
         <v>18</v>
       </c>
       <c r="N50" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O50" s="1" t="n">
         <v>25</v>
       </c>
       <c r="P50" s="1" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="Q50" s="1" t="n">
         <v>22</v>
       </c>
       <c r="R50" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="S50" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T50" s="1" t="n">
         <v>24</v>
@@ -6857,47 +6857,47 @@
         <v>8</v>
       </c>
       <c r="V50" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="W50" s="1" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="X50" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y50" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z50" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA50" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="Y50" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="Z50" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA50" s="1" t="n">
-        <v>21</v>
-      </c>
       <c r="AB50" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B51" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D51" s="1" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E51" s="1" t="n">
         <v>26</v>
       </c>
       <c r="F51" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G51" s="1" t="n">
         <v>20</v>
@@ -6909,31 +6909,31 @@
         <v>3</v>
       </c>
       <c r="J51" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K51" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L51" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="M51" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="N51" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="O51" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="P51" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q51" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="R51" s="1" t="n">
         <v>10</v>
-      </c>
-      <c r="M51" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="N51" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="O51" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="P51" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="Q51" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="R51" s="1" t="n">
-        <v>12</v>
       </c>
       <c r="S51" s="1" t="n">
         <v>2</v>
@@ -6942,7 +6942,7 @@
         <v>23</v>
       </c>
       <c r="U51" s="1" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="V51" s="1" t="n">
         <v>13</v>
@@ -6951,68 +6951,68 @@
         <v>4</v>
       </c>
       <c r="X51" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Y51" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z51" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA51" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="AB51" s="1" t="n">
         <v>8</v>
-      </c>
-      <c r="Z51" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA51" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="AB51" s="1" t="n">
-        <v>9</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B52" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C52" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="D52" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="E52" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="F52" s="1" t="n">
         <v>13</v>
-      </c>
-      <c r="D52" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="E52" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="F52" s="1" t="n">
-        <v>16</v>
       </c>
       <c r="G52" s="1" t="n">
         <v>20</v>
       </c>
       <c r="H52" s="1" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I52" s="1" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="J52" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K52" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L52" s="1" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="M52" s="1" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N52" s="1" t="n">
         <v>15</v>
       </c>
       <c r="O52" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="P52" s="1" t="n">
         <v>17</v>
@@ -7021,77 +7021,77 @@
         <v>22</v>
       </c>
       <c r="R52" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="S52" s="1" t="n">
         <v>2</v>
       </c>
       <c r="T52" s="1" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="U52" s="1" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V52" s="1" t="n">
         <v>14</v>
       </c>
       <c r="W52" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="X52" s="1" t="n">
         <v>23</v>
       </c>
       <c r="Y52" s="1" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Z52" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AA52" s="1" t="n">
         <v>21</v>
       </c>
       <c r="AB52" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B53" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C53" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="D53" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="D53" s="1" t="n">
-        <v>10</v>
-      </c>
       <c r="E53" s="1" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F53" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G53" s="1" t="n">
         <v>20</v>
       </c>
       <c r="H53" s="1" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="I53" s="1" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="J53" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K53" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L53" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M53" s="1" t="n">
         <v>19</v>
@@ -7100,37 +7100,37 @@
         <v>16</v>
       </c>
       <c r="O53" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P53" s="1" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Q53" s="1" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="R53" s="1" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="S53" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T53" s="1" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="U53" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V53" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="W53" s="1" t="n">
         <v>4</v>
       </c>
       <c r="X53" s="1" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Y53" s="1" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z53" s="1" t="n">
         <v>5</v>
@@ -7139,44 +7139,44 @@
         <v>21</v>
       </c>
       <c r="AB53" s="1" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B54" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D54" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F54" s="1" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G54" s="1" t="n">
         <v>20</v>
       </c>
       <c r="H54" s="1" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="I54" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J54" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K54" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L54" s="1" t="n">
         <v>8</v>
@@ -7185,177 +7185,177 @@
         <v>19</v>
       </c>
       <c r="N54" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="O54" s="1" t="n">
         <v>24</v>
       </c>
       <c r="P54" s="1" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="Q54" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="R54" s="1" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="S54" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T54" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="U54" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V54" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="W54" s="1" t="n">
         <v>4</v>
       </c>
       <c r="X54" s="1" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="Y54" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z54" s="1" t="n">
         <v>5</v>
       </c>
       <c r="AA54" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AB54" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B55" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D55" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F55" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="G55" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="H55" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="I55" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="J55" s="1" t="n">
         <v>18</v>
-      </c>
-      <c r="G55" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="H55" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="I55" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="J55" s="1" t="n">
-        <v>11</v>
       </c>
       <c r="K55" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L55" s="1" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="M55" s="1" t="n">
         <v>19</v>
       </c>
       <c r="N55" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O55" s="1" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="P55" s="1" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="Q55" s="1" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="R55" s="1" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="S55" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T55" s="1" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="U55" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V55" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="W55" s="1" t="n">
         <v>4</v>
       </c>
       <c r="X55" s="1" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="Y55" s="1" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Z55" s="1" t="n">
         <v>5</v>
       </c>
       <c r="AA55" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AB55" s="1" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B56" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D56" s="1" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F56" s="1" t="n">
         <v>18</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H56" s="1" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="I56" s="1" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="J56" s="1" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="K56" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L56" s="1" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="M56" s="1" t="n">
         <v>19</v>
@@ -7364,213 +7364,213 @@
         <v>17</v>
       </c>
       <c r="O56" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P56" s="1" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="Q56" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R56" s="1" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="S56" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T56" s="1" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="U56" s="1" t="n">
         <v>7</v>
       </c>
       <c r="V56" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="W56" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X56" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Y56" s="1" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="Z56" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA56" s="1" t="n">
         <v>22</v>
       </c>
       <c r="AB56" s="1" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B57" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D57" s="1" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F57" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G57" s="1" t="n">
         <v>21</v>
       </c>
       <c r="H57" s="1" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="I57" s="1" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="J57" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K57" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L57" s="1" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="M57" s="1" t="n">
         <v>19</v>
       </c>
       <c r="N57" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O57" s="1" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="P57" s="1" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="Q57" s="1" t="n">
         <v>20</v>
       </c>
       <c r="R57" s="1" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="S57" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T57" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="U57" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="V57" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="W57" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="X57" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="U57" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="V57" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="W57" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="X57" s="1" t="n">
-        <v>23</v>
-      </c>
       <c r="Y57" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Z57" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA57" s="1" t="n">
         <v>22</v>
       </c>
       <c r="AB57" s="1" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B58" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D58" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="E58" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="F58" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="G58" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="H58" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="I58" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="J58" s="1" t="n">
         <v>8</v>
-      </c>
-      <c r="E58" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="F58" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="G58" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="H58" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="I58" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="J58" s="1" t="n">
-        <v>17</v>
       </c>
       <c r="K58" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L58" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M58" s="1" t="n">
         <v>19</v>
       </c>
       <c r="N58" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O58" s="1" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="P58" s="1" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="Q58" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="R58" s="1" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="S58" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T58" s="1" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="U58" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V58" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="W58" s="1" t="n">
         <v>3</v>
       </c>
       <c r="X58" s="1" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Y58" s="1" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="Z58" s="1" t="n">
         <v>4</v>
@@ -7585,147 +7585,147 @@
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B59" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C59" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="D59" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="E59" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="F59" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="D59" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="E59" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="F59" s="1" t="n">
-        <v>19</v>
-      </c>
       <c r="G59" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H59" s="1" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="I59" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="J59" s="1" t="n">
         <v>10</v>
-      </c>
-      <c r="J59" s="1" t="n">
-        <v>13</v>
       </c>
       <c r="K59" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L59" s="1" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="M59" s="1" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="N59" s="1" t="n">
         <v>18</v>
       </c>
       <c r="O59" s="1" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="P59" s="1" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="Q59" s="1" t="n">
         <v>20</v>
       </c>
       <c r="R59" s="1" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="S59" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T59" s="1" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="U59" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V59" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="W59" s="1" t="n">
         <v>3</v>
       </c>
       <c r="X59" s="1" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="Y59" s="1" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="Z59" s="1" t="n">
         <v>4</v>
       </c>
       <c r="AA59" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AB59" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B60" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D60" s="1" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E60" s="1" t="n">
         <v>25</v>
       </c>
       <c r="F60" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="G60" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="G60" s="1" t="n">
-        <v>21</v>
-      </c>
       <c r="H60" s="1" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="I60" s="1" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J60" s="1" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="K60" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L60" s="1" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="M60" s="1" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="N60" s="1" t="n">
         <v>18</v>
       </c>
       <c r="O60" s="1" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="P60" s="1" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="Q60" s="1" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="R60" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S60" s="1" t="n">
         <v>1</v>
@@ -7734,47 +7734,47 @@
         <v>24</v>
       </c>
       <c r="U60" s="1" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="V60" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="W60" s="1" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="X60" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y60" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z60" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA60" s="1" t="n">
         <v>22</v>
       </c>
-      <c r="Y60" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z60" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="AA60" s="1" t="n">
-        <v>26</v>
-      </c>
       <c r="AB60" s="1" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B61" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D61" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F61" s="1" t="n">
         <v>19</v>
@@ -7783,37 +7783,37 @@
         <v>22</v>
       </c>
       <c r="H61" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="I61" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="J61" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="K61" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="L61" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="M61" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="N61" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="O61" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="P61" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q61" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="R61" s="1" t="n">
         <v>11</v>
-      </c>
-      <c r="I61" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="J61" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="K61" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="L61" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="M61" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="N61" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="O61" s="1" t="n">
-        <v>23</v>
-      </c>
-      <c r="P61" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q61" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="R61" s="1" t="n">
-        <v>10</v>
       </c>
       <c r="S61" s="1" t="n">
         <v>1</v>
@@ -7822,25 +7822,25 @@
         <v>26</v>
       </c>
       <c r="U61" s="1" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="V61" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="W61" s="1" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="X61" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Y61" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z61" s="1" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AA61" s="1" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AB61" s="1" t="n">
         <v>6</v>
@@ -7849,126 +7849,126 @@
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B62" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C62" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="D62" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="E62" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="F62" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="D62" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="E62" s="1" t="n">
+      <c r="G62" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="H62" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="I62" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="J62" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="K62" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="L62" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="M62" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="N62" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="O62" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="F62" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="G62" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="H62" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="I62" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="J62" s="1" t="n">
+      <c r="P62" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="K62" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="L62" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="M62" s="1" t="n">
+      <c r="Q62" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="N62" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="O62" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="P62" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q62" s="1" t="n">
-        <v>19</v>
-      </c>
       <c r="R62" s="1" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="S62" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T62" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="U62" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="V62" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="W62" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="X62" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y62" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z62" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA62" s="1" t="n">
         <v>26</v>
       </c>
-      <c r="U62" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="V62" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="W62" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="X62" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="Y62" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="Z62" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="AA62" s="1" t="n">
-        <v>25</v>
-      </c>
       <c r="AB62" s="1" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B63" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D63" s="1" t="n">
         <v>15</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F63" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="G63" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="H63" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="G63" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="H63" s="1" t="n">
-        <v>21</v>
-      </c>
       <c r="I63" s="1" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="J63" s="1" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="K63" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L63" s="1" t="n">
         <v>14</v>
@@ -7977,16 +7977,16 @@
         <v>16</v>
       </c>
       <c r="N63" s="1" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="O63" s="1" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="P63" s="1" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Q63" s="1" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="R63" s="1" t="n">
         <v>10</v>
@@ -7998,25 +7998,25 @@
         <v>26</v>
       </c>
       <c r="U63" s="1" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="V63" s="1" t="n">
         <v>12</v>
       </c>
       <c r="W63" s="1" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="X63" s="1" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="Y63" s="1" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Z63" s="1" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AA63" s="1" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AB63" s="1" t="n">
         <v>6</v>
@@ -8025,59 +8025,59 @@
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B64" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D64" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="E64" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="F64" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="G64" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="H64" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="I64" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="E64" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="F64" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="G64" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="H64" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="I64" s="1" t="n">
-        <v>21</v>
-      </c>
       <c r="J64" s="1" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K64" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L64" s="1" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="M64" s="1" t="n">
         <v>17</v>
       </c>
       <c r="N64" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="O64" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="P64" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q64" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="R64" s="1" t="n">
         <v>10</v>
-      </c>
-      <c r="O64" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="P64" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q64" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="R64" s="1" t="n">
-        <v>8</v>
       </c>
       <c r="S64" s="1" t="n">
         <v>1</v>
@@ -8089,22 +8089,22 @@
         <v>7</v>
       </c>
       <c r="V64" s="1" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="W64" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X64" s="1" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="Y64" s="1" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Z64" s="1" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AA64" s="1" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AB64" s="1" t="n">
         <v>5</v>
@@ -8113,41 +8113,41 @@
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B65" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C65" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="D65" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="E65" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="F65" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="G65" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="H65" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="D65" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="E65" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="F65" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="G65" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="H65" s="1" t="n">
+      <c r="I65" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="I65" s="1" t="n">
-        <v>19</v>
-      </c>
       <c r="J65" s="1" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K65" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L65" s="1" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="M65" s="1" t="n">
         <v>16</v>
@@ -8156,219 +8156,219 @@
         <v>13</v>
       </c>
       <c r="O65" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="P65" s="1" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="Q65" s="1" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="R65" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="S65" s="1" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T65" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="U65" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V65" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="W65" s="1" t="n">
         <v>3</v>
       </c>
       <c r="X65" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Y65" s="1" t="n">
         <v>4</v>
       </c>
       <c r="Z65" s="1" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AA65" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AB65" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B66" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D66" s="1" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F66" s="1" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G66" s="1" t="n">
         <v>22</v>
       </c>
       <c r="H66" s="1" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="I66" s="1" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="J66" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="K66" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="L66" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="M66" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="N66" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="O66" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="P66" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q66" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="R66" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="S66" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="K66" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="L66" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="M66" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="N66" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="O66" s="1" t="n">
-        <v>23</v>
-      </c>
-      <c r="P66" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q66" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="R66" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="S66" s="1" t="n">
-        <v>3</v>
-      </c>
       <c r="T66" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="U66" s="1" t="n">
         <v>7</v>
       </c>
       <c r="V66" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="W66" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="X66" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y66" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z66" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="W66" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="X66" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="Y66" s="1" t="n">
+      <c r="AA66" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="AB66" s="1" t="n">
         <v>5</v>
-      </c>
-      <c r="Z66" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="AA66" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="AB66" s="1" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B67" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D67" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F67" s="1" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G67" s="1" t="n">
         <v>22</v>
       </c>
       <c r="H67" s="1" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="I67" s="1" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="J67" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="K67" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="K67" s="1" t="n">
-        <v>6</v>
-      </c>
       <c r="L67" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="M67" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="M67" s="1" t="n">
-        <v>18</v>
-      </c>
       <c r="N67" s="1" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="O67" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P67" s="1" t="n">
         <v>2</v>
       </c>
       <c r="Q67" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R67" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="S67" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="T67" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="U67" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="V67" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="W67" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="X67" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y67" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="T67" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="U67" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="V67" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="W67" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="X67" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="Y67" s="1" t="n">
-        <v>9</v>
-      </c>
       <c r="Z67" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AA67" s="1" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AB67" s="1" t="n">
         <v>8</v>

--- a/NSE_Sector_Monitor.xlsx
+++ b/NSE_Sector_Monitor.xlsx
@@ -571,19 +571,19 @@
         <v>3</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>14.45</v>
+        <v>14.46</v>
       </c>
       <c r="H2" s="1" t="n">
-        <v>-2.82</v>
+        <v>-2.76</v>
       </c>
       <c r="I2" s="1" t="n">
-        <v>1.74</v>
+        <v>0.71</v>
       </c>
       <c r="J2" s="1" t="n">
-        <v>5.57</v>
+        <v>5.93</v>
       </c>
       <c r="K2" s="1" t="n">
-        <v>20</v>
+        <v>18.65</v>
       </c>
       <c r="L2" s="1" t="inlineStr">
         <is>
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="M2" s="1" t="n">
-        <v>-1.14</v>
+        <v>-2.99</v>
       </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
@@ -627,28 +627,28 @@
         <v>2</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>18</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>26.94</v>
+        <v>26.95</v>
       </c>
       <c r="H3" s="1" t="n">
-        <v>-1.28</v>
+        <v>0.04</v>
       </c>
       <c r="I3" s="1" t="n">
-        <v>0.12</v>
+        <v>-0.14</v>
       </c>
       <c r="J3" s="1" t="n">
-        <v>3.91</v>
+        <v>3.29</v>
       </c>
       <c r="K3" s="1" t="n">
-        <v>11.14</v>
+        <v>11.68</v>
       </c>
       <c r="L3" s="1" t="inlineStr">
         <is>
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="M3" s="1" t="n">
-        <v>0</v>
+        <v>-0.21</v>
       </c>
       <c r="N3" s="1" t="inlineStr">
         <is>
@@ -692,28 +692,28 @@
         <v>0</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>88.19</v>
+        <v>87.97</v>
       </c>
       <c r="H4" s="1" t="n">
-        <v>-0.19</v>
+        <v>-0.44</v>
       </c>
       <c r="I4" s="1" t="n">
-        <v>1.1</v>
+        <v>1.36</v>
       </c>
       <c r="J4" s="1" t="n">
-        <v>1.77</v>
+        <v>2.14</v>
       </c>
       <c r="K4" s="1" t="n">
-        <v>10.81</v>
+        <v>9.51</v>
       </c>
       <c r="L4" s="1" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
         </is>
       </c>
       <c r="M4" s="1" t="n">
-        <v>-7.05</v>
+        <v>-7.51</v>
       </c>
       <c r="N4" s="1" t="inlineStr">
         <is>
@@ -760,25 +760,25 @@
         <v>1</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>16.84</v>
+        <v>16.77</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>-0.71</v>
+        <v>-1.12</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>1.29</v>
+        <v>0.22</v>
       </c>
       <c r="J5" s="1" t="n">
-        <v>3.91</v>
+        <v>3.07</v>
       </c>
       <c r="K5" s="1" t="n">
-        <v>8.57</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="L5" s="1" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="M5" s="1" t="n">
-        <v>0</v>
+        <v>-1.36</v>
       </c>
       <c r="N5" s="1" t="inlineStr">
         <is>
@@ -812,46 +812,46 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Realty</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
         <v>5</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>6</v>
+        <v>-3</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>14</v>
+        <v>-3</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>5</v>
+        <v>-4</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>22</v>
+        <v>-3</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>32.87</v>
+        <v>83.01000000000001</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>2.18</v>
+        <v>-2.58</v>
       </c>
       <c r="I6" s="1" t="n">
-        <v>1.56</v>
+        <v>-3.76</v>
       </c>
       <c r="J6" s="1" t="n">
-        <v>0.64</v>
+        <v>-4.37</v>
       </c>
       <c r="K6" s="1" t="n">
-        <v>6.02</v>
+        <v>5.02</v>
       </c>
       <c r="L6" s="1" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Down</t>
         </is>
       </c>
       <c r="M6" s="1" t="n">
-        <v>-21.5</v>
+        <v>-9.630000000000001</v>
       </c>
       <c r="N6" s="1" t="inlineStr">
         <is>
@@ -870,53 +870,53 @@
       </c>
       <c r="Q6" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>EV &amp; New Age Auto</t>
+          <t>Auto</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
         <v>6</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>-1</v>
+        <v>-4</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>31.48</v>
+        <v>279.35</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>-1.35</v>
+        <v>-1.24</v>
       </c>
       <c r="I7" s="1" t="n">
-        <v>0.4</v>
+        <v>-0.3</v>
       </c>
       <c r="J7" s="1" t="n">
-        <v>-3.45</v>
+        <v>-4.2</v>
       </c>
       <c r="K7" s="1" t="n">
-        <v>3.4</v>
+        <v>4.01</v>
       </c>
       <c r="L7" s="1" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Down</t>
         </is>
       </c>
       <c r="M7" s="1" t="n">
-        <v>-3.45</v>
+        <v>-4.37</v>
       </c>
       <c r="N7" s="1" t="inlineStr">
         <is>
@@ -942,46 +942,46 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Realty</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
         <v>7</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>-5</v>
+        <v>11</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>-5</v>
+        <v>6</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>-6</v>
+        <v>12</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-6</v>
+        <v>20</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>82.37</v>
+        <v>32.3</v>
       </c>
       <c r="H8" s="1" t="n">
-        <v>-3.33</v>
+        <v>0.4</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>-5.69</v>
+        <v>2.37</v>
       </c>
       <c r="J8" s="1" t="n">
-        <v>-5.57</v>
+        <v>0.2</v>
       </c>
       <c r="K8" s="1" t="n">
-        <v>3.35</v>
+        <v>3.85</v>
       </c>
       <c r="L8" s="1" t="inlineStr">
         <is>
-          <t>Down</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="M8" s="1" t="n">
-        <v>-10.11</v>
+        <v>-23.05</v>
       </c>
       <c r="N8" s="1" t="inlineStr">
         <is>
@@ -1007,38 +1007,38 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>Defence</t>
+          <t>EV &amp; New Age Auto</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
         <v>8</v>
       </c>
       <c r="C9" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E9" s="2" t="n">
         <v>-3</v>
-      </c>
-      <c r="D9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>1</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>-3</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>100.76</v>
+        <v>31.21</v>
       </c>
       <c r="H9" s="1" t="n">
-        <v>-5.59</v>
+        <v>-2.19</v>
       </c>
       <c r="I9" s="1" t="n">
-        <v>-5.6</v>
+        <v>-1.27</v>
       </c>
       <c r="J9" s="1" t="n">
-        <v>-2.39</v>
+        <v>-4.18</v>
       </c>
       <c r="K9" s="1" t="n">
-        <v>3</v>
+        <v>2.86</v>
       </c>
       <c r="L9" s="1" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="M9" s="1" t="n">
-        <v>-5.6</v>
+        <v>-4.51</v>
       </c>
       <c r="N9" s="1" t="inlineStr">
         <is>
@@ -1072,38 +1072,38 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>Consumption</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
         <v>9</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>-3</v>
+        <v>4</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>-3</v>
+        <v>5</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>-7</v>
+        <v>2</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>278.31</v>
+        <v>127.09</v>
       </c>
       <c r="H10" s="1" t="n">
-        <v>-1.61</v>
+        <v>0.52</v>
       </c>
       <c r="I10" s="1" t="n">
-        <v>-0.26</v>
+        <v>0.51</v>
       </c>
       <c r="J10" s="1" t="n">
-        <v>-3.74</v>
+        <v>-1.35</v>
       </c>
       <c r="K10" s="1" t="n">
-        <v>2.8</v>
+        <v>1.65</v>
       </c>
       <c r="L10" s="1" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="M10" s="1" t="n">
-        <v>-4.5</v>
+        <v>-5.14</v>
       </c>
       <c r="N10" s="1" t="inlineStr">
         <is>
@@ -1137,46 +1137,46 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>Consumption</t>
+          <t>Metal</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
         <v>10</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>3</v>
+        <v>-4</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>126.43</v>
+        <v>12.85</v>
       </c>
       <c r="H11" s="1" t="n">
-        <v>-1.2</v>
+        <v>-1.91</v>
       </c>
       <c r="I11" s="1" t="n">
-        <v>0.63</v>
+        <v>-2.58</v>
       </c>
       <c r="J11" s="1" t="n">
-        <v>-1.99</v>
+        <v>2.34</v>
       </c>
       <c r="K11" s="1" t="n">
-        <v>1.47</v>
+        <v>0.68</v>
       </c>
       <c r="L11" s="1" t="inlineStr">
         <is>
-          <t>Down</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="M11" s="1" t="n">
-        <v>-5.4</v>
+        <v>-5.99</v>
       </c>
       <c r="N11" s="1" t="inlineStr">
         <is>
@@ -1195,53 +1195,53 @@
       </c>
       <c r="Q11" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Tourism</t>
+          <t>Bank</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
         <v>11</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>-3</v>
+        <v>5</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>75.27</v>
+        <v>582.6799999999999</v>
       </c>
       <c r="H12" s="1" t="n">
-        <v>-2.06</v>
+        <v>-0.63</v>
       </c>
       <c r="I12" s="1" t="n">
-        <v>-0.15</v>
+        <v>1.34</v>
       </c>
       <c r="J12" s="1" t="n">
-        <v>-1.72</v>
+        <v>2.04</v>
       </c>
       <c r="K12" s="1" t="n">
-        <v>1.29</v>
+        <v>0.67</v>
       </c>
       <c r="L12" s="1" t="inlineStr">
         <is>
-          <t>Down</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="M12" s="1" t="n">
-        <v>-16.41</v>
+        <v>-4.42</v>
       </c>
       <c r="N12" s="1" t="inlineStr">
         <is>
@@ -1267,38 +1267,38 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Services</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
         <v>12</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D13" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E13" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="E13" s="2" t="n">
-        <v>4</v>
-      </c>
       <c r="F13" s="2" t="n">
-        <v>-6</v>
+        <v>11</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>29.24</v>
+        <v>30.11</v>
       </c>
       <c r="H13" s="1" t="n">
-        <v>-2.11</v>
+        <v>-0.73</v>
       </c>
       <c r="I13" s="1" t="n">
-        <v>-0.5</v>
+        <v>1.66</v>
       </c>
       <c r="J13" s="1" t="n">
-        <v>-0.28</v>
+        <v>0.99</v>
       </c>
       <c r="K13" s="1" t="n">
-        <v>0.83</v>
+        <v>0.63</v>
       </c>
       <c r="L13" s="1" t="inlineStr">
         <is>
@@ -1332,38 +1332,38 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Manufacturing</t>
+          <t>Fin Services</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
         <v>13</v>
       </c>
       <c r="C14" s="2" t="n">
+        <v>-5</v>
+      </c>
+      <c r="D14" s="2" t="n">
         <v>-1</v>
       </c>
-      <c r="D14" s="2" t="n">
-        <v>2</v>
-      </c>
       <c r="E14" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>158.97</v>
+        <v>31.61</v>
       </c>
       <c r="H14" s="1" t="n">
-        <v>-2.35</v>
+        <v>-2.44</v>
       </c>
       <c r="I14" s="1" t="n">
-        <v>-1.24</v>
+        <v>-0.34</v>
       </c>
       <c r="J14" s="1" t="n">
-        <v>-1.55</v>
+        <v>-0.61</v>
       </c>
       <c r="K14" s="1" t="n">
-        <v>0.77</v>
+        <v>0.62</v>
       </c>
       <c r="L14" s="1" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         </is>
       </c>
       <c r="M14" s="1" t="n">
-        <v>-1.76</v>
+        <v>-2.67</v>
       </c>
       <c r="N14" s="1" t="inlineStr">
         <is>
@@ -1390,14 +1390,14 @@
       </c>
       <c r="Q14" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>Fin Services</t>
+          <t>Tourism</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
@@ -1407,28 +1407,28 @@
         <v>-5</v>
       </c>
       <c r="D15" s="2" t="n">
+        <v>-6</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>-7</v>
+      </c>
+      <c r="F15" s="2" t="n">
         <v>-1</v>
       </c>
-      <c r="E15" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="F15" s="2" t="n">
-        <v>-4</v>
-      </c>
       <c r="G15" s="1" t="n">
-        <v>31.64</v>
+        <v>75.02</v>
       </c>
       <c r="H15" s="1" t="n">
-        <v>-2.35</v>
+        <v>-2.38</v>
       </c>
       <c r="I15" s="1" t="n">
-        <v>-0.11</v>
+        <v>-0.97</v>
       </c>
       <c r="J15" s="1" t="n">
-        <v>-0.24</v>
+        <v>-2.08</v>
       </c>
       <c r="K15" s="1" t="n">
-        <v>0.53</v>
+        <v>0.57</v>
       </c>
       <c r="L15" s="1" t="inlineStr">
         <is>
@@ -1436,7 +1436,7 @@
         </is>
       </c>
       <c r="M15" s="1" t="n">
-        <v>-1.62</v>
+        <v>-16.62</v>
       </c>
       <c r="N15" s="1" t="inlineStr">
         <is>
@@ -1462,46 +1462,46 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Metal</t>
+          <t>Manufacturing</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
         <v>15</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>5</v>
+        <v>-4</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>8</v>
+        <v>-3</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-8</v>
+        <v>0</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>12.77</v>
+        <v>159.39</v>
       </c>
       <c r="H16" s="1" t="n">
-        <v>-2.52</v>
+        <v>0.26</v>
       </c>
       <c r="I16" s="1" t="n">
-        <v>-0.93</v>
+        <v>-1.74</v>
       </c>
       <c r="J16" s="1" t="n">
-        <v>1.11</v>
+        <v>-1.72</v>
       </c>
       <c r="K16" s="1" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="L16" s="1" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Down</t>
         </is>
       </c>
       <c r="M16" s="1" t="n">
-        <v>-6.35</v>
+        <v>-1.74</v>
       </c>
       <c r="N16" s="1" t="inlineStr">
         <is>
@@ -1527,46 +1527,46 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>Bank</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
         <v>16</v>
       </c>
       <c r="C17" s="2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D17" s="2" t="n">
-        <v>-6</v>
-      </c>
-      <c r="E17" s="2" t="n">
-        <v>-5</v>
-      </c>
       <c r="F17" s="2" t="n">
-        <v>5</v>
+        <v>-9</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>579.33</v>
+        <v>28.97</v>
       </c>
       <c r="H17" s="1" t="n">
-        <v>-1.2</v>
+        <v>-3.01</v>
       </c>
       <c r="I17" s="1" t="n">
-        <v>1.09</v>
+        <v>-1.93</v>
       </c>
       <c r="J17" s="1" t="n">
-        <v>1.49</v>
+        <v>-1.25</v>
       </c>
       <c r="K17" s="1" t="n">
-        <v>0.36</v>
+        <v>0.38</v>
       </c>
       <c r="L17" s="1" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Down</t>
         </is>
       </c>
       <c r="M17" s="1" t="n">
-        <v>-4.74</v>
+        <v>0</v>
       </c>
       <c r="N17" s="1" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Private Bank</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
@@ -1602,28 +1602,28 @@
         <v>0</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>-1</v>
+        <v>-8</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>6</v>
+        <v>-5</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>30</v>
+        <v>27.8</v>
       </c>
       <c r="H18" s="1" t="n">
-        <v>-1.09</v>
+        <v>-0.5</v>
       </c>
       <c r="I18" s="1" t="n">
-        <v>1.28</v>
+        <v>1.57</v>
       </c>
       <c r="J18" s="1" t="n">
-        <v>0.48</v>
+        <v>4.02</v>
       </c>
       <c r="K18" s="1" t="n">
-        <v>0.34</v>
+        <v>0.36</v>
       </c>
       <c r="L18" s="1" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         </is>
       </c>
       <c r="M18" s="1" t="n">
-        <v>0</v>
+        <v>-2.68</v>
       </c>
       <c r="N18" s="1" t="inlineStr">
         <is>
@@ -1657,46 +1657,46 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>Private Bank</t>
+          <t>Defence</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
         <v>18</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>-3</v>
+        <v>-13</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="E19" s="2" t="n">
+        <v>-12</v>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>-17</v>
+      </c>
+      <c r="G19" s="1" t="n">
+        <v>100.52</v>
+      </c>
+      <c r="H19" s="1" t="n">
+        <v>-5.82</v>
+      </c>
+      <c r="I19" s="1" t="n">
+        <v>-5.92</v>
+      </c>
+      <c r="J19" s="1" t="n">
+        <v>-4.54</v>
+      </c>
+      <c r="K19" s="1" t="n">
         <v>-1</v>
       </c>
-      <c r="F19" s="2" t="n">
-        <v>-6</v>
-      </c>
-      <c r="G19" s="1" t="n">
-        <v>27.76</v>
-      </c>
-      <c r="H19" s="1" t="n">
-        <v>-0.64</v>
-      </c>
-      <c r="I19" s="1" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="J19" s="1" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="K19" s="1" t="n">
-        <v>0.11</v>
-      </c>
       <c r="L19" s="1" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Down</t>
         </is>
       </c>
       <c r="M19" s="1" t="n">
-        <v>-2.58</v>
+        <v>-6.05</v>
       </c>
       <c r="N19" s="1" t="inlineStr">
         <is>
@@ -1715,53 +1715,53 @@
       </c>
       <c r="Q19" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>MNC</t>
+          <t>Oil &amp; Gas</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
         <v>19</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>-6</v>
+        <v>3</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>-10</v>
+        <v>7</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>32.18</v>
+        <v>11.06</v>
       </c>
       <c r="H20" s="1" t="n">
-        <v>-1.62</v>
+        <v>-0.98</v>
       </c>
       <c r="I20" s="1" t="n">
-        <v>-0.09</v>
+        <v>0.26</v>
       </c>
       <c r="J20" s="1" t="n">
-        <v>-2.95</v>
+        <v>1.16</v>
       </c>
       <c r="K20" s="1" t="n">
-        <v>-0.71</v>
+        <v>-1.02</v>
       </c>
       <c r="L20" s="1" t="inlineStr">
         <is>
-          <t>Down</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="M20" s="1" t="n">
-        <v>-3.94</v>
+        <v>-8.460000000000001</v>
       </c>
       <c r="N20" s="1" t="inlineStr">
         <is>
@@ -1787,46 +1787,46 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas</t>
+          <t>MNC</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
         <v>20</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>2</v>
+        <v>-6</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>5</v>
+        <v>-12</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>11</v>
+        <v>32.09</v>
       </c>
       <c r="H21" s="1" t="n">
-        <v>-1.52</v>
+        <v>-1.9</v>
       </c>
       <c r="I21" s="1" t="n">
-        <v>0.87</v>
+        <v>-0.58</v>
       </c>
       <c r="J21" s="1" t="n">
-        <v>0.98</v>
+        <v>-3.1</v>
       </c>
       <c r="K21" s="1" t="n">
-        <v>-1.62</v>
+        <v>-1.64</v>
       </c>
       <c r="L21" s="1" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Down</t>
         </is>
       </c>
       <c r="M21" s="1" t="n">
-        <v>-8.73</v>
+        <v>-4.44</v>
       </c>
       <c r="N21" s="1" t="inlineStr">
         <is>
@@ -1859,31 +1859,31 @@
         <v>21</v>
       </c>
       <c r="C22" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D22" s="2" t="n">
         <v>4</v>
-      </c>
-      <c r="D22" s="2" t="n">
-        <v>3</v>
       </c>
       <c r="E22" s="2" t="n">
         <v>5</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>9.93</v>
+        <v>10</v>
       </c>
       <c r="H22" s="1" t="n">
-        <v>-1.78</v>
+        <v>-1.09</v>
       </c>
       <c r="I22" s="1" t="n">
-        <v>0.77</v>
+        <v>-0.01</v>
       </c>
       <c r="J22" s="1" t="n">
-        <v>1.27</v>
+        <v>2.03</v>
       </c>
       <c r="K22" s="1" t="n">
-        <v>-2.31</v>
+        <v>-2.23</v>
       </c>
       <c r="L22" s="1" t="inlineStr">
         <is>
@@ -1891,7 +1891,7 @@
         </is>
       </c>
       <c r="M22" s="1" t="n">
-        <v>-10.05</v>
+        <v>-9.630000000000001</v>
       </c>
       <c r="N22" s="1" t="inlineStr">
         <is>
@@ -1924,7 +1924,7 @@
         <v>22</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>-3</v>
+        <v>-7</v>
       </c>
       <c r="D23" s="2" t="n">
         <v>-2</v>
@@ -1936,19 +1936,19 @@
         <v>-19</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>52.85</v>
+        <v>52.57</v>
       </c>
       <c r="H23" s="1" t="n">
-        <v>-2.11</v>
+        <v>-2.63</v>
       </c>
       <c r="I23" s="1" t="n">
-        <v>-0.35</v>
+        <v>-0.79</v>
       </c>
       <c r="J23" s="1" t="n">
-        <v>3.37</v>
+        <v>2.63</v>
       </c>
       <c r="K23" s="1" t="n">
-        <v>-2.54</v>
+        <v>-2.25</v>
       </c>
       <c r="L23" s="1" t="inlineStr">
         <is>
@@ -1982,46 +1982,46 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>PSU Bank</t>
+          <t>Commodities</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
         <v>23</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>-9</v>
+        <v>3</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>-15</v>
+        <v>2</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>3</v>
+        <v>-5</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>91.25</v>
+        <v>96.56</v>
       </c>
       <c r="H24" s="1" t="n">
-        <v>-2.11</v>
+        <v>0.33</v>
       </c>
       <c r="I24" s="1" t="n">
-        <v>-0.18</v>
+        <v>-0.93</v>
       </c>
       <c r="J24" s="1" t="n">
-        <v>-2.04</v>
+        <v>0.76</v>
       </c>
       <c r="K24" s="1" t="n">
-        <v>-2.65</v>
+        <v>-2.99</v>
       </c>
       <c r="L24" s="1" t="inlineStr">
         <is>
-          <t>Down</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="M24" s="1" t="n">
-        <v>-13.84</v>
+        <v>-8.460000000000001</v>
       </c>
       <c r="N24" s="1" t="inlineStr">
         <is>
@@ -2047,46 +2047,46 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>PSU Bank</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
         <v>24</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>-2</v>
+        <v>-8</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>-3</v>
+        <v>-15</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>-8</v>
+        <v>0</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>91.91</v>
+        <v>92.20999999999999</v>
       </c>
       <c r="H25" s="1" t="n">
-        <v>-2.41</v>
+        <v>-1.08</v>
       </c>
       <c r="I25" s="1" t="n">
-        <v>-0.29</v>
+        <v>0.4</v>
       </c>
       <c r="J25" s="1" t="n">
-        <v>-0.61</v>
+        <v>-0.48</v>
       </c>
       <c r="K25" s="1" t="n">
-        <v>-3.14</v>
+        <v>-3.03</v>
       </c>
       <c r="L25" s="1" t="inlineStr">
         <is>
-          <t>Down</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="M25" s="1" t="n">
-        <v>-4.58</v>
+        <v>-13.15</v>
       </c>
       <c r="N25" s="1" t="inlineStr">
         <is>
@@ -2112,38 +2112,38 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>Commodities</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
         <v>25</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>-1</v>
+        <v>-3</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>-11</v>
+        <v>-8</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>96.23999999999999</v>
+        <v>91.87</v>
       </c>
       <c r="H26" s="1" t="n">
-        <v>-2.06</v>
+        <v>-0.04</v>
       </c>
       <c r="I26" s="1" t="n">
-        <v>0.26</v>
+        <v>-0.32</v>
       </c>
       <c r="J26" s="1" t="n">
-        <v>0.65</v>
+        <v>-0.86</v>
       </c>
       <c r="K26" s="1" t="n">
-        <v>-3.33</v>
+        <v>-3.36</v>
       </c>
       <c r="L26" s="1" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="M26" s="1" t="n">
-        <v>-8.539999999999999</v>
+        <v>-4.85</v>
       </c>
       <c r="N26" s="1" t="inlineStr">
         <is>
@@ -2184,7 +2184,7 @@
         <v>26</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="D27" s="2" t="n">
         <v>1</v>
@@ -2193,22 +2193,22 @@
         <v>-2</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>-24</v>
+        <v>-17</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>37.48</v>
+        <v>37.45</v>
       </c>
       <c r="H27" s="1" t="n">
-        <v>-1.52</v>
+        <v>-1.6</v>
       </c>
       <c r="I27" s="1" t="n">
-        <v>0.33</v>
+        <v>-1.4</v>
       </c>
       <c r="J27" s="1" t="n">
-        <v>1.06</v>
+        <v>0.6</v>
       </c>
       <c r="K27" s="1" t="n">
-        <v>-4.28</v>
+        <v>-4.64</v>
       </c>
       <c r="L27" s="1" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         <v>0</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="E28" s="2" t="n">
         <v>0</v>
@@ -2261,19 +2261,19 @@
         <v>-5</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>48.49</v>
+        <v>49.14</v>
       </c>
       <c r="H28" s="1" t="n">
-        <v>-0.23</v>
+        <v>1.34</v>
       </c>
       <c r="I28" s="1" t="n">
-        <v>1.09</v>
+        <v>2.42</v>
       </c>
       <c r="J28" s="1" t="n">
-        <v>-2.2</v>
+        <v>-0.31</v>
       </c>
       <c r="K28" s="1" t="n">
-        <v>-6.61</v>
+        <v>-4.91</v>
       </c>
       <c r="L28" s="1" t="inlineStr">
         <is>
@@ -2281,11 +2281,11 @@
         </is>
       </c>
       <c r="M28" s="1" t="n">
-        <v>-17.08</v>
+        <v>-15.56</v>
       </c>
       <c r="N28" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O28" s="1" t="inlineStr">
@@ -2569,23 +2569,23 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G2" s="1" t="n">
         <v>27</v>
@@ -2597,19 +2597,19 @@
         <v>4</v>
       </c>
       <c r="J2" s="1" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="K2" s="1" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L2" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M2" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="N2" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O2" s="1" t="n">
         <v>21</v>
@@ -2618,22 +2618,22 @@
         <v>26</v>
       </c>
       <c r="Q2" s="1" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="R2" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="S2" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="T2" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="S2" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="T2" s="1" t="n">
-        <v>20</v>
-      </c>
       <c r="U2" s="1" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="V2" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="W2" s="1" t="n">
         <v>22</v>
@@ -2645,35 +2645,35 @@
         <v>1</v>
       </c>
       <c r="Z2" s="1" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AA2" s="1" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="AB2" s="1" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G3" s="1" t="n">
         <v>27</v>
@@ -2682,49 +2682,49 @@
         <v>2</v>
       </c>
       <c r="I3" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="J3" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="K3" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="J3" s="1" t="n">
+      <c r="L3" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="M3" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="N3" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="O3" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="P3" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q3" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="R3" s="1" t="n">
         <v>17</v>
-      </c>
-      <c r="K3" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="L3" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="M3" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="N3" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="O3" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="P3" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="Q3" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="R3" s="1" t="n">
-        <v>20</v>
       </c>
       <c r="S3" s="1" t="n">
         <v>5</v>
       </c>
       <c r="T3" s="1" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="U3" s="1" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="V3" s="1" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="W3" s="1" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="X3" s="1" t="n">
         <v>3</v>
@@ -2733,62 +2733,62 @@
         <v>1</v>
       </c>
       <c r="Z3" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AA3" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AB3" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E4" s="1" t="n">
         <v>24</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G4" s="1" t="n">
         <v>27</v>
       </c>
       <c r="H4" s="1" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I4" s="1" t="n">
         <v>6</v>
       </c>
       <c r="J4" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K4" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L4" s="1" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="M4" s="1" t="n">
         <v>22</v>
       </c>
       <c r="N4" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O4" s="1" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="P4" s="1" t="n">
         <v>26</v>
@@ -2797,86 +2797,86 @@
         <v>25</v>
       </c>
       <c r="R4" s="1" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="S4" s="1" t="n">
         <v>5</v>
       </c>
       <c r="T4" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="U4" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="V4" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="V4" s="1" t="n">
-        <v>13</v>
-      </c>
       <c r="W4" s="1" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="X4" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y4" s="1" t="n">
         <v>1</v>
       </c>
       <c r="Z4" s="1" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AA4" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AB4" s="1" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D5" s="1" t="n">
         <v>21</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G5" s="1" t="n">
         <v>27</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J5" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K5" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L5" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M5" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N5" s="1" t="n">
         <v>12</v>
       </c>
       <c r="O5" s="1" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="P5" s="1" t="n">
         <v>26</v>
@@ -2885,110 +2885,110 @@
         <v>25</v>
       </c>
       <c r="R5" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="S5" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T5" s="1" t="n">
         <v>20</v>
       </c>
       <c r="U5" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="V5" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="V5" s="1" t="n">
-        <v>11</v>
-      </c>
       <c r="W5" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="X5" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y5" s="1" t="n">
         <v>1</v>
       </c>
       <c r="Z5" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA5" s="1" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AB5" s="1" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="C6" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="C6" s="1" t="n">
-        <v>16</v>
-      </c>
       <c r="D6" s="1" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G6" s="1" t="n">
         <v>27</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I6" s="1" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J6" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K6" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L6" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M6" s="1" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N6" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="O6" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="P6" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q6" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="R6" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="S6" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="T6" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="U6" s="1" t="n">
         <v>13</v>
-      </c>
-      <c r="O6" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="P6" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="Q6" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="R6" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="S6" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="T6" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="U6" s="1" t="n">
-        <v>14</v>
       </c>
       <c r="V6" s="1" t="n">
         <v>11</v>
       </c>
       <c r="W6" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="X6" s="1" t="n">
         <v>3</v>
@@ -2997,29 +2997,29 @@
         <v>1</v>
       </c>
       <c r="Z6" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA6" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="AB6" s="1" t="n">
         <v>9</v>
-      </c>
-      <c r="AA6" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="AB6" s="1" t="n">
-        <v>10</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="C7" s="1" t="n">
         <v>16</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E7" s="1" t="n">
         <v>23</v>
@@ -3037,46 +3037,46 @@
         <v>7</v>
       </c>
       <c r="J7" s="1" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="K7" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M7" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N7" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O7" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="P7" s="1" t="n">
         <v>25</v>
-      </c>
-      <c r="P7" s="1" t="n">
-        <v>26</v>
       </c>
       <c r="Q7" s="1" t="n">
         <v>24</v>
       </c>
       <c r="R7" s="1" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="S7" s="1" t="n">
         <v>5</v>
       </c>
       <c r="T7" s="1" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="U7" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="V7" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="W7" s="1" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="X7" s="1" t="n">
         <v>3</v>
@@ -3085,10 +3085,10 @@
         <v>1</v>
       </c>
       <c r="Z7" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA7" s="1" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AB7" s="1" t="n">
         <v>10</v>
@@ -3097,59 +3097,59 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>6</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H8" s="1" t="n">
         <v>4</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J8" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K8" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M8" s="1" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N8" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="O8" s="1" t="n">
         <v>25</v>
       </c>
       <c r="P8" s="1" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Q8" s="1" t="n">
         <v>24</v>
       </c>
       <c r="R8" s="1" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="S8" s="1" t="n">
         <v>5</v>
@@ -3161,10 +3161,10 @@
         <v>13</v>
       </c>
       <c r="V8" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="W8" s="1" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="X8" s="1" t="n">
         <v>3</v>
@@ -3173,35 +3173,35 @@
         <v>1</v>
       </c>
       <c r="Z8" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA8" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AB8" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="C9" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="C9" s="1" t="n">
-        <v>10</v>
-      </c>
       <c r="D9" s="1" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G9" s="1" t="n">
         <v>26</v>
@@ -3210,22 +3210,22 @@
         <v>4</v>
       </c>
       <c r="I9" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J9" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K9" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L9" s="1" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M9" s="1" t="n">
         <v>23</v>
       </c>
       <c r="N9" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O9" s="1" t="n">
         <v>25</v>
@@ -3237,22 +3237,22 @@
         <v>24</v>
       </c>
       <c r="R9" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="S9" s="1" t="n">
         <v>5</v>
       </c>
       <c r="T9" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="U9" s="1" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="V9" s="1" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="W9" s="1" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="X9" s="1" t="n">
         <v>3</v>
@@ -3264,32 +3264,32 @@
         <v>7</v>
       </c>
       <c r="AA9" s="1" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="AB9" s="1" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G10" s="1" t="n">
         <v>26</v>
@@ -3298,49 +3298,49 @@
         <v>4</v>
       </c>
       <c r="I10" s="1" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="J10" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K10" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L10" s="1" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="M10" s="1" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="N10" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O10" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="P10" s="1" t="n">
         <v>27</v>
       </c>
       <c r="Q10" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R10" s="1" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="S10" s="1" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T10" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="U10" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="V10" s="1" t="n">
         <v>18</v>
       </c>
       <c r="W10" s="1" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="X10" s="1" t="n">
         <v>3</v>
@@ -3349,19 +3349,19 @@
         <v>1</v>
       </c>
       <c r="Z10" s="1" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AA10" s="1" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AB10" s="1" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
@@ -3371,7 +3371,7 @@
         <v>11</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E11" s="1" t="n">
         <v>16</v>
@@ -3380,7 +3380,7 @@
         <v>6</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H11" s="1" t="n">
         <v>4</v>
@@ -3395,40 +3395,40 @@
         <v>2</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="M11" s="1" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="N11" s="1" t="n">
         <v>14</v>
       </c>
       <c r="O11" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P11" s="1" t="n">
         <v>27</v>
       </c>
       <c r="Q11" s="1" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="R11" s="1" t="n">
         <v>19</v>
       </c>
       <c r="S11" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T11" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="U11" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="V11" s="1" t="n">
         <v>18</v>
       </c>
       <c r="W11" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="X11" s="1" t="n">
         <v>3</v>
@@ -3437,10 +3437,10 @@
         <v>1</v>
       </c>
       <c r="Z11" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA11" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AB11" s="1" t="n">
         <v>7</v>
@@ -3449,29 +3449,29 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F12" s="1" t="n">
         <v>6</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H12" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I12" s="1" t="n">
         <v>5</v>
@@ -3483,16 +3483,16 @@
         <v>2</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M12" s="1" t="n">
         <v>22</v>
       </c>
       <c r="N12" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="O12" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="P12" s="1" t="n">
         <v>27</v>
@@ -3501,34 +3501,34 @@
         <v>26</v>
       </c>
       <c r="R12" s="1" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="S12" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T12" s="1" t="n">
         <v>21</v>
       </c>
       <c r="U12" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="V12" s="1" t="n">
         <v>18</v>
-      </c>
-      <c r="V12" s="1" t="n">
-        <v>15</v>
       </c>
       <c r="W12" s="1" t="n">
         <v>20</v>
       </c>
       <c r="X12" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y12" s="1" t="n">
         <v>1</v>
       </c>
       <c r="Z12" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA12" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AB12" s="1" t="n">
         <v>7</v>
@@ -3537,7 +3537,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
@@ -3547,22 +3547,22 @@
         <v>10</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F13" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="G13" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="H13" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="G13" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="H13" s="1" t="n">
+      <c r="I13" s="1" t="n">
         <v>5</v>
-      </c>
-      <c r="I13" s="1" t="n">
-        <v>6</v>
       </c>
       <c r="J13" s="1" t="n">
         <v>23</v>
@@ -3571,37 +3571,37 @@
         <v>2</v>
       </c>
       <c r="L13" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M13" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="N13" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="O13" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="P13" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q13" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="R13" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="S13" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="T13" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="N13" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="O13" s="1" t="n">
-        <v>27</v>
-      </c>
-      <c r="P13" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="Q13" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="R13" s="1" t="n">
+      <c r="U13" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="S13" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="T13" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="U13" s="1" t="n">
+      <c r="V13" s="1" t="n">
         <v>15</v>
-      </c>
-      <c r="V13" s="1" t="n">
-        <v>17</v>
       </c>
       <c r="W13" s="1" t="n">
         <v>20</v>
@@ -3613,7 +3613,7 @@
         <v>1</v>
       </c>
       <c r="Z13" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA13" s="1" t="n">
         <v>16</v>
@@ -3625,77 +3625,77 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D14" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="E14" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="E14" s="1" t="n">
-        <v>14</v>
-      </c>
       <c r="F14" s="1" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G14" s="1" t="n">
         <v>24</v>
       </c>
       <c r="H14" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I14" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J14" s="1" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="K14" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L14" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="M14" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="N14" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="O14" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="P14" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q14" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="R14" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="S14" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="T14" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="U14" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="V14" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="M14" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="N14" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="O14" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="P14" s="1" t="n">
-        <v>27</v>
-      </c>
-      <c r="Q14" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="R14" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="S14" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="T14" s="1" t="n">
-        <v>23</v>
-      </c>
-      <c r="U14" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="V14" s="1" t="n">
-        <v>16</v>
-      </c>
       <c r="W14" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="X14" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y14" s="1" t="n">
         <v>1</v>
@@ -3704,26 +3704,26 @@
         <v>8</v>
       </c>
       <c r="AA14" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AB14" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="C15" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="C15" s="1" t="n">
-        <v>10</v>
-      </c>
       <c r="D15" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E15" s="1" t="n">
         <v>14</v>
@@ -3741,34 +3741,34 @@
         <v>7</v>
       </c>
       <c r="J15" s="1" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K15" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L15" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M15" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N15" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="O15" s="1" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P15" s="1" t="n">
         <v>27</v>
       </c>
       <c r="Q15" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="R15" s="1" t="n">
         <v>19</v>
       </c>
       <c r="S15" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T15" s="1" t="n">
         <v>23</v>
@@ -3780,7 +3780,7 @@
         <v>16</v>
       </c>
       <c r="W15" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="X15" s="1" t="n">
         <v>3</v>
@@ -3789,47 +3789,47 @@
         <v>1</v>
       </c>
       <c r="Z15" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA15" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="AB15" s="1" t="n">
         <v>6</v>
-      </c>
-      <c r="AA15" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="AB15" s="1" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
         <v>11</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D16" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="E16" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="E16" s="1" t="n">
-        <v>12</v>
-      </c>
       <c r="F16" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G16" s="1" t="n">
         <v>24</v>
       </c>
       <c r="H16" s="1" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I16" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J16" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K16" s="1" t="n">
         <v>2</v>
@@ -3838,7 +3838,7 @@
         <v>15</v>
       </c>
       <c r="M16" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N16" s="1" t="n">
         <v>13</v>
@@ -3856,7 +3856,7 @@
         <v>19</v>
       </c>
       <c r="S16" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T16" s="1" t="n">
         <v>23</v>
@@ -3865,7 +3865,7 @@
         <v>18</v>
       </c>
       <c r="V16" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="W16" s="1" t="n">
         <v>20</v>
@@ -3877,32 +3877,32 @@
         <v>1</v>
       </c>
       <c r="Z16" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA16" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AB16" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C17" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="E17" s="1" t="n">
         <v>12</v>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>13</v>
       </c>
       <c r="F17" s="1" t="n">
         <v>4</v>
@@ -3911,10 +3911,10 @@
         <v>24</v>
       </c>
       <c r="H17" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I17" s="1" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J17" s="1" t="n">
         <v>21</v>
@@ -3923,40 +3923,40 @@
         <v>2</v>
       </c>
       <c r="L17" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="M17" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="N17" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="O17" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="P17" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q17" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="R17" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="S17" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="U17" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="M17" s="1" t="n">
+      <c r="V17" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="W17" s="1" t="n">
         <v>20</v>
-      </c>
-      <c r="N17" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="O17" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="P17" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="Q17" s="1" t="n">
-        <v>27</v>
-      </c>
-      <c r="R17" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="S17" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="T17" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="U17" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="V17" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="W17" s="1" t="n">
-        <v>23</v>
       </c>
       <c r="X17" s="1" t="n">
         <v>3</v>
@@ -3965,38 +3965,38 @@
         <v>1</v>
       </c>
       <c r="Z17" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA17" s="1" t="n">
         <v>16</v>
       </c>
       <c r="AB17" s="1" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C18" s="1" t="n">
         <v>12</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F18" s="1" t="n">
         <v>4</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H18" s="1" t="n">
         <v>7</v>
@@ -4005,7 +4005,7 @@
         <v>11</v>
       </c>
       <c r="J18" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K18" s="1" t="n">
         <v>2</v>
@@ -4014,25 +4014,25 @@
         <v>18</v>
       </c>
       <c r="M18" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="N18" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="O18" s="1" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="P18" s="1" t="n">
         <v>26</v>
       </c>
       <c r="Q18" s="1" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="R18" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="S18" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T18" s="1" t="n">
         <v>22</v>
@@ -4041,7 +4041,7 @@
         <v>19</v>
       </c>
       <c r="V18" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="W18" s="1" t="n">
         <v>23</v>
@@ -4056,7 +4056,7 @@
         <v>6</v>
       </c>
       <c r="AA18" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AB18" s="1" t="n">
         <v>5</v>
@@ -4065,47 +4065,47 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C19" s="1" t="n">
         <v>12</v>
       </c>
       <c r="D19" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="E19" s="1" t="n">
         <v>15</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>10</v>
       </c>
       <c r="F19" s="1" t="n">
         <v>4</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H19" s="1" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I19" s="1" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J19" s="1" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K19" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L19" s="1" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M19" s="1" t="n">
         <v>21</v>
       </c>
       <c r="N19" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O19" s="1" t="n">
         <v>27</v>
@@ -4114,59 +4114,59 @@
         <v>26</v>
       </c>
       <c r="Q19" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R19" s="1" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="S19" s="1" t="n">
         <v>8</v>
       </c>
       <c r="T19" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="U19" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="V19" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="W19" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="U19" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="V19" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="W19" s="1" t="n">
+      <c r="X19" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y19" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="X19" s="1" t="n">
+      <c r="Z19" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA19" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="AB19" s="1" t="n">
         <v>5</v>
-      </c>
-      <c r="Y19" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z19" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA19" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="AB19" s="1" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
         <v>13</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D20" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F20" s="1" t="n">
         <v>4</v>
@@ -4175,13 +4175,13 @@
         <v>24</v>
       </c>
       <c r="H20" s="1" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I20" s="1" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="J20" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K20" s="1" t="n">
         <v>3</v>
@@ -4205,25 +4205,25 @@
         <v>25</v>
       </c>
       <c r="R20" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="S20" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="T20" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="U20" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="V20" s="1" t="n">
         <v>16</v>
-      </c>
-      <c r="S20" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="T20" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="U20" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="V20" s="1" t="n">
-        <v>15</v>
       </c>
       <c r="W20" s="1" t="n">
         <v>1</v>
       </c>
       <c r="X20" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y20" s="1" t="n">
         <v>2</v>
@@ -4232,26 +4232,26 @@
         <v>7</v>
       </c>
       <c r="AA20" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AB20" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D21" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E21" s="1" t="n">
         <v>9</v>
@@ -4260,22 +4260,22 @@
         <v>4</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H21" s="1" t="n">
         <v>12</v>
       </c>
       <c r="I21" s="1" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J21" s="1" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K21" s="1" t="n">
         <v>3</v>
       </c>
       <c r="L21" s="1" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="M21" s="1" t="n">
         <v>21</v>
@@ -4287,25 +4287,25 @@
         <v>27</v>
       </c>
       <c r="P21" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q21" s="1" t="n">
         <v>25</v>
-      </c>
-      <c r="Q21" s="1" t="n">
-        <v>24</v>
       </c>
       <c r="R21" s="1" t="n">
         <v>16</v>
       </c>
       <c r="S21" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T21" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="U21" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="V21" s="1" t="n">
         <v>15</v>
-      </c>
-      <c r="V21" s="1" t="n">
-        <v>14</v>
       </c>
       <c r="W21" s="1" t="n">
         <v>1</v>
@@ -4329,38 +4329,38 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C22" s="1" t="n">
         <v>10</v>
       </c>
       <c r="D22" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E22" s="1" t="n">
         <v>9</v>
       </c>
       <c r="F22" s="1" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H22" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I22" s="1" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J22" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K22" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L22" s="1" t="n">
         <v>20</v>
@@ -4372,37 +4372,37 @@
         <v>11</v>
       </c>
       <c r="O22" s="1" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P22" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q22" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="Q22" s="1" t="n">
-        <v>25</v>
-      </c>
       <c r="R22" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="S22" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="T22" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="U22" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="V22" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="S22" s="1" t="n">
+      <c r="W22" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="X22" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="T22" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="U22" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="V22" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="W22" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="X22" s="1" t="n">
-        <v>8</v>
-      </c>
       <c r="Y22" s="1" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Z22" s="1" t="n">
         <v>7</v>
@@ -4417,20 +4417,20 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="C23" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="C23" s="1" t="n">
-        <v>11</v>
-      </c>
       <c r="D23" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F23" s="1" t="n">
         <v>2</v>
@@ -4439,10 +4439,10 @@
         <v>27</v>
       </c>
       <c r="H23" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I23" s="1" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J23" s="1" t="n">
         <v>23</v>
@@ -4457,7 +4457,7 @@
         <v>21</v>
       </c>
       <c r="N23" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="O23" s="1" t="n">
         <v>26</v>
@@ -4469,10 +4469,10 @@
         <v>25</v>
       </c>
       <c r="R23" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S23" s="1" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T23" s="1" t="n">
         <v>22</v>
@@ -4481,13 +4481,13 @@
         <v>16</v>
       </c>
       <c r="V23" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="W23" s="1" t="n">
         <v>3</v>
       </c>
       <c r="X23" s="1" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y23" s="1" t="n">
         <v>4</v>
@@ -4505,38 +4505,38 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D24" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="E24" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="F24" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G24" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="H24" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="I24" s="1" t="n">
         <v>19</v>
-      </c>
-      <c r="E24" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="F24" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="G24" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="H24" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="I24" s="1" t="n">
-        <v>18</v>
       </c>
       <c r="J24" s="1" t="n">
         <v>23</v>
       </c>
       <c r="K24" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L24" s="1" t="n">
         <v>20</v>
@@ -4545,10 +4545,10 @@
         <v>21</v>
       </c>
       <c r="N24" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="O24" s="1" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P24" s="1" t="n">
         <v>24</v>
@@ -4557,7 +4557,7 @@
         <v>25</v>
       </c>
       <c r="R24" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="S24" s="1" t="n">
         <v>9</v>
@@ -4566,25 +4566,25 @@
         <v>22</v>
       </c>
       <c r="U24" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="V24" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="W24" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X24" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y24" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="Y24" s="1" t="n">
-        <v>2</v>
-      </c>
       <c r="Z24" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA24" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AB24" s="1" t="n">
         <v>5</v>
@@ -4593,41 +4593,41 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C25" s="1" t="n">
         <v>12</v>
       </c>
       <c r="D25" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F25" s="1" t="n">
         <v>7</v>
       </c>
       <c r="G25" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="H25" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="I25" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="J25" s="1" t="n">
         <v>23</v>
-      </c>
-      <c r="H25" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="I25" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="J25" s="1" t="n">
-        <v>24</v>
       </c>
       <c r="K25" s="1" t="n">
         <v>3</v>
       </c>
       <c r="L25" s="1" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M25" s="1" t="n">
         <v>21</v>
@@ -4639,25 +4639,25 @@
         <v>27</v>
       </c>
       <c r="P25" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q25" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="Q25" s="1" t="n">
-        <v>26</v>
-      </c>
       <c r="R25" s="1" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="S25" s="1" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="T25" s="1" t="n">
         <v>22</v>
       </c>
       <c r="U25" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="V25" s="1" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="W25" s="1" t="n">
         <v>1</v>
@@ -4672,50 +4672,50 @@
         <v>8</v>
       </c>
       <c r="AA25" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AB25" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="C26" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D26" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="E26" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="F26" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C26" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="D26" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="E26" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="F26" s="1" t="n">
-        <v>5</v>
-      </c>
       <c r="G26" s="1" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="H26" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I26" s="1" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J26" s="1" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K26" s="1" t="n">
         <v>3</v>
       </c>
       <c r="L26" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M26" s="1" t="n">
         <v>21</v>
@@ -4727,25 +4727,25 @@
         <v>27</v>
       </c>
       <c r="P26" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Q26" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="R26" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="S26" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="S26" s="1" t="n">
-        <v>19</v>
-      </c>
       <c r="T26" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="U26" s="1" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="V26" s="1" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="W26" s="1" t="n">
         <v>1</v>
@@ -4757,10 +4757,10 @@
         <v>2</v>
       </c>
       <c r="Z26" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA26" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AB26" s="1" t="n">
         <v>6</v>
@@ -4769,20 +4769,20 @@
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C27" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="D27" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="D27" s="1" t="n">
-        <v>20</v>
-      </c>
       <c r="E27" s="1" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F27" s="1" t="n">
         <v>5</v>
@@ -4791,10 +4791,10 @@
         <v>26</v>
       </c>
       <c r="H27" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I27" s="1" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J27" s="1" t="n">
         <v>22</v>
@@ -4803,34 +4803,34 @@
         <v>3</v>
       </c>
       <c r="L27" s="1" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M27" s="1" t="n">
         <v>21</v>
       </c>
       <c r="N27" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="O27" s="1" t="n">
         <v>27</v>
       </c>
       <c r="P27" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q27" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="Q27" s="1" t="n">
-        <v>24</v>
-      </c>
       <c r="R27" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="S27" s="1" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="T27" s="1" t="n">
         <v>23</v>
       </c>
       <c r="U27" s="1" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="V27" s="1" t="n">
         <v>17</v>
@@ -4845,10 +4845,10 @@
         <v>2</v>
       </c>
       <c r="Z27" s="1" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AA27" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AB27" s="1" t="n">
         <v>6</v>
@@ -4857,44 +4857,44 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D28" s="1" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F28" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G28" s="1" t="n">
         <v>26</v>
       </c>
       <c r="H28" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I28" s="1" t="n">
         <v>10</v>
       </c>
       <c r="J28" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K28" s="1" t="n">
         <v>3</v>
       </c>
       <c r="L28" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M28" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N28" s="1" t="n">
         <v>11</v>
@@ -4909,10 +4909,10 @@
         <v>24</v>
       </c>
       <c r="R28" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="S28" s="1" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="T28" s="1" t="n">
         <v>23</v>
@@ -4921,13 +4921,13 @@
         <v>18</v>
       </c>
       <c r="V28" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="W28" s="1" t="n">
         <v>1</v>
       </c>
       <c r="X28" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y28" s="1" t="n">
         <v>2</v>
@@ -4936,7 +4936,7 @@
         <v>7</v>
       </c>
       <c r="AA28" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AB28" s="1" t="n">
         <v>6</v>
@@ -4945,38 +4945,38 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
         <v>9</v>
       </c>
       <c r="C29" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D29" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="E29" s="1" t="n">
         <v>13</v>
-      </c>
-      <c r="D29" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="E29" s="1" t="n">
-        <v>11</v>
       </c>
       <c r="F29" s="1" t="n">
         <v>4</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H29" s="1" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I29" s="1" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J29" s="1" t="n">
         <v>21</v>
       </c>
       <c r="K29" s="1" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="L29" s="1" t="n">
         <v>20</v>
@@ -4985,28 +4985,28 @@
         <v>22</v>
       </c>
       <c r="N29" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="O29" s="1" t="n">
         <v>27</v>
       </c>
       <c r="P29" s="1" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Q29" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R29" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="S29" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="T29" s="1" t="n">
         <v>23</v>
       </c>
       <c r="U29" s="1" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="V29" s="1" t="n">
         <v>15</v>
@@ -5021,10 +5021,10 @@
         <v>2</v>
       </c>
       <c r="Z29" s="1" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AA29" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AB29" s="1" t="n">
         <v>6</v>
@@ -5033,47 +5033,47 @@
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C30" s="1" t="n">
         <v>13</v>
       </c>
       <c r="D30" s="1" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="F30" s="1" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H30" s="1" t="n">
         <v>3</v>
       </c>
       <c r="I30" s="1" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J30" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="K30" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="L30" s="1" t="n">
         <v>20</v>
-      </c>
-      <c r="K30" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="L30" s="1" t="n">
-        <v>18</v>
       </c>
       <c r="M30" s="1" t="n">
         <v>22</v>
       </c>
       <c r="N30" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O30" s="1" t="n">
         <v>27</v>
@@ -5085,25 +5085,25 @@
         <v>25</v>
       </c>
       <c r="R30" s="1" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="S30" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="T30" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="U30" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="T30" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="U30" s="1" t="n">
-        <v>12</v>
-      </c>
       <c r="V30" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="W30" s="1" t="n">
         <v>1</v>
       </c>
       <c r="X30" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y30" s="1" t="n">
         <v>2</v>
@@ -5121,44 +5121,44 @@
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D31" s="1" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F31" s="1" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G31" s="1" t="n">
         <v>23</v>
       </c>
       <c r="H31" s="1" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I31" s="1" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J31" s="1" t="n">
         <v>20</v>
       </c>
       <c r="K31" s="1" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L31" s="1" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="M31" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N31" s="1" t="n">
         <v>11</v>
@@ -5170,86 +5170,86 @@
         <v>26</v>
       </c>
       <c r="Q31" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="R31" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="S31" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="T31" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="R31" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="S31" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="T31" s="1" t="n">
-        <v>25</v>
-      </c>
       <c r="U31" s="1" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="V31" s="1" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="W31" s="1" t="n">
         <v>1</v>
       </c>
       <c r="X31" s="1" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Y31" s="1" t="n">
         <v>2</v>
       </c>
       <c r="Z31" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA31" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AB31" s="1" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
         <v>10</v>
       </c>
       <c r="C32" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="D32" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="D32" s="1" t="n">
-        <v>11</v>
-      </c>
       <c r="E32" s="1" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F32" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G32" s="1" t="n">
         <v>23</v>
       </c>
       <c r="H32" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="I32" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="J32" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="K32" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="I32" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="J32" s="1" t="n">
+      <c r="L32" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="M32" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="K32" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="L32" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="M32" s="1" t="n">
-        <v>22</v>
-      </c>
       <c r="N32" s="1" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="O32" s="1" t="n">
         <v>27</v>
@@ -5261,7 +5261,7 @@
         <v>24</v>
       </c>
       <c r="R32" s="1" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="S32" s="1" t="n">
         <v>19</v>
@@ -5270,16 +5270,16 @@
         <v>25</v>
       </c>
       <c r="U32" s="1" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="V32" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="W32" s="1" t="n">
         <v>1</v>
       </c>
       <c r="X32" s="1" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Y32" s="1" t="n">
         <v>2</v>
@@ -5288,23 +5288,23 @@
         <v>9</v>
       </c>
       <c r="AA32" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AB32" s="1" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
         <v>10</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D33" s="1" t="n">
         <v>11</v>
@@ -5313,7 +5313,7 @@
         <v>20</v>
       </c>
       <c r="F33" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G33" s="1" t="n">
         <v>23</v>
@@ -5325,19 +5325,19 @@
         <v>7</v>
       </c>
       <c r="J33" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K33" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L33" s="1" t="n">
         <v>13</v>
       </c>
       <c r="M33" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N33" s="1" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="O33" s="1" t="n">
         <v>27</v>
@@ -5349,19 +5349,19 @@
         <v>24</v>
       </c>
       <c r="R33" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="S33" s="1" t="n">
         <v>19</v>
-      </c>
-      <c r="S33" s="1" t="n">
-        <v>18</v>
       </c>
       <c r="T33" s="1" t="n">
         <v>25</v>
       </c>
       <c r="U33" s="1" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="V33" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="W33" s="1" t="n">
         <v>1</v>
@@ -5376,7 +5376,7 @@
         <v>9</v>
       </c>
       <c r="AA33" s="1" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AB33" s="1" t="n">
         <v>8</v>
@@ -5385,44 +5385,44 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="C34" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="C34" s="1" t="n">
-        <v>16</v>
-      </c>
       <c r="D34" s="1" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F34" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G34" s="1" t="n">
         <v>23</v>
       </c>
       <c r="H34" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I34" s="1" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J34" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="K34" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="L34" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="M34" s="1" t="n">
         <v>21</v>
-      </c>
-      <c r="K34" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="L34" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="M34" s="1" t="n">
-        <v>20</v>
       </c>
       <c r="N34" s="1" t="n">
         <v>12</v>
@@ -5446,19 +5446,19 @@
         <v>25</v>
       </c>
       <c r="U34" s="1" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="V34" s="1" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="W34" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="X34" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="X34" s="1" t="n">
-        <v>7</v>
-      </c>
       <c r="Y34" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Z34" s="1" t="n">
         <v>9</v>
@@ -5473,23 +5473,23 @@
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C35" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="D35" s="1" t="n">
         <v>14</v>
-      </c>
-      <c r="D35" s="1" t="n">
-        <v>13</v>
       </c>
       <c r="E35" s="1" t="n">
         <v>22</v>
       </c>
       <c r="F35" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G35" s="1" t="n">
         <v>23</v>
@@ -5501,16 +5501,16 @@
         <v>3</v>
       </c>
       <c r="J35" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K35" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L35" s="1" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="M35" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="N35" s="1" t="n">
         <v>12</v>
@@ -5525,47 +5525,47 @@
         <v>24</v>
       </c>
       <c r="R35" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="S35" s="1" t="n">
         <v>18</v>
-      </c>
-      <c r="S35" s="1" t="n">
-        <v>19</v>
       </c>
       <c r="T35" s="1" t="n">
         <v>25</v>
       </c>
       <c r="U35" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="V35" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="W35" s="1" t="n">
         <v>4</v>
       </c>
       <c r="X35" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y35" s="1" t="n">
         <v>5</v>
       </c>
       <c r="Z35" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA35" s="1" t="n">
         <v>17</v>
       </c>
       <c r="AB35" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B36" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C36" s="1" t="n">
         <v>14</v>
@@ -5574,31 +5574,31 @@
         <v>13</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F36" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G36" s="1" t="n">
         <v>23</v>
       </c>
       <c r="H36" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I36" s="1" t="n">
         <v>3</v>
       </c>
       <c r="J36" s="1" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K36" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L36" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M36" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N36" s="1" t="n">
         <v>12</v>
@@ -5613,19 +5613,19 @@
         <v>24</v>
       </c>
       <c r="R36" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="S36" s="1" t="n">
         <v>19</v>
-      </c>
-      <c r="S36" s="1" t="n">
-        <v>18</v>
       </c>
       <c r="T36" s="1" t="n">
         <v>25</v>
       </c>
       <c r="U36" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="V36" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="W36" s="1" t="n">
         <v>4</v>
@@ -5637,10 +5637,10 @@
         <v>5</v>
       </c>
       <c r="Z36" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA36" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AB36" s="1" t="n">
         <v>9</v>
@@ -5649,26 +5649,26 @@
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B37" s="1" t="n">
         <v>11</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D37" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F37" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H37" s="1" t="n">
         <v>2</v>
@@ -5677,13 +5677,13 @@
         <v>3</v>
       </c>
       <c r="J37" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K37" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L37" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M37" s="1" t="n">
         <v>20</v>
@@ -5698,16 +5698,16 @@
         <v>26</v>
       </c>
       <c r="Q37" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="R37" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="S37" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="T37" s="1" t="n">
         <v>25</v>
-      </c>
-      <c r="R37" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="S37" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="T37" s="1" t="n">
-        <v>24</v>
       </c>
       <c r="U37" s="1" t="n">
         <v>10</v>
@@ -5725,35 +5725,35 @@
         <v>5</v>
       </c>
       <c r="Z37" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA37" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="AB37" s="1" t="n">
         <v>9</v>
-      </c>
-      <c r="AA37" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="AB37" s="1" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B38" s="1" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D38" s="1" t="n">
         <v>14</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F38" s="1" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G38" s="1" t="n">
         <v>21</v>
@@ -5771,7 +5771,7 @@
         <v>1</v>
       </c>
       <c r="L38" s="1" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="M38" s="1" t="n">
         <v>20</v>
@@ -5783,56 +5783,56 @@
         <v>27</v>
       </c>
       <c r="P38" s="1" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="Q38" s="1" t="n">
         <v>25</v>
       </c>
       <c r="R38" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="S38" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="T38" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="U38" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="T38" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="U38" s="1" t="n">
+      <c r="V38" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="W38" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="V38" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="W38" s="1" t="n">
+      <c r="X38" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="X38" s="1" t="n">
-        <v>11</v>
-      </c>
       <c r="Y38" s="1" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Z38" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA38" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="AB38" s="1" t="n">
         <v>8</v>
-      </c>
-      <c r="AA38" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="AB38" s="1" t="n">
-        <v>9</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B39" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="C39" s="1" t="n">
         <v>17</v>
-      </c>
-      <c r="C39" s="1" t="n">
-        <v>15</v>
       </c>
       <c r="D39" s="1" t="n">
         <v>14</v>
@@ -5844,7 +5844,7 @@
         <v>5</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="H39" s="1" t="n">
         <v>2</v>
@@ -5853,25 +5853,25 @@
         <v>3</v>
       </c>
       <c r="J39" s="1" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K39" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L39" s="1" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="M39" s="1" t="n">
         <v>20</v>
       </c>
       <c r="N39" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="O39" s="1" t="n">
         <v>27</v>
       </c>
       <c r="P39" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q39" s="1" t="n">
         <v>25</v>
@@ -5880,47 +5880,47 @@
         <v>16</v>
       </c>
       <c r="S39" s="1" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T39" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="U39" s="1" t="n">
         <v>4</v>
       </c>
       <c r="V39" s="1" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="W39" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X39" s="1" t="n">
         <v>11</v>
       </c>
       <c r="Y39" s="1" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Z39" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA39" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="AB39" s="1" t="n">
         <v>9</v>
-      </c>
-      <c r="AA39" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="AB39" s="1" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B40" s="1" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D40" s="1" t="n">
         <v>14</v>
@@ -5941,34 +5941,34 @@
         <v>3</v>
       </c>
       <c r="J40" s="1" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K40" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L40" s="1" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M40" s="1" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="N40" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="O40" s="1" t="n">
         <v>27</v>
       </c>
       <c r="P40" s="1" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q40" s="1" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="R40" s="1" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="S40" s="1" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T40" s="1" t="n">
         <v>21</v>
@@ -5980,13 +5980,13 @@
         <v>12</v>
       </c>
       <c r="W40" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X40" s="1" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="Y40" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z40" s="1" t="n">
         <v>9</v>
@@ -5995,59 +5995,59 @@
         <v>19</v>
       </c>
       <c r="AB40" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B41" s="1" t="n">
         <v>25</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D41" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F41" s="1" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G41" s="1" t="n">
         <v>24</v>
       </c>
       <c r="H41" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I41" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="J41" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="K41" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="I41" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="J41" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="K41" s="1" t="n">
-        <v>3</v>
-      </c>
       <c r="L41" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M41" s="1" t="n">
         <v>18</v>
       </c>
       <c r="N41" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="O41" s="1" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P41" s="1" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="Q41" s="1" t="n">
         <v>23</v>
@@ -6056,56 +6056,56 @@
         <v>13</v>
       </c>
       <c r="S41" s="1" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T41" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="U41" s="1" t="n">
         <v>4</v>
       </c>
       <c r="V41" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="W41" s="1" t="n">
         <v>6</v>
       </c>
       <c r="X41" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Y41" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z41" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA41" s="1" t="n">
         <v>19</v>
       </c>
       <c r="AB41" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B42" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="C42" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="D42" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="E42" s="1" t="n">
         <v>27</v>
       </c>
-      <c r="C42" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="D42" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="E42" s="1" t="n">
-        <v>25</v>
-      </c>
       <c r="F42" s="1" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G42" s="1" t="n">
         <v>24</v>
@@ -6114,61 +6114,61 @@
         <v>1</v>
       </c>
       <c r="I42" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="J42" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="K42" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="J42" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="K42" s="1" t="n">
-        <v>2</v>
-      </c>
       <c r="L42" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M42" s="1" t="n">
         <v>18</v>
       </c>
       <c r="N42" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="O42" s="1" t="n">
         <v>26</v>
       </c>
       <c r="P42" s="1" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q42" s="1" t="n">
         <v>23</v>
       </c>
       <c r="R42" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="S42" s="1" t="n">
         <v>5</v>
       </c>
       <c r="T42" s="1" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="U42" s="1" t="n">
         <v>4</v>
       </c>
       <c r="V42" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="W42" s="1" t="n">
         <v>6</v>
       </c>
       <c r="X42" s="1" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="Y42" s="1" t="n">
         <v>7</v>
       </c>
       <c r="Z42" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA42" s="1" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AB42" s="1" t="n">
         <v>8</v>
@@ -6177,47 +6177,47 @@
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B43" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C43" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="D43" s="1" t="n">
         <v>13</v>
-      </c>
-      <c r="D43" s="1" t="n">
-        <v>6</v>
       </c>
       <c r="E43" s="1" t="n">
         <v>25</v>
       </c>
       <c r="F43" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H43" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I43" s="1" t="n">
         <v>3</v>
       </c>
       <c r="J43" s="1" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="K43" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L43" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M43" s="1" t="n">
         <v>18</v>
       </c>
       <c r="N43" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="O43" s="1" t="n">
         <v>26</v>
@@ -6235,53 +6235,53 @@
         <v>5</v>
       </c>
       <c r="T43" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="U43" s="1" t="n">
         <v>4</v>
       </c>
       <c r="V43" s="1" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="W43" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X43" s="1" t="n">
         <v>17</v>
       </c>
       <c r="Y43" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z43" s="1" t="n">
         <v>9</v>
       </c>
       <c r="AA43" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AB43" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B44" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C44" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="D44" s="1" t="n">
         <v>6</v>
-      </c>
-      <c r="D44" s="1" t="n">
-        <v>5</v>
       </c>
       <c r="E44" s="1" t="n">
         <v>25</v>
       </c>
       <c r="F44" s="1" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="G44" s="1" t="n">
         <v>22</v>
@@ -6305,22 +6305,22 @@
         <v>18</v>
       </c>
       <c r="N44" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="O44" s="1" t="n">
         <v>26</v>
       </c>
       <c r="P44" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Q44" s="1" t="n">
         <v>23</v>
       </c>
       <c r="R44" s="1" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="S44" s="1" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T44" s="1" t="n">
         <v>21</v>
@@ -6329,50 +6329,50 @@
         <v>4</v>
       </c>
       <c r="V44" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="W44" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X44" s="1" t="n">
         <v>17</v>
       </c>
       <c r="Y44" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z44" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="Z44" s="1" t="n">
+      <c r="AA44" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="AB44" s="1" t="n">
         <v>10</v>
-      </c>
-      <c r="AA44" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="AB44" s="1" t="n">
-        <v>11</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B45" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D45" s="1" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E45" s="1" t="n">
         <v>25</v>
       </c>
       <c r="F45" s="1" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H45" s="1" t="n">
         <v>2</v>
@@ -6390,7 +6390,7 @@
         <v>16</v>
       </c>
       <c r="M45" s="1" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N45" s="1" t="n">
         <v>14</v>
@@ -6399,68 +6399,68 @@
         <v>26</v>
       </c>
       <c r="P45" s="1" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="Q45" s="1" t="n">
         <v>23</v>
       </c>
       <c r="R45" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="S45" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="T45" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="U45" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="V45" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="W45" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="X45" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y45" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="S45" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="T45" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="U45" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="V45" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="W45" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="X45" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="Y45" s="1" t="n">
-        <v>5</v>
-      </c>
       <c r="Z45" s="1" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AA45" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AB45" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B46" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D46" s="1" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E46" s="1" t="n">
         <v>25</v>
       </c>
       <c r="F46" s="1" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H46" s="1" t="n">
         <v>2</v>
@@ -6469,25 +6469,25 @@
         <v>3</v>
       </c>
       <c r="J46" s="1" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K46" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L46" s="1" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="M46" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N46" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O46" s="1" t="n">
         <v>26</v>
       </c>
       <c r="P46" s="1" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="Q46" s="1" t="n">
         <v>23</v>
@@ -6496,31 +6496,31 @@
         <v>9</v>
       </c>
       <c r="S46" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="T46" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="U46" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="T46" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="U46" s="1" t="n">
-        <v>7</v>
-      </c>
       <c r="V46" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="W46" s="1" t="n">
         <v>4</v>
       </c>
       <c r="X46" s="1" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Y46" s="1" t="n">
         <v>5</v>
       </c>
       <c r="Z46" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA46" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AB46" s="1" t="n">
         <v>10</v>
@@ -6529,23 +6529,23 @@
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B47" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D47" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F47" s="1" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G47" s="1" t="n">
         <v>20</v>
@@ -6557,13 +6557,13 @@
         <v>3</v>
       </c>
       <c r="J47" s="1" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="K47" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L47" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="M47" s="1" t="n">
         <v>18</v>
@@ -6572,10 +6572,10 @@
         <v>15</v>
       </c>
       <c r="O47" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P47" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Q47" s="1" t="n">
         <v>23</v>
@@ -6590,25 +6590,25 @@
         <v>24</v>
       </c>
       <c r="U47" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V47" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="W47" s="1" t="n">
         <v>4</v>
       </c>
       <c r="X47" s="1" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Y47" s="1" t="n">
         <v>5</v>
       </c>
       <c r="Z47" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA47" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AB47" s="1" t="n">
         <v>10</v>
@@ -6617,26 +6617,26 @@
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B48" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C48" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="D48" s="1" t="n">
         <v>16</v>
-      </c>
-      <c r="D48" s="1" t="n">
-        <v>13</v>
       </c>
       <c r="E48" s="1" t="n">
         <v>26</v>
       </c>
       <c r="F48" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="G48" s="1" t="n">
         <v>20</v>
-      </c>
-      <c r="G48" s="1" t="n">
-        <v>22</v>
       </c>
       <c r="H48" s="1" t="n">
         <v>2</v>
@@ -6657,13 +6657,13 @@
         <v>18</v>
       </c>
       <c r="N48" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="O48" s="1" t="n">
         <v>25</v>
       </c>
       <c r="P48" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Q48" s="1" t="n">
         <v>23</v>
@@ -6681,7 +6681,7 @@
         <v>8</v>
       </c>
       <c r="V48" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="W48" s="1" t="n">
         <v>4</v>
@@ -6696,7 +6696,7 @@
         <v>7</v>
       </c>
       <c r="AA48" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AB48" s="1" t="n">
         <v>10</v>
@@ -6705,7 +6705,7 @@
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B49" s="1" t="n">
@@ -6715,16 +6715,16 @@
         <v>16</v>
       </c>
       <c r="D49" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F49" s="1" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H49" s="1" t="n">
         <v>2</v>
@@ -6742,22 +6742,22 @@
         <v>11</v>
       </c>
       <c r="M49" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="N49" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="N49" s="1" t="n">
-        <v>15</v>
-      </c>
       <c r="O49" s="1" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P49" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="Q49" s="1" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="R49" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="S49" s="1" t="n">
         <v>6</v>
@@ -6769,13 +6769,13 @@
         <v>8</v>
       </c>
       <c r="V49" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="W49" s="1" t="n">
         <v>4</v>
       </c>
       <c r="X49" s="1" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="Y49" s="1" t="n">
         <v>5</v>
@@ -6784,71 +6784,71 @@
         <v>7</v>
       </c>
       <c r="AA49" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AB49" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B50" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D50" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F50" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="G50" s="1" t="n">
         <v>20</v>
-      </c>
-      <c r="G50" s="1" t="n">
-        <v>17</v>
       </c>
       <c r="H50" s="1" t="n">
         <v>2</v>
       </c>
       <c r="I50" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J50" s="1" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K50" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L50" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="M50" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N50" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="O50" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="P50" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="O50" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="P50" s="1" t="n">
-        <v>11</v>
-      </c>
       <c r="Q50" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R50" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="S50" s="1" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T50" s="1" t="n">
         <v>24</v>
@@ -6860,132 +6860,132 @@
         <v>13</v>
       </c>
       <c r="W50" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="X50" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y50" s="1" t="n">
         <v>5</v>
-      </c>
-      <c r="X50" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="Y50" s="1" t="n">
-        <v>6</v>
       </c>
       <c r="Z50" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AA50" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AB50" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B51" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D51" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E51" s="1" t="n">
         <v>26</v>
       </c>
       <c r="F51" s="1" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H51" s="1" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I51" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J51" s="1" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="K51" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L51" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M51" s="1" t="n">
         <v>18</v>
       </c>
       <c r="N51" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O51" s="1" t="n">
         <v>25</v>
       </c>
       <c r="P51" s="1" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="Q51" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="R51" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="S51" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T51" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="U51" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V51" s="1" t="n">
         <v>13</v>
       </c>
       <c r="W51" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X51" s="1" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="Y51" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z51" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AA51" s="1" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AB51" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B52" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D52" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E52" s="1" t="n">
         <v>26</v>
       </c>
       <c r="F52" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G52" s="1" t="n">
         <v>20</v>
@@ -6994,7 +6994,7 @@
         <v>6</v>
       </c>
       <c r="I52" s="1" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J52" s="1" t="n">
         <v>19</v>
@@ -7015,10 +7015,10 @@
         <v>25</v>
       </c>
       <c r="P52" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Q52" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R52" s="1" t="n">
         <v>10</v>
@@ -7027,53 +7027,53 @@
         <v>2</v>
       </c>
       <c r="T52" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="U52" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="V52" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="W52" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="X52" s="1" t="n">
         <v>24</v>
-      </c>
-      <c r="U52" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="V52" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="W52" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="X52" s="1" t="n">
-        <v>23</v>
       </c>
       <c r="Y52" s="1" t="n">
         <v>5</v>
       </c>
       <c r="Z52" s="1" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AA52" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AB52" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B53" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D53" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E53" s="1" t="n">
         <v>26</v>
       </c>
       <c r="F53" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G53" s="1" t="n">
         <v>20</v>
@@ -7082,25 +7082,25 @@
         <v>6</v>
       </c>
       <c r="I53" s="1" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J53" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K53" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L53" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M53" s="1" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N53" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O53" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="P53" s="1" t="n">
         <v>17</v>
@@ -7109,31 +7109,31 @@
         <v>22</v>
       </c>
       <c r="R53" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="S53" s="1" t="n">
         <v>2</v>
       </c>
       <c r="T53" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="U53" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="V53" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="W53" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="X53" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="U53" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="V53" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="W53" s="1" t="n">
+      <c r="Y53" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z53" s="1" t="n">
         <v>4</v>
-      </c>
-      <c r="X53" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="Y53" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z53" s="1" t="n">
-        <v>5</v>
       </c>
       <c r="AA53" s="1" t="n">
         <v>21</v>
@@ -7145,32 +7145,32 @@
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B54" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D54" s="1" t="n">
         <v>11</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F54" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G54" s="1" t="n">
         <v>20</v>
       </c>
       <c r="H54" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="I54" s="1" t="n">
         <v>3</v>
-      </c>
-      <c r="I54" s="1" t="n">
-        <v>12</v>
       </c>
       <c r="J54" s="1" t="n">
         <v>18</v>
@@ -7179,13 +7179,13 @@
         <v>1</v>
       </c>
       <c r="L54" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M54" s="1" t="n">
         <v>19</v>
       </c>
       <c r="N54" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O54" s="1" t="n">
         <v>24</v>
@@ -7197,28 +7197,28 @@
         <v>22</v>
       </c>
       <c r="R54" s="1" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="S54" s="1" t="n">
         <v>2</v>
       </c>
       <c r="T54" s="1" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="U54" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V54" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="W54" s="1" t="n">
         <v>4</v>
       </c>
       <c r="X54" s="1" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Y54" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z54" s="1" t="n">
         <v>5</v>
@@ -7227,77 +7227,77 @@
         <v>21</v>
       </c>
       <c r="AB54" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B55" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C55" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="D55" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="D55" s="1" t="n">
-        <v>10</v>
-      </c>
       <c r="E55" s="1" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F55" s="1" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G55" s="1" t="n">
         <v>20</v>
       </c>
       <c r="H55" s="1" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="I55" s="1" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="J55" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K55" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L55" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M55" s="1" t="n">
         <v>19</v>
       </c>
       <c r="N55" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O55" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P55" s="1" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Q55" s="1" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="R55" s="1" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="S55" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T55" s="1" t="n">
         <v>26</v>
       </c>
       <c r="U55" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="V55" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="W55" s="1" t="n">
         <v>4</v>
@@ -7306,7 +7306,7 @@
         <v>23</v>
       </c>
       <c r="Y55" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z55" s="1" t="n">
         <v>5</v>
@@ -7315,62 +7315,62 @@
         <v>21</v>
       </c>
       <c r="AB55" s="1" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B56" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D56" s="1" t="n">
         <v>10</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F56" s="1" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="G56" s="1" t="n">
         <v>20</v>
       </c>
       <c r="H56" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I56" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J56" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K56" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L56" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M56" s="1" t="n">
         <v>19</v>
       </c>
       <c r="N56" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O56" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="P56" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q56" s="1" t="n">
         <v>24</v>
-      </c>
-      <c r="P56" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q56" s="1" t="n">
-        <v>21</v>
       </c>
       <c r="R56" s="1" t="n">
         <v>3</v>
@@ -7379,10 +7379,10 @@
         <v>1</v>
       </c>
       <c r="T56" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="U56" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V56" s="1" t="n">
         <v>12</v>
@@ -7391,7 +7391,7 @@
         <v>4</v>
       </c>
       <c r="X56" s="1" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="Y56" s="1" t="n">
         <v>6</v>
@@ -7400,50 +7400,50 @@
         <v>5</v>
       </c>
       <c r="AA56" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AB56" s="1" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B57" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D57" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F57" s="1" t="n">
         <v>18</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H57" s="1" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="I57" s="1" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="J57" s="1" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="K57" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L57" s="1" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="M57" s="1" t="n">
         <v>19</v>
@@ -7452,37 +7452,37 @@
         <v>17</v>
       </c>
       <c r="O57" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P57" s="1" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="Q57" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R57" s="1" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="S57" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T57" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="U57" s="1" t="n">
         <v>7</v>
       </c>
       <c r="V57" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="W57" s="1" t="n">
         <v>4</v>
       </c>
       <c r="X57" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Y57" s="1" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Z57" s="1" t="n">
         <v>5</v>
@@ -7497,7 +7497,7 @@
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B58" s="1" t="n">
@@ -7507,10 +7507,10 @@
         <v>16</v>
       </c>
       <c r="D58" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F58" s="1" t="n">
         <v>18</v>
@@ -7519,19 +7519,19 @@
         <v>21</v>
       </c>
       <c r="H58" s="1" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="I58" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J58" s="1" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K58" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L58" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M58" s="1" t="n">
         <v>19</v>
@@ -7549,13 +7549,13 @@
         <v>20</v>
       </c>
       <c r="R58" s="1" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="S58" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T58" s="1" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="U58" s="1" t="n">
         <v>7</v>
@@ -7564,101 +7564,101 @@
         <v>15</v>
       </c>
       <c r="W58" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X58" s="1" t="n">
         <v>25</v>
       </c>
       <c r="Y58" s="1" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="Z58" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA58" s="1" t="n">
         <v>22</v>
       </c>
       <c r="AB58" s="1" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B59" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D59" s="1" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E59" s="1" t="n">
         <v>24</v>
       </c>
       <c r="F59" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G59" s="1" t="n">
         <v>21</v>
       </c>
       <c r="H59" s="1" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I59" s="1" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="J59" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K59" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L59" s="1" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="M59" s="1" t="n">
         <v>19</v>
       </c>
       <c r="N59" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O59" s="1" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="P59" s="1" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="Q59" s="1" t="n">
         <v>20</v>
       </c>
       <c r="R59" s="1" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="S59" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T59" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="U59" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V59" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="W59" s="1" t="n">
         <v>3</v>
       </c>
       <c r="X59" s="1" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Y59" s="1" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="Z59" s="1" t="n">
         <v>4</v>
@@ -7673,41 +7673,41 @@
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B60" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D60" s="1" t="n">
         <v>8</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F60" s="1" t="n">
         <v>16</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H60" s="1" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="I60" s="1" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="J60" s="1" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="K60" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L60" s="1" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="M60" s="1" t="n">
         <v>19</v>
@@ -7722,7 +7722,7 @@
         <v>12</v>
       </c>
       <c r="Q60" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="R60" s="1" t="n">
         <v>7</v>
@@ -7731,13 +7731,13 @@
         <v>1</v>
       </c>
       <c r="T60" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="U60" s="1" t="n">
         <v>6</v>
       </c>
       <c r="V60" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="W60" s="1" t="n">
         <v>3</v>
@@ -7746,7 +7746,7 @@
         <v>23</v>
       </c>
       <c r="Y60" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Z60" s="1" t="n">
         <v>4</v>
@@ -7761,68 +7761,68 @@
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B61" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D61" s="1" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E61" s="1" t="n">
         <v>25</v>
       </c>
       <c r="F61" s="1" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H61" s="1" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I61" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J61" s="1" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="K61" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L61" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="M61" s="1" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="N61" s="1" t="n">
         <v>18</v>
       </c>
       <c r="O61" s="1" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="P61" s="1" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="Q61" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R61" s="1" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="S61" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T61" s="1" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="U61" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V61" s="1" t="n">
         <v>14</v>
@@ -7831,250 +7831,250 @@
         <v>3</v>
       </c>
       <c r="X61" s="1" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="Y61" s="1" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Z61" s="1" t="n">
         <v>4</v>
       </c>
       <c r="AA61" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AB61" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B62" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D62" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E62" s="1" t="n">
         <v>25</v>
       </c>
       <c r="F62" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H62" s="1" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I62" s="1" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J62" s="1" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="K62" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L62" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M62" s="1" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="N62" s="1" t="n">
         <v>18</v>
       </c>
       <c r="O62" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P62" s="1" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="Q62" s="1" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="R62" s="1" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="S62" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T62" s="1" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="U62" s="1" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="V62" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="W62" s="1" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="X62" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y62" s="1" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="Z62" s="1" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="AA62" s="1" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AB62" s="1" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B63" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D63" s="1" t="n">
         <v>15</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F63" s="1" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H63" s="1" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="I63" s="1" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="J63" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K63" s="1" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L63" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="M63" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="M63" s="1" t="n">
-        <v>16</v>
-      </c>
       <c r="N63" s="1" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O63" s="1" t="n">
         <v>23</v>
       </c>
       <c r="P63" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q63" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="R63" s="1" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="S63" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T63" s="1" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="U63" s="1" t="n">
         <v>2</v>
       </c>
       <c r="V63" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="W63" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="X63" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y63" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="W63" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="X63" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="Y63" s="1" t="n">
-        <v>8</v>
-      </c>
       <c r="Z63" s="1" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AA63" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AB63" s="1" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B64" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D64" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="E64" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="F64" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="G64" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="H64" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="I64" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="E64" s="1" t="n">
+      <c r="J64" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="K64" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="L64" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="M64" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="N64" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="O64" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="F64" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="G64" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="H64" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="I64" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="J64" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="K64" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="L64" s="1" t="n">
+      <c r="P64" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q64" s="1" t="n">
         <v>18</v>
-      </c>
-      <c r="M64" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="N64" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="O64" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="P64" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q64" s="1" t="n">
-        <v>19</v>
       </c>
       <c r="R64" s="1" t="n">
         <v>10</v>
@@ -8086,77 +8086,77 @@
         <v>26</v>
       </c>
       <c r="U64" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="V64" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="W64" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="X64" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y64" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z64" s="1" t="n">
         <v>7</v>
-      </c>
-      <c r="V64" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="W64" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="X64" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="Y64" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="Z64" s="1" t="n">
-        <v>9</v>
       </c>
       <c r="AA64" s="1" t="n">
         <v>25</v>
       </c>
       <c r="AB64" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B65" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D65" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E65" s="1" t="n">
         <v>23</v>
       </c>
       <c r="F65" s="1" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="G65" s="1" t="n">
         <v>24</v>
       </c>
       <c r="H65" s="1" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="I65" s="1" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J65" s="1" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K65" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L65" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="M65" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="N65" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="M65" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="N65" s="1" t="n">
-        <v>13</v>
-      </c>
       <c r="O65" s="1" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="P65" s="1" t="n">
         <v>8</v>
@@ -8177,83 +8177,83 @@
         <v>7</v>
       </c>
       <c r="V65" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="W65" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X65" s="1" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="Y65" s="1" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Z65" s="1" t="n">
         <v>9</v>
       </c>
       <c r="AA65" s="1" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AB65" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B66" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D66" s="1" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E66" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="F66" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="G66" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="F66" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="G66" s="1" t="n">
-        <v>22</v>
-      </c>
       <c r="H66" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="I66" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="I66" s="1" t="n">
-        <v>21</v>
-      </c>
       <c r="J66" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K66" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L66" s="1" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="M66" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N66" s="1" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="O66" s="1" t="n">
         <v>25</v>
       </c>
       <c r="P66" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q66" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="R66" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="S66" s="1" t="n">
         <v>1</v>
@@ -8265,47 +8265,47 @@
         <v>7</v>
       </c>
       <c r="V66" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="W66" s="1" t="n">
         <v>3</v>
       </c>
       <c r="X66" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Y66" s="1" t="n">
         <v>4</v>
       </c>
       <c r="Z66" s="1" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AA66" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AB66" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B67" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D67" s="1" t="n">
         <v>12</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F67" s="1" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G67" s="1" t="n">
         <v>22</v>
@@ -8314,43 +8314,43 @@
         <v>20</v>
       </c>
       <c r="I67" s="1" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J67" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="K67" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="L67" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="M67" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="N67" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="O67" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="P67" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q67" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="R67" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="S67" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T67" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="U67" s="1" t="n">
         <v>7</v>
-      </c>
-      <c r="K67" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L67" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="M67" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="N67" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="O67" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="P67" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q67" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="R67" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="S67" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="T67" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="U67" s="1" t="n">
-        <v>6</v>
       </c>
       <c r="V67" s="1" t="n">
         <v>15</v>
@@ -8359,19 +8359,19 @@
         <v>3</v>
       </c>
       <c r="X67" s="1" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Y67" s="1" t="n">
         <v>4</v>
       </c>
       <c r="Z67" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AA67" s="1" t="n">
         <v>23</v>
       </c>
       <c r="AB67" s="1" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/NSE_Sector_Monitor.xlsx
+++ b/NSE_Sector_Monitor.xlsx
@@ -565,25 +565,25 @@
         <v>0</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>3</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>14.46</v>
+        <v>14.45</v>
       </c>
       <c r="H2" s="1" t="n">
-        <v>-2.76</v>
+        <v>0</v>
       </c>
       <c r="I2" s="1" t="n">
-        <v>0.71</v>
+        <v>0.34</v>
       </c>
       <c r="J2" s="1" t="n">
-        <v>5.93</v>
+        <v>4.17</v>
       </c>
       <c r="K2" s="1" t="n">
-        <v>18.65</v>
+        <v>18.23</v>
       </c>
       <c r="L2" s="1" t="inlineStr">
         <is>
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="M2" s="1" t="n">
-        <v>-2.99</v>
+        <v>-1.92</v>
       </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
@@ -624,31 +624,31 @@
         <v>2</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>2</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>26.95</v>
+        <v>27.36</v>
       </c>
       <c r="H3" s="1" t="n">
-        <v>0.04</v>
+        <v>1.52</v>
       </c>
       <c r="I3" s="1" t="n">
-        <v>-0.14</v>
+        <v>1.65</v>
       </c>
       <c r="J3" s="1" t="n">
-        <v>3.29</v>
+        <v>4.45</v>
       </c>
       <c r="K3" s="1" t="n">
-        <v>11.68</v>
+        <v>12.56</v>
       </c>
       <c r="L3" s="1" t="inlineStr">
         <is>
@@ -656,21 +656,21 @@
         </is>
       </c>
       <c r="M3" s="1" t="n">
-        <v>-0.21</v>
+        <v>0</v>
       </c>
       <c r="N3" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O3" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P3" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Q3" s="1" t="inlineStr">
@@ -695,25 +695,25 @@
         <v>0</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>87.97</v>
+        <v>88.37</v>
       </c>
       <c r="H4" s="1" t="n">
-        <v>-0.44</v>
+        <v>0.2</v>
       </c>
       <c r="I4" s="1" t="n">
-        <v>1.36</v>
+        <v>1.05</v>
       </c>
       <c r="J4" s="1" t="n">
-        <v>2.14</v>
+        <v>1.29</v>
       </c>
       <c r="K4" s="1" t="n">
-        <v>9.51</v>
+        <v>9.82</v>
       </c>
       <c r="L4" s="1" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
         </is>
       </c>
       <c r="M4" s="1" t="n">
-        <v>-7.51</v>
+        <v>-7.59</v>
       </c>
       <c r="N4" s="1" t="inlineStr">
         <is>
@@ -754,31 +754,31 @@
         <v>4</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>1</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>16.77</v>
+        <v>17.01</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>-1.12</v>
+        <v>1.01</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>0.22</v>
+        <v>1.37</v>
       </c>
       <c r="J5" s="1" t="n">
-        <v>3.07</v>
+        <v>4.15</v>
       </c>
       <c r="K5" s="1" t="n">
-        <v>8.789999999999999</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="L5" s="1" t="inlineStr">
         <is>
@@ -786,21 +786,21 @@
         </is>
       </c>
       <c r="M5" s="1" t="n">
-        <v>-1.36</v>
+        <v>0</v>
       </c>
       <c r="N5" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O5" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P5" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Q5" s="1" t="inlineStr">
@@ -825,25 +825,25 @@
         <v>-3</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>-3</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>83.01000000000001</v>
+        <v>83.84999999999999</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>-2.58</v>
+        <v>1.8</v>
       </c>
       <c r="I6" s="1" t="n">
-        <v>-3.76</v>
+        <v>-2.93</v>
       </c>
       <c r="J6" s="1" t="n">
-        <v>-4.37</v>
+        <v>-3.21</v>
       </c>
       <c r="K6" s="1" t="n">
-        <v>5.02</v>
+        <v>5</v>
       </c>
       <c r="L6" s="1" t="inlineStr">
         <is>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="M6" s="1" t="n">
-        <v>-9.630000000000001</v>
+        <v>-9.210000000000001</v>
       </c>
       <c r="N6" s="1" t="inlineStr">
         <is>
@@ -877,38 +877,38 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
         <v>6</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>-4</v>
+        <v>11</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>279.35</v>
+        <v>32.39</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>-1.24</v>
+        <v>-1.46</v>
       </c>
       <c r="I7" s="1" t="n">
-        <v>-0.3</v>
+        <v>2.36</v>
       </c>
       <c r="J7" s="1" t="n">
-        <v>-4.2</v>
+        <v>-0.72</v>
       </c>
       <c r="K7" s="1" t="n">
-        <v>4.01</v>
+        <v>4.93</v>
       </c>
       <c r="L7" s="1" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         </is>
       </c>
       <c r="M7" s="1" t="n">
-        <v>-4.37</v>
+        <v>-23.25</v>
       </c>
       <c r="N7" s="1" t="inlineStr">
         <is>
@@ -935,53 +935,53 @@
       </c>
       <c r="Q7" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Auto</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
         <v>7</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>12</v>
+        <v>-3</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>32.3</v>
+        <v>282.4</v>
       </c>
       <c r="H8" s="1" t="n">
-        <v>0.4</v>
+        <v>1.47</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>2.37</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="J8" s="1" t="n">
-        <v>0.2</v>
+        <v>-3.45</v>
       </c>
       <c r="K8" s="1" t="n">
-        <v>3.85</v>
+        <v>4.81</v>
       </c>
       <c r="L8" s="1" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Down</t>
         </is>
       </c>
       <c r="M8" s="1" t="n">
-        <v>-23.05</v>
+        <v>-3.85</v>
       </c>
       <c r="N8" s="1" t="inlineStr">
         <is>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="Q8" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
         <v>8</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>-1</v>
@@ -1023,22 +1023,22 @@
         <v>-3</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>31.21</v>
+        <v>31.69</v>
       </c>
       <c r="H9" s="1" t="n">
-        <v>-2.19</v>
+        <v>0.67</v>
       </c>
       <c r="I9" s="1" t="n">
-        <v>-1.27</v>
+        <v>-0.04</v>
       </c>
       <c r="J9" s="1" t="n">
-        <v>-4.18</v>
+        <v>-2.9</v>
       </c>
       <c r="K9" s="1" t="n">
-        <v>2.86</v>
+        <v>4.04</v>
       </c>
       <c r="L9" s="1" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="M9" s="1" t="n">
-        <v>-4.51</v>
+        <v>-3.56</v>
       </c>
       <c r="N9" s="1" t="inlineStr">
         <is>
@@ -1072,46 +1072,46 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Consumption</t>
+          <t>Metal</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
         <v>9</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>127.09</v>
+        <v>12.97</v>
       </c>
       <c r="H10" s="1" t="n">
-        <v>0.52</v>
+        <v>1.57</v>
       </c>
       <c r="I10" s="1" t="n">
-        <v>0.51</v>
+        <v>-1.5</v>
       </c>
       <c r="J10" s="1" t="n">
-        <v>-1.35</v>
+        <v>2.6</v>
       </c>
       <c r="K10" s="1" t="n">
         <v>1.65</v>
       </c>
       <c r="L10" s="1" t="inlineStr">
         <is>
-          <t>Down</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="M10" s="1" t="n">
-        <v>-5.14</v>
+        <v>-5.62</v>
       </c>
       <c r="N10" s="1" t="inlineStr">
         <is>
@@ -1130,53 +1130,53 @@
       </c>
       <c r="Q10" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>Metal</t>
+          <t>Fin Services</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
         <v>10</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>2</v>
+        <v>-4</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>13</v>
+        <v>-1</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-4</v>
+        <v>4</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>12.85</v>
+        <v>31.93</v>
       </c>
       <c r="H11" s="1" t="n">
-        <v>-1.91</v>
+        <v>0.92</v>
       </c>
       <c r="I11" s="1" t="n">
-        <v>-2.58</v>
+        <v>-0.03</v>
       </c>
       <c r="J11" s="1" t="n">
-        <v>2.34</v>
+        <v>-0.12</v>
       </c>
       <c r="K11" s="1" t="n">
-        <v>0.68</v>
+        <v>1.39</v>
       </c>
       <c r="L11" s="1" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Down</t>
         </is>
       </c>
       <c r="M11" s="1" t="n">
-        <v>-5.99</v>
+        <v>-1.5</v>
       </c>
       <c r="N11" s="1" t="inlineStr">
         <is>
@@ -1195,53 +1195,53 @@
       </c>
       <c r="Q11" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Bank</t>
+          <t>Manufacturing</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
         <v>11</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>582.6799999999999</v>
+        <v>161.14</v>
       </c>
       <c r="H12" s="1" t="n">
-        <v>-0.63</v>
+        <v>1.1</v>
       </c>
       <c r="I12" s="1" t="n">
+        <v>-0.39</v>
+      </c>
+      <c r="J12" s="1" t="n">
+        <v>-0.8100000000000001</v>
+      </c>
+      <c r="K12" s="1" t="n">
         <v>1.34</v>
       </c>
-      <c r="J12" s="1" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="K12" s="1" t="n">
-        <v>0.67</v>
-      </c>
       <c r="L12" s="1" t="inlineStr">
         <is>
           <t>Up</t>
         </is>
       </c>
       <c r="M12" s="1" t="n">
-        <v>-4.42</v>
+        <v>-1.2</v>
       </c>
       <c r="N12" s="1" t="inlineStr">
         <is>
@@ -1260,53 +1260,53 @@
       </c>
       <c r="Q12" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Tourism</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
         <v>12</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>9</v>
+        <v>-4</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>3</v>
+        <v>-2</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>6</v>
+        <v>-5</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>11</v>
+        <v>-3</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>30.11</v>
+        <v>76.53</v>
       </c>
       <c r="H13" s="1" t="n">
-        <v>-0.73</v>
+        <v>1.67</v>
       </c>
       <c r="I13" s="1" t="n">
-        <v>1.66</v>
+        <v>1.25</v>
       </c>
       <c r="J13" s="1" t="n">
-        <v>0.99</v>
+        <v>-0.55</v>
       </c>
       <c r="K13" s="1" t="n">
-        <v>0.63</v>
+        <v>1.04</v>
       </c>
       <c r="L13" s="1" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Down</t>
         </is>
       </c>
       <c r="M13" s="1" t="n">
-        <v>0</v>
+        <v>-14.93</v>
       </c>
       <c r="N13" s="1" t="inlineStr">
         <is>
@@ -1332,38 +1332,38 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Fin Services</t>
+          <t>Consumption</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
         <v>13</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>7</v>
+        <v>-2</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>31.61</v>
+        <v>126.99</v>
       </c>
       <c r="H14" s="1" t="n">
-        <v>-2.44</v>
+        <v>-0.08</v>
       </c>
       <c r="I14" s="1" t="n">
-        <v>-0.34</v>
+        <v>0.25</v>
       </c>
       <c r="J14" s="1" t="n">
-        <v>-0.61</v>
+        <v>-1.75</v>
       </c>
       <c r="K14" s="1" t="n">
-        <v>0.62</v>
+        <v>0.87</v>
       </c>
       <c r="L14" s="1" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         </is>
       </c>
       <c r="M14" s="1" t="n">
-        <v>-2.67</v>
+        <v>-5.72</v>
       </c>
       <c r="N14" s="1" t="inlineStr">
         <is>
@@ -1397,46 +1397,46 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>Tourism</t>
+          <t>Private Bank</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
         <v>14</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>-5</v>
+        <v>7</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>-6</v>
+        <v>-2</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>-7</v>
+        <v>-1</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>75.02</v>
+        <v>27.74</v>
       </c>
       <c r="H15" s="1" t="n">
-        <v>-2.38</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="I15" s="1" t="n">
-        <v>-0.97</v>
+        <v>1.31</v>
       </c>
       <c r="J15" s="1" t="n">
-        <v>-2.08</v>
+        <v>3.12</v>
       </c>
       <c r="K15" s="1" t="n">
-        <v>0.57</v>
+        <v>-0.02</v>
       </c>
       <c r="L15" s="1" t="inlineStr">
         <is>
-          <t>Down</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="M15" s="1" t="n">
-        <v>-16.62</v>
+        <v>-3.41</v>
       </c>
       <c r="N15" s="1" t="inlineStr">
         <is>
@@ -1462,38 +1462,38 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Manufacturing</t>
+          <t>Defence</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
         <v>15</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>-4</v>
+        <v>-11</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>3</v>
+        <v>-7</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>-3</v>
+        <v>-7</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>0</v>
+        <v>-14</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>159.39</v>
+        <v>101.87</v>
       </c>
       <c r="H16" s="1" t="n">
-        <v>0.26</v>
+        <v>1.1</v>
       </c>
       <c r="I16" s="1" t="n">
-        <v>-1.74</v>
+        <v>-4.1</v>
       </c>
       <c r="J16" s="1" t="n">
-        <v>-1.72</v>
+        <v>-2.58</v>
       </c>
       <c r="K16" s="1" t="n">
-        <v>0.53</v>
+        <v>-0.05</v>
       </c>
       <c r="L16" s="1" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         </is>
       </c>
       <c r="M16" s="1" t="n">
-        <v>-1.74</v>
+        <v>-5.3</v>
       </c>
       <c r="N16" s="1" t="inlineStr">
         <is>
@@ -1527,38 +1527,38 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Services</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
         <v>16</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>-2</v>
+        <v>3</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>1</v>
       </c>
       <c r="E17" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="G17" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="H17" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="F17" s="2" t="n">
-        <v>-9</v>
-      </c>
-      <c r="G17" s="1" t="n">
-        <v>28.97</v>
-      </c>
-      <c r="H17" s="1" t="n">
-        <v>-3.01</v>
-      </c>
       <c r="I17" s="1" t="n">
-        <v>-1.93</v>
+        <v>0.88</v>
       </c>
       <c r="J17" s="1" t="n">
-        <v>-1.25</v>
+        <v>0.16</v>
       </c>
       <c r="K17" s="1" t="n">
-        <v>0.38</v>
+        <v>-0.32</v>
       </c>
       <c r="L17" s="1" t="inlineStr">
         <is>
@@ -1592,38 +1592,38 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>Private Bank</t>
+          <t>Bank</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
         <v>17</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>-8</v>
+        <v>-6</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>-2</v>
+        <v>-7</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-5</v>
+        <v>1</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>27.8</v>
+        <v>581.64</v>
       </c>
       <c r="H18" s="1" t="n">
-        <v>-0.5</v>
+        <v>0.4</v>
       </c>
       <c r="I18" s="1" t="n">
-        <v>1.57</v>
+        <v>0.99</v>
       </c>
       <c r="J18" s="1" t="n">
-        <v>4.02</v>
+        <v>1.21</v>
       </c>
       <c r="K18" s="1" t="n">
-        <v>0.36</v>
+        <v>-0.33</v>
       </c>
       <c r="L18" s="1" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         </is>
       </c>
       <c r="M18" s="1" t="n">
-        <v>-2.68</v>
+        <v>-5.11</v>
       </c>
       <c r="N18" s="1" t="inlineStr">
         <is>
@@ -1657,38 +1657,38 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>Defence</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
         <v>18</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>-13</v>
+        <v>-5</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>-8</v>
+        <v>-3</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>-12</v>
+        <v>-3</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>-17</v>
+        <v>-11</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>100.52</v>
+        <v>29.06</v>
       </c>
       <c r="H19" s="1" t="n">
-        <v>-5.82</v>
+        <v>-0.62</v>
       </c>
       <c r="I19" s="1" t="n">
-        <v>-5.92</v>
+        <v>-2.02</v>
       </c>
       <c r="J19" s="1" t="n">
-        <v>-4.54</v>
+        <v>-1.45</v>
       </c>
       <c r="K19" s="1" t="n">
-        <v>-1</v>
+        <v>-0.41</v>
       </c>
       <c r="L19" s="1" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         </is>
       </c>
       <c r="M19" s="1" t="n">
-        <v>-6.05</v>
+        <v>0</v>
       </c>
       <c r="N19" s="1" t="inlineStr">
         <is>
@@ -1715,53 +1715,53 @@
       </c>
       <c r="Q19" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas</t>
+          <t>MNC</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
         <v>19</v>
       </c>
       <c r="C20" s="2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="D20" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D20" s="2" t="n">
-        <v>2</v>
-      </c>
       <c r="E20" s="2" t="n">
-        <v>3</v>
+        <v>-3</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>7</v>
+        <v>-9</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>11.06</v>
+        <v>32.29</v>
       </c>
       <c r="H20" s="1" t="n">
-        <v>-0.98</v>
+        <v>0.34</v>
       </c>
       <c r="I20" s="1" t="n">
-        <v>0.26</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="J20" s="1" t="n">
-        <v>1.16</v>
+        <v>-2.22</v>
       </c>
       <c r="K20" s="1" t="n">
-        <v>-1.02</v>
+        <v>-1.03</v>
       </c>
       <c r="L20" s="1" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Down</t>
         </is>
       </c>
       <c r="M20" s="1" t="n">
-        <v>-8.460000000000001</v>
+        <v>-4.37</v>
       </c>
       <c r="N20" s="1" t="inlineStr">
         <is>
@@ -1787,7 +1787,7 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>MNC</t>
+          <t>Oil &amp; Gas</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
@@ -1797,36 +1797,36 @@
         <v>0</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>-6</v>
+        <v>3</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>-12</v>
+        <v>6</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>32.09</v>
+        <v>11.02</v>
       </c>
       <c r="H21" s="1" t="n">
-        <v>-1.9</v>
+        <v>0.18</v>
       </c>
       <c r="I21" s="1" t="n">
-        <v>-0.58</v>
+        <v>-0.05</v>
       </c>
       <c r="J21" s="1" t="n">
-        <v>-3.1</v>
+        <v>0.4</v>
       </c>
       <c r="K21" s="1" t="n">
-        <v>-1.64</v>
+        <v>-1.41</v>
       </c>
       <c r="L21" s="1" t="inlineStr">
         <is>
-          <t>Down</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="M21" s="1" t="n">
-        <v>-4.44</v>
+        <v>-9.279999999999999</v>
       </c>
       <c r="N21" s="1" t="inlineStr">
         <is>
@@ -1852,38 +1852,38 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>PSE</t>
+          <t>Capital Market</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
         <v>21</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>5</v>
+        <v>-5</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>5</v>
+        <v>-20</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>4</v>
+        <v>-18</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>10</v>
+        <v>53.1</v>
       </c>
       <c r="H22" s="1" t="n">
-        <v>-1.09</v>
+        <v>0.47</v>
       </c>
       <c r="I22" s="1" t="n">
-        <v>-0.01</v>
+        <v>0.31</v>
       </c>
       <c r="J22" s="1" t="n">
-        <v>2.03</v>
+        <v>2.59</v>
       </c>
       <c r="K22" s="1" t="n">
-        <v>-2.23</v>
+        <v>-2.31</v>
       </c>
       <c r="L22" s="1" t="inlineStr">
         <is>
@@ -1891,7 +1891,7 @@
         </is>
       </c>
       <c r="M22" s="1" t="n">
-        <v>-9.630000000000001</v>
+        <v>0</v>
       </c>
       <c r="N22" s="1" t="inlineStr">
         <is>
@@ -1917,38 +1917,38 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>Capital Market</t>
+          <t>Commodities</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
         <v>22</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>-7</v>
+        <v>3</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>-2</v>
+        <v>3</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>-19</v>
+        <v>2</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>-19</v>
+        <v>-3</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>52.57</v>
+        <v>97.15000000000001</v>
       </c>
       <c r="H23" s="1" t="n">
-        <v>-2.63</v>
+        <v>0.61</v>
       </c>
       <c r="I23" s="1" t="n">
-        <v>-0.79</v>
+        <v>-0.15</v>
       </c>
       <c r="J23" s="1" t="n">
-        <v>2.63</v>
+        <v>1.15</v>
       </c>
       <c r="K23" s="1" t="n">
-        <v>-2.25</v>
+        <v>-2.83</v>
       </c>
       <c r="L23" s="1" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         </is>
       </c>
       <c r="M23" s="1" t="n">
-        <v>0</v>
+        <v>-8.4</v>
       </c>
       <c r="N23" s="1" t="inlineStr">
         <is>
@@ -1982,46 +1982,46 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Commodities</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
         <v>23</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>3</v>
+        <v>-3</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>-5</v>
+        <v>-7</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>96.56</v>
+        <v>92.3</v>
       </c>
       <c r="H24" s="1" t="n">
-        <v>0.33</v>
+        <v>0.47</v>
       </c>
       <c r="I24" s="1" t="n">
-        <v>-0.93</v>
+        <v>-0.03</v>
       </c>
       <c r="J24" s="1" t="n">
-        <v>0.76</v>
+        <v>-0.29</v>
       </c>
       <c r="K24" s="1" t="n">
-        <v>-2.99</v>
+        <v>-3.35</v>
       </c>
       <c r="L24" s="1" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Down</t>
         </is>
       </c>
       <c r="M24" s="1" t="n">
-        <v>-8.460000000000001</v>
+        <v>-4.93</v>
       </c>
       <c r="N24" s="1" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         <v>24</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D25" s="2" t="n">
         <v>-8</v>
@@ -2063,22 +2063,22 @@
         <v>-15</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>92.20999999999999</v>
+        <v>92.38</v>
       </c>
       <c r="H25" s="1" t="n">
-        <v>-1.08</v>
+        <v>1.24</v>
       </c>
       <c r="I25" s="1" t="n">
-        <v>0.4</v>
+        <v>0.06</v>
       </c>
       <c r="J25" s="1" t="n">
-        <v>-0.48</v>
+        <v>-0.8</v>
       </c>
       <c r="K25" s="1" t="n">
-        <v>-3.03</v>
+        <v>-3.65</v>
       </c>
       <c r="L25" s="1" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         </is>
       </c>
       <c r="M25" s="1" t="n">
-        <v>-13.15</v>
+        <v>-13.46</v>
       </c>
       <c r="N25" s="1" t="inlineStr">
         <is>
@@ -2112,46 +2112,46 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>PSE</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
         <v>25</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>-4</v>
+        <v>2</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>-8</v>
+        <v>0</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>91.87</v>
+        <v>9.93</v>
       </c>
       <c r="H26" s="1" t="n">
-        <v>-0.04</v>
+        <v>0</v>
       </c>
       <c r="I26" s="1" t="n">
-        <v>-0.32</v>
+        <v>-0.78</v>
       </c>
       <c r="J26" s="1" t="n">
-        <v>-0.86</v>
+        <v>1.19</v>
       </c>
       <c r="K26" s="1" t="n">
-        <v>-3.36</v>
+        <v>-3.95</v>
       </c>
       <c r="L26" s="1" t="inlineStr">
         <is>
-          <t>Down</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="M26" s="1" t="n">
-        <v>-4.85</v>
+        <v>-10.75</v>
       </c>
       <c r="N26" s="1" t="inlineStr">
         <is>
@@ -2184,31 +2184,31 @@
         <v>26</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D27" s="2" t="n">
         <v>1</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>-17</v>
+        <v>-18</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>37.45</v>
+        <v>37.53</v>
       </c>
       <c r="H27" s="1" t="n">
-        <v>-1.6</v>
+        <v>0.13</v>
       </c>
       <c r="I27" s="1" t="n">
-        <v>-1.4</v>
+        <v>-0.33</v>
       </c>
       <c r="J27" s="1" t="n">
-        <v>0.6</v>
+        <v>1.05</v>
       </c>
       <c r="K27" s="1" t="n">
-        <v>-4.64</v>
+        <v>-5.12</v>
       </c>
       <c r="L27" s="1" t="inlineStr">
         <is>
@@ -2252,28 +2252,28 @@
         <v>0</v>
       </c>
       <c r="D28" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F28" s="2" t="n">
         <v>-3</v>
       </c>
-      <c r="E28" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F28" s="2" t="n">
-        <v>-5</v>
-      </c>
       <c r="G28" s="1" t="n">
-        <v>49.14</v>
+        <v>49.12</v>
       </c>
       <c r="H28" s="1" t="n">
-        <v>1.34</v>
+        <v>-0.04</v>
       </c>
       <c r="I28" s="1" t="n">
-        <v>2.42</v>
+        <v>2.29</v>
       </c>
       <c r="J28" s="1" t="n">
-        <v>-0.31</v>
+        <v>-0.67</v>
       </c>
       <c r="K28" s="1" t="n">
-        <v>-4.91</v>
+        <v>-5.15</v>
       </c>
       <c r="L28" s="1" t="inlineStr">
         <is>
@@ -2281,7 +2281,7 @@
         </is>
       </c>
       <c r="M28" s="1" t="n">
-        <v>-15.56</v>
+        <v>-16.05</v>
       </c>
       <c r="N28" s="1" t="inlineStr">
         <is>
@@ -2569,23 +2569,23 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E2" s="1" t="n">
         <v>24</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G2" s="1" t="n">
         <v>27</v>
@@ -2597,46 +2597,46 @@
         <v>4</v>
       </c>
       <c r="J2" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K2" s="1" t="n">
         <v>5</v>
       </c>
       <c r="L2" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="M2" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="N2" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="M2" s="1" t="n">
+      <c r="O2" s="1" t="n">
         <v>25</v>
-      </c>
-      <c r="N2" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="O2" s="1" t="n">
-        <v>21</v>
       </c>
       <c r="P2" s="1" t="n">
         <v>26</v>
       </c>
       <c r="Q2" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R2" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="S2" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="T2" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="S2" s="1" t="n">
+      <c r="U2" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="T2" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="U2" s="1" t="n">
-        <v>16</v>
-      </c>
       <c r="V2" s="1" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="W2" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="X2" s="1" t="n">
         <v>3</v>
@@ -2645,10 +2645,10 @@
         <v>1</v>
       </c>
       <c r="Z2" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AA2" s="1" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AB2" s="1" t="n">
         <v>8</v>
@@ -2657,20 +2657,20 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F3" s="1" t="n">
         <v>8</v>
@@ -2685,43 +2685,43 @@
         <v>4</v>
       </c>
       <c r="J3" s="1" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="K3" s="1" t="n">
         <v>6</v>
       </c>
       <c r="L3" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M3" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N3" s="1" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="O3" s="1" t="n">
         <v>22</v>
       </c>
       <c r="P3" s="1" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="Q3" s="1" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="R3" s="1" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="S3" s="1" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="T3" s="1" t="n">
         <v>20</v>
       </c>
       <c r="U3" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="V3" s="1" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="W3" s="1" t="n">
         <v>21</v>
@@ -2733,10 +2733,10 @@
         <v>1</v>
       </c>
       <c r="Z3" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA3" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AB3" s="1" t="n">
         <v>7</v>
@@ -2745,11 +2745,11 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C4" s="1" t="n">
         <v>16</v>
@@ -2758,7 +2758,7 @@
         <v>18</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>9</v>
@@ -2770,22 +2770,22 @@
         <v>2</v>
       </c>
       <c r="I4" s="1" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J4" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="K4" s="1" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L4" s="1" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="M4" s="1" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="N4" s="1" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="O4" s="1" t="n">
         <v>21</v>
@@ -2797,22 +2797,22 @@
         <v>25</v>
       </c>
       <c r="R4" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="S4" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="T4" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="S4" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="T4" s="1" t="n">
-        <v>19</v>
-      </c>
       <c r="U4" s="1" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="V4" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="W4" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="X4" s="1" t="n">
         <v>3</v>
@@ -2821,62 +2821,62 @@
         <v>1</v>
       </c>
       <c r="Z4" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AA4" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AB4" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E5" s="1" t="n">
         <v>24</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G5" s="1" t="n">
         <v>27</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I5" s="1" t="n">
         <v>6</v>
       </c>
       <c r="J5" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K5" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L5" s="1" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="M5" s="1" t="n">
         <v>22</v>
       </c>
       <c r="N5" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O5" s="1" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="P5" s="1" t="n">
         <v>26</v>
@@ -2885,86 +2885,86 @@
         <v>25</v>
       </c>
       <c r="R5" s="1" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="S5" s="1" t="n">
         <v>5</v>
       </c>
       <c r="T5" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="U5" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="V5" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="V5" s="1" t="n">
-        <v>13</v>
-      </c>
       <c r="W5" s="1" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="X5" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y5" s="1" t="n">
         <v>1</v>
       </c>
       <c r="Z5" s="1" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AA5" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AB5" s="1" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D6" s="1" t="n">
         <v>21</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G6" s="1" t="n">
         <v>27</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I6" s="1" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J6" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K6" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L6" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M6" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N6" s="1" t="n">
         <v>12</v>
       </c>
       <c r="O6" s="1" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="P6" s="1" t="n">
         <v>26</v>
@@ -2973,110 +2973,110 @@
         <v>25</v>
       </c>
       <c r="R6" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="S6" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T6" s="1" t="n">
         <v>20</v>
       </c>
       <c r="U6" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="V6" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="V6" s="1" t="n">
-        <v>11</v>
-      </c>
       <c r="W6" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="X6" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y6" s="1" t="n">
         <v>1</v>
       </c>
       <c r="Z6" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA6" s="1" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AB6" s="1" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="C7" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="C7" s="1" t="n">
-        <v>16</v>
-      </c>
       <c r="D7" s="1" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G7" s="1" t="n">
         <v>27</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I7" s="1" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J7" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K7" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M7" s="1" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N7" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="O7" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="P7" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q7" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="R7" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="S7" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="T7" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="U7" s="1" t="n">
         <v>13</v>
-      </c>
-      <c r="O7" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="P7" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="Q7" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="R7" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="S7" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="T7" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="U7" s="1" t="n">
-        <v>14</v>
       </c>
       <c r="V7" s="1" t="n">
         <v>11</v>
       </c>
       <c r="W7" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="X7" s="1" t="n">
         <v>3</v>
@@ -3085,29 +3085,29 @@
         <v>1</v>
       </c>
       <c r="Z7" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA7" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="AB7" s="1" t="n">
         <v>9</v>
-      </c>
-      <c r="AA7" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="AB7" s="1" t="n">
-        <v>10</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="C8" s="1" t="n">
         <v>16</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E8" s="1" t="n">
         <v>23</v>
@@ -3125,46 +3125,46 @@
         <v>7</v>
       </c>
       <c r="J8" s="1" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="K8" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M8" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N8" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O8" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="P8" s="1" t="n">
         <v>25</v>
-      </c>
-      <c r="P8" s="1" t="n">
-        <v>26</v>
       </c>
       <c r="Q8" s="1" t="n">
         <v>24</v>
       </c>
       <c r="R8" s="1" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="S8" s="1" t="n">
         <v>5</v>
       </c>
       <c r="T8" s="1" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="U8" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="V8" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="W8" s="1" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="X8" s="1" t="n">
         <v>3</v>
@@ -3173,10 +3173,10 @@
         <v>1</v>
       </c>
       <c r="Z8" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA8" s="1" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AB8" s="1" t="n">
         <v>10</v>
@@ -3185,59 +3185,59 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F9" s="1" t="n">
         <v>6</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H9" s="1" t="n">
         <v>4</v>
       </c>
       <c r="I9" s="1" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J9" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K9" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L9" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M9" s="1" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N9" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="O9" s="1" t="n">
         <v>25</v>
       </c>
       <c r="P9" s="1" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Q9" s="1" t="n">
         <v>24</v>
       </c>
       <c r="R9" s="1" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="S9" s="1" t="n">
         <v>5</v>
@@ -3249,10 +3249,10 @@
         <v>13</v>
       </c>
       <c r="V9" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="W9" s="1" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="X9" s="1" t="n">
         <v>3</v>
@@ -3261,35 +3261,35 @@
         <v>1</v>
       </c>
       <c r="Z9" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA9" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AB9" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="C10" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="C10" s="1" t="n">
-        <v>10</v>
-      </c>
       <c r="D10" s="1" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G10" s="1" t="n">
         <v>26</v>
@@ -3298,22 +3298,22 @@
         <v>4</v>
       </c>
       <c r="I10" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J10" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K10" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L10" s="1" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M10" s="1" t="n">
         <v>23</v>
       </c>
       <c r="N10" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O10" s="1" t="n">
         <v>25</v>
@@ -3325,22 +3325,22 @@
         <v>24</v>
       </c>
       <c r="R10" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="S10" s="1" t="n">
         <v>5</v>
       </c>
       <c r="T10" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="U10" s="1" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="V10" s="1" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="W10" s="1" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="X10" s="1" t="n">
         <v>3</v>
@@ -3352,32 +3352,32 @@
         <v>7</v>
       </c>
       <c r="AA10" s="1" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="AB10" s="1" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G11" s="1" t="n">
         <v>26</v>
@@ -3386,49 +3386,49 @@
         <v>4</v>
       </c>
       <c r="I11" s="1" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="J11" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K11" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="M11" s="1" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="N11" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O11" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="P11" s="1" t="n">
         <v>27</v>
       </c>
       <c r="Q11" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R11" s="1" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="S11" s="1" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T11" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="U11" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="V11" s="1" t="n">
         <v>18</v>
       </c>
       <c r="W11" s="1" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="X11" s="1" t="n">
         <v>3</v>
@@ -3437,19 +3437,19 @@
         <v>1</v>
       </c>
       <c r="Z11" s="1" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AA11" s="1" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AB11" s="1" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
@@ -3459,7 +3459,7 @@
         <v>11</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E12" s="1" t="n">
         <v>16</v>
@@ -3468,7 +3468,7 @@
         <v>6</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H12" s="1" t="n">
         <v>4</v>
@@ -3483,40 +3483,40 @@
         <v>2</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="M12" s="1" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="N12" s="1" t="n">
         <v>14</v>
       </c>
       <c r="O12" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P12" s="1" t="n">
         <v>27</v>
       </c>
       <c r="Q12" s="1" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="R12" s="1" t="n">
         <v>19</v>
       </c>
       <c r="S12" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T12" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="U12" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="V12" s="1" t="n">
         <v>18</v>
       </c>
       <c r="W12" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="X12" s="1" t="n">
         <v>3</v>
@@ -3525,10 +3525,10 @@
         <v>1</v>
       </c>
       <c r="Z12" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA12" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AB12" s="1" t="n">
         <v>7</v>
@@ -3537,29 +3537,29 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F13" s="1" t="n">
         <v>6</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H13" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I13" s="1" t="n">
         <v>5</v>
@@ -3571,16 +3571,16 @@
         <v>2</v>
       </c>
       <c r="L13" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M13" s="1" t="n">
         <v>22</v>
       </c>
       <c r="N13" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="O13" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="P13" s="1" t="n">
         <v>27</v>
@@ -3589,34 +3589,34 @@
         <v>26</v>
       </c>
       <c r="R13" s="1" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="S13" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T13" s="1" t="n">
         <v>21</v>
       </c>
       <c r="U13" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="V13" s="1" t="n">
         <v>18</v>
-      </c>
-      <c r="V13" s="1" t="n">
-        <v>15</v>
       </c>
       <c r="W13" s="1" t="n">
         <v>20</v>
       </c>
       <c r="X13" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y13" s="1" t="n">
         <v>1</v>
       </c>
       <c r="Z13" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA13" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AB13" s="1" t="n">
         <v>7</v>
@@ -3625,7 +3625,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
@@ -3635,22 +3635,22 @@
         <v>10</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F14" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="G14" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="H14" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="G14" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="H14" s="1" t="n">
+      <c r="I14" s="1" t="n">
         <v>5</v>
-      </c>
-      <c r="I14" s="1" t="n">
-        <v>6</v>
       </c>
       <c r="J14" s="1" t="n">
         <v>23</v>
@@ -3659,37 +3659,37 @@
         <v>2</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M14" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="N14" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="O14" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="P14" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q14" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="R14" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="S14" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="T14" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="N14" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="O14" s="1" t="n">
-        <v>27</v>
-      </c>
-      <c r="P14" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="Q14" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="R14" s="1" t="n">
+      <c r="U14" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="S14" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="T14" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="U14" s="1" t="n">
+      <c r="V14" s="1" t="n">
         <v>15</v>
-      </c>
-      <c r="V14" s="1" t="n">
-        <v>17</v>
       </c>
       <c r="W14" s="1" t="n">
         <v>20</v>
@@ -3701,7 +3701,7 @@
         <v>1</v>
       </c>
       <c r="Z14" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA14" s="1" t="n">
         <v>16</v>
@@ -3713,77 +3713,77 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D15" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="E15" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="E15" s="1" t="n">
-        <v>14</v>
-      </c>
       <c r="F15" s="1" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G15" s="1" t="n">
         <v>24</v>
       </c>
       <c r="H15" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I15" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J15" s="1" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="K15" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L15" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="M15" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="N15" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="O15" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="P15" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q15" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="R15" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="S15" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="T15" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="U15" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="V15" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="M15" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="N15" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="O15" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="P15" s="1" t="n">
-        <v>27</v>
-      </c>
-      <c r="Q15" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="R15" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="S15" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="T15" s="1" t="n">
-        <v>23</v>
-      </c>
-      <c r="U15" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="V15" s="1" t="n">
-        <v>16</v>
-      </c>
       <c r="W15" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="X15" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y15" s="1" t="n">
         <v>1</v>
@@ -3792,26 +3792,26 @@
         <v>8</v>
       </c>
       <c r="AA15" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AB15" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="C16" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="C16" s="1" t="n">
-        <v>10</v>
-      </c>
       <c r="D16" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E16" s="1" t="n">
         <v>14</v>
@@ -3829,34 +3829,34 @@
         <v>7</v>
       </c>
       <c r="J16" s="1" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K16" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L16" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M16" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N16" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="O16" s="1" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P16" s="1" t="n">
         <v>27</v>
       </c>
       <c r="Q16" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="R16" s="1" t="n">
         <v>19</v>
       </c>
       <c r="S16" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T16" s="1" t="n">
         <v>23</v>
@@ -3868,7 +3868,7 @@
         <v>16</v>
       </c>
       <c r="W16" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="X16" s="1" t="n">
         <v>3</v>
@@ -3877,47 +3877,47 @@
         <v>1</v>
       </c>
       <c r="Z16" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA16" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="AB16" s="1" t="n">
         <v>6</v>
-      </c>
-      <c r="AA16" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="AB16" s="1" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
         <v>11</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D17" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="E17" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="E17" s="1" t="n">
-        <v>12</v>
-      </c>
       <c r="F17" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G17" s="1" t="n">
         <v>24</v>
       </c>
       <c r="H17" s="1" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I17" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J17" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K17" s="1" t="n">
         <v>2</v>
@@ -3926,7 +3926,7 @@
         <v>15</v>
       </c>
       <c r="M17" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N17" s="1" t="n">
         <v>13</v>
@@ -3944,7 +3944,7 @@
         <v>19</v>
       </c>
       <c r="S17" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T17" s="1" t="n">
         <v>23</v>
@@ -3953,7 +3953,7 @@
         <v>18</v>
       </c>
       <c r="V17" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="W17" s="1" t="n">
         <v>20</v>
@@ -3965,32 +3965,32 @@
         <v>1</v>
       </c>
       <c r="Z17" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA17" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AB17" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C18" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="E18" s="1" t="n">
         <v>12</v>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>13</v>
       </c>
       <c r="F18" s="1" t="n">
         <v>4</v>
@@ -3999,10 +3999,10 @@
         <v>24</v>
       </c>
       <c r="H18" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I18" s="1" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J18" s="1" t="n">
         <v>21</v>
@@ -4011,40 +4011,40 @@
         <v>2</v>
       </c>
       <c r="L18" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="M18" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="N18" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="O18" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="P18" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q18" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="R18" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="S18" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="U18" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="M18" s="1" t="n">
+      <c r="V18" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="W18" s="1" t="n">
         <v>20</v>
-      </c>
-      <c r="N18" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="O18" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="P18" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="Q18" s="1" t="n">
-        <v>27</v>
-      </c>
-      <c r="R18" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="S18" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="T18" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="U18" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="V18" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="W18" s="1" t="n">
-        <v>23</v>
       </c>
       <c r="X18" s="1" t="n">
         <v>3</v>
@@ -4053,38 +4053,38 @@
         <v>1</v>
       </c>
       <c r="Z18" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA18" s="1" t="n">
         <v>16</v>
       </c>
       <c r="AB18" s="1" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C19" s="1" t="n">
         <v>12</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F19" s="1" t="n">
         <v>4</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H19" s="1" t="n">
         <v>7</v>
@@ -4093,7 +4093,7 @@
         <v>11</v>
       </c>
       <c r="J19" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K19" s="1" t="n">
         <v>2</v>
@@ -4102,25 +4102,25 @@
         <v>18</v>
       </c>
       <c r="M19" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="N19" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="O19" s="1" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="P19" s="1" t="n">
         <v>26</v>
       </c>
       <c r="Q19" s="1" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="R19" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="S19" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T19" s="1" t="n">
         <v>22</v>
@@ -4129,7 +4129,7 @@
         <v>19</v>
       </c>
       <c r="V19" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="W19" s="1" t="n">
         <v>23</v>
@@ -4144,7 +4144,7 @@
         <v>6</v>
       </c>
       <c r="AA19" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AB19" s="1" t="n">
         <v>5</v>
@@ -4153,47 +4153,47 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C20" s="1" t="n">
         <v>12</v>
       </c>
       <c r="D20" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="E20" s="1" t="n">
         <v>15</v>
-      </c>
-      <c r="E20" s="1" t="n">
-        <v>10</v>
       </c>
       <c r="F20" s="1" t="n">
         <v>4</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H20" s="1" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I20" s="1" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J20" s="1" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K20" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L20" s="1" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M20" s="1" t="n">
         <v>21</v>
       </c>
       <c r="N20" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O20" s="1" t="n">
         <v>27</v>
@@ -4202,59 +4202,59 @@
         <v>26</v>
       </c>
       <c r="Q20" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R20" s="1" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="S20" s="1" t="n">
         <v>8</v>
       </c>
       <c r="T20" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="U20" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="V20" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="W20" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="U20" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="V20" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="W20" s="1" t="n">
+      <c r="X20" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y20" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="X20" s="1" t="n">
+      <c r="Z20" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA20" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="AB20" s="1" t="n">
         <v>5</v>
-      </c>
-      <c r="Y20" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z20" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA20" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="AB20" s="1" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
         <v>13</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D21" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F21" s="1" t="n">
         <v>4</v>
@@ -4263,13 +4263,13 @@
         <v>24</v>
       </c>
       <c r="H21" s="1" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I21" s="1" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="J21" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K21" s="1" t="n">
         <v>3</v>
@@ -4293,25 +4293,25 @@
         <v>25</v>
       </c>
       <c r="R21" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="S21" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="T21" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="U21" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="V21" s="1" t="n">
         <v>16</v>
-      </c>
-      <c r="S21" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="T21" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="U21" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="V21" s="1" t="n">
-        <v>15</v>
       </c>
       <c r="W21" s="1" t="n">
         <v>1</v>
       </c>
       <c r="X21" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y21" s="1" t="n">
         <v>2</v>
@@ -4320,26 +4320,26 @@
         <v>7</v>
       </c>
       <c r="AA21" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AB21" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D22" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E22" s="1" t="n">
         <v>9</v>
@@ -4348,22 +4348,22 @@
         <v>4</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H22" s="1" t="n">
         <v>12</v>
       </c>
       <c r="I22" s="1" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J22" s="1" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K22" s="1" t="n">
         <v>3</v>
       </c>
       <c r="L22" s="1" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="M22" s="1" t="n">
         <v>21</v>
@@ -4375,25 +4375,25 @@
         <v>27</v>
       </c>
       <c r="P22" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q22" s="1" t="n">
         <v>25</v>
-      </c>
-      <c r="Q22" s="1" t="n">
-        <v>24</v>
       </c>
       <c r="R22" s="1" t="n">
         <v>16</v>
       </c>
       <c r="S22" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T22" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="U22" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="V22" s="1" t="n">
         <v>15</v>
-      </c>
-      <c r="V22" s="1" t="n">
-        <v>14</v>
       </c>
       <c r="W22" s="1" t="n">
         <v>1</v>
@@ -4417,38 +4417,38 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C23" s="1" t="n">
         <v>10</v>
       </c>
       <c r="D23" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E23" s="1" t="n">
         <v>9</v>
       </c>
       <c r="F23" s="1" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H23" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I23" s="1" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J23" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K23" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L23" s="1" t="n">
         <v>20</v>
@@ -4460,37 +4460,37 @@
         <v>11</v>
       </c>
       <c r="O23" s="1" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P23" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q23" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="Q23" s="1" t="n">
-        <v>25</v>
-      </c>
       <c r="R23" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="S23" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="T23" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="U23" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="V23" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="S23" s="1" t="n">
+      <c r="W23" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="X23" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="T23" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="U23" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="V23" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="W23" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="X23" s="1" t="n">
-        <v>8</v>
-      </c>
       <c r="Y23" s="1" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Z23" s="1" t="n">
         <v>7</v>
@@ -4505,20 +4505,20 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="C24" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="C24" s="1" t="n">
-        <v>11</v>
-      </c>
       <c r="D24" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F24" s="1" t="n">
         <v>2</v>
@@ -4527,10 +4527,10 @@
         <v>27</v>
       </c>
       <c r="H24" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I24" s="1" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J24" s="1" t="n">
         <v>23</v>
@@ -4545,7 +4545,7 @@
         <v>21</v>
       </c>
       <c r="N24" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="O24" s="1" t="n">
         <v>26</v>
@@ -4557,10 +4557,10 @@
         <v>25</v>
       </c>
       <c r="R24" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S24" s="1" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T24" s="1" t="n">
         <v>22</v>
@@ -4569,13 +4569,13 @@
         <v>16</v>
       </c>
       <c r="V24" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="W24" s="1" t="n">
         <v>3</v>
       </c>
       <c r="X24" s="1" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y24" s="1" t="n">
         <v>4</v>
@@ -4593,38 +4593,38 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D25" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="E25" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="F25" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G25" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="H25" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="I25" s="1" t="n">
         <v>19</v>
-      </c>
-      <c r="E25" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="F25" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="G25" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="H25" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="I25" s="1" t="n">
-        <v>18</v>
       </c>
       <c r="J25" s="1" t="n">
         <v>23</v>
       </c>
       <c r="K25" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L25" s="1" t="n">
         <v>20</v>
@@ -4633,10 +4633,10 @@
         <v>21</v>
       </c>
       <c r="N25" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="O25" s="1" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P25" s="1" t="n">
         <v>24</v>
@@ -4645,7 +4645,7 @@
         <v>25</v>
       </c>
       <c r="R25" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="S25" s="1" t="n">
         <v>9</v>
@@ -4654,25 +4654,25 @@
         <v>22</v>
       </c>
       <c r="U25" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="V25" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="W25" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X25" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y25" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="Y25" s="1" t="n">
-        <v>2</v>
-      </c>
       <c r="Z25" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA25" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AB25" s="1" t="n">
         <v>5</v>
@@ -4681,41 +4681,41 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C26" s="1" t="n">
         <v>12</v>
       </c>
       <c r="D26" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F26" s="1" t="n">
         <v>7</v>
       </c>
       <c r="G26" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="H26" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="I26" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="J26" s="1" t="n">
         <v>23</v>
-      </c>
-      <c r="H26" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="I26" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="J26" s="1" t="n">
-        <v>24</v>
       </c>
       <c r="K26" s="1" t="n">
         <v>3</v>
       </c>
       <c r="L26" s="1" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M26" s="1" t="n">
         <v>21</v>
@@ -4727,25 +4727,25 @@
         <v>27</v>
       </c>
       <c r="P26" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q26" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="Q26" s="1" t="n">
-        <v>26</v>
-      </c>
       <c r="R26" s="1" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="S26" s="1" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="T26" s="1" t="n">
         <v>22</v>
       </c>
       <c r="U26" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="V26" s="1" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="W26" s="1" t="n">
         <v>1</v>
@@ -4760,50 +4760,50 @@
         <v>8</v>
       </c>
       <c r="AA26" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AB26" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="C27" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D27" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="E27" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="F27" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C27" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="D27" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="E27" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="F27" s="1" t="n">
-        <v>5</v>
-      </c>
       <c r="G27" s="1" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="H27" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I27" s="1" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J27" s="1" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K27" s="1" t="n">
         <v>3</v>
       </c>
       <c r="L27" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M27" s="1" t="n">
         <v>21</v>
@@ -4815,25 +4815,25 @@
         <v>27</v>
       </c>
       <c r="P27" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Q27" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="R27" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="S27" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="S27" s="1" t="n">
-        <v>19</v>
-      </c>
       <c r="T27" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="U27" s="1" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="V27" s="1" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="W27" s="1" t="n">
         <v>1</v>
@@ -4845,10 +4845,10 @@
         <v>2</v>
       </c>
       <c r="Z27" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA27" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AB27" s="1" t="n">
         <v>6</v>
@@ -4857,20 +4857,20 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C28" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="D28" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="D28" s="1" t="n">
-        <v>20</v>
-      </c>
       <c r="E28" s="1" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F28" s="1" t="n">
         <v>5</v>
@@ -4879,10 +4879,10 @@
         <v>26</v>
       </c>
       <c r="H28" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I28" s="1" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J28" s="1" t="n">
         <v>22</v>
@@ -4891,34 +4891,34 @@
         <v>3</v>
       </c>
       <c r="L28" s="1" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M28" s="1" t="n">
         <v>21</v>
       </c>
       <c r="N28" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="O28" s="1" t="n">
         <v>27</v>
       </c>
       <c r="P28" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q28" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="Q28" s="1" t="n">
-        <v>24</v>
-      </c>
       <c r="R28" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="S28" s="1" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="T28" s="1" t="n">
         <v>23</v>
       </c>
       <c r="U28" s="1" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="V28" s="1" t="n">
         <v>17</v>
@@ -4933,10 +4933,10 @@
         <v>2</v>
       </c>
       <c r="Z28" s="1" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AA28" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AB28" s="1" t="n">
         <v>6</v>
@@ -4945,44 +4945,44 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D29" s="1" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F29" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G29" s="1" t="n">
         <v>26</v>
       </c>
       <c r="H29" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I29" s="1" t="n">
         <v>10</v>
       </c>
       <c r="J29" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K29" s="1" t="n">
         <v>3</v>
       </c>
       <c r="L29" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M29" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N29" s="1" t="n">
         <v>11</v>
@@ -4997,10 +4997,10 @@
         <v>24</v>
       </c>
       <c r="R29" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="S29" s="1" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="T29" s="1" t="n">
         <v>23</v>
@@ -5009,13 +5009,13 @@
         <v>18</v>
       </c>
       <c r="V29" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="W29" s="1" t="n">
         <v>1</v>
       </c>
       <c r="X29" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y29" s="1" t="n">
         <v>2</v>
@@ -5024,7 +5024,7 @@
         <v>7</v>
       </c>
       <c r="AA29" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AB29" s="1" t="n">
         <v>6</v>
@@ -5033,38 +5033,38 @@
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
         <v>9</v>
       </c>
       <c r="C30" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D30" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="E30" s="1" t="n">
         <v>13</v>
-      </c>
-      <c r="D30" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="E30" s="1" t="n">
-        <v>11</v>
       </c>
       <c r="F30" s="1" t="n">
         <v>4</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H30" s="1" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I30" s="1" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J30" s="1" t="n">
         <v>21</v>
       </c>
       <c r="K30" s="1" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="L30" s="1" t="n">
         <v>20</v>
@@ -5073,28 +5073,28 @@
         <v>22</v>
       </c>
       <c r="N30" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="O30" s="1" t="n">
         <v>27</v>
       </c>
       <c r="P30" s="1" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Q30" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R30" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="S30" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="T30" s="1" t="n">
         <v>23</v>
       </c>
       <c r="U30" s="1" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="V30" s="1" t="n">
         <v>15</v>
@@ -5109,10 +5109,10 @@
         <v>2</v>
       </c>
       <c r="Z30" s="1" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AA30" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AB30" s="1" t="n">
         <v>6</v>
@@ -5121,47 +5121,47 @@
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C31" s="1" t="n">
         <v>13</v>
       </c>
       <c r="D31" s="1" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="F31" s="1" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H31" s="1" t="n">
         <v>3</v>
       </c>
       <c r="I31" s="1" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J31" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="K31" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="L31" s="1" t="n">
         <v>20</v>
-      </c>
-      <c r="K31" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="L31" s="1" t="n">
-        <v>18</v>
       </c>
       <c r="M31" s="1" t="n">
         <v>22</v>
       </c>
       <c r="N31" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O31" s="1" t="n">
         <v>27</v>
@@ -5173,25 +5173,25 @@
         <v>25</v>
       </c>
       <c r="R31" s="1" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="S31" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="T31" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="U31" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="T31" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="U31" s="1" t="n">
-        <v>12</v>
-      </c>
       <c r="V31" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="W31" s="1" t="n">
         <v>1</v>
       </c>
       <c r="X31" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y31" s="1" t="n">
         <v>2</v>
@@ -5209,44 +5209,44 @@
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D32" s="1" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F32" s="1" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G32" s="1" t="n">
         <v>23</v>
       </c>
       <c r="H32" s="1" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I32" s="1" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J32" s="1" t="n">
         <v>20</v>
       </c>
       <c r="K32" s="1" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L32" s="1" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="M32" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N32" s="1" t="n">
         <v>11</v>
@@ -5258,86 +5258,86 @@
         <v>26</v>
       </c>
       <c r="Q32" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="R32" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="S32" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="T32" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="R32" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="S32" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="T32" s="1" t="n">
-        <v>25</v>
-      </c>
       <c r="U32" s="1" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="V32" s="1" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="W32" s="1" t="n">
         <v>1</v>
       </c>
       <c r="X32" s="1" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Y32" s="1" t="n">
         <v>2</v>
       </c>
       <c r="Z32" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA32" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AB32" s="1" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
         <v>10</v>
       </c>
       <c r="C33" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="D33" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="D33" s="1" t="n">
-        <v>11</v>
-      </c>
       <c r="E33" s="1" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F33" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G33" s="1" t="n">
         <v>23</v>
       </c>
       <c r="H33" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="I33" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="J33" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="K33" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="I33" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="J33" s="1" t="n">
+      <c r="L33" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="M33" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="K33" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="L33" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="M33" s="1" t="n">
-        <v>22</v>
-      </c>
       <c r="N33" s="1" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="O33" s="1" t="n">
         <v>27</v>
@@ -5349,7 +5349,7 @@
         <v>24</v>
       </c>
       <c r="R33" s="1" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="S33" s="1" t="n">
         <v>19</v>
@@ -5358,16 +5358,16 @@
         <v>25</v>
       </c>
       <c r="U33" s="1" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="V33" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="W33" s="1" t="n">
         <v>1</v>
       </c>
       <c r="X33" s="1" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Y33" s="1" t="n">
         <v>2</v>
@@ -5376,23 +5376,23 @@
         <v>9</v>
       </c>
       <c r="AA33" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AB33" s="1" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
         <v>10</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D34" s="1" t="n">
         <v>11</v>
@@ -5401,7 +5401,7 @@
         <v>20</v>
       </c>
       <c r="F34" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G34" s="1" t="n">
         <v>23</v>
@@ -5413,19 +5413,19 @@
         <v>7</v>
       </c>
       <c r="J34" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K34" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L34" s="1" t="n">
         <v>13</v>
       </c>
       <c r="M34" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N34" s="1" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="O34" s="1" t="n">
         <v>27</v>
@@ -5437,19 +5437,19 @@
         <v>24</v>
       </c>
       <c r="R34" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="S34" s="1" t="n">
         <v>19</v>
-      </c>
-      <c r="S34" s="1" t="n">
-        <v>18</v>
       </c>
       <c r="T34" s="1" t="n">
         <v>25</v>
       </c>
       <c r="U34" s="1" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="V34" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="W34" s="1" t="n">
         <v>1</v>
@@ -5464,7 +5464,7 @@
         <v>9</v>
       </c>
       <c r="AA34" s="1" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AB34" s="1" t="n">
         <v>8</v>
@@ -5473,44 +5473,44 @@
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="C35" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="C35" s="1" t="n">
-        <v>16</v>
-      </c>
       <c r="D35" s="1" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F35" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G35" s="1" t="n">
         <v>23</v>
       </c>
       <c r="H35" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I35" s="1" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J35" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="K35" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="L35" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="M35" s="1" t="n">
         <v>21</v>
-      </c>
-      <c r="K35" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="L35" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="M35" s="1" t="n">
-        <v>20</v>
       </c>
       <c r="N35" s="1" t="n">
         <v>12</v>
@@ -5534,19 +5534,19 @@
         <v>25</v>
       </c>
       <c r="U35" s="1" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="V35" s="1" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="W35" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="X35" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="X35" s="1" t="n">
-        <v>7</v>
-      </c>
       <c r="Y35" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Z35" s="1" t="n">
         <v>9</v>
@@ -5561,23 +5561,23 @@
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B36" s="1" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C36" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="D36" s="1" t="n">
         <v>14</v>
-      </c>
-      <c r="D36" s="1" t="n">
-        <v>13</v>
       </c>
       <c r="E36" s="1" t="n">
         <v>22</v>
       </c>
       <c r="F36" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G36" s="1" t="n">
         <v>23</v>
@@ -5589,16 +5589,16 @@
         <v>3</v>
       </c>
       <c r="J36" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K36" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L36" s="1" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="M36" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="N36" s="1" t="n">
         <v>12</v>
@@ -5613,47 +5613,47 @@
         <v>24</v>
       </c>
       <c r="R36" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="S36" s="1" t="n">
         <v>18</v>
-      </c>
-      <c r="S36" s="1" t="n">
-        <v>19</v>
       </c>
       <c r="T36" s="1" t="n">
         <v>25</v>
       </c>
       <c r="U36" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="V36" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="W36" s="1" t="n">
         <v>4</v>
       </c>
       <c r="X36" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y36" s="1" t="n">
         <v>5</v>
       </c>
       <c r="Z36" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA36" s="1" t="n">
         <v>17</v>
       </c>
       <c r="AB36" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B37" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C37" s="1" t="n">
         <v>14</v>
@@ -5662,31 +5662,31 @@
         <v>13</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F37" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G37" s="1" t="n">
         <v>23</v>
       </c>
       <c r="H37" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I37" s="1" t="n">
         <v>3</v>
       </c>
       <c r="J37" s="1" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K37" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L37" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M37" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N37" s="1" t="n">
         <v>12</v>
@@ -5701,19 +5701,19 @@
         <v>24</v>
       </c>
       <c r="R37" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="S37" s="1" t="n">
         <v>19</v>
-      </c>
-      <c r="S37" s="1" t="n">
-        <v>18</v>
       </c>
       <c r="T37" s="1" t="n">
         <v>25</v>
       </c>
       <c r="U37" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="V37" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="W37" s="1" t="n">
         <v>4</v>
@@ -5725,10 +5725,10 @@
         <v>5</v>
       </c>
       <c r="Z37" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA37" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AB37" s="1" t="n">
         <v>9</v>
@@ -5737,26 +5737,26 @@
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B38" s="1" t="n">
         <v>11</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D38" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F38" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H38" s="1" t="n">
         <v>2</v>
@@ -5765,13 +5765,13 @@
         <v>3</v>
       </c>
       <c r="J38" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K38" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L38" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M38" s="1" t="n">
         <v>20</v>
@@ -5786,16 +5786,16 @@
         <v>26</v>
       </c>
       <c r="Q38" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="R38" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="S38" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="T38" s="1" t="n">
         <v>25</v>
-      </c>
-      <c r="R38" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="S38" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="T38" s="1" t="n">
-        <v>24</v>
       </c>
       <c r="U38" s="1" t="n">
         <v>10</v>
@@ -5813,35 +5813,35 @@
         <v>5</v>
       </c>
       <c r="Z38" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA38" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="AB38" s="1" t="n">
         <v>9</v>
-      </c>
-      <c r="AA38" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="AB38" s="1" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B39" s="1" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D39" s="1" t="n">
         <v>14</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F39" s="1" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G39" s="1" t="n">
         <v>21</v>
@@ -5859,7 +5859,7 @@
         <v>1</v>
       </c>
       <c r="L39" s="1" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="M39" s="1" t="n">
         <v>20</v>
@@ -5871,56 +5871,56 @@
         <v>27</v>
       </c>
       <c r="P39" s="1" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="Q39" s="1" t="n">
         <v>25</v>
       </c>
       <c r="R39" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="S39" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="T39" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="U39" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="T39" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="U39" s="1" t="n">
+      <c r="V39" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="W39" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="V39" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="W39" s="1" t="n">
+      <c r="X39" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="X39" s="1" t="n">
-        <v>11</v>
-      </c>
       <c r="Y39" s="1" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Z39" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA39" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="AB39" s="1" t="n">
         <v>8</v>
-      </c>
-      <c r="AA39" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="AB39" s="1" t="n">
-        <v>9</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B40" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="C40" s="1" t="n">
         <v>17</v>
-      </c>
-      <c r="C40" s="1" t="n">
-        <v>15</v>
       </c>
       <c r="D40" s="1" t="n">
         <v>14</v>
@@ -5932,7 +5932,7 @@
         <v>5</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="H40" s="1" t="n">
         <v>2</v>
@@ -5941,25 +5941,25 @@
         <v>3</v>
       </c>
       <c r="J40" s="1" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K40" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L40" s="1" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="M40" s="1" t="n">
         <v>20</v>
       </c>
       <c r="N40" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="O40" s="1" t="n">
         <v>27</v>
       </c>
       <c r="P40" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q40" s="1" t="n">
         <v>25</v>
@@ -5968,47 +5968,47 @@
         <v>16</v>
       </c>
       <c r="S40" s="1" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T40" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="U40" s="1" t="n">
         <v>4</v>
       </c>
       <c r="V40" s="1" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="W40" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X40" s="1" t="n">
         <v>11</v>
       </c>
       <c r="Y40" s="1" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Z40" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA40" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="AB40" s="1" t="n">
         <v>9</v>
-      </c>
-      <c r="AA40" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="AB40" s="1" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B41" s="1" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D41" s="1" t="n">
         <v>14</v>
@@ -6029,34 +6029,34 @@
         <v>3</v>
       </c>
       <c r="J41" s="1" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K41" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L41" s="1" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M41" s="1" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="N41" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="O41" s="1" t="n">
         <v>27</v>
       </c>
       <c r="P41" s="1" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q41" s="1" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="R41" s="1" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="S41" s="1" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T41" s="1" t="n">
         <v>21</v>
@@ -6068,13 +6068,13 @@
         <v>12</v>
       </c>
       <c r="W41" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X41" s="1" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="Y41" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z41" s="1" t="n">
         <v>9</v>
@@ -6083,59 +6083,59 @@
         <v>19</v>
       </c>
       <c r="AB41" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B42" s="1" t="n">
         <v>25</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D42" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F42" s="1" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G42" s="1" t="n">
         <v>24</v>
       </c>
       <c r="H42" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I42" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="J42" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="K42" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="I42" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="J42" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="K42" s="1" t="n">
-        <v>3</v>
-      </c>
       <c r="L42" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M42" s="1" t="n">
         <v>18</v>
       </c>
       <c r="N42" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="O42" s="1" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P42" s="1" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="Q42" s="1" t="n">
         <v>23</v>
@@ -6144,56 +6144,56 @@
         <v>13</v>
       </c>
       <c r="S42" s="1" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T42" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="U42" s="1" t="n">
         <v>4</v>
       </c>
       <c r="V42" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="W42" s="1" t="n">
         <v>6</v>
       </c>
       <c r="X42" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Y42" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z42" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA42" s="1" t="n">
         <v>19</v>
       </c>
       <c r="AB42" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B43" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="C43" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="D43" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="E43" s="1" t="n">
         <v>27</v>
       </c>
-      <c r="C43" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="D43" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="E43" s="1" t="n">
-        <v>25</v>
-      </c>
       <c r="F43" s="1" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G43" s="1" t="n">
         <v>24</v>
@@ -6202,61 +6202,61 @@
         <v>1</v>
       </c>
       <c r="I43" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="J43" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="K43" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="J43" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="K43" s="1" t="n">
-        <v>2</v>
-      </c>
       <c r="L43" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M43" s="1" t="n">
         <v>18</v>
       </c>
       <c r="N43" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="O43" s="1" t="n">
         <v>26</v>
       </c>
       <c r="P43" s="1" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q43" s="1" t="n">
         <v>23</v>
       </c>
       <c r="R43" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="S43" s="1" t="n">
         <v>5</v>
       </c>
       <c r="T43" s="1" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="U43" s="1" t="n">
         <v>4</v>
       </c>
       <c r="V43" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="W43" s="1" t="n">
         <v>6</v>
       </c>
       <c r="X43" s="1" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="Y43" s="1" t="n">
         <v>7</v>
       </c>
       <c r="Z43" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA43" s="1" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AB43" s="1" t="n">
         <v>8</v>
@@ -6265,47 +6265,47 @@
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B44" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C44" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="D44" s="1" t="n">
         <v>13</v>
-      </c>
-      <c r="D44" s="1" t="n">
-        <v>6</v>
       </c>
       <c r="E44" s="1" t="n">
         <v>25</v>
       </c>
       <c r="F44" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H44" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I44" s="1" t="n">
         <v>3</v>
       </c>
       <c r="J44" s="1" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="K44" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L44" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M44" s="1" t="n">
         <v>18</v>
       </c>
       <c r="N44" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="O44" s="1" t="n">
         <v>26</v>
@@ -6323,53 +6323,53 @@
         <v>5</v>
       </c>
       <c r="T44" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="U44" s="1" t="n">
         <v>4</v>
       </c>
       <c r="V44" s="1" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="W44" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X44" s="1" t="n">
         <v>17</v>
       </c>
       <c r="Y44" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z44" s="1" t="n">
         <v>9</v>
       </c>
       <c r="AA44" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AB44" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B45" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C45" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="D45" s="1" t="n">
         <v>6</v>
-      </c>
-      <c r="D45" s="1" t="n">
-        <v>5</v>
       </c>
       <c r="E45" s="1" t="n">
         <v>25</v>
       </c>
       <c r="F45" s="1" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="G45" s="1" t="n">
         <v>22</v>
@@ -6393,22 +6393,22 @@
         <v>18</v>
       </c>
       <c r="N45" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="O45" s="1" t="n">
         <v>26</v>
       </c>
       <c r="P45" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Q45" s="1" t="n">
         <v>23</v>
       </c>
       <c r="R45" s="1" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="S45" s="1" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T45" s="1" t="n">
         <v>21</v>
@@ -6417,50 +6417,50 @@
         <v>4</v>
       </c>
       <c r="V45" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="W45" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X45" s="1" t="n">
         <v>17</v>
       </c>
       <c r="Y45" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z45" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="Z45" s="1" t="n">
+      <c r="AA45" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="AB45" s="1" t="n">
         <v>10</v>
-      </c>
-      <c r="AA45" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="AB45" s="1" t="n">
-        <v>11</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B46" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D46" s="1" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E46" s="1" t="n">
         <v>25</v>
       </c>
       <c r="F46" s="1" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H46" s="1" t="n">
         <v>2</v>
@@ -6478,7 +6478,7 @@
         <v>16</v>
       </c>
       <c r="M46" s="1" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N46" s="1" t="n">
         <v>14</v>
@@ -6487,68 +6487,68 @@
         <v>26</v>
       </c>
       <c r="P46" s="1" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="Q46" s="1" t="n">
         <v>23</v>
       </c>
       <c r="R46" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="S46" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="T46" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="U46" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="V46" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="W46" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="X46" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y46" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="S46" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="T46" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="U46" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="V46" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="W46" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="X46" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="Y46" s="1" t="n">
-        <v>5</v>
-      </c>
       <c r="Z46" s="1" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AA46" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AB46" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B47" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D47" s="1" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E47" s="1" t="n">
         <v>25</v>
       </c>
       <c r="F47" s="1" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H47" s="1" t="n">
         <v>2</v>
@@ -6557,25 +6557,25 @@
         <v>3</v>
       </c>
       <c r="J47" s="1" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K47" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L47" s="1" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="M47" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N47" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O47" s="1" t="n">
         <v>26</v>
       </c>
       <c r="P47" s="1" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="Q47" s="1" t="n">
         <v>23</v>
@@ -6584,31 +6584,31 @@
         <v>9</v>
       </c>
       <c r="S47" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="T47" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="U47" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="T47" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="U47" s="1" t="n">
-        <v>7</v>
-      </c>
       <c r="V47" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="W47" s="1" t="n">
         <v>4</v>
       </c>
       <c r="X47" s="1" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Y47" s="1" t="n">
         <v>5</v>
       </c>
       <c r="Z47" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA47" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AB47" s="1" t="n">
         <v>10</v>
@@ -6617,23 +6617,23 @@
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B48" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D48" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F48" s="1" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G48" s="1" t="n">
         <v>20</v>
@@ -6645,13 +6645,13 @@
         <v>3</v>
       </c>
       <c r="J48" s="1" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="K48" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L48" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="M48" s="1" t="n">
         <v>18</v>
@@ -6660,10 +6660,10 @@
         <v>15</v>
       </c>
       <c r="O48" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P48" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Q48" s="1" t="n">
         <v>23</v>
@@ -6678,25 +6678,25 @@
         <v>24</v>
       </c>
       <c r="U48" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V48" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="W48" s="1" t="n">
         <v>4</v>
       </c>
       <c r="X48" s="1" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Y48" s="1" t="n">
         <v>5</v>
       </c>
       <c r="Z48" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA48" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AB48" s="1" t="n">
         <v>10</v>
@@ -6705,26 +6705,26 @@
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B49" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C49" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="D49" s="1" t="n">
         <v>16</v>
-      </c>
-      <c r="D49" s="1" t="n">
-        <v>13</v>
       </c>
       <c r="E49" s="1" t="n">
         <v>26</v>
       </c>
       <c r="F49" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="G49" s="1" t="n">
         <v>20</v>
-      </c>
-      <c r="G49" s="1" t="n">
-        <v>22</v>
       </c>
       <c r="H49" s="1" t="n">
         <v>2</v>
@@ -6745,13 +6745,13 @@
         <v>18</v>
       </c>
       <c r="N49" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="O49" s="1" t="n">
         <v>25</v>
       </c>
       <c r="P49" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Q49" s="1" t="n">
         <v>23</v>
@@ -6769,7 +6769,7 @@
         <v>8</v>
       </c>
       <c r="V49" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="W49" s="1" t="n">
         <v>4</v>
@@ -6784,7 +6784,7 @@
         <v>7</v>
       </c>
       <c r="AA49" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AB49" s="1" t="n">
         <v>10</v>
@@ -6793,7 +6793,7 @@
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B50" s="1" t="n">
@@ -6803,16 +6803,16 @@
         <v>16</v>
       </c>
       <c r="D50" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F50" s="1" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H50" s="1" t="n">
         <v>2</v>
@@ -6830,22 +6830,22 @@
         <v>11</v>
       </c>
       <c r="M50" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="N50" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="N50" s="1" t="n">
-        <v>15</v>
-      </c>
       <c r="O50" s="1" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P50" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="Q50" s="1" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="R50" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="S50" s="1" t="n">
         <v>6</v>
@@ -6857,13 +6857,13 @@
         <v>8</v>
       </c>
       <c r="V50" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="W50" s="1" t="n">
         <v>4</v>
       </c>
       <c r="X50" s="1" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="Y50" s="1" t="n">
         <v>5</v>
@@ -6872,71 +6872,71 @@
         <v>7</v>
       </c>
       <c r="AA50" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AB50" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B51" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D51" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F51" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="G51" s="1" t="n">
         <v>20</v>
-      </c>
-      <c r="G51" s="1" t="n">
-        <v>17</v>
       </c>
       <c r="H51" s="1" t="n">
         <v>2</v>
       </c>
       <c r="I51" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J51" s="1" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K51" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L51" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="M51" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N51" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="O51" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="P51" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="O51" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="P51" s="1" t="n">
-        <v>11</v>
-      </c>
       <c r="Q51" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R51" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="S51" s="1" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T51" s="1" t="n">
         <v>24</v>
@@ -6948,132 +6948,132 @@
         <v>13</v>
       </c>
       <c r="W51" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="X51" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y51" s="1" t="n">
         <v>5</v>
-      </c>
-      <c r="X51" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="Y51" s="1" t="n">
-        <v>6</v>
       </c>
       <c r="Z51" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AA51" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AB51" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B52" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D52" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E52" s="1" t="n">
         <v>26</v>
       </c>
       <c r="F52" s="1" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H52" s="1" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I52" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J52" s="1" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="K52" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L52" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M52" s="1" t="n">
         <v>18</v>
       </c>
       <c r="N52" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O52" s="1" t="n">
         <v>25</v>
       </c>
       <c r="P52" s="1" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="Q52" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="R52" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="S52" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T52" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="U52" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V52" s="1" t="n">
         <v>13</v>
       </c>
       <c r="W52" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X52" s="1" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="Y52" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z52" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AA52" s="1" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AB52" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B53" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D53" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E53" s="1" t="n">
         <v>26</v>
       </c>
       <c r="F53" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G53" s="1" t="n">
         <v>20</v>
@@ -7082,7 +7082,7 @@
         <v>6</v>
       </c>
       <c r="I53" s="1" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J53" s="1" t="n">
         <v>19</v>
@@ -7103,10 +7103,10 @@
         <v>25</v>
       </c>
       <c r="P53" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Q53" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R53" s="1" t="n">
         <v>10</v>
@@ -7115,53 +7115,53 @@
         <v>2</v>
       </c>
       <c r="T53" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="U53" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="V53" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="W53" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="X53" s="1" t="n">
         <v>24</v>
-      </c>
-      <c r="U53" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="V53" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="W53" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="X53" s="1" t="n">
-        <v>23</v>
       </c>
       <c r="Y53" s="1" t="n">
         <v>5</v>
       </c>
       <c r="Z53" s="1" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AA53" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AB53" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B54" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D54" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E54" s="1" t="n">
         <v>26</v>
       </c>
       <c r="F54" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G54" s="1" t="n">
         <v>20</v>
@@ -7170,25 +7170,25 @@
         <v>6</v>
       </c>
       <c r="I54" s="1" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J54" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K54" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L54" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M54" s="1" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N54" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O54" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="P54" s="1" t="n">
         <v>17</v>
@@ -7197,31 +7197,31 @@
         <v>22</v>
       </c>
       <c r="R54" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="S54" s="1" t="n">
         <v>2</v>
       </c>
       <c r="T54" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="U54" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="V54" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="W54" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="X54" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="U54" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="V54" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="W54" s="1" t="n">
+      <c r="Y54" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z54" s="1" t="n">
         <v>4</v>
-      </c>
-      <c r="X54" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="Y54" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z54" s="1" t="n">
-        <v>5</v>
       </c>
       <c r="AA54" s="1" t="n">
         <v>21</v>
@@ -7233,32 +7233,32 @@
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B55" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D55" s="1" t="n">
         <v>11</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F55" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G55" s="1" t="n">
         <v>20</v>
       </c>
       <c r="H55" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="I55" s="1" t="n">
         <v>3</v>
-      </c>
-      <c r="I55" s="1" t="n">
-        <v>12</v>
       </c>
       <c r="J55" s="1" t="n">
         <v>18</v>
@@ -7267,13 +7267,13 @@
         <v>1</v>
       </c>
       <c r="L55" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M55" s="1" t="n">
         <v>19</v>
       </c>
       <c r="N55" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O55" s="1" t="n">
         <v>24</v>
@@ -7285,28 +7285,28 @@
         <v>22</v>
       </c>
       <c r="R55" s="1" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="S55" s="1" t="n">
         <v>2</v>
       </c>
       <c r="T55" s="1" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="U55" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V55" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="W55" s="1" t="n">
         <v>4</v>
       </c>
       <c r="X55" s="1" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Y55" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z55" s="1" t="n">
         <v>5</v>
@@ -7315,77 +7315,77 @@
         <v>21</v>
       </c>
       <c r="AB55" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B56" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C56" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="D56" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="D56" s="1" t="n">
-        <v>10</v>
-      </c>
       <c r="E56" s="1" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F56" s="1" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G56" s="1" t="n">
         <v>20</v>
       </c>
       <c r="H56" s="1" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="I56" s="1" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="J56" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K56" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L56" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M56" s="1" t="n">
         <v>19</v>
       </c>
       <c r="N56" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O56" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P56" s="1" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Q56" s="1" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="R56" s="1" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="S56" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T56" s="1" t="n">
         <v>26</v>
       </c>
       <c r="U56" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="V56" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="W56" s="1" t="n">
         <v>4</v>
@@ -7394,7 +7394,7 @@
         <v>23</v>
       </c>
       <c r="Y56" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z56" s="1" t="n">
         <v>5</v>
@@ -7403,62 +7403,62 @@
         <v>21</v>
       </c>
       <c r="AB56" s="1" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B57" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D57" s="1" t="n">
         <v>10</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F57" s="1" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="G57" s="1" t="n">
         <v>20</v>
       </c>
       <c r="H57" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I57" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J57" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K57" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L57" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M57" s="1" t="n">
         <v>19</v>
       </c>
       <c r="N57" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O57" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="P57" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q57" s="1" t="n">
         <v>24</v>
-      </c>
-      <c r="P57" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q57" s="1" t="n">
-        <v>21</v>
       </c>
       <c r="R57" s="1" t="n">
         <v>3</v>
@@ -7467,10 +7467,10 @@
         <v>1</v>
       </c>
       <c r="T57" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="U57" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V57" s="1" t="n">
         <v>12</v>
@@ -7479,7 +7479,7 @@
         <v>4</v>
       </c>
       <c r="X57" s="1" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="Y57" s="1" t="n">
         <v>6</v>
@@ -7488,50 +7488,50 @@
         <v>5</v>
       </c>
       <c r="AA57" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AB57" s="1" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B58" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D58" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F58" s="1" t="n">
         <v>18</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H58" s="1" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="I58" s="1" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="J58" s="1" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="K58" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L58" s="1" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="M58" s="1" t="n">
         <v>19</v>
@@ -7540,37 +7540,37 @@
         <v>17</v>
       </c>
       <c r="O58" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P58" s="1" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="Q58" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R58" s="1" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="S58" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T58" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="U58" s="1" t="n">
         <v>7</v>
       </c>
       <c r="V58" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="W58" s="1" t="n">
         <v>4</v>
       </c>
       <c r="X58" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Y58" s="1" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Z58" s="1" t="n">
         <v>5</v>
@@ -7585,7 +7585,7 @@
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B59" s="1" t="n">
@@ -7595,10 +7595,10 @@
         <v>16</v>
       </c>
       <c r="D59" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F59" s="1" t="n">
         <v>18</v>
@@ -7607,19 +7607,19 @@
         <v>21</v>
       </c>
       <c r="H59" s="1" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="I59" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J59" s="1" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K59" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L59" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M59" s="1" t="n">
         <v>19</v>
@@ -7637,13 +7637,13 @@
         <v>20</v>
       </c>
       <c r="R59" s="1" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="S59" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T59" s="1" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="U59" s="1" t="n">
         <v>7</v>
@@ -7652,101 +7652,101 @@
         <v>15</v>
       </c>
       <c r="W59" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X59" s="1" t="n">
         <v>25</v>
       </c>
       <c r="Y59" s="1" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="Z59" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA59" s="1" t="n">
         <v>22</v>
       </c>
       <c r="AB59" s="1" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B60" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D60" s="1" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E60" s="1" t="n">
         <v>24</v>
       </c>
       <c r="F60" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G60" s="1" t="n">
         <v>21</v>
       </c>
       <c r="H60" s="1" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I60" s="1" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="J60" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K60" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L60" s="1" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="M60" s="1" t="n">
         <v>19</v>
       </c>
       <c r="N60" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O60" s="1" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="P60" s="1" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="Q60" s="1" t="n">
         <v>20</v>
       </c>
       <c r="R60" s="1" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="S60" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T60" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="U60" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V60" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="W60" s="1" t="n">
         <v>3</v>
       </c>
       <c r="X60" s="1" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Y60" s="1" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="Z60" s="1" t="n">
         <v>4</v>
@@ -7761,41 +7761,41 @@
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B61" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D61" s="1" t="n">
         <v>8</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F61" s="1" t="n">
         <v>16</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H61" s="1" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="I61" s="1" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="J61" s="1" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="K61" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L61" s="1" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="M61" s="1" t="n">
         <v>19</v>
@@ -7810,7 +7810,7 @@
         <v>12</v>
       </c>
       <c r="Q61" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="R61" s="1" t="n">
         <v>7</v>
@@ -7819,13 +7819,13 @@
         <v>1</v>
       </c>
       <c r="T61" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="U61" s="1" t="n">
         <v>6</v>
       </c>
       <c r="V61" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="W61" s="1" t="n">
         <v>3</v>
@@ -7834,7 +7834,7 @@
         <v>23</v>
       </c>
       <c r="Y61" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Z61" s="1" t="n">
         <v>4</v>
@@ -7849,68 +7849,68 @@
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B62" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D62" s="1" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E62" s="1" t="n">
         <v>25</v>
       </c>
       <c r="F62" s="1" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H62" s="1" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I62" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J62" s="1" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="K62" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L62" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="M62" s="1" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="N62" s="1" t="n">
         <v>18</v>
       </c>
       <c r="O62" s="1" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="P62" s="1" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="Q62" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R62" s="1" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="S62" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T62" s="1" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="U62" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V62" s="1" t="n">
         <v>14</v>
@@ -7919,250 +7919,250 @@
         <v>3</v>
       </c>
       <c r="X62" s="1" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="Y62" s="1" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Z62" s="1" t="n">
         <v>4</v>
       </c>
       <c r="AA62" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AB62" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B63" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D63" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E63" s="1" t="n">
         <v>25</v>
       </c>
       <c r="F63" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H63" s="1" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I63" s="1" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J63" s="1" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="K63" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L63" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M63" s="1" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="N63" s="1" t="n">
         <v>18</v>
       </c>
       <c r="O63" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P63" s="1" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="Q63" s="1" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="R63" s="1" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="S63" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T63" s="1" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="U63" s="1" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="V63" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="W63" s="1" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="X63" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y63" s="1" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="Z63" s="1" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="AA63" s="1" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AB63" s="1" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B64" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D64" s="1" t="n">
         <v>15</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F64" s="1" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H64" s="1" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="I64" s="1" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="J64" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K64" s="1" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L64" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="M64" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="M64" s="1" t="n">
-        <v>16</v>
-      </c>
       <c r="N64" s="1" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O64" s="1" t="n">
         <v>23</v>
       </c>
       <c r="P64" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q64" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="R64" s="1" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="S64" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T64" s="1" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="U64" s="1" t="n">
         <v>2</v>
       </c>
       <c r="V64" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="W64" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="X64" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y64" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="W64" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="X64" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="Y64" s="1" t="n">
-        <v>8</v>
-      </c>
       <c r="Z64" s="1" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AA64" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AB64" s="1" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B65" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D65" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="E65" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="F65" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="G65" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="H65" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="I65" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="E65" s="1" t="n">
+      <c r="J65" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="K65" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="L65" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="M65" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="N65" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="O65" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="F65" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="G65" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="H65" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="I65" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="J65" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="K65" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="L65" s="1" t="n">
+      <c r="P65" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q65" s="1" t="n">
         <v>18</v>
-      </c>
-      <c r="M65" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="N65" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="O65" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="P65" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q65" s="1" t="n">
-        <v>19</v>
       </c>
       <c r="R65" s="1" t="n">
         <v>10</v>
@@ -8174,77 +8174,77 @@
         <v>26</v>
       </c>
       <c r="U65" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="V65" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="W65" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="X65" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y65" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z65" s="1" t="n">
         <v>7</v>
-      </c>
-      <c r="V65" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="W65" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="X65" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="Y65" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="Z65" s="1" t="n">
-        <v>9</v>
       </c>
       <c r="AA65" s="1" t="n">
         <v>25</v>
       </c>
       <c r="AB65" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B66" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D66" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E66" s="1" t="n">
         <v>23</v>
       </c>
       <c r="F66" s="1" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="G66" s="1" t="n">
         <v>24</v>
       </c>
       <c r="H66" s="1" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="I66" s="1" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J66" s="1" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K66" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L66" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="M66" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="N66" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="M66" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="N66" s="1" t="n">
-        <v>13</v>
-      </c>
       <c r="O66" s="1" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="P66" s="1" t="n">
         <v>8</v>
@@ -8265,83 +8265,83 @@
         <v>7</v>
       </c>
       <c r="V66" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="W66" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X66" s="1" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="Y66" s="1" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Z66" s="1" t="n">
         <v>9</v>
       </c>
       <c r="AA66" s="1" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AB66" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B67" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D67" s="1" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E67" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="F67" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="G67" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="F67" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="G67" s="1" t="n">
-        <v>22</v>
-      </c>
       <c r="H67" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="I67" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="I67" s="1" t="n">
-        <v>21</v>
-      </c>
       <c r="J67" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K67" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L67" s="1" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="M67" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N67" s="1" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="O67" s="1" t="n">
         <v>25</v>
       </c>
       <c r="P67" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q67" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="R67" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="S67" s="1" t="n">
         <v>1</v>
@@ -8353,25 +8353,25 @@
         <v>7</v>
       </c>
       <c r="V67" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="W67" s="1" t="n">
         <v>3</v>
       </c>
       <c r="X67" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Y67" s="1" t="n">
         <v>4</v>
       </c>
       <c r="Z67" s="1" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AA67" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AB67" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/NSE_Sector_Monitor.xlsx
+++ b/NSE_Sector_Monitor.xlsx
@@ -568,22 +568,22 @@
         <v>1</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>14.45</v>
+        <v>14.72</v>
       </c>
       <c r="H2" s="1" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="I2" s="1" t="n">
-        <v>0.34</v>
+        <v>-0.9</v>
       </c>
       <c r="J2" s="1" t="n">
-        <v>4.17</v>
+        <v>4.43</v>
       </c>
       <c r="K2" s="1" t="n">
-        <v>18.23</v>
+        <v>18.66</v>
       </c>
       <c r="L2" s="1" t="inlineStr">
         <is>
@@ -591,16 +591,16 @@
         </is>
       </c>
       <c r="M2" s="1" t="n">
-        <v>-1.92</v>
+        <v>-0.9</v>
       </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr">
@@ -624,7 +624,7 @@
         <v>2</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>2</v>
@@ -633,22 +633,22 @@
         <v>10</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>27.36</v>
+        <v>27.5</v>
       </c>
       <c r="H3" s="1" t="n">
-        <v>1.52</v>
+        <v>0.51</v>
       </c>
       <c r="I3" s="1" t="n">
-        <v>1.65</v>
+        <v>0.88</v>
       </c>
       <c r="J3" s="1" t="n">
-        <v>4.45</v>
+        <v>4.12</v>
       </c>
       <c r="K3" s="1" t="n">
-        <v>12.56</v>
+        <v>11.06</v>
       </c>
       <c r="L3" s="1" t="inlineStr">
         <is>
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="M3" s="1" t="n">
-        <v>0</v>
+        <v>-0.31</v>
       </c>
       <c r="N3" s="1" t="inlineStr">
         <is>
@@ -689,7 +689,7 @@
         <v>3</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>0</v>
@@ -698,22 +698,22 @@
         <v>3</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>88.37</v>
+        <v>88.34</v>
       </c>
       <c r="H4" s="1" t="n">
-        <v>0.2</v>
+        <v>0.42</v>
       </c>
       <c r="I4" s="1" t="n">
-        <v>1.05</v>
+        <v>0.09</v>
       </c>
       <c r="J4" s="1" t="n">
-        <v>1.29</v>
+        <v>0.15</v>
       </c>
       <c r="K4" s="1" t="n">
-        <v>9.82</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="L4" s="1" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
         </is>
       </c>
       <c r="M4" s="1" t="n">
-        <v>-7.59</v>
+        <v>-8.369999999999999</v>
       </c>
       <c r="N4" s="1" t="inlineStr">
         <is>
@@ -754,31 +754,31 @@
         <v>4</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>17.01</v>
+        <v>17.14</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>1.01</v>
+        <v>2.21</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>1.37</v>
+        <v>1.18</v>
       </c>
       <c r="J5" s="1" t="n">
-        <v>4.15</v>
+        <v>4.22</v>
       </c>
       <c r="K5" s="1" t="n">
-        <v>9.039999999999999</v>
+        <v>7.74</v>
       </c>
       <c r="L5" s="1" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         <v>5</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>-3</v>
@@ -831,19 +831,19 @@
         <v>-3</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>83.84999999999999</v>
+        <v>85.27</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>1.8</v>
+        <v>2.72</v>
       </c>
       <c r="I6" s="1" t="n">
-        <v>-2.93</v>
+        <v>0.18</v>
       </c>
       <c r="J6" s="1" t="n">
-        <v>-3.21</v>
+        <v>-3.74</v>
       </c>
       <c r="K6" s="1" t="n">
-        <v>5</v>
+        <v>6.74</v>
       </c>
       <c r="L6" s="1" t="inlineStr">
         <is>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="M6" s="1" t="n">
-        <v>-9.210000000000001</v>
+        <v>-8.43</v>
       </c>
       <c r="N6" s="1" t="inlineStr">
         <is>
@@ -884,31 +884,31 @@
         <v>6</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E7" s="2" t="n">
         <v>7</v>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>11</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>21</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>32.39</v>
+        <v>31.94</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>-1.46</v>
+        <v>-1.11</v>
       </c>
       <c r="I7" s="1" t="n">
-        <v>2.36</v>
+        <v>-0.6</v>
       </c>
       <c r="J7" s="1" t="n">
-        <v>-0.72</v>
+        <v>-3.49</v>
       </c>
       <c r="K7" s="1" t="n">
-        <v>4.93</v>
+        <v>6.43</v>
       </c>
       <c r="L7" s="1" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         </is>
       </c>
       <c r="M7" s="1" t="n">
-        <v>-23.25</v>
+        <v>-24.93</v>
       </c>
       <c r="N7" s="1" t="inlineStr">
         <is>
@@ -949,31 +949,31 @@
         <v>7</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>-3</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>282.4</v>
+        <v>282.71</v>
       </c>
       <c r="H8" s="1" t="n">
-        <v>1.47</v>
+        <v>1.2</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="J8" s="1" t="n">
-        <v>-3.45</v>
+        <v>-4.19</v>
       </c>
       <c r="K8" s="1" t="n">
-        <v>4.81</v>
+        <v>4.48</v>
       </c>
       <c r="L8" s="1" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         </is>
       </c>
       <c r="M8" s="1" t="n">
-        <v>-3.85</v>
+        <v>-4.53</v>
       </c>
       <c r="N8" s="1" t="inlineStr">
         <is>
@@ -1014,31 +1014,31 @@
         <v>8</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>-3</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>31.69</v>
+        <v>31.94</v>
       </c>
       <c r="H9" s="1" t="n">
-        <v>0.67</v>
+        <v>2.34</v>
       </c>
       <c r="I9" s="1" t="n">
-        <v>-0.04</v>
+        <v>0.21</v>
       </c>
       <c r="J9" s="1" t="n">
-        <v>-2.9</v>
+        <v>-2.84</v>
       </c>
       <c r="K9" s="1" t="n">
-        <v>4.04</v>
+        <v>3.04</v>
       </c>
       <c r="L9" s="1" t="inlineStr">
         <is>
@@ -1046,11 +1046,11 @@
         </is>
       </c>
       <c r="M9" s="1" t="n">
-        <v>-3.56</v>
+        <v>-3.59</v>
       </c>
       <c r="N9" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O9" s="1" t="inlineStr">
@@ -1072,38 +1072,38 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Metal</t>
+          <t>Fin Services</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
         <v>9</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>5</v>
+        <v>-2</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>14</v>
+        <v>-3</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-4</v>
+        <v>9</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>12.97</v>
+        <v>32.28</v>
       </c>
       <c r="H10" s="1" t="n">
-        <v>1.57</v>
+        <v>2.12</v>
       </c>
       <c r="I10" s="1" t="n">
-        <v>-1.5</v>
+        <v>-0.26</v>
       </c>
       <c r="J10" s="1" t="n">
-        <v>2.6</v>
+        <v>-0.45</v>
       </c>
       <c r="K10" s="1" t="n">
-        <v>1.65</v>
+        <v>1.46</v>
       </c>
       <c r="L10" s="1" t="inlineStr">
         <is>
@@ -1111,11 +1111,11 @@
         </is>
       </c>
       <c r="M10" s="1" t="n">
-        <v>-5.62</v>
+        <v>-1.23</v>
       </c>
       <c r="N10" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O10" s="1" t="inlineStr">
@@ -1137,103 +1137,103 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>Fin Services</t>
+          <t>Manufacturing</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
         <v>10</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>-4</v>
+        <v>3</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>31.93</v>
+        <v>162.62</v>
       </c>
       <c r="H11" s="1" t="n">
         <v>0.92</v>
       </c>
       <c r="I11" s="1" t="n">
-        <v>-0.03</v>
+        <v>0.01</v>
       </c>
       <c r="J11" s="1" t="n">
-        <v>-0.12</v>
+        <v>-0.31</v>
       </c>
       <c r="K11" s="1" t="n">
-        <v>1.39</v>
+        <v>1.2</v>
       </c>
       <c r="L11" s="1" t="inlineStr">
         <is>
-          <t>Down</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="M11" s="1" t="n">
-        <v>-1.5</v>
+        <v>-1.1</v>
       </c>
       <c r="N11" s="1" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O11" s="1" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="O11" s="1" t="inlineStr">
+      <c r="P11" s="1" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P11" s="1" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="Q11" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Manufacturing</t>
+          <t>Metal</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
         <v>11</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>1</v>
+        <v>-8</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>161.14</v>
+        <v>13.08</v>
       </c>
       <c r="H12" s="1" t="n">
-        <v>1.1</v>
+        <v>1.79</v>
       </c>
       <c r="I12" s="1" t="n">
-        <v>-0.39</v>
+        <v>-0.04</v>
       </c>
       <c r="J12" s="1" t="n">
-        <v>-0.8100000000000001</v>
+        <v>2.71</v>
       </c>
       <c r="K12" s="1" t="n">
-        <v>1.34</v>
+        <v>1.17</v>
       </c>
       <c r="L12" s="1" t="inlineStr">
         <is>
@@ -1241,21 +1241,21 @@
         </is>
       </c>
       <c r="M12" s="1" t="n">
-        <v>-1.2</v>
+        <v>-5.6</v>
       </c>
       <c r="N12" s="1" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O12" s="1" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="O12" s="1" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="P12" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Q12" s="1" t="inlineStr">
@@ -1274,10 +1274,10 @@
         <v>12</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>-2</v>
+        <v>-5</v>
       </c>
       <c r="E13" s="2" t="n">
         <v>-5</v>
@@ -1286,46 +1286,46 @@
         <v>-3</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>76.53</v>
+        <v>77.95</v>
       </c>
       <c r="H13" s="1" t="n">
-        <v>1.67</v>
+        <v>3.91</v>
       </c>
       <c r="I13" s="1" t="n">
-        <v>1.25</v>
+        <v>1.55</v>
       </c>
       <c r="J13" s="1" t="n">
-        <v>-0.55</v>
+        <v>0.82</v>
       </c>
       <c r="K13" s="1" t="n">
-        <v>1.04</v>
+        <v>0.88</v>
       </c>
       <c r="L13" s="1" t="inlineStr">
         <is>
-          <t>Down</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="M13" s="1" t="n">
-        <v>-14.93</v>
+        <v>-13.67</v>
       </c>
       <c r="N13" s="1" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O13" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P13" s="1" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="O13" s="1" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="P13" s="1" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="Q13" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1342,25 +1342,25 @@
         <v>-1</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>-2</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>126.99</v>
+        <v>128.32</v>
       </c>
       <c r="H14" s="1" t="n">
-        <v>-0.08</v>
+        <v>1.05</v>
       </c>
       <c r="I14" s="1" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="J14" s="1" t="n">
-        <v>-1.75</v>
+        <v>-1.82</v>
       </c>
       <c r="K14" s="1" t="n">
         <v>0.87</v>
@@ -1371,11 +1371,11 @@
         </is>
       </c>
       <c r="M14" s="1" t="n">
-        <v>-5.72</v>
+        <v>-5.51</v>
       </c>
       <c r="N14" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O14" s="1" t="inlineStr">
@@ -1397,50 +1397,50 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>Private Bank</t>
+          <t>Services</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
         <v>14</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>27.74</v>
+        <v>30.35</v>
       </c>
       <c r="H15" s="1" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="I15" s="1" t="n">
-        <v>1.31</v>
+        <v>0.18</v>
       </c>
       <c r="J15" s="1" t="n">
-        <v>3.12</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="K15" s="1" t="n">
-        <v>-0.02</v>
+        <v>0.27</v>
       </c>
       <c r="L15" s="1" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Down</t>
         </is>
       </c>
       <c r="M15" s="1" t="n">
-        <v>-3.41</v>
+        <v>0</v>
       </c>
       <c r="N15" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O15" s="1" t="inlineStr">
@@ -1462,38 +1462,38 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Defence</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
         <v>15</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>-11</v>
+        <v>-1</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>-7</v>
+        <v>1</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>-7</v>
+        <v>4</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-14</v>
+        <v>-8</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>101.87</v>
+        <v>29.3</v>
       </c>
       <c r="H16" s="1" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="I16" s="1" t="n">
-        <v>-4.1</v>
+        <v>-1.8</v>
       </c>
       <c r="J16" s="1" t="n">
-        <v>-2.58</v>
+        <v>-0.32</v>
       </c>
       <c r="K16" s="1" t="n">
-        <v>-0.05</v>
+        <v>-0.3</v>
       </c>
       <c r="L16" s="1" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         </is>
       </c>
       <c r="M16" s="1" t="n">
-        <v>-5.3</v>
+        <v>0</v>
       </c>
       <c r="N16" s="1" t="inlineStr">
         <is>
@@ -1520,53 +1520,53 @@
       </c>
       <c r="Q16" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Oil &amp; Gas</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
         <v>16</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>30</v>
+        <v>11.14</v>
       </c>
       <c r="H17" s="1" t="n">
-        <v>0</v>
+        <v>0.72</v>
       </c>
       <c r="I17" s="1" t="n">
-        <v>0.88</v>
+        <v>-0.16</v>
       </c>
       <c r="J17" s="1" t="n">
-        <v>0.16</v>
+        <v>0.86</v>
       </c>
       <c r="K17" s="1" t="n">
-        <v>-0.32</v>
+        <v>-0.55</v>
       </c>
       <c r="L17" s="1" t="inlineStr">
         <is>
-          <t>Down</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="M17" s="1" t="n">
-        <v>0</v>
+        <v>-9.039999999999999</v>
       </c>
       <c r="N17" s="1" t="inlineStr">
         <is>
@@ -1592,38 +1592,38 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>Bank</t>
+          <t>Defence</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
         <v>17</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>1</v>
+        <v>-12</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>-6</v>
+        <v>-12</v>
       </c>
       <c r="E18" s="2" t="n">
         <v>-7</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>1</v>
+        <v>-16</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>581.64</v>
+        <v>103.28</v>
       </c>
       <c r="H18" s="1" t="n">
-        <v>0.4</v>
+        <v>2.75</v>
       </c>
       <c r="I18" s="1" t="n">
-        <v>0.99</v>
+        <v>-3.12</v>
       </c>
       <c r="J18" s="1" t="n">
-        <v>1.21</v>
+        <v>-1.03</v>
       </c>
       <c r="K18" s="1" t="n">
-        <v>-0.33</v>
+        <v>-0.61</v>
       </c>
       <c r="L18" s="1" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         </is>
       </c>
       <c r="M18" s="1" t="n">
-        <v>-5.11</v>
+        <v>-4.78</v>
       </c>
       <c r="N18" s="1" t="inlineStr">
         <is>
@@ -1650,45 +1650,45 @@
       </c>
       <c r="Q18" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>MNC</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
         <v>18</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>-5</v>
+        <v>-2</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>-3</v>
+        <v>2</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>-11</v>
+        <v>-8</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>29.06</v>
+        <v>32.69</v>
       </c>
       <c r="H19" s="1" t="n">
-        <v>-0.62</v>
+        <v>1.87</v>
       </c>
       <c r="I19" s="1" t="n">
-        <v>-2.02</v>
+        <v>0.05</v>
       </c>
       <c r="J19" s="1" t="n">
-        <v>-1.45</v>
+        <v>-2.09</v>
       </c>
       <c r="K19" s="1" t="n">
-        <v>-0.41</v>
+        <v>-0.79</v>
       </c>
       <c r="L19" s="1" t="inlineStr">
         <is>
@@ -1696,72 +1696,72 @@
         </is>
       </c>
       <c r="M19" s="1" t="n">
-        <v>0</v>
+        <v>-3.97</v>
       </c>
       <c r="N19" s="1" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O19" s="1" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="O19" s="1" t="inlineStr">
+      <c r="P19" s="1" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P19" s="1" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="Q19" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>MNC</t>
+          <t>Private Bank</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
         <v>19</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>-3</v>
+        <v>-5</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>-9</v>
+        <v>-6</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>32.29</v>
+        <v>27.83</v>
       </c>
       <c r="H20" s="1" t="n">
-        <v>0.34</v>
+        <v>0.11</v>
       </c>
       <c r="I20" s="1" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.28</v>
       </c>
       <c r="J20" s="1" t="n">
-        <v>-2.22</v>
+        <v>2.39</v>
       </c>
       <c r="K20" s="1" t="n">
-        <v>-1.03</v>
+        <v>-0.95</v>
       </c>
       <c r="L20" s="1" t="inlineStr">
         <is>
-          <t>Down</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="M20" s="1" t="n">
-        <v>-4.37</v>
+        <v>-3.89</v>
       </c>
       <c r="N20" s="1" t="inlineStr">
         <is>
@@ -1787,38 +1787,38 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas</t>
+          <t>Bank</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
         <v>20</v>
       </c>
       <c r="C21" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>-10</v>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>-12</v>
+      </c>
+      <c r="F21" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D21" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E21" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="F21" s="2" t="n">
-        <v>6</v>
-      </c>
       <c r="G21" s="1" t="n">
-        <v>11.02</v>
+        <v>583.58</v>
       </c>
       <c r="H21" s="1" t="n">
-        <v>0.18</v>
+        <v>0.15</v>
       </c>
       <c r="I21" s="1" t="n">
-        <v>-0.05</v>
+        <v>-0.36</v>
       </c>
       <c r="J21" s="1" t="n">
-        <v>0.4</v>
+        <v>0.79</v>
       </c>
       <c r="K21" s="1" t="n">
-        <v>-1.41</v>
+        <v>-1</v>
       </c>
       <c r="L21" s="1" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         </is>
       </c>
       <c r="M21" s="1" t="n">
-        <v>-9.279999999999999</v>
+        <v>-5.57</v>
       </c>
       <c r="N21" s="1" t="inlineStr">
         <is>
@@ -1859,31 +1859,31 @@
         <v>21</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>-5</v>
+        <v>-3</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="E22" s="2" t="n">
         <v>-20</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>-18</v>
+        <v>-17</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>53.1</v>
+        <v>53.58</v>
       </c>
       <c r="H22" s="1" t="n">
-        <v>0.47</v>
+        <v>1.92</v>
       </c>
       <c r="I22" s="1" t="n">
-        <v>0.31</v>
+        <v>-0.65</v>
       </c>
       <c r="J22" s="1" t="n">
-        <v>2.59</v>
+        <v>1.88</v>
       </c>
       <c r="K22" s="1" t="n">
-        <v>-2.31</v>
+        <v>-2.6</v>
       </c>
       <c r="L22" s="1" t="inlineStr">
         <is>
@@ -1895,7 +1895,7 @@
       </c>
       <c r="N22" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O22" s="1" t="inlineStr">
@@ -1917,38 +1917,38 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>Commodities</t>
+          <t>PSE</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
         <v>22</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D23" s="2" t="n">
         <v>3</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>97.15000000000001</v>
+        <v>10.05</v>
       </c>
       <c r="H23" s="1" t="n">
-        <v>0.61</v>
+        <v>0.5</v>
       </c>
       <c r="I23" s="1" t="n">
-        <v>-0.15</v>
+        <v>-0.48</v>
       </c>
       <c r="J23" s="1" t="n">
-        <v>1.15</v>
+        <v>1.93</v>
       </c>
       <c r="K23" s="1" t="n">
-        <v>-2.83</v>
+        <v>-3.29</v>
       </c>
       <c r="L23" s="1" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         </is>
       </c>
       <c r="M23" s="1" t="n">
-        <v>-8.4</v>
+        <v>-10.41</v>
       </c>
       <c r="N23" s="1" t="inlineStr">
         <is>
@@ -1982,38 +1982,38 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Commodities</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
         <v>23</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>-3</v>
+        <v>1</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>-7</v>
+        <v>-4</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>92.3</v>
+        <v>97.5</v>
       </c>
       <c r="H24" s="1" t="n">
-        <v>0.47</v>
+        <v>0.36</v>
       </c>
       <c r="I24" s="1" t="n">
-        <v>-0.03</v>
+        <v>-0.66</v>
       </c>
       <c r="J24" s="1" t="n">
-        <v>-0.29</v>
+        <v>0.79</v>
       </c>
       <c r="K24" s="1" t="n">
-        <v>-3.35</v>
+        <v>-3.29</v>
       </c>
       <c r="L24" s="1" t="inlineStr">
         <is>
@@ -2021,7 +2021,7 @@
         </is>
       </c>
       <c r="M24" s="1" t="n">
-        <v>-4.93</v>
+        <v>-8.81</v>
       </c>
       <c r="N24" s="1" t="inlineStr">
         <is>
@@ -2047,7 +2047,7 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>PSU Bank</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
@@ -2057,36 +2057,36 @@
         <v>-2</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>-8</v>
+        <v>-1</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>-15</v>
+        <v>-3</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>-1</v>
+        <v>-7</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>92.38</v>
+        <v>92.95999999999999</v>
       </c>
       <c r="H25" s="1" t="n">
-        <v>1.24</v>
+        <v>0.72</v>
       </c>
       <c r="I25" s="1" t="n">
-        <v>0.06</v>
+        <v>-1.18</v>
       </c>
       <c r="J25" s="1" t="n">
-        <v>-0.8</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="K25" s="1" t="n">
-        <v>-3.65</v>
+        <v>-3.51</v>
       </c>
       <c r="L25" s="1" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Down</t>
         </is>
       </c>
       <c r="M25" s="1" t="n">
-        <v>-13.46</v>
+        <v>-5.03</v>
       </c>
       <c r="N25" s="1" t="inlineStr">
         <is>
@@ -2112,7 +2112,7 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>PSE</t>
+          <t>PSU Bank</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
@@ -2122,36 +2122,36 @@
         <v>-1</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>-1</v>
+        <v>-8</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>2</v>
+        <v>-16</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>9.93</v>
+        <v>92.65000000000001</v>
       </c>
       <c r="H26" s="1" t="n">
-        <v>0</v>
+        <v>0.48</v>
       </c>
       <c r="I26" s="1" t="n">
-        <v>-0.78</v>
+        <v>-0.5</v>
       </c>
       <c r="J26" s="1" t="n">
-        <v>1.19</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="K26" s="1" t="n">
-        <v>-3.95</v>
+        <v>-3.75</v>
       </c>
       <c r="L26" s="1" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Down</t>
         </is>
       </c>
       <c r="M26" s="1" t="n">
-        <v>-10.75</v>
+        <v>-13.91</v>
       </c>
       <c r="N26" s="1" t="inlineStr">
         <is>
@@ -2190,25 +2190,25 @@
         <v>1</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="F27" s="2" t="n">
         <v>-18</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>37.53</v>
+        <v>38</v>
       </c>
       <c r="H27" s="1" t="n">
-        <v>0.13</v>
+        <v>1.47</v>
       </c>
       <c r="I27" s="1" t="n">
-        <v>-0.33</v>
+        <v>-0.04</v>
       </c>
       <c r="J27" s="1" t="n">
-        <v>1.05</v>
+        <v>2.06</v>
       </c>
       <c r="K27" s="1" t="n">
-        <v>-5.12</v>
+        <v>-5.28</v>
       </c>
       <c r="L27" s="1" t="inlineStr">
         <is>
@@ -2220,22 +2220,22 @@
       </c>
       <c r="N27" s="1" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O27" s="1" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="O27" s="1" t="inlineStr">
+      <c r="P27" s="1" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P27" s="1" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="Q27" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -2255,25 +2255,25 @@
         <v>-1</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>-1</v>
+        <v>-3</v>
       </c>
       <c r="F28" s="2" t="n">
         <v>-3</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>49.12</v>
+        <v>49.28</v>
       </c>
       <c r="H28" s="1" t="n">
-        <v>-0.04</v>
+        <v>0.33</v>
       </c>
       <c r="I28" s="1" t="n">
-        <v>2.29</v>
+        <v>1.51</v>
       </c>
       <c r="J28" s="1" t="n">
-        <v>-0.67</v>
+        <v>-1.61</v>
       </c>
       <c r="K28" s="1" t="n">
-        <v>-5.15</v>
+        <v>-5.69</v>
       </c>
       <c r="L28" s="1" t="inlineStr">
         <is>
@@ -2281,7 +2281,7 @@
         </is>
       </c>
       <c r="M28" s="1" t="n">
-        <v>-16.05</v>
+        <v>-16.46</v>
       </c>
       <c r="N28" s="1" t="inlineStr">
         <is>
@@ -2569,20 +2569,20 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B2" s="1" t="n">
         <v>6</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F2" s="1" t="n">
         <v>7</v>
@@ -2597,43 +2597,43 @@
         <v>4</v>
       </c>
       <c r="J2" s="1" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K2" s="1" t="n">
         <v>5</v>
       </c>
       <c r="L2" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M2" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N2" s="1" t="n">
         <v>13</v>
       </c>
       <c r="O2" s="1" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="P2" s="1" t="n">
         <v>26</v>
       </c>
       <c r="Q2" s="1" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="R2" s="1" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="S2" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="T2" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="U2" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="T2" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="U2" s="1" t="n">
-        <v>18</v>
-      </c>
       <c r="V2" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="W2" s="1" t="n">
         <v>21</v>
@@ -2648,7 +2648,7 @@
         <v>12</v>
       </c>
       <c r="AA2" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AB2" s="1" t="n">
         <v>8</v>
@@ -2657,26 +2657,26 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
         <v>5</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E3" s="1" t="n">
         <v>25</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H3" s="1" t="n">
         <v>2</v>
@@ -2685,7 +2685,7 @@
         <v>4</v>
       </c>
       <c r="J3" s="1" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="K3" s="1" t="n">
         <v>6</v>
@@ -2697,34 +2697,34 @@
         <v>24</v>
       </c>
       <c r="N3" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O3" s="1" t="n">
         <v>22</v>
       </c>
       <c r="P3" s="1" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Q3" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="R3" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="S3" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="T3" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="U3" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="V3" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="W3" s="1" t="n">
         <v>23</v>
-      </c>
-      <c r="R3" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="S3" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="T3" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="U3" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="V3" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="W3" s="1" t="n">
-        <v>21</v>
       </c>
       <c r="X3" s="1" t="n">
         <v>3</v>
@@ -2733,35 +2733,35 @@
         <v>1</v>
       </c>
       <c r="Z3" s="1" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="AA3" s="1" t="n">
         <v>14</v>
       </c>
       <c r="AB3" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G4" s="1" t="n">
         <v>27</v>
@@ -2773,19 +2773,19 @@
         <v>4</v>
       </c>
       <c r="J4" s="1" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="K4" s="1" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L4" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M4" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="N4" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O4" s="1" t="n">
         <v>21</v>
@@ -2794,22 +2794,22 @@
         <v>26</v>
       </c>
       <c r="Q4" s="1" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="R4" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="S4" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="T4" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="S4" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="T4" s="1" t="n">
-        <v>20</v>
-      </c>
       <c r="U4" s="1" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="V4" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="W4" s="1" t="n">
         <v>22</v>
@@ -2821,23 +2821,23 @@
         <v>1</v>
       </c>
       <c r="Z4" s="1" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AA4" s="1" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="AB4" s="1" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C5" s="1" t="n">
         <v>16</v>
@@ -2846,7 +2846,7 @@
         <v>18</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F5" s="1" t="n">
         <v>9</v>
@@ -2858,22 +2858,22 @@
         <v>2</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J5" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="K5" s="1" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L5" s="1" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="M5" s="1" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="N5" s="1" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="O5" s="1" t="n">
         <v>21</v>
@@ -2885,22 +2885,22 @@
         <v>25</v>
       </c>
       <c r="R5" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="S5" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="T5" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="S5" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="T5" s="1" t="n">
-        <v>19</v>
-      </c>
       <c r="U5" s="1" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="V5" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="W5" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="X5" s="1" t="n">
         <v>3</v>
@@ -2909,62 +2909,62 @@
         <v>1</v>
       </c>
       <c r="Z5" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AA5" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AB5" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E6" s="1" t="n">
         <v>24</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G6" s="1" t="n">
         <v>27</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I6" s="1" t="n">
         <v>6</v>
       </c>
       <c r="J6" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K6" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L6" s="1" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="M6" s="1" t="n">
         <v>22</v>
       </c>
       <c r="N6" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O6" s="1" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="P6" s="1" t="n">
         <v>26</v>
@@ -2973,86 +2973,86 @@
         <v>25</v>
       </c>
       <c r="R6" s="1" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="S6" s="1" t="n">
         <v>5</v>
       </c>
       <c r="T6" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="U6" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="V6" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="V6" s="1" t="n">
-        <v>13</v>
-      </c>
       <c r="W6" s="1" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="X6" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y6" s="1" t="n">
         <v>1</v>
       </c>
       <c r="Z6" s="1" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AA6" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AB6" s="1" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D7" s="1" t="n">
         <v>21</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G7" s="1" t="n">
         <v>27</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I7" s="1" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J7" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K7" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M7" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N7" s="1" t="n">
         <v>12</v>
       </c>
       <c r="O7" s="1" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="P7" s="1" t="n">
         <v>26</v>
@@ -3061,110 +3061,110 @@
         <v>25</v>
       </c>
       <c r="R7" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="S7" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T7" s="1" t="n">
         <v>20</v>
       </c>
       <c r="U7" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="V7" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="V7" s="1" t="n">
-        <v>11</v>
-      </c>
       <c r="W7" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="X7" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y7" s="1" t="n">
         <v>1</v>
       </c>
       <c r="Z7" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA7" s="1" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AB7" s="1" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="C8" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="C8" s="1" t="n">
-        <v>16</v>
-      </c>
       <c r="D8" s="1" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G8" s="1" t="n">
         <v>27</v>
       </c>
       <c r="H8" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J8" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K8" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M8" s="1" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N8" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="O8" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="P8" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q8" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="R8" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="S8" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="T8" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="U8" s="1" t="n">
         <v>13</v>
-      </c>
-      <c r="O8" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="P8" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="Q8" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="R8" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="S8" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="T8" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="U8" s="1" t="n">
-        <v>14</v>
       </c>
       <c r="V8" s="1" t="n">
         <v>11</v>
       </c>
       <c r="W8" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="X8" s="1" t="n">
         <v>3</v>
@@ -3173,29 +3173,29 @@
         <v>1</v>
       </c>
       <c r="Z8" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA8" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="AB8" s="1" t="n">
         <v>9</v>
-      </c>
-      <c r="AA8" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="AB8" s="1" t="n">
-        <v>10</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="C9" s="1" t="n">
         <v>16</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E9" s="1" t="n">
         <v>23</v>
@@ -3213,46 +3213,46 @@
         <v>7</v>
       </c>
       <c r="J9" s="1" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="K9" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L9" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M9" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N9" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O9" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="P9" s="1" t="n">
         <v>25</v>
-      </c>
-      <c r="P9" s="1" t="n">
-        <v>26</v>
       </c>
       <c r="Q9" s="1" t="n">
         <v>24</v>
       </c>
       <c r="R9" s="1" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="S9" s="1" t="n">
         <v>5</v>
       </c>
       <c r="T9" s="1" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="U9" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="V9" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="W9" s="1" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="X9" s="1" t="n">
         <v>3</v>
@@ -3261,10 +3261,10 @@
         <v>1</v>
       </c>
       <c r="Z9" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA9" s="1" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AB9" s="1" t="n">
         <v>10</v>
@@ -3273,59 +3273,59 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F10" s="1" t="n">
         <v>6</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H10" s="1" t="n">
         <v>4</v>
       </c>
       <c r="I10" s="1" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J10" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K10" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L10" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M10" s="1" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N10" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="O10" s="1" t="n">
         <v>25</v>
       </c>
       <c r="P10" s="1" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Q10" s="1" t="n">
         <v>24</v>
       </c>
       <c r="R10" s="1" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="S10" s="1" t="n">
         <v>5</v>
@@ -3337,10 +3337,10 @@
         <v>13</v>
       </c>
       <c r="V10" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="W10" s="1" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="X10" s="1" t="n">
         <v>3</v>
@@ -3349,35 +3349,35 @@
         <v>1</v>
       </c>
       <c r="Z10" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA10" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AB10" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="C11" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="C11" s="1" t="n">
-        <v>10</v>
-      </c>
       <c r="D11" s="1" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G11" s="1" t="n">
         <v>26</v>
@@ -3386,22 +3386,22 @@
         <v>4</v>
       </c>
       <c r="I11" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J11" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K11" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M11" s="1" t="n">
         <v>23</v>
       </c>
       <c r="N11" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O11" s="1" t="n">
         <v>25</v>
@@ -3413,22 +3413,22 @@
         <v>24</v>
       </c>
       <c r="R11" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="S11" s="1" t="n">
         <v>5</v>
       </c>
       <c r="T11" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="U11" s="1" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="V11" s="1" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="W11" s="1" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="X11" s="1" t="n">
         <v>3</v>
@@ -3440,32 +3440,32 @@
         <v>7</v>
       </c>
       <c r="AA11" s="1" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="AB11" s="1" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G12" s="1" t="n">
         <v>26</v>
@@ -3474,49 +3474,49 @@
         <v>4</v>
       </c>
       <c r="I12" s="1" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="J12" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K12" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="M12" s="1" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="N12" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O12" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="P12" s="1" t="n">
         <v>27</v>
       </c>
       <c r="Q12" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R12" s="1" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="S12" s="1" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T12" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="U12" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="V12" s="1" t="n">
         <v>18</v>
       </c>
       <c r="W12" s="1" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="X12" s="1" t="n">
         <v>3</v>
@@ -3525,19 +3525,19 @@
         <v>1</v>
       </c>
       <c r="Z12" s="1" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AA12" s="1" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AB12" s="1" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
@@ -3547,7 +3547,7 @@
         <v>11</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E13" s="1" t="n">
         <v>16</v>
@@ -3556,7 +3556,7 @@
         <v>6</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H13" s="1" t="n">
         <v>4</v>
@@ -3571,40 +3571,40 @@
         <v>2</v>
       </c>
       <c r="L13" s="1" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="M13" s="1" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="N13" s="1" t="n">
         <v>14</v>
       </c>
       <c r="O13" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P13" s="1" t="n">
         <v>27</v>
       </c>
       <c r="Q13" s="1" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="R13" s="1" t="n">
         <v>19</v>
       </c>
       <c r="S13" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T13" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="U13" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="V13" s="1" t="n">
         <v>18</v>
       </c>
       <c r="W13" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="X13" s="1" t="n">
         <v>3</v>
@@ -3613,10 +3613,10 @@
         <v>1</v>
       </c>
       <c r="Z13" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA13" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AB13" s="1" t="n">
         <v>7</v>
@@ -3625,29 +3625,29 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F14" s="1" t="n">
         <v>6</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H14" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I14" s="1" t="n">
         <v>5</v>
@@ -3659,16 +3659,16 @@
         <v>2</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M14" s="1" t="n">
         <v>22</v>
       </c>
       <c r="N14" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="O14" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="P14" s="1" t="n">
         <v>27</v>
@@ -3677,34 +3677,34 @@
         <v>26</v>
       </c>
       <c r="R14" s="1" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="S14" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T14" s="1" t="n">
         <v>21</v>
       </c>
       <c r="U14" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="V14" s="1" t="n">
         <v>18</v>
-      </c>
-      <c r="V14" s="1" t="n">
-        <v>15</v>
       </c>
       <c r="W14" s="1" t="n">
         <v>20</v>
       </c>
       <c r="X14" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y14" s="1" t="n">
         <v>1</v>
       </c>
       <c r="Z14" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA14" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AB14" s="1" t="n">
         <v>7</v>
@@ -3713,7 +3713,7 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
@@ -3723,22 +3723,22 @@
         <v>10</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F15" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="G15" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="H15" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="G15" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="H15" s="1" t="n">
+      <c r="I15" s="1" t="n">
         <v>5</v>
-      </c>
-      <c r="I15" s="1" t="n">
-        <v>6</v>
       </c>
       <c r="J15" s="1" t="n">
         <v>23</v>
@@ -3747,37 +3747,37 @@
         <v>2</v>
       </c>
       <c r="L15" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M15" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="N15" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="O15" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="P15" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q15" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="R15" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="S15" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="T15" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="N15" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="O15" s="1" t="n">
-        <v>27</v>
-      </c>
-      <c r="P15" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="Q15" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="R15" s="1" t="n">
+      <c r="U15" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="S15" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="T15" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="U15" s="1" t="n">
+      <c r="V15" s="1" t="n">
         <v>15</v>
-      </c>
-      <c r="V15" s="1" t="n">
-        <v>17</v>
       </c>
       <c r="W15" s="1" t="n">
         <v>20</v>
@@ -3789,7 +3789,7 @@
         <v>1</v>
       </c>
       <c r="Z15" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA15" s="1" t="n">
         <v>16</v>
@@ -3801,77 +3801,77 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D16" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="E16" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="E16" s="1" t="n">
-        <v>14</v>
-      </c>
       <c r="F16" s="1" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G16" s="1" t="n">
         <v>24</v>
       </c>
       <c r="H16" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I16" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J16" s="1" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="K16" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L16" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="M16" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="N16" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="O16" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="P16" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q16" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="R16" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="S16" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="T16" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="U16" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="V16" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="M16" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="N16" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="O16" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="P16" s="1" t="n">
-        <v>27</v>
-      </c>
-      <c r="Q16" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="R16" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="S16" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="T16" s="1" t="n">
-        <v>23</v>
-      </c>
-      <c r="U16" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="V16" s="1" t="n">
-        <v>16</v>
-      </c>
       <c r="W16" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="X16" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y16" s="1" t="n">
         <v>1</v>
@@ -3880,26 +3880,26 @@
         <v>8</v>
       </c>
       <c r="AA16" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AB16" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="C17" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="C17" s="1" t="n">
-        <v>10</v>
-      </c>
       <c r="D17" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E17" s="1" t="n">
         <v>14</v>
@@ -3917,34 +3917,34 @@
         <v>7</v>
       </c>
       <c r="J17" s="1" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K17" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L17" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M17" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N17" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="O17" s="1" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P17" s="1" t="n">
         <v>27</v>
       </c>
       <c r="Q17" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="R17" s="1" t="n">
         <v>19</v>
       </c>
       <c r="S17" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T17" s="1" t="n">
         <v>23</v>
@@ -3956,7 +3956,7 @@
         <v>16</v>
       </c>
       <c r="W17" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="X17" s="1" t="n">
         <v>3</v>
@@ -3965,47 +3965,47 @@
         <v>1</v>
       </c>
       <c r="Z17" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA17" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="AB17" s="1" t="n">
         <v>6</v>
-      </c>
-      <c r="AA17" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="AB17" s="1" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
         <v>11</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D18" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="E18" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="E18" s="1" t="n">
-        <v>12</v>
-      </c>
       <c r="F18" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G18" s="1" t="n">
         <v>24</v>
       </c>
       <c r="H18" s="1" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I18" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J18" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K18" s="1" t="n">
         <v>2</v>
@@ -4014,7 +4014,7 @@
         <v>15</v>
       </c>
       <c r="M18" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N18" s="1" t="n">
         <v>13</v>
@@ -4032,7 +4032,7 @@
         <v>19</v>
       </c>
       <c r="S18" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T18" s="1" t="n">
         <v>23</v>
@@ -4041,7 +4041,7 @@
         <v>18</v>
       </c>
       <c r="V18" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="W18" s="1" t="n">
         <v>20</v>
@@ -4053,32 +4053,32 @@
         <v>1</v>
       </c>
       <c r="Z18" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA18" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AB18" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C19" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="E19" s="1" t="n">
         <v>12</v>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>13</v>
       </c>
       <c r="F19" s="1" t="n">
         <v>4</v>
@@ -4087,10 +4087,10 @@
         <v>24</v>
       </c>
       <c r="H19" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I19" s="1" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J19" s="1" t="n">
         <v>21</v>
@@ -4099,40 +4099,40 @@
         <v>2</v>
       </c>
       <c r="L19" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="M19" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="N19" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="O19" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="P19" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q19" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="R19" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="S19" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="U19" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="M19" s="1" t="n">
+      <c r="V19" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="W19" s="1" t="n">
         <v>20</v>
-      </c>
-      <c r="N19" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="O19" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="P19" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="Q19" s="1" t="n">
-        <v>27</v>
-      </c>
-      <c r="R19" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="S19" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="T19" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="U19" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="V19" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="W19" s="1" t="n">
-        <v>23</v>
       </c>
       <c r="X19" s="1" t="n">
         <v>3</v>
@@ -4141,38 +4141,38 @@
         <v>1</v>
       </c>
       <c r="Z19" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA19" s="1" t="n">
         <v>16</v>
       </c>
       <c r="AB19" s="1" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C20" s="1" t="n">
         <v>12</v>
       </c>
       <c r="D20" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F20" s="1" t="n">
         <v>4</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H20" s="1" t="n">
         <v>7</v>
@@ -4181,7 +4181,7 @@
         <v>11</v>
       </c>
       <c r="J20" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K20" s="1" t="n">
         <v>2</v>
@@ -4190,25 +4190,25 @@
         <v>18</v>
       </c>
       <c r="M20" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="N20" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="O20" s="1" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="P20" s="1" t="n">
         <v>26</v>
       </c>
       <c r="Q20" s="1" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="R20" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="S20" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T20" s="1" t="n">
         <v>22</v>
@@ -4217,7 +4217,7 @@
         <v>19</v>
       </c>
       <c r="V20" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="W20" s="1" t="n">
         <v>23</v>
@@ -4232,7 +4232,7 @@
         <v>6</v>
       </c>
       <c r="AA20" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AB20" s="1" t="n">
         <v>5</v>
@@ -4241,47 +4241,47 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C21" s="1" t="n">
         <v>12</v>
       </c>
       <c r="D21" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="E21" s="1" t="n">
         <v>15</v>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>10</v>
       </c>
       <c r="F21" s="1" t="n">
         <v>4</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H21" s="1" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I21" s="1" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J21" s="1" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K21" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L21" s="1" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M21" s="1" t="n">
         <v>21</v>
       </c>
       <c r="N21" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O21" s="1" t="n">
         <v>27</v>
@@ -4290,59 +4290,59 @@
         <v>26</v>
       </c>
       <c r="Q21" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R21" s="1" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="S21" s="1" t="n">
         <v>8</v>
       </c>
       <c r="T21" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="U21" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="V21" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="W21" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="U21" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="V21" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="W21" s="1" t="n">
+      <c r="X21" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y21" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="X21" s="1" t="n">
+      <c r="Z21" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA21" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="AB21" s="1" t="n">
         <v>5</v>
-      </c>
-      <c r="Y21" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z21" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA21" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="AB21" s="1" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
         <v>13</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D22" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F22" s="1" t="n">
         <v>4</v>
@@ -4351,13 +4351,13 @@
         <v>24</v>
       </c>
       <c r="H22" s="1" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I22" s="1" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="J22" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K22" s="1" t="n">
         <v>3</v>
@@ -4381,25 +4381,25 @@
         <v>25</v>
       </c>
       <c r="R22" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="S22" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="T22" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="U22" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="V22" s="1" t="n">
         <v>16</v>
-      </c>
-      <c r="S22" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="T22" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="U22" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="V22" s="1" t="n">
-        <v>15</v>
       </c>
       <c r="W22" s="1" t="n">
         <v>1</v>
       </c>
       <c r="X22" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y22" s="1" t="n">
         <v>2</v>
@@ -4408,26 +4408,26 @@
         <v>7</v>
       </c>
       <c r="AA22" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AB22" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D23" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E23" s="1" t="n">
         <v>9</v>
@@ -4436,22 +4436,22 @@
         <v>4</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H23" s="1" t="n">
         <v>12</v>
       </c>
       <c r="I23" s="1" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J23" s="1" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K23" s="1" t="n">
         <v>3</v>
       </c>
       <c r="L23" s="1" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="M23" s="1" t="n">
         <v>21</v>
@@ -4463,25 +4463,25 @@
         <v>27</v>
       </c>
       <c r="P23" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q23" s="1" t="n">
         <v>25</v>
-      </c>
-      <c r="Q23" s="1" t="n">
-        <v>24</v>
       </c>
       <c r="R23" s="1" t="n">
         <v>16</v>
       </c>
       <c r="S23" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T23" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="U23" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="V23" s="1" t="n">
         <v>15</v>
-      </c>
-      <c r="V23" s="1" t="n">
-        <v>14</v>
       </c>
       <c r="W23" s="1" t="n">
         <v>1</v>
@@ -4505,38 +4505,38 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C24" s="1" t="n">
         <v>10</v>
       </c>
       <c r="D24" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E24" s="1" t="n">
         <v>9</v>
       </c>
       <c r="F24" s="1" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H24" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I24" s="1" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J24" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K24" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L24" s="1" t="n">
         <v>20</v>
@@ -4548,37 +4548,37 @@
         <v>11</v>
       </c>
       <c r="O24" s="1" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P24" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q24" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="Q24" s="1" t="n">
-        <v>25</v>
-      </c>
       <c r="R24" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="S24" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="T24" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="U24" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="V24" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="S24" s="1" t="n">
+      <c r="W24" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="X24" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="T24" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="U24" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="V24" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="W24" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="X24" s="1" t="n">
-        <v>8</v>
-      </c>
       <c r="Y24" s="1" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Z24" s="1" t="n">
         <v>7</v>
@@ -4593,20 +4593,20 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="C25" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="C25" s="1" t="n">
-        <v>11</v>
-      </c>
       <c r="D25" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F25" s="1" t="n">
         <v>2</v>
@@ -4615,10 +4615,10 @@
         <v>27</v>
       </c>
       <c r="H25" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I25" s="1" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J25" s="1" t="n">
         <v>23</v>
@@ -4633,7 +4633,7 @@
         <v>21</v>
       </c>
       <c r="N25" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="O25" s="1" t="n">
         <v>26</v>
@@ -4645,10 +4645,10 @@
         <v>25</v>
       </c>
       <c r="R25" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S25" s="1" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T25" s="1" t="n">
         <v>22</v>
@@ -4657,13 +4657,13 @@
         <v>16</v>
       </c>
       <c r="V25" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="W25" s="1" t="n">
         <v>3</v>
       </c>
       <c r="X25" s="1" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y25" s="1" t="n">
         <v>4</v>
@@ -4681,38 +4681,38 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D26" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="E26" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="F26" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G26" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="H26" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="I26" s="1" t="n">
         <v>19</v>
-      </c>
-      <c r="E26" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="F26" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="G26" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="H26" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="I26" s="1" t="n">
-        <v>18</v>
       </c>
       <c r="J26" s="1" t="n">
         <v>23</v>
       </c>
       <c r="K26" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L26" s="1" t="n">
         <v>20</v>
@@ -4721,10 +4721,10 @@
         <v>21</v>
       </c>
       <c r="N26" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="O26" s="1" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P26" s="1" t="n">
         <v>24</v>
@@ -4733,7 +4733,7 @@
         <v>25</v>
       </c>
       <c r="R26" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="S26" s="1" t="n">
         <v>9</v>
@@ -4742,25 +4742,25 @@
         <v>22</v>
       </c>
       <c r="U26" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="V26" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="W26" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X26" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y26" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="Y26" s="1" t="n">
-        <v>2</v>
-      </c>
       <c r="Z26" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA26" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AB26" s="1" t="n">
         <v>5</v>
@@ -4769,41 +4769,41 @@
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C27" s="1" t="n">
         <v>12</v>
       </c>
       <c r="D27" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F27" s="1" t="n">
         <v>7</v>
       </c>
       <c r="G27" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="H27" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="I27" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="J27" s="1" t="n">
         <v>23</v>
-      </c>
-      <c r="H27" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="I27" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="J27" s="1" t="n">
-        <v>24</v>
       </c>
       <c r="K27" s="1" t="n">
         <v>3</v>
       </c>
       <c r="L27" s="1" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M27" s="1" t="n">
         <v>21</v>
@@ -4815,25 +4815,25 @@
         <v>27</v>
       </c>
       <c r="P27" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q27" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="Q27" s="1" t="n">
-        <v>26</v>
-      </c>
       <c r="R27" s="1" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="S27" s="1" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="T27" s="1" t="n">
         <v>22</v>
       </c>
       <c r="U27" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="V27" s="1" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="W27" s="1" t="n">
         <v>1</v>
@@ -4848,50 +4848,50 @@
         <v>8</v>
       </c>
       <c r="AA27" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AB27" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="C28" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D28" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="E28" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="F28" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C28" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="D28" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="E28" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="F28" s="1" t="n">
-        <v>5</v>
-      </c>
       <c r="G28" s="1" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="H28" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I28" s="1" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J28" s="1" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K28" s="1" t="n">
         <v>3</v>
       </c>
       <c r="L28" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M28" s="1" t="n">
         <v>21</v>
@@ -4903,25 +4903,25 @@
         <v>27</v>
       </c>
       <c r="P28" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Q28" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="R28" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="S28" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="S28" s="1" t="n">
-        <v>19</v>
-      </c>
       <c r="T28" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="U28" s="1" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="V28" s="1" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="W28" s="1" t="n">
         <v>1</v>
@@ -4933,10 +4933,10 @@
         <v>2</v>
       </c>
       <c r="Z28" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA28" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AB28" s="1" t="n">
         <v>6</v>
@@ -4945,20 +4945,20 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C29" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="D29" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="D29" s="1" t="n">
-        <v>20</v>
-      </c>
       <c r="E29" s="1" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F29" s="1" t="n">
         <v>5</v>
@@ -4967,10 +4967,10 @@
         <v>26</v>
       </c>
       <c r="H29" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I29" s="1" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J29" s="1" t="n">
         <v>22</v>
@@ -4979,34 +4979,34 @@
         <v>3</v>
       </c>
       <c r="L29" s="1" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M29" s="1" t="n">
         <v>21</v>
       </c>
       <c r="N29" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="O29" s="1" t="n">
         <v>27</v>
       </c>
       <c r="P29" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q29" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="Q29" s="1" t="n">
-        <v>24</v>
-      </c>
       <c r="R29" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="S29" s="1" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="T29" s="1" t="n">
         <v>23</v>
       </c>
       <c r="U29" s="1" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="V29" s="1" t="n">
         <v>17</v>
@@ -5021,10 +5021,10 @@
         <v>2</v>
       </c>
       <c r="Z29" s="1" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AA29" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AB29" s="1" t="n">
         <v>6</v>
@@ -5033,44 +5033,44 @@
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D30" s="1" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F30" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G30" s="1" t="n">
         <v>26</v>
       </c>
       <c r="H30" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I30" s="1" t="n">
         <v>10</v>
       </c>
       <c r="J30" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K30" s="1" t="n">
         <v>3</v>
       </c>
       <c r="L30" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M30" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N30" s="1" t="n">
         <v>11</v>
@@ -5085,10 +5085,10 @@
         <v>24</v>
       </c>
       <c r="R30" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="S30" s="1" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="T30" s="1" t="n">
         <v>23</v>
@@ -5097,13 +5097,13 @@
         <v>18</v>
       </c>
       <c r="V30" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="W30" s="1" t="n">
         <v>1</v>
       </c>
       <c r="X30" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y30" s="1" t="n">
         <v>2</v>
@@ -5112,7 +5112,7 @@
         <v>7</v>
       </c>
       <c r="AA30" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AB30" s="1" t="n">
         <v>6</v>
@@ -5121,38 +5121,38 @@
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
         <v>9</v>
       </c>
       <c r="C31" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D31" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="E31" s="1" t="n">
         <v>13</v>
-      </c>
-      <c r="D31" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="E31" s="1" t="n">
-        <v>11</v>
       </c>
       <c r="F31" s="1" t="n">
         <v>4</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H31" s="1" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I31" s="1" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J31" s="1" t="n">
         <v>21</v>
       </c>
       <c r="K31" s="1" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="L31" s="1" t="n">
         <v>20</v>
@@ -5161,28 +5161,28 @@
         <v>22</v>
       </c>
       <c r="N31" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="O31" s="1" t="n">
         <v>27</v>
       </c>
       <c r="P31" s="1" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Q31" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R31" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="S31" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="T31" s="1" t="n">
         <v>23</v>
       </c>
       <c r="U31" s="1" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="V31" s="1" t="n">
         <v>15</v>
@@ -5197,10 +5197,10 @@
         <v>2</v>
       </c>
       <c r="Z31" s="1" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AA31" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AB31" s="1" t="n">
         <v>6</v>
@@ -5209,47 +5209,47 @@
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C32" s="1" t="n">
         <v>13</v>
       </c>
       <c r="D32" s="1" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="F32" s="1" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H32" s="1" t="n">
         <v>3</v>
       </c>
       <c r="I32" s="1" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J32" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="K32" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="L32" s="1" t="n">
         <v>20</v>
-      </c>
-      <c r="K32" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="L32" s="1" t="n">
-        <v>18</v>
       </c>
       <c r="M32" s="1" t="n">
         <v>22</v>
       </c>
       <c r="N32" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O32" s="1" t="n">
         <v>27</v>
@@ -5261,25 +5261,25 @@
         <v>25</v>
       </c>
       <c r="R32" s="1" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="S32" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="T32" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="U32" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="T32" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="U32" s="1" t="n">
-        <v>12</v>
-      </c>
       <c r="V32" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="W32" s="1" t="n">
         <v>1</v>
       </c>
       <c r="X32" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y32" s="1" t="n">
         <v>2</v>
@@ -5297,44 +5297,44 @@
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D33" s="1" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F33" s="1" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G33" s="1" t="n">
         <v>23</v>
       </c>
       <c r="H33" s="1" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I33" s="1" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J33" s="1" t="n">
         <v>20</v>
       </c>
       <c r="K33" s="1" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L33" s="1" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="M33" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N33" s="1" t="n">
         <v>11</v>
@@ -5346,86 +5346,86 @@
         <v>26</v>
       </c>
       <c r="Q33" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="R33" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="S33" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="T33" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="R33" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="S33" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="T33" s="1" t="n">
-        <v>25</v>
-      </c>
       <c r="U33" s="1" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="V33" s="1" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="W33" s="1" t="n">
         <v>1</v>
       </c>
       <c r="X33" s="1" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Y33" s="1" t="n">
         <v>2</v>
       </c>
       <c r="Z33" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA33" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AB33" s="1" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
         <v>10</v>
       </c>
       <c r="C34" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="D34" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="D34" s="1" t="n">
-        <v>11</v>
-      </c>
       <c r="E34" s="1" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F34" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G34" s="1" t="n">
         <v>23</v>
       </c>
       <c r="H34" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="I34" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="J34" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="K34" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="I34" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="J34" s="1" t="n">
+      <c r="L34" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="M34" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="K34" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="L34" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="M34" s="1" t="n">
-        <v>22</v>
-      </c>
       <c r="N34" s="1" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="O34" s="1" t="n">
         <v>27</v>
@@ -5437,7 +5437,7 @@
         <v>24</v>
       </c>
       <c r="R34" s="1" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="S34" s="1" t="n">
         <v>19</v>
@@ -5446,16 +5446,16 @@
         <v>25</v>
       </c>
       <c r="U34" s="1" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="V34" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="W34" s="1" t="n">
         <v>1</v>
       </c>
       <c r="X34" s="1" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Y34" s="1" t="n">
         <v>2</v>
@@ -5464,23 +5464,23 @@
         <v>9</v>
       </c>
       <c r="AA34" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AB34" s="1" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
         <v>10</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D35" s="1" t="n">
         <v>11</v>
@@ -5489,7 +5489,7 @@
         <v>20</v>
       </c>
       <c r="F35" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G35" s="1" t="n">
         <v>23</v>
@@ -5501,19 +5501,19 @@
         <v>7</v>
       </c>
       <c r="J35" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K35" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L35" s="1" t="n">
         <v>13</v>
       </c>
       <c r="M35" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N35" s="1" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="O35" s="1" t="n">
         <v>27</v>
@@ -5525,19 +5525,19 @@
         <v>24</v>
       </c>
       <c r="R35" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="S35" s="1" t="n">
         <v>19</v>
-      </c>
-      <c r="S35" s="1" t="n">
-        <v>18</v>
       </c>
       <c r="T35" s="1" t="n">
         <v>25</v>
       </c>
       <c r="U35" s="1" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="V35" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="W35" s="1" t="n">
         <v>1</v>
@@ -5552,7 +5552,7 @@
         <v>9</v>
       </c>
       <c r="AA35" s="1" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AB35" s="1" t="n">
         <v>8</v>
@@ -5561,44 +5561,44 @@
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B36" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="C36" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="C36" s="1" t="n">
-        <v>16</v>
-      </c>
       <c r="D36" s="1" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F36" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G36" s="1" t="n">
         <v>23</v>
       </c>
       <c r="H36" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I36" s="1" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J36" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="K36" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="L36" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="M36" s="1" t="n">
         <v>21</v>
-      </c>
-      <c r="K36" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="L36" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="M36" s="1" t="n">
-        <v>20</v>
       </c>
       <c r="N36" s="1" t="n">
         <v>12</v>
@@ -5622,19 +5622,19 @@
         <v>25</v>
       </c>
       <c r="U36" s="1" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="V36" s="1" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="W36" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="X36" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="X36" s="1" t="n">
-        <v>7</v>
-      </c>
       <c r="Y36" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Z36" s="1" t="n">
         <v>9</v>
@@ -5649,23 +5649,23 @@
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B37" s="1" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C37" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="D37" s="1" t="n">
         <v>14</v>
-      </c>
-      <c r="D37" s="1" t="n">
-        <v>13</v>
       </c>
       <c r="E37" s="1" t="n">
         <v>22</v>
       </c>
       <c r="F37" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G37" s="1" t="n">
         <v>23</v>
@@ -5677,16 +5677,16 @@
         <v>3</v>
       </c>
       <c r="J37" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K37" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L37" s="1" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="M37" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="N37" s="1" t="n">
         <v>12</v>
@@ -5701,47 +5701,47 @@
         <v>24</v>
       </c>
       <c r="R37" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="S37" s="1" t="n">
         <v>18</v>
-      </c>
-      <c r="S37" s="1" t="n">
-        <v>19</v>
       </c>
       <c r="T37" s="1" t="n">
         <v>25</v>
       </c>
       <c r="U37" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="V37" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="W37" s="1" t="n">
         <v>4</v>
       </c>
       <c r="X37" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y37" s="1" t="n">
         <v>5</v>
       </c>
       <c r="Z37" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA37" s="1" t="n">
         <v>17</v>
       </c>
       <c r="AB37" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B38" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C38" s="1" t="n">
         <v>14</v>
@@ -5750,31 +5750,31 @@
         <v>13</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F38" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G38" s="1" t="n">
         <v>23</v>
       </c>
       <c r="H38" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I38" s="1" t="n">
         <v>3</v>
       </c>
       <c r="J38" s="1" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K38" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L38" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M38" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N38" s="1" t="n">
         <v>12</v>
@@ -5789,19 +5789,19 @@
         <v>24</v>
       </c>
       <c r="R38" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="S38" s="1" t="n">
         <v>19</v>
-      </c>
-      <c r="S38" s="1" t="n">
-        <v>18</v>
       </c>
       <c r="T38" s="1" t="n">
         <v>25</v>
       </c>
       <c r="U38" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="V38" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="W38" s="1" t="n">
         <v>4</v>
@@ -5813,10 +5813,10 @@
         <v>5</v>
       </c>
       <c r="Z38" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA38" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AB38" s="1" t="n">
         <v>9</v>
@@ -5825,26 +5825,26 @@
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B39" s="1" t="n">
         <v>11</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D39" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F39" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H39" s="1" t="n">
         <v>2</v>
@@ -5853,13 +5853,13 @@
         <v>3</v>
       </c>
       <c r="J39" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K39" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L39" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M39" s="1" t="n">
         <v>20</v>
@@ -5874,16 +5874,16 @@
         <v>26</v>
       </c>
       <c r="Q39" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="R39" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="S39" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="T39" s="1" t="n">
         <v>25</v>
-      </c>
-      <c r="R39" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="S39" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="T39" s="1" t="n">
-        <v>24</v>
       </c>
       <c r="U39" s="1" t="n">
         <v>10</v>
@@ -5901,35 +5901,35 @@
         <v>5</v>
       </c>
       <c r="Z39" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA39" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="AB39" s="1" t="n">
         <v>9</v>
-      </c>
-      <c r="AA39" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="AB39" s="1" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B40" s="1" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D40" s="1" t="n">
         <v>14</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F40" s="1" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G40" s="1" t="n">
         <v>21</v>
@@ -5947,7 +5947,7 @@
         <v>1</v>
       </c>
       <c r="L40" s="1" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="M40" s="1" t="n">
         <v>20</v>
@@ -5959,56 +5959,56 @@
         <v>27</v>
       </c>
       <c r="P40" s="1" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="Q40" s="1" t="n">
         <v>25</v>
       </c>
       <c r="R40" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="S40" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="T40" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="U40" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="T40" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="U40" s="1" t="n">
+      <c r="V40" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="W40" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="V40" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="W40" s="1" t="n">
+      <c r="X40" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="X40" s="1" t="n">
-        <v>11</v>
-      </c>
       <c r="Y40" s="1" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Z40" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA40" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="AB40" s="1" t="n">
         <v>8</v>
-      </c>
-      <c r="AA40" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="AB40" s="1" t="n">
-        <v>9</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B41" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="C41" s="1" t="n">
         <v>17</v>
-      </c>
-      <c r="C41" s="1" t="n">
-        <v>15</v>
       </c>
       <c r="D41" s="1" t="n">
         <v>14</v>
@@ -6020,7 +6020,7 @@
         <v>5</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="H41" s="1" t="n">
         <v>2</v>
@@ -6029,25 +6029,25 @@
         <v>3</v>
       </c>
       <c r="J41" s="1" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K41" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L41" s="1" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="M41" s="1" t="n">
         <v>20</v>
       </c>
       <c r="N41" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="O41" s="1" t="n">
         <v>27</v>
       </c>
       <c r="P41" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q41" s="1" t="n">
         <v>25</v>
@@ -6056,47 +6056,47 @@
         <v>16</v>
       </c>
       <c r="S41" s="1" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T41" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="U41" s="1" t="n">
         <v>4</v>
       </c>
       <c r="V41" s="1" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="W41" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X41" s="1" t="n">
         <v>11</v>
       </c>
       <c r="Y41" s="1" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Z41" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA41" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="AB41" s="1" t="n">
         <v>9</v>
-      </c>
-      <c r="AA41" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="AB41" s="1" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B42" s="1" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D42" s="1" t="n">
         <v>14</v>
@@ -6117,34 +6117,34 @@
         <v>3</v>
       </c>
       <c r="J42" s="1" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K42" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L42" s="1" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M42" s="1" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="N42" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="O42" s="1" t="n">
         <v>27</v>
       </c>
       <c r="P42" s="1" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q42" s="1" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="R42" s="1" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="S42" s="1" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T42" s="1" t="n">
         <v>21</v>
@@ -6156,13 +6156,13 @@
         <v>12</v>
       </c>
       <c r="W42" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X42" s="1" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="Y42" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z42" s="1" t="n">
         <v>9</v>
@@ -6171,59 +6171,59 @@
         <v>19</v>
       </c>
       <c r="AB42" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B43" s="1" t="n">
         <v>25</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D43" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F43" s="1" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G43" s="1" t="n">
         <v>24</v>
       </c>
       <c r="H43" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I43" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="J43" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="K43" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="I43" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="J43" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="K43" s="1" t="n">
-        <v>3</v>
-      </c>
       <c r="L43" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M43" s="1" t="n">
         <v>18</v>
       </c>
       <c r="N43" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="O43" s="1" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P43" s="1" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="Q43" s="1" t="n">
         <v>23</v>
@@ -6232,56 +6232,56 @@
         <v>13</v>
       </c>
       <c r="S43" s="1" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T43" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="U43" s="1" t="n">
         <v>4</v>
       </c>
       <c r="V43" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="W43" s="1" t="n">
         <v>6</v>
       </c>
       <c r="X43" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Y43" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z43" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA43" s="1" t="n">
         <v>19</v>
       </c>
       <c r="AB43" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B44" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="C44" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="D44" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="E44" s="1" t="n">
         <v>27</v>
       </c>
-      <c r="C44" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="D44" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="E44" s="1" t="n">
-        <v>25</v>
-      </c>
       <c r="F44" s="1" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G44" s="1" t="n">
         <v>24</v>
@@ -6290,61 +6290,61 @@
         <v>1</v>
       </c>
       <c r="I44" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="J44" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="K44" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="J44" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="K44" s="1" t="n">
-        <v>2</v>
-      </c>
       <c r="L44" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M44" s="1" t="n">
         <v>18</v>
       </c>
       <c r="N44" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="O44" s="1" t="n">
         <v>26</v>
       </c>
       <c r="P44" s="1" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q44" s="1" t="n">
         <v>23</v>
       </c>
       <c r="R44" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="S44" s="1" t="n">
         <v>5</v>
       </c>
       <c r="T44" s="1" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="U44" s="1" t="n">
         <v>4</v>
       </c>
       <c r="V44" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="W44" s="1" t="n">
         <v>6</v>
       </c>
       <c r="X44" s="1" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="Y44" s="1" t="n">
         <v>7</v>
       </c>
       <c r="Z44" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA44" s="1" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AB44" s="1" t="n">
         <v>8</v>
@@ -6353,47 +6353,47 @@
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B45" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C45" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="D45" s="1" t="n">
         <v>13</v>
-      </c>
-      <c r="D45" s="1" t="n">
-        <v>6</v>
       </c>
       <c r="E45" s="1" t="n">
         <v>25</v>
       </c>
       <c r="F45" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H45" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I45" s="1" t="n">
         <v>3</v>
       </c>
       <c r="J45" s="1" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="K45" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L45" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M45" s="1" t="n">
         <v>18</v>
       </c>
       <c r="N45" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="O45" s="1" t="n">
         <v>26</v>
@@ -6411,53 +6411,53 @@
         <v>5</v>
       </c>
       <c r="T45" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="U45" s="1" t="n">
         <v>4</v>
       </c>
       <c r="V45" s="1" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="W45" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X45" s="1" t="n">
         <v>17</v>
       </c>
       <c r="Y45" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z45" s="1" t="n">
         <v>9</v>
       </c>
       <c r="AA45" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AB45" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B46" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C46" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="D46" s="1" t="n">
         <v>6</v>
-      </c>
-      <c r="D46" s="1" t="n">
-        <v>5</v>
       </c>
       <c r="E46" s="1" t="n">
         <v>25</v>
       </c>
       <c r="F46" s="1" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="G46" s="1" t="n">
         <v>22</v>
@@ -6481,22 +6481,22 @@
         <v>18</v>
       </c>
       <c r="N46" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="O46" s="1" t="n">
         <v>26</v>
       </c>
       <c r="P46" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Q46" s="1" t="n">
         <v>23</v>
       </c>
       <c r="R46" s="1" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="S46" s="1" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T46" s="1" t="n">
         <v>21</v>
@@ -6505,50 +6505,50 @@
         <v>4</v>
       </c>
       <c r="V46" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="W46" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X46" s="1" t="n">
         <v>17</v>
       </c>
       <c r="Y46" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z46" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="Z46" s="1" t="n">
+      <c r="AA46" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="AB46" s="1" t="n">
         <v>10</v>
-      </c>
-      <c r="AA46" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="AB46" s="1" t="n">
-        <v>11</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B47" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D47" s="1" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E47" s="1" t="n">
         <v>25</v>
       </c>
       <c r="F47" s="1" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H47" s="1" t="n">
         <v>2</v>
@@ -6566,7 +6566,7 @@
         <v>16</v>
       </c>
       <c r="M47" s="1" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N47" s="1" t="n">
         <v>14</v>
@@ -6575,68 +6575,68 @@
         <v>26</v>
       </c>
       <c r="P47" s="1" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="Q47" s="1" t="n">
         <v>23</v>
       </c>
       <c r="R47" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="S47" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="T47" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="U47" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="V47" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="W47" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="X47" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y47" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="S47" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="T47" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="U47" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="V47" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="W47" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="X47" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="Y47" s="1" t="n">
-        <v>5</v>
-      </c>
       <c r="Z47" s="1" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AA47" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AB47" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B48" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D48" s="1" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E48" s="1" t="n">
         <v>25</v>
       </c>
       <c r="F48" s="1" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H48" s="1" t="n">
         <v>2</v>
@@ -6645,25 +6645,25 @@
         <v>3</v>
       </c>
       <c r="J48" s="1" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K48" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L48" s="1" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="M48" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N48" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O48" s="1" t="n">
         <v>26</v>
       </c>
       <c r="P48" s="1" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="Q48" s="1" t="n">
         <v>23</v>
@@ -6672,31 +6672,31 @@
         <v>9</v>
       </c>
       <c r="S48" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="T48" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="U48" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="T48" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="U48" s="1" t="n">
-        <v>7</v>
-      </c>
       <c r="V48" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="W48" s="1" t="n">
         <v>4</v>
       </c>
       <c r="X48" s="1" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Y48" s="1" t="n">
         <v>5</v>
       </c>
       <c r="Z48" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA48" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AB48" s="1" t="n">
         <v>10</v>
@@ -6705,23 +6705,23 @@
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B49" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D49" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F49" s="1" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G49" s="1" t="n">
         <v>20</v>
@@ -6733,13 +6733,13 @@
         <v>3</v>
       </c>
       <c r="J49" s="1" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="K49" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L49" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="M49" s="1" t="n">
         <v>18</v>
@@ -6748,10 +6748,10 @@
         <v>15</v>
       </c>
       <c r="O49" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P49" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Q49" s="1" t="n">
         <v>23</v>
@@ -6766,25 +6766,25 @@
         <v>24</v>
       </c>
       <c r="U49" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V49" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="W49" s="1" t="n">
         <v>4</v>
       </c>
       <c r="X49" s="1" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Y49" s="1" t="n">
         <v>5</v>
       </c>
       <c r="Z49" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA49" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AB49" s="1" t="n">
         <v>10</v>
@@ -6793,26 +6793,26 @@
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B50" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C50" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="D50" s="1" t="n">
         <v>16</v>
-      </c>
-      <c r="D50" s="1" t="n">
-        <v>13</v>
       </c>
       <c r="E50" s="1" t="n">
         <v>26</v>
       </c>
       <c r="F50" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="G50" s="1" t="n">
         <v>20</v>
-      </c>
-      <c r="G50" s="1" t="n">
-        <v>22</v>
       </c>
       <c r="H50" s="1" t="n">
         <v>2</v>
@@ -6833,13 +6833,13 @@
         <v>18</v>
       </c>
       <c r="N50" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="O50" s="1" t="n">
         <v>25</v>
       </c>
       <c r="P50" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Q50" s="1" t="n">
         <v>23</v>
@@ -6857,7 +6857,7 @@
         <v>8</v>
       </c>
       <c r="V50" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="W50" s="1" t="n">
         <v>4</v>
@@ -6872,7 +6872,7 @@
         <v>7</v>
       </c>
       <c r="AA50" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AB50" s="1" t="n">
         <v>10</v>
@@ -6881,7 +6881,7 @@
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B51" s="1" t="n">
@@ -6891,16 +6891,16 @@
         <v>16</v>
       </c>
       <c r="D51" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F51" s="1" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H51" s="1" t="n">
         <v>2</v>
@@ -6918,22 +6918,22 @@
         <v>11</v>
       </c>
       <c r="M51" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="N51" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="N51" s="1" t="n">
-        <v>15</v>
-      </c>
       <c r="O51" s="1" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P51" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="Q51" s="1" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="R51" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="S51" s="1" t="n">
         <v>6</v>
@@ -6945,13 +6945,13 @@
         <v>8</v>
       </c>
       <c r="V51" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="W51" s="1" t="n">
         <v>4</v>
       </c>
       <c r="X51" s="1" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="Y51" s="1" t="n">
         <v>5</v>
@@ -6960,71 +6960,71 @@
         <v>7</v>
       </c>
       <c r="AA51" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AB51" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B52" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D52" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F52" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="G52" s="1" t="n">
         <v>20</v>
-      </c>
-      <c r="G52" s="1" t="n">
-        <v>17</v>
       </c>
       <c r="H52" s="1" t="n">
         <v>2</v>
       </c>
       <c r="I52" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J52" s="1" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K52" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L52" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="M52" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N52" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="O52" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="P52" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="O52" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="P52" s="1" t="n">
-        <v>11</v>
-      </c>
       <c r="Q52" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R52" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="S52" s="1" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T52" s="1" t="n">
         <v>24</v>
@@ -7036,132 +7036,132 @@
         <v>13</v>
       </c>
       <c r="W52" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="X52" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y52" s="1" t="n">
         <v>5</v>
-      </c>
-      <c r="X52" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="Y52" s="1" t="n">
-        <v>6</v>
       </c>
       <c r="Z52" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AA52" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AB52" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B53" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D53" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E53" s="1" t="n">
         <v>26</v>
       </c>
       <c r="F53" s="1" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H53" s="1" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I53" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J53" s="1" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="K53" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L53" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M53" s="1" t="n">
         <v>18</v>
       </c>
       <c r="N53" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O53" s="1" t="n">
         <v>25</v>
       </c>
       <c r="P53" s="1" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="Q53" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="R53" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="S53" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T53" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="U53" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V53" s="1" t="n">
         <v>13</v>
       </c>
       <c r="W53" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X53" s="1" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="Y53" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z53" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AA53" s="1" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AB53" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B54" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D54" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E54" s="1" t="n">
         <v>26</v>
       </c>
       <c r="F54" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G54" s="1" t="n">
         <v>20</v>
@@ -7170,7 +7170,7 @@
         <v>6</v>
       </c>
       <c r="I54" s="1" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J54" s="1" t="n">
         <v>19</v>
@@ -7191,10 +7191,10 @@
         <v>25</v>
       </c>
       <c r="P54" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Q54" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R54" s="1" t="n">
         <v>10</v>
@@ -7203,53 +7203,53 @@
         <v>2</v>
       </c>
       <c r="T54" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="U54" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="V54" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="W54" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="X54" s="1" t="n">
         <v>24</v>
-      </c>
-      <c r="U54" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="V54" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="W54" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="X54" s="1" t="n">
-        <v>23</v>
       </c>
       <c r="Y54" s="1" t="n">
         <v>5</v>
       </c>
       <c r="Z54" s="1" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AA54" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AB54" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B55" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D55" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E55" s="1" t="n">
         <v>26</v>
       </c>
       <c r="F55" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G55" s="1" t="n">
         <v>20</v>
@@ -7258,25 +7258,25 @@
         <v>6</v>
       </c>
       <c r="I55" s="1" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J55" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K55" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L55" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M55" s="1" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N55" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O55" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="P55" s="1" t="n">
         <v>17</v>
@@ -7285,31 +7285,31 @@
         <v>22</v>
       </c>
       <c r="R55" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="S55" s="1" t="n">
         <v>2</v>
       </c>
       <c r="T55" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="U55" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="V55" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="W55" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="X55" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="U55" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="V55" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="W55" s="1" t="n">
+      <c r="Y55" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z55" s="1" t="n">
         <v>4</v>
-      </c>
-      <c r="X55" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="Y55" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z55" s="1" t="n">
-        <v>5</v>
       </c>
       <c r="AA55" s="1" t="n">
         <v>21</v>
@@ -7321,32 +7321,32 @@
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B56" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D56" s="1" t="n">
         <v>11</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F56" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G56" s="1" t="n">
         <v>20</v>
       </c>
       <c r="H56" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="I56" s="1" t="n">
         <v>3</v>
-      </c>
-      <c r="I56" s="1" t="n">
-        <v>12</v>
       </c>
       <c r="J56" s="1" t="n">
         <v>18</v>
@@ -7355,13 +7355,13 @@
         <v>1</v>
       </c>
       <c r="L56" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M56" s="1" t="n">
         <v>19</v>
       </c>
       <c r="N56" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O56" s="1" t="n">
         <v>24</v>
@@ -7373,28 +7373,28 @@
         <v>22</v>
       </c>
       <c r="R56" s="1" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="S56" s="1" t="n">
         <v>2</v>
       </c>
       <c r="T56" s="1" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="U56" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V56" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="W56" s="1" t="n">
         <v>4</v>
       </c>
       <c r="X56" s="1" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Y56" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z56" s="1" t="n">
         <v>5</v>
@@ -7403,77 +7403,77 @@
         <v>21</v>
       </c>
       <c r="AB56" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B57" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C57" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="D57" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="D57" s="1" t="n">
-        <v>10</v>
-      </c>
       <c r="E57" s="1" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F57" s="1" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G57" s="1" t="n">
         <v>20</v>
       </c>
       <c r="H57" s="1" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="I57" s="1" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="J57" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K57" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L57" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M57" s="1" t="n">
         <v>19</v>
       </c>
       <c r="N57" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O57" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P57" s="1" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Q57" s="1" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="R57" s="1" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="S57" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T57" s="1" t="n">
         <v>26</v>
       </c>
       <c r="U57" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="V57" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="W57" s="1" t="n">
         <v>4</v>
@@ -7482,7 +7482,7 @@
         <v>23</v>
       </c>
       <c r="Y57" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z57" s="1" t="n">
         <v>5</v>
@@ -7491,62 +7491,62 @@
         <v>21</v>
       </c>
       <c r="AB57" s="1" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B58" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D58" s="1" t="n">
         <v>10</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F58" s="1" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="G58" s="1" t="n">
         <v>20</v>
       </c>
       <c r="H58" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I58" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J58" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K58" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L58" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M58" s="1" t="n">
         <v>19</v>
       </c>
       <c r="N58" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O58" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="P58" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q58" s="1" t="n">
         <v>24</v>
-      </c>
-      <c r="P58" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q58" s="1" t="n">
-        <v>21</v>
       </c>
       <c r="R58" s="1" t="n">
         <v>3</v>
@@ -7555,10 +7555,10 @@
         <v>1</v>
       </c>
       <c r="T58" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="U58" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V58" s="1" t="n">
         <v>12</v>
@@ -7567,7 +7567,7 @@
         <v>4</v>
       </c>
       <c r="X58" s="1" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="Y58" s="1" t="n">
         <v>6</v>
@@ -7576,50 +7576,50 @@
         <v>5</v>
       </c>
       <c r="AA58" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AB58" s="1" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B59" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D59" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F59" s="1" t="n">
         <v>18</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H59" s="1" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="I59" s="1" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="J59" s="1" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="K59" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L59" s="1" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="M59" s="1" t="n">
         <v>19</v>
@@ -7628,37 +7628,37 @@
         <v>17</v>
       </c>
       <c r="O59" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P59" s="1" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="Q59" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R59" s="1" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="S59" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T59" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="U59" s="1" t="n">
         <v>7</v>
       </c>
       <c r="V59" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="W59" s="1" t="n">
         <v>4</v>
       </c>
       <c r="X59" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Y59" s="1" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Z59" s="1" t="n">
         <v>5</v>
@@ -7673,7 +7673,7 @@
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B60" s="1" t="n">
@@ -7683,10 +7683,10 @@
         <v>16</v>
       </c>
       <c r="D60" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F60" s="1" t="n">
         <v>18</v>
@@ -7695,19 +7695,19 @@
         <v>21</v>
       </c>
       <c r="H60" s="1" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="I60" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J60" s="1" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K60" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L60" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M60" s="1" t="n">
         <v>19</v>
@@ -7725,13 +7725,13 @@
         <v>20</v>
       </c>
       <c r="R60" s="1" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="S60" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T60" s="1" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="U60" s="1" t="n">
         <v>7</v>
@@ -7740,101 +7740,101 @@
         <v>15</v>
       </c>
       <c r="W60" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X60" s="1" t="n">
         <v>25</v>
       </c>
       <c r="Y60" s="1" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="Z60" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA60" s="1" t="n">
         <v>22</v>
       </c>
       <c r="AB60" s="1" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B61" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D61" s="1" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E61" s="1" t="n">
         <v>24</v>
       </c>
       <c r="F61" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G61" s="1" t="n">
         <v>21</v>
       </c>
       <c r="H61" s="1" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I61" s="1" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="J61" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K61" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L61" s="1" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="M61" s="1" t="n">
         <v>19</v>
       </c>
       <c r="N61" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O61" s="1" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="P61" s="1" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="Q61" s="1" t="n">
         <v>20</v>
       </c>
       <c r="R61" s="1" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="S61" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T61" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="U61" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V61" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="W61" s="1" t="n">
         <v>3</v>
       </c>
       <c r="X61" s="1" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Y61" s="1" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="Z61" s="1" t="n">
         <v>4</v>
@@ -7849,41 +7849,41 @@
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B62" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D62" s="1" t="n">
         <v>8</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F62" s="1" t="n">
         <v>16</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H62" s="1" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="I62" s="1" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="J62" s="1" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="K62" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L62" s="1" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="M62" s="1" t="n">
         <v>19</v>
@@ -7898,7 +7898,7 @@
         <v>12</v>
       </c>
       <c r="Q62" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="R62" s="1" t="n">
         <v>7</v>
@@ -7907,13 +7907,13 @@
         <v>1</v>
       </c>
       <c r="T62" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="U62" s="1" t="n">
         <v>6</v>
       </c>
       <c r="V62" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="W62" s="1" t="n">
         <v>3</v>
@@ -7922,7 +7922,7 @@
         <v>23</v>
       </c>
       <c r="Y62" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Z62" s="1" t="n">
         <v>4</v>
@@ -7937,68 +7937,68 @@
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B63" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D63" s="1" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E63" s="1" t="n">
         <v>25</v>
       </c>
       <c r="F63" s="1" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H63" s="1" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I63" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J63" s="1" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="K63" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L63" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="M63" s="1" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="N63" s="1" t="n">
         <v>18</v>
       </c>
       <c r="O63" s="1" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="P63" s="1" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="Q63" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R63" s="1" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="S63" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T63" s="1" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="U63" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V63" s="1" t="n">
         <v>14</v>
@@ -8007,250 +8007,250 @@
         <v>3</v>
       </c>
       <c r="X63" s="1" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="Y63" s="1" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Z63" s="1" t="n">
         <v>4</v>
       </c>
       <c r="AA63" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AB63" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B64" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D64" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E64" s="1" t="n">
         <v>25</v>
       </c>
       <c r="F64" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H64" s="1" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I64" s="1" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J64" s="1" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="K64" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L64" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M64" s="1" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="N64" s="1" t="n">
         <v>18</v>
       </c>
       <c r="O64" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P64" s="1" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="Q64" s="1" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="R64" s="1" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="S64" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T64" s="1" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="U64" s="1" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="V64" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="W64" s="1" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="X64" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y64" s="1" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="Z64" s="1" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="AA64" s="1" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AB64" s="1" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B65" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D65" s="1" t="n">
         <v>15</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F65" s="1" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H65" s="1" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="I65" s="1" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="J65" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K65" s="1" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L65" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="M65" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="M65" s="1" t="n">
-        <v>16</v>
-      </c>
       <c r="N65" s="1" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O65" s="1" t="n">
         <v>23</v>
       </c>
       <c r="P65" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q65" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="R65" s="1" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="S65" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T65" s="1" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="U65" s="1" t="n">
         <v>2</v>
       </c>
       <c r="V65" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="W65" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="X65" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y65" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="W65" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="X65" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="Y65" s="1" t="n">
-        <v>8</v>
-      </c>
       <c r="Z65" s="1" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AA65" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AB65" s="1" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B66" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D66" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="E66" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="F66" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="G66" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="H66" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="I66" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="E66" s="1" t="n">
+      <c r="J66" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="K66" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="L66" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="M66" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="N66" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="O66" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="F66" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="G66" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="H66" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="I66" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="J66" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="K66" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="L66" s="1" t="n">
+      <c r="P66" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q66" s="1" t="n">
         <v>18</v>
-      </c>
-      <c r="M66" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="N66" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="O66" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="P66" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q66" s="1" t="n">
-        <v>19</v>
       </c>
       <c r="R66" s="1" t="n">
         <v>10</v>
@@ -8262,77 +8262,77 @@
         <v>26</v>
       </c>
       <c r="U66" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="V66" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="W66" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="X66" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y66" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z66" s="1" t="n">
         <v>7</v>
-      </c>
-      <c r="V66" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="W66" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="X66" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="Y66" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="Z66" s="1" t="n">
-        <v>9</v>
       </c>
       <c r="AA66" s="1" t="n">
         <v>25</v>
       </c>
       <c r="AB66" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B67" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D67" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E67" s="1" t="n">
         <v>23</v>
       </c>
       <c r="F67" s="1" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="G67" s="1" t="n">
         <v>24</v>
       </c>
       <c r="H67" s="1" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="I67" s="1" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J67" s="1" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K67" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L67" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="M67" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="N67" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="M67" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="N67" s="1" t="n">
-        <v>13</v>
-      </c>
       <c r="O67" s="1" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="P67" s="1" t="n">
         <v>8</v>
@@ -8353,25 +8353,25 @@
         <v>7</v>
       </c>
       <c r="V67" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="W67" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X67" s="1" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="Y67" s="1" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Z67" s="1" t="n">
         <v>9</v>
       </c>
       <c r="AA67" s="1" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AB67" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/NSE_Sector_Monitor.xlsx
+++ b/NSE_Sector_Monitor.xlsx
@@ -568,22 +568,22 @@
         <v>1</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>14.72</v>
+        <v>14.83</v>
       </c>
       <c r="H2" s="1" t="n">
-        <v>1.8</v>
+        <v>0.75</v>
       </c>
       <c r="I2" s="1" t="n">
-        <v>-0.9</v>
+        <v>-0.3</v>
       </c>
       <c r="J2" s="1" t="n">
-        <v>4.43</v>
+        <v>4.63</v>
       </c>
       <c r="K2" s="1" t="n">
-        <v>18.66</v>
+        <v>19.13</v>
       </c>
       <c r="L2" s="1" t="inlineStr">
         <is>
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="M2" s="1" t="n">
-        <v>-0.9</v>
+        <v>-0.3</v>
       </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
@@ -624,31 +624,31 @@
         <v>2</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>2</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>27.5</v>
+        <v>27.78</v>
       </c>
       <c r="H3" s="1" t="n">
-        <v>0.51</v>
+        <v>1.02</v>
       </c>
       <c r="I3" s="1" t="n">
-        <v>0.88</v>
+        <v>1.76</v>
       </c>
       <c r="J3" s="1" t="n">
-        <v>4.12</v>
+        <v>5.53</v>
       </c>
       <c r="K3" s="1" t="n">
-        <v>11.06</v>
+        <v>11.27</v>
       </c>
       <c r="L3" s="1" t="inlineStr">
         <is>
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="M3" s="1" t="n">
-        <v>-0.31</v>
+        <v>0</v>
       </c>
       <c r="N3" s="1" t="inlineStr">
         <is>
@@ -689,31 +689,31 @@
         <v>3</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>88.34</v>
+        <v>88.79000000000001</v>
       </c>
       <c r="H4" s="1" t="n">
-        <v>0.42</v>
+        <v>0.51</v>
       </c>
       <c r="I4" s="1" t="n">
-        <v>0.09</v>
+        <v>0.45</v>
       </c>
       <c r="J4" s="1" t="n">
-        <v>0.15</v>
+        <v>0.59</v>
       </c>
       <c r="K4" s="1" t="n">
-        <v>9.869999999999999</v>
+        <v>10.21</v>
       </c>
       <c r="L4" s="1" t="inlineStr">
         <is>
@@ -721,11 +721,11 @@
         </is>
       </c>
       <c r="M4" s="1" t="n">
-        <v>-8.369999999999999</v>
+        <v>-8.039999999999999</v>
       </c>
       <c r="N4" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O4" s="1" t="inlineStr">
@@ -757,28 +757,28 @@
         <v>2</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>17.14</v>
+        <v>17.35</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>2.21</v>
+        <v>1.23</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>1.18</v>
+        <v>2.27</v>
       </c>
       <c r="J5" s="1" t="n">
-        <v>4.22</v>
+        <v>5.67</v>
       </c>
       <c r="K5" s="1" t="n">
-        <v>7.74</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="L5" s="1" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         <v>5</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>-3</v>
@@ -828,22 +828,22 @@
         <v>-2</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>85.27</v>
+        <v>85.65000000000001</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>2.72</v>
+        <v>0.45</v>
       </c>
       <c r="I6" s="1" t="n">
-        <v>0.18</v>
+        <v>0.48</v>
       </c>
       <c r="J6" s="1" t="n">
-        <v>-3.74</v>
+        <v>-3.4</v>
       </c>
       <c r="K6" s="1" t="n">
-        <v>6.74</v>
+        <v>7.23</v>
       </c>
       <c r="L6" s="1" t="inlineStr">
         <is>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="M6" s="1" t="n">
-        <v>-8.43</v>
+        <v>-8.15</v>
       </c>
       <c r="N6" s="1" t="inlineStr">
         <is>
@@ -884,10 +884,10 @@
         <v>6</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>7</v>
@@ -896,19 +896,19 @@
         <v>21</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>31.94</v>
+        <v>32.15</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>-1.11</v>
+        <v>0.66</v>
       </c>
       <c r="I7" s="1" t="n">
-        <v>-0.6</v>
+        <v>-0.1</v>
       </c>
       <c r="J7" s="1" t="n">
-        <v>-3.49</v>
+        <v>-2.36</v>
       </c>
       <c r="K7" s="1" t="n">
-        <v>6.43</v>
+        <v>6.53</v>
       </c>
       <c r="L7" s="1" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         </is>
       </c>
       <c r="M7" s="1" t="n">
-        <v>-24.93</v>
+        <v>-24.55</v>
       </c>
       <c r="N7" s="1" t="inlineStr">
         <is>
@@ -949,31 +949,31 @@
         <v>7</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>-3</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>282.71</v>
+        <v>281.29</v>
       </c>
       <c r="H8" s="1" t="n">
-        <v>1.2</v>
+        <v>-0.5</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>0.06</v>
+        <v>-0.59</v>
       </c>
       <c r="J8" s="1" t="n">
-        <v>-4.19</v>
+        <v>-4.01</v>
       </c>
       <c r="K8" s="1" t="n">
-        <v>4.48</v>
+        <v>3.96</v>
       </c>
       <c r="L8" s="1" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         </is>
       </c>
       <c r="M8" s="1" t="n">
-        <v>-4.53</v>
+        <v>-5.15</v>
       </c>
       <c r="N8" s="1" t="inlineStr">
         <is>
@@ -1014,31 +1014,31 @@
         <v>8</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>31.94</v>
+        <v>31.81</v>
       </c>
       <c r="H9" s="1" t="n">
-        <v>2.34</v>
+        <v>-0.41</v>
       </c>
       <c r="I9" s="1" t="n">
-        <v>0.21</v>
+        <v>-0.35</v>
       </c>
       <c r="J9" s="1" t="n">
-        <v>-2.84</v>
+        <v>-2.03</v>
       </c>
       <c r="K9" s="1" t="n">
-        <v>3.04</v>
+        <v>2.92</v>
       </c>
       <c r="L9" s="1" t="inlineStr">
         <is>
@@ -1046,11 +1046,11 @@
         </is>
       </c>
       <c r="M9" s="1" t="n">
-        <v>-3.59</v>
+        <v>-4.13</v>
       </c>
       <c r="N9" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O9" s="1" t="inlineStr">
@@ -1072,38 +1072,38 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Fin Services</t>
+          <t>Metal</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
         <v>9</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>-2</v>
+        <v>8</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>-3</v>
+        <v>12</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>32.28</v>
+        <v>13.07</v>
       </c>
       <c r="H10" s="1" t="n">
-        <v>2.12</v>
+        <v>-0.08</v>
       </c>
       <c r="I10" s="1" t="n">
         <v>-0.26</v>
       </c>
       <c r="J10" s="1" t="n">
-        <v>-0.45</v>
+        <v>1.62</v>
       </c>
       <c r="K10" s="1" t="n">
-        <v>1.46</v>
+        <v>1.31</v>
       </c>
       <c r="L10" s="1" t="inlineStr">
         <is>
@@ -1111,21 +1111,21 @@
         </is>
       </c>
       <c r="M10" s="1" t="n">
-        <v>-1.23</v>
+        <v>-5.81</v>
       </c>
       <c r="N10" s="1" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O10" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P10" s="1" t="inlineStr">
+        <is>
           <t>Yes</t>
-        </is>
-      </c>
-      <c r="O10" s="1" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="P10" s="1" t="inlineStr">
-        <is>
-          <t>No</t>
         </is>
       </c>
       <c r="Q10" s="1" t="inlineStr">
@@ -1137,7 +1137,7 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>Manufacturing</t>
+          <t>Consumption</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
@@ -1147,40 +1147,40 @@
         <v>3</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>162.62</v>
+        <v>128</v>
       </c>
       <c r="H11" s="1" t="n">
-        <v>0.92</v>
+        <v>-0.25</v>
       </c>
       <c r="I11" s="1" t="n">
-        <v>0.01</v>
+        <v>-0</v>
       </c>
       <c r="J11" s="1" t="n">
-        <v>-0.31</v>
+        <v>-1.72</v>
       </c>
       <c r="K11" s="1" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="L11" s="1" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Down</t>
         </is>
       </c>
       <c r="M11" s="1" t="n">
-        <v>-1.1</v>
+        <v>-5.89</v>
       </c>
       <c r="N11" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O11" s="1" t="inlineStr">
@@ -1195,53 +1195,53 @@
       </c>
       <c r="Q11" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Metal</t>
+          <t>Fin Services</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
         <v>11</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>11</v>
+        <v>-3</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-8</v>
+        <v>3</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>13.08</v>
+        <v>32.25</v>
       </c>
       <c r="H12" s="1" t="n">
-        <v>1.79</v>
+        <v>-0.09</v>
       </c>
       <c r="I12" s="1" t="n">
-        <v>-0.04</v>
+        <v>-0.5</v>
       </c>
       <c r="J12" s="1" t="n">
-        <v>2.71</v>
+        <v>-1.03</v>
       </c>
       <c r="K12" s="1" t="n">
-        <v>1.17</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="L12" s="1" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Down</t>
         </is>
       </c>
       <c r="M12" s="1" t="n">
-        <v>-5.6</v>
+        <v>-1.47</v>
       </c>
       <c r="N12" s="1" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
       </c>
       <c r="P12" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Q12" s="1" t="inlineStr">
@@ -1267,38 +1267,38 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>Tourism</t>
+          <t>Manufacturing</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
         <v>12</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>-5</v>
+        <v>3</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>-5</v>
+        <v>4</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>77.95</v>
+        <v>162.67</v>
       </c>
       <c r="H13" s="1" t="n">
-        <v>3.91</v>
+        <v>0.03</v>
       </c>
       <c r="I13" s="1" t="n">
-        <v>1.55</v>
+        <v>-0.11</v>
       </c>
       <c r="J13" s="1" t="n">
-        <v>0.82</v>
+        <v>-0.25</v>
       </c>
       <c r="K13" s="1" t="n">
-        <v>0.88</v>
+        <v>0.91</v>
       </c>
       <c r="L13" s="1" t="inlineStr">
         <is>
@@ -1306,7 +1306,7 @@
         </is>
       </c>
       <c r="M13" s="1" t="n">
-        <v>-13.67</v>
+        <v>-1.21</v>
       </c>
       <c r="N13" s="1" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
       </c>
       <c r="O13" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P13" s="1" t="inlineStr">
@@ -1332,7 +1332,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Consumption</t>
+          <t>Tourism</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
@@ -1342,36 +1342,36 @@
         <v>-1</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>2</v>
+        <v>-6</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>-2</v>
+        <v>-6</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>1</v>
+        <v>-6</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>128.32</v>
+        <v>78.43000000000001</v>
       </c>
       <c r="H14" s="1" t="n">
-        <v>1.05</v>
+        <v>0.62</v>
       </c>
       <c r="I14" s="1" t="n">
-        <v>0.4</v>
+        <v>2.02</v>
       </c>
       <c r="J14" s="1" t="n">
-        <v>-1.82</v>
+        <v>1.74</v>
       </c>
       <c r="K14" s="1" t="n">
-        <v>0.87</v>
+        <v>0.73</v>
       </c>
       <c r="L14" s="1" t="inlineStr">
         <is>
-          <t>Down</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="M14" s="1" t="n">
-        <v>-5.51</v>
+        <v>-13.14</v>
       </c>
       <c r="N14" s="1" t="inlineStr">
         <is>
@@ -1380,17 +1380,17 @@
       </c>
       <c r="O14" s="1" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P14" s="1" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P14" s="1" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="Q14" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1404,31 +1404,31 @@
         <v>14</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F15" s="2" t="n">
         <v>11</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>30.35</v>
+        <v>30.25</v>
       </c>
       <c r="H15" s="1" t="n">
-        <v>0.8</v>
+        <v>-0.33</v>
       </c>
       <c r="I15" s="1" t="n">
-        <v>0.18</v>
+        <v>-0.3</v>
       </c>
       <c r="J15" s="1" t="n">
-        <v>0.5600000000000001</v>
+        <v>-0.2</v>
       </c>
       <c r="K15" s="1" t="n">
-        <v>0.27</v>
+        <v>-0.11</v>
       </c>
       <c r="L15" s="1" t="inlineStr">
         <is>
@@ -1440,7 +1440,7 @@
       </c>
       <c r="N15" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O15" s="1" t="inlineStr">
@@ -1462,50 +1462,50 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Private Bank</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
         <v>15</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-8</v>
+        <v>0</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>29.3</v>
+        <v>27.94</v>
       </c>
       <c r="H16" s="1" t="n">
-        <v>1.14</v>
+        <v>0.4</v>
       </c>
       <c r="I16" s="1" t="n">
-        <v>-1.8</v>
+        <v>-0.03</v>
       </c>
       <c r="J16" s="1" t="n">
-        <v>-0.32</v>
+        <v>2.25</v>
       </c>
       <c r="K16" s="1" t="n">
-        <v>-0.3</v>
+        <v>-0.41</v>
       </c>
       <c r="L16" s="1" t="inlineStr">
         <is>
-          <t>Down</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="M16" s="1" t="n">
-        <v>0</v>
+        <v>-3.65</v>
       </c>
       <c r="N16" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O16" s="1" t="inlineStr">
@@ -1527,38 +1527,38 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas</t>
+          <t>Bank</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
         <v>16</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D17" s="2" t="n">
+        <v>-4</v>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>-4</v>
+      </c>
+      <c r="F17" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="E17" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="F17" s="2" t="n">
-        <v>10</v>
-      </c>
       <c r="G17" s="1" t="n">
-        <v>11.14</v>
+        <v>585.55</v>
       </c>
       <c r="H17" s="1" t="n">
-        <v>0.72</v>
+        <v>0.34</v>
       </c>
       <c r="I17" s="1" t="n">
-        <v>-0.16</v>
+        <v>-0.17</v>
       </c>
       <c r="J17" s="1" t="n">
-        <v>0.86</v>
+        <v>0.77</v>
       </c>
       <c r="K17" s="1" t="n">
-        <v>-0.55</v>
+        <v>-0.58</v>
       </c>
       <c r="L17" s="1" t="inlineStr">
         <is>
@@ -1566,11 +1566,11 @@
         </is>
       </c>
       <c r="M17" s="1" t="n">
-        <v>-9.039999999999999</v>
+        <v>-5.39</v>
       </c>
       <c r="N17" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O17" s="1" t="inlineStr">
@@ -1592,46 +1592,46 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>Defence</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
         <v>17</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>-12</v>
+        <v>-7</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>-12</v>
+        <v>-4</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>-7</v>
+        <v>3</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-16</v>
+        <v>-15</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>103.28</v>
+        <v>29.31</v>
       </c>
       <c r="H18" s="1" t="n">
-        <v>2.75</v>
+        <v>0.03</v>
       </c>
       <c r="I18" s="1" t="n">
-        <v>-3.12</v>
+        <v>-1.91</v>
       </c>
       <c r="J18" s="1" t="n">
-        <v>-1.03</v>
+        <v>0.91</v>
       </c>
       <c r="K18" s="1" t="n">
-        <v>-0.61</v>
+        <v>-0.64</v>
       </c>
       <c r="L18" s="1" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Down</t>
         </is>
       </c>
       <c r="M18" s="1" t="n">
-        <v>-4.78</v>
+        <v>0</v>
       </c>
       <c r="N18" s="1" t="inlineStr">
         <is>
@@ -1650,53 +1650,53 @@
       </c>
       <c r="Q18" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>MNC</t>
+          <t>Oil &amp; Gas</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
         <v>18</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>-2</v>
+        <v>5</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>-8</v>
+        <v>8</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>32.69</v>
+        <v>11.16</v>
       </c>
       <c r="H19" s="1" t="n">
-        <v>1.87</v>
+        <v>0.18</v>
       </c>
       <c r="I19" s="1" t="n">
-        <v>0.05</v>
+        <v>-0.12</v>
       </c>
       <c r="J19" s="1" t="n">
-        <v>-2.09</v>
+        <v>1.41</v>
       </c>
       <c r="K19" s="1" t="n">
         <v>-0.79</v>
       </c>
       <c r="L19" s="1" t="inlineStr">
         <is>
-          <t>Down</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="M19" s="1" t="n">
-        <v>-3.97</v>
+        <v>-9.01</v>
       </c>
       <c r="N19" s="1" t="inlineStr">
         <is>
@@ -1715,53 +1715,53 @@
       </c>
       <c r="Q19" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>Private Bank</t>
+          <t>MNC</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
         <v>19</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>-6</v>
+        <v>-9</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>27.83</v>
+        <v>32.66</v>
       </c>
       <c r="H20" s="1" t="n">
-        <v>0.11</v>
+        <v>-0.09</v>
       </c>
       <c r="I20" s="1" t="n">
-        <v>-0.28</v>
+        <v>-0.19</v>
       </c>
       <c r="J20" s="1" t="n">
-        <v>2.39</v>
+        <v>-1.45</v>
       </c>
       <c r="K20" s="1" t="n">
-        <v>-0.95</v>
+        <v>-1.56</v>
       </c>
       <c r="L20" s="1" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Down</t>
         </is>
       </c>
       <c r="M20" s="1" t="n">
-        <v>-3.89</v>
+        <v>-4.2</v>
       </c>
       <c r="N20" s="1" t="inlineStr">
         <is>
@@ -1780,45 +1780,45 @@
       </c>
       <c r="Q20" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>Bank</t>
+          <t>Defence</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
         <v>20</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>-1</v>
+        <v>-15</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>-10</v>
+        <v>-15</v>
       </c>
       <c r="E21" s="2" t="n">
         <v>-12</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>0</v>
+        <v>-19</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>583.58</v>
+        <v>103.26</v>
       </c>
       <c r="H21" s="1" t="n">
-        <v>0.15</v>
+        <v>-0.02</v>
       </c>
       <c r="I21" s="1" t="n">
-        <v>-0.36</v>
+        <v>-3.28</v>
       </c>
       <c r="J21" s="1" t="n">
-        <v>0.79</v>
+        <v>-1.74</v>
       </c>
       <c r="K21" s="1" t="n">
-        <v>-1</v>
+        <v>-1.79</v>
       </c>
       <c r="L21" s="1" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         </is>
       </c>
       <c r="M21" s="1" t="n">
-        <v>-5.57</v>
+        <v>-4.93</v>
       </c>
       <c r="N21" s="1" t="inlineStr">
         <is>
@@ -1845,57 +1845,57 @@
       </c>
       <c r="Q21" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>Capital Market</t>
+          <t>Commodities</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
         <v>21</v>
       </c>
       <c r="C22" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F22" s="2" t="n">
         <v>-3</v>
       </c>
-      <c r="D22" s="2" t="n">
-        <v>-2</v>
-      </c>
-      <c r="E22" s="2" t="n">
-        <v>-20</v>
-      </c>
-      <c r="F22" s="2" t="n">
-        <v>-17</v>
-      </c>
       <c r="G22" s="1" t="n">
-        <v>53.58</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="H22" s="1" t="n">
-        <v>1.92</v>
+        <v>0.1</v>
       </c>
       <c r="I22" s="1" t="n">
-        <v>-0.65</v>
+        <v>-0.7</v>
       </c>
       <c r="J22" s="1" t="n">
-        <v>1.88</v>
+        <v>0.84</v>
       </c>
       <c r="K22" s="1" t="n">
-        <v>-2.6</v>
+        <v>-3.38</v>
       </c>
       <c r="L22" s="1" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Down</t>
         </is>
       </c>
       <c r="M22" s="1" t="n">
-        <v>0</v>
+        <v>-8.85</v>
       </c>
       <c r="N22" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O22" s="1" t="inlineStr">
@@ -1924,7 +1924,7 @@
         <v>22</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="D23" s="2" t="n">
         <v>3</v>
@@ -1933,22 +1933,22 @@
         <v>5</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>10.05</v>
+        <v>10.06</v>
       </c>
       <c r="H23" s="1" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="I23" s="1" t="n">
-        <v>-0.48</v>
+        <v>-0.53</v>
       </c>
       <c r="J23" s="1" t="n">
-        <v>1.93</v>
+        <v>1.66</v>
       </c>
       <c r="K23" s="1" t="n">
-        <v>-3.29</v>
+        <v>-3.39</v>
       </c>
       <c r="L23" s="1" t="inlineStr">
         <is>
@@ -1956,11 +1956,11 @@
         </is>
       </c>
       <c r="M23" s="1" t="n">
-        <v>-10.41</v>
+        <v>-10.45</v>
       </c>
       <c r="N23" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O23" s="1" t="inlineStr">
@@ -1982,38 +1982,38 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Commodities</t>
+          <t>PSU Bank</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
         <v>23</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D24" s="2" t="n">
+        <v>-3</v>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>-13</v>
+      </c>
+      <c r="F24" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E24" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="F24" s="2" t="n">
-        <v>-4</v>
-      </c>
       <c r="G24" s="1" t="n">
-        <v>97.5</v>
+        <v>92.91</v>
       </c>
       <c r="H24" s="1" t="n">
-        <v>0.36</v>
+        <v>0.28</v>
       </c>
       <c r="I24" s="1" t="n">
-        <v>-0.66</v>
+        <v>-0.37</v>
       </c>
       <c r="J24" s="1" t="n">
-        <v>0.79</v>
+        <v>-0.26</v>
       </c>
       <c r="K24" s="1" t="n">
-        <v>-3.29</v>
+        <v>-3.47</v>
       </c>
       <c r="L24" s="1" t="inlineStr">
         <is>
@@ -2021,7 +2021,7 @@
         </is>
       </c>
       <c r="M24" s="1" t="n">
-        <v>-8.81</v>
+        <v>-13.8</v>
       </c>
       <c r="N24" s="1" t="inlineStr">
         <is>
@@ -2063,22 +2063,22 @@
         <v>-3</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>92.95999999999999</v>
+        <v>93.01000000000001</v>
       </c>
       <c r="H25" s="1" t="n">
-        <v>0.72</v>
+        <v>0.05</v>
       </c>
       <c r="I25" s="1" t="n">
-        <v>-1.18</v>
+        <v>-1.28</v>
       </c>
       <c r="J25" s="1" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.41</v>
       </c>
       <c r="K25" s="1" t="n">
-        <v>-3.51</v>
+        <v>-3.47</v>
       </c>
       <c r="L25" s="1" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         </is>
       </c>
       <c r="M25" s="1" t="n">
-        <v>-5.03</v>
+        <v>-5.11</v>
       </c>
       <c r="N25" s="1" t="inlineStr">
         <is>
@@ -2112,46 +2112,46 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>PSU Bank</t>
+          <t>Capital Market</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
         <v>25</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D26" s="2" t="n">
         <v>-8</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>-16</v>
+        <v>-24</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>-2</v>
+        <v>-20</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>92.65000000000001</v>
+        <v>53</v>
       </c>
       <c r="H26" s="1" t="n">
-        <v>0.48</v>
+        <v>-1.08</v>
       </c>
       <c r="I26" s="1" t="n">
-        <v>-0.5</v>
+        <v>-1.87</v>
       </c>
       <c r="J26" s="1" t="n">
-        <v>-0.9399999999999999</v>
+        <v>0.15</v>
       </c>
       <c r="K26" s="1" t="n">
-        <v>-3.75</v>
+        <v>-3.84</v>
       </c>
       <c r="L26" s="1" t="inlineStr">
         <is>
-          <t>Down</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="M26" s="1" t="n">
-        <v>-13.91</v>
+        <v>0</v>
       </c>
       <c r="N26" s="1" t="inlineStr">
         <is>
@@ -2177,46 +2177,46 @@
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
         <v>26</v>
       </c>
       <c r="C27" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D27" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="E27" s="2" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>-18</v>
+        <v>-4</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>38</v>
+        <v>49.55</v>
       </c>
       <c r="H27" s="1" t="n">
-        <v>1.47</v>
+        <v>0.55</v>
       </c>
       <c r="I27" s="1" t="n">
-        <v>-0.04</v>
+        <v>1.92</v>
       </c>
       <c r="J27" s="1" t="n">
-        <v>2.06</v>
+        <v>-0.45</v>
       </c>
       <c r="K27" s="1" t="n">
-        <v>-5.28</v>
+        <v>-4.51</v>
       </c>
       <c r="L27" s="1" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Down</t>
         </is>
       </c>
       <c r="M27" s="1" t="n">
-        <v>0</v>
+        <v>-16.13</v>
       </c>
       <c r="N27" s="1" t="inlineStr">
         <is>
@@ -2235,53 +2235,53 @@
       </c>
       <c r="Q27" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C28" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D28" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D28" s="2" t="n">
+      <c r="E28" s="2" t="n">
         <v>-1</v>
       </c>
-      <c r="E28" s="2" t="n">
-        <v>-3</v>
-      </c>
       <c r="F28" s="2" t="n">
-        <v>-3</v>
+        <v>-23</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>49.28</v>
+        <v>38.1</v>
       </c>
       <c r="H28" s="1" t="n">
-        <v>0.33</v>
+        <v>0.26</v>
       </c>
       <c r="I28" s="1" t="n">
-        <v>1.51</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J28" s="1" t="n">
-        <v>-1.61</v>
+        <v>2.17</v>
       </c>
       <c r="K28" s="1" t="n">
-        <v>-5.69</v>
+        <v>-5.24</v>
       </c>
       <c r="L28" s="1" t="inlineStr">
         <is>
-          <t>Down</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="M28" s="1" t="n">
-        <v>-16.46</v>
+        <v>0</v>
       </c>
       <c r="N28" s="1" t="inlineStr">
         <is>
@@ -2290,17 +2290,17 @@
       </c>
       <c r="O28" s="1" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P28" s="1" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P28" s="1" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="Q28" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -2569,26 +2569,26 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B2" s="1" t="n">
         <v>6</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F2" s="1" t="n">
         <v>7</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H2" s="1" t="n">
         <v>2</v>
@@ -2597,46 +2597,46 @@
         <v>4</v>
       </c>
       <c r="J2" s="1" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="K2" s="1" t="n">
         <v>5</v>
       </c>
       <c r="L2" s="1" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="M2" s="1" t="n">
         <v>24</v>
       </c>
       <c r="N2" s="1" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="O2" s="1" t="n">
         <v>22</v>
       </c>
       <c r="P2" s="1" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Q2" s="1" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="R2" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="S2" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="T2" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="S2" s="1" t="n">
+      <c r="U2" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="T2" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="U2" s="1" t="n">
-        <v>15</v>
-      </c>
       <c r="V2" s="1" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="W2" s="1" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="X2" s="1" t="n">
         <v>3</v>
@@ -2645,7 +2645,7 @@
         <v>1</v>
       </c>
       <c r="Z2" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA2" s="1" t="n">
         <v>14</v>
@@ -2657,17 +2657,17 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E3" s="1" t="n">
         <v>25</v>
@@ -2676,7 +2676,7 @@
         <v>7</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H3" s="1" t="n">
         <v>2</v>
@@ -2688,43 +2688,43 @@
         <v>11</v>
       </c>
       <c r="K3" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L3" s="1" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="M3" s="1" t="n">
         <v>24</v>
       </c>
       <c r="N3" s="1" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="O3" s="1" t="n">
         <v>22</v>
       </c>
       <c r="P3" s="1" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Q3" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="R3" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="S3" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="T3" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="U3" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="V3" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="W3" s="1" t="n">
         <v>21</v>
-      </c>
-      <c r="R3" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="S3" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="T3" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="U3" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="V3" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="W3" s="1" t="n">
-        <v>23</v>
       </c>
       <c r="X3" s="1" t="n">
         <v>3</v>
@@ -2733,7 +2733,7 @@
         <v>1</v>
       </c>
       <c r="Z3" s="1" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="AA3" s="1" t="n">
         <v>14</v>
@@ -2745,23 +2745,23 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E4" s="1" t="n">
         <v>24</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G4" s="1" t="n">
         <v>27</v>
@@ -2773,46 +2773,46 @@
         <v>4</v>
       </c>
       <c r="J4" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K4" s="1" t="n">
         <v>5</v>
       </c>
       <c r="L4" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="M4" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="N4" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="M4" s="1" t="n">
+      <c r="O4" s="1" t="n">
         <v>25</v>
-      </c>
-      <c r="N4" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="O4" s="1" t="n">
-        <v>21</v>
       </c>
       <c r="P4" s="1" t="n">
         <v>26</v>
       </c>
       <c r="Q4" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R4" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="S4" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="T4" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="S4" s="1" t="n">
+      <c r="U4" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="T4" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="U4" s="1" t="n">
-        <v>16</v>
-      </c>
       <c r="V4" s="1" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="W4" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="X4" s="1" t="n">
         <v>3</v>
@@ -2821,10 +2821,10 @@
         <v>1</v>
       </c>
       <c r="Z4" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AA4" s="1" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AB4" s="1" t="n">
         <v>8</v>
@@ -2833,23 +2833,23 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G5" s="1" t="n">
         <v>27</v>
@@ -2861,19 +2861,19 @@
         <v>4</v>
       </c>
       <c r="J5" s="1" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="K5" s="1" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L5" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M5" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="N5" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O5" s="1" t="n">
         <v>21</v>
@@ -2882,22 +2882,22 @@
         <v>26</v>
       </c>
       <c r="Q5" s="1" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="R5" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="S5" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="T5" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="S5" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="T5" s="1" t="n">
-        <v>20</v>
-      </c>
       <c r="U5" s="1" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="V5" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="W5" s="1" t="n">
         <v>22</v>
@@ -2909,23 +2909,23 @@
         <v>1</v>
       </c>
       <c r="Z5" s="1" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AA5" s="1" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="AB5" s="1" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C6" s="1" t="n">
         <v>16</v>
@@ -2934,7 +2934,7 @@
         <v>18</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>9</v>
@@ -2946,22 +2946,22 @@
         <v>2</v>
       </c>
       <c r="I6" s="1" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J6" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="K6" s="1" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L6" s="1" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="M6" s="1" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="N6" s="1" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="O6" s="1" t="n">
         <v>21</v>
@@ -2973,22 +2973,22 @@
         <v>25</v>
       </c>
       <c r="R6" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="S6" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="T6" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="S6" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="T6" s="1" t="n">
-        <v>19</v>
-      </c>
       <c r="U6" s="1" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="V6" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="W6" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="X6" s="1" t="n">
         <v>3</v>
@@ -2997,62 +2997,62 @@
         <v>1</v>
       </c>
       <c r="Z6" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AA6" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AB6" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E7" s="1" t="n">
         <v>24</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G7" s="1" t="n">
         <v>27</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I7" s="1" t="n">
         <v>6</v>
       </c>
       <c r="J7" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K7" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="M7" s="1" t="n">
         <v>22</v>
       </c>
       <c r="N7" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O7" s="1" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="P7" s="1" t="n">
         <v>26</v>
@@ -3061,86 +3061,86 @@
         <v>25</v>
       </c>
       <c r="R7" s="1" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="S7" s="1" t="n">
         <v>5</v>
       </c>
       <c r="T7" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="U7" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="V7" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="V7" s="1" t="n">
-        <v>13</v>
-      </c>
       <c r="W7" s="1" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="X7" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y7" s="1" t="n">
         <v>1</v>
       </c>
       <c r="Z7" s="1" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AA7" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AB7" s="1" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D8" s="1" t="n">
         <v>21</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G8" s="1" t="n">
         <v>27</v>
       </c>
       <c r="H8" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J8" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K8" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M8" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N8" s="1" t="n">
         <v>12</v>
       </c>
       <c r="O8" s="1" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="P8" s="1" t="n">
         <v>26</v>
@@ -3149,110 +3149,110 @@
         <v>25</v>
       </c>
       <c r="R8" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="S8" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T8" s="1" t="n">
         <v>20</v>
       </c>
       <c r="U8" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="V8" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="V8" s="1" t="n">
-        <v>11</v>
-      </c>
       <c r="W8" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="X8" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y8" s="1" t="n">
         <v>1</v>
       </c>
       <c r="Z8" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA8" s="1" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AB8" s="1" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="C9" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="C9" s="1" t="n">
-        <v>16</v>
-      </c>
       <c r="D9" s="1" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G9" s="1" t="n">
         <v>27</v>
       </c>
       <c r="H9" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I9" s="1" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J9" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K9" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L9" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M9" s="1" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N9" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="O9" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="P9" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q9" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="R9" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="S9" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="T9" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="U9" s="1" t="n">
         <v>13</v>
-      </c>
-      <c r="O9" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="P9" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="Q9" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="R9" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="S9" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="T9" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="U9" s="1" t="n">
-        <v>14</v>
       </c>
       <c r="V9" s="1" t="n">
         <v>11</v>
       </c>
       <c r="W9" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="X9" s="1" t="n">
         <v>3</v>
@@ -3261,29 +3261,29 @@
         <v>1</v>
       </c>
       <c r="Z9" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA9" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="AB9" s="1" t="n">
         <v>9</v>
-      </c>
-      <c r="AA9" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="AB9" s="1" t="n">
-        <v>10</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="C10" s="1" t="n">
         <v>16</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E10" s="1" t="n">
         <v>23</v>
@@ -3301,46 +3301,46 @@
         <v>7</v>
       </c>
       <c r="J10" s="1" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="K10" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L10" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M10" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N10" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O10" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="P10" s="1" t="n">
         <v>25</v>
-      </c>
-      <c r="P10" s="1" t="n">
-        <v>26</v>
       </c>
       <c r="Q10" s="1" t="n">
         <v>24</v>
       </c>
       <c r="R10" s="1" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="S10" s="1" t="n">
         <v>5</v>
       </c>
       <c r="T10" s="1" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="U10" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="V10" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="W10" s="1" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="X10" s="1" t="n">
         <v>3</v>
@@ -3349,10 +3349,10 @@
         <v>1</v>
       </c>
       <c r="Z10" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA10" s="1" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AB10" s="1" t="n">
         <v>10</v>
@@ -3361,59 +3361,59 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F11" s="1" t="n">
         <v>6</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H11" s="1" t="n">
         <v>4</v>
       </c>
       <c r="I11" s="1" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J11" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K11" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M11" s="1" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N11" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="O11" s="1" t="n">
         <v>25</v>
       </c>
       <c r="P11" s="1" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Q11" s="1" t="n">
         <v>24</v>
       </c>
       <c r="R11" s="1" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="S11" s="1" t="n">
         <v>5</v>
@@ -3425,10 +3425,10 @@
         <v>13</v>
       </c>
       <c r="V11" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="W11" s="1" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="X11" s="1" t="n">
         <v>3</v>
@@ -3437,35 +3437,35 @@
         <v>1</v>
       </c>
       <c r="Z11" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA11" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AB11" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="C12" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="C12" s="1" t="n">
-        <v>10</v>
-      </c>
       <c r="D12" s="1" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G12" s="1" t="n">
         <v>26</v>
@@ -3474,22 +3474,22 @@
         <v>4</v>
       </c>
       <c r="I12" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J12" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K12" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M12" s="1" t="n">
         <v>23</v>
       </c>
       <c r="N12" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O12" s="1" t="n">
         <v>25</v>
@@ -3501,22 +3501,22 @@
         <v>24</v>
       </c>
       <c r="R12" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="S12" s="1" t="n">
         <v>5</v>
       </c>
       <c r="T12" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="U12" s="1" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="V12" s="1" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="W12" s="1" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="X12" s="1" t="n">
         <v>3</v>
@@ -3528,32 +3528,32 @@
         <v>7</v>
       </c>
       <c r="AA12" s="1" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="AB12" s="1" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G13" s="1" t="n">
         <v>26</v>
@@ -3562,49 +3562,49 @@
         <v>4</v>
       </c>
       <c r="I13" s="1" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="J13" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K13" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L13" s="1" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="M13" s="1" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="N13" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O13" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="P13" s="1" t="n">
         <v>27</v>
       </c>
       <c r="Q13" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R13" s="1" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="S13" s="1" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T13" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="U13" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="V13" s="1" t="n">
         <v>18</v>
       </c>
       <c r="W13" s="1" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="X13" s="1" t="n">
         <v>3</v>
@@ -3613,19 +3613,19 @@
         <v>1</v>
       </c>
       <c r="Z13" s="1" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AA13" s="1" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AB13" s="1" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
@@ -3635,7 +3635,7 @@
         <v>11</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E14" s="1" t="n">
         <v>16</v>
@@ -3644,7 +3644,7 @@
         <v>6</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H14" s="1" t="n">
         <v>4</v>
@@ -3659,40 +3659,40 @@
         <v>2</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="M14" s="1" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="N14" s="1" t="n">
         <v>14</v>
       </c>
       <c r="O14" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P14" s="1" t="n">
         <v>27</v>
       </c>
       <c r="Q14" s="1" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="R14" s="1" t="n">
         <v>19</v>
       </c>
       <c r="S14" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T14" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="U14" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="V14" s="1" t="n">
         <v>18</v>
       </c>
       <c r="W14" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="X14" s="1" t="n">
         <v>3</v>
@@ -3701,10 +3701,10 @@
         <v>1</v>
       </c>
       <c r="Z14" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA14" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AB14" s="1" t="n">
         <v>7</v>
@@ -3713,29 +3713,29 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F15" s="1" t="n">
         <v>6</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H15" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I15" s="1" t="n">
         <v>5</v>
@@ -3747,16 +3747,16 @@
         <v>2</v>
       </c>
       <c r="L15" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M15" s="1" t="n">
         <v>22</v>
       </c>
       <c r="N15" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="O15" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="P15" s="1" t="n">
         <v>27</v>
@@ -3765,34 +3765,34 @@
         <v>26</v>
       </c>
       <c r="R15" s="1" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="S15" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T15" s="1" t="n">
         <v>21</v>
       </c>
       <c r="U15" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="V15" s="1" t="n">
         <v>18</v>
-      </c>
-      <c r="V15" s="1" t="n">
-        <v>15</v>
       </c>
       <c r="W15" s="1" t="n">
         <v>20</v>
       </c>
       <c r="X15" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y15" s="1" t="n">
         <v>1</v>
       </c>
       <c r="Z15" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA15" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AB15" s="1" t="n">
         <v>7</v>
@@ -3801,7 +3801,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
@@ -3811,22 +3811,22 @@
         <v>10</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F16" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="G16" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="H16" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="G16" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="H16" s="1" t="n">
+      <c r="I16" s="1" t="n">
         <v>5</v>
-      </c>
-      <c r="I16" s="1" t="n">
-        <v>6</v>
       </c>
       <c r="J16" s="1" t="n">
         <v>23</v>
@@ -3835,37 +3835,37 @@
         <v>2</v>
       </c>
       <c r="L16" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M16" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="N16" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="O16" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="P16" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q16" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="R16" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="S16" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="T16" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="N16" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="O16" s="1" t="n">
-        <v>27</v>
-      </c>
-      <c r="P16" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="Q16" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="R16" s="1" t="n">
+      <c r="U16" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="S16" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="T16" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="U16" s="1" t="n">
+      <c r="V16" s="1" t="n">
         <v>15</v>
-      </c>
-      <c r="V16" s="1" t="n">
-        <v>17</v>
       </c>
       <c r="W16" s="1" t="n">
         <v>20</v>
@@ -3877,7 +3877,7 @@
         <v>1</v>
       </c>
       <c r="Z16" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA16" s="1" t="n">
         <v>16</v>
@@ -3889,77 +3889,77 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D17" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="E17" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="E17" s="1" t="n">
-        <v>14</v>
-      </c>
       <c r="F17" s="1" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G17" s="1" t="n">
         <v>24</v>
       </c>
       <c r="H17" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I17" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J17" s="1" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="K17" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L17" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="M17" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="N17" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="O17" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="P17" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q17" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="R17" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="S17" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="T17" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="U17" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="V17" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="M17" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="N17" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="O17" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="P17" s="1" t="n">
-        <v>27</v>
-      </c>
-      <c r="Q17" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="R17" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="S17" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="T17" s="1" t="n">
-        <v>23</v>
-      </c>
-      <c r="U17" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="V17" s="1" t="n">
-        <v>16</v>
-      </c>
       <c r="W17" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="X17" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y17" s="1" t="n">
         <v>1</v>
@@ -3968,26 +3968,26 @@
         <v>8</v>
       </c>
       <c r="AA17" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AB17" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="C18" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="C18" s="1" t="n">
-        <v>10</v>
-      </c>
       <c r="D18" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E18" s="1" t="n">
         <v>14</v>
@@ -4005,34 +4005,34 @@
         <v>7</v>
       </c>
       <c r="J18" s="1" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K18" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L18" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M18" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N18" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="O18" s="1" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P18" s="1" t="n">
         <v>27</v>
       </c>
       <c r="Q18" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="R18" s="1" t="n">
         <v>19</v>
       </c>
       <c r="S18" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T18" s="1" t="n">
         <v>23</v>
@@ -4044,7 +4044,7 @@
         <v>16</v>
       </c>
       <c r="W18" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="X18" s="1" t="n">
         <v>3</v>
@@ -4053,47 +4053,47 @@
         <v>1</v>
       </c>
       <c r="Z18" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA18" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="AB18" s="1" t="n">
         <v>6</v>
-      </c>
-      <c r="AA18" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="AB18" s="1" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
         <v>11</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D19" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="E19" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="E19" s="1" t="n">
-        <v>12</v>
-      </c>
       <c r="F19" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G19" s="1" t="n">
         <v>24</v>
       </c>
       <c r="H19" s="1" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I19" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J19" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K19" s="1" t="n">
         <v>2</v>
@@ -4102,7 +4102,7 @@
         <v>15</v>
       </c>
       <c r="M19" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N19" s="1" t="n">
         <v>13</v>
@@ -4120,7 +4120,7 @@
         <v>19</v>
       </c>
       <c r="S19" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T19" s="1" t="n">
         <v>23</v>
@@ -4129,7 +4129,7 @@
         <v>18</v>
       </c>
       <c r="V19" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="W19" s="1" t="n">
         <v>20</v>
@@ -4141,32 +4141,32 @@
         <v>1</v>
       </c>
       <c r="Z19" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA19" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AB19" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C20" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="E20" s="1" t="n">
         <v>12</v>
-      </c>
-      <c r="D20" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="E20" s="1" t="n">
-        <v>13</v>
       </c>
       <c r="F20" s="1" t="n">
         <v>4</v>
@@ -4175,10 +4175,10 @@
         <v>24</v>
       </c>
       <c r="H20" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I20" s="1" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J20" s="1" t="n">
         <v>21</v>
@@ -4187,40 +4187,40 @@
         <v>2</v>
       </c>
       <c r="L20" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="M20" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="N20" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="O20" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="P20" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q20" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="R20" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="S20" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="U20" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="M20" s="1" t="n">
+      <c r="V20" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="W20" s="1" t="n">
         <v>20</v>
-      </c>
-      <c r="N20" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="O20" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="P20" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="Q20" s="1" t="n">
-        <v>27</v>
-      </c>
-      <c r="R20" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="S20" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="T20" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="U20" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="V20" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="W20" s="1" t="n">
-        <v>23</v>
       </c>
       <c r="X20" s="1" t="n">
         <v>3</v>
@@ -4229,38 +4229,38 @@
         <v>1</v>
       </c>
       <c r="Z20" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA20" s="1" t="n">
         <v>16</v>
       </c>
       <c r="AB20" s="1" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C21" s="1" t="n">
         <v>12</v>
       </c>
       <c r="D21" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F21" s="1" t="n">
         <v>4</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H21" s="1" t="n">
         <v>7</v>
@@ -4269,7 +4269,7 @@
         <v>11</v>
       </c>
       <c r="J21" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K21" s="1" t="n">
         <v>2</v>
@@ -4278,25 +4278,25 @@
         <v>18</v>
       </c>
       <c r="M21" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="N21" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="O21" s="1" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="P21" s="1" t="n">
         <v>26</v>
       </c>
       <c r="Q21" s="1" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="R21" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="S21" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T21" s="1" t="n">
         <v>22</v>
@@ -4305,7 +4305,7 @@
         <v>19</v>
       </c>
       <c r="V21" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="W21" s="1" t="n">
         <v>23</v>
@@ -4320,7 +4320,7 @@
         <v>6</v>
       </c>
       <c r="AA21" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AB21" s="1" t="n">
         <v>5</v>
@@ -4329,47 +4329,47 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C22" s="1" t="n">
         <v>12</v>
       </c>
       <c r="D22" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="E22" s="1" t="n">
         <v>15</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>10</v>
       </c>
       <c r="F22" s="1" t="n">
         <v>4</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H22" s="1" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I22" s="1" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J22" s="1" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K22" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L22" s="1" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M22" s="1" t="n">
         <v>21</v>
       </c>
       <c r="N22" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O22" s="1" t="n">
         <v>27</v>
@@ -4378,59 +4378,59 @@
         <v>26</v>
       </c>
       <c r="Q22" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R22" s="1" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="S22" s="1" t="n">
         <v>8</v>
       </c>
       <c r="T22" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="U22" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="V22" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="W22" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="U22" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="V22" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="W22" s="1" t="n">
+      <c r="X22" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y22" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="X22" s="1" t="n">
+      <c r="Z22" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA22" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="AB22" s="1" t="n">
         <v>5</v>
-      </c>
-      <c r="Y22" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z22" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA22" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="AB22" s="1" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
         <v>13</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D23" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F23" s="1" t="n">
         <v>4</v>
@@ -4439,13 +4439,13 @@
         <v>24</v>
       </c>
       <c r="H23" s="1" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I23" s="1" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="J23" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K23" s="1" t="n">
         <v>3</v>
@@ -4469,25 +4469,25 @@
         <v>25</v>
       </c>
       <c r="R23" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="S23" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="T23" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="U23" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="V23" s="1" t="n">
         <v>16</v>
-      </c>
-      <c r="S23" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="T23" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="U23" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="V23" s="1" t="n">
-        <v>15</v>
       </c>
       <c r="W23" s="1" t="n">
         <v>1</v>
       </c>
       <c r="X23" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y23" s="1" t="n">
         <v>2</v>
@@ -4496,26 +4496,26 @@
         <v>7</v>
       </c>
       <c r="AA23" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AB23" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D24" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E24" s="1" t="n">
         <v>9</v>
@@ -4524,22 +4524,22 @@
         <v>4</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H24" s="1" t="n">
         <v>12</v>
       </c>
       <c r="I24" s="1" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J24" s="1" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K24" s="1" t="n">
         <v>3</v>
       </c>
       <c r="L24" s="1" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="M24" s="1" t="n">
         <v>21</v>
@@ -4551,25 +4551,25 @@
         <v>27</v>
       </c>
       <c r="P24" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q24" s="1" t="n">
         <v>25</v>
-      </c>
-      <c r="Q24" s="1" t="n">
-        <v>24</v>
       </c>
       <c r="R24" s="1" t="n">
         <v>16</v>
       </c>
       <c r="S24" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T24" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="U24" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="V24" s="1" t="n">
         <v>15</v>
-      </c>
-      <c r="V24" s="1" t="n">
-        <v>14</v>
       </c>
       <c r="W24" s="1" t="n">
         <v>1</v>
@@ -4593,38 +4593,38 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C25" s="1" t="n">
         <v>10</v>
       </c>
       <c r="D25" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E25" s="1" t="n">
         <v>9</v>
       </c>
       <c r="F25" s="1" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H25" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I25" s="1" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J25" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K25" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L25" s="1" t="n">
         <v>20</v>
@@ -4636,37 +4636,37 @@
         <v>11</v>
       </c>
       <c r="O25" s="1" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P25" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q25" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="Q25" s="1" t="n">
-        <v>25</v>
-      </c>
       <c r="R25" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="S25" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="T25" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="U25" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="V25" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="S25" s="1" t="n">
+      <c r="W25" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="X25" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="T25" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="U25" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="V25" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="W25" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="X25" s="1" t="n">
-        <v>8</v>
-      </c>
       <c r="Y25" s="1" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Z25" s="1" t="n">
         <v>7</v>
@@ -4681,20 +4681,20 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="C26" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="C26" s="1" t="n">
-        <v>11</v>
-      </c>
       <c r="D26" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F26" s="1" t="n">
         <v>2</v>
@@ -4703,10 +4703,10 @@
         <v>27</v>
       </c>
       <c r="H26" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I26" s="1" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J26" s="1" t="n">
         <v>23</v>
@@ -4721,7 +4721,7 @@
         <v>21</v>
       </c>
       <c r="N26" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="O26" s="1" t="n">
         <v>26</v>
@@ -4733,10 +4733,10 @@
         <v>25</v>
       </c>
       <c r="R26" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S26" s="1" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T26" s="1" t="n">
         <v>22</v>
@@ -4745,13 +4745,13 @@
         <v>16</v>
       </c>
       <c r="V26" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="W26" s="1" t="n">
         <v>3</v>
       </c>
       <c r="X26" s="1" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y26" s="1" t="n">
         <v>4</v>
@@ -4769,38 +4769,38 @@
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D27" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="E27" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="F27" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G27" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="H27" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="I27" s="1" t="n">
         <v>19</v>
-      </c>
-      <c r="E27" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="F27" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="G27" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="H27" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="I27" s="1" t="n">
-        <v>18</v>
       </c>
       <c r="J27" s="1" t="n">
         <v>23</v>
       </c>
       <c r="K27" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L27" s="1" t="n">
         <v>20</v>
@@ -4809,10 +4809,10 @@
         <v>21</v>
       </c>
       <c r="N27" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="O27" s="1" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P27" s="1" t="n">
         <v>24</v>
@@ -4821,7 +4821,7 @@
         <v>25</v>
       </c>
       <c r="R27" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="S27" s="1" t="n">
         <v>9</v>
@@ -4830,25 +4830,25 @@
         <v>22</v>
       </c>
       <c r="U27" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="V27" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="W27" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X27" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y27" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="Y27" s="1" t="n">
-        <v>2</v>
-      </c>
       <c r="Z27" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA27" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AB27" s="1" t="n">
         <v>5</v>
@@ -4857,41 +4857,41 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C28" s="1" t="n">
         <v>12</v>
       </c>
       <c r="D28" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F28" s="1" t="n">
         <v>7</v>
       </c>
       <c r="G28" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="H28" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="I28" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="J28" s="1" t="n">
         <v>23</v>
-      </c>
-      <c r="H28" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="I28" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="J28" s="1" t="n">
-        <v>24</v>
       </c>
       <c r="K28" s="1" t="n">
         <v>3</v>
       </c>
       <c r="L28" s="1" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M28" s="1" t="n">
         <v>21</v>
@@ -4903,25 +4903,25 @@
         <v>27</v>
       </c>
       <c r="P28" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q28" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="Q28" s="1" t="n">
-        <v>26</v>
-      </c>
       <c r="R28" s="1" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="S28" s="1" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="T28" s="1" t="n">
         <v>22</v>
       </c>
       <c r="U28" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="V28" s="1" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="W28" s="1" t="n">
         <v>1</v>
@@ -4936,50 +4936,50 @@
         <v>8</v>
       </c>
       <c r="AA28" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AB28" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="C29" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D29" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="E29" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="F29" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C29" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="D29" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="E29" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="F29" s="1" t="n">
-        <v>5</v>
-      </c>
       <c r="G29" s="1" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="H29" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I29" s="1" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J29" s="1" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K29" s="1" t="n">
         <v>3</v>
       </c>
       <c r="L29" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M29" s="1" t="n">
         <v>21</v>
@@ -4991,25 +4991,25 @@
         <v>27</v>
       </c>
       <c r="P29" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Q29" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="R29" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="S29" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="S29" s="1" t="n">
-        <v>19</v>
-      </c>
       <c r="T29" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="U29" s="1" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="V29" s="1" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="W29" s="1" t="n">
         <v>1</v>
@@ -5021,10 +5021,10 @@
         <v>2</v>
       </c>
       <c r="Z29" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA29" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AB29" s="1" t="n">
         <v>6</v>
@@ -5033,20 +5033,20 @@
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C30" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="D30" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="D30" s="1" t="n">
-        <v>20</v>
-      </c>
       <c r="E30" s="1" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F30" s="1" t="n">
         <v>5</v>
@@ -5055,10 +5055,10 @@
         <v>26</v>
       </c>
       <c r="H30" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I30" s="1" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J30" s="1" t="n">
         <v>22</v>
@@ -5067,34 +5067,34 @@
         <v>3</v>
       </c>
       <c r="L30" s="1" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M30" s="1" t="n">
         <v>21</v>
       </c>
       <c r="N30" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="O30" s="1" t="n">
         <v>27</v>
       </c>
       <c r="P30" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q30" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="Q30" s="1" t="n">
-        <v>24</v>
-      </c>
       <c r="R30" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="S30" s="1" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="T30" s="1" t="n">
         <v>23</v>
       </c>
       <c r="U30" s="1" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="V30" s="1" t="n">
         <v>17</v>
@@ -5109,10 +5109,10 @@
         <v>2</v>
       </c>
       <c r="Z30" s="1" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AA30" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AB30" s="1" t="n">
         <v>6</v>
@@ -5121,44 +5121,44 @@
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D31" s="1" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F31" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G31" s="1" t="n">
         <v>26</v>
       </c>
       <c r="H31" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I31" s="1" t="n">
         <v>10</v>
       </c>
       <c r="J31" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K31" s="1" t="n">
         <v>3</v>
       </c>
       <c r="L31" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M31" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N31" s="1" t="n">
         <v>11</v>
@@ -5173,10 +5173,10 @@
         <v>24</v>
       </c>
       <c r="R31" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="S31" s="1" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="T31" s="1" t="n">
         <v>23</v>
@@ -5185,13 +5185,13 @@
         <v>18</v>
       </c>
       <c r="V31" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="W31" s="1" t="n">
         <v>1</v>
       </c>
       <c r="X31" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y31" s="1" t="n">
         <v>2</v>
@@ -5200,7 +5200,7 @@
         <v>7</v>
       </c>
       <c r="AA31" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AB31" s="1" t="n">
         <v>6</v>
@@ -5209,38 +5209,38 @@
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
         <v>9</v>
       </c>
       <c r="C32" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D32" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="E32" s="1" t="n">
         <v>13</v>
-      </c>
-      <c r="D32" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="E32" s="1" t="n">
-        <v>11</v>
       </c>
       <c r="F32" s="1" t="n">
         <v>4</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H32" s="1" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I32" s="1" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J32" s="1" t="n">
         <v>21</v>
       </c>
       <c r="K32" s="1" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="L32" s="1" t="n">
         <v>20</v>
@@ -5249,28 +5249,28 @@
         <v>22</v>
       </c>
       <c r="N32" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="O32" s="1" t="n">
         <v>27</v>
       </c>
       <c r="P32" s="1" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Q32" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R32" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="S32" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="T32" s="1" t="n">
         <v>23</v>
       </c>
       <c r="U32" s="1" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="V32" s="1" t="n">
         <v>15</v>
@@ -5285,10 +5285,10 @@
         <v>2</v>
       </c>
       <c r="Z32" s="1" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AA32" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AB32" s="1" t="n">
         <v>6</v>
@@ -5297,47 +5297,47 @@
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C33" s="1" t="n">
         <v>13</v>
       </c>
       <c r="D33" s="1" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="F33" s="1" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H33" s="1" t="n">
         <v>3</v>
       </c>
       <c r="I33" s="1" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J33" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="K33" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="L33" s="1" t="n">
         <v>20</v>
-      </c>
-      <c r="K33" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="L33" s="1" t="n">
-        <v>18</v>
       </c>
       <c r="M33" s="1" t="n">
         <v>22</v>
       </c>
       <c r="N33" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O33" s="1" t="n">
         <v>27</v>
@@ -5349,25 +5349,25 @@
         <v>25</v>
       </c>
       <c r="R33" s="1" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="S33" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="T33" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="U33" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="T33" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="U33" s="1" t="n">
-        <v>12</v>
-      </c>
       <c r="V33" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="W33" s="1" t="n">
         <v>1</v>
       </c>
       <c r="X33" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y33" s="1" t="n">
         <v>2</v>
@@ -5385,44 +5385,44 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D34" s="1" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F34" s="1" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G34" s="1" t="n">
         <v>23</v>
       </c>
       <c r="H34" s="1" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I34" s="1" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J34" s="1" t="n">
         <v>20</v>
       </c>
       <c r="K34" s="1" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L34" s="1" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="M34" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N34" s="1" t="n">
         <v>11</v>
@@ -5434,86 +5434,86 @@
         <v>26</v>
       </c>
       <c r="Q34" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="R34" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="S34" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="T34" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="R34" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="S34" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="T34" s="1" t="n">
-        <v>25</v>
-      </c>
       <c r="U34" s="1" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="V34" s="1" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="W34" s="1" t="n">
         <v>1</v>
       </c>
       <c r="X34" s="1" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Y34" s="1" t="n">
         <v>2</v>
       </c>
       <c r="Z34" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA34" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AB34" s="1" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
         <v>10</v>
       </c>
       <c r="C35" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="D35" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="D35" s="1" t="n">
-        <v>11</v>
-      </c>
       <c r="E35" s="1" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F35" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G35" s="1" t="n">
         <v>23</v>
       </c>
       <c r="H35" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="I35" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="J35" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="K35" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="I35" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="J35" s="1" t="n">
+      <c r="L35" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="M35" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="K35" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="L35" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="M35" s="1" t="n">
-        <v>22</v>
-      </c>
       <c r="N35" s="1" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="O35" s="1" t="n">
         <v>27</v>
@@ -5525,7 +5525,7 @@
         <v>24</v>
       </c>
       <c r="R35" s="1" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="S35" s="1" t="n">
         <v>19</v>
@@ -5534,16 +5534,16 @@
         <v>25</v>
       </c>
       <c r="U35" s="1" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="V35" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="W35" s="1" t="n">
         <v>1</v>
       </c>
       <c r="X35" s="1" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Y35" s="1" t="n">
         <v>2</v>
@@ -5552,23 +5552,23 @@
         <v>9</v>
       </c>
       <c r="AA35" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AB35" s="1" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B36" s="1" t="n">
         <v>10</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D36" s="1" t="n">
         <v>11</v>
@@ -5577,7 +5577,7 @@
         <v>20</v>
       </c>
       <c r="F36" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G36" s="1" t="n">
         <v>23</v>
@@ -5589,19 +5589,19 @@
         <v>7</v>
       </c>
       <c r="J36" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K36" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L36" s="1" t="n">
         <v>13</v>
       </c>
       <c r="M36" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N36" s="1" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="O36" s="1" t="n">
         <v>27</v>
@@ -5613,19 +5613,19 @@
         <v>24</v>
       </c>
       <c r="R36" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="S36" s="1" t="n">
         <v>19</v>
-      </c>
-      <c r="S36" s="1" t="n">
-        <v>18</v>
       </c>
       <c r="T36" s="1" t="n">
         <v>25</v>
       </c>
       <c r="U36" s="1" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="V36" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="W36" s="1" t="n">
         <v>1</v>
@@ -5640,7 +5640,7 @@
         <v>9</v>
       </c>
       <c r="AA36" s="1" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AB36" s="1" t="n">
         <v>8</v>
@@ -5649,44 +5649,44 @@
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B37" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="C37" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="C37" s="1" t="n">
-        <v>16</v>
-      </c>
       <c r="D37" s="1" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F37" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G37" s="1" t="n">
         <v>23</v>
       </c>
       <c r="H37" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I37" s="1" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J37" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="K37" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="L37" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="M37" s="1" t="n">
         <v>21</v>
-      </c>
-      <c r="K37" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="L37" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="M37" s="1" t="n">
-        <v>20</v>
       </c>
       <c r="N37" s="1" t="n">
         <v>12</v>
@@ -5710,19 +5710,19 @@
         <v>25</v>
       </c>
       <c r="U37" s="1" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="V37" s="1" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="W37" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="X37" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="X37" s="1" t="n">
-        <v>7</v>
-      </c>
       <c r="Y37" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Z37" s="1" t="n">
         <v>9</v>
@@ -5737,23 +5737,23 @@
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B38" s="1" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C38" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="D38" s="1" t="n">
         <v>14</v>
-      </c>
-      <c r="D38" s="1" t="n">
-        <v>13</v>
       </c>
       <c r="E38" s="1" t="n">
         <v>22</v>
       </c>
       <c r="F38" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G38" s="1" t="n">
         <v>23</v>
@@ -5765,16 +5765,16 @@
         <v>3</v>
       </c>
       <c r="J38" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K38" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L38" s="1" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="M38" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="N38" s="1" t="n">
         <v>12</v>
@@ -5789,47 +5789,47 @@
         <v>24</v>
       </c>
       <c r="R38" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="S38" s="1" t="n">
         <v>18</v>
-      </c>
-      <c r="S38" s="1" t="n">
-        <v>19</v>
       </c>
       <c r="T38" s="1" t="n">
         <v>25</v>
       </c>
       <c r="U38" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="V38" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="W38" s="1" t="n">
         <v>4</v>
       </c>
       <c r="X38" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y38" s="1" t="n">
         <v>5</v>
       </c>
       <c r="Z38" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA38" s="1" t="n">
         <v>17</v>
       </c>
       <c r="AB38" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B39" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C39" s="1" t="n">
         <v>14</v>
@@ -5838,31 +5838,31 @@
         <v>13</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F39" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G39" s="1" t="n">
         <v>23</v>
       </c>
       <c r="H39" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I39" s="1" t="n">
         <v>3</v>
       </c>
       <c r="J39" s="1" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K39" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L39" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M39" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N39" s="1" t="n">
         <v>12</v>
@@ -5877,19 +5877,19 @@
         <v>24</v>
       </c>
       <c r="R39" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="S39" s="1" t="n">
         <v>19</v>
-      </c>
-      <c r="S39" s="1" t="n">
-        <v>18</v>
       </c>
       <c r="T39" s="1" t="n">
         <v>25</v>
       </c>
       <c r="U39" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="V39" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="W39" s="1" t="n">
         <v>4</v>
@@ -5901,10 +5901,10 @@
         <v>5</v>
       </c>
       <c r="Z39" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA39" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AB39" s="1" t="n">
         <v>9</v>
@@ -5913,26 +5913,26 @@
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B40" s="1" t="n">
         <v>11</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D40" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F40" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H40" s="1" t="n">
         <v>2</v>
@@ -5941,13 +5941,13 @@
         <v>3</v>
       </c>
       <c r="J40" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K40" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L40" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M40" s="1" t="n">
         <v>20</v>
@@ -5962,16 +5962,16 @@
         <v>26</v>
       </c>
       <c r="Q40" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="R40" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="S40" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="T40" s="1" t="n">
         <v>25</v>
-      </c>
-      <c r="R40" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="S40" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="T40" s="1" t="n">
-        <v>24</v>
       </c>
       <c r="U40" s="1" t="n">
         <v>10</v>
@@ -5989,35 +5989,35 @@
         <v>5</v>
       </c>
       <c r="Z40" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA40" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="AB40" s="1" t="n">
         <v>9</v>
-      </c>
-      <c r="AA40" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="AB40" s="1" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B41" s="1" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D41" s="1" t="n">
         <v>14</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F41" s="1" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G41" s="1" t="n">
         <v>21</v>
@@ -6035,7 +6035,7 @@
         <v>1</v>
       </c>
       <c r="L41" s="1" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="M41" s="1" t="n">
         <v>20</v>
@@ -6047,56 +6047,56 @@
         <v>27</v>
       </c>
       <c r="P41" s="1" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="Q41" s="1" t="n">
         <v>25</v>
       </c>
       <c r="R41" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="S41" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="T41" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="U41" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="T41" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="U41" s="1" t="n">
+      <c r="V41" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="W41" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="V41" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="W41" s="1" t="n">
+      <c r="X41" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="X41" s="1" t="n">
-        <v>11</v>
-      </c>
       <c r="Y41" s="1" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Z41" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA41" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="AB41" s="1" t="n">
         <v>8</v>
-      </c>
-      <c r="AA41" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="AB41" s="1" t="n">
-        <v>9</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B42" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="C42" s="1" t="n">
         <v>17</v>
-      </c>
-      <c r="C42" s="1" t="n">
-        <v>15</v>
       </c>
       <c r="D42" s="1" t="n">
         <v>14</v>
@@ -6108,7 +6108,7 @@
         <v>5</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="H42" s="1" t="n">
         <v>2</v>
@@ -6117,25 +6117,25 @@
         <v>3</v>
       </c>
       <c r="J42" s="1" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K42" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L42" s="1" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="M42" s="1" t="n">
         <v>20</v>
       </c>
       <c r="N42" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="O42" s="1" t="n">
         <v>27</v>
       </c>
       <c r="P42" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q42" s="1" t="n">
         <v>25</v>
@@ -6144,47 +6144,47 @@
         <v>16</v>
       </c>
       <c r="S42" s="1" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T42" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="U42" s="1" t="n">
         <v>4</v>
       </c>
       <c r="V42" s="1" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="W42" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X42" s="1" t="n">
         <v>11</v>
       </c>
       <c r="Y42" s="1" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Z42" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA42" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="AB42" s="1" t="n">
         <v>9</v>
-      </c>
-      <c r="AA42" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="AB42" s="1" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B43" s="1" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D43" s="1" t="n">
         <v>14</v>
@@ -6205,34 +6205,34 @@
         <v>3</v>
       </c>
       <c r="J43" s="1" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K43" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L43" s="1" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M43" s="1" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="N43" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="O43" s="1" t="n">
         <v>27</v>
       </c>
       <c r="P43" s="1" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q43" s="1" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="R43" s="1" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="S43" s="1" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T43" s="1" t="n">
         <v>21</v>
@@ -6244,13 +6244,13 @@
         <v>12</v>
       </c>
       <c r="W43" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X43" s="1" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="Y43" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z43" s="1" t="n">
         <v>9</v>
@@ -6259,59 +6259,59 @@
         <v>19</v>
       </c>
       <c r="AB43" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B44" s="1" t="n">
         <v>25</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D44" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F44" s="1" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G44" s="1" t="n">
         <v>24</v>
       </c>
       <c r="H44" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I44" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="J44" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="K44" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="I44" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="J44" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="K44" s="1" t="n">
-        <v>3</v>
-      </c>
       <c r="L44" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M44" s="1" t="n">
         <v>18</v>
       </c>
       <c r="N44" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="O44" s="1" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P44" s="1" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="Q44" s="1" t="n">
         <v>23</v>
@@ -6320,56 +6320,56 @@
         <v>13</v>
       </c>
       <c r="S44" s="1" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T44" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="U44" s="1" t="n">
         <v>4</v>
       </c>
       <c r="V44" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="W44" s="1" t="n">
         <v>6</v>
       </c>
       <c r="X44" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Y44" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z44" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA44" s="1" t="n">
         <v>19</v>
       </c>
       <c r="AB44" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B45" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="C45" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="D45" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="E45" s="1" t="n">
         <v>27</v>
       </c>
-      <c r="C45" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="D45" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="E45" s="1" t="n">
-        <v>25</v>
-      </c>
       <c r="F45" s="1" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G45" s="1" t="n">
         <v>24</v>
@@ -6378,61 +6378,61 @@
         <v>1</v>
       </c>
       <c r="I45" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="J45" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="K45" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="J45" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="K45" s="1" t="n">
-        <v>2</v>
-      </c>
       <c r="L45" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M45" s="1" t="n">
         <v>18</v>
       </c>
       <c r="N45" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="O45" s="1" t="n">
         <v>26</v>
       </c>
       <c r="P45" s="1" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q45" s="1" t="n">
         <v>23</v>
       </c>
       <c r="R45" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="S45" s="1" t="n">
         <v>5</v>
       </c>
       <c r="T45" s="1" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="U45" s="1" t="n">
         <v>4</v>
       </c>
       <c r="V45" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="W45" s="1" t="n">
         <v>6</v>
       </c>
       <c r="X45" s="1" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="Y45" s="1" t="n">
         <v>7</v>
       </c>
       <c r="Z45" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA45" s="1" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AB45" s="1" t="n">
         <v>8</v>
@@ -6441,47 +6441,47 @@
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B46" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C46" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="D46" s="1" t="n">
         <v>13</v>
-      </c>
-      <c r="D46" s="1" t="n">
-        <v>6</v>
       </c>
       <c r="E46" s="1" t="n">
         <v>25</v>
       </c>
       <c r="F46" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H46" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I46" s="1" t="n">
         <v>3</v>
       </c>
       <c r="J46" s="1" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="K46" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L46" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M46" s="1" t="n">
         <v>18</v>
       </c>
       <c r="N46" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="O46" s="1" t="n">
         <v>26</v>
@@ -6499,53 +6499,53 @@
         <v>5</v>
       </c>
       <c r="T46" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="U46" s="1" t="n">
         <v>4</v>
       </c>
       <c r="V46" s="1" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="W46" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X46" s="1" t="n">
         <v>17</v>
       </c>
       <c r="Y46" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z46" s="1" t="n">
         <v>9</v>
       </c>
       <c r="AA46" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AB46" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B47" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C47" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="D47" s="1" t="n">
         <v>6</v>
-      </c>
-      <c r="D47" s="1" t="n">
-        <v>5</v>
       </c>
       <c r="E47" s="1" t="n">
         <v>25</v>
       </c>
       <c r="F47" s="1" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="G47" s="1" t="n">
         <v>22</v>
@@ -6569,22 +6569,22 @@
         <v>18</v>
       </c>
       <c r="N47" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="O47" s="1" t="n">
         <v>26</v>
       </c>
       <c r="P47" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Q47" s="1" t="n">
         <v>23</v>
       </c>
       <c r="R47" s="1" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="S47" s="1" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T47" s="1" t="n">
         <v>21</v>
@@ -6593,50 +6593,50 @@
         <v>4</v>
       </c>
       <c r="V47" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="W47" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X47" s="1" t="n">
         <v>17</v>
       </c>
       <c r="Y47" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z47" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="Z47" s="1" t="n">
+      <c r="AA47" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="AB47" s="1" t="n">
         <v>10</v>
-      </c>
-      <c r="AA47" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="AB47" s="1" t="n">
-        <v>11</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B48" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D48" s="1" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E48" s="1" t="n">
         <v>25</v>
       </c>
       <c r="F48" s="1" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H48" s="1" t="n">
         <v>2</v>
@@ -6654,7 +6654,7 @@
         <v>16</v>
       </c>
       <c r="M48" s="1" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N48" s="1" t="n">
         <v>14</v>
@@ -6663,68 +6663,68 @@
         <v>26</v>
       </c>
       <c r="P48" s="1" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="Q48" s="1" t="n">
         <v>23</v>
       </c>
       <c r="R48" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="S48" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="T48" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="U48" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="V48" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="W48" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="X48" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y48" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="S48" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="T48" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="U48" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="V48" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="W48" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="X48" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="Y48" s="1" t="n">
-        <v>5</v>
-      </c>
       <c r="Z48" s="1" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AA48" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AB48" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B49" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D49" s="1" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E49" s="1" t="n">
         <v>25</v>
       </c>
       <c r="F49" s="1" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H49" s="1" t="n">
         <v>2</v>
@@ -6733,25 +6733,25 @@
         <v>3</v>
       </c>
       <c r="J49" s="1" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K49" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L49" s="1" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="M49" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N49" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O49" s="1" t="n">
         <v>26</v>
       </c>
       <c r="P49" s="1" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="Q49" s="1" t="n">
         <v>23</v>
@@ -6760,31 +6760,31 @@
         <v>9</v>
       </c>
       <c r="S49" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="T49" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="U49" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="T49" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="U49" s="1" t="n">
-        <v>7</v>
-      </c>
       <c r="V49" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="W49" s="1" t="n">
         <v>4</v>
       </c>
       <c r="X49" s="1" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Y49" s="1" t="n">
         <v>5</v>
       </c>
       <c r="Z49" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA49" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AB49" s="1" t="n">
         <v>10</v>
@@ -6793,23 +6793,23 @@
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B50" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D50" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F50" s="1" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G50" s="1" t="n">
         <v>20</v>
@@ -6821,13 +6821,13 @@
         <v>3</v>
       </c>
       <c r="J50" s="1" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="K50" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L50" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="M50" s="1" t="n">
         <v>18</v>
@@ -6836,10 +6836,10 @@
         <v>15</v>
       </c>
       <c r="O50" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P50" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Q50" s="1" t="n">
         <v>23</v>
@@ -6854,25 +6854,25 @@
         <v>24</v>
       </c>
       <c r="U50" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V50" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="W50" s="1" t="n">
         <v>4</v>
       </c>
       <c r="X50" s="1" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Y50" s="1" t="n">
         <v>5</v>
       </c>
       <c r="Z50" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA50" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AB50" s="1" t="n">
         <v>10</v>
@@ -6881,26 +6881,26 @@
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B51" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C51" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="D51" s="1" t="n">
         <v>16</v>
-      </c>
-      <c r="D51" s="1" t="n">
-        <v>13</v>
       </c>
       <c r="E51" s="1" t="n">
         <v>26</v>
       </c>
       <c r="F51" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="G51" s="1" t="n">
         <v>20</v>
-      </c>
-      <c r="G51" s="1" t="n">
-        <v>22</v>
       </c>
       <c r="H51" s="1" t="n">
         <v>2</v>
@@ -6921,13 +6921,13 @@
         <v>18</v>
       </c>
       <c r="N51" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="O51" s="1" t="n">
         <v>25</v>
       </c>
       <c r="P51" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Q51" s="1" t="n">
         <v>23</v>
@@ -6945,7 +6945,7 @@
         <v>8</v>
       </c>
       <c r="V51" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="W51" s="1" t="n">
         <v>4</v>
@@ -6960,7 +6960,7 @@
         <v>7</v>
       </c>
       <c r="AA51" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AB51" s="1" t="n">
         <v>10</v>
@@ -6969,7 +6969,7 @@
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B52" s="1" t="n">
@@ -6979,16 +6979,16 @@
         <v>16</v>
       </c>
       <c r="D52" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F52" s="1" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H52" s="1" t="n">
         <v>2</v>
@@ -7006,22 +7006,22 @@
         <v>11</v>
       </c>
       <c r="M52" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="N52" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="N52" s="1" t="n">
-        <v>15</v>
-      </c>
       <c r="O52" s="1" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P52" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="Q52" s="1" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="R52" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="S52" s="1" t="n">
         <v>6</v>
@@ -7033,13 +7033,13 @@
         <v>8</v>
       </c>
       <c r="V52" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="W52" s="1" t="n">
         <v>4</v>
       </c>
       <c r="X52" s="1" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="Y52" s="1" t="n">
         <v>5</v>
@@ -7048,71 +7048,71 @@
         <v>7</v>
       </c>
       <c r="AA52" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AB52" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B53" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D53" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F53" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="G53" s="1" t="n">
         <v>20</v>
-      </c>
-      <c r="G53" s="1" t="n">
-        <v>17</v>
       </c>
       <c r="H53" s="1" t="n">
         <v>2</v>
       </c>
       <c r="I53" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J53" s="1" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K53" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L53" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="M53" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N53" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="O53" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="P53" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="O53" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="P53" s="1" t="n">
-        <v>11</v>
-      </c>
       <c r="Q53" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R53" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="S53" s="1" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T53" s="1" t="n">
         <v>24</v>
@@ -7124,132 +7124,132 @@
         <v>13</v>
       </c>
       <c r="W53" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="X53" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y53" s="1" t="n">
         <v>5</v>
-      </c>
-      <c r="X53" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="Y53" s="1" t="n">
-        <v>6</v>
       </c>
       <c r="Z53" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AA53" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AB53" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B54" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D54" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E54" s="1" t="n">
         <v>26</v>
       </c>
       <c r="F54" s="1" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H54" s="1" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I54" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J54" s="1" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="K54" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L54" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M54" s="1" t="n">
         <v>18</v>
       </c>
       <c r="N54" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O54" s="1" t="n">
         <v>25</v>
       </c>
       <c r="P54" s="1" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="Q54" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="R54" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="S54" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T54" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="U54" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V54" s="1" t="n">
         <v>13</v>
       </c>
       <c r="W54" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X54" s="1" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="Y54" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z54" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AA54" s="1" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AB54" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B55" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D55" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E55" s="1" t="n">
         <v>26</v>
       </c>
       <c r="F55" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G55" s="1" t="n">
         <v>20</v>
@@ -7258,7 +7258,7 @@
         <v>6</v>
       </c>
       <c r="I55" s="1" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J55" s="1" t="n">
         <v>19</v>
@@ -7279,10 +7279,10 @@
         <v>25</v>
       </c>
       <c r="P55" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Q55" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R55" s="1" t="n">
         <v>10</v>
@@ -7291,53 +7291,53 @@
         <v>2</v>
       </c>
       <c r="T55" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="U55" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="V55" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="W55" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="X55" s="1" t="n">
         <v>24</v>
-      </c>
-      <c r="U55" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="V55" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="W55" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="X55" s="1" t="n">
-        <v>23</v>
       </c>
       <c r="Y55" s="1" t="n">
         <v>5</v>
       </c>
       <c r="Z55" s="1" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AA55" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AB55" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B56" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D56" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E56" s="1" t="n">
         <v>26</v>
       </c>
       <c r="F56" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G56" s="1" t="n">
         <v>20</v>
@@ -7346,25 +7346,25 @@
         <v>6</v>
       </c>
       <c r="I56" s="1" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J56" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K56" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L56" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M56" s="1" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N56" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O56" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="P56" s="1" t="n">
         <v>17</v>
@@ -7373,31 +7373,31 @@
         <v>22</v>
       </c>
       <c r="R56" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="S56" s="1" t="n">
         <v>2</v>
       </c>
       <c r="T56" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="U56" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="V56" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="W56" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="X56" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="U56" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="V56" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="W56" s="1" t="n">
+      <c r="Y56" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z56" s="1" t="n">
         <v>4</v>
-      </c>
-      <c r="X56" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="Y56" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z56" s="1" t="n">
-        <v>5</v>
       </c>
       <c r="AA56" s="1" t="n">
         <v>21</v>
@@ -7409,32 +7409,32 @@
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B57" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D57" s="1" t="n">
         <v>11</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F57" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G57" s="1" t="n">
         <v>20</v>
       </c>
       <c r="H57" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="I57" s="1" t="n">
         <v>3</v>
-      </c>
-      <c r="I57" s="1" t="n">
-        <v>12</v>
       </c>
       <c r="J57" s="1" t="n">
         <v>18</v>
@@ -7443,13 +7443,13 @@
         <v>1</v>
       </c>
       <c r="L57" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M57" s="1" t="n">
         <v>19</v>
       </c>
       <c r="N57" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O57" s="1" t="n">
         <v>24</v>
@@ -7461,28 +7461,28 @@
         <v>22</v>
       </c>
       <c r="R57" s="1" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="S57" s="1" t="n">
         <v>2</v>
       </c>
       <c r="T57" s="1" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="U57" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V57" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="W57" s="1" t="n">
         <v>4</v>
       </c>
       <c r="X57" s="1" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Y57" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z57" s="1" t="n">
         <v>5</v>
@@ -7491,77 +7491,77 @@
         <v>21</v>
       </c>
       <c r="AB57" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B58" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C58" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="D58" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="D58" s="1" t="n">
-        <v>10</v>
-      </c>
       <c r="E58" s="1" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F58" s="1" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G58" s="1" t="n">
         <v>20</v>
       </c>
       <c r="H58" s="1" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="I58" s="1" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="J58" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K58" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L58" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M58" s="1" t="n">
         <v>19</v>
       </c>
       <c r="N58" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O58" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P58" s="1" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Q58" s="1" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="R58" s="1" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="S58" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T58" s="1" t="n">
         <v>26</v>
       </c>
       <c r="U58" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="V58" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="W58" s="1" t="n">
         <v>4</v>
@@ -7570,7 +7570,7 @@
         <v>23</v>
       </c>
       <c r="Y58" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z58" s="1" t="n">
         <v>5</v>
@@ -7579,62 +7579,62 @@
         <v>21</v>
       </c>
       <c r="AB58" s="1" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B59" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D59" s="1" t="n">
         <v>10</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F59" s="1" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="G59" s="1" t="n">
         <v>20</v>
       </c>
       <c r="H59" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I59" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J59" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K59" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L59" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M59" s="1" t="n">
         <v>19</v>
       </c>
       <c r="N59" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O59" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="P59" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q59" s="1" t="n">
         <v>24</v>
-      </c>
-      <c r="P59" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q59" s="1" t="n">
-        <v>21</v>
       </c>
       <c r="R59" s="1" t="n">
         <v>3</v>
@@ -7643,10 +7643,10 @@
         <v>1</v>
       </c>
       <c r="T59" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="U59" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V59" s="1" t="n">
         <v>12</v>
@@ -7655,7 +7655,7 @@
         <v>4</v>
       </c>
       <c r="X59" s="1" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="Y59" s="1" t="n">
         <v>6</v>
@@ -7664,50 +7664,50 @@
         <v>5</v>
       </c>
       <c r="AA59" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AB59" s="1" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B60" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D60" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F60" s="1" t="n">
         <v>18</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H60" s="1" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="I60" s="1" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="J60" s="1" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="K60" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L60" s="1" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="M60" s="1" t="n">
         <v>19</v>
@@ -7716,37 +7716,37 @@
         <v>17</v>
       </c>
       <c r="O60" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P60" s="1" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="Q60" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R60" s="1" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="S60" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T60" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="U60" s="1" t="n">
         <v>7</v>
       </c>
       <c r="V60" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="W60" s="1" t="n">
         <v>4</v>
       </c>
       <c r="X60" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Y60" s="1" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Z60" s="1" t="n">
         <v>5</v>
@@ -7761,7 +7761,7 @@
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B61" s="1" t="n">
@@ -7771,10 +7771,10 @@
         <v>16</v>
       </c>
       <c r="D61" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F61" s="1" t="n">
         <v>18</v>
@@ -7783,19 +7783,19 @@
         <v>21</v>
       </c>
       <c r="H61" s="1" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="I61" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J61" s="1" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K61" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L61" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M61" s="1" t="n">
         <v>19</v>
@@ -7813,13 +7813,13 @@
         <v>20</v>
       </c>
       <c r="R61" s="1" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="S61" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T61" s="1" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="U61" s="1" t="n">
         <v>7</v>
@@ -7828,101 +7828,101 @@
         <v>15</v>
       </c>
       <c r="W61" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X61" s="1" t="n">
         <v>25</v>
       </c>
       <c r="Y61" s="1" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="Z61" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA61" s="1" t="n">
         <v>22</v>
       </c>
       <c r="AB61" s="1" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B62" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D62" s="1" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E62" s="1" t="n">
         <v>24</v>
       </c>
       <c r="F62" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G62" s="1" t="n">
         <v>21</v>
       </c>
       <c r="H62" s="1" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I62" s="1" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="J62" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K62" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L62" s="1" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="M62" s="1" t="n">
         <v>19</v>
       </c>
       <c r="N62" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O62" s="1" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="P62" s="1" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="Q62" s="1" t="n">
         <v>20</v>
       </c>
       <c r="R62" s="1" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="S62" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T62" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="U62" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V62" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="W62" s="1" t="n">
         <v>3</v>
       </c>
       <c r="X62" s="1" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Y62" s="1" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="Z62" s="1" t="n">
         <v>4</v>
@@ -7937,41 +7937,41 @@
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B63" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D63" s="1" t="n">
         <v>8</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F63" s="1" t="n">
         <v>16</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H63" s="1" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="I63" s="1" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="J63" s="1" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="K63" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L63" s="1" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="M63" s="1" t="n">
         <v>19</v>
@@ -7986,7 +7986,7 @@
         <v>12</v>
       </c>
       <c r="Q63" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="R63" s="1" t="n">
         <v>7</v>
@@ -7995,13 +7995,13 @@
         <v>1</v>
       </c>
       <c r="T63" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="U63" s="1" t="n">
         <v>6</v>
       </c>
       <c r="V63" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="W63" s="1" t="n">
         <v>3</v>
@@ -8010,7 +8010,7 @@
         <v>23</v>
       </c>
       <c r="Y63" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Z63" s="1" t="n">
         <v>4</v>
@@ -8025,68 +8025,68 @@
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B64" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D64" s="1" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E64" s="1" t="n">
         <v>25</v>
       </c>
       <c r="F64" s="1" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H64" s="1" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I64" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J64" s="1" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="K64" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L64" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="M64" s="1" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="N64" s="1" t="n">
         <v>18</v>
       </c>
       <c r="O64" s="1" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="P64" s="1" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="Q64" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R64" s="1" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="S64" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T64" s="1" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="U64" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V64" s="1" t="n">
         <v>14</v>
@@ -8095,250 +8095,250 @@
         <v>3</v>
       </c>
       <c r="X64" s="1" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="Y64" s="1" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Z64" s="1" t="n">
         <v>4</v>
       </c>
       <c r="AA64" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AB64" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B65" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D65" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E65" s="1" t="n">
         <v>25</v>
       </c>
       <c r="F65" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H65" s="1" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I65" s="1" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J65" s="1" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="K65" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L65" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M65" s="1" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="N65" s="1" t="n">
         <v>18</v>
       </c>
       <c r="O65" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P65" s="1" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="Q65" s="1" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="R65" s="1" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="S65" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T65" s="1" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="U65" s="1" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="V65" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="W65" s="1" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="X65" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y65" s="1" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="Z65" s="1" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="AA65" s="1" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AB65" s="1" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B66" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D66" s="1" t="n">
         <v>15</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F66" s="1" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H66" s="1" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="I66" s="1" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="J66" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K66" s="1" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L66" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="M66" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="M66" s="1" t="n">
-        <v>16</v>
-      </c>
       <c r="N66" s="1" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O66" s="1" t="n">
         <v>23</v>
       </c>
       <c r="P66" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q66" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="R66" s="1" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="S66" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T66" s="1" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="U66" s="1" t="n">
         <v>2</v>
       </c>
       <c r="V66" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="W66" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="X66" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y66" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="W66" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="X66" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="Y66" s="1" t="n">
-        <v>8</v>
-      </c>
       <c r="Z66" s="1" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AA66" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AB66" s="1" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B67" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D67" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="E67" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="F67" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="G67" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="H67" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="I67" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="E67" s="1" t="n">
+      <c r="J67" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="K67" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="L67" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="M67" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="N67" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="O67" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="F67" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="G67" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="H67" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="I67" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="J67" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="K67" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="L67" s="1" t="n">
+      <c r="P67" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q67" s="1" t="n">
         <v>18</v>
-      </c>
-      <c r="M67" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="N67" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="O67" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="P67" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q67" s="1" t="n">
-        <v>19</v>
       </c>
       <c r="R67" s="1" t="n">
         <v>10</v>
@@ -8350,28 +8350,28 @@
         <v>26</v>
       </c>
       <c r="U67" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="V67" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="W67" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="X67" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y67" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z67" s="1" t="n">
         <v>7</v>
-      </c>
-      <c r="V67" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="W67" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="X67" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="Y67" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="Z67" s="1" t="n">
-        <v>9</v>
       </c>
       <c r="AA67" s="1" t="n">
         <v>25</v>
       </c>
       <c r="AB67" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/NSE_Sector_Monitor.xlsx
+++ b/NSE_Sector_Monitor.xlsx
@@ -565,25 +565,25 @@
         <v>0</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>14.83</v>
+        <v>14.97</v>
       </c>
       <c r="H2" s="1" t="n">
-        <v>0.75</v>
+        <v>1.7</v>
       </c>
       <c r="I2" s="1" t="n">
-        <v>-0.3</v>
+        <v>2.16</v>
       </c>
       <c r="J2" s="1" t="n">
-        <v>4.63</v>
+        <v>5.19</v>
       </c>
       <c r="K2" s="1" t="n">
-        <v>19.13</v>
+        <v>21</v>
       </c>
       <c r="L2" s="1" t="inlineStr">
         <is>
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="M2" s="1" t="n">
-        <v>-0.3</v>
+        <v>0</v>
       </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
@@ -617,38 +617,38 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Pharma</t>
+          <t>Digital</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
         <v>2</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>27.78</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="H3" s="1" t="n">
-        <v>1.02</v>
+        <v>0.29</v>
       </c>
       <c r="I3" s="1" t="n">
-        <v>1.76</v>
+        <v>-0.93</v>
       </c>
       <c r="J3" s="1" t="n">
-        <v>5.53</v>
+        <v>0.85</v>
       </c>
       <c r="K3" s="1" t="n">
-        <v>11.27</v>
+        <v>10.71</v>
       </c>
       <c r="L3" s="1" t="inlineStr">
         <is>
@@ -656,21 +656,21 @@
         </is>
       </c>
       <c r="M3" s="1" t="n">
-        <v>0</v>
+        <v>-7.92</v>
       </c>
       <c r="N3" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O3" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P3" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Q3" s="1" t="inlineStr">
@@ -682,38 +682,38 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Digital</t>
+          <t>Pharma</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
         <v>3</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>88.79000000000001</v>
+        <v>27.68</v>
       </c>
       <c r="H4" s="1" t="n">
-        <v>0.51</v>
+        <v>-0.29</v>
       </c>
       <c r="I4" s="1" t="n">
-        <v>0.45</v>
+        <v>1.32</v>
       </c>
       <c r="J4" s="1" t="n">
-        <v>0.59</v>
+        <v>5.47</v>
       </c>
       <c r="K4" s="1" t="n">
-        <v>10.21</v>
+        <v>8.77</v>
       </c>
       <c r="L4" s="1" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
         </is>
       </c>
       <c r="M4" s="1" t="n">
-        <v>-8.039999999999999</v>
+        <v>-0</v>
       </c>
       <c r="N4" s="1" t="inlineStr">
         <is>
@@ -730,12 +730,12 @@
       </c>
       <c r="O4" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P4" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Q4" s="1" t="inlineStr">
@@ -747,46 +747,46 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Realty</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
         <v>4</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>6</v>
+        <v>-2</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>10</v>
+        <v>-2</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>17.35</v>
+        <v>86.08</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>1.23</v>
+        <v>0.95</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>2.27</v>
+        <v>3.05</v>
       </c>
       <c r="J5" s="1" t="n">
-        <v>5.67</v>
+        <v>-3</v>
       </c>
       <c r="K5" s="1" t="n">
-        <v>8.779999999999999</v>
+        <v>7.92</v>
       </c>
       <c r="L5" s="1" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Down</t>
         </is>
       </c>
       <c r="M5" s="1" t="n">
-        <v>0</v>
+        <v>-7.37</v>
       </c>
       <c r="N5" s="1" t="inlineStr">
         <is>
@@ -795,12 +795,12 @@
       </c>
       <c r="O5" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P5" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Q5" s="1" t="inlineStr">
@@ -812,38 +812,38 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Realty</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
         <v>5</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>-3</v>
+        <v>6</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>-2</v>
+        <v>4</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-2</v>
+        <v>22</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>85.65000000000001</v>
+        <v>31.77</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>0.45</v>
+        <v>-0.53</v>
       </c>
       <c r="I6" s="1" t="n">
-        <v>0.48</v>
+        <v>-4.69</v>
       </c>
       <c r="J6" s="1" t="n">
-        <v>-3.4</v>
+        <v>-3.39</v>
       </c>
       <c r="K6" s="1" t="n">
-        <v>7.23</v>
+        <v>6.98</v>
       </c>
       <c r="L6" s="1" t="inlineStr">
         <is>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="M6" s="1" t="n">
-        <v>-8.15</v>
+        <v>-25.18</v>
       </c>
       <c r="N6" s="1" t="inlineStr">
         <is>
@@ -870,72 +870,72 @@
       </c>
       <c r="Q6" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
         <v>6</v>
       </c>
       <c r="C7" s="2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="D7" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D7" s="2" t="n">
-        <v>8</v>
-      </c>
       <c r="E7" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>32.15</v>
+        <v>17.24</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>0.66</v>
+        <v>0.58</v>
       </c>
       <c r="I7" s="1" t="n">
-        <v>-0.1</v>
+        <v>0.95</v>
       </c>
       <c r="J7" s="1" t="n">
-        <v>-2.36</v>
+        <v>5.47</v>
       </c>
       <c r="K7" s="1" t="n">
-        <v>6.53</v>
+        <v>6.45</v>
       </c>
       <c r="L7" s="1" t="inlineStr">
         <is>
-          <t>Down</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="M7" s="1" t="n">
-        <v>-24.55</v>
+        <v>0</v>
       </c>
       <c r="N7" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O7" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P7" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Q7" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -958,22 +958,22 @@
         <v>-3</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>281.29</v>
+        <v>280.12</v>
       </c>
       <c r="H8" s="1" t="n">
-        <v>-0.5</v>
+        <v>-0.92</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>-0.59</v>
+        <v>-0.75</v>
       </c>
       <c r="J8" s="1" t="n">
-        <v>-4.01</v>
+        <v>-3.65</v>
       </c>
       <c r="K8" s="1" t="n">
-        <v>3.96</v>
+        <v>3.61</v>
       </c>
       <c r="L8" s="1" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         </is>
       </c>
       <c r="M8" s="1" t="n">
-        <v>-5.15</v>
+        <v>-5.21</v>
       </c>
       <c r="N8" s="1" t="inlineStr">
         <is>
@@ -1007,46 +1007,46 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>EV &amp; New Age Auto</t>
+          <t>Metal</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
         <v>8</v>
       </c>
       <c r="C9" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="F9" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D9" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>-2</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>-2</v>
-      </c>
       <c r="G9" s="1" t="n">
-        <v>31.81</v>
+        <v>13.05</v>
       </c>
       <c r="H9" s="1" t="n">
-        <v>-0.41</v>
+        <v>-0.23</v>
       </c>
       <c r="I9" s="1" t="n">
-        <v>-0.35</v>
+        <v>0.77</v>
       </c>
       <c r="J9" s="1" t="n">
-        <v>-2.03</v>
+        <v>0.01</v>
       </c>
       <c r="K9" s="1" t="n">
-        <v>2.92</v>
+        <v>3.41</v>
       </c>
       <c r="L9" s="1" t="inlineStr">
         <is>
-          <t>Down</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="M9" s="1" t="n">
-        <v>-4.13</v>
+        <v>-5.62</v>
       </c>
       <c r="N9" s="1" t="inlineStr">
         <is>
@@ -1072,46 +1072,46 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Metal</t>
+          <t>EV &amp; New Age Auto</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
         <v>9</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>8</v>
+        <v>-3</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>13</v>
+        <v>-4</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>13.07</v>
+        <v>31.41</v>
       </c>
       <c r="H10" s="1" t="n">
-        <v>-0.08</v>
+        <v>-1.66</v>
       </c>
       <c r="I10" s="1" t="n">
-        <v>-0.26</v>
+        <v>-1.61</v>
       </c>
       <c r="J10" s="1" t="n">
-        <v>1.62</v>
+        <v>-2.85</v>
       </c>
       <c r="K10" s="1" t="n">
-        <v>1.31</v>
+        <v>2.02</v>
       </c>
       <c r="L10" s="1" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Down</t>
         </is>
       </c>
       <c r="M10" s="1" t="n">
-        <v>-5.81</v>
+        <v>-5</v>
       </c>
       <c r="N10" s="1" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
       </c>
       <c r="P10" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Q10" s="1" t="inlineStr">
@@ -1144,31 +1144,31 @@
         <v>10</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>128</v>
+        <v>128.23</v>
       </c>
       <c r="H11" s="1" t="n">
-        <v>-0.25</v>
+        <v>-0.21</v>
       </c>
       <c r="I11" s="1" t="n">
-        <v>-0</v>
+        <v>0.01</v>
       </c>
       <c r="J11" s="1" t="n">
-        <v>-1.72</v>
+        <v>-0.95</v>
       </c>
       <c r="K11" s="1" t="n">
-        <v>1.17</v>
+        <v>2.01</v>
       </c>
       <c r="L11" s="1" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         </is>
       </c>
       <c r="M11" s="1" t="n">
-        <v>-5.89</v>
+        <v>-5.39</v>
       </c>
       <c r="N11" s="1" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Fin Services</t>
+          <t>Tourism</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
@@ -1215,33 +1215,33 @@
         <v>-3</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>6</v>
+        <v>-5</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>32.25</v>
+        <v>78.52</v>
       </c>
       <c r="H12" s="1" t="n">
-        <v>-0.09</v>
+        <v>0.73</v>
       </c>
       <c r="I12" s="1" t="n">
-        <v>-0.5</v>
+        <v>2.87</v>
       </c>
       <c r="J12" s="1" t="n">
-        <v>-1.03</v>
+        <v>2.09</v>
       </c>
       <c r="K12" s="1" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.82</v>
       </c>
       <c r="L12" s="1" t="inlineStr">
         <is>
-          <t>Down</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="M12" s="1" t="n">
-        <v>-1.47</v>
+        <v>-12.62</v>
       </c>
       <c r="N12" s="1" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
       </c>
       <c r="O12" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P12" s="1" t="inlineStr">
@@ -1274,43 +1274,43 @@
         <v>12</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>162.67</v>
+        <v>161.65</v>
       </c>
       <c r="H13" s="1" t="n">
-        <v>0.03</v>
+        <v>-0.63</v>
       </c>
       <c r="I13" s="1" t="n">
-        <v>-0.11</v>
+        <v>0.27</v>
       </c>
       <c r="J13" s="1" t="n">
-        <v>-0.25</v>
+        <v>-0.71</v>
       </c>
       <c r="K13" s="1" t="n">
-        <v>0.91</v>
+        <v>0.8</v>
       </c>
       <c r="L13" s="1" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Down</t>
         </is>
       </c>
       <c r="M13" s="1" t="n">
-        <v>-1.21</v>
+        <v>-1.49</v>
       </c>
       <c r="N13" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O13" s="1" t="inlineStr">
@@ -1332,55 +1332,55 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Tourism</t>
+          <t>Fin Services</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
         <v>13</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>-6</v>
+        <v>-4</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>-6</v>
+        <v>5</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-6</v>
+        <v>3</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>78.43000000000001</v>
+        <v>32</v>
       </c>
       <c r="H14" s="1" t="n">
-        <v>0.62</v>
+        <v>-0.87</v>
       </c>
       <c r="I14" s="1" t="n">
-        <v>2.02</v>
+        <v>-0.27</v>
       </c>
       <c r="J14" s="1" t="n">
-        <v>1.74</v>
+        <v>-1.09</v>
       </c>
       <c r="K14" s="1" t="n">
-        <v>0.73</v>
+        <v>0.57</v>
       </c>
       <c r="L14" s="1" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Down</t>
         </is>
       </c>
       <c r="M14" s="1" t="n">
-        <v>-13.14</v>
+        <v>-1.89</v>
       </c>
       <c r="N14" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O14" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P14" s="1" t="inlineStr">
@@ -1404,31 +1404,31 @@
         <v>14</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>30.25</v>
+        <v>30.2</v>
       </c>
       <c r="H15" s="1" t="n">
-        <v>-0.33</v>
+        <v>-0.49</v>
       </c>
       <c r="I15" s="1" t="n">
-        <v>-0.3</v>
+        <v>-0.73</v>
       </c>
       <c r="J15" s="1" t="n">
-        <v>-0.2</v>
+        <v>0.16</v>
       </c>
       <c r="K15" s="1" t="n">
-        <v>-0.11</v>
+        <v>0.2</v>
       </c>
       <c r="L15" s="1" t="inlineStr">
         <is>
@@ -1472,28 +1472,28 @@
         <v>3</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>27.94</v>
+        <v>27.88</v>
       </c>
       <c r="H16" s="1" t="n">
-        <v>0.4</v>
+        <v>0.18</v>
       </c>
       <c r="I16" s="1" t="n">
-        <v>-0.03</v>
+        <v>-0.96</v>
       </c>
       <c r="J16" s="1" t="n">
-        <v>2.25</v>
+        <v>2.78</v>
       </c>
       <c r="K16" s="1" t="n">
-        <v>-0.41</v>
+        <v>-0.55</v>
       </c>
       <c r="L16" s="1" t="inlineStr">
         <is>
@@ -1501,11 +1501,11 @@
         </is>
       </c>
       <c r="M16" s="1" t="n">
-        <v>-3.65</v>
+        <v>-3.52</v>
       </c>
       <c r="N16" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O16" s="1" t="inlineStr">
@@ -1537,25 +1537,25 @@
         <v>0</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="E17" s="2" t="n">
         <v>-4</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>585.55</v>
+        <v>583.52</v>
       </c>
       <c r="H17" s="1" t="n">
-        <v>0.34</v>
+        <v>-0.01</v>
       </c>
       <c r="I17" s="1" t="n">
-        <v>-0.17</v>
+        <v>-0.68</v>
       </c>
       <c r="J17" s="1" t="n">
-        <v>0.77</v>
+        <v>1.21</v>
       </c>
       <c r="K17" s="1" t="n">
         <v>-0.58</v>
@@ -1566,11 +1566,11 @@
         </is>
       </c>
       <c r="M17" s="1" t="n">
-        <v>-5.39</v>
+        <v>-5.38</v>
       </c>
       <c r="N17" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O17" s="1" t="inlineStr">
@@ -1599,31 +1599,31 @@
         <v>17</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>-7</v>
+        <v>-5</v>
       </c>
       <c r="D18" s="2" t="n">
         <v>-4</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F18" s="2" t="n">
         <v>-15</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>29.31</v>
+        <v>29.27</v>
       </c>
       <c r="H18" s="1" t="n">
-        <v>0.03</v>
+        <v>-0.1</v>
       </c>
       <c r="I18" s="1" t="n">
-        <v>-1.91</v>
+        <v>-1.29</v>
       </c>
       <c r="J18" s="1" t="n">
-        <v>0.91</v>
+        <v>0.87</v>
       </c>
       <c r="K18" s="1" t="n">
-        <v>-0.64</v>
+        <v>-0.91</v>
       </c>
       <c r="L18" s="1" t="inlineStr">
         <is>
@@ -1657,38 +1657,38 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas</t>
+          <t>Defence</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
         <v>18</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>1</v>
+        <v>-10</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>4</v>
+        <v>-13</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>5</v>
+        <v>-10</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>8</v>
+        <v>-17</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>11.16</v>
+        <v>103.81</v>
       </c>
       <c r="H19" s="1" t="n">
-        <v>0.18</v>
+        <v>0.51</v>
       </c>
       <c r="I19" s="1" t="n">
-        <v>-0.12</v>
+        <v>1.6</v>
       </c>
       <c r="J19" s="1" t="n">
-        <v>1.41</v>
+        <v>0.04</v>
       </c>
       <c r="K19" s="1" t="n">
-        <v>-0.79</v>
+        <v>-0.99</v>
       </c>
       <c r="L19" s="1" t="inlineStr">
         <is>
@@ -1696,33 +1696,33 @@
         </is>
       </c>
       <c r="M19" s="1" t="n">
-        <v>-9.01</v>
+        <v>-4.09</v>
       </c>
       <c r="N19" s="1" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O19" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P19" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q19" s="1" t="inlineStr">
+        <is>
           <t>Yes</t>
-        </is>
-      </c>
-      <c r="O19" s="1" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="P19" s="1" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Q19" s="1" t="inlineStr">
-        <is>
-          <t>No</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>MNC</t>
+          <t>Oil &amp; Gas</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
@@ -1732,36 +1732,36 @@
         <v>1</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>-9</v>
+        <v>5</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>32.66</v>
+        <v>11.12</v>
       </c>
       <c r="H20" s="1" t="n">
-        <v>-0.09</v>
+        <v>-0.18</v>
       </c>
       <c r="I20" s="1" t="n">
-        <v>-0.19</v>
+        <v>-0.31</v>
       </c>
       <c r="J20" s="1" t="n">
-        <v>-1.45</v>
+        <v>1.24</v>
       </c>
       <c r="K20" s="1" t="n">
-        <v>-1.56</v>
+        <v>-1.18</v>
       </c>
       <c r="L20" s="1" t="inlineStr">
         <is>
-          <t>Down</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="M20" s="1" t="n">
-        <v>-4.2</v>
+        <v>-9.02</v>
       </c>
       <c r="N20" s="1" t="inlineStr">
         <is>
@@ -1780,53 +1780,53 @@
       </c>
       <c r="Q20" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>Defence</t>
+          <t>MNC</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
         <v>20</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>-15</v>
+        <v>-1</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>-15</v>
+        <v>-2</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>-12</v>
+        <v>-6</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>-19</v>
+        <v>-14</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>103.26</v>
+        <v>32.28</v>
       </c>
       <c r="H21" s="1" t="n">
-        <v>-0.02</v>
+        <v>-1.25</v>
       </c>
       <c r="I21" s="1" t="n">
-        <v>-3.28</v>
+        <v>-1.08</v>
       </c>
       <c r="J21" s="1" t="n">
-        <v>-1.74</v>
+        <v>-2.67</v>
       </c>
       <c r="K21" s="1" t="n">
-        <v>-1.79</v>
+        <v>-2.11</v>
       </c>
       <c r="L21" s="1" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Down</t>
         </is>
       </c>
       <c r="M21" s="1" t="n">
-        <v>-4.93</v>
+        <v>-4.98</v>
       </c>
       <c r="N21" s="1" t="inlineStr">
         <is>
@@ -1845,7 +1845,7 @@
       </c>
       <c r="Q21" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1865,33 +1865,33 @@
         <v>3</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>97.59999999999999</v>
+        <v>97.67</v>
       </c>
       <c r="H22" s="1" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="I22" s="1" t="n">
-        <v>-0.7</v>
+        <v>0.08</v>
       </c>
       <c r="J22" s="1" t="n">
-        <v>0.84</v>
+        <v>0.57</v>
       </c>
       <c r="K22" s="1" t="n">
-        <v>-3.38</v>
+        <v>-2.71</v>
       </c>
       <c r="L22" s="1" t="inlineStr">
         <is>
-          <t>Down</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="M22" s="1" t="n">
-        <v>-8.85</v>
+        <v>-8.470000000000001</v>
       </c>
       <c r="N22" s="1" t="inlineStr">
         <is>
@@ -1917,38 +1917,38 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>PSE</t>
+          <t>Capital Market</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
         <v>22</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>3</v>
+        <v>-3</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>1</v>
+        <v>-13</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>10.06</v>
+        <v>52.94</v>
       </c>
       <c r="H23" s="1" t="n">
-        <v>0.1</v>
+        <v>-1.19</v>
       </c>
       <c r="I23" s="1" t="n">
+        <v>-1.22</v>
+      </c>
+      <c r="J23" s="1" t="n">
         <v>-0.53</v>
       </c>
-      <c r="J23" s="1" t="n">
-        <v>1.66</v>
-      </c>
       <c r="K23" s="1" t="n">
-        <v>-3.39</v>
+        <v>-3.22</v>
       </c>
       <c r="L23" s="1" t="inlineStr">
         <is>
@@ -1956,11 +1956,11 @@
         </is>
       </c>
       <c r="M23" s="1" t="n">
-        <v>-10.45</v>
+        <v>0</v>
       </c>
       <c r="N23" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O23" s="1" t="inlineStr">
@@ -1989,31 +1989,31 @@
         <v>23</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>-13</v>
+        <v>-8</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>92.91</v>
+        <v>92.15000000000001</v>
       </c>
       <c r="H24" s="1" t="n">
-        <v>0.28</v>
+        <v>-0.54</v>
       </c>
       <c r="I24" s="1" t="n">
-        <v>-0.37</v>
+        <v>-0.42</v>
       </c>
       <c r="J24" s="1" t="n">
-        <v>-0.26</v>
+        <v>-0.08</v>
       </c>
       <c r="K24" s="1" t="n">
-        <v>-3.47</v>
+        <v>-3.28</v>
       </c>
       <c r="L24" s="1" t="inlineStr">
         <is>
@@ -2021,7 +2021,7 @@
         </is>
       </c>
       <c r="M24" s="1" t="n">
-        <v>-13.8</v>
+        <v>-14.2</v>
       </c>
       <c r="N24" s="1" t="inlineStr">
         <is>
@@ -2054,31 +2054,31 @@
         <v>24</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>-1</v>
+        <v>-3</v>
       </c>
       <c r="E25" s="2" t="n">
         <v>-3</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>-8</v>
+        <v>-10</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>93.01000000000001</v>
+        <v>93.09</v>
       </c>
       <c r="H25" s="1" t="n">
-        <v>0.05</v>
+        <v>-0.08</v>
       </c>
       <c r="I25" s="1" t="n">
-        <v>-1.28</v>
+        <v>-0.12</v>
       </c>
       <c r="J25" s="1" t="n">
-        <v>-0.41</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="K25" s="1" t="n">
-        <v>-3.47</v>
+        <v>-3.6</v>
       </c>
       <c r="L25" s="1" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         </is>
       </c>
       <c r="M25" s="1" t="n">
-        <v>-5.11</v>
+        <v>-4.7</v>
       </c>
       <c r="N25" s="1" t="inlineStr">
         <is>
@@ -2112,38 +2112,38 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>Capital Market</t>
+          <t>PSE</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
         <v>25</v>
       </c>
       <c r="C26" s="2" t="n">
+        <v>-4</v>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F26" s="2" t="n">
         <v>-2</v>
       </c>
-      <c r="D26" s="2" t="n">
-        <v>-8</v>
-      </c>
-      <c r="E26" s="2" t="n">
-        <v>-24</v>
-      </c>
-      <c r="F26" s="2" t="n">
-        <v>-20</v>
-      </c>
       <c r="G26" s="1" t="n">
-        <v>53</v>
+        <v>10</v>
       </c>
       <c r="H26" s="1" t="n">
-        <v>-1.08</v>
+        <v>-0.5</v>
       </c>
       <c r="I26" s="1" t="n">
-        <v>-1.87</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="J26" s="1" t="n">
-        <v>0.15</v>
+        <v>1.52</v>
       </c>
       <c r="K26" s="1" t="n">
-        <v>-3.84</v>
+        <v>-3.95</v>
       </c>
       <c r="L26" s="1" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="M26" s="1" t="n">
-        <v>0</v>
+        <v>-10.67</v>
       </c>
       <c r="N26" s="1" t="inlineStr">
         <is>
@@ -2177,120 +2177,120 @@
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
         <v>26</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D27" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>-4</v>
+        <v>-23</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>49.55</v>
+        <v>37.91</v>
       </c>
       <c r="H27" s="1" t="n">
-        <v>0.55</v>
+        <v>-0.24</v>
       </c>
       <c r="I27" s="1" t="n">
-        <v>1.92</v>
+        <v>-0.26</v>
       </c>
       <c r="J27" s="1" t="n">
-        <v>-0.45</v>
+        <v>1.88</v>
       </c>
       <c r="K27" s="1" t="n">
-        <v>-4.51</v>
+        <v>-5.01</v>
       </c>
       <c r="L27" s="1" t="inlineStr">
         <is>
-          <t>Down</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="M27" s="1" t="n">
-        <v>-16.13</v>
+        <v>0</v>
       </c>
       <c r="N27" s="1" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O27" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P27" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q27" s="1" t="inlineStr">
+        <is>
           <t>Yes</t>
-        </is>
-      </c>
-      <c r="O27" s="1" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="P27" s="1" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Q27" s="1" t="inlineStr">
-        <is>
-          <t>No</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D28" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>-23</v>
+        <v>-6</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>38.1</v>
+        <v>49.19</v>
       </c>
       <c r="H28" s="1" t="n">
-        <v>0.26</v>
+        <v>-0.83</v>
       </c>
       <c r="I28" s="1" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.03</v>
       </c>
       <c r="J28" s="1" t="n">
-        <v>2.17</v>
+        <v>-0.51</v>
       </c>
       <c r="K28" s="1" t="n">
-        <v>-5.24</v>
+        <v>-5.47</v>
       </c>
       <c r="L28" s="1" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Down</t>
         </is>
       </c>
       <c r="M28" s="1" t="n">
-        <v>0</v>
+        <v>-16.45</v>
       </c>
       <c r="N28" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O28" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P28" s="1" t="inlineStr">
@@ -2300,7 +2300,7 @@
       </c>
       <c r="Q28" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2569,11 +2569,11 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C2" s="1" t="n">
         <v>16</v>
@@ -2588,22 +2588,22 @@
         <v>7</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H2" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I2" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="J2" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="K2" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="J2" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="K2" s="1" t="n">
-        <v>5</v>
-      </c>
       <c r="L2" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="M2" s="1" t="n">
         <v>24</v>
@@ -2612,22 +2612,22 @@
         <v>10</v>
       </c>
       <c r="O2" s="1" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="P2" s="1" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Q2" s="1" t="n">
         <v>21</v>
       </c>
       <c r="R2" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="S2" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="T2" s="1" t="n">
         <v>19</v>
-      </c>
-      <c r="S2" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="T2" s="1" t="n">
-        <v>18</v>
       </c>
       <c r="U2" s="1" t="n">
         <v>17</v>
@@ -2636,38 +2636,38 @@
         <v>12</v>
       </c>
       <c r="W2" s="1" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="X2" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y2" s="1" t="n">
         <v>1</v>
       </c>
       <c r="Z2" s="1" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AA2" s="1" t="n">
         <v>14</v>
       </c>
       <c r="AB2" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
         <v>6</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E3" s="1" t="n">
         <v>25</v>
@@ -2676,7 +2676,7 @@
         <v>7</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H3" s="1" t="n">
         <v>2</v>
@@ -2685,43 +2685,43 @@
         <v>4</v>
       </c>
       <c r="J3" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K3" s="1" t="n">
         <v>5</v>
       </c>
       <c r="L3" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="M3" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="N3" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="M3" s="1" t="n">
+      <c r="O3" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="P3" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q3" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="N3" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="O3" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="P3" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="Q3" s="1" t="n">
-        <v>23</v>
-      </c>
       <c r="R3" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="S3" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="T3" s="1" t="n">
         <v>18</v>
-      </c>
-      <c r="S3" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="T3" s="1" t="n">
-        <v>16</v>
       </c>
       <c r="U3" s="1" t="n">
         <v>15</v>
       </c>
       <c r="V3" s="1" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="W3" s="1" t="n">
         <v>21</v>
@@ -2733,10 +2733,10 @@
         <v>1</v>
       </c>
       <c r="Z3" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AA3" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AB3" s="1" t="n">
         <v>8</v>
@@ -2745,20 +2745,20 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
         <v>6</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>7</v>
@@ -2773,43 +2773,43 @@
         <v>4</v>
       </c>
       <c r="J4" s="1" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K4" s="1" t="n">
         <v>5</v>
       </c>
       <c r="L4" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M4" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N4" s="1" t="n">
         <v>13</v>
       </c>
       <c r="O4" s="1" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="P4" s="1" t="n">
         <v>26</v>
       </c>
       <c r="Q4" s="1" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="R4" s="1" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="S4" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="T4" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="U4" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="T4" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="U4" s="1" t="n">
-        <v>18</v>
-      </c>
       <c r="V4" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="W4" s="1" t="n">
         <v>21</v>
@@ -2824,7 +2824,7 @@
         <v>12</v>
       </c>
       <c r="AA4" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AB4" s="1" t="n">
         <v>8</v>
@@ -2833,23 +2833,23 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E5" s="1" t="n">
         <v>24</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G5" s="1" t="n">
         <v>27</v>
@@ -2861,46 +2861,46 @@
         <v>4</v>
       </c>
       <c r="J5" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K5" s="1" t="n">
         <v>5</v>
       </c>
       <c r="L5" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="M5" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="N5" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="M5" s="1" t="n">
+      <c r="O5" s="1" t="n">
         <v>25</v>
-      </c>
-      <c r="N5" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="O5" s="1" t="n">
-        <v>21</v>
       </c>
       <c r="P5" s="1" t="n">
         <v>26</v>
       </c>
       <c r="Q5" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R5" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="S5" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="T5" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="S5" s="1" t="n">
+      <c r="U5" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="T5" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="U5" s="1" t="n">
-        <v>16</v>
-      </c>
       <c r="V5" s="1" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="W5" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="X5" s="1" t="n">
         <v>3</v>
@@ -2909,10 +2909,10 @@
         <v>1</v>
       </c>
       <c r="Z5" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AA5" s="1" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AB5" s="1" t="n">
         <v>8</v>
@@ -2921,23 +2921,23 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G6" s="1" t="n">
         <v>27</v>
@@ -2949,19 +2949,19 @@
         <v>4</v>
       </c>
       <c r="J6" s="1" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="K6" s="1" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L6" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M6" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="N6" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O6" s="1" t="n">
         <v>21</v>
@@ -2970,22 +2970,22 @@
         <v>26</v>
       </c>
       <c r="Q6" s="1" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="R6" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="S6" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="T6" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="S6" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="T6" s="1" t="n">
-        <v>20</v>
-      </c>
       <c r="U6" s="1" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="V6" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="W6" s="1" t="n">
         <v>22</v>
@@ -2997,23 +2997,23 @@
         <v>1</v>
       </c>
       <c r="Z6" s="1" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AA6" s="1" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="AB6" s="1" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C7" s="1" t="n">
         <v>16</v>
@@ -3022,7 +3022,7 @@
         <v>18</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F7" s="1" t="n">
         <v>9</v>
@@ -3034,22 +3034,22 @@
         <v>2</v>
       </c>
       <c r="I7" s="1" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J7" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="K7" s="1" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="M7" s="1" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="N7" s="1" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="O7" s="1" t="n">
         <v>21</v>
@@ -3061,22 +3061,22 @@
         <v>25</v>
       </c>
       <c r="R7" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="S7" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="T7" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="S7" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="T7" s="1" t="n">
-        <v>19</v>
-      </c>
       <c r="U7" s="1" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="V7" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="W7" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="X7" s="1" t="n">
         <v>3</v>
@@ -3085,62 +3085,62 @@
         <v>1</v>
       </c>
       <c r="Z7" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AA7" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AB7" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E8" s="1" t="n">
         <v>24</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G8" s="1" t="n">
         <v>27</v>
       </c>
       <c r="H8" s="1" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I8" s="1" t="n">
         <v>6</v>
       </c>
       <c r="J8" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K8" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="M8" s="1" t="n">
         <v>22</v>
       </c>
       <c r="N8" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O8" s="1" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="P8" s="1" t="n">
         <v>26</v>
@@ -3149,86 +3149,86 @@
         <v>25</v>
       </c>
       <c r="R8" s="1" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="S8" s="1" t="n">
         <v>5</v>
       </c>
       <c r="T8" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="U8" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="V8" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="V8" s="1" t="n">
-        <v>13</v>
-      </c>
       <c r="W8" s="1" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="X8" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y8" s="1" t="n">
         <v>1</v>
       </c>
       <c r="Z8" s="1" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AA8" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AB8" s="1" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D9" s="1" t="n">
         <v>21</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G9" s="1" t="n">
         <v>27</v>
       </c>
       <c r="H9" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I9" s="1" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J9" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K9" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L9" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M9" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N9" s="1" t="n">
         <v>12</v>
       </c>
       <c r="O9" s="1" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="P9" s="1" t="n">
         <v>26</v>
@@ -3237,110 +3237,110 @@
         <v>25</v>
       </c>
       <c r="R9" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="S9" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T9" s="1" t="n">
         <v>20</v>
       </c>
       <c r="U9" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="V9" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="V9" s="1" t="n">
-        <v>11</v>
-      </c>
       <c r="W9" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="X9" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y9" s="1" t="n">
         <v>1</v>
       </c>
       <c r="Z9" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA9" s="1" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AB9" s="1" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="C10" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="C10" s="1" t="n">
-        <v>16</v>
-      </c>
       <c r="D10" s="1" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G10" s="1" t="n">
         <v>27</v>
       </c>
       <c r="H10" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I10" s="1" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J10" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K10" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L10" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M10" s="1" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N10" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="O10" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="P10" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q10" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="R10" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="S10" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="T10" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="U10" s="1" t="n">
         <v>13</v>
-      </c>
-      <c r="O10" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="P10" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="Q10" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="R10" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="S10" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="T10" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="U10" s="1" t="n">
-        <v>14</v>
       </c>
       <c r="V10" s="1" t="n">
         <v>11</v>
       </c>
       <c r="W10" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="X10" s="1" t="n">
         <v>3</v>
@@ -3349,29 +3349,29 @@
         <v>1</v>
       </c>
       <c r="Z10" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA10" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="AB10" s="1" t="n">
         <v>9</v>
-      </c>
-      <c r="AA10" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="AB10" s="1" t="n">
-        <v>10</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="C11" s="1" t="n">
         <v>16</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E11" s="1" t="n">
         <v>23</v>
@@ -3389,46 +3389,46 @@
         <v>7</v>
       </c>
       <c r="J11" s="1" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="K11" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M11" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N11" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O11" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="P11" s="1" t="n">
         <v>25</v>
-      </c>
-      <c r="P11" s="1" t="n">
-        <v>26</v>
       </c>
       <c r="Q11" s="1" t="n">
         <v>24</v>
       </c>
       <c r="R11" s="1" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="S11" s="1" t="n">
         <v>5</v>
       </c>
       <c r="T11" s="1" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="U11" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="V11" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="W11" s="1" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="X11" s="1" t="n">
         <v>3</v>
@@ -3437,10 +3437,10 @@
         <v>1</v>
       </c>
       <c r="Z11" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA11" s="1" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AB11" s="1" t="n">
         <v>10</v>
@@ -3449,59 +3449,59 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F12" s="1" t="n">
         <v>6</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H12" s="1" t="n">
         <v>4</v>
       </c>
       <c r="I12" s="1" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J12" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K12" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M12" s="1" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N12" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="O12" s="1" t="n">
         <v>25</v>
       </c>
       <c r="P12" s="1" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Q12" s="1" t="n">
         <v>24</v>
       </c>
       <c r="R12" s="1" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="S12" s="1" t="n">
         <v>5</v>
@@ -3513,10 +3513,10 @@
         <v>13</v>
       </c>
       <c r="V12" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="W12" s="1" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="X12" s="1" t="n">
         <v>3</v>
@@ -3525,35 +3525,35 @@
         <v>1</v>
       </c>
       <c r="Z12" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA12" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AB12" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="C13" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="C13" s="1" t="n">
-        <v>10</v>
-      </c>
       <c r="D13" s="1" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G13" s="1" t="n">
         <v>26</v>
@@ -3562,22 +3562,22 @@
         <v>4</v>
       </c>
       <c r="I13" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J13" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K13" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L13" s="1" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M13" s="1" t="n">
         <v>23</v>
       </c>
       <c r="N13" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O13" s="1" t="n">
         <v>25</v>
@@ -3589,22 +3589,22 @@
         <v>24</v>
       </c>
       <c r="R13" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="S13" s="1" t="n">
         <v>5</v>
       </c>
       <c r="T13" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="U13" s="1" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="V13" s="1" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="W13" s="1" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="X13" s="1" t="n">
         <v>3</v>
@@ -3616,32 +3616,32 @@
         <v>7</v>
       </c>
       <c r="AA13" s="1" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="AB13" s="1" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G14" s="1" t="n">
         <v>26</v>
@@ -3650,49 +3650,49 @@
         <v>4</v>
       </c>
       <c r="I14" s="1" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="J14" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K14" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="M14" s="1" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="N14" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O14" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="P14" s="1" t="n">
         <v>27</v>
       </c>
       <c r="Q14" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R14" s="1" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="S14" s="1" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T14" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="U14" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="V14" s="1" t="n">
         <v>18</v>
       </c>
       <c r="W14" s="1" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="X14" s="1" t="n">
         <v>3</v>
@@ -3701,19 +3701,19 @@
         <v>1</v>
       </c>
       <c r="Z14" s="1" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AA14" s="1" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AB14" s="1" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
@@ -3723,7 +3723,7 @@
         <v>11</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E15" s="1" t="n">
         <v>16</v>
@@ -3732,7 +3732,7 @@
         <v>6</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H15" s="1" t="n">
         <v>4</v>
@@ -3747,40 +3747,40 @@
         <v>2</v>
       </c>
       <c r="L15" s="1" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="M15" s="1" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="N15" s="1" t="n">
         <v>14</v>
       </c>
       <c r="O15" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P15" s="1" t="n">
         <v>27</v>
       </c>
       <c r="Q15" s="1" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="R15" s="1" t="n">
         <v>19</v>
       </c>
       <c r="S15" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T15" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="U15" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="V15" s="1" t="n">
         <v>18</v>
       </c>
       <c r="W15" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="X15" s="1" t="n">
         <v>3</v>
@@ -3789,10 +3789,10 @@
         <v>1</v>
       </c>
       <c r="Z15" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA15" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AB15" s="1" t="n">
         <v>7</v>
@@ -3801,29 +3801,29 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F16" s="1" t="n">
         <v>6</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H16" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I16" s="1" t="n">
         <v>5</v>
@@ -3835,16 +3835,16 @@
         <v>2</v>
       </c>
       <c r="L16" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M16" s="1" t="n">
         <v>22</v>
       </c>
       <c r="N16" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="O16" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="P16" s="1" t="n">
         <v>27</v>
@@ -3853,34 +3853,34 @@
         <v>26</v>
       </c>
       <c r="R16" s="1" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="S16" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T16" s="1" t="n">
         <v>21</v>
       </c>
       <c r="U16" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="V16" s="1" t="n">
         <v>18</v>
-      </c>
-      <c r="V16" s="1" t="n">
-        <v>15</v>
       </c>
       <c r="W16" s="1" t="n">
         <v>20</v>
       </c>
       <c r="X16" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y16" s="1" t="n">
         <v>1</v>
       </c>
       <c r="Z16" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA16" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AB16" s="1" t="n">
         <v>7</v>
@@ -3889,7 +3889,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
@@ -3899,22 +3899,22 @@
         <v>10</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F17" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="G17" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="H17" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="G17" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="H17" s="1" t="n">
+      <c r="I17" s="1" t="n">
         <v>5</v>
-      </c>
-      <c r="I17" s="1" t="n">
-        <v>6</v>
       </c>
       <c r="J17" s="1" t="n">
         <v>23</v>
@@ -3923,37 +3923,37 @@
         <v>2</v>
       </c>
       <c r="L17" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M17" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="N17" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="O17" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="P17" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q17" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="R17" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="S17" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="T17" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="N17" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="O17" s="1" t="n">
-        <v>27</v>
-      </c>
-      <c r="P17" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="Q17" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="R17" s="1" t="n">
+      <c r="U17" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="S17" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="T17" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="U17" s="1" t="n">
+      <c r="V17" s="1" t="n">
         <v>15</v>
-      </c>
-      <c r="V17" s="1" t="n">
-        <v>17</v>
       </c>
       <c r="W17" s="1" t="n">
         <v>20</v>
@@ -3965,7 +3965,7 @@
         <v>1</v>
       </c>
       <c r="Z17" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA17" s="1" t="n">
         <v>16</v>
@@ -3977,77 +3977,77 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D18" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="E18" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="E18" s="1" t="n">
-        <v>14</v>
-      </c>
       <c r="F18" s="1" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G18" s="1" t="n">
         <v>24</v>
       </c>
       <c r="H18" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I18" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J18" s="1" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="K18" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L18" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="M18" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="N18" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="O18" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="P18" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q18" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="R18" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="S18" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="T18" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="U18" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="V18" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="M18" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="N18" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="O18" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="P18" s="1" t="n">
-        <v>27</v>
-      </c>
-      <c r="Q18" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="R18" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="S18" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="T18" s="1" t="n">
-        <v>23</v>
-      </c>
-      <c r="U18" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="V18" s="1" t="n">
-        <v>16</v>
-      </c>
       <c r="W18" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="X18" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y18" s="1" t="n">
         <v>1</v>
@@ -4056,26 +4056,26 @@
         <v>8</v>
       </c>
       <c r="AA18" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AB18" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="C19" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="C19" s="1" t="n">
-        <v>10</v>
-      </c>
       <c r="D19" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E19" s="1" t="n">
         <v>14</v>
@@ -4093,34 +4093,34 @@
         <v>7</v>
       </c>
       <c r="J19" s="1" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K19" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L19" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M19" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N19" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="O19" s="1" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P19" s="1" t="n">
         <v>27</v>
       </c>
       <c r="Q19" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="R19" s="1" t="n">
         <v>19</v>
       </c>
       <c r="S19" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T19" s="1" t="n">
         <v>23</v>
@@ -4132,7 +4132,7 @@
         <v>16</v>
       </c>
       <c r="W19" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="X19" s="1" t="n">
         <v>3</v>
@@ -4141,47 +4141,47 @@
         <v>1</v>
       </c>
       <c r="Z19" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA19" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="AB19" s="1" t="n">
         <v>6</v>
-      </c>
-      <c r="AA19" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="AB19" s="1" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
         <v>11</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D20" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="E20" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="E20" s="1" t="n">
-        <v>12</v>
-      </c>
       <c r="F20" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G20" s="1" t="n">
         <v>24</v>
       </c>
       <c r="H20" s="1" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I20" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J20" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K20" s="1" t="n">
         <v>2</v>
@@ -4190,7 +4190,7 @@
         <v>15</v>
       </c>
       <c r="M20" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N20" s="1" t="n">
         <v>13</v>
@@ -4208,7 +4208,7 @@
         <v>19</v>
       </c>
       <c r="S20" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T20" s="1" t="n">
         <v>23</v>
@@ -4217,7 +4217,7 @@
         <v>18</v>
       </c>
       <c r="V20" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="W20" s="1" t="n">
         <v>20</v>
@@ -4229,32 +4229,32 @@
         <v>1</v>
       </c>
       <c r="Z20" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA20" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AB20" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C21" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="E21" s="1" t="n">
         <v>12</v>
-      </c>
-      <c r="D21" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>13</v>
       </c>
       <c r="F21" s="1" t="n">
         <v>4</v>
@@ -4263,10 +4263,10 @@
         <v>24</v>
       </c>
       <c r="H21" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I21" s="1" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J21" s="1" t="n">
         <v>21</v>
@@ -4275,40 +4275,40 @@
         <v>2</v>
       </c>
       <c r="L21" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="M21" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="N21" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="O21" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="P21" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q21" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="R21" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="S21" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="U21" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="M21" s="1" t="n">
+      <c r="V21" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="W21" s="1" t="n">
         <v>20</v>
-      </c>
-      <c r="N21" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="O21" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="P21" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="Q21" s="1" t="n">
-        <v>27</v>
-      </c>
-      <c r="R21" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="S21" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="T21" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="U21" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="V21" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="W21" s="1" t="n">
-        <v>23</v>
       </c>
       <c r="X21" s="1" t="n">
         <v>3</v>
@@ -4317,38 +4317,38 @@
         <v>1</v>
       </c>
       <c r="Z21" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA21" s="1" t="n">
         <v>16</v>
       </c>
       <c r="AB21" s="1" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C22" s="1" t="n">
         <v>12</v>
       </c>
       <c r="D22" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F22" s="1" t="n">
         <v>4</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H22" s="1" t="n">
         <v>7</v>
@@ -4357,7 +4357,7 @@
         <v>11</v>
       </c>
       <c r="J22" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K22" s="1" t="n">
         <v>2</v>
@@ -4366,25 +4366,25 @@
         <v>18</v>
       </c>
       <c r="M22" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="N22" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="O22" s="1" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="P22" s="1" t="n">
         <v>26</v>
       </c>
       <c r="Q22" s="1" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="R22" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="S22" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T22" s="1" t="n">
         <v>22</v>
@@ -4393,7 +4393,7 @@
         <v>19</v>
       </c>
       <c r="V22" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="W22" s="1" t="n">
         <v>23</v>
@@ -4408,7 +4408,7 @@
         <v>6</v>
       </c>
       <c r="AA22" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AB22" s="1" t="n">
         <v>5</v>
@@ -4417,47 +4417,47 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C23" s="1" t="n">
         <v>12</v>
       </c>
       <c r="D23" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="E23" s="1" t="n">
         <v>15</v>
-      </c>
-      <c r="E23" s="1" t="n">
-        <v>10</v>
       </c>
       <c r="F23" s="1" t="n">
         <v>4</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H23" s="1" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I23" s="1" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J23" s="1" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K23" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L23" s="1" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M23" s="1" t="n">
         <v>21</v>
       </c>
       <c r="N23" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O23" s="1" t="n">
         <v>27</v>
@@ -4466,59 +4466,59 @@
         <v>26</v>
       </c>
       <c r="Q23" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R23" s="1" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="S23" s="1" t="n">
         <v>8</v>
       </c>
       <c r="T23" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="U23" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="V23" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="W23" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="U23" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="V23" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="W23" s="1" t="n">
+      <c r="X23" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y23" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="X23" s="1" t="n">
+      <c r="Z23" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA23" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="AB23" s="1" t="n">
         <v>5</v>
-      </c>
-      <c r="Y23" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z23" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA23" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="AB23" s="1" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
         <v>13</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D24" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F24" s="1" t="n">
         <v>4</v>
@@ -4527,13 +4527,13 @@
         <v>24</v>
       </c>
       <c r="H24" s="1" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I24" s="1" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="J24" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K24" s="1" t="n">
         <v>3</v>
@@ -4557,25 +4557,25 @@
         <v>25</v>
       </c>
       <c r="R24" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="S24" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="T24" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="U24" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="V24" s="1" t="n">
         <v>16</v>
-      </c>
-      <c r="S24" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="T24" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="U24" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="V24" s="1" t="n">
-        <v>15</v>
       </c>
       <c r="W24" s="1" t="n">
         <v>1</v>
       </c>
       <c r="X24" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y24" s="1" t="n">
         <v>2</v>
@@ -4584,26 +4584,26 @@
         <v>7</v>
       </c>
       <c r="AA24" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AB24" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D25" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E25" s="1" t="n">
         <v>9</v>
@@ -4612,22 +4612,22 @@
         <v>4</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H25" s="1" t="n">
         <v>12</v>
       </c>
       <c r="I25" s="1" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J25" s="1" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K25" s="1" t="n">
         <v>3</v>
       </c>
       <c r="L25" s="1" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="M25" s="1" t="n">
         <v>21</v>
@@ -4639,25 +4639,25 @@
         <v>27</v>
       </c>
       <c r="P25" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q25" s="1" t="n">
         <v>25</v>
-      </c>
-      <c r="Q25" s="1" t="n">
-        <v>24</v>
       </c>
       <c r="R25" s="1" t="n">
         <v>16</v>
       </c>
       <c r="S25" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T25" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="U25" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="V25" s="1" t="n">
         <v>15</v>
-      </c>
-      <c r="V25" s="1" t="n">
-        <v>14</v>
       </c>
       <c r="W25" s="1" t="n">
         <v>1</v>
@@ -4681,38 +4681,38 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C26" s="1" t="n">
         <v>10</v>
       </c>
       <c r="D26" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E26" s="1" t="n">
         <v>9</v>
       </c>
       <c r="F26" s="1" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H26" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I26" s="1" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J26" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K26" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L26" s="1" t="n">
         <v>20</v>
@@ -4724,37 +4724,37 @@
         <v>11</v>
       </c>
       <c r="O26" s="1" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P26" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q26" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="Q26" s="1" t="n">
-        <v>25</v>
-      </c>
       <c r="R26" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="S26" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="T26" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="U26" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="V26" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="S26" s="1" t="n">
+      <c r="W26" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="X26" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="T26" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="U26" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="V26" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="W26" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="X26" s="1" t="n">
-        <v>8</v>
-      </c>
       <c r="Y26" s="1" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Z26" s="1" t="n">
         <v>7</v>
@@ -4769,20 +4769,20 @@
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="C27" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="C27" s="1" t="n">
-        <v>11</v>
-      </c>
       <c r="D27" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F27" s="1" t="n">
         <v>2</v>
@@ -4791,10 +4791,10 @@
         <v>27</v>
       </c>
       <c r="H27" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I27" s="1" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J27" s="1" t="n">
         <v>23</v>
@@ -4809,7 +4809,7 @@
         <v>21</v>
       </c>
       <c r="N27" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="O27" s="1" t="n">
         <v>26</v>
@@ -4821,10 +4821,10 @@
         <v>25</v>
       </c>
       <c r="R27" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S27" s="1" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T27" s="1" t="n">
         <v>22</v>
@@ -4833,13 +4833,13 @@
         <v>16</v>
       </c>
       <c r="V27" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="W27" s="1" t="n">
         <v>3</v>
       </c>
       <c r="X27" s="1" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y27" s="1" t="n">
         <v>4</v>
@@ -4857,38 +4857,38 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D28" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="E28" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="F28" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G28" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="H28" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="I28" s="1" t="n">
         <v>19</v>
-      </c>
-      <c r="E28" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="F28" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="G28" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="H28" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="I28" s="1" t="n">
-        <v>18</v>
       </c>
       <c r="J28" s="1" t="n">
         <v>23</v>
       </c>
       <c r="K28" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L28" s="1" t="n">
         <v>20</v>
@@ -4897,10 +4897,10 @@
         <v>21</v>
       </c>
       <c r="N28" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="O28" s="1" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P28" s="1" t="n">
         <v>24</v>
@@ -4909,7 +4909,7 @@
         <v>25</v>
       </c>
       <c r="R28" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="S28" s="1" t="n">
         <v>9</v>
@@ -4918,25 +4918,25 @@
         <v>22</v>
       </c>
       <c r="U28" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="V28" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="W28" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X28" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y28" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="Y28" s="1" t="n">
-        <v>2</v>
-      </c>
       <c r="Z28" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA28" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AB28" s="1" t="n">
         <v>5</v>
@@ -4945,41 +4945,41 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C29" s="1" t="n">
         <v>12</v>
       </c>
       <c r="D29" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F29" s="1" t="n">
         <v>7</v>
       </c>
       <c r="G29" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="H29" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="I29" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="J29" s="1" t="n">
         <v>23</v>
-      </c>
-      <c r="H29" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="I29" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="J29" s="1" t="n">
-        <v>24</v>
       </c>
       <c r="K29" s="1" t="n">
         <v>3</v>
       </c>
       <c r="L29" s="1" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M29" s="1" t="n">
         <v>21</v>
@@ -4991,25 +4991,25 @@
         <v>27</v>
       </c>
       <c r="P29" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q29" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="Q29" s="1" t="n">
-        <v>26</v>
-      </c>
       <c r="R29" s="1" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="S29" s="1" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="T29" s="1" t="n">
         <v>22</v>
       </c>
       <c r="U29" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="V29" s="1" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="W29" s="1" t="n">
         <v>1</v>
@@ -5024,50 +5024,50 @@
         <v>8</v>
       </c>
       <c r="AA29" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AB29" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="C30" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D30" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="E30" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="F30" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C30" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="D30" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="E30" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="F30" s="1" t="n">
-        <v>5</v>
-      </c>
       <c r="G30" s="1" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="H30" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I30" s="1" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J30" s="1" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K30" s="1" t="n">
         <v>3</v>
       </c>
       <c r="L30" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M30" s="1" t="n">
         <v>21</v>
@@ -5079,25 +5079,25 @@
         <v>27</v>
       </c>
       <c r="P30" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Q30" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="R30" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="S30" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="S30" s="1" t="n">
-        <v>19</v>
-      </c>
       <c r="T30" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="U30" s="1" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="V30" s="1" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="W30" s="1" t="n">
         <v>1</v>
@@ -5109,10 +5109,10 @@
         <v>2</v>
       </c>
       <c r="Z30" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA30" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AB30" s="1" t="n">
         <v>6</v>
@@ -5121,20 +5121,20 @@
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C31" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="D31" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="D31" s="1" t="n">
-        <v>20</v>
-      </c>
       <c r="E31" s="1" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F31" s="1" t="n">
         <v>5</v>
@@ -5143,10 +5143,10 @@
         <v>26</v>
       </c>
       <c r="H31" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I31" s="1" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J31" s="1" t="n">
         <v>22</v>
@@ -5155,34 +5155,34 @@
         <v>3</v>
       </c>
       <c r="L31" s="1" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M31" s="1" t="n">
         <v>21</v>
       </c>
       <c r="N31" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="O31" s="1" t="n">
         <v>27</v>
       </c>
       <c r="P31" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q31" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="Q31" s="1" t="n">
-        <v>24</v>
-      </c>
       <c r="R31" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="S31" s="1" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="T31" s="1" t="n">
         <v>23</v>
       </c>
       <c r="U31" s="1" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="V31" s="1" t="n">
         <v>17</v>
@@ -5197,10 +5197,10 @@
         <v>2</v>
       </c>
       <c r="Z31" s="1" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AA31" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AB31" s="1" t="n">
         <v>6</v>
@@ -5209,44 +5209,44 @@
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D32" s="1" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F32" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G32" s="1" t="n">
         <v>26</v>
       </c>
       <c r="H32" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I32" s="1" t="n">
         <v>10</v>
       </c>
       <c r="J32" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K32" s="1" t="n">
         <v>3</v>
       </c>
       <c r="L32" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M32" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N32" s="1" t="n">
         <v>11</v>
@@ -5261,10 +5261,10 @@
         <v>24</v>
       </c>
       <c r="R32" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="S32" s="1" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="T32" s="1" t="n">
         <v>23</v>
@@ -5273,13 +5273,13 @@
         <v>18</v>
       </c>
       <c r="V32" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="W32" s="1" t="n">
         <v>1</v>
       </c>
       <c r="X32" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y32" s="1" t="n">
         <v>2</v>
@@ -5288,7 +5288,7 @@
         <v>7</v>
       </c>
       <c r="AA32" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AB32" s="1" t="n">
         <v>6</v>
@@ -5297,38 +5297,38 @@
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
         <v>9</v>
       </c>
       <c r="C33" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D33" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="E33" s="1" t="n">
         <v>13</v>
-      </c>
-      <c r="D33" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="E33" s="1" t="n">
-        <v>11</v>
       </c>
       <c r="F33" s="1" t="n">
         <v>4</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H33" s="1" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I33" s="1" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J33" s="1" t="n">
         <v>21</v>
       </c>
       <c r="K33" s="1" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="L33" s="1" t="n">
         <v>20</v>
@@ -5337,28 +5337,28 @@
         <v>22</v>
       </c>
       <c r="N33" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="O33" s="1" t="n">
         <v>27</v>
       </c>
       <c r="P33" s="1" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Q33" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R33" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="S33" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="T33" s="1" t="n">
         <v>23</v>
       </c>
       <c r="U33" s="1" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="V33" s="1" t="n">
         <v>15</v>
@@ -5373,10 +5373,10 @@
         <v>2</v>
       </c>
       <c r="Z33" s="1" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AA33" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AB33" s="1" t="n">
         <v>6</v>
@@ -5385,47 +5385,47 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C34" s="1" t="n">
         <v>13</v>
       </c>
       <c r="D34" s="1" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="F34" s="1" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H34" s="1" t="n">
         <v>3</v>
       </c>
       <c r="I34" s="1" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J34" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="K34" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="L34" s="1" t="n">
         <v>20</v>
-      </c>
-      <c r="K34" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="L34" s="1" t="n">
-        <v>18</v>
       </c>
       <c r="M34" s="1" t="n">
         <v>22</v>
       </c>
       <c r="N34" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O34" s="1" t="n">
         <v>27</v>
@@ -5437,25 +5437,25 @@
         <v>25</v>
       </c>
       <c r="R34" s="1" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="S34" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="T34" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="U34" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="T34" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="U34" s="1" t="n">
-        <v>12</v>
-      </c>
       <c r="V34" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="W34" s="1" t="n">
         <v>1</v>
       </c>
       <c r="X34" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y34" s="1" t="n">
         <v>2</v>
@@ -5473,44 +5473,44 @@
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D35" s="1" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F35" s="1" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G35" s="1" t="n">
         <v>23</v>
       </c>
       <c r="H35" s="1" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I35" s="1" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J35" s="1" t="n">
         <v>20</v>
       </c>
       <c r="K35" s="1" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L35" s="1" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="M35" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N35" s="1" t="n">
         <v>11</v>
@@ -5522,86 +5522,86 @@
         <v>26</v>
       </c>
       <c r="Q35" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="R35" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="S35" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="T35" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="R35" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="S35" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="T35" s="1" t="n">
-        <v>25</v>
-      </c>
       <c r="U35" s="1" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="V35" s="1" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="W35" s="1" t="n">
         <v>1</v>
       </c>
       <c r="X35" s="1" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Y35" s="1" t="n">
         <v>2</v>
       </c>
       <c r="Z35" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA35" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AB35" s="1" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B36" s="1" t="n">
         <v>10</v>
       </c>
       <c r="C36" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="D36" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="D36" s="1" t="n">
-        <v>11</v>
-      </c>
       <c r="E36" s="1" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F36" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G36" s="1" t="n">
         <v>23</v>
       </c>
       <c r="H36" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="I36" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="J36" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="K36" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="I36" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="J36" s="1" t="n">
+      <c r="L36" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="M36" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="K36" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="L36" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="M36" s="1" t="n">
-        <v>22</v>
-      </c>
       <c r="N36" s="1" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="O36" s="1" t="n">
         <v>27</v>
@@ -5613,7 +5613,7 @@
         <v>24</v>
       </c>
       <c r="R36" s="1" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="S36" s="1" t="n">
         <v>19</v>
@@ -5622,16 +5622,16 @@
         <v>25</v>
       </c>
       <c r="U36" s="1" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="V36" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="W36" s="1" t="n">
         <v>1</v>
       </c>
       <c r="X36" s="1" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Y36" s="1" t="n">
         <v>2</v>
@@ -5640,23 +5640,23 @@
         <v>9</v>
       </c>
       <c r="AA36" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AB36" s="1" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B37" s="1" t="n">
         <v>10</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D37" s="1" t="n">
         <v>11</v>
@@ -5665,7 +5665,7 @@
         <v>20</v>
       </c>
       <c r="F37" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G37" s="1" t="n">
         <v>23</v>
@@ -5677,19 +5677,19 @@
         <v>7</v>
       </c>
       <c r="J37" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K37" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L37" s="1" t="n">
         <v>13</v>
       </c>
       <c r="M37" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N37" s="1" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="O37" s="1" t="n">
         <v>27</v>
@@ -5701,19 +5701,19 @@
         <v>24</v>
       </c>
       <c r="R37" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="S37" s="1" t="n">
         <v>19</v>
-      </c>
-      <c r="S37" s="1" t="n">
-        <v>18</v>
       </c>
       <c r="T37" s="1" t="n">
         <v>25</v>
       </c>
       <c r="U37" s="1" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="V37" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="W37" s="1" t="n">
         <v>1</v>
@@ -5728,7 +5728,7 @@
         <v>9</v>
       </c>
       <c r="AA37" s="1" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AB37" s="1" t="n">
         <v>8</v>
@@ -5737,44 +5737,44 @@
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B38" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="C38" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="C38" s="1" t="n">
-        <v>16</v>
-      </c>
       <c r="D38" s="1" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F38" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G38" s="1" t="n">
         <v>23</v>
       </c>
       <c r="H38" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I38" s="1" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J38" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="K38" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="L38" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="M38" s="1" t="n">
         <v>21</v>
-      </c>
-      <c r="K38" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="L38" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="M38" s="1" t="n">
-        <v>20</v>
       </c>
       <c r="N38" s="1" t="n">
         <v>12</v>
@@ -5798,19 +5798,19 @@
         <v>25</v>
       </c>
       <c r="U38" s="1" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="V38" s="1" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="W38" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="X38" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="X38" s="1" t="n">
-        <v>7</v>
-      </c>
       <c r="Y38" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Z38" s="1" t="n">
         <v>9</v>
@@ -5825,23 +5825,23 @@
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B39" s="1" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C39" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="D39" s="1" t="n">
         <v>14</v>
-      </c>
-      <c r="D39" s="1" t="n">
-        <v>13</v>
       </c>
       <c r="E39" s="1" t="n">
         <v>22</v>
       </c>
       <c r="F39" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G39" s="1" t="n">
         <v>23</v>
@@ -5853,16 +5853,16 @@
         <v>3</v>
       </c>
       <c r="J39" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K39" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L39" s="1" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="M39" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="N39" s="1" t="n">
         <v>12</v>
@@ -5877,47 +5877,47 @@
         <v>24</v>
       </c>
       <c r="R39" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="S39" s="1" t="n">
         <v>18</v>
-      </c>
-      <c r="S39" s="1" t="n">
-        <v>19</v>
       </c>
       <c r="T39" s="1" t="n">
         <v>25</v>
       </c>
       <c r="U39" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="V39" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="W39" s="1" t="n">
         <v>4</v>
       </c>
       <c r="X39" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y39" s="1" t="n">
         <v>5</v>
       </c>
       <c r="Z39" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA39" s="1" t="n">
         <v>17</v>
       </c>
       <c r="AB39" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B40" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C40" s="1" t="n">
         <v>14</v>
@@ -5926,31 +5926,31 @@
         <v>13</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F40" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G40" s="1" t="n">
         <v>23</v>
       </c>
       <c r="H40" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I40" s="1" t="n">
         <v>3</v>
       </c>
       <c r="J40" s="1" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K40" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L40" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M40" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N40" s="1" t="n">
         <v>12</v>
@@ -5965,19 +5965,19 @@
         <v>24</v>
       </c>
       <c r="R40" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="S40" s="1" t="n">
         <v>19</v>
-      </c>
-      <c r="S40" s="1" t="n">
-        <v>18</v>
       </c>
       <c r="T40" s="1" t="n">
         <v>25</v>
       </c>
       <c r="U40" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="V40" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="W40" s="1" t="n">
         <v>4</v>
@@ -5989,10 +5989,10 @@
         <v>5</v>
       </c>
       <c r="Z40" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA40" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AB40" s="1" t="n">
         <v>9</v>
@@ -6001,26 +6001,26 @@
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B41" s="1" t="n">
         <v>11</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D41" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F41" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H41" s="1" t="n">
         <v>2</v>
@@ -6029,13 +6029,13 @@
         <v>3</v>
       </c>
       <c r="J41" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K41" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L41" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M41" s="1" t="n">
         <v>20</v>
@@ -6050,16 +6050,16 @@
         <v>26</v>
       </c>
       <c r="Q41" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="R41" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="S41" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="T41" s="1" t="n">
         <v>25</v>
-      </c>
-      <c r="R41" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="S41" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="T41" s="1" t="n">
-        <v>24</v>
       </c>
       <c r="U41" s="1" t="n">
         <v>10</v>
@@ -6077,35 +6077,35 @@
         <v>5</v>
       </c>
       <c r="Z41" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA41" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="AB41" s="1" t="n">
         <v>9</v>
-      </c>
-      <c r="AA41" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="AB41" s="1" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B42" s="1" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D42" s="1" t="n">
         <v>14</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F42" s="1" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G42" s="1" t="n">
         <v>21</v>
@@ -6123,7 +6123,7 @@
         <v>1</v>
       </c>
       <c r="L42" s="1" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="M42" s="1" t="n">
         <v>20</v>
@@ -6135,56 +6135,56 @@
         <v>27</v>
       </c>
       <c r="P42" s="1" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="Q42" s="1" t="n">
         <v>25</v>
       </c>
       <c r="R42" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="S42" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="T42" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="U42" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="T42" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="U42" s="1" t="n">
+      <c r="V42" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="W42" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="V42" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="W42" s="1" t="n">
+      <c r="X42" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="X42" s="1" t="n">
-        <v>11</v>
-      </c>
       <c r="Y42" s="1" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Z42" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA42" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="AB42" s="1" t="n">
         <v>8</v>
-      </c>
-      <c r="AA42" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="AB42" s="1" t="n">
-        <v>9</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B43" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="C43" s="1" t="n">
         <v>17</v>
-      </c>
-      <c r="C43" s="1" t="n">
-        <v>15</v>
       </c>
       <c r="D43" s="1" t="n">
         <v>14</v>
@@ -6196,7 +6196,7 @@
         <v>5</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="H43" s="1" t="n">
         <v>2</v>
@@ -6205,25 +6205,25 @@
         <v>3</v>
       </c>
       <c r="J43" s="1" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K43" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L43" s="1" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="M43" s="1" t="n">
         <v>20</v>
       </c>
       <c r="N43" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="O43" s="1" t="n">
         <v>27</v>
       </c>
       <c r="P43" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q43" s="1" t="n">
         <v>25</v>
@@ -6232,47 +6232,47 @@
         <v>16</v>
       </c>
       <c r="S43" s="1" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T43" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="U43" s="1" t="n">
         <v>4</v>
       </c>
       <c r="V43" s="1" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="W43" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X43" s="1" t="n">
         <v>11</v>
       </c>
       <c r="Y43" s="1" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Z43" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA43" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="AB43" s="1" t="n">
         <v>9</v>
-      </c>
-      <c r="AA43" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="AB43" s="1" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B44" s="1" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D44" s="1" t="n">
         <v>14</v>
@@ -6293,34 +6293,34 @@
         <v>3</v>
       </c>
       <c r="J44" s="1" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K44" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L44" s="1" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M44" s="1" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="N44" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="O44" s="1" t="n">
         <v>27</v>
       </c>
       <c r="P44" s="1" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q44" s="1" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="R44" s="1" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="S44" s="1" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T44" s="1" t="n">
         <v>21</v>
@@ -6332,13 +6332,13 @@
         <v>12</v>
       </c>
       <c r="W44" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X44" s="1" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="Y44" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z44" s="1" t="n">
         <v>9</v>
@@ -6347,59 +6347,59 @@
         <v>19</v>
       </c>
       <c r="AB44" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B45" s="1" t="n">
         <v>25</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D45" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F45" s="1" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G45" s="1" t="n">
         <v>24</v>
       </c>
       <c r="H45" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I45" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="J45" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="K45" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="I45" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="J45" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="K45" s="1" t="n">
-        <v>3</v>
-      </c>
       <c r="L45" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M45" s="1" t="n">
         <v>18</v>
       </c>
       <c r="N45" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="O45" s="1" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P45" s="1" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="Q45" s="1" t="n">
         <v>23</v>
@@ -6408,56 +6408,56 @@
         <v>13</v>
       </c>
       <c r="S45" s="1" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T45" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="U45" s="1" t="n">
         <v>4</v>
       </c>
       <c r="V45" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="W45" s="1" t="n">
         <v>6</v>
       </c>
       <c r="X45" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Y45" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z45" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA45" s="1" t="n">
         <v>19</v>
       </c>
       <c r="AB45" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B46" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="C46" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="D46" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="E46" s="1" t="n">
         <v>27</v>
       </c>
-      <c r="C46" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="D46" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="E46" s="1" t="n">
-        <v>25</v>
-      </c>
       <c r="F46" s="1" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G46" s="1" t="n">
         <v>24</v>
@@ -6466,61 +6466,61 @@
         <v>1</v>
       </c>
       <c r="I46" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="J46" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="K46" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="J46" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="K46" s="1" t="n">
-        <v>2</v>
-      </c>
       <c r="L46" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M46" s="1" t="n">
         <v>18</v>
       </c>
       <c r="N46" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="O46" s="1" t="n">
         <v>26</v>
       </c>
       <c r="P46" s="1" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q46" s="1" t="n">
         <v>23</v>
       </c>
       <c r="R46" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="S46" s="1" t="n">
         <v>5</v>
       </c>
       <c r="T46" s="1" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="U46" s="1" t="n">
         <v>4</v>
       </c>
       <c r="V46" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="W46" s="1" t="n">
         <v>6</v>
       </c>
       <c r="X46" s="1" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="Y46" s="1" t="n">
         <v>7</v>
       </c>
       <c r="Z46" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA46" s="1" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AB46" s="1" t="n">
         <v>8</v>
@@ -6529,47 +6529,47 @@
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B47" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C47" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="D47" s="1" t="n">
         <v>13</v>
-      </c>
-      <c r="D47" s="1" t="n">
-        <v>6</v>
       </c>
       <c r="E47" s="1" t="n">
         <v>25</v>
       </c>
       <c r="F47" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H47" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I47" s="1" t="n">
         <v>3</v>
       </c>
       <c r="J47" s="1" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="K47" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L47" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M47" s="1" t="n">
         <v>18</v>
       </c>
       <c r="N47" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="O47" s="1" t="n">
         <v>26</v>
@@ -6587,53 +6587,53 @@
         <v>5</v>
       </c>
       <c r="T47" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="U47" s="1" t="n">
         <v>4</v>
       </c>
       <c r="V47" s="1" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="W47" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X47" s="1" t="n">
         <v>17</v>
       </c>
       <c r="Y47" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z47" s="1" t="n">
         <v>9</v>
       </c>
       <c r="AA47" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AB47" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B48" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C48" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="D48" s="1" t="n">
         <v>6</v>
-      </c>
-      <c r="D48" s="1" t="n">
-        <v>5</v>
       </c>
       <c r="E48" s="1" t="n">
         <v>25</v>
       </c>
       <c r="F48" s="1" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="G48" s="1" t="n">
         <v>22</v>
@@ -6657,22 +6657,22 @@
         <v>18</v>
       </c>
       <c r="N48" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="O48" s="1" t="n">
         <v>26</v>
       </c>
       <c r="P48" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Q48" s="1" t="n">
         <v>23</v>
       </c>
       <c r="R48" s="1" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="S48" s="1" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T48" s="1" t="n">
         <v>21</v>
@@ -6681,50 +6681,50 @@
         <v>4</v>
       </c>
       <c r="V48" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="W48" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X48" s="1" t="n">
         <v>17</v>
       </c>
       <c r="Y48" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z48" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="Z48" s="1" t="n">
+      <c r="AA48" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="AB48" s="1" t="n">
         <v>10</v>
-      </c>
-      <c r="AA48" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="AB48" s="1" t="n">
-        <v>11</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B49" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D49" s="1" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E49" s="1" t="n">
         <v>25</v>
       </c>
       <c r="F49" s="1" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H49" s="1" t="n">
         <v>2</v>
@@ -6742,7 +6742,7 @@
         <v>16</v>
       </c>
       <c r="M49" s="1" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N49" s="1" t="n">
         <v>14</v>
@@ -6751,68 +6751,68 @@
         <v>26</v>
       </c>
       <c r="P49" s="1" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="Q49" s="1" t="n">
         <v>23</v>
       </c>
       <c r="R49" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="S49" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="T49" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="U49" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="V49" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="W49" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="X49" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y49" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="S49" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="T49" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="U49" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="V49" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="W49" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="X49" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="Y49" s="1" t="n">
-        <v>5</v>
-      </c>
       <c r="Z49" s="1" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AA49" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AB49" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B50" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D50" s="1" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E50" s="1" t="n">
         <v>25</v>
       </c>
       <c r="F50" s="1" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H50" s="1" t="n">
         <v>2</v>
@@ -6821,25 +6821,25 @@
         <v>3</v>
       </c>
       <c r="J50" s="1" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K50" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L50" s="1" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="M50" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N50" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O50" s="1" t="n">
         <v>26</v>
       </c>
       <c r="P50" s="1" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="Q50" s="1" t="n">
         <v>23</v>
@@ -6848,31 +6848,31 @@
         <v>9</v>
       </c>
       <c r="S50" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="T50" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="U50" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="T50" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="U50" s="1" t="n">
-        <v>7</v>
-      </c>
       <c r="V50" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="W50" s="1" t="n">
         <v>4</v>
       </c>
       <c r="X50" s="1" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Y50" s="1" t="n">
         <v>5</v>
       </c>
       <c r="Z50" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA50" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AB50" s="1" t="n">
         <v>10</v>
@@ -6881,23 +6881,23 @@
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B51" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D51" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F51" s="1" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G51" s="1" t="n">
         <v>20</v>
@@ -6909,13 +6909,13 @@
         <v>3</v>
       </c>
       <c r="J51" s="1" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="K51" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L51" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="M51" s="1" t="n">
         <v>18</v>
@@ -6924,10 +6924,10 @@
         <v>15</v>
       </c>
       <c r="O51" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P51" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Q51" s="1" t="n">
         <v>23</v>
@@ -6942,25 +6942,25 @@
         <v>24</v>
       </c>
       <c r="U51" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V51" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="W51" s="1" t="n">
         <v>4</v>
       </c>
       <c r="X51" s="1" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Y51" s="1" t="n">
         <v>5</v>
       </c>
       <c r="Z51" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA51" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AB51" s="1" t="n">
         <v>10</v>
@@ -6969,26 +6969,26 @@
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B52" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C52" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="D52" s="1" t="n">
         <v>16</v>
-      </c>
-      <c r="D52" s="1" t="n">
-        <v>13</v>
       </c>
       <c r="E52" s="1" t="n">
         <v>26</v>
       </c>
       <c r="F52" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="G52" s="1" t="n">
         <v>20</v>
-      </c>
-      <c r="G52" s="1" t="n">
-        <v>22</v>
       </c>
       <c r="H52" s="1" t="n">
         <v>2</v>
@@ -7009,13 +7009,13 @@
         <v>18</v>
       </c>
       <c r="N52" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="O52" s="1" t="n">
         <v>25</v>
       </c>
       <c r="P52" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Q52" s="1" t="n">
         <v>23</v>
@@ -7033,7 +7033,7 @@
         <v>8</v>
       </c>
       <c r="V52" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="W52" s="1" t="n">
         <v>4</v>
@@ -7048,7 +7048,7 @@
         <v>7</v>
       </c>
       <c r="AA52" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AB52" s="1" t="n">
         <v>10</v>
@@ -7057,7 +7057,7 @@
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B53" s="1" t="n">
@@ -7067,16 +7067,16 @@
         <v>16</v>
       </c>
       <c r="D53" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F53" s="1" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H53" s="1" t="n">
         <v>2</v>
@@ -7094,22 +7094,22 @@
         <v>11</v>
       </c>
       <c r="M53" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="N53" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="N53" s="1" t="n">
-        <v>15</v>
-      </c>
       <c r="O53" s="1" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P53" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="Q53" s="1" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="R53" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="S53" s="1" t="n">
         <v>6</v>
@@ -7121,13 +7121,13 @@
         <v>8</v>
       </c>
       <c r="V53" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="W53" s="1" t="n">
         <v>4</v>
       </c>
       <c r="X53" s="1" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="Y53" s="1" t="n">
         <v>5</v>
@@ -7136,71 +7136,71 @@
         <v>7</v>
       </c>
       <c r="AA53" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AB53" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B54" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D54" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F54" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="G54" s="1" t="n">
         <v>20</v>
-      </c>
-      <c r="G54" s="1" t="n">
-        <v>17</v>
       </c>
       <c r="H54" s="1" t="n">
         <v>2</v>
       </c>
       <c r="I54" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J54" s="1" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K54" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L54" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="M54" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N54" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="O54" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="P54" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="O54" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="P54" s="1" t="n">
-        <v>11</v>
-      </c>
       <c r="Q54" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R54" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="S54" s="1" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T54" s="1" t="n">
         <v>24</v>
@@ -7212,132 +7212,132 @@
         <v>13</v>
       </c>
       <c r="W54" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="X54" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y54" s="1" t="n">
         <v>5</v>
-      </c>
-      <c r="X54" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="Y54" s="1" t="n">
-        <v>6</v>
       </c>
       <c r="Z54" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AA54" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AB54" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B55" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D55" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E55" s="1" t="n">
         <v>26</v>
       </c>
       <c r="F55" s="1" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H55" s="1" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I55" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J55" s="1" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="K55" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L55" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M55" s="1" t="n">
         <v>18</v>
       </c>
       <c r="N55" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O55" s="1" t="n">
         <v>25</v>
       </c>
       <c r="P55" s="1" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="Q55" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="R55" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="S55" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T55" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="U55" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V55" s="1" t="n">
         <v>13</v>
       </c>
       <c r="W55" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X55" s="1" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="Y55" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z55" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AA55" s="1" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AB55" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B56" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D56" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E56" s="1" t="n">
         <v>26</v>
       </c>
       <c r="F56" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G56" s="1" t="n">
         <v>20</v>
@@ -7346,7 +7346,7 @@
         <v>6</v>
       </c>
       <c r="I56" s="1" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J56" s="1" t="n">
         <v>19</v>
@@ -7367,10 +7367,10 @@
         <v>25</v>
       </c>
       <c r="P56" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Q56" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R56" s="1" t="n">
         <v>10</v>
@@ -7379,53 +7379,53 @@
         <v>2</v>
       </c>
       <c r="T56" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="U56" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="V56" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="W56" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="X56" s="1" t="n">
         <v>24</v>
-      </c>
-      <c r="U56" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="V56" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="W56" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="X56" s="1" t="n">
-        <v>23</v>
       </c>
       <c r="Y56" s="1" t="n">
         <v>5</v>
       </c>
       <c r="Z56" s="1" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AA56" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AB56" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B57" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D57" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E57" s="1" t="n">
         <v>26</v>
       </c>
       <c r="F57" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G57" s="1" t="n">
         <v>20</v>
@@ -7434,25 +7434,25 @@
         <v>6</v>
       </c>
       <c r="I57" s="1" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J57" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K57" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L57" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M57" s="1" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N57" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O57" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="P57" s="1" t="n">
         <v>17</v>
@@ -7461,31 +7461,31 @@
         <v>22</v>
       </c>
       <c r="R57" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="S57" s="1" t="n">
         <v>2</v>
       </c>
       <c r="T57" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="U57" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="V57" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="W57" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="X57" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="U57" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="V57" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="W57" s="1" t="n">
+      <c r="Y57" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z57" s="1" t="n">
         <v>4</v>
-      </c>
-      <c r="X57" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="Y57" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z57" s="1" t="n">
-        <v>5</v>
       </c>
       <c r="AA57" s="1" t="n">
         <v>21</v>
@@ -7497,32 +7497,32 @@
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B58" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D58" s="1" t="n">
         <v>11</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F58" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G58" s="1" t="n">
         <v>20</v>
       </c>
       <c r="H58" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="I58" s="1" t="n">
         <v>3</v>
-      </c>
-      <c r="I58" s="1" t="n">
-        <v>12</v>
       </c>
       <c r="J58" s="1" t="n">
         <v>18</v>
@@ -7531,13 +7531,13 @@
         <v>1</v>
       </c>
       <c r="L58" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M58" s="1" t="n">
         <v>19</v>
       </c>
       <c r="N58" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O58" s="1" t="n">
         <v>24</v>
@@ -7549,28 +7549,28 @@
         <v>22</v>
       </c>
       <c r="R58" s="1" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="S58" s="1" t="n">
         <v>2</v>
       </c>
       <c r="T58" s="1" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="U58" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V58" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="W58" s="1" t="n">
         <v>4</v>
       </c>
       <c r="X58" s="1" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Y58" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z58" s="1" t="n">
         <v>5</v>
@@ -7579,77 +7579,77 @@
         <v>21</v>
       </c>
       <c r="AB58" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B59" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C59" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="D59" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="D59" s="1" t="n">
-        <v>10</v>
-      </c>
       <c r="E59" s="1" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F59" s="1" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G59" s="1" t="n">
         <v>20</v>
       </c>
       <c r="H59" s="1" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="I59" s="1" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="J59" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K59" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L59" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M59" s="1" t="n">
         <v>19</v>
       </c>
       <c r="N59" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O59" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P59" s="1" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Q59" s="1" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="R59" s="1" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="S59" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T59" s="1" t="n">
         <v>26</v>
       </c>
       <c r="U59" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="V59" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="W59" s="1" t="n">
         <v>4</v>
@@ -7658,7 +7658,7 @@
         <v>23</v>
       </c>
       <c r="Y59" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z59" s="1" t="n">
         <v>5</v>
@@ -7667,62 +7667,62 @@
         <v>21</v>
       </c>
       <c r="AB59" s="1" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B60" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D60" s="1" t="n">
         <v>10</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F60" s="1" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="G60" s="1" t="n">
         <v>20</v>
       </c>
       <c r="H60" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I60" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J60" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K60" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L60" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M60" s="1" t="n">
         <v>19</v>
       </c>
       <c r="N60" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O60" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="P60" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q60" s="1" t="n">
         <v>24</v>
-      </c>
-      <c r="P60" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q60" s="1" t="n">
-        <v>21</v>
       </c>
       <c r="R60" s="1" t="n">
         <v>3</v>
@@ -7731,10 +7731,10 @@
         <v>1</v>
       </c>
       <c r="T60" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="U60" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V60" s="1" t="n">
         <v>12</v>
@@ -7743,7 +7743,7 @@
         <v>4</v>
       </c>
       <c r="X60" s="1" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="Y60" s="1" t="n">
         <v>6</v>
@@ -7752,50 +7752,50 @@
         <v>5</v>
       </c>
       <c r="AA60" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AB60" s="1" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B61" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D61" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F61" s="1" t="n">
         <v>18</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H61" s="1" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="I61" s="1" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="J61" s="1" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="K61" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L61" s="1" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="M61" s="1" t="n">
         <v>19</v>
@@ -7804,37 +7804,37 @@
         <v>17</v>
       </c>
       <c r="O61" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P61" s="1" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="Q61" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R61" s="1" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="S61" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T61" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="U61" s="1" t="n">
         <v>7</v>
       </c>
       <c r="V61" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="W61" s="1" t="n">
         <v>4</v>
       </c>
       <c r="X61" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Y61" s="1" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Z61" s="1" t="n">
         <v>5</v>
@@ -7849,7 +7849,7 @@
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B62" s="1" t="n">
@@ -7859,10 +7859,10 @@
         <v>16</v>
       </c>
       <c r="D62" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F62" s="1" t="n">
         <v>18</v>
@@ -7871,19 +7871,19 @@
         <v>21</v>
       </c>
       <c r="H62" s="1" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="I62" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J62" s="1" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K62" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L62" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M62" s="1" t="n">
         <v>19</v>
@@ -7901,13 +7901,13 @@
         <v>20</v>
       </c>
       <c r="R62" s="1" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="S62" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T62" s="1" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="U62" s="1" t="n">
         <v>7</v>
@@ -7916,101 +7916,101 @@
         <v>15</v>
       </c>
       <c r="W62" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X62" s="1" t="n">
         <v>25</v>
       </c>
       <c r="Y62" s="1" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="Z62" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA62" s="1" t="n">
         <v>22</v>
       </c>
       <c r="AB62" s="1" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B63" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D63" s="1" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E63" s="1" t="n">
         <v>24</v>
       </c>
       <c r="F63" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G63" s="1" t="n">
         <v>21</v>
       </c>
       <c r="H63" s="1" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I63" s="1" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="J63" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K63" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L63" s="1" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="M63" s="1" t="n">
         <v>19</v>
       </c>
       <c r="N63" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O63" s="1" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="P63" s="1" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="Q63" s="1" t="n">
         <v>20</v>
       </c>
       <c r="R63" s="1" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="S63" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T63" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="U63" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V63" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="W63" s="1" t="n">
         <v>3</v>
       </c>
       <c r="X63" s="1" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Y63" s="1" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="Z63" s="1" t="n">
         <v>4</v>
@@ -8025,41 +8025,41 @@
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B64" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D64" s="1" t="n">
         <v>8</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F64" s="1" t="n">
         <v>16</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H64" s="1" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="I64" s="1" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="J64" s="1" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="K64" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L64" s="1" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="M64" s="1" t="n">
         <v>19</v>
@@ -8074,7 +8074,7 @@
         <v>12</v>
       </c>
       <c r="Q64" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="R64" s="1" t="n">
         <v>7</v>
@@ -8083,13 +8083,13 @@
         <v>1</v>
       </c>
       <c r="T64" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="U64" s="1" t="n">
         <v>6</v>
       </c>
       <c r="V64" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="W64" s="1" t="n">
         <v>3</v>
@@ -8098,7 +8098,7 @@
         <v>23</v>
       </c>
       <c r="Y64" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Z64" s="1" t="n">
         <v>4</v>
@@ -8113,68 +8113,68 @@
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B65" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D65" s="1" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E65" s="1" t="n">
         <v>25</v>
       </c>
       <c r="F65" s="1" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H65" s="1" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I65" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J65" s="1" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="K65" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L65" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="M65" s="1" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="N65" s="1" t="n">
         <v>18</v>
       </c>
       <c r="O65" s="1" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="P65" s="1" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="Q65" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R65" s="1" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="S65" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T65" s="1" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="U65" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V65" s="1" t="n">
         <v>14</v>
@@ -8183,195 +8183,195 @@
         <v>3</v>
       </c>
       <c r="X65" s="1" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="Y65" s="1" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Z65" s="1" t="n">
         <v>4</v>
       </c>
       <c r="AA65" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AB65" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B66" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D66" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E66" s="1" t="n">
         <v>25</v>
       </c>
       <c r="F66" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H66" s="1" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I66" s="1" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J66" s="1" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="K66" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L66" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M66" s="1" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="N66" s="1" t="n">
         <v>18</v>
       </c>
       <c r="O66" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P66" s="1" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="Q66" s="1" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="R66" s="1" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="S66" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T66" s="1" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="U66" s="1" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="V66" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="W66" s="1" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="X66" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y66" s="1" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="Z66" s="1" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="AA66" s="1" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AB66" s="1" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B67" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D67" s="1" t="n">
         <v>15</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F67" s="1" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H67" s="1" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="I67" s="1" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="J67" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K67" s="1" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L67" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="M67" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="M67" s="1" t="n">
-        <v>16</v>
-      </c>
       <c r="N67" s="1" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O67" s="1" t="n">
         <v>23</v>
       </c>
       <c r="P67" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q67" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="R67" s="1" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="S67" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T67" s="1" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="U67" s="1" t="n">
         <v>2</v>
       </c>
       <c r="V67" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="W67" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="X67" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y67" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="W67" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="X67" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="Y67" s="1" t="n">
-        <v>8</v>
-      </c>
       <c r="Z67" s="1" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AA67" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AB67" s="1" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/NSE_Sector_Monitor.xlsx
+++ b/NSE_Sector_Monitor.xlsx
@@ -568,22 +568,22 @@
         <v>0</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>14.97</v>
+        <v>15.03</v>
       </c>
       <c r="H2" s="1" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="I2" s="1" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="J2" s="1" t="n">
-        <v>5.19</v>
+        <v>4.76</v>
       </c>
       <c r="K2" s="1" t="n">
-        <v>21</v>
+        <v>21.44</v>
       </c>
       <c r="L2" s="1" t="inlineStr">
         <is>
@@ -633,22 +633,22 @@
         <v>1</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>88.59999999999999</v>
+        <v>88.8</v>
       </c>
       <c r="H3" s="1" t="n">
-        <v>0.29</v>
+        <v>0.03</v>
       </c>
       <c r="I3" s="1" t="n">
-        <v>-0.93</v>
+        <v>-0.83</v>
       </c>
       <c r="J3" s="1" t="n">
-        <v>0.85</v>
+        <v>0.13</v>
       </c>
       <c r="K3" s="1" t="n">
-        <v>10.71</v>
+        <v>10.37</v>
       </c>
       <c r="L3" s="1" t="inlineStr">
         <is>
@@ -656,11 +656,11 @@
         </is>
       </c>
       <c r="M3" s="1" t="n">
-        <v>-7.92</v>
+        <v>-8.279999999999999</v>
       </c>
       <c r="N3" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O3" s="1" t="inlineStr">
@@ -698,22 +698,22 @@
         <v>4</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>27.68</v>
+        <v>27.89</v>
       </c>
       <c r="H4" s="1" t="n">
-        <v>-0.29</v>
+        <v>0.76</v>
       </c>
       <c r="I4" s="1" t="n">
-        <v>1.32</v>
+        <v>1.67</v>
       </c>
       <c r="J4" s="1" t="n">
-        <v>5.47</v>
+        <v>5.64</v>
       </c>
       <c r="K4" s="1" t="n">
-        <v>8.77</v>
+        <v>9.34</v>
       </c>
       <c r="L4" s="1" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
         </is>
       </c>
       <c r="M4" s="1" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N4" s="1" t="inlineStr">
         <is>
@@ -754,7 +754,7 @@
         <v>4</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>-2</v>
@@ -763,22 +763,22 @@
         <v>-2</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>86.08</v>
+        <v>87.23999999999999</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>0.95</v>
+        <v>1.86</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="J5" s="1" t="n">
-        <v>-3</v>
+        <v>-2.13</v>
       </c>
       <c r="K5" s="1" t="n">
-        <v>7.92</v>
+        <v>7.13</v>
       </c>
       <c r="L5" s="1" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="M5" s="1" t="n">
-        <v>-7.37</v>
+        <v>-6.7</v>
       </c>
       <c r="N5" s="1" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
       </c>
       <c r="O5" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P5" s="1" t="inlineStr">
@@ -812,103 +812,103 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
         <v>5</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="D6" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="E6" s="2" t="n">
-        <v>4</v>
-      </c>
       <c r="F6" s="2" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>31.77</v>
+        <v>17.36</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>-0.53</v>
+        <v>0.17</v>
       </c>
       <c r="I6" s="1" t="n">
-        <v>-4.69</v>
+        <v>1.7</v>
       </c>
       <c r="J6" s="1" t="n">
-        <v>-3.39</v>
+        <v>5.19</v>
       </c>
       <c r="K6" s="1" t="n">
-        <v>6.98</v>
+        <v>6.93</v>
       </c>
       <c r="L6" s="1" t="inlineStr">
         <is>
-          <t>Down</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="M6" s="1" t="n">
-        <v>-25.18</v>
+        <v>-0.15</v>
       </c>
       <c r="N6" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O6" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P6" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Q6" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Metal</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
         <v>6</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>-2</v>
+        <v>4</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>17.24</v>
+        <v>13.34</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>0.58</v>
+        <v>2.22</v>
       </c>
       <c r="I7" s="1" t="n">
-        <v>0.95</v>
+        <v>1.99</v>
       </c>
       <c r="J7" s="1" t="n">
-        <v>5.47</v>
+        <v>2.49</v>
       </c>
       <c r="K7" s="1" t="n">
-        <v>6.45</v>
+        <v>6.17</v>
       </c>
       <c r="L7" s="1" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         </is>
       </c>
       <c r="M7" s="1" t="n">
-        <v>0</v>
+        <v>-4.12</v>
       </c>
       <c r="N7" s="1" t="inlineStr">
         <is>
@@ -949,7 +949,7 @@
         <v>7</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>-1</v>
@@ -958,22 +958,22 @@
         <v>-3</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>280.12</v>
+        <v>280.54</v>
       </c>
       <c r="H8" s="1" t="n">
-        <v>-0.92</v>
+        <v>-0.25</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>-0.75</v>
+        <v>-1.34</v>
       </c>
       <c r="J8" s="1" t="n">
-        <v>-3.65</v>
+        <v>-4.37</v>
       </c>
       <c r="K8" s="1" t="n">
-        <v>3.61</v>
+        <v>4.07</v>
       </c>
       <c r="L8" s="1" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         </is>
       </c>
       <c r="M8" s="1" t="n">
-        <v>-5.21</v>
+        <v>-5.66</v>
       </c>
       <c r="N8" s="1" t="inlineStr">
         <is>
@@ -1007,46 +1007,46 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>Metal</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
         <v>8</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>7</v>
+        <v>-1</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>13.05</v>
+        <v>31.47</v>
       </c>
       <c r="H9" s="1" t="n">
-        <v>-0.23</v>
+        <v>-2.02</v>
       </c>
       <c r="I9" s="1" t="n">
-        <v>0.77</v>
+        <v>-4.28</v>
       </c>
       <c r="J9" s="1" t="n">
-        <v>0.01</v>
+        <v>-4.49</v>
       </c>
       <c r="K9" s="1" t="n">
-        <v>3.41</v>
+        <v>3.67</v>
       </c>
       <c r="L9" s="1" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Down</t>
         </is>
       </c>
       <c r="M9" s="1" t="n">
-        <v>-5.62</v>
+        <v>-26.34</v>
       </c>
       <c r="N9" s="1" t="inlineStr">
         <is>
@@ -1065,7 +1065,7 @@
       </c>
       <c r="Q9" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1079,7 +1079,7 @@
         <v>9</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>1</v>
@@ -1088,22 +1088,22 @@
         <v>-4</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>31.41</v>
+        <v>31.5</v>
       </c>
       <c r="H10" s="1" t="n">
-        <v>-1.66</v>
+        <v>-0.91</v>
       </c>
       <c r="I10" s="1" t="n">
-        <v>-1.61</v>
+        <v>-0.84</v>
       </c>
       <c r="J10" s="1" t="n">
-        <v>-2.85</v>
+        <v>-2.96</v>
       </c>
       <c r="K10" s="1" t="n">
-        <v>2.02</v>
+        <v>2.56</v>
       </c>
       <c r="L10" s="1" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="M10" s="1" t="n">
-        <v>-5</v>
+        <v>-5.31</v>
       </c>
       <c r="N10" s="1" t="inlineStr">
         <is>
@@ -1137,111 +1137,111 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>Consumption</t>
+          <t>Manufacturing</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
         <v>10</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E11" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="F11" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>128.23</v>
+        <v>163.01</v>
       </c>
       <c r="H11" s="1" t="n">
-        <v>-0.21</v>
+        <v>0.84</v>
       </c>
       <c r="I11" s="1" t="n">
-        <v>0.01</v>
+        <v>0.47</v>
       </c>
       <c r="J11" s="1" t="n">
-        <v>-0.95</v>
+        <v>-0.19</v>
       </c>
       <c r="K11" s="1" t="n">
-        <v>2.01</v>
+        <v>1.98</v>
       </c>
       <c r="L11" s="1" t="inlineStr">
         <is>
-          <t>Down</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="M11" s="1" t="n">
-        <v>-5.39</v>
+        <v>-1.27</v>
       </c>
       <c r="N11" s="1" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O11" s="1" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="O11" s="1" t="inlineStr">
+      <c r="P11" s="1" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P11" s="1" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="Q11" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Tourism</t>
+          <t>Consumption</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
         <v>11</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="D12" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E12" s="2" t="n">
         <v>-3</v>
       </c>
-      <c r="E12" s="2" t="n">
-        <v>-5</v>
-      </c>
       <c r="F12" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>78.52</v>
+        <v>128.81</v>
       </c>
       <c r="H12" s="1" t="n">
-        <v>0.73</v>
+        <v>0.45</v>
       </c>
       <c r="I12" s="1" t="n">
-        <v>2.87</v>
+        <v>-0.43</v>
       </c>
       <c r="J12" s="1" t="n">
-        <v>2.09</v>
+        <v>-1.26</v>
       </c>
       <c r="K12" s="1" t="n">
-        <v>0.82</v>
+        <v>1.69</v>
       </c>
       <c r="L12" s="1" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Down</t>
         </is>
       </c>
       <c r="M12" s="1" t="n">
-        <v>-12.62</v>
+        <v>-5.54</v>
       </c>
       <c r="N12" s="1" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
       </c>
       <c r="O12" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P12" s="1" t="inlineStr">
@@ -1260,14 +1260,14 @@
       </c>
       <c r="Q12" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>Manufacturing</t>
+          <t>Fin Services</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
@@ -1277,40 +1277,40 @@
         <v>1</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>161.65</v>
+        <v>32.37</v>
       </c>
       <c r="H13" s="1" t="n">
-        <v>-0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I13" s="1" t="n">
-        <v>0.27</v>
+        <v>0.6</v>
       </c>
       <c r="J13" s="1" t="n">
-        <v>-0.71</v>
+        <v>-0.58</v>
       </c>
       <c r="K13" s="1" t="n">
-        <v>0.8</v>
+        <v>1.11</v>
       </c>
       <c r="L13" s="1" t="inlineStr">
         <is>
-          <t>Down</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="M13" s="1" t="n">
-        <v>-1.49</v>
+        <v>-1.36</v>
       </c>
       <c r="N13" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O13" s="1" t="inlineStr">
@@ -1332,38 +1332,38 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Fin Services</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
         <v>13</v>
       </c>
       <c r="C14" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D14" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D14" s="2" t="n">
-        <v>-4</v>
-      </c>
       <c r="E14" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>3</v>
+        <v>-8</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>32</v>
+        <v>29.6</v>
       </c>
       <c r="H14" s="1" t="n">
-        <v>-0.87</v>
+        <v>0.92</v>
       </c>
       <c r="I14" s="1" t="n">
-        <v>-0.27</v>
+        <v>0.38</v>
       </c>
       <c r="J14" s="1" t="n">
-        <v>-1.09</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="K14" s="1" t="n">
-        <v>0.57</v>
+        <v>0.7</v>
       </c>
       <c r="L14" s="1" t="inlineStr">
         <is>
@@ -1371,72 +1371,72 @@
         </is>
       </c>
       <c r="M14" s="1" t="n">
-        <v>-1.89</v>
+        <v>0</v>
       </c>
       <c r="N14" s="1" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O14" s="1" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="O14" s="1" t="inlineStr">
+      <c r="P14" s="1" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P14" s="1" t="inlineStr">
+      <c r="Q14" s="1" t="inlineStr">
         <is>
           <t>No</t>
-        </is>
-      </c>
-      <c r="Q14" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Defence</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
         <v>14</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>3</v>
+        <v>-9</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>3</v>
+        <v>-5</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>12</v>
+        <v>-13</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>30.2</v>
+        <v>103.76</v>
       </c>
       <c r="H15" s="1" t="n">
-        <v>-0.49</v>
+        <v>0.47</v>
       </c>
       <c r="I15" s="1" t="n">
-        <v>-0.73</v>
+        <v>1.41</v>
       </c>
       <c r="J15" s="1" t="n">
-        <v>0.16</v>
+        <v>-0.38</v>
       </c>
       <c r="K15" s="1" t="n">
-        <v>0.2</v>
+        <v>0.57</v>
       </c>
       <c r="L15" s="1" t="inlineStr">
         <is>
-          <t>Down</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="M15" s="1" t="n">
-        <v>0</v>
+        <v>-4.73</v>
       </c>
       <c r="N15" s="1" t="inlineStr">
         <is>
@@ -1455,57 +1455,57 @@
       </c>
       <c r="Q15" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Private Bank</t>
+          <t>Services</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
         <v>15</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>3</v>
+        <v>-3</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E16" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F16" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="G16" s="1" t="n">
+        <v>30.38</v>
+      </c>
+      <c r="H16" s="1" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="I16" s="1" t="n">
+        <v>-0.88</v>
+      </c>
+      <c r="J16" s="1" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="K16" s="1" t="n">
+        <v>-0.63</v>
+      </c>
+      <c r="L16" s="1" t="inlineStr">
+        <is>
+          <t>Down</t>
+        </is>
+      </c>
+      <c r="M16" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="G16" s="1" t="n">
-        <v>27.88</v>
-      </c>
-      <c r="H16" s="1" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="I16" s="1" t="n">
-        <v>-0.96</v>
-      </c>
-      <c r="J16" s="1" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="K16" s="1" t="n">
-        <v>-0.55</v>
-      </c>
-      <c r="L16" s="1" t="inlineStr">
-        <is>
-          <t>Up</t>
-        </is>
-      </c>
-      <c r="M16" s="1" t="n">
-        <v>-3.52</v>
-      </c>
       <c r="N16" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O16" s="1" t="inlineStr">
@@ -1527,38 +1527,38 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>Bank</t>
+          <t>Tourism</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
         <v>16</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>-4</v>
+        <v>-10</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>3</v>
+        <v>-12</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>583.52</v>
+        <v>78.33</v>
       </c>
       <c r="H17" s="1" t="n">
-        <v>-0.01</v>
+        <v>0.41</v>
       </c>
       <c r="I17" s="1" t="n">
-        <v>-0.68</v>
+        <v>2.58</v>
       </c>
       <c r="J17" s="1" t="n">
-        <v>1.21</v>
+        <v>1</v>
       </c>
       <c r="K17" s="1" t="n">
-        <v>-0.58</v>
+        <v>-0.74</v>
       </c>
       <c r="L17" s="1" t="inlineStr">
         <is>
@@ -1566,68 +1566,68 @@
         </is>
       </c>
       <c r="M17" s="1" t="n">
-        <v>-5.38</v>
+        <v>-12.86</v>
       </c>
       <c r="N17" s="1" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O17" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P17" s="1" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="O17" s="1" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="P17" s="1" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="Q17" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Capital Market</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
         <v>17</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>-5</v>
+        <v>5</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-15</v>
+        <v>-14</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>29.27</v>
+        <v>53.88</v>
       </c>
       <c r="H18" s="1" t="n">
-        <v>-0.1</v>
+        <v>1.79</v>
       </c>
       <c r="I18" s="1" t="n">
-        <v>-1.29</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="J18" s="1" t="n">
-        <v>0.87</v>
+        <v>0.31</v>
       </c>
       <c r="K18" s="1" t="n">
-        <v>-0.91</v>
+        <v>-0.9</v>
       </c>
       <c r="L18" s="1" t="inlineStr">
         <is>
-          <t>Down</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="M18" s="1" t="n">
@@ -1635,17 +1635,17 @@
       </c>
       <c r="N18" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O18" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P18" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Q18" s="1" t="inlineStr">
@@ -1657,46 +1657,46 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>Defence</t>
+          <t>MNC</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
         <v>18</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>-10</v>
+        <v>2</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>-13</v>
+        <v>2</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>-10</v>
+        <v>-3</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>-17</v>
+        <v>-7</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>103.81</v>
+        <v>32.49</v>
       </c>
       <c r="H19" s="1" t="n">
-        <v>0.51</v>
+        <v>-0.28</v>
       </c>
       <c r="I19" s="1" t="n">
-        <v>1.6</v>
+        <v>-0.53</v>
       </c>
       <c r="J19" s="1" t="n">
-        <v>0.04</v>
+        <v>-2.45</v>
       </c>
       <c r="K19" s="1" t="n">
-        <v>-0.99</v>
+        <v>-1.11</v>
       </c>
       <c r="L19" s="1" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Down</t>
         </is>
       </c>
       <c r="M19" s="1" t="n">
-        <v>-4.09</v>
+        <v>-4.95</v>
       </c>
       <c r="N19" s="1" t="inlineStr">
         <is>
@@ -1729,31 +1729,31 @@
         <v>19</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E20" s="2" t="n">
         <v>3</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>11.12</v>
+        <v>11.15</v>
       </c>
       <c r="H20" s="1" t="n">
-        <v>-0.18</v>
+        <v>-0.36</v>
       </c>
       <c r="I20" s="1" t="n">
-        <v>-0.31</v>
+        <v>-0.96</v>
       </c>
       <c r="J20" s="1" t="n">
-        <v>1.24</v>
+        <v>1.14</v>
       </c>
       <c r="K20" s="1" t="n">
-        <v>-1.18</v>
+        <v>-1.38</v>
       </c>
       <c r="L20" s="1" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
         </is>
       </c>
       <c r="M20" s="1" t="n">
-        <v>-9.02</v>
+        <v>-9.33</v>
       </c>
       <c r="N20" s="1" t="inlineStr">
         <is>
@@ -1787,50 +1787,50 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>MNC</t>
+          <t>Bank</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
         <v>20</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>-1</v>
+        <v>-9</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>-6</v>
+        <v>-8</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>-14</v>
+        <v>-4</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>32.28</v>
+        <v>585.5700000000001</v>
       </c>
       <c r="H21" s="1" t="n">
-        <v>-1.25</v>
+        <v>0.05</v>
       </c>
       <c r="I21" s="1" t="n">
-        <v>-1.08</v>
+        <v>-1.27</v>
       </c>
       <c r="J21" s="1" t="n">
-        <v>-2.67</v>
+        <v>1.31</v>
       </c>
       <c r="K21" s="1" t="n">
-        <v>-2.11</v>
+        <v>-1.96</v>
       </c>
       <c r="L21" s="1" t="inlineStr">
         <is>
-          <t>Down</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="M21" s="1" t="n">
-        <v>-4.98</v>
+        <v>-5.63</v>
       </c>
       <c r="N21" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O21" s="1" t="inlineStr">
@@ -1852,38 +1852,38 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>Commodities</t>
+          <t>Private Bank</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
         <v>21</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>4</v>
+        <v>-4</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>3</v>
+        <v>-4</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>3</v>
+        <v>-4</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>-4</v>
+        <v>-9</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>97.67</v>
+        <v>27.95</v>
       </c>
       <c r="H22" s="1" t="n">
-        <v>0.18</v>
+        <v>0.29</v>
       </c>
       <c r="I22" s="1" t="n">
-        <v>0.08</v>
+        <v>-1.23</v>
       </c>
       <c r="J22" s="1" t="n">
-        <v>0.57</v>
+        <v>2.88</v>
       </c>
       <c r="K22" s="1" t="n">
-        <v>-2.71</v>
+        <v>-2.31</v>
       </c>
       <c r="L22" s="1" t="inlineStr">
         <is>
@@ -1891,11 +1891,11 @@
         </is>
       </c>
       <c r="M22" s="1" t="n">
-        <v>-8.470000000000001</v>
+        <v>-3.87</v>
       </c>
       <c r="N22" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O22" s="1" t="inlineStr">
@@ -1917,50 +1917,50 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>Capital Market</t>
+          <t>Commodities</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
         <v>22</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>-3</v>
+        <v>2</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>-13</v>
+        <v>-2</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>52.94</v>
+        <v>98.01000000000001</v>
       </c>
       <c r="H23" s="1" t="n">
-        <v>-1.19</v>
+        <v>0.35</v>
       </c>
       <c r="I23" s="1" t="n">
-        <v>-1.22</v>
+        <v>-0.28</v>
       </c>
       <c r="J23" s="1" t="n">
-        <v>-0.53</v>
+        <v>0.91</v>
       </c>
       <c r="K23" s="1" t="n">
-        <v>-3.22</v>
+        <v>-2.46</v>
       </c>
       <c r="L23" s="1" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Down</t>
         </is>
       </c>
       <c r="M23" s="1" t="n">
-        <v>0</v>
+        <v>-8.720000000000001</v>
       </c>
       <c r="N23" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O23" s="1" t="inlineStr">
@@ -1989,31 +1989,31 @@
         <v>23</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D24" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>-8</v>
+        <v>-10</v>
       </c>
       <c r="F24" s="2" t="n">
         <v>2</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>92.15000000000001</v>
+        <v>93.19</v>
       </c>
       <c r="H24" s="1" t="n">
-        <v>-0.54</v>
+        <v>0.46</v>
       </c>
       <c r="I24" s="1" t="n">
-        <v>-0.42</v>
+        <v>-0.71</v>
       </c>
       <c r="J24" s="1" t="n">
-        <v>-0.08</v>
+        <v>-0.03</v>
       </c>
       <c r="K24" s="1" t="n">
-        <v>-3.28</v>
+        <v>-2.55</v>
       </c>
       <c r="L24" s="1" t="inlineStr">
         <is>
@@ -2021,11 +2021,11 @@
         </is>
       </c>
       <c r="M24" s="1" t="n">
-        <v>-14.2</v>
+        <v>-13.77</v>
       </c>
       <c r="N24" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O24" s="1" t="inlineStr">
@@ -2047,38 +2047,38 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>PSE</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
         <v>24</v>
       </c>
       <c r="C25" s="2" t="n">
+        <v>-3</v>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D25" s="2" t="n">
-        <v>-3</v>
-      </c>
-      <c r="E25" s="2" t="n">
-        <v>-3</v>
-      </c>
-      <c r="F25" s="2" t="n">
-        <v>-10</v>
-      </c>
       <c r="G25" s="1" t="n">
-        <v>93.09</v>
+        <v>10.02</v>
       </c>
       <c r="H25" s="1" t="n">
-        <v>-0.08</v>
+        <v>-0.3</v>
       </c>
       <c r="I25" s="1" t="n">
-        <v>-0.12</v>
+        <v>-1.56</v>
       </c>
       <c r="J25" s="1" t="n">
-        <v>0.07000000000000001</v>
+        <v>1.63</v>
       </c>
       <c r="K25" s="1" t="n">
-        <v>-3.6</v>
+        <v>-3.22</v>
       </c>
       <c r="L25" s="1" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         </is>
       </c>
       <c r="M25" s="1" t="n">
-        <v>-4.7</v>
+        <v>-11.04</v>
       </c>
       <c r="N25" s="1" t="inlineStr">
         <is>
@@ -2112,50 +2112,50 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>PSE</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
         <v>25</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>2</v>
+        <v>-5</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>-2</v>
+        <v>-8</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>10</v>
+        <v>93.36</v>
       </c>
       <c r="H26" s="1" t="n">
-        <v>-0.5</v>
+        <v>0.29</v>
       </c>
       <c r="I26" s="1" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.16</v>
       </c>
       <c r="J26" s="1" t="n">
-        <v>1.52</v>
+        <v>-0.64</v>
       </c>
       <c r="K26" s="1" t="n">
-        <v>-3.95</v>
+        <v>-3.45</v>
       </c>
       <c r="L26" s="1" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Down</t>
         </is>
       </c>
       <c r="M26" s="1" t="n">
-        <v>-10.67</v>
+        <v>-5.01</v>
       </c>
       <c r="N26" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O26" s="1" t="inlineStr">
@@ -2187,28 +2187,28 @@
         <v>0</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E27" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>-23</v>
+        <v>-17</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>37.91</v>
+        <v>38.02</v>
       </c>
       <c r="H27" s="1" t="n">
-        <v>-0.24</v>
+        <v>0.08</v>
       </c>
       <c r="I27" s="1" t="n">
         <v>-0.26</v>
       </c>
       <c r="J27" s="1" t="n">
-        <v>1.88</v>
+        <v>2.12</v>
       </c>
       <c r="K27" s="1" t="n">
-        <v>-5.01</v>
+        <v>-4.06</v>
       </c>
       <c r="L27" s="1" t="inlineStr">
         <is>
@@ -2220,7 +2220,7 @@
       </c>
       <c r="N27" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O27" s="1" t="inlineStr">
@@ -2255,25 +2255,25 @@
         <v>0</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>49.19</v>
+        <v>49.71</v>
       </c>
       <c r="H28" s="1" t="n">
-        <v>-0.83</v>
+        <v>1.06</v>
       </c>
       <c r="I28" s="1" t="n">
-        <v>0.03</v>
+        <v>-0.62</v>
       </c>
       <c r="J28" s="1" t="n">
-        <v>-0.51</v>
+        <v>0.01</v>
       </c>
       <c r="K28" s="1" t="n">
-        <v>-5.47</v>
+        <v>-4.69</v>
       </c>
       <c r="L28" s="1" t="inlineStr">
         <is>
@@ -2281,16 +2281,16 @@
         </is>
       </c>
       <c r="M28" s="1" t="n">
-        <v>-16.45</v>
+        <v>-16.08</v>
       </c>
       <c r="N28" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O28" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P28" s="1" t="inlineStr">
@@ -2569,17 +2569,17 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E2" s="1" t="n">
         <v>23</v>
@@ -2594,49 +2594,49 @@
         <v>3</v>
       </c>
       <c r="I2" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="J2" s="1" t="n">
         <v>6</v>
-      </c>
-      <c r="J2" s="1" t="n">
-        <v>8</v>
       </c>
       <c r="K2" s="1" t="n">
         <v>4</v>
       </c>
       <c r="L2" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M2" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="N2" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="O2" s="1" t="n">
         <v>24</v>
-      </c>
-      <c r="N2" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="O2" s="1" t="n">
-        <v>25</v>
       </c>
       <c r="P2" s="1" t="n">
         <v>26</v>
       </c>
       <c r="Q2" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="R2" s="1" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="S2" s="1" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="T2" s="1" t="n">
         <v>19</v>
       </c>
       <c r="U2" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="V2" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="W2" s="1" t="n">
         <v>17</v>
-      </c>
-      <c r="V2" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="W2" s="1" t="n">
-        <v>22</v>
       </c>
       <c r="X2" s="1" t="n">
         <v>2</v>
@@ -2645,10 +2645,10 @@
         <v>1</v>
       </c>
       <c r="Z2" s="1" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="AA2" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AB2" s="1" t="n">
         <v>9</v>
@@ -2657,35 +2657,35 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C3" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="D3" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="D3" s="1" t="n">
-        <v>16</v>
-      </c>
       <c r="E3" s="1" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F3" s="1" t="n">
         <v>7</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H3" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I3" s="1" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J3" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K3" s="1" t="n">
         <v>5</v>
@@ -2694,19 +2694,19 @@
         <v>11</v>
       </c>
       <c r="M3" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="N3" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="O3" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="P3" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q3" s="1" t="n">
         <v>22</v>
-      </c>
-      <c r="N3" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="O3" s="1" t="n">
-        <v>23</v>
-      </c>
-      <c r="P3" s="1" t="n">
-        <v>27</v>
-      </c>
-      <c r="Q3" s="1" t="n">
-        <v>24</v>
       </c>
       <c r="R3" s="1" t="n">
         <v>19</v>
@@ -2715,19 +2715,19 @@
         <v>20</v>
       </c>
       <c r="T3" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="U3" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="U3" s="1" t="n">
-        <v>15</v>
-      </c>
       <c r="V3" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="W3" s="1" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="X3" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y3" s="1" t="n">
         <v>1</v>
@@ -2736,35 +2736,35 @@
         <v>14</v>
       </c>
       <c r="AA3" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AB3" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
         <v>6</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>7</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H4" s="1" t="n">
         <v>2</v>
@@ -2773,46 +2773,46 @@
         <v>4</v>
       </c>
       <c r="J4" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K4" s="1" t="n">
         <v>5</v>
       </c>
       <c r="L4" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="M4" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="N4" s="1" t="n">
         <v>9</v>
-      </c>
-      <c r="M4" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="N4" s="1" t="n">
-        <v>13</v>
       </c>
       <c r="O4" s="1" t="n">
         <v>22</v>
       </c>
       <c r="P4" s="1" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Q4" s="1" t="n">
         <v>23</v>
       </c>
       <c r="R4" s="1" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="S4" s="1" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="T4" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="U4" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="U4" s="1" t="n">
-        <v>15</v>
-      </c>
       <c r="V4" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="W4" s="1" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="X4" s="1" t="n">
         <v>3</v>
@@ -2821,10 +2821,10 @@
         <v>1</v>
       </c>
       <c r="Z4" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AA4" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AB4" s="1" t="n">
         <v>8</v>
@@ -2833,20 +2833,20 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
         <v>6</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F5" s="1" t="n">
         <v>7</v>
@@ -2861,43 +2861,43 @@
         <v>4</v>
       </c>
       <c r="J5" s="1" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K5" s="1" t="n">
         <v>5</v>
       </c>
       <c r="L5" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M5" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N5" s="1" t="n">
         <v>13</v>
       </c>
       <c r="O5" s="1" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="P5" s="1" t="n">
         <v>26</v>
       </c>
       <c r="Q5" s="1" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="R5" s="1" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="S5" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="T5" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="U5" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="T5" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="U5" s="1" t="n">
-        <v>18</v>
-      </c>
       <c r="V5" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="W5" s="1" t="n">
         <v>21</v>
@@ -2912,7 +2912,7 @@
         <v>12</v>
       </c>
       <c r="AA5" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AB5" s="1" t="n">
         <v>8</v>
@@ -2921,23 +2921,23 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E6" s="1" t="n">
         <v>24</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G6" s="1" t="n">
         <v>27</v>
@@ -2949,46 +2949,46 @@
         <v>4</v>
       </c>
       <c r="J6" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K6" s="1" t="n">
         <v>5</v>
       </c>
       <c r="L6" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="M6" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="N6" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="M6" s="1" t="n">
+      <c r="O6" s="1" t="n">
         <v>25</v>
-      </c>
-      <c r="N6" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="O6" s="1" t="n">
-        <v>21</v>
       </c>
       <c r="P6" s="1" t="n">
         <v>26</v>
       </c>
       <c r="Q6" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R6" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="S6" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="T6" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="S6" s="1" t="n">
+      <c r="U6" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="T6" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="U6" s="1" t="n">
-        <v>16</v>
-      </c>
       <c r="V6" s="1" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="W6" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="X6" s="1" t="n">
         <v>3</v>
@@ -2997,10 +2997,10 @@
         <v>1</v>
       </c>
       <c r="Z6" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AA6" s="1" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AB6" s="1" t="n">
         <v>8</v>
@@ -3009,23 +3009,23 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G7" s="1" t="n">
         <v>27</v>
@@ -3037,19 +3037,19 @@
         <v>4</v>
       </c>
       <c r="J7" s="1" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="K7" s="1" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M7" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="N7" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O7" s="1" t="n">
         <v>21</v>
@@ -3058,22 +3058,22 @@
         <v>26</v>
       </c>
       <c r="Q7" s="1" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="R7" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="S7" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="T7" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="S7" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="T7" s="1" t="n">
-        <v>20</v>
-      </c>
       <c r="U7" s="1" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="V7" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="W7" s="1" t="n">
         <v>22</v>
@@ -3085,23 +3085,23 @@
         <v>1</v>
       </c>
       <c r="Z7" s="1" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AA7" s="1" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="AB7" s="1" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C8" s="1" t="n">
         <v>16</v>
@@ -3110,7 +3110,7 @@
         <v>18</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>9</v>
@@ -3122,22 +3122,22 @@
         <v>2</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J8" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="K8" s="1" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="M8" s="1" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="N8" s="1" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="O8" s="1" t="n">
         <v>21</v>
@@ -3149,22 +3149,22 @@
         <v>25</v>
       </c>
       <c r="R8" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="S8" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="T8" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="S8" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="T8" s="1" t="n">
-        <v>19</v>
-      </c>
       <c r="U8" s="1" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="V8" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="W8" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="X8" s="1" t="n">
         <v>3</v>
@@ -3173,62 +3173,62 @@
         <v>1</v>
       </c>
       <c r="Z8" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AA8" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AB8" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E9" s="1" t="n">
         <v>24</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G9" s="1" t="n">
         <v>27</v>
       </c>
       <c r="H9" s="1" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I9" s="1" t="n">
         <v>6</v>
       </c>
       <c r="J9" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K9" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L9" s="1" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="M9" s="1" t="n">
         <v>22</v>
       </c>
       <c r="N9" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O9" s="1" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="P9" s="1" t="n">
         <v>26</v>
@@ -3237,86 +3237,86 @@
         <v>25</v>
       </c>
       <c r="R9" s="1" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="S9" s="1" t="n">
         <v>5</v>
       </c>
       <c r="T9" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="U9" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="V9" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="V9" s="1" t="n">
-        <v>13</v>
-      </c>
       <c r="W9" s="1" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="X9" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y9" s="1" t="n">
         <v>1</v>
       </c>
       <c r="Z9" s="1" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AA9" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AB9" s="1" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D10" s="1" t="n">
         <v>21</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G10" s="1" t="n">
         <v>27</v>
       </c>
       <c r="H10" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I10" s="1" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J10" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K10" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L10" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M10" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N10" s="1" t="n">
         <v>12</v>
       </c>
       <c r="O10" s="1" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="P10" s="1" t="n">
         <v>26</v>
@@ -3325,110 +3325,110 @@
         <v>25</v>
       </c>
       <c r="R10" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="S10" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T10" s="1" t="n">
         <v>20</v>
       </c>
       <c r="U10" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="V10" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="V10" s="1" t="n">
-        <v>11</v>
-      </c>
       <c r="W10" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="X10" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y10" s="1" t="n">
         <v>1</v>
       </c>
       <c r="Z10" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA10" s="1" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AB10" s="1" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="C11" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="C11" s="1" t="n">
-        <v>16</v>
-      </c>
       <c r="D11" s="1" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G11" s="1" t="n">
         <v>27</v>
       </c>
       <c r="H11" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I11" s="1" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J11" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K11" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M11" s="1" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N11" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="O11" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="P11" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q11" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="R11" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="S11" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="T11" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="U11" s="1" t="n">
         <v>13</v>
-      </c>
-      <c r="O11" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="P11" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="Q11" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="R11" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="S11" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="T11" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="U11" s="1" t="n">
-        <v>14</v>
       </c>
       <c r="V11" s="1" t="n">
         <v>11</v>
       </c>
       <c r="W11" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="X11" s="1" t="n">
         <v>3</v>
@@ -3437,29 +3437,29 @@
         <v>1</v>
       </c>
       <c r="Z11" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA11" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="AB11" s="1" t="n">
         <v>9</v>
-      </c>
-      <c r="AA11" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="AB11" s="1" t="n">
-        <v>10</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="C12" s="1" t="n">
         <v>16</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E12" s="1" t="n">
         <v>23</v>
@@ -3477,46 +3477,46 @@
         <v>7</v>
       </c>
       <c r="J12" s="1" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="K12" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M12" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N12" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O12" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="P12" s="1" t="n">
         <v>25</v>
-      </c>
-      <c r="P12" s="1" t="n">
-        <v>26</v>
       </c>
       <c r="Q12" s="1" t="n">
         <v>24</v>
       </c>
       <c r="R12" s="1" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="S12" s="1" t="n">
         <v>5</v>
       </c>
       <c r="T12" s="1" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="U12" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="V12" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="W12" s="1" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="X12" s="1" t="n">
         <v>3</v>
@@ -3525,10 +3525,10 @@
         <v>1</v>
       </c>
       <c r="Z12" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA12" s="1" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AB12" s="1" t="n">
         <v>10</v>
@@ -3537,59 +3537,59 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F13" s="1" t="n">
         <v>6</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H13" s="1" t="n">
         <v>4</v>
       </c>
       <c r="I13" s="1" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J13" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K13" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L13" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M13" s="1" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N13" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="O13" s="1" t="n">
         <v>25</v>
       </c>
       <c r="P13" s="1" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Q13" s="1" t="n">
         <v>24</v>
       </c>
       <c r="R13" s="1" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="S13" s="1" t="n">
         <v>5</v>
@@ -3601,10 +3601,10 @@
         <v>13</v>
       </c>
       <c r="V13" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="W13" s="1" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="X13" s="1" t="n">
         <v>3</v>
@@ -3613,35 +3613,35 @@
         <v>1</v>
       </c>
       <c r="Z13" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA13" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AB13" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="C14" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="C14" s="1" t="n">
-        <v>10</v>
-      </c>
       <c r="D14" s="1" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G14" s="1" t="n">
         <v>26</v>
@@ -3650,22 +3650,22 @@
         <v>4</v>
       </c>
       <c r="I14" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J14" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K14" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M14" s="1" t="n">
         <v>23</v>
       </c>
       <c r="N14" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O14" s="1" t="n">
         <v>25</v>
@@ -3677,22 +3677,22 @@
         <v>24</v>
       </c>
       <c r="R14" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="S14" s="1" t="n">
         <v>5</v>
       </c>
       <c r="T14" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="U14" s="1" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="V14" s="1" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="W14" s="1" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="X14" s="1" t="n">
         <v>3</v>
@@ -3704,32 +3704,32 @@
         <v>7</v>
       </c>
       <c r="AA14" s="1" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="AB14" s="1" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G15" s="1" t="n">
         <v>26</v>
@@ -3738,49 +3738,49 @@
         <v>4</v>
       </c>
       <c r="I15" s="1" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="J15" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K15" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L15" s="1" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="M15" s="1" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="N15" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O15" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="P15" s="1" t="n">
         <v>27</v>
       </c>
       <c r="Q15" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R15" s="1" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="S15" s="1" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T15" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="U15" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="V15" s="1" t="n">
         <v>18</v>
       </c>
       <c r="W15" s="1" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="X15" s="1" t="n">
         <v>3</v>
@@ -3789,19 +3789,19 @@
         <v>1</v>
       </c>
       <c r="Z15" s="1" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AA15" s="1" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AB15" s="1" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
@@ -3811,7 +3811,7 @@
         <v>11</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E16" s="1" t="n">
         <v>16</v>
@@ -3820,7 +3820,7 @@
         <v>6</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H16" s="1" t="n">
         <v>4</v>
@@ -3835,40 +3835,40 @@
         <v>2</v>
       </c>
       <c r="L16" s="1" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="M16" s="1" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="N16" s="1" t="n">
         <v>14</v>
       </c>
       <c r="O16" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P16" s="1" t="n">
         <v>27</v>
       </c>
       <c r="Q16" s="1" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="R16" s="1" t="n">
         <v>19</v>
       </c>
       <c r="S16" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T16" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="U16" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="V16" s="1" t="n">
         <v>18</v>
       </c>
       <c r="W16" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="X16" s="1" t="n">
         <v>3</v>
@@ -3877,10 +3877,10 @@
         <v>1</v>
       </c>
       <c r="Z16" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA16" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AB16" s="1" t="n">
         <v>7</v>
@@ -3889,29 +3889,29 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F17" s="1" t="n">
         <v>6</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H17" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I17" s="1" t="n">
         <v>5</v>
@@ -3923,16 +3923,16 @@
         <v>2</v>
       </c>
       <c r="L17" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M17" s="1" t="n">
         <v>22</v>
       </c>
       <c r="N17" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="O17" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="P17" s="1" t="n">
         <v>27</v>
@@ -3941,34 +3941,34 @@
         <v>26</v>
       </c>
       <c r="R17" s="1" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="S17" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T17" s="1" t="n">
         <v>21</v>
       </c>
       <c r="U17" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="V17" s="1" t="n">
         <v>18</v>
-      </c>
-      <c r="V17" s="1" t="n">
-        <v>15</v>
       </c>
       <c r="W17" s="1" t="n">
         <v>20</v>
       </c>
       <c r="X17" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y17" s="1" t="n">
         <v>1</v>
       </c>
       <c r="Z17" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA17" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AB17" s="1" t="n">
         <v>7</v>
@@ -3977,7 +3977,7 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
@@ -3987,22 +3987,22 @@
         <v>10</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F18" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="G18" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="H18" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="G18" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="H18" s="1" t="n">
+      <c r="I18" s="1" t="n">
         <v>5</v>
-      </c>
-      <c r="I18" s="1" t="n">
-        <v>6</v>
       </c>
       <c r="J18" s="1" t="n">
         <v>23</v>
@@ -4011,37 +4011,37 @@
         <v>2</v>
       </c>
       <c r="L18" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M18" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="N18" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="O18" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="P18" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q18" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="R18" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="S18" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="T18" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="N18" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="O18" s="1" t="n">
-        <v>27</v>
-      </c>
-      <c r="P18" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="Q18" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="R18" s="1" t="n">
+      <c r="U18" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="S18" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="T18" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="U18" s="1" t="n">
+      <c r="V18" s="1" t="n">
         <v>15</v>
-      </c>
-      <c r="V18" s="1" t="n">
-        <v>17</v>
       </c>
       <c r="W18" s="1" t="n">
         <v>20</v>
@@ -4053,7 +4053,7 @@
         <v>1</v>
       </c>
       <c r="Z18" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA18" s="1" t="n">
         <v>16</v>
@@ -4065,77 +4065,77 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D19" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="E19" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="E19" s="1" t="n">
-        <v>14</v>
-      </c>
       <c r="F19" s="1" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G19" s="1" t="n">
         <v>24</v>
       </c>
       <c r="H19" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I19" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J19" s="1" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="K19" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L19" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="M19" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="N19" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="O19" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="P19" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q19" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="R19" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="S19" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="T19" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="U19" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="V19" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="M19" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="N19" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="O19" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="P19" s="1" t="n">
-        <v>27</v>
-      </c>
-      <c r="Q19" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="R19" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="S19" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="T19" s="1" t="n">
-        <v>23</v>
-      </c>
-      <c r="U19" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="V19" s="1" t="n">
-        <v>16</v>
-      </c>
       <c r="W19" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="X19" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y19" s="1" t="n">
         <v>1</v>
@@ -4144,26 +4144,26 @@
         <v>8</v>
       </c>
       <c r="AA19" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AB19" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="C20" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="C20" s="1" t="n">
-        <v>10</v>
-      </c>
       <c r="D20" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E20" s="1" t="n">
         <v>14</v>
@@ -4181,34 +4181,34 @@
         <v>7</v>
       </c>
       <c r="J20" s="1" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K20" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L20" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M20" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N20" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="O20" s="1" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P20" s="1" t="n">
         <v>27</v>
       </c>
       <c r="Q20" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="R20" s="1" t="n">
         <v>19</v>
       </c>
       <c r="S20" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T20" s="1" t="n">
         <v>23</v>
@@ -4220,7 +4220,7 @@
         <v>16</v>
       </c>
       <c r="W20" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="X20" s="1" t="n">
         <v>3</v>
@@ -4229,47 +4229,47 @@
         <v>1</v>
       </c>
       <c r="Z20" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA20" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="AB20" s="1" t="n">
         <v>6</v>
-      </c>
-      <c r="AA20" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="AB20" s="1" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
         <v>11</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D21" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="E21" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="E21" s="1" t="n">
-        <v>12</v>
-      </c>
       <c r="F21" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G21" s="1" t="n">
         <v>24</v>
       </c>
       <c r="H21" s="1" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I21" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J21" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K21" s="1" t="n">
         <v>2</v>
@@ -4278,7 +4278,7 @@
         <v>15</v>
       </c>
       <c r="M21" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N21" s="1" t="n">
         <v>13</v>
@@ -4296,7 +4296,7 @@
         <v>19</v>
       </c>
       <c r="S21" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T21" s="1" t="n">
         <v>23</v>
@@ -4305,7 +4305,7 @@
         <v>18</v>
       </c>
       <c r="V21" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="W21" s="1" t="n">
         <v>20</v>
@@ -4317,32 +4317,32 @@
         <v>1</v>
       </c>
       <c r="Z21" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA21" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AB21" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C22" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="E22" s="1" t="n">
         <v>12</v>
-      </c>
-      <c r="D22" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>13</v>
       </c>
       <c r="F22" s="1" t="n">
         <v>4</v>
@@ -4351,10 +4351,10 @@
         <v>24</v>
       </c>
       <c r="H22" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I22" s="1" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J22" s="1" t="n">
         <v>21</v>
@@ -4363,40 +4363,40 @@
         <v>2</v>
       </c>
       <c r="L22" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="M22" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="N22" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="O22" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="P22" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q22" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="R22" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="S22" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="U22" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="M22" s="1" t="n">
+      <c r="V22" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="W22" s="1" t="n">
         <v>20</v>
-      </c>
-      <c r="N22" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="O22" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="P22" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="Q22" s="1" t="n">
-        <v>27</v>
-      </c>
-      <c r="R22" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="S22" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="T22" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="U22" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="V22" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="W22" s="1" t="n">
-        <v>23</v>
       </c>
       <c r="X22" s="1" t="n">
         <v>3</v>
@@ -4405,38 +4405,38 @@
         <v>1</v>
       </c>
       <c r="Z22" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA22" s="1" t="n">
         <v>16</v>
       </c>
       <c r="AB22" s="1" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C23" s="1" t="n">
         <v>12</v>
       </c>
       <c r="D23" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F23" s="1" t="n">
         <v>4</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H23" s="1" t="n">
         <v>7</v>
@@ -4445,7 +4445,7 @@
         <v>11</v>
       </c>
       <c r="J23" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K23" s="1" t="n">
         <v>2</v>
@@ -4454,25 +4454,25 @@
         <v>18</v>
       </c>
       <c r="M23" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="N23" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="O23" s="1" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="P23" s="1" t="n">
         <v>26</v>
       </c>
       <c r="Q23" s="1" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="R23" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="S23" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T23" s="1" t="n">
         <v>22</v>
@@ -4481,7 +4481,7 @@
         <v>19</v>
       </c>
       <c r="V23" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="W23" s="1" t="n">
         <v>23</v>
@@ -4496,7 +4496,7 @@
         <v>6</v>
       </c>
       <c r="AA23" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AB23" s="1" t="n">
         <v>5</v>
@@ -4505,47 +4505,47 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C24" s="1" t="n">
         <v>12</v>
       </c>
       <c r="D24" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="E24" s="1" t="n">
         <v>15</v>
-      </c>
-      <c r="E24" s="1" t="n">
-        <v>10</v>
       </c>
       <c r="F24" s="1" t="n">
         <v>4</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H24" s="1" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I24" s="1" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J24" s="1" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K24" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L24" s="1" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M24" s="1" t="n">
         <v>21</v>
       </c>
       <c r="N24" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O24" s="1" t="n">
         <v>27</v>
@@ -4554,59 +4554,59 @@
         <v>26</v>
       </c>
       <c r="Q24" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R24" s="1" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="S24" s="1" t="n">
         <v>8</v>
       </c>
       <c r="T24" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="U24" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="V24" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="W24" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="U24" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="V24" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="W24" s="1" t="n">
+      <c r="X24" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y24" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="X24" s="1" t="n">
+      <c r="Z24" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA24" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="AB24" s="1" t="n">
         <v>5</v>
-      </c>
-      <c r="Y24" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z24" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA24" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="AB24" s="1" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
         <v>13</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D25" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F25" s="1" t="n">
         <v>4</v>
@@ -4615,13 +4615,13 @@
         <v>24</v>
       </c>
       <c r="H25" s="1" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I25" s="1" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="J25" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K25" s="1" t="n">
         <v>3</v>
@@ -4645,25 +4645,25 @@
         <v>25</v>
       </c>
       <c r="R25" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="S25" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="T25" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="U25" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="V25" s="1" t="n">
         <v>16</v>
-      </c>
-      <c r="S25" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="T25" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="U25" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="V25" s="1" t="n">
-        <v>15</v>
       </c>
       <c r="W25" s="1" t="n">
         <v>1</v>
       </c>
       <c r="X25" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y25" s="1" t="n">
         <v>2</v>
@@ -4672,26 +4672,26 @@
         <v>7</v>
       </c>
       <c r="AA25" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AB25" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D26" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E26" s="1" t="n">
         <v>9</v>
@@ -4700,22 +4700,22 @@
         <v>4</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H26" s="1" t="n">
         <v>12</v>
       </c>
       <c r="I26" s="1" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J26" s="1" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K26" s="1" t="n">
         <v>3</v>
       </c>
       <c r="L26" s="1" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="M26" s="1" t="n">
         <v>21</v>
@@ -4727,25 +4727,25 @@
         <v>27</v>
       </c>
       <c r="P26" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q26" s="1" t="n">
         <v>25</v>
-      </c>
-      <c r="Q26" s="1" t="n">
-        <v>24</v>
       </c>
       <c r="R26" s="1" t="n">
         <v>16</v>
       </c>
       <c r="S26" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T26" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="U26" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="V26" s="1" t="n">
         <v>15</v>
-      </c>
-      <c r="V26" s="1" t="n">
-        <v>14</v>
       </c>
       <c r="W26" s="1" t="n">
         <v>1</v>
@@ -4769,38 +4769,38 @@
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C27" s="1" t="n">
         <v>10</v>
       </c>
       <c r="D27" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E27" s="1" t="n">
         <v>9</v>
       </c>
       <c r="F27" s="1" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H27" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I27" s="1" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J27" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K27" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L27" s="1" t="n">
         <v>20</v>
@@ -4812,37 +4812,37 @@
         <v>11</v>
       </c>
       <c r="O27" s="1" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P27" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q27" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="Q27" s="1" t="n">
-        <v>25</v>
-      </c>
       <c r="R27" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="S27" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="T27" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="U27" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="V27" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="S27" s="1" t="n">
+      <c r="W27" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="X27" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="T27" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="U27" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="V27" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="W27" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="X27" s="1" t="n">
-        <v>8</v>
-      </c>
       <c r="Y27" s="1" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Z27" s="1" t="n">
         <v>7</v>
@@ -4857,20 +4857,20 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="C28" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="C28" s="1" t="n">
-        <v>11</v>
-      </c>
       <c r="D28" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F28" s="1" t="n">
         <v>2</v>
@@ -4879,10 +4879,10 @@
         <v>27</v>
       </c>
       <c r="H28" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I28" s="1" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J28" s="1" t="n">
         <v>23</v>
@@ -4897,7 +4897,7 @@
         <v>21</v>
       </c>
       <c r="N28" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="O28" s="1" t="n">
         <v>26</v>
@@ -4909,10 +4909,10 @@
         <v>25</v>
       </c>
       <c r="R28" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S28" s="1" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T28" s="1" t="n">
         <v>22</v>
@@ -4921,13 +4921,13 @@
         <v>16</v>
       </c>
       <c r="V28" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="W28" s="1" t="n">
         <v>3</v>
       </c>
       <c r="X28" s="1" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y28" s="1" t="n">
         <v>4</v>
@@ -4945,38 +4945,38 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D29" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="E29" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="F29" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G29" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="H29" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="I29" s="1" t="n">
         <v>19</v>
-      </c>
-      <c r="E29" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="F29" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="G29" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="H29" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="I29" s="1" t="n">
-        <v>18</v>
       </c>
       <c r="J29" s="1" t="n">
         <v>23</v>
       </c>
       <c r="K29" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L29" s="1" t="n">
         <v>20</v>
@@ -4985,10 +4985,10 @@
         <v>21</v>
       </c>
       <c r="N29" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="O29" s="1" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P29" s="1" t="n">
         <v>24</v>
@@ -4997,7 +4997,7 @@
         <v>25</v>
       </c>
       <c r="R29" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="S29" s="1" t="n">
         <v>9</v>
@@ -5006,25 +5006,25 @@
         <v>22</v>
       </c>
       <c r="U29" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="V29" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="W29" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X29" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y29" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="Y29" s="1" t="n">
-        <v>2</v>
-      </c>
       <c r="Z29" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA29" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AB29" s="1" t="n">
         <v>5</v>
@@ -5033,41 +5033,41 @@
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C30" s="1" t="n">
         <v>12</v>
       </c>
       <c r="D30" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F30" s="1" t="n">
         <v>7</v>
       </c>
       <c r="G30" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="H30" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="I30" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="J30" s="1" t="n">
         <v>23</v>
-      </c>
-      <c r="H30" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="I30" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="J30" s="1" t="n">
-        <v>24</v>
       </c>
       <c r="K30" s="1" t="n">
         <v>3</v>
       </c>
       <c r="L30" s="1" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M30" s="1" t="n">
         <v>21</v>
@@ -5079,25 +5079,25 @@
         <v>27</v>
       </c>
       <c r="P30" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q30" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="Q30" s="1" t="n">
-        <v>26</v>
-      </c>
       <c r="R30" s="1" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="S30" s="1" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="T30" s="1" t="n">
         <v>22</v>
       </c>
       <c r="U30" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="V30" s="1" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="W30" s="1" t="n">
         <v>1</v>
@@ -5112,50 +5112,50 @@
         <v>8</v>
       </c>
       <c r="AA30" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AB30" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="C31" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D31" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="E31" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="F31" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C31" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="D31" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="E31" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="F31" s="1" t="n">
-        <v>5</v>
-      </c>
       <c r="G31" s="1" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="H31" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I31" s="1" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J31" s="1" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K31" s="1" t="n">
         <v>3</v>
       </c>
       <c r="L31" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M31" s="1" t="n">
         <v>21</v>
@@ -5167,25 +5167,25 @@
         <v>27</v>
       </c>
       <c r="P31" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Q31" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="R31" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="S31" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="S31" s="1" t="n">
-        <v>19</v>
-      </c>
       <c r="T31" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="U31" s="1" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="V31" s="1" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="W31" s="1" t="n">
         <v>1</v>
@@ -5197,10 +5197,10 @@
         <v>2</v>
       </c>
       <c r="Z31" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA31" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AB31" s="1" t="n">
         <v>6</v>
@@ -5209,20 +5209,20 @@
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C32" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="D32" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="D32" s="1" t="n">
-        <v>20</v>
-      </c>
       <c r="E32" s="1" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F32" s="1" t="n">
         <v>5</v>
@@ -5231,10 +5231,10 @@
         <v>26</v>
       </c>
       <c r="H32" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I32" s="1" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J32" s="1" t="n">
         <v>22</v>
@@ -5243,34 +5243,34 @@
         <v>3</v>
       </c>
       <c r="L32" s="1" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M32" s="1" t="n">
         <v>21</v>
       </c>
       <c r="N32" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="O32" s="1" t="n">
         <v>27</v>
       </c>
       <c r="P32" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q32" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="Q32" s="1" t="n">
-        <v>24</v>
-      </c>
       <c r="R32" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="S32" s="1" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="T32" s="1" t="n">
         <v>23</v>
       </c>
       <c r="U32" s="1" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="V32" s="1" t="n">
         <v>17</v>
@@ -5285,10 +5285,10 @@
         <v>2</v>
       </c>
       <c r="Z32" s="1" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AA32" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AB32" s="1" t="n">
         <v>6</v>
@@ -5297,44 +5297,44 @@
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D33" s="1" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F33" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G33" s="1" t="n">
         <v>26</v>
       </c>
       <c r="H33" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I33" s="1" t="n">
         <v>10</v>
       </c>
       <c r="J33" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K33" s="1" t="n">
         <v>3</v>
       </c>
       <c r="L33" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M33" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N33" s="1" t="n">
         <v>11</v>
@@ -5349,10 +5349,10 @@
         <v>24</v>
       </c>
       <c r="R33" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="S33" s="1" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="T33" s="1" t="n">
         <v>23</v>
@@ -5361,13 +5361,13 @@
         <v>18</v>
       </c>
       <c r="V33" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="W33" s="1" t="n">
         <v>1</v>
       </c>
       <c r="X33" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y33" s="1" t="n">
         <v>2</v>
@@ -5376,7 +5376,7 @@
         <v>7</v>
       </c>
       <c r="AA33" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AB33" s="1" t="n">
         <v>6</v>
@@ -5385,38 +5385,38 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
         <v>9</v>
       </c>
       <c r="C34" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D34" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="E34" s="1" t="n">
         <v>13</v>
-      </c>
-      <c r="D34" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="E34" s="1" t="n">
-        <v>11</v>
       </c>
       <c r="F34" s="1" t="n">
         <v>4</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H34" s="1" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I34" s="1" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J34" s="1" t="n">
         <v>21</v>
       </c>
       <c r="K34" s="1" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="L34" s="1" t="n">
         <v>20</v>
@@ -5425,28 +5425,28 @@
         <v>22</v>
       </c>
       <c r="N34" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="O34" s="1" t="n">
         <v>27</v>
       </c>
       <c r="P34" s="1" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Q34" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R34" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="S34" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="T34" s="1" t="n">
         <v>23</v>
       </c>
       <c r="U34" s="1" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="V34" s="1" t="n">
         <v>15</v>
@@ -5461,10 +5461,10 @@
         <v>2</v>
       </c>
       <c r="Z34" s="1" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AA34" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AB34" s="1" t="n">
         <v>6</v>
@@ -5473,47 +5473,47 @@
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C35" s="1" t="n">
         <v>13</v>
       </c>
       <c r="D35" s="1" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="F35" s="1" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H35" s="1" t="n">
         <v>3</v>
       </c>
       <c r="I35" s="1" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J35" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="K35" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="L35" s="1" t="n">
         <v>20</v>
-      </c>
-      <c r="K35" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="L35" s="1" t="n">
-        <v>18</v>
       </c>
       <c r="M35" s="1" t="n">
         <v>22</v>
       </c>
       <c r="N35" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O35" s="1" t="n">
         <v>27</v>
@@ -5525,25 +5525,25 @@
         <v>25</v>
       </c>
       <c r="R35" s="1" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="S35" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="T35" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="U35" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="T35" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="U35" s="1" t="n">
-        <v>12</v>
-      </c>
       <c r="V35" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="W35" s="1" t="n">
         <v>1</v>
       </c>
       <c r="X35" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y35" s="1" t="n">
         <v>2</v>
@@ -5561,44 +5561,44 @@
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B36" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D36" s="1" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F36" s="1" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G36" s="1" t="n">
         <v>23</v>
       </c>
       <c r="H36" s="1" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I36" s="1" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J36" s="1" t="n">
         <v>20</v>
       </c>
       <c r="K36" s="1" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L36" s="1" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="M36" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N36" s="1" t="n">
         <v>11</v>
@@ -5610,86 +5610,86 @@
         <v>26</v>
       </c>
       <c r="Q36" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="R36" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="S36" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="T36" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="R36" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="S36" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="T36" s="1" t="n">
-        <v>25</v>
-      </c>
       <c r="U36" s="1" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="V36" s="1" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="W36" s="1" t="n">
         <v>1</v>
       </c>
       <c r="X36" s="1" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Y36" s="1" t="n">
         <v>2</v>
       </c>
       <c r="Z36" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA36" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AB36" s="1" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B37" s="1" t="n">
         <v>10</v>
       </c>
       <c r="C37" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="D37" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="D37" s="1" t="n">
-        <v>11</v>
-      </c>
       <c r="E37" s="1" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F37" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G37" s="1" t="n">
         <v>23</v>
       </c>
       <c r="H37" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="I37" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="J37" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="K37" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="I37" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="J37" s="1" t="n">
+      <c r="L37" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="M37" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="K37" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="L37" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="M37" s="1" t="n">
-        <v>22</v>
-      </c>
       <c r="N37" s="1" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="O37" s="1" t="n">
         <v>27</v>
@@ -5701,7 +5701,7 @@
         <v>24</v>
       </c>
       <c r="R37" s="1" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="S37" s="1" t="n">
         <v>19</v>
@@ -5710,16 +5710,16 @@
         <v>25</v>
       </c>
       <c r="U37" s="1" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="V37" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="W37" s="1" t="n">
         <v>1</v>
       </c>
       <c r="X37" s="1" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Y37" s="1" t="n">
         <v>2</v>
@@ -5728,23 +5728,23 @@
         <v>9</v>
       </c>
       <c r="AA37" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AB37" s="1" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B38" s="1" t="n">
         <v>10</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D38" s="1" t="n">
         <v>11</v>
@@ -5753,7 +5753,7 @@
         <v>20</v>
       </c>
       <c r="F38" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G38" s="1" t="n">
         <v>23</v>
@@ -5765,19 +5765,19 @@
         <v>7</v>
       </c>
       <c r="J38" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K38" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L38" s="1" t="n">
         <v>13</v>
       </c>
       <c r="M38" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N38" s="1" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="O38" s="1" t="n">
         <v>27</v>
@@ -5789,19 +5789,19 @@
         <v>24</v>
       </c>
       <c r="R38" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="S38" s="1" t="n">
         <v>19</v>
-      </c>
-      <c r="S38" s="1" t="n">
-        <v>18</v>
       </c>
       <c r="T38" s="1" t="n">
         <v>25</v>
       </c>
       <c r="U38" s="1" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="V38" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="W38" s="1" t="n">
         <v>1</v>
@@ -5816,7 +5816,7 @@
         <v>9</v>
       </c>
       <c r="AA38" s="1" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AB38" s="1" t="n">
         <v>8</v>
@@ -5825,44 +5825,44 @@
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B39" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="C39" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="C39" s="1" t="n">
-        <v>16</v>
-      </c>
       <c r="D39" s="1" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F39" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G39" s="1" t="n">
         <v>23</v>
       </c>
       <c r="H39" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I39" s="1" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J39" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="K39" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="L39" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="M39" s="1" t="n">
         <v>21</v>
-      </c>
-      <c r="K39" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="L39" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="M39" s="1" t="n">
-        <v>20</v>
       </c>
       <c r="N39" s="1" t="n">
         <v>12</v>
@@ -5886,19 +5886,19 @@
         <v>25</v>
       </c>
       <c r="U39" s="1" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="V39" s="1" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="W39" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="X39" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="X39" s="1" t="n">
-        <v>7</v>
-      </c>
       <c r="Y39" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Z39" s="1" t="n">
         <v>9</v>
@@ -5913,23 +5913,23 @@
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B40" s="1" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C40" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="D40" s="1" t="n">
         <v>14</v>
-      </c>
-      <c r="D40" s="1" t="n">
-        <v>13</v>
       </c>
       <c r="E40" s="1" t="n">
         <v>22</v>
       </c>
       <c r="F40" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G40" s="1" t="n">
         <v>23</v>
@@ -5941,16 +5941,16 @@
         <v>3</v>
       </c>
       <c r="J40" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K40" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L40" s="1" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="M40" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="N40" s="1" t="n">
         <v>12</v>
@@ -5965,47 +5965,47 @@
         <v>24</v>
       </c>
       <c r="R40" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="S40" s="1" t="n">
         <v>18</v>
-      </c>
-      <c r="S40" s="1" t="n">
-        <v>19</v>
       </c>
       <c r="T40" s="1" t="n">
         <v>25</v>
       </c>
       <c r="U40" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="V40" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="W40" s="1" t="n">
         <v>4</v>
       </c>
       <c r="X40" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y40" s="1" t="n">
         <v>5</v>
       </c>
       <c r="Z40" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA40" s="1" t="n">
         <v>17</v>
       </c>
       <c r="AB40" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B41" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C41" s="1" t="n">
         <v>14</v>
@@ -6014,31 +6014,31 @@
         <v>13</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F41" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G41" s="1" t="n">
         <v>23</v>
       </c>
       <c r="H41" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I41" s="1" t="n">
         <v>3</v>
       </c>
       <c r="J41" s="1" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K41" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L41" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M41" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N41" s="1" t="n">
         <v>12</v>
@@ -6053,19 +6053,19 @@
         <v>24</v>
       </c>
       <c r="R41" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="S41" s="1" t="n">
         <v>19</v>
-      </c>
-      <c r="S41" s="1" t="n">
-        <v>18</v>
       </c>
       <c r="T41" s="1" t="n">
         <v>25</v>
       </c>
       <c r="U41" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="V41" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="W41" s="1" t="n">
         <v>4</v>
@@ -6077,10 +6077,10 @@
         <v>5</v>
       </c>
       <c r="Z41" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA41" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AB41" s="1" t="n">
         <v>9</v>
@@ -6089,26 +6089,26 @@
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B42" s="1" t="n">
         <v>11</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D42" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F42" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H42" s="1" t="n">
         <v>2</v>
@@ -6117,13 +6117,13 @@
         <v>3</v>
       </c>
       <c r="J42" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K42" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L42" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M42" s="1" t="n">
         <v>20</v>
@@ -6138,16 +6138,16 @@
         <v>26</v>
       </c>
       <c r="Q42" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="R42" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="S42" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="T42" s="1" t="n">
         <v>25</v>
-      </c>
-      <c r="R42" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="S42" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="T42" s="1" t="n">
-        <v>24</v>
       </c>
       <c r="U42" s="1" t="n">
         <v>10</v>
@@ -6165,35 +6165,35 @@
         <v>5</v>
       </c>
       <c r="Z42" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA42" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="AB42" s="1" t="n">
         <v>9</v>
-      </c>
-      <c r="AA42" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="AB42" s="1" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B43" s="1" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D43" s="1" t="n">
         <v>14</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F43" s="1" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G43" s="1" t="n">
         <v>21</v>
@@ -6211,7 +6211,7 @@
         <v>1</v>
       </c>
       <c r="L43" s="1" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="M43" s="1" t="n">
         <v>20</v>
@@ -6223,56 +6223,56 @@
         <v>27</v>
       </c>
       <c r="P43" s="1" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="Q43" s="1" t="n">
         <v>25</v>
       </c>
       <c r="R43" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="S43" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="T43" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="U43" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="T43" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="U43" s="1" t="n">
+      <c r="V43" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="W43" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="V43" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="W43" s="1" t="n">
+      <c r="X43" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="X43" s="1" t="n">
-        <v>11</v>
-      </c>
       <c r="Y43" s="1" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Z43" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA43" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="AB43" s="1" t="n">
         <v>8</v>
-      </c>
-      <c r="AA43" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="AB43" s="1" t="n">
-        <v>9</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B44" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="C44" s="1" t="n">
         <v>17</v>
-      </c>
-      <c r="C44" s="1" t="n">
-        <v>15</v>
       </c>
       <c r="D44" s="1" t="n">
         <v>14</v>
@@ -6284,7 +6284,7 @@
         <v>5</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="H44" s="1" t="n">
         <v>2</v>
@@ -6293,25 +6293,25 @@
         <v>3</v>
       </c>
       <c r="J44" s="1" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K44" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L44" s="1" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="M44" s="1" t="n">
         <v>20</v>
       </c>
       <c r="N44" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="O44" s="1" t="n">
         <v>27</v>
       </c>
       <c r="P44" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q44" s="1" t="n">
         <v>25</v>
@@ -6320,47 +6320,47 @@
         <v>16</v>
       </c>
       <c r="S44" s="1" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T44" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="U44" s="1" t="n">
         <v>4</v>
       </c>
       <c r="V44" s="1" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="W44" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X44" s="1" t="n">
         <v>11</v>
       </c>
       <c r="Y44" s="1" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Z44" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA44" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="AB44" s="1" t="n">
         <v>9</v>
-      </c>
-      <c r="AA44" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="AB44" s="1" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B45" s="1" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D45" s="1" t="n">
         <v>14</v>
@@ -6381,34 +6381,34 @@
         <v>3</v>
       </c>
       <c r="J45" s="1" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K45" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L45" s="1" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M45" s="1" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="N45" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="O45" s="1" t="n">
         <v>27</v>
       </c>
       <c r="P45" s="1" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q45" s="1" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="R45" s="1" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="S45" s="1" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T45" s="1" t="n">
         <v>21</v>
@@ -6420,13 +6420,13 @@
         <v>12</v>
       </c>
       <c r="W45" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X45" s="1" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="Y45" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z45" s="1" t="n">
         <v>9</v>
@@ -6435,59 +6435,59 @@
         <v>19</v>
       </c>
       <c r="AB45" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B46" s="1" t="n">
         <v>25</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D46" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F46" s="1" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G46" s="1" t="n">
         <v>24</v>
       </c>
       <c r="H46" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I46" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="J46" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="K46" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="I46" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="J46" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="K46" s="1" t="n">
-        <v>3</v>
-      </c>
       <c r="L46" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M46" s="1" t="n">
         <v>18</v>
       </c>
       <c r="N46" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="O46" s="1" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P46" s="1" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="Q46" s="1" t="n">
         <v>23</v>
@@ -6496,56 +6496,56 @@
         <v>13</v>
       </c>
       <c r="S46" s="1" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T46" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="U46" s="1" t="n">
         <v>4</v>
       </c>
       <c r="V46" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="W46" s="1" t="n">
         <v>6</v>
       </c>
       <c r="X46" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Y46" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z46" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA46" s="1" t="n">
         <v>19</v>
       </c>
       <c r="AB46" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B47" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="C47" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="D47" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="E47" s="1" t="n">
         <v>27</v>
       </c>
-      <c r="C47" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="D47" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="E47" s="1" t="n">
-        <v>25</v>
-      </c>
       <c r="F47" s="1" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G47" s="1" t="n">
         <v>24</v>
@@ -6554,61 +6554,61 @@
         <v>1</v>
       </c>
       <c r="I47" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="J47" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="K47" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="J47" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="K47" s="1" t="n">
-        <v>2</v>
-      </c>
       <c r="L47" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M47" s="1" t="n">
         <v>18</v>
       </c>
       <c r="N47" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="O47" s="1" t="n">
         <v>26</v>
       </c>
       <c r="P47" s="1" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q47" s="1" t="n">
         <v>23</v>
       </c>
       <c r="R47" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="S47" s="1" t="n">
         <v>5</v>
       </c>
       <c r="T47" s="1" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="U47" s="1" t="n">
         <v>4</v>
       </c>
       <c r="V47" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="W47" s="1" t="n">
         <v>6</v>
       </c>
       <c r="X47" s="1" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="Y47" s="1" t="n">
         <v>7</v>
       </c>
       <c r="Z47" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA47" s="1" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AB47" s="1" t="n">
         <v>8</v>
@@ -6617,47 +6617,47 @@
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B48" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C48" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="D48" s="1" t="n">
         <v>13</v>
-      </c>
-      <c r="D48" s="1" t="n">
-        <v>6</v>
       </c>
       <c r="E48" s="1" t="n">
         <v>25</v>
       </c>
       <c r="F48" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H48" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I48" s="1" t="n">
         <v>3</v>
       </c>
       <c r="J48" s="1" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="K48" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L48" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M48" s="1" t="n">
         <v>18</v>
       </c>
       <c r="N48" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="O48" s="1" t="n">
         <v>26</v>
@@ -6675,53 +6675,53 @@
         <v>5</v>
       </c>
       <c r="T48" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="U48" s="1" t="n">
         <v>4</v>
       </c>
       <c r="V48" s="1" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="W48" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X48" s="1" t="n">
         <v>17</v>
       </c>
       <c r="Y48" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z48" s="1" t="n">
         <v>9</v>
       </c>
       <c r="AA48" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AB48" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B49" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C49" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="D49" s="1" t="n">
         <v>6</v>
-      </c>
-      <c r="D49" s="1" t="n">
-        <v>5</v>
       </c>
       <c r="E49" s="1" t="n">
         <v>25</v>
       </c>
       <c r="F49" s="1" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="G49" s="1" t="n">
         <v>22</v>
@@ -6745,22 +6745,22 @@
         <v>18</v>
       </c>
       <c r="N49" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="O49" s="1" t="n">
         <v>26</v>
       </c>
       <c r="P49" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Q49" s="1" t="n">
         <v>23</v>
       </c>
       <c r="R49" s="1" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="S49" s="1" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T49" s="1" t="n">
         <v>21</v>
@@ -6769,50 +6769,50 @@
         <v>4</v>
       </c>
       <c r="V49" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="W49" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X49" s="1" t="n">
         <v>17</v>
       </c>
       <c r="Y49" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z49" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="Z49" s="1" t="n">
+      <c r="AA49" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="AB49" s="1" t="n">
         <v>10</v>
-      </c>
-      <c r="AA49" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="AB49" s="1" t="n">
-        <v>11</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B50" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D50" s="1" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E50" s="1" t="n">
         <v>25</v>
       </c>
       <c r="F50" s="1" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H50" s="1" t="n">
         <v>2</v>
@@ -6830,7 +6830,7 @@
         <v>16</v>
       </c>
       <c r="M50" s="1" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N50" s="1" t="n">
         <v>14</v>
@@ -6839,68 +6839,68 @@
         <v>26</v>
       </c>
       <c r="P50" s="1" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="Q50" s="1" t="n">
         <v>23</v>
       </c>
       <c r="R50" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="S50" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="T50" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="U50" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="V50" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="W50" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="X50" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y50" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="S50" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="T50" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="U50" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="V50" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="W50" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="X50" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="Y50" s="1" t="n">
-        <v>5</v>
-      </c>
       <c r="Z50" s="1" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AA50" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AB50" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B51" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D51" s="1" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E51" s="1" t="n">
         <v>25</v>
       </c>
       <c r="F51" s="1" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H51" s="1" t="n">
         <v>2</v>
@@ -6909,25 +6909,25 @@
         <v>3</v>
       </c>
       <c r="J51" s="1" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K51" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L51" s="1" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="M51" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N51" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O51" s="1" t="n">
         <v>26</v>
       </c>
       <c r="P51" s="1" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="Q51" s="1" t="n">
         <v>23</v>
@@ -6936,31 +6936,31 @@
         <v>9</v>
       </c>
       <c r="S51" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="T51" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="U51" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="T51" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="U51" s="1" t="n">
-        <v>7</v>
-      </c>
       <c r="V51" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="W51" s="1" t="n">
         <v>4</v>
       </c>
       <c r="X51" s="1" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Y51" s="1" t="n">
         <v>5</v>
       </c>
       <c r="Z51" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA51" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AB51" s="1" t="n">
         <v>10</v>
@@ -6969,23 +6969,23 @@
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B52" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D52" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F52" s="1" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G52" s="1" t="n">
         <v>20</v>
@@ -6997,13 +6997,13 @@
         <v>3</v>
       </c>
       <c r="J52" s="1" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="K52" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L52" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="M52" s="1" t="n">
         <v>18</v>
@@ -7012,10 +7012,10 @@
         <v>15</v>
       </c>
       <c r="O52" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P52" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Q52" s="1" t="n">
         <v>23</v>
@@ -7030,25 +7030,25 @@
         <v>24</v>
       </c>
       <c r="U52" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V52" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="W52" s="1" t="n">
         <v>4</v>
       </c>
       <c r="X52" s="1" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Y52" s="1" t="n">
         <v>5</v>
       </c>
       <c r="Z52" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA52" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AB52" s="1" t="n">
         <v>10</v>
@@ -7057,26 +7057,26 @@
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B53" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C53" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="D53" s="1" t="n">
         <v>16</v>
-      </c>
-      <c r="D53" s="1" t="n">
-        <v>13</v>
       </c>
       <c r="E53" s="1" t="n">
         <v>26</v>
       </c>
       <c r="F53" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="G53" s="1" t="n">
         <v>20</v>
-      </c>
-      <c r="G53" s="1" t="n">
-        <v>22</v>
       </c>
       <c r="H53" s="1" t="n">
         <v>2</v>
@@ -7097,13 +7097,13 @@
         <v>18</v>
       </c>
       <c r="N53" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="O53" s="1" t="n">
         <v>25</v>
       </c>
       <c r="P53" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Q53" s="1" t="n">
         <v>23</v>
@@ -7121,7 +7121,7 @@
         <v>8</v>
       </c>
       <c r="V53" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="W53" s="1" t="n">
         <v>4</v>
@@ -7136,7 +7136,7 @@
         <v>7</v>
       </c>
       <c r="AA53" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AB53" s="1" t="n">
         <v>10</v>
@@ -7145,7 +7145,7 @@
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B54" s="1" t="n">
@@ -7155,16 +7155,16 @@
         <v>16</v>
       </c>
       <c r="D54" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F54" s="1" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H54" s="1" t="n">
         <v>2</v>
@@ -7182,22 +7182,22 @@
         <v>11</v>
       </c>
       <c r="M54" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="N54" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="N54" s="1" t="n">
-        <v>15</v>
-      </c>
       <c r="O54" s="1" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P54" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="Q54" s="1" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="R54" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="S54" s="1" t="n">
         <v>6</v>
@@ -7209,13 +7209,13 @@
         <v>8</v>
       </c>
       <c r="V54" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="W54" s="1" t="n">
         <v>4</v>
       </c>
       <c r="X54" s="1" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="Y54" s="1" t="n">
         <v>5</v>
@@ -7224,71 +7224,71 @@
         <v>7</v>
       </c>
       <c r="AA54" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AB54" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B55" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D55" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F55" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="G55" s="1" t="n">
         <v>20</v>
-      </c>
-      <c r="G55" s="1" t="n">
-        <v>17</v>
       </c>
       <c r="H55" s="1" t="n">
         <v>2</v>
       </c>
       <c r="I55" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J55" s="1" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K55" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L55" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="M55" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N55" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="O55" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="P55" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="O55" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="P55" s="1" t="n">
-        <v>11</v>
-      </c>
       <c r="Q55" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R55" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="S55" s="1" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T55" s="1" t="n">
         <v>24</v>
@@ -7300,132 +7300,132 @@
         <v>13</v>
       </c>
       <c r="W55" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="X55" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y55" s="1" t="n">
         <v>5</v>
-      </c>
-      <c r="X55" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="Y55" s="1" t="n">
-        <v>6</v>
       </c>
       <c r="Z55" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AA55" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AB55" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B56" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D56" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E56" s="1" t="n">
         <v>26</v>
       </c>
       <c r="F56" s="1" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H56" s="1" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I56" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J56" s="1" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="K56" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L56" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M56" s="1" t="n">
         <v>18</v>
       </c>
       <c r="N56" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O56" s="1" t="n">
         <v>25</v>
       </c>
       <c r="P56" s="1" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="Q56" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="R56" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="S56" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T56" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="U56" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V56" s="1" t="n">
         <v>13</v>
       </c>
       <c r="W56" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X56" s="1" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="Y56" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z56" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AA56" s="1" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AB56" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B57" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D57" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E57" s="1" t="n">
         <v>26</v>
       </c>
       <c r="F57" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G57" s="1" t="n">
         <v>20</v>
@@ -7434,7 +7434,7 @@
         <v>6</v>
       </c>
       <c r="I57" s="1" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J57" s="1" t="n">
         <v>19</v>
@@ -7455,10 +7455,10 @@
         <v>25</v>
       </c>
       <c r="P57" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Q57" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R57" s="1" t="n">
         <v>10</v>
@@ -7467,53 +7467,53 @@
         <v>2</v>
       </c>
       <c r="T57" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="U57" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="V57" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="W57" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="X57" s="1" t="n">
         <v>24</v>
-      </c>
-      <c r="U57" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="V57" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="W57" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="X57" s="1" t="n">
-        <v>23</v>
       </c>
       <c r="Y57" s="1" t="n">
         <v>5</v>
       </c>
       <c r="Z57" s="1" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AA57" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AB57" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B58" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D58" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E58" s="1" t="n">
         <v>26</v>
       </c>
       <c r="F58" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G58" s="1" t="n">
         <v>20</v>
@@ -7522,25 +7522,25 @@
         <v>6</v>
       </c>
       <c r="I58" s="1" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J58" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K58" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L58" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M58" s="1" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N58" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O58" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="P58" s="1" t="n">
         <v>17</v>
@@ -7549,31 +7549,31 @@
         <v>22</v>
       </c>
       <c r="R58" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="S58" s="1" t="n">
         <v>2</v>
       </c>
       <c r="T58" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="U58" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="V58" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="W58" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="X58" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="U58" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="V58" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="W58" s="1" t="n">
+      <c r="Y58" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z58" s="1" t="n">
         <v>4</v>
-      </c>
-      <c r="X58" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="Y58" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z58" s="1" t="n">
-        <v>5</v>
       </c>
       <c r="AA58" s="1" t="n">
         <v>21</v>
@@ -7585,32 +7585,32 @@
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B59" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D59" s="1" t="n">
         <v>11</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F59" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G59" s="1" t="n">
         <v>20</v>
       </c>
       <c r="H59" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="I59" s="1" t="n">
         <v>3</v>
-      </c>
-      <c r="I59" s="1" t="n">
-        <v>12</v>
       </c>
       <c r="J59" s="1" t="n">
         <v>18</v>
@@ -7619,13 +7619,13 @@
         <v>1</v>
       </c>
       <c r="L59" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M59" s="1" t="n">
         <v>19</v>
       </c>
       <c r="N59" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O59" s="1" t="n">
         <v>24</v>
@@ -7637,28 +7637,28 @@
         <v>22</v>
       </c>
       <c r="R59" s="1" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="S59" s="1" t="n">
         <v>2</v>
       </c>
       <c r="T59" s="1" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="U59" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V59" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="W59" s="1" t="n">
         <v>4</v>
       </c>
       <c r="X59" s="1" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Y59" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z59" s="1" t="n">
         <v>5</v>
@@ -7667,77 +7667,77 @@
         <v>21</v>
       </c>
       <c r="AB59" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B60" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C60" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="D60" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="D60" s="1" t="n">
-        <v>10</v>
-      </c>
       <c r="E60" s="1" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F60" s="1" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G60" s="1" t="n">
         <v>20</v>
       </c>
       <c r="H60" s="1" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="I60" s="1" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="J60" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K60" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L60" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M60" s="1" t="n">
         <v>19</v>
       </c>
       <c r="N60" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O60" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P60" s="1" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Q60" s="1" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="R60" s="1" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="S60" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T60" s="1" t="n">
         <v>26</v>
       </c>
       <c r="U60" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="V60" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="W60" s="1" t="n">
         <v>4</v>
@@ -7746,7 +7746,7 @@
         <v>23</v>
       </c>
       <c r="Y60" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z60" s="1" t="n">
         <v>5</v>
@@ -7755,62 +7755,62 @@
         <v>21</v>
       </c>
       <c r="AB60" s="1" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B61" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D61" s="1" t="n">
         <v>10</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F61" s="1" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="G61" s="1" t="n">
         <v>20</v>
       </c>
       <c r="H61" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I61" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J61" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K61" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L61" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M61" s="1" t="n">
         <v>19</v>
       </c>
       <c r="N61" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O61" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="P61" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q61" s="1" t="n">
         <v>24</v>
-      </c>
-      <c r="P61" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q61" s="1" t="n">
-        <v>21</v>
       </c>
       <c r="R61" s="1" t="n">
         <v>3</v>
@@ -7819,10 +7819,10 @@
         <v>1</v>
       </c>
       <c r="T61" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="U61" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V61" s="1" t="n">
         <v>12</v>
@@ -7831,7 +7831,7 @@
         <v>4</v>
       </c>
       <c r="X61" s="1" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="Y61" s="1" t="n">
         <v>6</v>
@@ -7840,50 +7840,50 @@
         <v>5</v>
       </c>
       <c r="AA61" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AB61" s="1" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B62" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D62" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F62" s="1" t="n">
         <v>18</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H62" s="1" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="I62" s="1" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="J62" s="1" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="K62" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L62" s="1" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="M62" s="1" t="n">
         <v>19</v>
@@ -7892,37 +7892,37 @@
         <v>17</v>
       </c>
       <c r="O62" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P62" s="1" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="Q62" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R62" s="1" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="S62" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T62" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="U62" s="1" t="n">
         <v>7</v>
       </c>
       <c r="V62" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="W62" s="1" t="n">
         <v>4</v>
       </c>
       <c r="X62" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Y62" s="1" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Z62" s="1" t="n">
         <v>5</v>
@@ -7937,7 +7937,7 @@
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B63" s="1" t="n">
@@ -7947,10 +7947,10 @@
         <v>16</v>
       </c>
       <c r="D63" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F63" s="1" t="n">
         <v>18</v>
@@ -7959,19 +7959,19 @@
         <v>21</v>
       </c>
       <c r="H63" s="1" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="I63" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J63" s="1" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K63" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L63" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M63" s="1" t="n">
         <v>19</v>
@@ -7989,13 +7989,13 @@
         <v>20</v>
       </c>
       <c r="R63" s="1" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="S63" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T63" s="1" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="U63" s="1" t="n">
         <v>7</v>
@@ -8004,101 +8004,101 @@
         <v>15</v>
       </c>
       <c r="W63" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X63" s="1" t="n">
         <v>25</v>
       </c>
       <c r="Y63" s="1" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="Z63" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA63" s="1" t="n">
         <v>22</v>
       </c>
       <c r="AB63" s="1" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B64" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D64" s="1" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E64" s="1" t="n">
         <v>24</v>
       </c>
       <c r="F64" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G64" s="1" t="n">
         <v>21</v>
       </c>
       <c r="H64" s="1" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I64" s="1" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="J64" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K64" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L64" s="1" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="M64" s="1" t="n">
         <v>19</v>
       </c>
       <c r="N64" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O64" s="1" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="P64" s="1" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="Q64" s="1" t="n">
         <v>20</v>
       </c>
       <c r="R64" s="1" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="S64" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T64" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="U64" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V64" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="W64" s="1" t="n">
         <v>3</v>
       </c>
       <c r="X64" s="1" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Y64" s="1" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="Z64" s="1" t="n">
         <v>4</v>
@@ -8113,41 +8113,41 @@
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B65" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D65" s="1" t="n">
         <v>8</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F65" s="1" t="n">
         <v>16</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H65" s="1" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="I65" s="1" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="J65" s="1" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="K65" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L65" s="1" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="M65" s="1" t="n">
         <v>19</v>
@@ -8162,7 +8162,7 @@
         <v>12</v>
       </c>
       <c r="Q65" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="R65" s="1" t="n">
         <v>7</v>
@@ -8171,13 +8171,13 @@
         <v>1</v>
       </c>
       <c r="T65" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="U65" s="1" t="n">
         <v>6</v>
       </c>
       <c r="V65" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="W65" s="1" t="n">
         <v>3</v>
@@ -8186,7 +8186,7 @@
         <v>23</v>
       </c>
       <c r="Y65" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Z65" s="1" t="n">
         <v>4</v>
@@ -8201,68 +8201,68 @@
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B66" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D66" s="1" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E66" s="1" t="n">
         <v>25</v>
       </c>
       <c r="F66" s="1" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H66" s="1" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I66" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J66" s="1" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="K66" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L66" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="M66" s="1" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="N66" s="1" t="n">
         <v>18</v>
       </c>
       <c r="O66" s="1" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="P66" s="1" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="Q66" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R66" s="1" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="S66" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T66" s="1" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="U66" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V66" s="1" t="n">
         <v>14</v>
@@ -8271,107 +8271,107 @@
         <v>3</v>
       </c>
       <c r="X66" s="1" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="Y66" s="1" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Z66" s="1" t="n">
         <v>4</v>
       </c>
       <c r="AA66" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AB66" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B67" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D67" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E67" s="1" t="n">
         <v>25</v>
       </c>
       <c r="F67" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H67" s="1" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I67" s="1" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J67" s="1" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="K67" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L67" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M67" s="1" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="N67" s="1" t="n">
         <v>18</v>
       </c>
       <c r="O67" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P67" s="1" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="Q67" s="1" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="R67" s="1" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="S67" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T67" s="1" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="U67" s="1" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="V67" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="W67" s="1" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="X67" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y67" s="1" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="Z67" s="1" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="AA67" s="1" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AB67" s="1" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/NSE_Sector_Monitor.xlsx
+++ b/NSE_Sector_Monitor.xlsx
@@ -568,22 +568,22 @@
         <v>0</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>15.03</v>
+        <v>14.14</v>
       </c>
       <c r="H2" s="1" t="n">
-        <v>1.55</v>
+        <v>-5.54</v>
       </c>
       <c r="I2" s="1" t="n">
-        <v>2.12</v>
+        <v>-1.7</v>
       </c>
       <c r="J2" s="1" t="n">
-        <v>4.76</v>
+        <v>-0.4</v>
       </c>
       <c r="K2" s="1" t="n">
-        <v>21.44</v>
+        <v>16.59</v>
       </c>
       <c r="L2" s="1" t="inlineStr">
         <is>
@@ -591,21 +591,21 @@
         </is>
       </c>
       <c r="M2" s="1" t="n">
-        <v>0</v>
+        <v>-4.26</v>
       </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Q2" s="1" t="inlineStr">
@@ -617,38 +617,38 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Digital</t>
+          <t>Pharma</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
         <v>2</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>88.8</v>
+        <v>27.8</v>
       </c>
       <c r="H3" s="1" t="n">
-        <v>0.03</v>
+        <v>-0.32</v>
       </c>
       <c r="I3" s="1" t="n">
-        <v>-0.83</v>
+        <v>2.07</v>
       </c>
       <c r="J3" s="1" t="n">
-        <v>0.13</v>
+        <v>5.8</v>
       </c>
       <c r="K3" s="1" t="n">
-        <v>10.37</v>
+        <v>11.17</v>
       </c>
       <c r="L3" s="1" t="inlineStr">
         <is>
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="M3" s="1" t="n">
-        <v>-8.279999999999999</v>
+        <v>0</v>
       </c>
       <c r="N3" s="1" t="inlineStr">
         <is>
@@ -665,12 +665,12 @@
       </c>
       <c r="O3" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P3" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Q3" s="1" t="inlineStr">
@@ -682,65 +682,65 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Pharma</t>
+          <t>Digital</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
         <v>3</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>27.89</v>
+        <v>86.3</v>
       </c>
       <c r="H4" s="1" t="n">
-        <v>0.76</v>
+        <v>-2.6</v>
       </c>
       <c r="I4" s="1" t="n">
-        <v>1.67</v>
+        <v>-1.9</v>
       </c>
       <c r="J4" s="1" t="n">
-        <v>5.64</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="K4" s="1" t="n">
-        <v>9.34</v>
+        <v>9.52</v>
       </c>
       <c r="L4" s="1" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Down</t>
         </is>
       </c>
       <c r="M4" s="1" t="n">
-        <v>0</v>
+        <v>-9.35</v>
       </c>
       <c r="N4" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O4" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P4" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Q4" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -766,27 +766,27 @@
         <v>-2</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>87.23999999999999</v>
+        <v>86.56999999999999</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>1.86</v>
+        <v>0.57</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>3.25</v>
+        <v>3.71</v>
       </c>
       <c r="J5" s="1" t="n">
-        <v>-2.13</v>
+        <v>-1.04</v>
       </c>
       <c r="K5" s="1" t="n">
-        <v>7.13</v>
+        <v>7.7</v>
       </c>
       <c r="L5" s="1" t="inlineStr">
         <is>
-          <t>Down</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="M5" s="1" t="n">
-        <v>-6.7</v>
+        <v>-5.84</v>
       </c>
       <c r="N5" s="1" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
       </c>
       <c r="O5" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P5" s="1" t="inlineStr">
@@ -812,38 +812,38 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Metal</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
         <v>5</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>17.36</v>
+        <v>13.11</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>0.17</v>
+        <v>0.46</v>
       </c>
       <c r="I6" s="1" t="n">
-        <v>1.7</v>
+        <v>1.54</v>
       </c>
       <c r="J6" s="1" t="n">
-        <v>5.19</v>
+        <v>0.11</v>
       </c>
       <c r="K6" s="1" t="n">
-        <v>6.93</v>
+        <v>7.66</v>
       </c>
       <c r="L6" s="1" t="inlineStr">
         <is>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="M6" s="1" t="n">
-        <v>-0.15</v>
+        <v>-4.17</v>
       </c>
       <c r="N6" s="1" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
       </c>
       <c r="O6" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P6" s="1" t="inlineStr">
@@ -877,38 +877,38 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>Metal</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
         <v>6</v>
       </c>
       <c r="C7" s="2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="D7" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="D7" s="2" t="n">
-        <v>6</v>
-      </c>
       <c r="E7" s="2" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>13.34</v>
+        <v>17.22</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>2.22</v>
+        <v>-0.12</v>
       </c>
       <c r="I7" s="1" t="n">
-        <v>1.99</v>
+        <v>1.69</v>
       </c>
       <c r="J7" s="1" t="n">
-        <v>2.49</v>
+        <v>5.01</v>
       </c>
       <c r="K7" s="1" t="n">
-        <v>6.17</v>
+        <v>7.61</v>
       </c>
       <c r="L7" s="1" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         </is>
       </c>
       <c r="M7" s="1" t="n">
-        <v>-4.12</v>
+        <v>0</v>
       </c>
       <c r="N7" s="1" t="inlineStr">
         <is>
@@ -942,7 +942,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
@@ -952,28 +952,28 @@
         <v>-1</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>-3</v>
+        <v>4</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>280.54</v>
+        <v>31.32</v>
       </c>
       <c r="H8" s="1" t="n">
-        <v>-0.25</v>
+        <v>-1.42</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>-1.34</v>
+        <v>-2.87</v>
       </c>
       <c r="J8" s="1" t="n">
-        <v>-4.37</v>
+        <v>-3.09</v>
       </c>
       <c r="K8" s="1" t="n">
-        <v>4.07</v>
+        <v>5.73</v>
       </c>
       <c r="L8" s="1" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         </is>
       </c>
       <c r="M8" s="1" t="n">
-        <v>-5.66</v>
+        <v>-25.45</v>
       </c>
       <c r="N8" s="1" t="inlineStr">
         <is>
@@ -1000,14 +1000,14 @@
       </c>
       <c r="Q8" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Auto</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
@@ -1017,28 +1017,28 @@
         <v>-1</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>10</v>
+        <v>-1</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>2</v>
+        <v>-4</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>31.47</v>
+        <v>277.2</v>
       </c>
       <c r="H9" s="1" t="n">
-        <v>-2.02</v>
+        <v>-1.04</v>
       </c>
       <c r="I9" s="1" t="n">
-        <v>-4.28</v>
+        <v>-1.4</v>
       </c>
       <c r="J9" s="1" t="n">
-        <v>-4.49</v>
+        <v>-3.83</v>
       </c>
       <c r="K9" s="1" t="n">
-        <v>3.67</v>
+        <v>2.46</v>
       </c>
       <c r="L9" s="1" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="M9" s="1" t="n">
-        <v>-26.34</v>
+        <v>-5.2</v>
       </c>
       <c r="N9" s="1" t="inlineStr">
         <is>
@@ -1072,46 +1072,46 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>EV &amp; New Age Auto</t>
+          <t>Defence</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
         <v>9</v>
       </c>
       <c r="C10" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>-5</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>-8</v>
+      </c>
+      <c r="G10" s="1" t="n">
+        <v>102.77</v>
+      </c>
+      <c r="H10" s="1" t="n">
         <v>-1</v>
       </c>
-      <c r="D10" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E10" s="2" t="n">
-        <v>-4</v>
-      </c>
-      <c r="F10" s="2" t="n">
-        <v>-3</v>
-      </c>
-      <c r="G10" s="1" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="H10" s="1" t="n">
-        <v>-0.91</v>
-      </c>
       <c r="I10" s="1" t="n">
-        <v>-0.84</v>
+        <v>1.34</v>
       </c>
       <c r="J10" s="1" t="n">
-        <v>-2.96</v>
+        <v>0.05</v>
       </c>
       <c r="K10" s="1" t="n">
-        <v>2.56</v>
+        <v>2.26</v>
       </c>
       <c r="L10" s="1" t="inlineStr">
         <is>
-          <t>Down</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="M10" s="1" t="n">
-        <v>-5.31</v>
+        <v>-4.04</v>
       </c>
       <c r="N10" s="1" t="inlineStr">
         <is>
@@ -1144,31 +1144,31 @@
         <v>10</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>1</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>4</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>163.01</v>
+        <v>160.93</v>
       </c>
       <c r="H11" s="1" t="n">
-        <v>0.84</v>
+        <v>-1.28</v>
       </c>
       <c r="I11" s="1" t="n">
-        <v>0.47</v>
+        <v>0.32</v>
       </c>
       <c r="J11" s="1" t="n">
-        <v>-0.19</v>
+        <v>-0.48</v>
       </c>
       <c r="K11" s="1" t="n">
-        <v>1.98</v>
+        <v>1.84</v>
       </c>
       <c r="L11" s="1" t="inlineStr">
         <is>
@@ -1176,11 +1176,11 @@
         </is>
       </c>
       <c r="M11" s="1" t="n">
-        <v>-1.27</v>
+        <v>-0.88</v>
       </c>
       <c r="N11" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O11" s="1" t="inlineStr">
@@ -1202,50 +1202,50 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Consumption</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
         <v>11</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>-2</v>
+        <v>7</v>
       </c>
       <c r="D12" s="2" t="n">
         <v>2</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>-3</v>
+        <v>7</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>7</v>
+        <v>-5</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>128.81</v>
+        <v>29.26</v>
       </c>
       <c r="H12" s="1" t="n">
-        <v>0.45</v>
+        <v>-0.03</v>
       </c>
       <c r="I12" s="1" t="n">
-        <v>-0.43</v>
+        <v>1.14</v>
       </c>
       <c r="J12" s="1" t="n">
-        <v>-1.26</v>
+        <v>-0.24</v>
       </c>
       <c r="K12" s="1" t="n">
-        <v>1.69</v>
+        <v>1.55</v>
       </c>
       <c r="L12" s="1" t="inlineStr">
         <is>
-          <t>Down</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="M12" s="1" t="n">
-        <v>-5.54</v>
+        <v>0</v>
       </c>
       <c r="N12" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O12" s="1" t="inlineStr">
@@ -1267,50 +1267,50 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>Fin Services</t>
+          <t>EV &amp; New Age Auto</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
         <v>12</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>6</v>
+        <v>-5</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>3</v>
+        <v>-7</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>32.37</v>
+        <v>31.17</v>
       </c>
       <c r="H13" s="1" t="n">
-        <v>0.5600000000000001</v>
+        <v>-0.76</v>
       </c>
       <c r="I13" s="1" t="n">
-        <v>0.6</v>
+        <v>-1.2</v>
       </c>
       <c r="J13" s="1" t="n">
-        <v>-0.58</v>
+        <v>-1.95</v>
       </c>
       <c r="K13" s="1" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="L13" s="1" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Down</t>
         </is>
       </c>
       <c r="M13" s="1" t="n">
-        <v>-1.36</v>
+        <v>-4.71</v>
       </c>
       <c r="N13" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O13" s="1" t="inlineStr">
@@ -1332,38 +1332,38 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Consumption</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
         <v>13</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-8</v>
+        <v>5</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>29.6</v>
+        <v>127.1</v>
       </c>
       <c r="H14" s="1" t="n">
-        <v>0.92</v>
+        <v>-1.33</v>
       </c>
       <c r="I14" s="1" t="n">
-        <v>0.38</v>
+        <v>0.54</v>
       </c>
       <c r="J14" s="1" t="n">
-        <v>0.9399999999999999</v>
+        <v>-0.75</v>
       </c>
       <c r="K14" s="1" t="n">
-        <v>0.7</v>
+        <v>1.01</v>
       </c>
       <c r="L14" s="1" t="inlineStr">
         <is>
@@ -1371,11 +1371,11 @@
         </is>
       </c>
       <c r="M14" s="1" t="n">
-        <v>0</v>
+        <v>-5.22</v>
       </c>
       <c r="N14" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O14" s="1" t="inlineStr">
@@ -1397,38 +1397,38 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>Defence</t>
+          <t>Oil &amp; Gas</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
         <v>14</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>-9</v>
+        <v>6</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>-5</v>
+        <v>9</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-13</v>
+        <v>10</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>103.76</v>
+        <v>11.02</v>
       </c>
       <c r="H15" s="1" t="n">
-        <v>0.47</v>
+        <v>-0.9</v>
       </c>
       <c r="I15" s="1" t="n">
-        <v>1.41</v>
+        <v>0.45</v>
       </c>
       <c r="J15" s="1" t="n">
-        <v>-0.38</v>
+        <v>1.69</v>
       </c>
       <c r="K15" s="1" t="n">
-        <v>0.57</v>
+        <v>-0.05</v>
       </c>
       <c r="L15" s="1" t="inlineStr">
         <is>
@@ -1436,7 +1436,7 @@
         </is>
       </c>
       <c r="M15" s="1" t="n">
-        <v>-4.73</v>
+        <v>-8.869999999999999</v>
       </c>
       <c r="N15" s="1" t="inlineStr">
         <is>
@@ -1455,49 +1455,49 @@
       </c>
       <c r="Q15" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Capital Market</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
         <v>15</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>-3</v>
+        <v>6</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>8</v>
+        <v>-12</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>30.38</v>
+        <v>53.18</v>
       </c>
       <c r="H16" s="1" t="n">
-        <v>-0.16</v>
+        <v>0.45</v>
       </c>
       <c r="I16" s="1" t="n">
-        <v>-0.88</v>
+        <v>0.6</v>
       </c>
       <c r="J16" s="1" t="n">
-        <v>0.28</v>
+        <v>-0.46</v>
       </c>
       <c r="K16" s="1" t="n">
-        <v>-0.63</v>
+        <v>-0.34</v>
       </c>
       <c r="L16" s="1" t="inlineStr">
         <is>
-          <t>Down</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="M16" s="1" t="n">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="N16" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O16" s="1" t="inlineStr">
@@ -1527,55 +1527,55 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>Tourism</t>
+          <t>Fin Services</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
         <v>16</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>-2</v>
+        <v>-6</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>-7</v>
+        <v>-10</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>-10</v>
+        <v>-1</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-12</v>
+        <v>-3</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>78.33</v>
+        <v>31.25</v>
       </c>
       <c r="H17" s="1" t="n">
-        <v>0.41</v>
+        <v>-2.34</v>
       </c>
       <c r="I17" s="1" t="n">
-        <v>2.58</v>
+        <v>-1.69</v>
       </c>
       <c r="J17" s="1" t="n">
-        <v>1</v>
+        <v>-3.16</v>
       </c>
       <c r="K17" s="1" t="n">
-        <v>-0.74</v>
+        <v>-0.66</v>
       </c>
       <c r="L17" s="1" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Down</t>
         </is>
       </c>
       <c r="M17" s="1" t="n">
-        <v>-12.86</v>
+        <v>-3.16</v>
       </c>
       <c r="N17" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O17" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P17" s="1" t="inlineStr">
@@ -1585,67 +1585,67 @@
       </c>
       <c r="Q17" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>Capital Market</t>
+          <t>MNC</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
         <v>17</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-14</v>
+        <v>-10</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>53.88</v>
+        <v>32.27</v>
       </c>
       <c r="H18" s="1" t="n">
-        <v>1.79</v>
+        <v>-0.03</v>
       </c>
       <c r="I18" s="1" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.39</v>
       </c>
       <c r="J18" s="1" t="n">
-        <v>0.31</v>
+        <v>-1.63</v>
       </c>
       <c r="K18" s="1" t="n">
-        <v>-0.9</v>
+        <v>-0.77</v>
       </c>
       <c r="L18" s="1" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Down</t>
         </is>
       </c>
       <c r="M18" s="1" t="n">
-        <v>0</v>
+        <v>-3.99</v>
       </c>
       <c r="N18" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O18" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P18" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Q18" s="1" t="inlineStr">
@@ -1657,46 +1657,46 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>MNC</t>
+          <t>PSE</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
         <v>18</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>-3</v>
+        <v>8</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>-7</v>
+        <v>8</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>32.49</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="H19" s="1" t="n">
-        <v>-0.28</v>
+        <v>-0.3</v>
       </c>
       <c r="I19" s="1" t="n">
-        <v>-0.53</v>
+        <v>0.86</v>
       </c>
       <c r="J19" s="1" t="n">
-        <v>-2.45</v>
+        <v>2.61</v>
       </c>
       <c r="K19" s="1" t="n">
-        <v>-1.11</v>
+        <v>-0.99</v>
       </c>
       <c r="L19" s="1" t="inlineStr">
         <is>
-          <t>Down</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="M19" s="1" t="n">
-        <v>-4.95</v>
+        <v>-9.99</v>
       </c>
       <c r="N19" s="1" t="inlineStr">
         <is>
@@ -1715,45 +1715,45 @@
       </c>
       <c r="Q19" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas</t>
+          <t>Tourism</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
         <v>19</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>0</v>
+        <v>-11</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>3</v>
+        <v>-14</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>7</v>
+        <v>-15</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>11.15</v>
+        <v>77.14</v>
       </c>
       <c r="H20" s="1" t="n">
-        <v>-0.36</v>
+        <v>-1.76</v>
       </c>
       <c r="I20" s="1" t="n">
-        <v>-0.96</v>
+        <v>1.25</v>
       </c>
       <c r="J20" s="1" t="n">
-        <v>1.14</v>
+        <v>0.83</v>
       </c>
       <c r="K20" s="1" t="n">
-        <v>-1.38</v>
+        <v>-1.03</v>
       </c>
       <c r="L20" s="1" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
         </is>
       </c>
       <c r="M20" s="1" t="n">
-        <v>-9.33</v>
+        <v>-12.73</v>
       </c>
       <c r="N20" s="1" t="inlineStr">
         <is>
@@ -1787,38 +1787,38 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>Bank</t>
+          <t>Commodities</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
         <v>20</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>-9</v>
+        <v>2</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>-4</v>
+        <v>5</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>-8</v>
+        <v>5</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>-4</v>
+        <v>1</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>585.5700000000001</v>
+        <v>96.98</v>
       </c>
       <c r="H21" s="1" t="n">
-        <v>0.05</v>
+        <v>-1.05</v>
       </c>
       <c r="I21" s="1" t="n">
-        <v>-1.27</v>
+        <v>0.28</v>
       </c>
       <c r="J21" s="1" t="n">
-        <v>1.31</v>
+        <v>0.7</v>
       </c>
       <c r="K21" s="1" t="n">
-        <v>-1.96</v>
+        <v>-1.11</v>
       </c>
       <c r="L21" s="1" t="inlineStr">
         <is>
@@ -1826,11 +1826,11 @@
         </is>
       </c>
       <c r="M21" s="1" t="n">
-        <v>-5.63</v>
+        <v>-8.140000000000001</v>
       </c>
       <c r="N21" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O21" s="1" t="inlineStr">
@@ -1852,50 +1852,50 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>Private Bank</t>
+          <t>Services</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
         <v>21</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>-9</v>
+        <v>1</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>27.95</v>
+        <v>29.72</v>
       </c>
       <c r="H22" s="1" t="n">
-        <v>0.29</v>
+        <v>-1.59</v>
       </c>
       <c r="I22" s="1" t="n">
-        <v>-1.23</v>
+        <v>-0.49</v>
       </c>
       <c r="J22" s="1" t="n">
-        <v>2.88</v>
+        <v>-0.43</v>
       </c>
       <c r="K22" s="1" t="n">
-        <v>-2.31</v>
+        <v>-1.12</v>
       </c>
       <c r="L22" s="1" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Down</t>
         </is>
       </c>
       <c r="M22" s="1" t="n">
-        <v>-3.87</v>
+        <v>0</v>
       </c>
       <c r="N22" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O22" s="1" t="inlineStr">
@@ -1917,50 +1917,50 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>Commodities</t>
+          <t>PSU Bank</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
         <v>22</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>5</v>
+        <v>-10</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>-2</v>
+        <v>3</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>98.01000000000001</v>
+        <v>92.45</v>
       </c>
       <c r="H23" s="1" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="I23" s="1" t="n">
-        <v>-0.28</v>
+        <v>0.53</v>
       </c>
       <c r="J23" s="1" t="n">
-        <v>0.91</v>
+        <v>-0.34</v>
       </c>
       <c r="K23" s="1" t="n">
-        <v>-2.46</v>
+        <v>-1.76</v>
       </c>
       <c r="L23" s="1" t="inlineStr">
         <is>
-          <t>Down</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="M23" s="1" t="n">
-        <v>-8.720000000000001</v>
+        <v>-13</v>
       </c>
       <c r="N23" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O23" s="1" t="inlineStr">
@@ -1982,50 +1982,50 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>PSU Bank</t>
+          <t>Bank</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
         <v>23</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>1</v>
+        <v>-6</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>-10</v>
+        <v>-14</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>2</v>
+        <v>-8</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>93.19</v>
+        <v>575.88</v>
       </c>
       <c r="H24" s="1" t="n">
-        <v>0.46</v>
+        <v>-1.31</v>
       </c>
       <c r="I24" s="1" t="n">
-        <v>-0.71</v>
+        <v>-0.54</v>
       </c>
       <c r="J24" s="1" t="n">
-        <v>-0.03</v>
+        <v>0.34</v>
       </c>
       <c r="K24" s="1" t="n">
-        <v>-2.55</v>
+        <v>-1.95</v>
       </c>
       <c r="L24" s="1" t="inlineStr">
         <is>
-          <t>Down</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="M24" s="1" t="n">
-        <v>-13.77</v>
+        <v>-5.62</v>
       </c>
       <c r="N24" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O24" s="1" t="inlineStr">
@@ -2047,46 +2047,46 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>PSE</t>
+          <t>Private Bank</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
         <v>24</v>
       </c>
       <c r="C25" s="2" t="n">
+        <v>-10</v>
+      </c>
+      <c r="D25" s="2" t="n">
         <v>-3</v>
       </c>
-      <c r="D25" s="2" t="n">
-        <v>2</v>
-      </c>
       <c r="E25" s="2" t="n">
-        <v>1</v>
+        <v>-10</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>10.02</v>
+        <v>27.43</v>
       </c>
       <c r="H25" s="1" t="n">
-        <v>-0.3</v>
+        <v>-1.61</v>
       </c>
       <c r="I25" s="1" t="n">
-        <v>-1.56</v>
+        <v>-0.67</v>
       </c>
       <c r="J25" s="1" t="n">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="K25" s="1" t="n">
-        <v>-3.22</v>
+        <v>-2.35</v>
       </c>
       <c r="L25" s="1" t="inlineStr">
         <is>
-          <t>Down</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="M25" s="1" t="n">
-        <v>-11.04</v>
+        <v>-4.06</v>
       </c>
       <c r="N25" s="1" t="inlineStr">
         <is>
@@ -2119,31 +2119,31 @@
         <v>25</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="D26" s="2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="E26" s="2" t="n">
         <v>-3</v>
       </c>
-      <c r="E26" s="2" t="n">
-        <v>-5</v>
-      </c>
       <c r="F26" s="2" t="n">
-        <v>-8</v>
+        <v>-6</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>93.36</v>
+        <v>92.08</v>
       </c>
       <c r="H26" s="1" t="n">
-        <v>0.29</v>
+        <v>-1.37</v>
       </c>
       <c r="I26" s="1" t="n">
-        <v>-0.16</v>
+        <v>0.21</v>
       </c>
       <c r="J26" s="1" t="n">
-        <v>-0.64</v>
+        <v>0.12</v>
       </c>
       <c r="K26" s="1" t="n">
-        <v>-3.45</v>
+        <v>-3.07</v>
       </c>
       <c r="L26" s="1" t="inlineStr">
         <is>
@@ -2151,11 +2151,11 @@
         </is>
       </c>
       <c r="M26" s="1" t="n">
-        <v>-5.01</v>
+        <v>-4.72</v>
       </c>
       <c r="N26" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O26" s="1" t="inlineStr">
@@ -2187,28 +2187,28 @@
         <v>0</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>-17</v>
+        <v>-14</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>38.02</v>
+        <v>37.5</v>
       </c>
       <c r="H27" s="1" t="n">
-        <v>0.08</v>
+        <v>-1.08</v>
       </c>
       <c r="I27" s="1" t="n">
-        <v>-0.26</v>
+        <v>0.37</v>
       </c>
       <c r="J27" s="1" t="n">
-        <v>2.12</v>
+        <v>2.25</v>
       </c>
       <c r="K27" s="1" t="n">
-        <v>-4.06</v>
+        <v>-3.41</v>
       </c>
       <c r="L27" s="1" t="inlineStr">
         <is>
@@ -2220,7 +2220,7 @@
       </c>
       <c r="N27" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O27" s="1" t="inlineStr">
@@ -2235,7 +2235,7 @@
       </c>
       <c r="Q27" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2258,22 +2258,22 @@
         <v>-3</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>-5</v>
+        <v>-7</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>49.71</v>
+        <v>49.2</v>
       </c>
       <c r="H28" s="1" t="n">
-        <v>1.06</v>
+        <v>-1.03</v>
       </c>
       <c r="I28" s="1" t="n">
-        <v>-0.62</v>
+        <v>0.62</v>
       </c>
       <c r="J28" s="1" t="n">
-        <v>0.01</v>
+        <v>0.78</v>
       </c>
       <c r="K28" s="1" t="n">
-        <v>-4.69</v>
+        <v>-4.72</v>
       </c>
       <c r="L28" s="1" t="inlineStr">
         <is>
@@ -2281,16 +2281,16 @@
         </is>
       </c>
       <c r="M28" s="1" t="n">
-        <v>-16.08</v>
+        <v>-15.53</v>
       </c>
       <c r="N28" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O28" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P28" s="1" t="inlineStr">
@@ -2569,108 +2569,108 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B2" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="C2" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="D2" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="E2" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="F2" s="1" t="n">
         <v>8</v>
-      </c>
-      <c r="C2" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="D2" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="E2" s="1" t="n">
-        <v>23</v>
-      </c>
-      <c r="F2" s="1" t="n">
-        <v>7</v>
       </c>
       <c r="G2" s="1" t="n">
         <v>27</v>
       </c>
       <c r="H2" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I2" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="J2" s="1" t="n">
         <v>5</v>
-      </c>
-      <c r="J2" s="1" t="n">
-        <v>6</v>
       </c>
       <c r="K2" s="1" t="n">
         <v>4</v>
       </c>
       <c r="L2" s="1" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="M2" s="1" t="n">
         <v>25</v>
       </c>
       <c r="N2" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="O2" s="1" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="P2" s="1" t="n">
         <v>26</v>
       </c>
       <c r="Q2" s="1" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="R2" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="S2" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="T2" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="T2" s="1" t="n">
-        <v>19</v>
-      </c>
       <c r="U2" s="1" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="V2" s="1" t="n">
         <v>10</v>
       </c>
       <c r="W2" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="X2" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y2" s="1" t="n">
         <v>1</v>
       </c>
       <c r="Z2" s="1" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AA2" s="1" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="AB2" s="1" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F3" s="1" t="n">
         <v>7</v>
@@ -2682,7 +2682,7 @@
         <v>3</v>
       </c>
       <c r="I3" s="1" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J3" s="1" t="n">
         <v>8</v>
@@ -2691,40 +2691,40 @@
         <v>5</v>
       </c>
       <c r="L3" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="M3" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="N3" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="M3" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="N3" s="1" t="n">
-        <v>10</v>
-      </c>
       <c r="O3" s="1" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="P3" s="1" t="n">
         <v>26</v>
       </c>
       <c r="Q3" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="R3" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="S3" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="T3" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="U3" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="V3" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="W3" s="1" t="n">
         <v>22</v>
-      </c>
-      <c r="R3" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="S3" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="T3" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="U3" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="V3" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="W3" s="1" t="n">
-        <v>23</v>
       </c>
       <c r="X3" s="1" t="n">
         <v>2</v>
@@ -2733,10 +2733,10 @@
         <v>1</v>
       </c>
       <c r="Z3" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA3" s="1" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AB3" s="1" t="n">
         <v>9</v>
@@ -2745,114 +2745,114 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>7</v>
       </c>
       <c r="G4" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="H4" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="I4" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="J4" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="K4" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="L4" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="M4" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="N4" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="O4" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="P4" s="1" t="n">
         <v>26</v>
       </c>
-      <c r="H4" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="I4" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="J4" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="K4" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="L4" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="M4" s="1" t="n">
+      <c r="Q4" s="1" t="n">
         <v>21</v>
-      </c>
-      <c r="N4" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="O4" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="P4" s="1" t="n">
-        <v>27</v>
-      </c>
-      <c r="Q4" s="1" t="n">
-        <v>23</v>
       </c>
       <c r="R4" s="1" t="n">
         <v>20</v>
       </c>
       <c r="S4" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="T4" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="T4" s="1" t="n">
-        <v>15</v>
-      </c>
       <c r="U4" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="V4" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="W4" s="1" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="X4" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y4" s="1" t="n">
         <v>1</v>
       </c>
       <c r="Z4" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA4" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="AA4" s="1" t="n">
-        <v>13</v>
-      </c>
       <c r="AB4" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
         <v>6</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F5" s="1" t="n">
         <v>7</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H5" s="1" t="n">
         <v>2</v>
@@ -2861,46 +2861,46 @@
         <v>4</v>
       </c>
       <c r="J5" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K5" s="1" t="n">
         <v>5</v>
       </c>
       <c r="L5" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="M5" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="N5" s="1" t="n">
         <v>9</v>
-      </c>
-      <c r="M5" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="N5" s="1" t="n">
-        <v>13</v>
       </c>
       <c r="O5" s="1" t="n">
         <v>22</v>
       </c>
       <c r="P5" s="1" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Q5" s="1" t="n">
         <v>23</v>
       </c>
       <c r="R5" s="1" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="S5" s="1" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="T5" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="U5" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="U5" s="1" t="n">
-        <v>15</v>
-      </c>
       <c r="V5" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="W5" s="1" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="X5" s="1" t="n">
         <v>3</v>
@@ -2909,10 +2909,10 @@
         <v>1</v>
       </c>
       <c r="Z5" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AA5" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AB5" s="1" t="n">
         <v>8</v>
@@ -2921,20 +2921,20 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
         <v>6</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>7</v>
@@ -2949,43 +2949,43 @@
         <v>4</v>
       </c>
       <c r="J6" s="1" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K6" s="1" t="n">
         <v>5</v>
       </c>
       <c r="L6" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M6" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N6" s="1" t="n">
         <v>13</v>
       </c>
       <c r="O6" s="1" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="P6" s="1" t="n">
         <v>26</v>
       </c>
       <c r="Q6" s="1" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="R6" s="1" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="S6" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="T6" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="U6" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="T6" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="U6" s="1" t="n">
-        <v>18</v>
-      </c>
       <c r="V6" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="W6" s="1" t="n">
         <v>21</v>
@@ -3000,7 +3000,7 @@
         <v>12</v>
       </c>
       <c r="AA6" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AB6" s="1" t="n">
         <v>8</v>
@@ -3009,23 +3009,23 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E7" s="1" t="n">
         <v>24</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G7" s="1" t="n">
         <v>27</v>
@@ -3037,46 +3037,46 @@
         <v>4</v>
       </c>
       <c r="J7" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K7" s="1" t="n">
         <v>5</v>
       </c>
       <c r="L7" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="M7" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="N7" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="M7" s="1" t="n">
+      <c r="O7" s="1" t="n">
         <v>25</v>
-      </c>
-      <c r="N7" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="O7" s="1" t="n">
-        <v>21</v>
       </c>
       <c r="P7" s="1" t="n">
         <v>26</v>
       </c>
       <c r="Q7" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R7" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="S7" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="T7" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="S7" s="1" t="n">
+      <c r="U7" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="T7" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="U7" s="1" t="n">
-        <v>16</v>
-      </c>
       <c r="V7" s="1" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="W7" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="X7" s="1" t="n">
         <v>3</v>
@@ -3085,10 +3085,10 @@
         <v>1</v>
       </c>
       <c r="Z7" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AA7" s="1" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AB7" s="1" t="n">
         <v>8</v>
@@ -3097,23 +3097,23 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G8" s="1" t="n">
         <v>27</v>
@@ -3125,19 +3125,19 @@
         <v>4</v>
       </c>
       <c r="J8" s="1" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="K8" s="1" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M8" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="N8" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O8" s="1" t="n">
         <v>21</v>
@@ -3146,22 +3146,22 @@
         <v>26</v>
       </c>
       <c r="Q8" s="1" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="R8" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="S8" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="T8" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="S8" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="T8" s="1" t="n">
-        <v>20</v>
-      </c>
       <c r="U8" s="1" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="V8" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="W8" s="1" t="n">
         <v>22</v>
@@ -3173,23 +3173,23 @@
         <v>1</v>
       </c>
       <c r="Z8" s="1" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AA8" s="1" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="AB8" s="1" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C9" s="1" t="n">
         <v>16</v>
@@ -3198,7 +3198,7 @@
         <v>18</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F9" s="1" t="n">
         <v>9</v>
@@ -3210,22 +3210,22 @@
         <v>2</v>
       </c>
       <c r="I9" s="1" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J9" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="K9" s="1" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L9" s="1" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="M9" s="1" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="N9" s="1" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="O9" s="1" t="n">
         <v>21</v>
@@ -3237,22 +3237,22 @@
         <v>25</v>
       </c>
       <c r="R9" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="S9" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="T9" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="S9" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="T9" s="1" t="n">
-        <v>19</v>
-      </c>
       <c r="U9" s="1" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="V9" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="W9" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="X9" s="1" t="n">
         <v>3</v>
@@ -3261,62 +3261,62 @@
         <v>1</v>
       </c>
       <c r="Z9" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AA9" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AB9" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E10" s="1" t="n">
         <v>24</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G10" s="1" t="n">
         <v>27</v>
       </c>
       <c r="H10" s="1" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I10" s="1" t="n">
         <v>6</v>
       </c>
       <c r="J10" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K10" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L10" s="1" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="M10" s="1" t="n">
         <v>22</v>
       </c>
       <c r="N10" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O10" s="1" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="P10" s="1" t="n">
         <v>26</v>
@@ -3325,86 +3325,86 @@
         <v>25</v>
       </c>
       <c r="R10" s="1" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="S10" s="1" t="n">
         <v>5</v>
       </c>
       <c r="T10" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="U10" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="V10" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="V10" s="1" t="n">
-        <v>13</v>
-      </c>
       <c r="W10" s="1" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="X10" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y10" s="1" t="n">
         <v>1</v>
       </c>
       <c r="Z10" s="1" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AA10" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AB10" s="1" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D11" s="1" t="n">
         <v>21</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G11" s="1" t="n">
         <v>27</v>
       </c>
       <c r="H11" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I11" s="1" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J11" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K11" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M11" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N11" s="1" t="n">
         <v>12</v>
       </c>
       <c r="O11" s="1" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="P11" s="1" t="n">
         <v>26</v>
@@ -3413,110 +3413,110 @@
         <v>25</v>
       </c>
       <c r="R11" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="S11" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T11" s="1" t="n">
         <v>20</v>
       </c>
       <c r="U11" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="V11" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="V11" s="1" t="n">
-        <v>11</v>
-      </c>
       <c r="W11" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="X11" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y11" s="1" t="n">
         <v>1</v>
       </c>
       <c r="Z11" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA11" s="1" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AB11" s="1" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="C12" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="C12" s="1" t="n">
-        <v>16</v>
-      </c>
       <c r="D12" s="1" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G12" s="1" t="n">
         <v>27</v>
       </c>
       <c r="H12" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I12" s="1" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J12" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K12" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M12" s="1" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N12" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="O12" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="P12" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q12" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="R12" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="S12" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="T12" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="U12" s="1" t="n">
         <v>13</v>
-      </c>
-      <c r="O12" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="P12" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="Q12" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="R12" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="S12" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="T12" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="U12" s="1" t="n">
-        <v>14</v>
       </c>
       <c r="V12" s="1" t="n">
         <v>11</v>
       </c>
       <c r="W12" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="X12" s="1" t="n">
         <v>3</v>
@@ -3525,29 +3525,29 @@
         <v>1</v>
       </c>
       <c r="Z12" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA12" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="AB12" s="1" t="n">
         <v>9</v>
-      </c>
-      <c r="AA12" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="AB12" s="1" t="n">
-        <v>10</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="C13" s="1" t="n">
         <v>16</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E13" s="1" t="n">
         <v>23</v>
@@ -3565,46 +3565,46 @@
         <v>7</v>
       </c>
       <c r="J13" s="1" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="K13" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L13" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M13" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N13" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O13" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="P13" s="1" t="n">
         <v>25</v>
-      </c>
-      <c r="P13" s="1" t="n">
-        <v>26</v>
       </c>
       <c r="Q13" s="1" t="n">
         <v>24</v>
       </c>
       <c r="R13" s="1" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="S13" s="1" t="n">
         <v>5</v>
       </c>
       <c r="T13" s="1" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="U13" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="V13" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="W13" s="1" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="X13" s="1" t="n">
         <v>3</v>
@@ -3613,10 +3613,10 @@
         <v>1</v>
       </c>
       <c r="Z13" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA13" s="1" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AB13" s="1" t="n">
         <v>10</v>
@@ -3625,59 +3625,59 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F14" s="1" t="n">
         <v>6</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H14" s="1" t="n">
         <v>4</v>
       </c>
       <c r="I14" s="1" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J14" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K14" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M14" s="1" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N14" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="O14" s="1" t="n">
         <v>25</v>
       </c>
       <c r="P14" s="1" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Q14" s="1" t="n">
         <v>24</v>
       </c>
       <c r="R14" s="1" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="S14" s="1" t="n">
         <v>5</v>
@@ -3689,10 +3689,10 @@
         <v>13</v>
       </c>
       <c r="V14" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="W14" s="1" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="X14" s="1" t="n">
         <v>3</v>
@@ -3701,35 +3701,35 @@
         <v>1</v>
       </c>
       <c r="Z14" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA14" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AB14" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="C15" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="C15" s="1" t="n">
-        <v>10</v>
-      </c>
       <c r="D15" s="1" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G15" s="1" t="n">
         <v>26</v>
@@ -3738,22 +3738,22 @@
         <v>4</v>
       </c>
       <c r="I15" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J15" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K15" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L15" s="1" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M15" s="1" t="n">
         <v>23</v>
       </c>
       <c r="N15" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O15" s="1" t="n">
         <v>25</v>
@@ -3765,22 +3765,22 @@
         <v>24</v>
       </c>
       <c r="R15" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="S15" s="1" t="n">
         <v>5</v>
       </c>
       <c r="T15" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="U15" s="1" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="V15" s="1" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="W15" s="1" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="X15" s="1" t="n">
         <v>3</v>
@@ -3792,32 +3792,32 @@
         <v>7</v>
       </c>
       <c r="AA15" s="1" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="AB15" s="1" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F16" s="1" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G16" s="1" t="n">
         <v>26</v>
@@ -3826,49 +3826,49 @@
         <v>4</v>
       </c>
       <c r="I16" s="1" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="J16" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K16" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L16" s="1" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="M16" s="1" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="N16" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O16" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="P16" s="1" t="n">
         <v>27</v>
       </c>
       <c r="Q16" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R16" s="1" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="S16" s="1" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T16" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="U16" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="V16" s="1" t="n">
         <v>18</v>
       </c>
       <c r="W16" s="1" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="X16" s="1" t="n">
         <v>3</v>
@@ -3877,19 +3877,19 @@
         <v>1</v>
       </c>
       <c r="Z16" s="1" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AA16" s="1" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AB16" s="1" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
@@ -3899,7 +3899,7 @@
         <v>11</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E17" s="1" t="n">
         <v>16</v>
@@ -3908,7 +3908,7 @@
         <v>6</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H17" s="1" t="n">
         <v>4</v>
@@ -3923,40 +3923,40 @@
         <v>2</v>
       </c>
       <c r="L17" s="1" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="M17" s="1" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="N17" s="1" t="n">
         <v>14</v>
       </c>
       <c r="O17" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P17" s="1" t="n">
         <v>27</v>
       </c>
       <c r="Q17" s="1" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="R17" s="1" t="n">
         <v>19</v>
       </c>
       <c r="S17" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T17" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="U17" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="V17" s="1" t="n">
         <v>18</v>
       </c>
       <c r="W17" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="X17" s="1" t="n">
         <v>3</v>
@@ -3965,10 +3965,10 @@
         <v>1</v>
       </c>
       <c r="Z17" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA17" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AB17" s="1" t="n">
         <v>7</v>
@@ -3977,29 +3977,29 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F18" s="1" t="n">
         <v>6</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H18" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I18" s="1" t="n">
         <v>5</v>
@@ -4011,16 +4011,16 @@
         <v>2</v>
       </c>
       <c r="L18" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M18" s="1" t="n">
         <v>22</v>
       </c>
       <c r="N18" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="O18" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="P18" s="1" t="n">
         <v>27</v>
@@ -4029,34 +4029,34 @@
         <v>26</v>
       </c>
       <c r="R18" s="1" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="S18" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T18" s="1" t="n">
         <v>21</v>
       </c>
       <c r="U18" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="V18" s="1" t="n">
         <v>18</v>
-      </c>
-      <c r="V18" s="1" t="n">
-        <v>15</v>
       </c>
       <c r="W18" s="1" t="n">
         <v>20</v>
       </c>
       <c r="X18" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y18" s="1" t="n">
         <v>1</v>
       </c>
       <c r="Z18" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA18" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AB18" s="1" t="n">
         <v>7</v>
@@ -4065,7 +4065,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
@@ -4075,22 +4075,22 @@
         <v>10</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F19" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="G19" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="H19" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="G19" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="H19" s="1" t="n">
+      <c r="I19" s="1" t="n">
         <v>5</v>
-      </c>
-      <c r="I19" s="1" t="n">
-        <v>6</v>
       </c>
       <c r="J19" s="1" t="n">
         <v>23</v>
@@ -4099,37 +4099,37 @@
         <v>2</v>
       </c>
       <c r="L19" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M19" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="N19" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="O19" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="P19" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q19" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="R19" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="S19" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="T19" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="N19" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="O19" s="1" t="n">
-        <v>27</v>
-      </c>
-      <c r="P19" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="Q19" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="R19" s="1" t="n">
+      <c r="U19" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="S19" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="T19" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="U19" s="1" t="n">
+      <c r="V19" s="1" t="n">
         <v>15</v>
-      </c>
-      <c r="V19" s="1" t="n">
-        <v>17</v>
       </c>
       <c r="W19" s="1" t="n">
         <v>20</v>
@@ -4141,7 +4141,7 @@
         <v>1</v>
       </c>
       <c r="Z19" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA19" s="1" t="n">
         <v>16</v>
@@ -4153,77 +4153,77 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D20" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="E20" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="E20" s="1" t="n">
-        <v>14</v>
-      </c>
       <c r="F20" s="1" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G20" s="1" t="n">
         <v>24</v>
       </c>
       <c r="H20" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I20" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J20" s="1" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="K20" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L20" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="M20" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="N20" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="O20" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="P20" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q20" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="R20" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="S20" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="T20" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="U20" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="V20" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="M20" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="N20" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="O20" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="P20" s="1" t="n">
-        <v>27</v>
-      </c>
-      <c r="Q20" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="R20" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="S20" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="T20" s="1" t="n">
-        <v>23</v>
-      </c>
-      <c r="U20" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="V20" s="1" t="n">
-        <v>16</v>
-      </c>
       <c r="W20" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="X20" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y20" s="1" t="n">
         <v>1</v>
@@ -4232,26 +4232,26 @@
         <v>8</v>
       </c>
       <c r="AA20" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AB20" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="C21" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="C21" s="1" t="n">
-        <v>10</v>
-      </c>
       <c r="D21" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E21" s="1" t="n">
         <v>14</v>
@@ -4269,34 +4269,34 @@
         <v>7</v>
       </c>
       <c r="J21" s="1" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K21" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L21" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M21" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N21" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="O21" s="1" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P21" s="1" t="n">
         <v>27</v>
       </c>
       <c r="Q21" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="R21" s="1" t="n">
         <v>19</v>
       </c>
       <c r="S21" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T21" s="1" t="n">
         <v>23</v>
@@ -4308,7 +4308,7 @@
         <v>16</v>
       </c>
       <c r="W21" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="X21" s="1" t="n">
         <v>3</v>
@@ -4317,47 +4317,47 @@
         <v>1</v>
       </c>
       <c r="Z21" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA21" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="AB21" s="1" t="n">
         <v>6</v>
-      </c>
-      <c r="AA21" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="AB21" s="1" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
         <v>11</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D22" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="E22" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="E22" s="1" t="n">
-        <v>12</v>
-      </c>
       <c r="F22" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G22" s="1" t="n">
         <v>24</v>
       </c>
       <c r="H22" s="1" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I22" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J22" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K22" s="1" t="n">
         <v>2</v>
@@ -4366,7 +4366,7 @@
         <v>15</v>
       </c>
       <c r="M22" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N22" s="1" t="n">
         <v>13</v>
@@ -4384,7 +4384,7 @@
         <v>19</v>
       </c>
       <c r="S22" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T22" s="1" t="n">
         <v>23</v>
@@ -4393,7 +4393,7 @@
         <v>18</v>
       </c>
       <c r="V22" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="W22" s="1" t="n">
         <v>20</v>
@@ -4405,32 +4405,32 @@
         <v>1</v>
       </c>
       <c r="Z22" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA22" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AB22" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C23" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="D23" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="E23" s="1" t="n">
         <v>12</v>
-      </c>
-      <c r="D23" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="E23" s="1" t="n">
-        <v>13</v>
       </c>
       <c r="F23" s="1" t="n">
         <v>4</v>
@@ -4439,10 +4439,10 @@
         <v>24</v>
       </c>
       <c r="H23" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I23" s="1" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J23" s="1" t="n">
         <v>21</v>
@@ -4451,40 +4451,40 @@
         <v>2</v>
       </c>
       <c r="L23" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="M23" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="N23" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="O23" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="P23" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q23" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="R23" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="S23" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="U23" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="M23" s="1" t="n">
+      <c r="V23" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="W23" s="1" t="n">
         <v>20</v>
-      </c>
-      <c r="N23" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="O23" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="P23" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="Q23" s="1" t="n">
-        <v>27</v>
-      </c>
-      <c r="R23" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="S23" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="T23" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="U23" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="V23" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="W23" s="1" t="n">
-        <v>23</v>
       </c>
       <c r="X23" s="1" t="n">
         <v>3</v>
@@ -4493,38 +4493,38 @@
         <v>1</v>
       </c>
       <c r="Z23" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA23" s="1" t="n">
         <v>16</v>
       </c>
       <c r="AB23" s="1" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C24" s="1" t="n">
         <v>12</v>
       </c>
       <c r="D24" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F24" s="1" t="n">
         <v>4</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H24" s="1" t="n">
         <v>7</v>
@@ -4533,7 +4533,7 @@
         <v>11</v>
       </c>
       <c r="J24" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K24" s="1" t="n">
         <v>2</v>
@@ -4542,25 +4542,25 @@
         <v>18</v>
       </c>
       <c r="M24" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="N24" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="O24" s="1" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="P24" s="1" t="n">
         <v>26</v>
       </c>
       <c r="Q24" s="1" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="R24" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="S24" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T24" s="1" t="n">
         <v>22</v>
@@ -4569,7 +4569,7 @@
         <v>19</v>
       </c>
       <c r="V24" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="W24" s="1" t="n">
         <v>23</v>
@@ -4584,7 +4584,7 @@
         <v>6</v>
       </c>
       <c r="AA24" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AB24" s="1" t="n">
         <v>5</v>
@@ -4593,47 +4593,47 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C25" s="1" t="n">
         <v>12</v>
       </c>
       <c r="D25" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="E25" s="1" t="n">
         <v>15</v>
-      </c>
-      <c r="E25" s="1" t="n">
-        <v>10</v>
       </c>
       <c r="F25" s="1" t="n">
         <v>4</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H25" s="1" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I25" s="1" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J25" s="1" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K25" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L25" s="1" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M25" s="1" t="n">
         <v>21</v>
       </c>
       <c r="N25" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O25" s="1" t="n">
         <v>27</v>
@@ -4642,59 +4642,59 @@
         <v>26</v>
       </c>
       <c r="Q25" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R25" s="1" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="S25" s="1" t="n">
         <v>8</v>
       </c>
       <c r="T25" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="U25" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="V25" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="W25" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="U25" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="V25" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="W25" s="1" t="n">
+      <c r="X25" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y25" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="X25" s="1" t="n">
+      <c r="Z25" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA25" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="AB25" s="1" t="n">
         <v>5</v>
-      </c>
-      <c r="Y25" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z25" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA25" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="AB25" s="1" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
         <v>13</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D26" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F26" s="1" t="n">
         <v>4</v>
@@ -4703,13 +4703,13 @@
         <v>24</v>
       </c>
       <c r="H26" s="1" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I26" s="1" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="J26" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K26" s="1" t="n">
         <v>3</v>
@@ -4733,25 +4733,25 @@
         <v>25</v>
       </c>
       <c r="R26" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="S26" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="T26" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="U26" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="V26" s="1" t="n">
         <v>16</v>
-      </c>
-      <c r="S26" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="T26" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="U26" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="V26" s="1" t="n">
-        <v>15</v>
       </c>
       <c r="W26" s="1" t="n">
         <v>1</v>
       </c>
       <c r="X26" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y26" s="1" t="n">
         <v>2</v>
@@ -4760,26 +4760,26 @@
         <v>7</v>
       </c>
       <c r="AA26" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AB26" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D27" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E27" s="1" t="n">
         <v>9</v>
@@ -4788,22 +4788,22 @@
         <v>4</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H27" s="1" t="n">
         <v>12</v>
       </c>
       <c r="I27" s="1" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J27" s="1" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K27" s="1" t="n">
         <v>3</v>
       </c>
       <c r="L27" s="1" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="M27" s="1" t="n">
         <v>21</v>
@@ -4815,25 +4815,25 @@
         <v>27</v>
       </c>
       <c r="P27" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q27" s="1" t="n">
         <v>25</v>
-      </c>
-      <c r="Q27" s="1" t="n">
-        <v>24</v>
       </c>
       <c r="R27" s="1" t="n">
         <v>16</v>
       </c>
       <c r="S27" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T27" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="U27" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="V27" s="1" t="n">
         <v>15</v>
-      </c>
-      <c r="V27" s="1" t="n">
-        <v>14</v>
       </c>
       <c r="W27" s="1" t="n">
         <v>1</v>
@@ -4857,38 +4857,38 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C28" s="1" t="n">
         <v>10</v>
       </c>
       <c r="D28" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E28" s="1" t="n">
         <v>9</v>
       </c>
       <c r="F28" s="1" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H28" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I28" s="1" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J28" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K28" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L28" s="1" t="n">
         <v>20</v>
@@ -4900,37 +4900,37 @@
         <v>11</v>
       </c>
       <c r="O28" s="1" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P28" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q28" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="Q28" s="1" t="n">
-        <v>25</v>
-      </c>
       <c r="R28" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="S28" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="T28" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="U28" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="V28" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="S28" s="1" t="n">
+      <c r="W28" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="X28" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="T28" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="U28" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="V28" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="W28" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="X28" s="1" t="n">
-        <v>8</v>
-      </c>
       <c r="Y28" s="1" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Z28" s="1" t="n">
         <v>7</v>
@@ -4945,20 +4945,20 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="C29" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="C29" s="1" t="n">
-        <v>11</v>
-      </c>
       <c r="D29" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F29" s="1" t="n">
         <v>2</v>
@@ -4967,10 +4967,10 @@
         <v>27</v>
       </c>
       <c r="H29" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I29" s="1" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J29" s="1" t="n">
         <v>23</v>
@@ -4985,7 +4985,7 @@
         <v>21</v>
       </c>
       <c r="N29" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="O29" s="1" t="n">
         <v>26</v>
@@ -4997,10 +4997,10 @@
         <v>25</v>
       </c>
       <c r="R29" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S29" s="1" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T29" s="1" t="n">
         <v>22</v>
@@ -5009,13 +5009,13 @@
         <v>16</v>
       </c>
       <c r="V29" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="W29" s="1" t="n">
         <v>3</v>
       </c>
       <c r="X29" s="1" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y29" s="1" t="n">
         <v>4</v>
@@ -5033,38 +5033,38 @@
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D30" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="E30" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="F30" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G30" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="H30" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="I30" s="1" t="n">
         <v>19</v>
-      </c>
-      <c r="E30" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="F30" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="G30" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="H30" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="I30" s="1" t="n">
-        <v>18</v>
       </c>
       <c r="J30" s="1" t="n">
         <v>23</v>
       </c>
       <c r="K30" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L30" s="1" t="n">
         <v>20</v>
@@ -5073,10 +5073,10 @@
         <v>21</v>
       </c>
       <c r="N30" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="O30" s="1" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P30" s="1" t="n">
         <v>24</v>
@@ -5085,7 +5085,7 @@
         <v>25</v>
       </c>
       <c r="R30" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="S30" s="1" t="n">
         <v>9</v>
@@ -5094,25 +5094,25 @@
         <v>22</v>
       </c>
       <c r="U30" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="V30" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="W30" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X30" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y30" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="Y30" s="1" t="n">
-        <v>2</v>
-      </c>
       <c r="Z30" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA30" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AB30" s="1" t="n">
         <v>5</v>
@@ -5121,41 +5121,41 @@
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C31" s="1" t="n">
         <v>12</v>
       </c>
       <c r="D31" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F31" s="1" t="n">
         <v>7</v>
       </c>
       <c r="G31" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="H31" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="I31" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="J31" s="1" t="n">
         <v>23</v>
-      </c>
-      <c r="H31" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="I31" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="J31" s="1" t="n">
-        <v>24</v>
       </c>
       <c r="K31" s="1" t="n">
         <v>3</v>
       </c>
       <c r="L31" s="1" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M31" s="1" t="n">
         <v>21</v>
@@ -5167,25 +5167,25 @@
         <v>27</v>
       </c>
       <c r="P31" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q31" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="Q31" s="1" t="n">
-        <v>26</v>
-      </c>
       <c r="R31" s="1" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="S31" s="1" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="T31" s="1" t="n">
         <v>22</v>
       </c>
       <c r="U31" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="V31" s="1" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="W31" s="1" t="n">
         <v>1</v>
@@ -5200,50 +5200,50 @@
         <v>8</v>
       </c>
       <c r="AA31" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AB31" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="C32" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D32" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="E32" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="F32" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C32" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="D32" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="E32" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="F32" s="1" t="n">
-        <v>5</v>
-      </c>
       <c r="G32" s="1" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="H32" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I32" s="1" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J32" s="1" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K32" s="1" t="n">
         <v>3</v>
       </c>
       <c r="L32" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M32" s="1" t="n">
         <v>21</v>
@@ -5255,25 +5255,25 @@
         <v>27</v>
       </c>
       <c r="P32" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Q32" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="R32" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="S32" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="S32" s="1" t="n">
-        <v>19</v>
-      </c>
       <c r="T32" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="U32" s="1" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="V32" s="1" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="W32" s="1" t="n">
         <v>1</v>
@@ -5285,10 +5285,10 @@
         <v>2</v>
       </c>
       <c r="Z32" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA32" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AB32" s="1" t="n">
         <v>6</v>
@@ -5297,20 +5297,20 @@
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C33" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="D33" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="D33" s="1" t="n">
-        <v>20</v>
-      </c>
       <c r="E33" s="1" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F33" s="1" t="n">
         <v>5</v>
@@ -5319,10 +5319,10 @@
         <v>26</v>
       </c>
       <c r="H33" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I33" s="1" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J33" s="1" t="n">
         <v>22</v>
@@ -5331,34 +5331,34 @@
         <v>3</v>
       </c>
       <c r="L33" s="1" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M33" s="1" t="n">
         <v>21</v>
       </c>
       <c r="N33" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="O33" s="1" t="n">
         <v>27</v>
       </c>
       <c r="P33" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q33" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="Q33" s="1" t="n">
-        <v>24</v>
-      </c>
       <c r="R33" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="S33" s="1" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="T33" s="1" t="n">
         <v>23</v>
       </c>
       <c r="U33" s="1" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="V33" s="1" t="n">
         <v>17</v>
@@ -5373,10 +5373,10 @@
         <v>2</v>
       </c>
       <c r="Z33" s="1" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AA33" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AB33" s="1" t="n">
         <v>6</v>
@@ -5385,44 +5385,44 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D34" s="1" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F34" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G34" s="1" t="n">
         <v>26</v>
       </c>
       <c r="H34" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I34" s="1" t="n">
         <v>10</v>
       </c>
       <c r="J34" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K34" s="1" t="n">
         <v>3</v>
       </c>
       <c r="L34" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M34" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N34" s="1" t="n">
         <v>11</v>
@@ -5437,10 +5437,10 @@
         <v>24</v>
       </c>
       <c r="R34" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="S34" s="1" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="T34" s="1" t="n">
         <v>23</v>
@@ -5449,13 +5449,13 @@
         <v>18</v>
       </c>
       <c r="V34" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="W34" s="1" t="n">
         <v>1</v>
       </c>
       <c r="X34" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y34" s="1" t="n">
         <v>2</v>
@@ -5464,7 +5464,7 @@
         <v>7</v>
       </c>
       <c r="AA34" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AB34" s="1" t="n">
         <v>6</v>
@@ -5473,38 +5473,38 @@
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
         <v>9</v>
       </c>
       <c r="C35" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D35" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="E35" s="1" t="n">
         <v>13</v>
-      </c>
-      <c r="D35" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="E35" s="1" t="n">
-        <v>11</v>
       </c>
       <c r="F35" s="1" t="n">
         <v>4</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H35" s="1" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I35" s="1" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J35" s="1" t="n">
         <v>21</v>
       </c>
       <c r="K35" s="1" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="L35" s="1" t="n">
         <v>20</v>
@@ -5513,28 +5513,28 @@
         <v>22</v>
       </c>
       <c r="N35" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="O35" s="1" t="n">
         <v>27</v>
       </c>
       <c r="P35" s="1" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Q35" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R35" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="S35" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="T35" s="1" t="n">
         <v>23</v>
       </c>
       <c r="U35" s="1" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="V35" s="1" t="n">
         <v>15</v>
@@ -5549,10 +5549,10 @@
         <v>2</v>
       </c>
       <c r="Z35" s="1" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AA35" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AB35" s="1" t="n">
         <v>6</v>
@@ -5561,47 +5561,47 @@
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B36" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C36" s="1" t="n">
         <v>13</v>
       </c>
       <c r="D36" s="1" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="F36" s="1" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H36" s="1" t="n">
         <v>3</v>
       </c>
       <c r="I36" s="1" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J36" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="K36" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="L36" s="1" t="n">
         <v>20</v>
-      </c>
-      <c r="K36" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="L36" s="1" t="n">
-        <v>18</v>
       </c>
       <c r="M36" s="1" t="n">
         <v>22</v>
       </c>
       <c r="N36" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O36" s="1" t="n">
         <v>27</v>
@@ -5613,25 +5613,25 @@
         <v>25</v>
       </c>
       <c r="R36" s="1" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="S36" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="T36" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="U36" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="T36" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="U36" s="1" t="n">
-        <v>12</v>
-      </c>
       <c r="V36" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="W36" s="1" t="n">
         <v>1</v>
       </c>
       <c r="X36" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y36" s="1" t="n">
         <v>2</v>
@@ -5649,44 +5649,44 @@
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B37" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D37" s="1" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F37" s="1" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G37" s="1" t="n">
         <v>23</v>
       </c>
       <c r="H37" s="1" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I37" s="1" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J37" s="1" t="n">
         <v>20</v>
       </c>
       <c r="K37" s="1" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L37" s="1" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="M37" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N37" s="1" t="n">
         <v>11</v>
@@ -5698,86 +5698,86 @@
         <v>26</v>
       </c>
       <c r="Q37" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="R37" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="S37" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="T37" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="R37" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="S37" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="T37" s="1" t="n">
-        <v>25</v>
-      </c>
       <c r="U37" s="1" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="V37" s="1" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="W37" s="1" t="n">
         <v>1</v>
       </c>
       <c r="X37" s="1" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Y37" s="1" t="n">
         <v>2</v>
       </c>
       <c r="Z37" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA37" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AB37" s="1" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B38" s="1" t="n">
         <v>10</v>
       </c>
       <c r="C38" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="D38" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="D38" s="1" t="n">
-        <v>11</v>
-      </c>
       <c r="E38" s="1" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F38" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G38" s="1" t="n">
         <v>23</v>
       </c>
       <c r="H38" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="I38" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="J38" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="K38" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="I38" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="J38" s="1" t="n">
+      <c r="L38" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="M38" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="K38" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="L38" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="M38" s="1" t="n">
-        <v>22</v>
-      </c>
       <c r="N38" s="1" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="O38" s="1" t="n">
         <v>27</v>
@@ -5789,7 +5789,7 @@
         <v>24</v>
       </c>
       <c r="R38" s="1" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="S38" s="1" t="n">
         <v>19</v>
@@ -5798,16 +5798,16 @@
         <v>25</v>
       </c>
       <c r="U38" s="1" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="V38" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="W38" s="1" t="n">
         <v>1</v>
       </c>
       <c r="X38" s="1" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Y38" s="1" t="n">
         <v>2</v>
@@ -5816,23 +5816,23 @@
         <v>9</v>
       </c>
       <c r="AA38" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AB38" s="1" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B39" s="1" t="n">
         <v>10</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D39" s="1" t="n">
         <v>11</v>
@@ -5841,7 +5841,7 @@
         <v>20</v>
       </c>
       <c r="F39" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G39" s="1" t="n">
         <v>23</v>
@@ -5853,19 +5853,19 @@
         <v>7</v>
       </c>
       <c r="J39" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K39" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L39" s="1" t="n">
         <v>13</v>
       </c>
       <c r="M39" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N39" s="1" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="O39" s="1" t="n">
         <v>27</v>
@@ -5877,19 +5877,19 @@
         <v>24</v>
       </c>
       <c r="R39" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="S39" s="1" t="n">
         <v>19</v>
-      </c>
-      <c r="S39" s="1" t="n">
-        <v>18</v>
       </c>
       <c r="T39" s="1" t="n">
         <v>25</v>
       </c>
       <c r="U39" s="1" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="V39" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="W39" s="1" t="n">
         <v>1</v>
@@ -5904,7 +5904,7 @@
         <v>9</v>
       </c>
       <c r="AA39" s="1" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AB39" s="1" t="n">
         <v>8</v>
@@ -5913,44 +5913,44 @@
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B40" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="C40" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="C40" s="1" t="n">
-        <v>16</v>
-      </c>
       <c r="D40" s="1" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F40" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G40" s="1" t="n">
         <v>23</v>
       </c>
       <c r="H40" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I40" s="1" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J40" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="K40" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="L40" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="M40" s="1" t="n">
         <v>21</v>
-      </c>
-      <c r="K40" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="L40" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="M40" s="1" t="n">
-        <v>20</v>
       </c>
       <c r="N40" s="1" t="n">
         <v>12</v>
@@ -5974,19 +5974,19 @@
         <v>25</v>
       </c>
       <c r="U40" s="1" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="V40" s="1" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="W40" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="X40" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="X40" s="1" t="n">
-        <v>7</v>
-      </c>
       <c r="Y40" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Z40" s="1" t="n">
         <v>9</v>
@@ -6001,23 +6001,23 @@
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B41" s="1" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C41" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="D41" s="1" t="n">
         <v>14</v>
-      </c>
-      <c r="D41" s="1" t="n">
-        <v>13</v>
       </c>
       <c r="E41" s="1" t="n">
         <v>22</v>
       </c>
       <c r="F41" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G41" s="1" t="n">
         <v>23</v>
@@ -6029,16 +6029,16 @@
         <v>3</v>
       </c>
       <c r="J41" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K41" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L41" s="1" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="M41" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="N41" s="1" t="n">
         <v>12</v>
@@ -6053,47 +6053,47 @@
         <v>24</v>
       </c>
       <c r="R41" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="S41" s="1" t="n">
         <v>18</v>
-      </c>
-      <c r="S41" s="1" t="n">
-        <v>19</v>
       </c>
       <c r="T41" s="1" t="n">
         <v>25</v>
       </c>
       <c r="U41" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="V41" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="W41" s="1" t="n">
         <v>4</v>
       </c>
       <c r="X41" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y41" s="1" t="n">
         <v>5</v>
       </c>
       <c r="Z41" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA41" s="1" t="n">
         <v>17</v>
       </c>
       <c r="AB41" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B42" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C42" s="1" t="n">
         <v>14</v>
@@ -6102,31 +6102,31 @@
         <v>13</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F42" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G42" s="1" t="n">
         <v>23</v>
       </c>
       <c r="H42" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I42" s="1" t="n">
         <v>3</v>
       </c>
       <c r="J42" s="1" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K42" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L42" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M42" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N42" s="1" t="n">
         <v>12</v>
@@ -6141,19 +6141,19 @@
         <v>24</v>
       </c>
       <c r="R42" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="S42" s="1" t="n">
         <v>19</v>
-      </c>
-      <c r="S42" s="1" t="n">
-        <v>18</v>
       </c>
       <c r="T42" s="1" t="n">
         <v>25</v>
       </c>
       <c r="U42" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="V42" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="W42" s="1" t="n">
         <v>4</v>
@@ -6165,10 +6165,10 @@
         <v>5</v>
       </c>
       <c r="Z42" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA42" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AB42" s="1" t="n">
         <v>9</v>
@@ -6177,26 +6177,26 @@
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B43" s="1" t="n">
         <v>11</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D43" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F43" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H43" s="1" t="n">
         <v>2</v>
@@ -6205,13 +6205,13 @@
         <v>3</v>
       </c>
       <c r="J43" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K43" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L43" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M43" s="1" t="n">
         <v>20</v>
@@ -6226,16 +6226,16 @@
         <v>26</v>
       </c>
       <c r="Q43" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="R43" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="S43" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="T43" s="1" t="n">
         <v>25</v>
-      </c>
-      <c r="R43" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="S43" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="T43" s="1" t="n">
-        <v>24</v>
       </c>
       <c r="U43" s="1" t="n">
         <v>10</v>
@@ -6253,35 +6253,35 @@
         <v>5</v>
       </c>
       <c r="Z43" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA43" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="AB43" s="1" t="n">
         <v>9</v>
-      </c>
-      <c r="AA43" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="AB43" s="1" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B44" s="1" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D44" s="1" t="n">
         <v>14</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F44" s="1" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G44" s="1" t="n">
         <v>21</v>
@@ -6299,7 +6299,7 @@
         <v>1</v>
       </c>
       <c r="L44" s="1" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="M44" s="1" t="n">
         <v>20</v>
@@ -6311,56 +6311,56 @@
         <v>27</v>
       </c>
       <c r="P44" s="1" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="Q44" s="1" t="n">
         <v>25</v>
       </c>
       <c r="R44" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="S44" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="T44" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="U44" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="T44" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="U44" s="1" t="n">
+      <c r="V44" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="W44" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="V44" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="W44" s="1" t="n">
+      <c r="X44" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="X44" s="1" t="n">
-        <v>11</v>
-      </c>
       <c r="Y44" s="1" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Z44" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA44" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="AB44" s="1" t="n">
         <v>8</v>
-      </c>
-      <c r="AA44" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="AB44" s="1" t="n">
-        <v>9</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B45" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="C45" s="1" t="n">
         <v>17</v>
-      </c>
-      <c r="C45" s="1" t="n">
-        <v>15</v>
       </c>
       <c r="D45" s="1" t="n">
         <v>14</v>
@@ -6372,7 +6372,7 @@
         <v>5</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="H45" s="1" t="n">
         <v>2</v>
@@ -6381,25 +6381,25 @@
         <v>3</v>
       </c>
       <c r="J45" s="1" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K45" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L45" s="1" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="M45" s="1" t="n">
         <v>20</v>
       </c>
       <c r="N45" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="O45" s="1" t="n">
         <v>27</v>
       </c>
       <c r="P45" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q45" s="1" t="n">
         <v>25</v>
@@ -6408,47 +6408,47 @@
         <v>16</v>
       </c>
       <c r="S45" s="1" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T45" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="U45" s="1" t="n">
         <v>4</v>
       </c>
       <c r="V45" s="1" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="W45" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X45" s="1" t="n">
         <v>11</v>
       </c>
       <c r="Y45" s="1" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Z45" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA45" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="AB45" s="1" t="n">
         <v>9</v>
-      </c>
-      <c r="AA45" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="AB45" s="1" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B46" s="1" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D46" s="1" t="n">
         <v>14</v>
@@ -6469,34 +6469,34 @@
         <v>3</v>
       </c>
       <c r="J46" s="1" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K46" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L46" s="1" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M46" s="1" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="N46" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="O46" s="1" t="n">
         <v>27</v>
       </c>
       <c r="P46" s="1" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q46" s="1" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="R46" s="1" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="S46" s="1" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T46" s="1" t="n">
         <v>21</v>
@@ -6508,13 +6508,13 @@
         <v>12</v>
       </c>
       <c r="W46" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X46" s="1" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="Y46" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z46" s="1" t="n">
         <v>9</v>
@@ -6523,59 +6523,59 @@
         <v>19</v>
       </c>
       <c r="AB46" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B47" s="1" t="n">
         <v>25</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D47" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F47" s="1" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G47" s="1" t="n">
         <v>24</v>
       </c>
       <c r="H47" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I47" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="J47" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="K47" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="I47" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="J47" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="K47" s="1" t="n">
-        <v>3</v>
-      </c>
       <c r="L47" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M47" s="1" t="n">
         <v>18</v>
       </c>
       <c r="N47" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="O47" s="1" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P47" s="1" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="Q47" s="1" t="n">
         <v>23</v>
@@ -6584,56 +6584,56 @@
         <v>13</v>
       </c>
       <c r="S47" s="1" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T47" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="U47" s="1" t="n">
         <v>4</v>
       </c>
       <c r="V47" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="W47" s="1" t="n">
         <v>6</v>
       </c>
       <c r="X47" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Y47" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z47" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA47" s="1" t="n">
         <v>19</v>
       </c>
       <c r="AB47" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B48" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="C48" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="D48" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="E48" s="1" t="n">
         <v>27</v>
       </c>
-      <c r="C48" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="D48" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="E48" s="1" t="n">
-        <v>25</v>
-      </c>
       <c r="F48" s="1" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G48" s="1" t="n">
         <v>24</v>
@@ -6642,61 +6642,61 @@
         <v>1</v>
       </c>
       <c r="I48" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="J48" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="K48" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="J48" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="K48" s="1" t="n">
-        <v>2</v>
-      </c>
       <c r="L48" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M48" s="1" t="n">
         <v>18</v>
       </c>
       <c r="N48" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="O48" s="1" t="n">
         <v>26</v>
       </c>
       <c r="P48" s="1" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q48" s="1" t="n">
         <v>23</v>
       </c>
       <c r="R48" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="S48" s="1" t="n">
         <v>5</v>
       </c>
       <c r="T48" s="1" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="U48" s="1" t="n">
         <v>4</v>
       </c>
       <c r="V48" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="W48" s="1" t="n">
         <v>6</v>
       </c>
       <c r="X48" s="1" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="Y48" s="1" t="n">
         <v>7</v>
       </c>
       <c r="Z48" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA48" s="1" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AB48" s="1" t="n">
         <v>8</v>
@@ -6705,47 +6705,47 @@
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B49" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C49" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="D49" s="1" t="n">
         <v>13</v>
-      </c>
-      <c r="D49" s="1" t="n">
-        <v>6</v>
       </c>
       <c r="E49" s="1" t="n">
         <v>25</v>
       </c>
       <c r="F49" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H49" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I49" s="1" t="n">
         <v>3</v>
       </c>
       <c r="J49" s="1" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="K49" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L49" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M49" s="1" t="n">
         <v>18</v>
       </c>
       <c r="N49" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="O49" s="1" t="n">
         <v>26</v>
@@ -6763,53 +6763,53 @@
         <v>5</v>
       </c>
       <c r="T49" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="U49" s="1" t="n">
         <v>4</v>
       </c>
       <c r="V49" s="1" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="W49" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X49" s="1" t="n">
         <v>17</v>
       </c>
       <c r="Y49" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z49" s="1" t="n">
         <v>9</v>
       </c>
       <c r="AA49" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AB49" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B50" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C50" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="D50" s="1" t="n">
         <v>6</v>
-      </c>
-      <c r="D50" s="1" t="n">
-        <v>5</v>
       </c>
       <c r="E50" s="1" t="n">
         <v>25</v>
       </c>
       <c r="F50" s="1" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="G50" s="1" t="n">
         <v>22</v>
@@ -6833,22 +6833,22 @@
         <v>18</v>
       </c>
       <c r="N50" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="O50" s="1" t="n">
         <v>26</v>
       </c>
       <c r="P50" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Q50" s="1" t="n">
         <v>23</v>
       </c>
       <c r="R50" s="1" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="S50" s="1" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T50" s="1" t="n">
         <v>21</v>
@@ -6857,50 +6857,50 @@
         <v>4</v>
       </c>
       <c r="V50" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="W50" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X50" s="1" t="n">
         <v>17</v>
       </c>
       <c r="Y50" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z50" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="Z50" s="1" t="n">
+      <c r="AA50" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="AB50" s="1" t="n">
         <v>10</v>
-      </c>
-      <c r="AA50" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="AB50" s="1" t="n">
-        <v>11</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B51" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D51" s="1" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E51" s="1" t="n">
         <v>25</v>
       </c>
       <c r="F51" s="1" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H51" s="1" t="n">
         <v>2</v>
@@ -6918,7 +6918,7 @@
         <v>16</v>
       </c>
       <c r="M51" s="1" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N51" s="1" t="n">
         <v>14</v>
@@ -6927,68 +6927,68 @@
         <v>26</v>
       </c>
       <c r="P51" s="1" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="Q51" s="1" t="n">
         <v>23</v>
       </c>
       <c r="R51" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="S51" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="T51" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="U51" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="V51" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="W51" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="X51" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y51" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="S51" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="T51" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="U51" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="V51" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="W51" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="X51" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="Y51" s="1" t="n">
-        <v>5</v>
-      </c>
       <c r="Z51" s="1" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AA51" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AB51" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B52" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D52" s="1" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E52" s="1" t="n">
         <v>25</v>
       </c>
       <c r="F52" s="1" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H52" s="1" t="n">
         <v>2</v>
@@ -6997,25 +6997,25 @@
         <v>3</v>
       </c>
       <c r="J52" s="1" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K52" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L52" s="1" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="M52" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N52" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O52" s="1" t="n">
         <v>26</v>
       </c>
       <c r="P52" s="1" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="Q52" s="1" t="n">
         <v>23</v>
@@ -7024,31 +7024,31 @@
         <v>9</v>
       </c>
       <c r="S52" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="T52" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="U52" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="T52" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="U52" s="1" t="n">
-        <v>7</v>
-      </c>
       <c r="V52" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="W52" s="1" t="n">
         <v>4</v>
       </c>
       <c r="X52" s="1" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Y52" s="1" t="n">
         <v>5</v>
       </c>
       <c r="Z52" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA52" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AB52" s="1" t="n">
         <v>10</v>
@@ -7057,23 +7057,23 @@
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B53" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D53" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F53" s="1" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G53" s="1" t="n">
         <v>20</v>
@@ -7085,13 +7085,13 @@
         <v>3</v>
       </c>
       <c r="J53" s="1" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="K53" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L53" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="M53" s="1" t="n">
         <v>18</v>
@@ -7100,10 +7100,10 @@
         <v>15</v>
       </c>
       <c r="O53" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P53" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Q53" s="1" t="n">
         <v>23</v>
@@ -7118,25 +7118,25 @@
         <v>24</v>
       </c>
       <c r="U53" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V53" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="W53" s="1" t="n">
         <v>4</v>
       </c>
       <c r="X53" s="1" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Y53" s="1" t="n">
         <v>5</v>
       </c>
       <c r="Z53" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA53" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AB53" s="1" t="n">
         <v>10</v>
@@ -7145,26 +7145,26 @@
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B54" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C54" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="D54" s="1" t="n">
         <v>16</v>
-      </c>
-      <c r="D54" s="1" t="n">
-        <v>13</v>
       </c>
       <c r="E54" s="1" t="n">
         <v>26</v>
       </c>
       <c r="F54" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="G54" s="1" t="n">
         <v>20</v>
-      </c>
-      <c r="G54" s="1" t="n">
-        <v>22</v>
       </c>
       <c r="H54" s="1" t="n">
         <v>2</v>
@@ -7185,13 +7185,13 @@
         <v>18</v>
       </c>
       <c r="N54" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="O54" s="1" t="n">
         <v>25</v>
       </c>
       <c r="P54" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Q54" s="1" t="n">
         <v>23</v>
@@ -7209,7 +7209,7 @@
         <v>8</v>
       </c>
       <c r="V54" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="W54" s="1" t="n">
         <v>4</v>
@@ -7224,7 +7224,7 @@
         <v>7</v>
       </c>
       <c r="AA54" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AB54" s="1" t="n">
         <v>10</v>
@@ -7233,7 +7233,7 @@
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B55" s="1" t="n">
@@ -7243,16 +7243,16 @@
         <v>16</v>
       </c>
       <c r="D55" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F55" s="1" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H55" s="1" t="n">
         <v>2</v>
@@ -7270,22 +7270,22 @@
         <v>11</v>
       </c>
       <c r="M55" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="N55" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="N55" s="1" t="n">
-        <v>15</v>
-      </c>
       <c r="O55" s="1" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P55" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="Q55" s="1" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="R55" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="S55" s="1" t="n">
         <v>6</v>
@@ -7297,13 +7297,13 @@
         <v>8</v>
       </c>
       <c r="V55" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="W55" s="1" t="n">
         <v>4</v>
       </c>
       <c r="X55" s="1" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="Y55" s="1" t="n">
         <v>5</v>
@@ -7312,71 +7312,71 @@
         <v>7</v>
       </c>
       <c r="AA55" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AB55" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B56" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D56" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F56" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="G56" s="1" t="n">
         <v>20</v>
-      </c>
-      <c r="G56" s="1" t="n">
-        <v>17</v>
       </c>
       <c r="H56" s="1" t="n">
         <v>2</v>
       </c>
       <c r="I56" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J56" s="1" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K56" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L56" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="M56" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N56" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="O56" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="P56" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="O56" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="P56" s="1" t="n">
-        <v>11</v>
-      </c>
       <c r="Q56" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R56" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="S56" s="1" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T56" s="1" t="n">
         <v>24</v>
@@ -7388,132 +7388,132 @@
         <v>13</v>
       </c>
       <c r="W56" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="X56" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y56" s="1" t="n">
         <v>5</v>
-      </c>
-      <c r="X56" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="Y56" s="1" t="n">
-        <v>6</v>
       </c>
       <c r="Z56" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AA56" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AB56" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B57" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D57" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E57" s="1" t="n">
         <v>26</v>
       </c>
       <c r="F57" s="1" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H57" s="1" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I57" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J57" s="1" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="K57" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L57" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M57" s="1" t="n">
         <v>18</v>
       </c>
       <c r="N57" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O57" s="1" t="n">
         <v>25</v>
       </c>
       <c r="P57" s="1" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="Q57" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="R57" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="S57" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T57" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="U57" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V57" s="1" t="n">
         <v>13</v>
       </c>
       <c r="W57" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X57" s="1" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="Y57" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z57" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AA57" s="1" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AB57" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B58" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D58" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E58" s="1" t="n">
         <v>26</v>
       </c>
       <c r="F58" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G58" s="1" t="n">
         <v>20</v>
@@ -7522,7 +7522,7 @@
         <v>6</v>
       </c>
       <c r="I58" s="1" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J58" s="1" t="n">
         <v>19</v>
@@ -7543,10 +7543,10 @@
         <v>25</v>
       </c>
       <c r="P58" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Q58" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R58" s="1" t="n">
         <v>10</v>
@@ -7555,53 +7555,53 @@
         <v>2</v>
       </c>
       <c r="T58" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="U58" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="V58" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="W58" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="X58" s="1" t="n">
         <v>24</v>
-      </c>
-      <c r="U58" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="V58" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="W58" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="X58" s="1" t="n">
-        <v>23</v>
       </c>
       <c r="Y58" s="1" t="n">
         <v>5</v>
       </c>
       <c r="Z58" s="1" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AA58" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AB58" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B59" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D59" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E59" s="1" t="n">
         <v>26</v>
       </c>
       <c r="F59" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G59" s="1" t="n">
         <v>20</v>
@@ -7610,25 +7610,25 @@
         <v>6</v>
       </c>
       <c r="I59" s="1" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J59" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K59" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L59" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M59" s="1" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N59" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O59" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="P59" s="1" t="n">
         <v>17</v>
@@ -7637,31 +7637,31 @@
         <v>22</v>
       </c>
       <c r="R59" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="S59" s="1" t="n">
         <v>2</v>
       </c>
       <c r="T59" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="U59" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="V59" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="W59" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="X59" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="U59" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="V59" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="W59" s="1" t="n">
+      <c r="Y59" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z59" s="1" t="n">
         <v>4</v>
-      </c>
-      <c r="X59" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="Y59" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z59" s="1" t="n">
-        <v>5</v>
       </c>
       <c r="AA59" s="1" t="n">
         <v>21</v>
@@ -7673,32 +7673,32 @@
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B60" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D60" s="1" t="n">
         <v>11</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F60" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G60" s="1" t="n">
         <v>20</v>
       </c>
       <c r="H60" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="I60" s="1" t="n">
         <v>3</v>
-      </c>
-      <c r="I60" s="1" t="n">
-        <v>12</v>
       </c>
       <c r="J60" s="1" t="n">
         <v>18</v>
@@ -7707,13 +7707,13 @@
         <v>1</v>
       </c>
       <c r="L60" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M60" s="1" t="n">
         <v>19</v>
       </c>
       <c r="N60" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O60" s="1" t="n">
         <v>24</v>
@@ -7725,28 +7725,28 @@
         <v>22</v>
       </c>
       <c r="R60" s="1" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="S60" s="1" t="n">
         <v>2</v>
       </c>
       <c r="T60" s="1" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="U60" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V60" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="W60" s="1" t="n">
         <v>4</v>
       </c>
       <c r="X60" s="1" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Y60" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z60" s="1" t="n">
         <v>5</v>
@@ -7755,77 +7755,77 @@
         <v>21</v>
       </c>
       <c r="AB60" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B61" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C61" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="D61" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="D61" s="1" t="n">
-        <v>10</v>
-      </c>
       <c r="E61" s="1" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F61" s="1" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G61" s="1" t="n">
         <v>20</v>
       </c>
       <c r="H61" s="1" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="I61" s="1" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="J61" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K61" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L61" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M61" s="1" t="n">
         <v>19</v>
       </c>
       <c r="N61" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O61" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P61" s="1" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Q61" s="1" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="R61" s="1" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="S61" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T61" s="1" t="n">
         <v>26</v>
       </c>
       <c r="U61" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="V61" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="W61" s="1" t="n">
         <v>4</v>
@@ -7834,7 +7834,7 @@
         <v>23</v>
       </c>
       <c r="Y61" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z61" s="1" t="n">
         <v>5</v>
@@ -7843,62 +7843,62 @@
         <v>21</v>
       </c>
       <c r="AB61" s="1" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B62" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D62" s="1" t="n">
         <v>10</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F62" s="1" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="G62" s="1" t="n">
         <v>20</v>
       </c>
       <c r="H62" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I62" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J62" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K62" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L62" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M62" s="1" t="n">
         <v>19</v>
       </c>
       <c r="N62" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O62" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="P62" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q62" s="1" t="n">
         <v>24</v>
-      </c>
-      <c r="P62" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q62" s="1" t="n">
-        <v>21</v>
       </c>
       <c r="R62" s="1" t="n">
         <v>3</v>
@@ -7907,10 +7907,10 @@
         <v>1</v>
       </c>
       <c r="T62" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="U62" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V62" s="1" t="n">
         <v>12</v>
@@ -7919,7 +7919,7 @@
         <v>4</v>
       </c>
       <c r="X62" s="1" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="Y62" s="1" t="n">
         <v>6</v>
@@ -7928,50 +7928,50 @@
         <v>5</v>
       </c>
       <c r="AA62" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AB62" s="1" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B63" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D63" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F63" s="1" t="n">
         <v>18</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H63" s="1" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="I63" s="1" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="J63" s="1" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="K63" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L63" s="1" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="M63" s="1" t="n">
         <v>19</v>
@@ -7980,37 +7980,37 @@
         <v>17</v>
       </c>
       <c r="O63" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P63" s="1" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="Q63" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R63" s="1" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="S63" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T63" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="U63" s="1" t="n">
         <v>7</v>
       </c>
       <c r="V63" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="W63" s="1" t="n">
         <v>4</v>
       </c>
       <c r="X63" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Y63" s="1" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Z63" s="1" t="n">
         <v>5</v>
@@ -8025,7 +8025,7 @@
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B64" s="1" t="n">
@@ -8035,10 +8035,10 @@
         <v>16</v>
       </c>
       <c r="D64" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F64" s="1" t="n">
         <v>18</v>
@@ -8047,19 +8047,19 @@
         <v>21</v>
       </c>
       <c r="H64" s="1" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="I64" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J64" s="1" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K64" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L64" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M64" s="1" t="n">
         <v>19</v>
@@ -8077,13 +8077,13 @@
         <v>20</v>
       </c>
       <c r="R64" s="1" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="S64" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T64" s="1" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="U64" s="1" t="n">
         <v>7</v>
@@ -8092,101 +8092,101 @@
         <v>15</v>
       </c>
       <c r="W64" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X64" s="1" t="n">
         <v>25</v>
       </c>
       <c r="Y64" s="1" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="Z64" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA64" s="1" t="n">
         <v>22</v>
       </c>
       <c r="AB64" s="1" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B65" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D65" s="1" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E65" s="1" t="n">
         <v>24</v>
       </c>
       <c r="F65" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G65" s="1" t="n">
         <v>21</v>
       </c>
       <c r="H65" s="1" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I65" s="1" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="J65" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K65" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L65" s="1" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="M65" s="1" t="n">
         <v>19</v>
       </c>
       <c r="N65" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O65" s="1" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="P65" s="1" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="Q65" s="1" t="n">
         <v>20</v>
       </c>
       <c r="R65" s="1" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="S65" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T65" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="U65" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V65" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="W65" s="1" t="n">
         <v>3</v>
       </c>
       <c r="X65" s="1" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Y65" s="1" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="Z65" s="1" t="n">
         <v>4</v>
@@ -8201,41 +8201,41 @@
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B66" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D66" s="1" t="n">
         <v>8</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F66" s="1" t="n">
         <v>16</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H66" s="1" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="I66" s="1" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="J66" s="1" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="K66" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L66" s="1" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="M66" s="1" t="n">
         <v>19</v>
@@ -8250,7 +8250,7 @@
         <v>12</v>
       </c>
       <c r="Q66" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="R66" s="1" t="n">
         <v>7</v>
@@ -8259,13 +8259,13 @@
         <v>1</v>
       </c>
       <c r="T66" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="U66" s="1" t="n">
         <v>6</v>
       </c>
       <c r="V66" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="W66" s="1" t="n">
         <v>3</v>
@@ -8274,7 +8274,7 @@
         <v>23</v>
       </c>
       <c r="Y66" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Z66" s="1" t="n">
         <v>4</v>
@@ -8289,68 +8289,68 @@
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B67" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D67" s="1" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E67" s="1" t="n">
         <v>25</v>
       </c>
       <c r="F67" s="1" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H67" s="1" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I67" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J67" s="1" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="K67" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L67" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="M67" s="1" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="N67" s="1" t="n">
         <v>18</v>
       </c>
       <c r="O67" s="1" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="P67" s="1" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="Q67" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R67" s="1" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="S67" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T67" s="1" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="U67" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V67" s="1" t="n">
         <v>14</v>
@@ -8359,19 +8359,19 @@
         <v>3</v>
       </c>
       <c r="X67" s="1" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="Y67" s="1" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Z67" s="1" t="n">
         <v>4</v>
       </c>
       <c r="AA67" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AB67" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/NSE_Sector_Monitor.xlsx
+++ b/NSE_Sector_Monitor.xlsx
@@ -568,22 +568,22 @@
         <v>0</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>14.14</v>
+        <v>13.93</v>
       </c>
       <c r="H2" s="1" t="n">
-        <v>-5.54</v>
+        <v>-7.32</v>
       </c>
       <c r="I2" s="1" t="n">
-        <v>-1.7</v>
+        <v>-4.37</v>
       </c>
       <c r="J2" s="1" t="n">
-        <v>-0.4</v>
+        <v>-1.96</v>
       </c>
       <c r="K2" s="1" t="n">
-        <v>16.59</v>
+        <v>14.6</v>
       </c>
       <c r="L2" s="1" t="inlineStr">
         <is>
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="M2" s="1" t="n">
-        <v>-4.26</v>
+        <v>-7.53</v>
       </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
@@ -627,28 +627,28 @@
         <v>0</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G3" s="1" t="n">
         <v>27.8</v>
       </c>
       <c r="H3" s="1" t="n">
-        <v>-0.32</v>
+        <v>0</v>
       </c>
       <c r="I3" s="1" t="n">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="J3" s="1" t="n">
-        <v>5.8</v>
+        <v>4.87</v>
       </c>
       <c r="K3" s="1" t="n">
-        <v>11.17</v>
+        <v>10.91</v>
       </c>
       <c r="L3" s="1" t="inlineStr">
         <is>
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="M3" s="1" t="n">
-        <v>0</v>
+        <v>-0.23</v>
       </c>
       <c r="N3" s="1" t="inlineStr">
         <is>
@@ -692,7 +692,7 @@
         <v>0</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>0</v>
@@ -701,19 +701,19 @@
         <v>20</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>86.3</v>
+        <v>85.7</v>
       </c>
       <c r="H4" s="1" t="n">
-        <v>-2.6</v>
+        <v>-3.49</v>
       </c>
       <c r="I4" s="1" t="n">
-        <v>-1.9</v>
+        <v>-1.97</v>
       </c>
       <c r="J4" s="1" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-2.13</v>
       </c>
       <c r="K4" s="1" t="n">
-        <v>9.52</v>
+        <v>8.51</v>
       </c>
       <c r="L4" s="1" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
         </is>
       </c>
       <c r="M4" s="1" t="n">
-        <v>-9.35</v>
+        <v>-10.18</v>
       </c>
       <c r="N4" s="1" t="inlineStr">
         <is>
@@ -757,7 +757,7 @@
         <v>1</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>-2</v>
@@ -766,19 +766,19 @@
         <v>-2</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>86.56999999999999</v>
+        <v>87.06999999999999</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>0.57</v>
+        <v>-0.19</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>3.71</v>
+        <v>3.18</v>
       </c>
       <c r="J5" s="1" t="n">
-        <v>-1.04</v>
+        <v>-0.89</v>
       </c>
       <c r="K5" s="1" t="n">
-        <v>7.7</v>
+        <v>8.08</v>
       </c>
       <c r="L5" s="1" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="M5" s="1" t="n">
-        <v>-5.84</v>
+        <v>-5.51</v>
       </c>
       <c r="N5" s="1" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
       </c>
       <c r="O5" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P5" s="1" t="inlineStr">
@@ -819,31 +819,31 @@
         <v>5</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>13.11</v>
+        <v>13.18</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>0.46</v>
+        <v>-1.2</v>
       </c>
       <c r="I6" s="1" t="n">
-        <v>1.54</v>
+        <v>1.82</v>
       </c>
       <c r="J6" s="1" t="n">
-        <v>0.11</v>
+        <v>1.5</v>
       </c>
       <c r="K6" s="1" t="n">
-        <v>7.66</v>
+        <v>7.99</v>
       </c>
       <c r="L6" s="1" t="inlineStr">
         <is>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="M6" s="1" t="n">
-        <v>-4.17</v>
+        <v>-3.88</v>
       </c>
       <c r="N6" s="1" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
       </c>
       <c r="O6" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P6" s="1" t="inlineStr">
@@ -887,28 +887,28 @@
         <v>-2</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>17.22</v>
+        <v>17.17</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>-0.12</v>
+        <v>-1.09</v>
       </c>
       <c r="I7" s="1" t="n">
-        <v>1.69</v>
+        <v>1.23</v>
       </c>
       <c r="J7" s="1" t="n">
-        <v>5.01</v>
+        <v>3.71</v>
       </c>
       <c r="K7" s="1" t="n">
-        <v>7.61</v>
+        <v>7.06</v>
       </c>
       <c r="L7" s="1" t="inlineStr">
         <is>
@@ -916,11 +916,11 @@
         </is>
       </c>
       <c r="M7" s="1" t="n">
-        <v>0</v>
+        <v>-1.32</v>
       </c>
       <c r="N7" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O7" s="1" t="inlineStr">
@@ -952,7 +952,7 @@
         <v>-1</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>4</v>
@@ -961,19 +961,19 @@
         <v>20</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>31.32</v>
+        <v>31.3</v>
       </c>
       <c r="H8" s="1" t="n">
-        <v>-1.42</v>
+        <v>-0.54</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>-2.87</v>
+        <v>-0.98</v>
       </c>
       <c r="J8" s="1" t="n">
-        <v>-3.09</v>
+        <v>-3.54</v>
       </c>
       <c r="K8" s="1" t="n">
-        <v>5.73</v>
+        <v>5.42</v>
       </c>
       <c r="L8" s="1" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         </is>
       </c>
       <c r="M8" s="1" t="n">
-        <v>-25.45</v>
+        <v>-25.67</v>
       </c>
       <c r="N8" s="1" t="inlineStr">
         <is>
@@ -1017,28 +1017,28 @@
         <v>-1</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>8</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>277.2</v>
+        <v>278.51</v>
       </c>
       <c r="H9" s="1" t="n">
-        <v>-1.04</v>
+        <v>-0.72</v>
       </c>
       <c r="I9" s="1" t="n">
-        <v>-1.4</v>
+        <v>-0.45</v>
       </c>
       <c r="J9" s="1" t="n">
-        <v>-3.83</v>
+        <v>-3.22</v>
       </c>
       <c r="K9" s="1" t="n">
-        <v>2.46</v>
+        <v>2.71</v>
       </c>
       <c r="L9" s="1" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="M9" s="1" t="n">
-        <v>-5.2</v>
+        <v>-4.96</v>
       </c>
       <c r="N9" s="1" t="inlineStr">
         <is>
@@ -1079,31 +1079,31 @@
         <v>9</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>-8</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>102.77</v>
+        <v>103.08</v>
       </c>
       <c r="H10" s="1" t="n">
-        <v>-1</v>
+        <v>-0.66</v>
       </c>
       <c r="I10" s="1" t="n">
-        <v>1.34</v>
+        <v>0.85</v>
       </c>
       <c r="J10" s="1" t="n">
-        <v>0.05</v>
+        <v>-0.21</v>
       </c>
       <c r="K10" s="1" t="n">
-        <v>2.26</v>
+        <v>2.34</v>
       </c>
       <c r="L10" s="1" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="M10" s="1" t="n">
-        <v>-4.04</v>
+        <v>-3.96</v>
       </c>
       <c r="N10" s="1" t="inlineStr">
         <is>
@@ -1144,31 +1144,31 @@
         <v>10</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>160.93</v>
+        <v>161.55</v>
       </c>
       <c r="H11" s="1" t="n">
-        <v>-1.28</v>
+        <v>0.39</v>
       </c>
       <c r="I11" s="1" t="n">
-        <v>0.32</v>
+        <v>0.38</v>
       </c>
       <c r="J11" s="1" t="n">
-        <v>-0.48</v>
+        <v>-0.62</v>
       </c>
       <c r="K11" s="1" t="n">
-        <v>1.84</v>
+        <v>2</v>
       </c>
       <c r="L11" s="1" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         </is>
       </c>
       <c r="M11" s="1" t="n">
-        <v>-0.88</v>
+        <v>-0.72</v>
       </c>
       <c r="N11" s="1" t="inlineStr">
         <is>
@@ -1209,10 +1209,10 @@
         <v>11</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>7</v>
@@ -1221,19 +1221,19 @@
         <v>-5</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>29.26</v>
+        <v>29.44</v>
       </c>
       <c r="H12" s="1" t="n">
-        <v>-0.03</v>
+        <v>-0.54</v>
       </c>
       <c r="I12" s="1" t="n">
-        <v>1.14</v>
+        <v>1.53</v>
       </c>
       <c r="J12" s="1" t="n">
-        <v>-0.24</v>
+        <v>0.61</v>
       </c>
       <c r="K12" s="1" t="n">
-        <v>1.55</v>
+        <v>1.95</v>
       </c>
       <c r="L12" s="1" t="inlineStr">
         <is>
@@ -1277,28 +1277,28 @@
         <v>-4</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>-7</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>31.17</v>
+        <v>31.43</v>
       </c>
       <c r="H13" s="1" t="n">
-        <v>-0.76</v>
+        <v>-0.22</v>
       </c>
       <c r="I13" s="1" t="n">
-        <v>-1.2</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="J13" s="1" t="n">
-        <v>-1.95</v>
+        <v>-1.8</v>
       </c>
       <c r="K13" s="1" t="n">
-        <v>1.06</v>
+        <v>1.67</v>
       </c>
       <c r="L13" s="1" t="inlineStr">
         <is>
@@ -1306,7 +1306,7 @@
         </is>
       </c>
       <c r="M13" s="1" t="n">
-        <v>-4.71</v>
+        <v>-4.14</v>
       </c>
       <c r="N13" s="1" t="inlineStr">
         <is>
@@ -1351,19 +1351,19 @@
         <v>5</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>127.1</v>
+        <v>127.51</v>
       </c>
       <c r="H14" s="1" t="n">
-        <v>-1.33</v>
+        <v>0.32</v>
       </c>
       <c r="I14" s="1" t="n">
-        <v>0.54</v>
+        <v>0.41</v>
       </c>
       <c r="J14" s="1" t="n">
-        <v>-0.75</v>
+        <v>-0.57</v>
       </c>
       <c r="K14" s="1" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="L14" s="1" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         </is>
       </c>
       <c r="M14" s="1" t="n">
-        <v>-5.22</v>
+        <v>-5.12</v>
       </c>
       <c r="N14" s="1" t="inlineStr">
         <is>
@@ -1404,7 +1404,7 @@
         <v>14</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D15" s="2" t="n">
         <v>6</v>
@@ -1413,22 +1413,22 @@
         <v>9</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>11.02</v>
+        <v>11.01</v>
       </c>
       <c r="H15" s="1" t="n">
-        <v>-0.9</v>
+        <v>-1.26</v>
       </c>
       <c r="I15" s="1" t="n">
-        <v>0.45</v>
+        <v>-0.13</v>
       </c>
       <c r="J15" s="1" t="n">
-        <v>1.69</v>
+        <v>1.58</v>
       </c>
       <c r="K15" s="1" t="n">
-        <v>-0.05</v>
+        <v>-0.37</v>
       </c>
       <c r="L15" s="1" t="inlineStr">
         <is>
@@ -1436,7 +1436,7 @@
         </is>
       </c>
       <c r="M15" s="1" t="n">
-        <v>-8.869999999999999</v>
+        <v>-9.16</v>
       </c>
       <c r="N15" s="1" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>6</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E16" s="2" t="n">
         <v>5</v>
@@ -1481,19 +1481,19 @@
         <v>-12</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>53.18</v>
+        <v>52.97</v>
       </c>
       <c r="H16" s="1" t="n">
-        <v>0.45</v>
+        <v>-1.69</v>
       </c>
       <c r="I16" s="1" t="n">
-        <v>0.6</v>
+        <v>-0.1</v>
       </c>
       <c r="J16" s="1" t="n">
-        <v>-0.46</v>
+        <v>-0</v>
       </c>
       <c r="K16" s="1" t="n">
-        <v>-0.34</v>
+        <v>-0.96</v>
       </c>
       <c r="L16" s="1" t="inlineStr">
         <is>
@@ -1527,38 +1527,38 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>Fin Services</t>
+          <t>Services</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
         <v>16</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>-6</v>
+        <v>-2</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>-10</v>
+        <v>1</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-3</v>
+        <v>6</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>31.25</v>
+        <v>29.82</v>
       </c>
       <c r="H17" s="1" t="n">
-        <v>-2.34</v>
+        <v>-1.84</v>
       </c>
       <c r="I17" s="1" t="n">
-        <v>-1.69</v>
+        <v>-0.72</v>
       </c>
       <c r="J17" s="1" t="n">
-        <v>-3.16</v>
+        <v>-0.1</v>
       </c>
       <c r="K17" s="1" t="n">
-        <v>-0.66</v>
+        <v>-1.02</v>
       </c>
       <c r="L17" s="1" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         </is>
       </c>
       <c r="M17" s="1" t="n">
-        <v>-3.16</v>
+        <v>0</v>
       </c>
       <c r="N17" s="1" t="inlineStr">
         <is>
@@ -1599,10 +1599,10 @@
         <v>17</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E18" s="2" t="n">
         <v>2</v>
@@ -1611,19 +1611,19 @@
         <v>-10</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>32.27</v>
+        <v>32.2</v>
       </c>
       <c r="H18" s="1" t="n">
-        <v>-0.03</v>
+        <v>-0.89</v>
       </c>
       <c r="I18" s="1" t="n">
-        <v>0.39</v>
+        <v>-0.47</v>
       </c>
       <c r="J18" s="1" t="n">
-        <v>-1.63</v>
+        <v>-1.76</v>
       </c>
       <c r="K18" s="1" t="n">
-        <v>-0.77</v>
+        <v>-1.21</v>
       </c>
       <c r="L18" s="1" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         </is>
       </c>
       <c r="M18" s="1" t="n">
-        <v>-3.99</v>
+        <v>-4.42</v>
       </c>
       <c r="N18" s="1" t="inlineStr">
         <is>
@@ -1664,10 +1664,10 @@
         <v>18</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E19" s="2" t="n">
         <v>8</v>
@@ -1679,16 +1679,16 @@
         <v>9.970000000000001</v>
       </c>
       <c r="H19" s="1" t="n">
-        <v>-0.3</v>
+        <v>-0.5</v>
       </c>
       <c r="I19" s="1" t="n">
-        <v>0.86</v>
+        <v>0.24</v>
       </c>
       <c r="J19" s="1" t="n">
-        <v>2.61</v>
+        <v>2.45</v>
       </c>
       <c r="K19" s="1" t="n">
-        <v>-0.99</v>
+        <v>-1.21</v>
       </c>
       <c r="L19" s="1" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         </is>
       </c>
       <c r="M19" s="1" t="n">
-        <v>-9.99</v>
+        <v>-10.19</v>
       </c>
       <c r="N19" s="1" t="inlineStr">
         <is>
@@ -1722,38 +1722,38 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>Tourism</t>
+          <t>Commodities</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
         <v>19</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>-7</v>
+        <v>4</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>-11</v>
+        <v>6</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>-14</v>
+        <v>6</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>-15</v>
+        <v>1</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>77.14</v>
+        <v>96.95999999999999</v>
       </c>
       <c r="H20" s="1" t="n">
-        <v>-1.76</v>
+        <v>-0.02</v>
       </c>
       <c r="I20" s="1" t="n">
-        <v>1.25</v>
+        <v>0.49</v>
       </c>
       <c r="J20" s="1" t="n">
-        <v>0.83</v>
+        <v>0.53</v>
       </c>
       <c r="K20" s="1" t="n">
-        <v>-1.03</v>
+        <v>-1.35</v>
       </c>
       <c r="L20" s="1" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
         </is>
       </c>
       <c r="M20" s="1" t="n">
-        <v>-12.73</v>
+        <v>-8.369999999999999</v>
       </c>
       <c r="N20" s="1" t="inlineStr">
         <is>
@@ -1787,46 +1787,46 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>Commodities</t>
+          <t>Fin Services</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
         <v>20</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>2</v>
+        <v>-11</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>5</v>
+        <v>-13</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>5</v>
+        <v>-5</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>1</v>
+        <v>-11</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>96.98</v>
+        <v>31.1</v>
       </c>
       <c r="H21" s="1" t="n">
-        <v>-1.05</v>
+        <v>-3.92</v>
       </c>
       <c r="I21" s="1" t="n">
-        <v>0.28</v>
+        <v>-2.65</v>
       </c>
       <c r="J21" s="1" t="n">
-        <v>0.7</v>
+        <v>-3.38</v>
       </c>
       <c r="K21" s="1" t="n">
-        <v>-1.11</v>
+        <v>-1.36</v>
       </c>
       <c r="L21" s="1" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Down</t>
         </is>
       </c>
       <c r="M21" s="1" t="n">
-        <v>-8.140000000000001</v>
+        <v>-4.14</v>
       </c>
       <c r="N21" s="1" t="inlineStr">
         <is>
@@ -1852,46 +1852,46 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Tourism</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
         <v>21</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>-5</v>
+        <v>-9</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>-2</v>
+        <v>-11</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>-5</v>
+        <v>-15</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>1</v>
+        <v>-17</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>29.72</v>
+        <v>76.7</v>
       </c>
       <c r="H22" s="1" t="n">
-        <v>-1.59</v>
+        <v>-2.08</v>
       </c>
       <c r="I22" s="1" t="n">
-        <v>-0.49</v>
+        <v>-0.57</v>
       </c>
       <c r="J22" s="1" t="n">
-        <v>-0.43</v>
+        <v>0.37</v>
       </c>
       <c r="K22" s="1" t="n">
-        <v>-1.12</v>
+        <v>-1.81</v>
       </c>
       <c r="L22" s="1" t="inlineStr">
         <is>
-          <t>Down</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="M22" s="1" t="n">
-        <v>0</v>
+        <v>-13.2</v>
       </c>
       <c r="N22" s="1" t="inlineStr">
         <is>
@@ -1924,31 +1924,31 @@
         <v>22</v>
       </c>
       <c r="C23" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D23" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D23" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="E23" s="2" t="n">
-        <v>-10</v>
+        <v>-8</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>92.45</v>
+        <v>92.34999999999999</v>
       </c>
       <c r="H23" s="1" t="n">
-        <v>0.33</v>
+        <v>-0.9</v>
       </c>
       <c r="I23" s="1" t="n">
-        <v>0.53</v>
+        <v>0.72</v>
       </c>
       <c r="J23" s="1" t="n">
-        <v>-0.34</v>
+        <v>-0.15</v>
       </c>
       <c r="K23" s="1" t="n">
-        <v>-1.76</v>
+        <v>-2.09</v>
       </c>
       <c r="L23" s="1" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         </is>
       </c>
       <c r="M23" s="1" t="n">
-        <v>-13</v>
+        <v>-13.29</v>
       </c>
       <c r="N23" s="1" t="inlineStr">
         <is>
@@ -1989,31 +1989,31 @@
         <v>23</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>-6</v>
+        <v>-3</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>575.88</v>
+        <v>576.33</v>
       </c>
       <c r="H24" s="1" t="n">
-        <v>-1.31</v>
+        <v>-1.58</v>
       </c>
       <c r="I24" s="1" t="n">
-        <v>-0.54</v>
+        <v>-0.21</v>
       </c>
       <c r="J24" s="1" t="n">
-        <v>0.34</v>
+        <v>0.32</v>
       </c>
       <c r="K24" s="1" t="n">
-        <v>-1.95</v>
+        <v>-2.09</v>
       </c>
       <c r="L24" s="1" t="inlineStr">
         <is>
@@ -2021,7 +2021,7 @@
         </is>
       </c>
       <c r="M24" s="1" t="n">
-        <v>-5.62</v>
+        <v>-5.76</v>
       </c>
       <c r="N24" s="1" t="inlineStr">
         <is>
@@ -2054,31 +2054,31 @@
         <v>24</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>-10</v>
+        <v>-5</v>
       </c>
       <c r="D25" s="2" t="n">
         <v>-3</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>-10</v>
+        <v>-12</v>
       </c>
       <c r="F25" s="2" t="n">
         <v>-16</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>27.43</v>
+        <v>27.45</v>
       </c>
       <c r="H25" s="1" t="n">
-        <v>-1.61</v>
+        <v>-1.79</v>
       </c>
       <c r="I25" s="1" t="n">
-        <v>-0.67</v>
+        <v>-0.33</v>
       </c>
       <c r="J25" s="1" t="n">
-        <v>1.68</v>
+        <v>0.62</v>
       </c>
       <c r="K25" s="1" t="n">
-        <v>-2.35</v>
+        <v>-2.5</v>
       </c>
       <c r="L25" s="1" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         </is>
       </c>
       <c r="M25" s="1" t="n">
-        <v>-4.06</v>
+        <v>-4.2</v>
       </c>
       <c r="N25" s="1" t="inlineStr">
         <is>
@@ -2119,31 +2119,31 @@
         <v>25</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="F26" s="2" t="n">
         <v>-6</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>92.08</v>
+        <v>92.43000000000001</v>
       </c>
       <c r="H26" s="1" t="n">
-        <v>-1.37</v>
+        <v>0.38</v>
       </c>
       <c r="I26" s="1" t="n">
-        <v>0.21</v>
+        <v>0.47</v>
       </c>
       <c r="J26" s="1" t="n">
-        <v>0.12</v>
+        <v>0.76</v>
       </c>
       <c r="K26" s="1" t="n">
-        <v>-3.07</v>
+        <v>-2.92</v>
       </c>
       <c r="L26" s="1" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="M26" s="1" t="n">
-        <v>-4.72</v>
+        <v>-4.58</v>
       </c>
       <c r="N26" s="1" t="inlineStr">
         <is>
@@ -2196,19 +2196,19 @@
         <v>-14</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>37.5</v>
+        <v>37.64</v>
       </c>
       <c r="H27" s="1" t="n">
-        <v>-1.08</v>
+        <v>-1</v>
       </c>
       <c r="I27" s="1" t="n">
-        <v>0.37</v>
+        <v>0.09</v>
       </c>
       <c r="J27" s="1" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="K27" s="1" t="n">
-        <v>-3.41</v>
+        <v>-3.27</v>
       </c>
       <c r="L27" s="1" t="inlineStr">
         <is>
@@ -2258,22 +2258,22 @@
         <v>-3</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>49.2</v>
+        <v>49.48</v>
       </c>
       <c r="H28" s="1" t="n">
-        <v>-1.03</v>
+        <v>0.57</v>
       </c>
       <c r="I28" s="1" t="n">
-        <v>0.62</v>
+        <v>1.46</v>
       </c>
       <c r="J28" s="1" t="n">
-        <v>0.78</v>
+        <v>1.57</v>
       </c>
       <c r="K28" s="1" t="n">
-        <v>-4.72</v>
+        <v>-4.39</v>
       </c>
       <c r="L28" s="1" t="inlineStr">
         <is>
@@ -2281,11 +2281,11 @@
         </is>
       </c>
       <c r="M28" s="1" t="n">
-        <v>-15.53</v>
+        <v>-15.24</v>
       </c>
       <c r="N28" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O28" s="1" t="inlineStr">
@@ -2569,7 +2569,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B2" s="1" t="n">
@@ -2603,7 +2603,7 @@
         <v>4</v>
       </c>
       <c r="L2" s="1" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="M2" s="1" t="n">
         <v>25</v>
@@ -2618,7 +2618,7 @@
         <v>26</v>
       </c>
       <c r="Q2" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="R2" s="1" t="n">
         <v>17</v>
@@ -2645,10 +2645,10 @@
         <v>1</v>
       </c>
       <c r="Z2" s="1" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AA2" s="1" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="AB2" s="1" t="n">
         <v>12</v>
@@ -2657,23 +2657,23 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G3" s="1" t="n">
         <v>27</v>
@@ -2682,49 +2682,49 @@
         <v>3</v>
       </c>
       <c r="I3" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="J3" s="1" t="n">
         <v>4</v>
-      </c>
-      <c r="J3" s="1" t="n">
-        <v>8</v>
       </c>
       <c r="K3" s="1" t="n">
         <v>5</v>
       </c>
       <c r="L3" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="M3" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="N3" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="O3" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="P3" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q3" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="R3" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="S3" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="T3" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="U3" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="V3" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="M3" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="N3" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="O3" s="1" t="n">
-        <v>23</v>
-      </c>
-      <c r="P3" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="Q3" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="R3" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="S3" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="T3" s="1" t="n">
+      <c r="W3" s="1" t="n">
         <v>17</v>
-      </c>
-      <c r="U3" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="V3" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="W3" s="1" t="n">
-        <v>22</v>
       </c>
       <c r="X3" s="1" t="n">
         <v>2</v>
@@ -2733,29 +2733,29 @@
         <v>1</v>
       </c>
       <c r="Z3" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA3" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="AA3" s="1" t="n">
-        <v>16</v>
-      </c>
       <c r="AB3" s="1" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E4" s="1" t="n">
         <v>23</v>
@@ -2770,49 +2770,49 @@
         <v>3</v>
       </c>
       <c r="I4" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="J4" s="1" t="n">
         <v>6</v>
-      </c>
-      <c r="J4" s="1" t="n">
-        <v>8</v>
       </c>
       <c r="K4" s="1" t="n">
         <v>4</v>
       </c>
       <c r="L4" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M4" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="N4" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="O4" s="1" t="n">
         <v>24</v>
-      </c>
-      <c r="N4" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="O4" s="1" t="n">
-        <v>25</v>
       </c>
       <c r="P4" s="1" t="n">
         <v>26</v>
       </c>
       <c r="Q4" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="R4" s="1" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="S4" s="1" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="T4" s="1" t="n">
         <v>19</v>
       </c>
       <c r="U4" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="V4" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="W4" s="1" t="n">
         <v>17</v>
-      </c>
-      <c r="V4" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="W4" s="1" t="n">
-        <v>22</v>
       </c>
       <c r="X4" s="1" t="n">
         <v>2</v>
@@ -2821,10 +2821,10 @@
         <v>1</v>
       </c>
       <c r="Z4" s="1" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="AA4" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AB4" s="1" t="n">
         <v>9</v>
@@ -2833,114 +2833,114 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F5" s="1" t="n">
         <v>7</v>
       </c>
       <c r="G5" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="H5" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="I5" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="J5" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="K5" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="L5" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="M5" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="N5" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="O5" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="P5" s="1" t="n">
         <v>26</v>
       </c>
-      <c r="H5" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="I5" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="J5" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="K5" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="L5" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="M5" s="1" t="n">
+      <c r="Q5" s="1" t="n">
         <v>21</v>
-      </c>
-      <c r="N5" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="O5" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="P5" s="1" t="n">
-        <v>27</v>
-      </c>
-      <c r="Q5" s="1" t="n">
-        <v>23</v>
       </c>
       <c r="R5" s="1" t="n">
         <v>20</v>
       </c>
       <c r="S5" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="T5" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="T5" s="1" t="n">
-        <v>15</v>
-      </c>
       <c r="U5" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="V5" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="W5" s="1" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="X5" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y5" s="1" t="n">
         <v>1</v>
       </c>
       <c r="Z5" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA5" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="AA5" s="1" t="n">
-        <v>13</v>
-      </c>
       <c r="AB5" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
         <v>6</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>7</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H6" s="1" t="n">
         <v>2</v>
@@ -2949,46 +2949,46 @@
         <v>4</v>
       </c>
       <c r="J6" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K6" s="1" t="n">
         <v>5</v>
       </c>
       <c r="L6" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="M6" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="N6" s="1" t="n">
         <v>9</v>
-      </c>
-      <c r="M6" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="N6" s="1" t="n">
-        <v>13</v>
       </c>
       <c r="O6" s="1" t="n">
         <v>22</v>
       </c>
       <c r="P6" s="1" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Q6" s="1" t="n">
         <v>23</v>
       </c>
       <c r="R6" s="1" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="S6" s="1" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="T6" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="U6" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="U6" s="1" t="n">
-        <v>15</v>
-      </c>
       <c r="V6" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="W6" s="1" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="X6" s="1" t="n">
         <v>3</v>
@@ -2997,10 +2997,10 @@
         <v>1</v>
       </c>
       <c r="Z6" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AA6" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AB6" s="1" t="n">
         <v>8</v>
@@ -3009,20 +3009,20 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
         <v>6</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F7" s="1" t="n">
         <v>7</v>
@@ -3037,43 +3037,43 @@
         <v>4</v>
       </c>
       <c r="J7" s="1" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K7" s="1" t="n">
         <v>5</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M7" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N7" s="1" t="n">
         <v>13</v>
       </c>
       <c r="O7" s="1" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="P7" s="1" t="n">
         <v>26</v>
       </c>
       <c r="Q7" s="1" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="R7" s="1" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="S7" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="T7" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="U7" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="T7" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="U7" s="1" t="n">
-        <v>18</v>
-      </c>
       <c r="V7" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="W7" s="1" t="n">
         <v>21</v>
@@ -3088,7 +3088,7 @@
         <v>12</v>
       </c>
       <c r="AA7" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AB7" s="1" t="n">
         <v>8</v>
@@ -3097,23 +3097,23 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E8" s="1" t="n">
         <v>24</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G8" s="1" t="n">
         <v>27</v>
@@ -3125,46 +3125,46 @@
         <v>4</v>
       </c>
       <c r="J8" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K8" s="1" t="n">
         <v>5</v>
       </c>
       <c r="L8" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="M8" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="N8" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="M8" s="1" t="n">
+      <c r="O8" s="1" t="n">
         <v>25</v>
-      </c>
-      <c r="N8" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="O8" s="1" t="n">
-        <v>21</v>
       </c>
       <c r="P8" s="1" t="n">
         <v>26</v>
       </c>
       <c r="Q8" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R8" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="S8" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="T8" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="S8" s="1" t="n">
+      <c r="U8" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="T8" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="U8" s="1" t="n">
-        <v>16</v>
-      </c>
       <c r="V8" s="1" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="W8" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="X8" s="1" t="n">
         <v>3</v>
@@ -3173,10 +3173,10 @@
         <v>1</v>
       </c>
       <c r="Z8" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AA8" s="1" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AB8" s="1" t="n">
         <v>8</v>
@@ -3185,23 +3185,23 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G9" s="1" t="n">
         <v>27</v>
@@ -3213,19 +3213,19 @@
         <v>4</v>
       </c>
       <c r="J9" s="1" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="K9" s="1" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L9" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M9" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="N9" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O9" s="1" t="n">
         <v>21</v>
@@ -3234,22 +3234,22 @@
         <v>26</v>
       </c>
       <c r="Q9" s="1" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="R9" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="S9" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="T9" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="S9" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="T9" s="1" t="n">
-        <v>20</v>
-      </c>
       <c r="U9" s="1" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="V9" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="W9" s="1" t="n">
         <v>22</v>
@@ -3261,23 +3261,23 @@
         <v>1</v>
       </c>
       <c r="Z9" s="1" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AA9" s="1" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="AB9" s="1" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C10" s="1" t="n">
         <v>16</v>
@@ -3286,7 +3286,7 @@
         <v>18</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F10" s="1" t="n">
         <v>9</v>
@@ -3298,22 +3298,22 @@
         <v>2</v>
       </c>
       <c r="I10" s="1" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J10" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="K10" s="1" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L10" s="1" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="M10" s="1" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="N10" s="1" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="O10" s="1" t="n">
         <v>21</v>
@@ -3325,22 +3325,22 @@
         <v>25</v>
       </c>
       <c r="R10" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="S10" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="T10" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="S10" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="T10" s="1" t="n">
-        <v>19</v>
-      </c>
       <c r="U10" s="1" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="V10" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="W10" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="X10" s="1" t="n">
         <v>3</v>
@@ -3349,62 +3349,62 @@
         <v>1</v>
       </c>
       <c r="Z10" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AA10" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AB10" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E11" s="1" t="n">
         <v>24</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G11" s="1" t="n">
         <v>27</v>
       </c>
       <c r="H11" s="1" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I11" s="1" t="n">
         <v>6</v>
       </c>
       <c r="J11" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K11" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="M11" s="1" t="n">
         <v>22</v>
       </c>
       <c r="N11" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O11" s="1" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="P11" s="1" t="n">
         <v>26</v>
@@ -3413,86 +3413,86 @@
         <v>25</v>
       </c>
       <c r="R11" s="1" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="S11" s="1" t="n">
         <v>5</v>
       </c>
       <c r="T11" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="U11" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="V11" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="V11" s="1" t="n">
-        <v>13</v>
-      </c>
       <c r="W11" s="1" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="X11" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y11" s="1" t="n">
         <v>1</v>
       </c>
       <c r="Z11" s="1" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AA11" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AB11" s="1" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D12" s="1" t="n">
         <v>21</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G12" s="1" t="n">
         <v>27</v>
       </c>
       <c r="H12" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I12" s="1" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J12" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K12" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M12" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N12" s="1" t="n">
         <v>12</v>
       </c>
       <c r="O12" s="1" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="P12" s="1" t="n">
         <v>26</v>
@@ -3501,110 +3501,110 @@
         <v>25</v>
       </c>
       <c r="R12" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="S12" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T12" s="1" t="n">
         <v>20</v>
       </c>
       <c r="U12" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="V12" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="V12" s="1" t="n">
-        <v>11</v>
-      </c>
       <c r="W12" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="X12" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y12" s="1" t="n">
         <v>1</v>
       </c>
       <c r="Z12" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA12" s="1" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AB12" s="1" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="C13" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="C13" s="1" t="n">
-        <v>16</v>
-      </c>
       <c r="D13" s="1" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G13" s="1" t="n">
         <v>27</v>
       </c>
       <c r="H13" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I13" s="1" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J13" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K13" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L13" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M13" s="1" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N13" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="O13" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="P13" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q13" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="R13" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="S13" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="T13" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="U13" s="1" t="n">
         <v>13</v>
-      </c>
-      <c r="O13" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="P13" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="Q13" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="R13" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="S13" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="T13" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="U13" s="1" t="n">
-        <v>14</v>
       </c>
       <c r="V13" s="1" t="n">
         <v>11</v>
       </c>
       <c r="W13" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="X13" s="1" t="n">
         <v>3</v>
@@ -3613,29 +3613,29 @@
         <v>1</v>
       </c>
       <c r="Z13" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA13" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="AB13" s="1" t="n">
         <v>9</v>
-      </c>
-      <c r="AA13" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="AB13" s="1" t="n">
-        <v>10</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="C14" s="1" t="n">
         <v>16</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E14" s="1" t="n">
         <v>23</v>
@@ -3653,46 +3653,46 @@
         <v>7</v>
       </c>
       <c r="J14" s="1" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="K14" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M14" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N14" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O14" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="P14" s="1" t="n">
         <v>25</v>
-      </c>
-      <c r="P14" s="1" t="n">
-        <v>26</v>
       </c>
       <c r="Q14" s="1" t="n">
         <v>24</v>
       </c>
       <c r="R14" s="1" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="S14" s="1" t="n">
         <v>5</v>
       </c>
       <c r="T14" s="1" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="U14" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="V14" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="W14" s="1" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="X14" s="1" t="n">
         <v>3</v>
@@ -3701,10 +3701,10 @@
         <v>1</v>
       </c>
       <c r="Z14" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA14" s="1" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AB14" s="1" t="n">
         <v>10</v>
@@ -3713,59 +3713,59 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F15" s="1" t="n">
         <v>6</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H15" s="1" t="n">
         <v>4</v>
       </c>
       <c r="I15" s="1" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J15" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K15" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L15" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M15" s="1" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N15" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="O15" s="1" t="n">
         <v>25</v>
       </c>
       <c r="P15" s="1" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Q15" s="1" t="n">
         <v>24</v>
       </c>
       <c r="R15" s="1" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="S15" s="1" t="n">
         <v>5</v>
@@ -3777,10 +3777,10 @@
         <v>13</v>
       </c>
       <c r="V15" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="W15" s="1" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="X15" s="1" t="n">
         <v>3</v>
@@ -3789,35 +3789,35 @@
         <v>1</v>
       </c>
       <c r="Z15" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA15" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AB15" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="C16" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="C16" s="1" t="n">
-        <v>10</v>
-      </c>
       <c r="D16" s="1" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F16" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G16" s="1" t="n">
         <v>26</v>
@@ -3826,22 +3826,22 @@
         <v>4</v>
       </c>
       <c r="I16" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J16" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K16" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L16" s="1" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M16" s="1" t="n">
         <v>23</v>
       </c>
       <c r="N16" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O16" s="1" t="n">
         <v>25</v>
@@ -3853,22 +3853,22 @@
         <v>24</v>
       </c>
       <c r="R16" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="S16" s="1" t="n">
         <v>5</v>
       </c>
       <c r="T16" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="U16" s="1" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="V16" s="1" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="W16" s="1" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="X16" s="1" t="n">
         <v>3</v>
@@ -3880,32 +3880,32 @@
         <v>7</v>
       </c>
       <c r="AA16" s="1" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="AB16" s="1" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F17" s="1" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G17" s="1" t="n">
         <v>26</v>
@@ -3914,49 +3914,49 @@
         <v>4</v>
       </c>
       <c r="I17" s="1" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="J17" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K17" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L17" s="1" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="M17" s="1" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="N17" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O17" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="P17" s="1" t="n">
         <v>27</v>
       </c>
       <c r="Q17" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R17" s="1" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="S17" s="1" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T17" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="U17" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="V17" s="1" t="n">
         <v>18</v>
       </c>
       <c r="W17" s="1" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="X17" s="1" t="n">
         <v>3</v>
@@ -3965,19 +3965,19 @@
         <v>1</v>
       </c>
       <c r="Z17" s="1" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AA17" s="1" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AB17" s="1" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
@@ -3987,7 +3987,7 @@
         <v>11</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E18" s="1" t="n">
         <v>16</v>
@@ -3996,7 +3996,7 @@
         <v>6</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H18" s="1" t="n">
         <v>4</v>
@@ -4011,40 +4011,40 @@
         <v>2</v>
       </c>
       <c r="L18" s="1" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="M18" s="1" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="N18" s="1" t="n">
         <v>14</v>
       </c>
       <c r="O18" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P18" s="1" t="n">
         <v>27</v>
       </c>
       <c r="Q18" s="1" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="R18" s="1" t="n">
         <v>19</v>
       </c>
       <c r="S18" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T18" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="U18" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="V18" s="1" t="n">
         <v>18</v>
       </c>
       <c r="W18" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="X18" s="1" t="n">
         <v>3</v>
@@ -4053,10 +4053,10 @@
         <v>1</v>
       </c>
       <c r="Z18" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA18" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AB18" s="1" t="n">
         <v>7</v>
@@ -4065,29 +4065,29 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F19" s="1" t="n">
         <v>6</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H19" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I19" s="1" t="n">
         <v>5</v>
@@ -4099,16 +4099,16 @@
         <v>2</v>
       </c>
       <c r="L19" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M19" s="1" t="n">
         <v>22</v>
       </c>
       <c r="N19" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="O19" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="P19" s="1" t="n">
         <v>27</v>
@@ -4117,34 +4117,34 @@
         <v>26</v>
       </c>
       <c r="R19" s="1" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="S19" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T19" s="1" t="n">
         <v>21</v>
       </c>
       <c r="U19" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="V19" s="1" t="n">
         <v>18</v>
-      </c>
-      <c r="V19" s="1" t="n">
-        <v>15</v>
       </c>
       <c r="W19" s="1" t="n">
         <v>20</v>
       </c>
       <c r="X19" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y19" s="1" t="n">
         <v>1</v>
       </c>
       <c r="Z19" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA19" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AB19" s="1" t="n">
         <v>7</v>
@@ -4153,7 +4153,7 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
@@ -4163,22 +4163,22 @@
         <v>10</v>
       </c>
       <c r="D20" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F20" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="G20" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="H20" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="G20" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="H20" s="1" t="n">
+      <c r="I20" s="1" t="n">
         <v>5</v>
-      </c>
-      <c r="I20" s="1" t="n">
-        <v>6</v>
       </c>
       <c r="J20" s="1" t="n">
         <v>23</v>
@@ -4187,37 +4187,37 @@
         <v>2</v>
       </c>
       <c r="L20" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M20" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="N20" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="O20" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="P20" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q20" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="R20" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="S20" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="T20" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="N20" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="O20" s="1" t="n">
-        <v>27</v>
-      </c>
-      <c r="P20" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="Q20" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="R20" s="1" t="n">
+      <c r="U20" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="S20" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="T20" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="U20" s="1" t="n">
+      <c r="V20" s="1" t="n">
         <v>15</v>
-      </c>
-      <c r="V20" s="1" t="n">
-        <v>17</v>
       </c>
       <c r="W20" s="1" t="n">
         <v>20</v>
@@ -4229,7 +4229,7 @@
         <v>1</v>
       </c>
       <c r="Z20" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA20" s="1" t="n">
         <v>16</v>
@@ -4241,77 +4241,77 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D21" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="E21" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="E21" s="1" t="n">
-        <v>14</v>
-      </c>
       <c r="F21" s="1" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G21" s="1" t="n">
         <v>24</v>
       </c>
       <c r="H21" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I21" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J21" s="1" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="K21" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L21" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="M21" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="N21" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="O21" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="P21" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q21" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="R21" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="S21" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="T21" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="U21" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="V21" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="M21" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="N21" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="O21" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="P21" s="1" t="n">
-        <v>27</v>
-      </c>
-      <c r="Q21" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="R21" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="S21" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="T21" s="1" t="n">
-        <v>23</v>
-      </c>
-      <c r="U21" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="V21" s="1" t="n">
-        <v>16</v>
-      </c>
       <c r="W21" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="X21" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y21" s="1" t="n">
         <v>1</v>
@@ -4320,26 +4320,26 @@
         <v>8</v>
       </c>
       <c r="AA21" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AB21" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="C22" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="C22" s="1" t="n">
-        <v>10</v>
-      </c>
       <c r="D22" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E22" s="1" t="n">
         <v>14</v>
@@ -4357,34 +4357,34 @@
         <v>7</v>
       </c>
       <c r="J22" s="1" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K22" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L22" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M22" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N22" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="O22" s="1" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P22" s="1" t="n">
         <v>27</v>
       </c>
       <c r="Q22" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="R22" s="1" t="n">
         <v>19</v>
       </c>
       <c r="S22" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T22" s="1" t="n">
         <v>23</v>
@@ -4396,7 +4396,7 @@
         <v>16</v>
       </c>
       <c r="W22" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="X22" s="1" t="n">
         <v>3</v>
@@ -4405,47 +4405,47 @@
         <v>1</v>
       </c>
       <c r="Z22" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA22" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="AB22" s="1" t="n">
         <v>6</v>
-      </c>
-      <c r="AA22" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="AB22" s="1" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
         <v>11</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D23" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="E23" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="E23" s="1" t="n">
-        <v>12</v>
-      </c>
       <c r="F23" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G23" s="1" t="n">
         <v>24</v>
       </c>
       <c r="H23" s="1" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I23" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J23" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K23" s="1" t="n">
         <v>2</v>
@@ -4454,7 +4454,7 @@
         <v>15</v>
       </c>
       <c r="M23" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N23" s="1" t="n">
         <v>13</v>
@@ -4472,7 +4472,7 @@
         <v>19</v>
       </c>
       <c r="S23" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T23" s="1" t="n">
         <v>23</v>
@@ -4481,7 +4481,7 @@
         <v>18</v>
       </c>
       <c r="V23" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="W23" s="1" t="n">
         <v>20</v>
@@ -4493,32 +4493,32 @@
         <v>1</v>
       </c>
       <c r="Z23" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA23" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AB23" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C24" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="D24" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="E24" s="1" t="n">
         <v>12</v>
-      </c>
-      <c r="D24" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="E24" s="1" t="n">
-        <v>13</v>
       </c>
       <c r="F24" s="1" t="n">
         <v>4</v>
@@ -4527,10 +4527,10 @@
         <v>24</v>
       </c>
       <c r="H24" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I24" s="1" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J24" s="1" t="n">
         <v>21</v>
@@ -4539,40 +4539,40 @@
         <v>2</v>
       </c>
       <c r="L24" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="M24" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="N24" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="O24" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="P24" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q24" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="R24" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="S24" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="U24" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="M24" s="1" t="n">
+      <c r="V24" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="W24" s="1" t="n">
         <v>20</v>
-      </c>
-      <c r="N24" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="O24" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="P24" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="Q24" s="1" t="n">
-        <v>27</v>
-      </c>
-      <c r="R24" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="S24" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="T24" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="U24" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="V24" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="W24" s="1" t="n">
-        <v>23</v>
       </c>
       <c r="X24" s="1" t="n">
         <v>3</v>
@@ -4581,38 +4581,38 @@
         <v>1</v>
       </c>
       <c r="Z24" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA24" s="1" t="n">
         <v>16</v>
       </c>
       <c r="AB24" s="1" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C25" s="1" t="n">
         <v>12</v>
       </c>
       <c r="D25" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F25" s="1" t="n">
         <v>4</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H25" s="1" t="n">
         <v>7</v>
@@ -4621,7 +4621,7 @@
         <v>11</v>
       </c>
       <c r="J25" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K25" s="1" t="n">
         <v>2</v>
@@ -4630,25 +4630,25 @@
         <v>18</v>
       </c>
       <c r="M25" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="N25" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="O25" s="1" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="P25" s="1" t="n">
         <v>26</v>
       </c>
       <c r="Q25" s="1" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="R25" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="S25" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T25" s="1" t="n">
         <v>22</v>
@@ -4657,7 +4657,7 @@
         <v>19</v>
       </c>
       <c r="V25" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="W25" s="1" t="n">
         <v>23</v>
@@ -4672,7 +4672,7 @@
         <v>6</v>
       </c>
       <c r="AA25" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AB25" s="1" t="n">
         <v>5</v>
@@ -4681,47 +4681,47 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C26" s="1" t="n">
         <v>12</v>
       </c>
       <c r="D26" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="E26" s="1" t="n">
         <v>15</v>
-      </c>
-      <c r="E26" s="1" t="n">
-        <v>10</v>
       </c>
       <c r="F26" s="1" t="n">
         <v>4</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H26" s="1" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I26" s="1" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J26" s="1" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K26" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L26" s="1" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M26" s="1" t="n">
         <v>21</v>
       </c>
       <c r="N26" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O26" s="1" t="n">
         <v>27</v>
@@ -4730,59 +4730,59 @@
         <v>26</v>
       </c>
       <c r="Q26" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R26" s="1" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="S26" s="1" t="n">
         <v>8</v>
       </c>
       <c r="T26" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="U26" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="V26" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="W26" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="U26" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="V26" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="W26" s="1" t="n">
+      <c r="X26" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y26" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="X26" s="1" t="n">
+      <c r="Z26" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA26" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="AB26" s="1" t="n">
         <v>5</v>
-      </c>
-      <c r="Y26" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z26" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA26" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="AB26" s="1" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
         <v>13</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D27" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F27" s="1" t="n">
         <v>4</v>
@@ -4791,13 +4791,13 @@
         <v>24</v>
       </c>
       <c r="H27" s="1" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I27" s="1" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="J27" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K27" s="1" t="n">
         <v>3</v>
@@ -4821,25 +4821,25 @@
         <v>25</v>
       </c>
       <c r="R27" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="S27" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="T27" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="U27" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="V27" s="1" t="n">
         <v>16</v>
-      </c>
-      <c r="S27" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="T27" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="U27" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="V27" s="1" t="n">
-        <v>15</v>
       </c>
       <c r="W27" s="1" t="n">
         <v>1</v>
       </c>
       <c r="X27" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y27" s="1" t="n">
         <v>2</v>
@@ -4848,26 +4848,26 @@
         <v>7</v>
       </c>
       <c r="AA27" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AB27" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D28" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E28" s="1" t="n">
         <v>9</v>
@@ -4876,22 +4876,22 @@
         <v>4</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H28" s="1" t="n">
         <v>12</v>
       </c>
       <c r="I28" s="1" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J28" s="1" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K28" s="1" t="n">
         <v>3</v>
       </c>
       <c r="L28" s="1" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="M28" s="1" t="n">
         <v>21</v>
@@ -4903,25 +4903,25 @@
         <v>27</v>
       </c>
       <c r="P28" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q28" s="1" t="n">
         <v>25</v>
-      </c>
-      <c r="Q28" s="1" t="n">
-        <v>24</v>
       </c>
       <c r="R28" s="1" t="n">
         <v>16</v>
       </c>
       <c r="S28" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T28" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="U28" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="V28" s="1" t="n">
         <v>15</v>
-      </c>
-      <c r="V28" s="1" t="n">
-        <v>14</v>
       </c>
       <c r="W28" s="1" t="n">
         <v>1</v>
@@ -4945,38 +4945,38 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C29" s="1" t="n">
         <v>10</v>
       </c>
       <c r="D29" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E29" s="1" t="n">
         <v>9</v>
       </c>
       <c r="F29" s="1" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H29" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I29" s="1" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J29" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K29" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L29" s="1" t="n">
         <v>20</v>
@@ -4988,37 +4988,37 @@
         <v>11</v>
       </c>
       <c r="O29" s="1" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P29" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q29" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="Q29" s="1" t="n">
-        <v>25</v>
-      </c>
       <c r="R29" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="S29" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="T29" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="U29" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="V29" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="S29" s="1" t="n">
+      <c r="W29" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="X29" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="T29" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="U29" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="V29" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="W29" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="X29" s="1" t="n">
-        <v>8</v>
-      </c>
       <c r="Y29" s="1" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Z29" s="1" t="n">
         <v>7</v>
@@ -5033,20 +5033,20 @@
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="C30" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="C30" s="1" t="n">
-        <v>11</v>
-      </c>
       <c r="D30" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F30" s="1" t="n">
         <v>2</v>
@@ -5055,10 +5055,10 @@
         <v>27</v>
       </c>
       <c r="H30" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I30" s="1" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J30" s="1" t="n">
         <v>23</v>
@@ -5073,7 +5073,7 @@
         <v>21</v>
       </c>
       <c r="N30" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="O30" s="1" t="n">
         <v>26</v>
@@ -5085,10 +5085,10 @@
         <v>25</v>
       </c>
       <c r="R30" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S30" s="1" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T30" s="1" t="n">
         <v>22</v>
@@ -5097,13 +5097,13 @@
         <v>16</v>
       </c>
       <c r="V30" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="W30" s="1" t="n">
         <v>3</v>
       </c>
       <c r="X30" s="1" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y30" s="1" t="n">
         <v>4</v>
@@ -5121,38 +5121,38 @@
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D31" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="E31" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="F31" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G31" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="H31" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="I31" s="1" t="n">
         <v>19</v>
-      </c>
-      <c r="E31" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="F31" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="G31" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="H31" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="I31" s="1" t="n">
-        <v>18</v>
       </c>
       <c r="J31" s="1" t="n">
         <v>23</v>
       </c>
       <c r="K31" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L31" s="1" t="n">
         <v>20</v>
@@ -5161,10 +5161,10 @@
         <v>21</v>
       </c>
       <c r="N31" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="O31" s="1" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P31" s="1" t="n">
         <v>24</v>
@@ -5173,7 +5173,7 @@
         <v>25</v>
       </c>
       <c r="R31" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="S31" s="1" t="n">
         <v>9</v>
@@ -5182,25 +5182,25 @@
         <v>22</v>
       </c>
       <c r="U31" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="V31" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="W31" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X31" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y31" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="Y31" s="1" t="n">
-        <v>2</v>
-      </c>
       <c r="Z31" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA31" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AB31" s="1" t="n">
         <v>5</v>
@@ -5209,41 +5209,41 @@
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C32" s="1" t="n">
         <v>12</v>
       </c>
       <c r="D32" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F32" s="1" t="n">
         <v>7</v>
       </c>
       <c r="G32" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="H32" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="I32" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="J32" s="1" t="n">
         <v>23</v>
-      </c>
-      <c r="H32" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="I32" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="J32" s="1" t="n">
-        <v>24</v>
       </c>
       <c r="K32" s="1" t="n">
         <v>3</v>
       </c>
       <c r="L32" s="1" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M32" s="1" t="n">
         <v>21</v>
@@ -5255,25 +5255,25 @@
         <v>27</v>
       </c>
       <c r="P32" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q32" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="Q32" s="1" t="n">
-        <v>26</v>
-      </c>
       <c r="R32" s="1" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="S32" s="1" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="T32" s="1" t="n">
         <v>22</v>
       </c>
       <c r="U32" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="V32" s="1" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="W32" s="1" t="n">
         <v>1</v>
@@ -5288,50 +5288,50 @@
         <v>8</v>
       </c>
       <c r="AA32" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AB32" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="C33" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D33" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="E33" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="F33" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C33" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="D33" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="E33" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="F33" s="1" t="n">
-        <v>5</v>
-      </c>
       <c r="G33" s="1" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="H33" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I33" s="1" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J33" s="1" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K33" s="1" t="n">
         <v>3</v>
       </c>
       <c r="L33" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M33" s="1" t="n">
         <v>21</v>
@@ -5343,25 +5343,25 @@
         <v>27</v>
       </c>
       <c r="P33" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Q33" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="R33" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="S33" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="S33" s="1" t="n">
-        <v>19</v>
-      </c>
       <c r="T33" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="U33" s="1" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="V33" s="1" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="W33" s="1" t="n">
         <v>1</v>
@@ -5373,10 +5373,10 @@
         <v>2</v>
       </c>
       <c r="Z33" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA33" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AB33" s="1" t="n">
         <v>6</v>
@@ -5385,20 +5385,20 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C34" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="D34" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="D34" s="1" t="n">
-        <v>20</v>
-      </c>
       <c r="E34" s="1" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F34" s="1" t="n">
         <v>5</v>
@@ -5407,10 +5407,10 @@
         <v>26</v>
       </c>
       <c r="H34" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I34" s="1" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J34" s="1" t="n">
         <v>22</v>
@@ -5419,34 +5419,34 @@
         <v>3</v>
       </c>
       <c r="L34" s="1" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M34" s="1" t="n">
         <v>21</v>
       </c>
       <c r="N34" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="O34" s="1" t="n">
         <v>27</v>
       </c>
       <c r="P34" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q34" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="Q34" s="1" t="n">
-        <v>24</v>
-      </c>
       <c r="R34" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="S34" s="1" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="T34" s="1" t="n">
         <v>23</v>
       </c>
       <c r="U34" s="1" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="V34" s="1" t="n">
         <v>17</v>
@@ -5461,10 +5461,10 @@
         <v>2</v>
       </c>
       <c r="Z34" s="1" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AA34" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AB34" s="1" t="n">
         <v>6</v>
@@ -5473,44 +5473,44 @@
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D35" s="1" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F35" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G35" s="1" t="n">
         <v>26</v>
       </c>
       <c r="H35" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I35" s="1" t="n">
         <v>10</v>
       </c>
       <c r="J35" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K35" s="1" t="n">
         <v>3</v>
       </c>
       <c r="L35" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M35" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N35" s="1" t="n">
         <v>11</v>
@@ -5525,10 +5525,10 @@
         <v>24</v>
       </c>
       <c r="R35" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="S35" s="1" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="T35" s="1" t="n">
         <v>23</v>
@@ -5537,13 +5537,13 @@
         <v>18</v>
       </c>
       <c r="V35" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="W35" s="1" t="n">
         <v>1</v>
       </c>
       <c r="X35" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y35" s="1" t="n">
         <v>2</v>
@@ -5552,7 +5552,7 @@
         <v>7</v>
       </c>
       <c r="AA35" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AB35" s="1" t="n">
         <v>6</v>
@@ -5561,38 +5561,38 @@
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B36" s="1" t="n">
         <v>9</v>
       </c>
       <c r="C36" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D36" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="E36" s="1" t="n">
         <v>13</v>
-      </c>
-      <c r="D36" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="E36" s="1" t="n">
-        <v>11</v>
       </c>
       <c r="F36" s="1" t="n">
         <v>4</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H36" s="1" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I36" s="1" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J36" s="1" t="n">
         <v>21</v>
       </c>
       <c r="K36" s="1" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="L36" s="1" t="n">
         <v>20</v>
@@ -5601,28 +5601,28 @@
         <v>22</v>
       </c>
       <c r="N36" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="O36" s="1" t="n">
         <v>27</v>
       </c>
       <c r="P36" s="1" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Q36" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R36" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="S36" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="T36" s="1" t="n">
         <v>23</v>
       </c>
       <c r="U36" s="1" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="V36" s="1" t="n">
         <v>15</v>
@@ -5637,10 +5637,10 @@
         <v>2</v>
       </c>
       <c r="Z36" s="1" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AA36" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AB36" s="1" t="n">
         <v>6</v>
@@ -5649,47 +5649,47 @@
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B37" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C37" s="1" t="n">
         <v>13</v>
       </c>
       <c r="D37" s="1" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="F37" s="1" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H37" s="1" t="n">
         <v>3</v>
       </c>
       <c r="I37" s="1" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J37" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="K37" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="L37" s="1" t="n">
         <v>20</v>
-      </c>
-      <c r="K37" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="L37" s="1" t="n">
-        <v>18</v>
       </c>
       <c r="M37" s="1" t="n">
         <v>22</v>
       </c>
       <c r="N37" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O37" s="1" t="n">
         <v>27</v>
@@ -5701,25 +5701,25 @@
         <v>25</v>
       </c>
       <c r="R37" s="1" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="S37" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="T37" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="U37" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="T37" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="U37" s="1" t="n">
-        <v>12</v>
-      </c>
       <c r="V37" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="W37" s="1" t="n">
         <v>1</v>
       </c>
       <c r="X37" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y37" s="1" t="n">
         <v>2</v>
@@ -5737,44 +5737,44 @@
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B38" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D38" s="1" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F38" s="1" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G38" s="1" t="n">
         <v>23</v>
       </c>
       <c r="H38" s="1" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I38" s="1" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J38" s="1" t="n">
         <v>20</v>
       </c>
       <c r="K38" s="1" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L38" s="1" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="M38" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N38" s="1" t="n">
         <v>11</v>
@@ -5786,86 +5786,86 @@
         <v>26</v>
       </c>
       <c r="Q38" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="R38" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="S38" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="T38" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="R38" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="S38" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="T38" s="1" t="n">
-        <v>25</v>
-      </c>
       <c r="U38" s="1" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="V38" s="1" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="W38" s="1" t="n">
         <v>1</v>
       </c>
       <c r="X38" s="1" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Y38" s="1" t="n">
         <v>2</v>
       </c>
       <c r="Z38" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA38" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AB38" s="1" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B39" s="1" t="n">
         <v>10</v>
       </c>
       <c r="C39" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="D39" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="D39" s="1" t="n">
-        <v>11</v>
-      </c>
       <c r="E39" s="1" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F39" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G39" s="1" t="n">
         <v>23</v>
       </c>
       <c r="H39" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="I39" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="J39" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="K39" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="I39" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="J39" s="1" t="n">
+      <c r="L39" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="M39" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="K39" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="L39" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="M39" s="1" t="n">
-        <v>22</v>
-      </c>
       <c r="N39" s="1" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="O39" s="1" t="n">
         <v>27</v>
@@ -5877,7 +5877,7 @@
         <v>24</v>
       </c>
       <c r="R39" s="1" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="S39" s="1" t="n">
         <v>19</v>
@@ -5886,16 +5886,16 @@
         <v>25</v>
       </c>
       <c r="U39" s="1" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="V39" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="W39" s="1" t="n">
         <v>1</v>
       </c>
       <c r="X39" s="1" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Y39" s="1" t="n">
         <v>2</v>
@@ -5904,23 +5904,23 @@
         <v>9</v>
       </c>
       <c r="AA39" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AB39" s="1" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B40" s="1" t="n">
         <v>10</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D40" s="1" t="n">
         <v>11</v>
@@ -5929,7 +5929,7 @@
         <v>20</v>
       </c>
       <c r="F40" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G40" s="1" t="n">
         <v>23</v>
@@ -5941,19 +5941,19 @@
         <v>7</v>
       </c>
       <c r="J40" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K40" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L40" s="1" t="n">
         <v>13</v>
       </c>
       <c r="M40" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N40" s="1" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="O40" s="1" t="n">
         <v>27</v>
@@ -5965,19 +5965,19 @@
         <v>24</v>
       </c>
       <c r="R40" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="S40" s="1" t="n">
         <v>19</v>
-      </c>
-      <c r="S40" s="1" t="n">
-        <v>18</v>
       </c>
       <c r="T40" s="1" t="n">
         <v>25</v>
       </c>
       <c r="U40" s="1" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="V40" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="W40" s="1" t="n">
         <v>1</v>
@@ -5992,7 +5992,7 @@
         <v>9</v>
       </c>
       <c r="AA40" s="1" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AB40" s="1" t="n">
         <v>8</v>
@@ -6001,44 +6001,44 @@
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B41" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="C41" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="C41" s="1" t="n">
-        <v>16</v>
-      </c>
       <c r="D41" s="1" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F41" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G41" s="1" t="n">
         <v>23</v>
       </c>
       <c r="H41" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I41" s="1" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J41" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="K41" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="L41" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="M41" s="1" t="n">
         <v>21</v>
-      </c>
-      <c r="K41" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="L41" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="M41" s="1" t="n">
-        <v>20</v>
       </c>
       <c r="N41" s="1" t="n">
         <v>12</v>
@@ -6062,19 +6062,19 @@
         <v>25</v>
       </c>
       <c r="U41" s="1" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="V41" s="1" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="W41" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="X41" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="X41" s="1" t="n">
-        <v>7</v>
-      </c>
       <c r="Y41" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Z41" s="1" t="n">
         <v>9</v>
@@ -6089,23 +6089,23 @@
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B42" s="1" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C42" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="D42" s="1" t="n">
         <v>14</v>
-      </c>
-      <c r="D42" s="1" t="n">
-        <v>13</v>
       </c>
       <c r="E42" s="1" t="n">
         <v>22</v>
       </c>
       <c r="F42" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G42" s="1" t="n">
         <v>23</v>
@@ -6117,16 +6117,16 @@
         <v>3</v>
       </c>
       <c r="J42" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K42" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L42" s="1" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="M42" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="N42" s="1" t="n">
         <v>12</v>
@@ -6141,47 +6141,47 @@
         <v>24</v>
       </c>
       <c r="R42" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="S42" s="1" t="n">
         <v>18</v>
-      </c>
-      <c r="S42" s="1" t="n">
-        <v>19</v>
       </c>
       <c r="T42" s="1" t="n">
         <v>25</v>
       </c>
       <c r="U42" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="V42" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="W42" s="1" t="n">
         <v>4</v>
       </c>
       <c r="X42" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y42" s="1" t="n">
         <v>5</v>
       </c>
       <c r="Z42" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA42" s="1" t="n">
         <v>17</v>
       </c>
       <c r="AB42" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B43" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C43" s="1" t="n">
         <v>14</v>
@@ -6190,31 +6190,31 @@
         <v>13</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F43" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G43" s="1" t="n">
         <v>23</v>
       </c>
       <c r="H43" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I43" s="1" t="n">
         <v>3</v>
       </c>
       <c r="J43" s="1" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K43" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L43" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M43" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N43" s="1" t="n">
         <v>12</v>
@@ -6229,19 +6229,19 @@
         <v>24</v>
       </c>
       <c r="R43" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="S43" s="1" t="n">
         <v>19</v>
-      </c>
-      <c r="S43" s="1" t="n">
-        <v>18</v>
       </c>
       <c r="T43" s="1" t="n">
         <v>25</v>
       </c>
       <c r="U43" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="V43" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="W43" s="1" t="n">
         <v>4</v>
@@ -6253,10 +6253,10 @@
         <v>5</v>
       </c>
       <c r="Z43" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA43" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AB43" s="1" t="n">
         <v>9</v>
@@ -6265,26 +6265,26 @@
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B44" s="1" t="n">
         <v>11</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D44" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F44" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H44" s="1" t="n">
         <v>2</v>
@@ -6293,13 +6293,13 @@
         <v>3</v>
       </c>
       <c r="J44" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K44" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L44" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M44" s="1" t="n">
         <v>20</v>
@@ -6314,16 +6314,16 @@
         <v>26</v>
       </c>
       <c r="Q44" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="R44" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="S44" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="T44" s="1" t="n">
         <v>25</v>
-      </c>
-      <c r="R44" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="S44" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="T44" s="1" t="n">
-        <v>24</v>
       </c>
       <c r="U44" s="1" t="n">
         <v>10</v>
@@ -6341,35 +6341,35 @@
         <v>5</v>
       </c>
       <c r="Z44" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA44" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="AB44" s="1" t="n">
         <v>9</v>
-      </c>
-      <c r="AA44" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="AB44" s="1" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B45" s="1" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D45" s="1" t="n">
         <v>14</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F45" s="1" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G45" s="1" t="n">
         <v>21</v>
@@ -6387,7 +6387,7 @@
         <v>1</v>
       </c>
       <c r="L45" s="1" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="M45" s="1" t="n">
         <v>20</v>
@@ -6399,56 +6399,56 @@
         <v>27</v>
       </c>
       <c r="P45" s="1" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="Q45" s="1" t="n">
         <v>25</v>
       </c>
       <c r="R45" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="S45" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="T45" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="U45" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="T45" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="U45" s="1" t="n">
+      <c r="V45" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="W45" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="V45" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="W45" s="1" t="n">
+      <c r="X45" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="X45" s="1" t="n">
-        <v>11</v>
-      </c>
       <c r="Y45" s="1" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Z45" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA45" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="AB45" s="1" t="n">
         <v>8</v>
-      </c>
-      <c r="AA45" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="AB45" s="1" t="n">
-        <v>9</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B46" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="C46" s="1" t="n">
         <v>17</v>
-      </c>
-      <c r="C46" s="1" t="n">
-        <v>15</v>
       </c>
       <c r="D46" s="1" t="n">
         <v>14</v>
@@ -6460,7 +6460,7 @@
         <v>5</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="H46" s="1" t="n">
         <v>2</v>
@@ -6469,25 +6469,25 @@
         <v>3</v>
       </c>
       <c r="J46" s="1" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K46" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L46" s="1" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="M46" s="1" t="n">
         <v>20</v>
       </c>
       <c r="N46" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="O46" s="1" t="n">
         <v>27</v>
       </c>
       <c r="P46" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q46" s="1" t="n">
         <v>25</v>
@@ -6496,47 +6496,47 @@
         <v>16</v>
       </c>
       <c r="S46" s="1" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T46" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="U46" s="1" t="n">
         <v>4</v>
       </c>
       <c r="V46" s="1" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="W46" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X46" s="1" t="n">
         <v>11</v>
       </c>
       <c r="Y46" s="1" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Z46" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA46" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="AB46" s="1" t="n">
         <v>9</v>
-      </c>
-      <c r="AA46" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="AB46" s="1" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B47" s="1" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D47" s="1" t="n">
         <v>14</v>
@@ -6557,34 +6557,34 @@
         <v>3</v>
       </c>
       <c r="J47" s="1" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K47" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L47" s="1" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M47" s="1" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="N47" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="O47" s="1" t="n">
         <v>27</v>
       </c>
       <c r="P47" s="1" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q47" s="1" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="R47" s="1" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="S47" s="1" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T47" s="1" t="n">
         <v>21</v>
@@ -6596,13 +6596,13 @@
         <v>12</v>
       </c>
       <c r="W47" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X47" s="1" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="Y47" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z47" s="1" t="n">
         <v>9</v>
@@ -6611,59 +6611,59 @@
         <v>19</v>
       </c>
       <c r="AB47" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B48" s="1" t="n">
         <v>25</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D48" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F48" s="1" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G48" s="1" t="n">
         <v>24</v>
       </c>
       <c r="H48" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I48" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="J48" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="K48" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="I48" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="J48" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="K48" s="1" t="n">
-        <v>3</v>
-      </c>
       <c r="L48" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M48" s="1" t="n">
         <v>18</v>
       </c>
       <c r="N48" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="O48" s="1" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P48" s="1" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="Q48" s="1" t="n">
         <v>23</v>
@@ -6672,56 +6672,56 @@
         <v>13</v>
       </c>
       <c r="S48" s="1" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T48" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="U48" s="1" t="n">
         <v>4</v>
       </c>
       <c r="V48" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="W48" s="1" t="n">
         <v>6</v>
       </c>
       <c r="X48" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Y48" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z48" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA48" s="1" t="n">
         <v>19</v>
       </c>
       <c r="AB48" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B49" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="C49" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="D49" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="E49" s="1" t="n">
         <v>27</v>
       </c>
-      <c r="C49" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="D49" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="E49" s="1" t="n">
-        <v>25</v>
-      </c>
       <c r="F49" s="1" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G49" s="1" t="n">
         <v>24</v>
@@ -6730,61 +6730,61 @@
         <v>1</v>
       </c>
       <c r="I49" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="J49" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="K49" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="J49" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="K49" s="1" t="n">
-        <v>2</v>
-      </c>
       <c r="L49" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M49" s="1" t="n">
         <v>18</v>
       </c>
       <c r="N49" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="O49" s="1" t="n">
         <v>26</v>
       </c>
       <c r="P49" s="1" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q49" s="1" t="n">
         <v>23</v>
       </c>
       <c r="R49" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="S49" s="1" t="n">
         <v>5</v>
       </c>
       <c r="T49" s="1" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="U49" s="1" t="n">
         <v>4</v>
       </c>
       <c r="V49" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="W49" s="1" t="n">
         <v>6</v>
       </c>
       <c r="X49" s="1" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="Y49" s="1" t="n">
         <v>7</v>
       </c>
       <c r="Z49" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA49" s="1" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AB49" s="1" t="n">
         <v>8</v>
@@ -6793,47 +6793,47 @@
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B50" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C50" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="D50" s="1" t="n">
         <v>13</v>
-      </c>
-      <c r="D50" s="1" t="n">
-        <v>6</v>
       </c>
       <c r="E50" s="1" t="n">
         <v>25</v>
       </c>
       <c r="F50" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H50" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I50" s="1" t="n">
         <v>3</v>
       </c>
       <c r="J50" s="1" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="K50" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L50" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M50" s="1" t="n">
         <v>18</v>
       </c>
       <c r="N50" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="O50" s="1" t="n">
         <v>26</v>
@@ -6851,53 +6851,53 @@
         <v>5</v>
       </c>
       <c r="T50" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="U50" s="1" t="n">
         <v>4</v>
       </c>
       <c r="V50" s="1" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="W50" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X50" s="1" t="n">
         <v>17</v>
       </c>
       <c r="Y50" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z50" s="1" t="n">
         <v>9</v>
       </c>
       <c r="AA50" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AB50" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B51" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C51" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="D51" s="1" t="n">
         <v>6</v>
-      </c>
-      <c r="D51" s="1" t="n">
-        <v>5</v>
       </c>
       <c r="E51" s="1" t="n">
         <v>25</v>
       </c>
       <c r="F51" s="1" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="G51" s="1" t="n">
         <v>22</v>
@@ -6921,22 +6921,22 @@
         <v>18</v>
       </c>
       <c r="N51" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="O51" s="1" t="n">
         <v>26</v>
       </c>
       <c r="P51" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Q51" s="1" t="n">
         <v>23</v>
       </c>
       <c r="R51" s="1" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="S51" s="1" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T51" s="1" t="n">
         <v>21</v>
@@ -6945,50 +6945,50 @@
         <v>4</v>
       </c>
       <c r="V51" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="W51" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X51" s="1" t="n">
         <v>17</v>
       </c>
       <c r="Y51" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z51" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="Z51" s="1" t="n">
+      <c r="AA51" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="AB51" s="1" t="n">
         <v>10</v>
-      </c>
-      <c r="AA51" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="AB51" s="1" t="n">
-        <v>11</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B52" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D52" s="1" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E52" s="1" t="n">
         <v>25</v>
       </c>
       <c r="F52" s="1" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H52" s="1" t="n">
         <v>2</v>
@@ -7006,7 +7006,7 @@
         <v>16</v>
       </c>
       <c r="M52" s="1" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N52" s="1" t="n">
         <v>14</v>
@@ -7015,68 +7015,68 @@
         <v>26</v>
       </c>
       <c r="P52" s="1" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="Q52" s="1" t="n">
         <v>23</v>
       </c>
       <c r="R52" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="S52" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="T52" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="U52" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="V52" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="W52" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="X52" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y52" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="S52" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="T52" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="U52" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="V52" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="W52" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="X52" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="Y52" s="1" t="n">
-        <v>5</v>
-      </c>
       <c r="Z52" s="1" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AA52" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AB52" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B53" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D53" s="1" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E53" s="1" t="n">
         <v>25</v>
       </c>
       <c r="F53" s="1" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H53" s="1" t="n">
         <v>2</v>
@@ -7085,25 +7085,25 @@
         <v>3</v>
       </c>
       <c r="J53" s="1" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K53" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L53" s="1" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="M53" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N53" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O53" s="1" t="n">
         <v>26</v>
       </c>
       <c r="P53" s="1" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="Q53" s="1" t="n">
         <v>23</v>
@@ -7112,31 +7112,31 @@
         <v>9</v>
       </c>
       <c r="S53" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="T53" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="U53" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="T53" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="U53" s="1" t="n">
-        <v>7</v>
-      </c>
       <c r="V53" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="W53" s="1" t="n">
         <v>4</v>
       </c>
       <c r="X53" s="1" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Y53" s="1" t="n">
         <v>5</v>
       </c>
       <c r="Z53" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA53" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AB53" s="1" t="n">
         <v>10</v>
@@ -7145,23 +7145,23 @@
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B54" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D54" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F54" s="1" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G54" s="1" t="n">
         <v>20</v>
@@ -7173,13 +7173,13 @@
         <v>3</v>
       </c>
       <c r="J54" s="1" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="K54" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L54" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="M54" s="1" t="n">
         <v>18</v>
@@ -7188,10 +7188,10 @@
         <v>15</v>
       </c>
       <c r="O54" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P54" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Q54" s="1" t="n">
         <v>23</v>
@@ -7206,25 +7206,25 @@
         <v>24</v>
       </c>
       <c r="U54" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V54" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="W54" s="1" t="n">
         <v>4</v>
       </c>
       <c r="X54" s="1" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Y54" s="1" t="n">
         <v>5</v>
       </c>
       <c r="Z54" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA54" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AB54" s="1" t="n">
         <v>10</v>
@@ -7233,26 +7233,26 @@
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B55" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C55" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="D55" s="1" t="n">
         <v>16</v>
-      </c>
-      <c r="D55" s="1" t="n">
-        <v>13</v>
       </c>
       <c r="E55" s="1" t="n">
         <v>26</v>
       </c>
       <c r="F55" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="G55" s="1" t="n">
         <v>20</v>
-      </c>
-      <c r="G55" s="1" t="n">
-        <v>22</v>
       </c>
       <c r="H55" s="1" t="n">
         <v>2</v>
@@ -7273,13 +7273,13 @@
         <v>18</v>
       </c>
       <c r="N55" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="O55" s="1" t="n">
         <v>25</v>
       </c>
       <c r="P55" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Q55" s="1" t="n">
         <v>23</v>
@@ -7297,7 +7297,7 @@
         <v>8</v>
       </c>
       <c r="V55" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="W55" s="1" t="n">
         <v>4</v>
@@ -7312,7 +7312,7 @@
         <v>7</v>
       </c>
       <c r="AA55" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AB55" s="1" t="n">
         <v>10</v>
@@ -7321,7 +7321,7 @@
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B56" s="1" t="n">
@@ -7331,16 +7331,16 @@
         <v>16</v>
       </c>
       <c r="D56" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F56" s="1" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H56" s="1" t="n">
         <v>2</v>
@@ -7358,22 +7358,22 @@
         <v>11</v>
       </c>
       <c r="M56" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="N56" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="N56" s="1" t="n">
-        <v>15</v>
-      </c>
       <c r="O56" s="1" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P56" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="Q56" s="1" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="R56" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="S56" s="1" t="n">
         <v>6</v>
@@ -7385,13 +7385,13 @@
         <v>8</v>
       </c>
       <c r="V56" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="W56" s="1" t="n">
         <v>4</v>
       </c>
       <c r="X56" s="1" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="Y56" s="1" t="n">
         <v>5</v>
@@ -7400,71 +7400,71 @@
         <v>7</v>
       </c>
       <c r="AA56" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AB56" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B57" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D57" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F57" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="G57" s="1" t="n">
         <v>20</v>
-      </c>
-      <c r="G57" s="1" t="n">
-        <v>17</v>
       </c>
       <c r="H57" s="1" t="n">
         <v>2</v>
       </c>
       <c r="I57" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J57" s="1" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K57" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L57" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="M57" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N57" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="O57" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="P57" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="O57" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="P57" s="1" t="n">
-        <v>11</v>
-      </c>
       <c r="Q57" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R57" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="S57" s="1" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T57" s="1" t="n">
         <v>24</v>
@@ -7476,132 +7476,132 @@
         <v>13</v>
       </c>
       <c r="W57" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="X57" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y57" s="1" t="n">
         <v>5</v>
-      </c>
-      <c r="X57" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="Y57" s="1" t="n">
-        <v>6</v>
       </c>
       <c r="Z57" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AA57" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AB57" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B58" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D58" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E58" s="1" t="n">
         <v>26</v>
       </c>
       <c r="F58" s="1" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H58" s="1" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I58" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J58" s="1" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="K58" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L58" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M58" s="1" t="n">
         <v>18</v>
       </c>
       <c r="N58" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O58" s="1" t="n">
         <v>25</v>
       </c>
       <c r="P58" s="1" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="Q58" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="R58" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="S58" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T58" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="U58" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V58" s="1" t="n">
         <v>13</v>
       </c>
       <c r="W58" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X58" s="1" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="Y58" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z58" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AA58" s="1" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AB58" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B59" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D59" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E59" s="1" t="n">
         <v>26</v>
       </c>
       <c r="F59" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G59" s="1" t="n">
         <v>20</v>
@@ -7610,7 +7610,7 @@
         <v>6</v>
       </c>
       <c r="I59" s="1" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J59" s="1" t="n">
         <v>19</v>
@@ -7631,10 +7631,10 @@
         <v>25</v>
       </c>
       <c r="P59" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Q59" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R59" s="1" t="n">
         <v>10</v>
@@ -7643,53 +7643,53 @@
         <v>2</v>
       </c>
       <c r="T59" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="U59" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="V59" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="W59" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="X59" s="1" t="n">
         <v>24</v>
-      </c>
-      <c r="U59" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="V59" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="W59" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="X59" s="1" t="n">
-        <v>23</v>
       </c>
       <c r="Y59" s="1" t="n">
         <v>5</v>
       </c>
       <c r="Z59" s="1" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AA59" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AB59" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B60" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D60" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E60" s="1" t="n">
         <v>26</v>
       </c>
       <c r="F60" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G60" s="1" t="n">
         <v>20</v>
@@ -7698,25 +7698,25 @@
         <v>6</v>
       </c>
       <c r="I60" s="1" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J60" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K60" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L60" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M60" s="1" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N60" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O60" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="P60" s="1" t="n">
         <v>17</v>
@@ -7725,31 +7725,31 @@
         <v>22</v>
       </c>
       <c r="R60" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="S60" s="1" t="n">
         <v>2</v>
       </c>
       <c r="T60" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="U60" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="V60" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="W60" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="X60" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="U60" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="V60" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="W60" s="1" t="n">
+      <c r="Y60" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z60" s="1" t="n">
         <v>4</v>
-      </c>
-      <c r="X60" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="Y60" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z60" s="1" t="n">
-        <v>5</v>
       </c>
       <c r="AA60" s="1" t="n">
         <v>21</v>
@@ -7761,32 +7761,32 @@
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B61" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D61" s="1" t="n">
         <v>11</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F61" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G61" s="1" t="n">
         <v>20</v>
       </c>
       <c r="H61" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="I61" s="1" t="n">
         <v>3</v>
-      </c>
-      <c r="I61" s="1" t="n">
-        <v>12</v>
       </c>
       <c r="J61" s="1" t="n">
         <v>18</v>
@@ -7795,13 +7795,13 @@
         <v>1</v>
       </c>
       <c r="L61" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M61" s="1" t="n">
         <v>19</v>
       </c>
       <c r="N61" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O61" s="1" t="n">
         <v>24</v>
@@ -7813,28 +7813,28 @@
         <v>22</v>
       </c>
       <c r="R61" s="1" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="S61" s="1" t="n">
         <v>2</v>
       </c>
       <c r="T61" s="1" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="U61" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V61" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="W61" s="1" t="n">
         <v>4</v>
       </c>
       <c r="X61" s="1" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Y61" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z61" s="1" t="n">
         <v>5</v>
@@ -7843,77 +7843,77 @@
         <v>21</v>
       </c>
       <c r="AB61" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B62" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C62" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="D62" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="D62" s="1" t="n">
-        <v>10</v>
-      </c>
       <c r="E62" s="1" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F62" s="1" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G62" s="1" t="n">
         <v>20</v>
       </c>
       <c r="H62" s="1" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="I62" s="1" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="J62" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K62" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L62" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M62" s="1" t="n">
         <v>19</v>
       </c>
       <c r="N62" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O62" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P62" s="1" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Q62" s="1" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="R62" s="1" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="S62" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T62" s="1" t="n">
         <v>26</v>
       </c>
       <c r="U62" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="V62" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="W62" s="1" t="n">
         <v>4</v>
@@ -7922,7 +7922,7 @@
         <v>23</v>
       </c>
       <c r="Y62" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z62" s="1" t="n">
         <v>5</v>
@@ -7931,62 +7931,62 @@
         <v>21</v>
       </c>
       <c r="AB62" s="1" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B63" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D63" s="1" t="n">
         <v>10</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F63" s="1" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="G63" s="1" t="n">
         <v>20</v>
       </c>
       <c r="H63" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I63" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J63" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K63" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L63" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M63" s="1" t="n">
         <v>19</v>
       </c>
       <c r="N63" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O63" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="P63" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q63" s="1" t="n">
         <v>24</v>
-      </c>
-      <c r="P63" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q63" s="1" t="n">
-        <v>21</v>
       </c>
       <c r="R63" s="1" t="n">
         <v>3</v>
@@ -7995,10 +7995,10 @@
         <v>1</v>
       </c>
       <c r="T63" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="U63" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V63" s="1" t="n">
         <v>12</v>
@@ -8007,7 +8007,7 @@
         <v>4</v>
       </c>
       <c r="X63" s="1" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="Y63" s="1" t="n">
         <v>6</v>
@@ -8016,50 +8016,50 @@
         <v>5</v>
       </c>
       <c r="AA63" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AB63" s="1" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B64" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D64" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F64" s="1" t="n">
         <v>18</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H64" s="1" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="I64" s="1" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="J64" s="1" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="K64" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L64" s="1" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="M64" s="1" t="n">
         <v>19</v>
@@ -8068,37 +8068,37 @@
         <v>17</v>
       </c>
       <c r="O64" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P64" s="1" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="Q64" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R64" s="1" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="S64" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T64" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="U64" s="1" t="n">
         <v>7</v>
       </c>
       <c r="V64" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="W64" s="1" t="n">
         <v>4</v>
       </c>
       <c r="X64" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Y64" s="1" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Z64" s="1" t="n">
         <v>5</v>
@@ -8113,7 +8113,7 @@
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B65" s="1" t="n">
@@ -8123,10 +8123,10 @@
         <v>16</v>
       </c>
       <c r="D65" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F65" s="1" t="n">
         <v>18</v>
@@ -8135,19 +8135,19 @@
         <v>21</v>
       </c>
       <c r="H65" s="1" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="I65" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J65" s="1" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K65" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L65" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M65" s="1" t="n">
         <v>19</v>
@@ -8165,13 +8165,13 @@
         <v>20</v>
       </c>
       <c r="R65" s="1" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="S65" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T65" s="1" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="U65" s="1" t="n">
         <v>7</v>
@@ -8180,101 +8180,101 @@
         <v>15</v>
       </c>
       <c r="W65" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X65" s="1" t="n">
         <v>25</v>
       </c>
       <c r="Y65" s="1" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="Z65" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA65" s="1" t="n">
         <v>22</v>
       </c>
       <c r="AB65" s="1" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B66" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D66" s="1" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E66" s="1" t="n">
         <v>24</v>
       </c>
       <c r="F66" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G66" s="1" t="n">
         <v>21</v>
       </c>
       <c r="H66" s="1" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I66" s="1" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="J66" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K66" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L66" s="1" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="M66" s="1" t="n">
         <v>19</v>
       </c>
       <c r="N66" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O66" s="1" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="P66" s="1" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="Q66" s="1" t="n">
         <v>20</v>
       </c>
       <c r="R66" s="1" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="S66" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T66" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="U66" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V66" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="W66" s="1" t="n">
         <v>3</v>
       </c>
       <c r="X66" s="1" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Y66" s="1" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="Z66" s="1" t="n">
         <v>4</v>
@@ -8289,41 +8289,41 @@
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B67" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D67" s="1" t="n">
         <v>8</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F67" s="1" t="n">
         <v>16</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H67" s="1" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="I67" s="1" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="J67" s="1" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="K67" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L67" s="1" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="M67" s="1" t="n">
         <v>19</v>
@@ -8338,7 +8338,7 @@
         <v>12</v>
       </c>
       <c r="Q67" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="R67" s="1" t="n">
         <v>7</v>
@@ -8347,13 +8347,13 @@
         <v>1</v>
       </c>
       <c r="T67" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="U67" s="1" t="n">
         <v>6</v>
       </c>
       <c r="V67" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="W67" s="1" t="n">
         <v>3</v>
@@ -8362,7 +8362,7 @@
         <v>23</v>
       </c>
       <c r="Y67" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Z67" s="1" t="n">
         <v>4</v>

--- a/NSE_Sector_Monitor.xlsx
+++ b/NSE_Sector_Monitor.xlsx
@@ -568,22 +568,22 @@
         <v>0</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>13.93</v>
+        <v>13.92</v>
       </c>
       <c r="H2" s="1" t="n">
-        <v>-7.32</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="I2" s="1" t="n">
-        <v>-4.37</v>
+        <v>-3.29</v>
       </c>
       <c r="J2" s="1" t="n">
-        <v>-1.96</v>
+        <v>0.49</v>
       </c>
       <c r="K2" s="1" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="L2" s="1" t="inlineStr">
         <is>
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="M2" s="1" t="n">
-        <v>-7.53</v>
+        <v>-4.66</v>
       </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
@@ -627,40 +627,40 @@
         <v>0</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>2</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>27.8</v>
+        <v>27.56</v>
       </c>
       <c r="H3" s="1" t="n">
+        <v>-0.86</v>
+      </c>
+      <c r="I3" s="1" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="J3" s="1" t="n">
+        <v>5.07</v>
+      </c>
+      <c r="K3" s="1" t="n">
+        <v>10.08</v>
+      </c>
+      <c r="L3" s="1" t="inlineStr">
+        <is>
+          <t>Up</t>
+        </is>
+      </c>
+      <c r="M3" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="I3" s="1" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="J3" s="1" t="n">
-        <v>4.87</v>
-      </c>
-      <c r="K3" s="1" t="n">
-        <v>10.91</v>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>Up</t>
-        </is>
-      </c>
-      <c r="M3" s="1" t="n">
-        <v>-0.23</v>
-      </c>
       <c r="N3" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O3" s="1" t="inlineStr">
@@ -692,28 +692,28 @@
         <v>0</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>85.7</v>
+        <v>84.53</v>
       </c>
       <c r="H4" s="1" t="n">
-        <v>-3.49</v>
+        <v>-1.37</v>
       </c>
       <c r="I4" s="1" t="n">
-        <v>-1.97</v>
+        <v>-2.09</v>
       </c>
       <c r="J4" s="1" t="n">
-        <v>-2.13</v>
+        <v>-2.53</v>
       </c>
       <c r="K4" s="1" t="n">
-        <v>8.51</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="L4" s="1" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
         </is>
       </c>
       <c r="M4" s="1" t="n">
-        <v>-10.18</v>
+        <v>-9.93</v>
       </c>
       <c r="N4" s="1" t="inlineStr">
         <is>
@@ -757,7 +757,7 @@
         <v>1</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>-2</v>
@@ -766,19 +766,19 @@
         <v>-2</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>87.06999999999999</v>
+        <v>85.33</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>-0.19</v>
+        <v>-2</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>3.18</v>
+        <v>2.44</v>
       </c>
       <c r="J5" s="1" t="n">
-        <v>-0.89</v>
+        <v>-0.57</v>
       </c>
       <c r="K5" s="1" t="n">
-        <v>8.08</v>
+        <v>8.1</v>
       </c>
       <c r="L5" s="1" t="inlineStr">
         <is>
@@ -786,16 +786,16 @@
         </is>
       </c>
       <c r="M5" s="1" t="n">
-        <v>-5.51</v>
+        <v>-5.85</v>
       </c>
       <c r="N5" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O5" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P5" s="1" t="inlineStr">
@@ -812,65 +812,65 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Metal</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
         <v>5</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>13.18</v>
+        <v>31.23</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>-1.2</v>
+        <v>-0.22</v>
       </c>
       <c r="I6" s="1" t="n">
-        <v>1.82</v>
+        <v>-0.02</v>
       </c>
       <c r="J6" s="1" t="n">
-        <v>1.5</v>
+        <v>-4.75</v>
       </c>
       <c r="K6" s="1" t="n">
-        <v>7.99</v>
+        <v>7.62</v>
       </c>
       <c r="L6" s="1" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Down</t>
         </is>
       </c>
       <c r="M6" s="1" t="n">
-        <v>-3.88</v>
+        <v>-24.59</v>
       </c>
       <c r="N6" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O6" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P6" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Q6" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -893,22 +893,22 @@
         <v>1</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>17.17</v>
+        <v>17.03</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>-1.09</v>
+        <v>-0.82</v>
       </c>
       <c r="I7" s="1" t="n">
-        <v>1.23</v>
+        <v>1.04</v>
       </c>
       <c r="J7" s="1" t="n">
-        <v>3.71</v>
+        <v>4.54</v>
       </c>
       <c r="K7" s="1" t="n">
-        <v>7.06</v>
+        <v>6.26</v>
       </c>
       <c r="L7" s="1" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         </is>
       </c>
       <c r="M7" s="1" t="n">
-        <v>-1.32</v>
+        <v>0</v>
       </c>
       <c r="N7" s="1" t="inlineStr">
         <is>
@@ -925,12 +925,12 @@
       </c>
       <c r="O7" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P7" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Q7" s="1" t="inlineStr">
@@ -942,46 +942,46 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Metal</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
         <v>7</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>31.3</v>
+        <v>12.91</v>
       </c>
       <c r="H8" s="1" t="n">
-        <v>-0.54</v>
+        <v>-2.05</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>-0.98</v>
+        <v>1.72</v>
       </c>
       <c r="J8" s="1" t="n">
-        <v>-3.54</v>
+        <v>0.76</v>
       </c>
       <c r="K8" s="1" t="n">
-        <v>5.42</v>
+        <v>6.08</v>
       </c>
       <c r="L8" s="1" t="inlineStr">
         <is>
-          <t>Down</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="M8" s="1" t="n">
-        <v>-25.67</v>
+        <v>-4.28</v>
       </c>
       <c r="N8" s="1" t="inlineStr">
         <is>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="Q8" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1017,28 +1017,28 @@
         <v>-1</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>-3</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>278.51</v>
+        <v>274.3</v>
       </c>
       <c r="H9" s="1" t="n">
-        <v>-0.72</v>
+        <v>-1.51</v>
       </c>
       <c r="I9" s="1" t="n">
-        <v>-0.45</v>
+        <v>0.28</v>
       </c>
       <c r="J9" s="1" t="n">
-        <v>-3.22</v>
+        <v>-2.62</v>
       </c>
       <c r="K9" s="1" t="n">
-        <v>2.71</v>
+        <v>4.06</v>
       </c>
       <c r="L9" s="1" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="M9" s="1" t="n">
-        <v>-4.96</v>
+        <v>-4.84</v>
       </c>
       <c r="N9" s="1" t="inlineStr">
         <is>
@@ -1072,38 +1072,38 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Defence</t>
+          <t>Manufacturing</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
         <v>9</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>-4</v>
+        <v>5</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-8</v>
+        <v>6</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>103.08</v>
+        <v>159.19</v>
       </c>
       <c r="H10" s="1" t="n">
-        <v>-0.66</v>
+        <v>-1.46</v>
       </c>
       <c r="I10" s="1" t="n">
-        <v>0.85</v>
+        <v>0.62</v>
       </c>
       <c r="J10" s="1" t="n">
-        <v>-0.21</v>
+        <v>0.04</v>
       </c>
       <c r="K10" s="1" t="n">
-        <v>2.34</v>
+        <v>2.48</v>
       </c>
       <c r="L10" s="1" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="M10" s="1" t="n">
-        <v>-3.96</v>
+        <v>-0.54</v>
       </c>
       <c r="N10" s="1" t="inlineStr">
         <is>
@@ -1137,46 +1137,46 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>Manufacturing</t>
+          <t>EV &amp; New Age Auto</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
         <v>10</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>3</v>
+        <v>-2</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>6</v>
+        <v>-4</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>3</v>
+        <v>-5</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>161.55</v>
+        <v>30.94</v>
       </c>
       <c r="H11" s="1" t="n">
-        <v>0.39</v>
+        <v>-1.56</v>
       </c>
       <c r="I11" s="1" t="n">
-        <v>0.38</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J11" s="1" t="n">
-        <v>-0.62</v>
+        <v>-1.9</v>
       </c>
       <c r="K11" s="1" t="n">
-        <v>2</v>
+        <v>2.46</v>
       </c>
       <c r="L11" s="1" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Down</t>
         </is>
       </c>
       <c r="M11" s="1" t="n">
-        <v>-0.72</v>
+        <v>-4.05</v>
       </c>
       <c r="N11" s="1" t="inlineStr">
         <is>
@@ -1202,38 +1202,38 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Consumption</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
         <v>11</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>4</v>
+        <v>-2</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-5</v>
+        <v>6</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>29.44</v>
+        <v>125.98</v>
       </c>
       <c r="H12" s="1" t="n">
-        <v>-0.54</v>
+        <v>-1.2</v>
       </c>
       <c r="I12" s="1" t="n">
-        <v>1.53</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="J12" s="1" t="n">
-        <v>0.61</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="K12" s="1" t="n">
-        <v>1.95</v>
+        <v>2.11</v>
       </c>
       <c r="L12" s="1" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="M12" s="1" t="n">
-        <v>0</v>
+        <v>-4.7</v>
       </c>
       <c r="N12" s="1" t="inlineStr">
         <is>
@@ -1267,46 +1267,46 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>EV &amp; New Age Auto</t>
+          <t>Defence</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
         <v>12</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>-4</v>
+        <v>7</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>-1</v>
+        <v>-7</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-7</v>
+        <v>-11</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>31.43</v>
+        <v>101.45</v>
       </c>
       <c r="H13" s="1" t="n">
-        <v>-0.22</v>
+        <v>-1.58</v>
       </c>
       <c r="I13" s="1" t="n">
-        <v>-0.5600000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="J13" s="1" t="n">
-        <v>-1.8</v>
+        <v>0.48</v>
       </c>
       <c r="K13" s="1" t="n">
-        <v>1.67</v>
+        <v>1.81</v>
       </c>
       <c r="L13" s="1" t="inlineStr">
         <is>
-          <t>Down</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="M13" s="1" t="n">
-        <v>-4.14</v>
+        <v>-3.9</v>
       </c>
       <c r="N13" s="1" t="inlineStr">
         <is>
@@ -1332,46 +1332,46 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Consumption</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
         <v>13</v>
       </c>
       <c r="C14" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>-3</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>-6</v>
+      </c>
+      <c r="G14" s="1" t="n">
+        <v>28.74</v>
+      </c>
+      <c r="H14" s="1" t="n">
+        <v>-2.38</v>
+      </c>
+      <c r="I14" s="1" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="J14" s="1" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="K14" s="1" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="L14" s="1" t="inlineStr">
+        <is>
+          <t>Down</t>
+        </is>
+      </c>
+      <c r="M14" s="1" t="n">
         <v>0</v>
-      </c>
-      <c r="D14" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="G14" s="1" t="n">
-        <v>127.51</v>
-      </c>
-      <c r="H14" s="1" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="I14" s="1" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="J14" s="1" t="n">
-        <v>-0.57</v>
-      </c>
-      <c r="K14" s="1" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="L14" s="1" t="inlineStr">
-        <is>
-          <t>Down</t>
-        </is>
-      </c>
-      <c r="M14" s="1" t="n">
-        <v>-5.12</v>
       </c>
       <c r="N14" s="1" t="inlineStr">
         <is>
@@ -1404,31 +1404,31 @@
         <v>14</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E15" s="2" t="n">
         <v>9</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>11.01</v>
+        <v>10.85</v>
       </c>
       <c r="H15" s="1" t="n">
-        <v>-1.26</v>
+        <v>-1.45</v>
       </c>
       <c r="I15" s="1" t="n">
-        <v>-0.13</v>
+        <v>-0.3</v>
       </c>
       <c r="J15" s="1" t="n">
-        <v>1.58</v>
+        <v>2.25</v>
       </c>
       <c r="K15" s="1" t="n">
-        <v>-0.37</v>
+        <v>0.31</v>
       </c>
       <c r="L15" s="1" t="inlineStr">
         <is>
@@ -1436,7 +1436,7 @@
         </is>
       </c>
       <c r="M15" s="1" t="n">
-        <v>-9.16</v>
+        <v>-8.98</v>
       </c>
       <c r="N15" s="1" t="inlineStr">
         <is>
@@ -1462,38 +1462,38 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Capital Market</t>
+          <t>Tourism</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
         <v>15</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>3</v>
+        <v>-3</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>5</v>
+        <v>-7</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-12</v>
+        <v>-11</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>52.97</v>
+        <v>75.95</v>
       </c>
       <c r="H16" s="1" t="n">
-        <v>-1.69</v>
+        <v>-0.98</v>
       </c>
       <c r="I16" s="1" t="n">
-        <v>-0.1</v>
+        <v>0.11</v>
       </c>
       <c r="J16" s="1" t="n">
-        <v>-0</v>
+        <v>2.13</v>
       </c>
       <c r="K16" s="1" t="n">
-        <v>-0.96</v>
+        <v>-0.34</v>
       </c>
       <c r="L16" s="1" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         </is>
       </c>
       <c r="M16" s="1" t="n">
-        <v>0</v>
+        <v>-11.88</v>
       </c>
       <c r="N16" s="1" t="inlineStr">
         <is>
@@ -1527,38 +1527,38 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>MNC</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
         <v>16</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>-2</v>
+        <v>4</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>6</v>
+        <v>-5</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>29.82</v>
+        <v>31.93</v>
       </c>
       <c r="H17" s="1" t="n">
-        <v>-1.84</v>
+        <v>-0.84</v>
       </c>
       <c r="I17" s="1" t="n">
-        <v>-0.72</v>
+        <v>0.77</v>
       </c>
       <c r="J17" s="1" t="n">
-        <v>-0.1</v>
+        <v>-0.52</v>
       </c>
       <c r="K17" s="1" t="n">
-        <v>-1.02</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="L17" s="1" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         </is>
       </c>
       <c r="M17" s="1" t="n">
-        <v>0</v>
+        <v>-3.64</v>
       </c>
       <c r="N17" s="1" t="inlineStr">
         <is>
@@ -1592,46 +1592,46 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>MNC</t>
+          <t>Commodities</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
         <v>17</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-10</v>
+        <v>3</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>32.2</v>
+        <v>95.39</v>
       </c>
       <c r="H18" s="1" t="n">
-        <v>-0.89</v>
+        <v>-1.62</v>
       </c>
       <c r="I18" s="1" t="n">
-        <v>-0.47</v>
+        <v>0.61</v>
       </c>
       <c r="J18" s="1" t="n">
-        <v>-1.76</v>
+        <v>1.13</v>
       </c>
       <c r="K18" s="1" t="n">
-        <v>-1.21</v>
+        <v>-0.96</v>
       </c>
       <c r="L18" s="1" t="inlineStr">
         <is>
-          <t>Down</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="M18" s="1" t="n">
-        <v>-4.42</v>
+        <v>-8.35</v>
       </c>
       <c r="N18" s="1" t="inlineStr">
         <is>
@@ -1657,46 +1657,46 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>PSE</t>
+          <t>Services</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
         <v>18</v>
       </c>
       <c r="C19" s="2" t="n">
+        <v>-5</v>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>-3</v>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>-3</v>
+      </c>
+      <c r="F19" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="D19" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="E19" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="F19" s="2" t="n">
-        <v>8</v>
-      </c>
       <c r="G19" s="1" t="n">
-        <v>9.970000000000001</v>
+        <v>29.24</v>
       </c>
       <c r="H19" s="1" t="n">
-        <v>-0.5</v>
+        <v>-1.95</v>
       </c>
       <c r="I19" s="1" t="n">
-        <v>0.24</v>
+        <v>-1.2</v>
       </c>
       <c r="J19" s="1" t="n">
-        <v>2.45</v>
+        <v>-0.88</v>
       </c>
       <c r="K19" s="1" t="n">
-        <v>-1.21</v>
+        <v>-1.57</v>
       </c>
       <c r="L19" s="1" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Down</t>
         </is>
       </c>
       <c r="M19" s="1" t="n">
-        <v>-10.19</v>
+        <v>0</v>
       </c>
       <c r="N19" s="1" t="inlineStr">
         <is>
@@ -1722,46 +1722,46 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>Commodities</t>
+          <t>Fin Services</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
         <v>19</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>4</v>
+        <v>-7</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>6</v>
+        <v>-8</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>6</v>
+        <v>-2</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>1</v>
+        <v>-7</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>96.95999999999999</v>
+        <v>30.56</v>
       </c>
       <c r="H20" s="1" t="n">
-        <v>-0.02</v>
+        <v>-1.74</v>
       </c>
       <c r="I20" s="1" t="n">
-        <v>0.49</v>
+        <v>-2.38</v>
       </c>
       <c r="J20" s="1" t="n">
-        <v>0.53</v>
+        <v>-2.76</v>
       </c>
       <c r="K20" s="1" t="n">
-        <v>-1.35</v>
+        <v>-1.57</v>
       </c>
       <c r="L20" s="1" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Down</t>
         </is>
       </c>
       <c r="M20" s="1" t="n">
-        <v>-8.369999999999999</v>
+        <v>-3.93</v>
       </c>
       <c r="N20" s="1" t="inlineStr">
         <is>
@@ -1787,46 +1787,46 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>Fin Services</t>
+          <t>Private Bank</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
         <v>20</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>-11</v>
+        <v>-2</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>-13</v>
+        <v>-2</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>-5</v>
+        <v>-7</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>-11</v>
+        <v>-7</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>31.1</v>
+        <v>27.09</v>
       </c>
       <c r="H21" s="1" t="n">
-        <v>-3.92</v>
+        <v>-1.31</v>
       </c>
       <c r="I21" s="1" t="n">
-        <v>-2.65</v>
+        <v>-0.05</v>
       </c>
       <c r="J21" s="1" t="n">
-        <v>-3.38</v>
+        <v>1.23</v>
       </c>
       <c r="K21" s="1" t="n">
-        <v>-1.36</v>
+        <v>-1.7</v>
       </c>
       <c r="L21" s="1" t="inlineStr">
         <is>
-          <t>Down</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="M21" s="1" t="n">
-        <v>-4.14</v>
+        <v>-3.88</v>
       </c>
       <c r="N21" s="1" t="inlineStr">
         <is>
@@ -1852,38 +1852,38 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>Tourism</t>
+          <t>PSE</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
         <v>21</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>-9</v>
+        <v>1</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>-11</v>
+        <v>0</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>-15</v>
+        <v>4</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>-17</v>
+        <v>2</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>76.7</v>
+        <v>9.81</v>
       </c>
       <c r="H22" s="1" t="n">
-        <v>-2.08</v>
+        <v>-1.6</v>
       </c>
       <c r="I22" s="1" t="n">
-        <v>-0.57</v>
+        <v>0.37</v>
       </c>
       <c r="J22" s="1" t="n">
-        <v>0.37</v>
+        <v>2.59</v>
       </c>
       <c r="K22" s="1" t="n">
-        <v>-1.81</v>
+        <v>-1.94</v>
       </c>
       <c r="L22" s="1" t="inlineStr">
         <is>
@@ -1891,7 +1891,7 @@
         </is>
       </c>
       <c r="M22" s="1" t="n">
-        <v>-13.2</v>
+        <v>-10.15</v>
       </c>
       <c r="N22" s="1" t="inlineStr">
         <is>
@@ -1917,46 +1917,46 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>PSU Bank</t>
+          <t>Bank</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
         <v>22</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>3</v>
+        <v>-5</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>2</v>
+        <v>-6</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>-8</v>
+        <v>-11</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>2</v>
+        <v>-6</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>92.34999999999999</v>
+        <v>565.3200000000001</v>
       </c>
       <c r="H23" s="1" t="n">
-        <v>-0.9</v>
+        <v>-1.91</v>
       </c>
       <c r="I23" s="1" t="n">
-        <v>0.72</v>
+        <v>-0.68</v>
       </c>
       <c r="J23" s="1" t="n">
-        <v>-0.15</v>
+        <v>0.37</v>
       </c>
       <c r="K23" s="1" t="n">
-        <v>-2.09</v>
+        <v>-2.2</v>
       </c>
       <c r="L23" s="1" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Down</t>
         </is>
       </c>
       <c r="M23" s="1" t="n">
-        <v>-13.29</v>
+        <v>-6.02</v>
       </c>
       <c r="N23" s="1" t="inlineStr">
         <is>
@@ -1982,38 +1982,38 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Bank</t>
+          <t>Capital Market</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
         <v>23</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>-3</v>
+        <v>2</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>-13</v>
+        <v>-2</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>-9</v>
+        <v>-20</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>576.33</v>
+        <v>51.77</v>
       </c>
       <c r="H24" s="1" t="n">
-        <v>-1.58</v>
+        <v>-2.27</v>
       </c>
       <c r="I24" s="1" t="n">
-        <v>-0.21</v>
+        <v>0.57</v>
       </c>
       <c r="J24" s="1" t="n">
-        <v>0.32</v>
+        <v>-1.09</v>
       </c>
       <c r="K24" s="1" t="n">
-        <v>-2.09</v>
+        <v>-2.27</v>
       </c>
       <c r="L24" s="1" t="inlineStr">
         <is>
@@ -2021,7 +2021,7 @@
         </is>
       </c>
       <c r="M24" s="1" t="n">
-        <v>-5.76</v>
+        <v>0</v>
       </c>
       <c r="N24" s="1" t="inlineStr">
         <is>
@@ -2047,46 +2047,46 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>Private Bank</t>
+          <t>PSU Bank</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
         <v>24</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>-12</v>
+        <v>-10</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>27.45</v>
+        <v>89.92</v>
       </c>
       <c r="H25" s="1" t="n">
-        <v>-1.79</v>
+        <v>-2.63</v>
       </c>
       <c r="I25" s="1" t="n">
-        <v>-0.33</v>
+        <v>-0.32</v>
       </c>
       <c r="J25" s="1" t="n">
-        <v>0.62</v>
+        <v>-0.91</v>
       </c>
       <c r="K25" s="1" t="n">
-        <v>-2.5</v>
+        <v>-2.61</v>
       </c>
       <c r="L25" s="1" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Down</t>
         </is>
       </c>
       <c r="M25" s="1" t="n">
-        <v>-4.2</v>
+        <v>-14.16</v>
       </c>
       <c r="N25" s="1" t="inlineStr">
         <is>
@@ -2119,31 +2119,31 @@
         <v>25</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>-1</v>
+        <v>-4</v>
       </c>
       <c r="D26" s="2" t="n">
         <v>-3</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="F26" s="2" t="n">
         <v>-6</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>92.43000000000001</v>
+        <v>90.51000000000001</v>
       </c>
       <c r="H26" s="1" t="n">
-        <v>0.38</v>
+        <v>-2.08</v>
       </c>
       <c r="I26" s="1" t="n">
-        <v>0.47</v>
+        <v>-0.1</v>
       </c>
       <c r="J26" s="1" t="n">
-        <v>0.76</v>
+        <v>1.05</v>
       </c>
       <c r="K26" s="1" t="n">
-        <v>-2.92</v>
+        <v>-3.13</v>
       </c>
       <c r="L26" s="1" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="M26" s="1" t="n">
-        <v>-4.58</v>
+        <v>-5</v>
       </c>
       <c r="N26" s="1" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
@@ -2187,28 +2187,28 @@
         <v>0</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>-14</v>
+        <v>-5</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>37.64</v>
+        <v>48.76</v>
       </c>
       <c r="H27" s="1" t="n">
-        <v>-1</v>
+        <v>-1.46</v>
       </c>
       <c r="I27" s="1" t="n">
-        <v>0.09</v>
+        <v>1.08</v>
       </c>
       <c r="J27" s="1" t="n">
-        <v>2.1</v>
+        <v>2.51</v>
       </c>
       <c r="K27" s="1" t="n">
-        <v>-3.27</v>
+        <v>-4.1</v>
       </c>
       <c r="L27" s="1" t="inlineStr">
         <is>
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M27" s="1" t="n">
-        <v>0</v>
+        <v>-15.08</v>
       </c>
       <c r="N27" s="1" t="inlineStr">
         <is>
@@ -2242,7 +2242,7 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
@@ -2252,40 +2252,40 @@
         <v>0</v>
       </c>
       <c r="D28" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E28" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="E28" s="2" t="n">
-        <v>-3</v>
-      </c>
       <c r="F28" s="2" t="n">
-        <v>-6</v>
+        <v>-21</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>49.48</v>
+        <v>37.05</v>
       </c>
       <c r="H28" s="1" t="n">
-        <v>0.57</v>
+        <v>-1.57</v>
       </c>
       <c r="I28" s="1" t="n">
-        <v>1.46</v>
+        <v>0.28</v>
       </c>
       <c r="J28" s="1" t="n">
-        <v>1.57</v>
+        <v>2.75</v>
       </c>
       <c r="K28" s="1" t="n">
-        <v>-4.39</v>
+        <v>-4.37</v>
       </c>
       <c r="L28" s="1" t="inlineStr">
         <is>
-          <t>Down</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="M28" s="1" t="n">
-        <v>-15.24</v>
+        <v>0</v>
       </c>
       <c r="N28" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O28" s="1" t="inlineStr">
@@ -2569,26 +2569,26 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D2" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="E2" s="1" t="n">
         <v>24</v>
-      </c>
-      <c r="E2" s="1" t="n">
-        <v>22</v>
       </c>
       <c r="F2" s="1" t="n">
         <v>8</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H2" s="1" t="n">
         <v>2</v>
@@ -2597,46 +2597,46 @@
         <v>6</v>
       </c>
       <c r="J2" s="1" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K2" s="1" t="n">
         <v>4</v>
       </c>
       <c r="L2" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M2" s="1" t="n">
         <v>25</v>
       </c>
       <c r="N2" s="1" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="O2" s="1" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="P2" s="1" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Q2" s="1" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="R2" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="S2" s="1" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T2" s="1" t="n">
         <v>14</v>
       </c>
       <c r="U2" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="V2" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W2" s="1" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="X2" s="1" t="n">
         <v>3</v>
@@ -2645,32 +2645,32 @@
         <v>1</v>
       </c>
       <c r="Z2" s="1" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="AA2" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AB2" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
         <v>7</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D3" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="E3" s="1" t="n">
         <v>22</v>
-      </c>
-      <c r="E3" s="1" t="n">
-        <v>23</v>
       </c>
       <c r="F3" s="1" t="n">
         <v>8</v>
@@ -2679,37 +2679,37 @@
         <v>27</v>
       </c>
       <c r="H3" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I3" s="1" t="n">
         <v>6</v>
       </c>
       <c r="J3" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="K3" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="K3" s="1" t="n">
-        <v>5</v>
-      </c>
       <c r="L3" s="1" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="M3" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="N3" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="O3" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="P3" s="1" t="n">
         <v>26</v>
       </c>
-      <c r="N3" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="O3" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="P3" s="1" t="n">
-        <v>25</v>
-      </c>
       <c r="Q3" s="1" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="R3" s="1" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="S3" s="1" t="n">
         <v>9</v>
@@ -2721,22 +2721,22 @@
         <v>11</v>
       </c>
       <c r="V3" s="1" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="W3" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="X3" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y3" s="1" t="n">
         <v>1</v>
       </c>
       <c r="Z3" s="1" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AA3" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AB3" s="1" t="n">
         <v>12</v>
@@ -2745,105 +2745,105 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="C4" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="F4" s="1" t="n">
         <v>8</v>
-      </c>
-      <c r="C4" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="D4" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="E4" s="1" t="n">
-        <v>23</v>
-      </c>
-      <c r="F4" s="1" t="n">
-        <v>7</v>
       </c>
       <c r="G4" s="1" t="n">
         <v>27</v>
       </c>
       <c r="H4" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I4" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="J4" s="1" t="n">
         <v>5</v>
-      </c>
-      <c r="J4" s="1" t="n">
-        <v>6</v>
       </c>
       <c r="K4" s="1" t="n">
         <v>4</v>
       </c>
       <c r="L4" s="1" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="M4" s="1" t="n">
         <v>25</v>
       </c>
       <c r="N4" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="O4" s="1" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="P4" s="1" t="n">
         <v>26</v>
       </c>
       <c r="Q4" s="1" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="R4" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="S4" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="T4" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="T4" s="1" t="n">
-        <v>19</v>
-      </c>
       <c r="U4" s="1" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="V4" s="1" t="n">
         <v>10</v>
       </c>
       <c r="W4" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="X4" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y4" s="1" t="n">
         <v>1</v>
       </c>
       <c r="Z4" s="1" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AA4" s="1" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="AB4" s="1" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E5" s="1" t="n">
         <v>23</v>
@@ -2858,49 +2858,49 @@
         <v>3</v>
       </c>
       <c r="I5" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="J5" s="1" t="n">
         <v>6</v>
-      </c>
-      <c r="J5" s="1" t="n">
-        <v>8</v>
       </c>
       <c r="K5" s="1" t="n">
         <v>4</v>
       </c>
       <c r="L5" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M5" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="N5" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="O5" s="1" t="n">
         <v>24</v>
-      </c>
-      <c r="N5" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="O5" s="1" t="n">
-        <v>25</v>
       </c>
       <c r="P5" s="1" t="n">
         <v>26</v>
       </c>
       <c r="Q5" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="R5" s="1" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="S5" s="1" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="T5" s="1" t="n">
         <v>19</v>
       </c>
       <c r="U5" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="V5" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="W5" s="1" t="n">
         <v>17</v>
-      </c>
-      <c r="V5" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="W5" s="1" t="n">
-        <v>22</v>
       </c>
       <c r="X5" s="1" t="n">
         <v>2</v>
@@ -2909,10 +2909,10 @@
         <v>1</v>
       </c>
       <c r="Z5" s="1" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="AA5" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AB5" s="1" t="n">
         <v>9</v>
@@ -2921,114 +2921,114 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>7</v>
       </c>
       <c r="G6" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="H6" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="I6" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="J6" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="K6" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="L6" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="M6" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="N6" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="O6" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="P6" s="1" t="n">
         <v>26</v>
       </c>
-      <c r="H6" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="I6" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="J6" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="K6" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="L6" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="M6" s="1" t="n">
+      <c r="Q6" s="1" t="n">
         <v>21</v>
-      </c>
-      <c r="N6" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="O6" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="P6" s="1" t="n">
-        <v>27</v>
-      </c>
-      <c r="Q6" s="1" t="n">
-        <v>23</v>
       </c>
       <c r="R6" s="1" t="n">
         <v>20</v>
       </c>
       <c r="S6" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="T6" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="T6" s="1" t="n">
-        <v>15</v>
-      </c>
       <c r="U6" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="V6" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="W6" s="1" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="X6" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y6" s="1" t="n">
         <v>1</v>
       </c>
       <c r="Z6" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA6" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="AA6" s="1" t="n">
-        <v>13</v>
-      </c>
       <c r="AB6" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
         <v>6</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F7" s="1" t="n">
         <v>7</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H7" s="1" t="n">
         <v>2</v>
@@ -3037,46 +3037,46 @@
         <v>4</v>
       </c>
       <c r="J7" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K7" s="1" t="n">
         <v>5</v>
       </c>
       <c r="L7" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="M7" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="N7" s="1" t="n">
         <v>9</v>
-      </c>
-      <c r="M7" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="N7" s="1" t="n">
-        <v>13</v>
       </c>
       <c r="O7" s="1" t="n">
         <v>22</v>
       </c>
       <c r="P7" s="1" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Q7" s="1" t="n">
         <v>23</v>
       </c>
       <c r="R7" s="1" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="S7" s="1" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="T7" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="U7" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="U7" s="1" t="n">
-        <v>15</v>
-      </c>
       <c r="V7" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="W7" s="1" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="X7" s="1" t="n">
         <v>3</v>
@@ -3085,10 +3085,10 @@
         <v>1</v>
       </c>
       <c r="Z7" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AA7" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AB7" s="1" t="n">
         <v>8</v>
@@ -3097,20 +3097,20 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
         <v>6</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>7</v>
@@ -3125,43 +3125,43 @@
         <v>4</v>
       </c>
       <c r="J8" s="1" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K8" s="1" t="n">
         <v>5</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M8" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N8" s="1" t="n">
         <v>13</v>
       </c>
       <c r="O8" s="1" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="P8" s="1" t="n">
         <v>26</v>
       </c>
       <c r="Q8" s="1" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="R8" s="1" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="S8" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="T8" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="U8" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="T8" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="U8" s="1" t="n">
-        <v>18</v>
-      </c>
       <c r="V8" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="W8" s="1" t="n">
         <v>21</v>
@@ -3176,7 +3176,7 @@
         <v>12</v>
       </c>
       <c r="AA8" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AB8" s="1" t="n">
         <v>8</v>
@@ -3185,23 +3185,23 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E9" s="1" t="n">
         <v>24</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G9" s="1" t="n">
         <v>27</v>
@@ -3213,46 +3213,46 @@
         <v>4</v>
       </c>
       <c r="J9" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K9" s="1" t="n">
         <v>5</v>
       </c>
       <c r="L9" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="M9" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="N9" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="M9" s="1" t="n">
+      <c r="O9" s="1" t="n">
         <v>25</v>
-      </c>
-      <c r="N9" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="O9" s="1" t="n">
-        <v>21</v>
       </c>
       <c r="P9" s="1" t="n">
         <v>26</v>
       </c>
       <c r="Q9" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R9" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="S9" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="T9" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="S9" s="1" t="n">
+      <c r="U9" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="T9" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="U9" s="1" t="n">
-        <v>16</v>
-      </c>
       <c r="V9" s="1" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="W9" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="X9" s="1" t="n">
         <v>3</v>
@@ -3261,10 +3261,10 @@
         <v>1</v>
       </c>
       <c r="Z9" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AA9" s="1" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AB9" s="1" t="n">
         <v>8</v>
@@ -3273,23 +3273,23 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G10" s="1" t="n">
         <v>27</v>
@@ -3301,19 +3301,19 @@
         <v>4</v>
       </c>
       <c r="J10" s="1" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="K10" s="1" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L10" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M10" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="N10" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O10" s="1" t="n">
         <v>21</v>
@@ -3322,22 +3322,22 @@
         <v>26</v>
       </c>
       <c r="Q10" s="1" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="R10" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="S10" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="T10" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="S10" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="T10" s="1" t="n">
-        <v>20</v>
-      </c>
       <c r="U10" s="1" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="V10" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="W10" s="1" t="n">
         <v>22</v>
@@ -3349,23 +3349,23 @@
         <v>1</v>
       </c>
       <c r="Z10" s="1" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AA10" s="1" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="AB10" s="1" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C11" s="1" t="n">
         <v>16</v>
@@ -3374,7 +3374,7 @@
         <v>18</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F11" s="1" t="n">
         <v>9</v>
@@ -3386,22 +3386,22 @@
         <v>2</v>
       </c>
       <c r="I11" s="1" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J11" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="K11" s="1" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="M11" s="1" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="N11" s="1" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="O11" s="1" t="n">
         <v>21</v>
@@ -3413,22 +3413,22 @@
         <v>25</v>
       </c>
       <c r="R11" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="S11" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="T11" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="S11" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="T11" s="1" t="n">
-        <v>19</v>
-      </c>
       <c r="U11" s="1" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="V11" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="W11" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="X11" s="1" t="n">
         <v>3</v>
@@ -3437,62 +3437,62 @@
         <v>1</v>
       </c>
       <c r="Z11" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AA11" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AB11" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E12" s="1" t="n">
         <v>24</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G12" s="1" t="n">
         <v>27</v>
       </c>
       <c r="H12" s="1" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I12" s="1" t="n">
         <v>6</v>
       </c>
       <c r="J12" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K12" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="M12" s="1" t="n">
         <v>22</v>
       </c>
       <c r="N12" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O12" s="1" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="P12" s="1" t="n">
         <v>26</v>
@@ -3501,86 +3501,86 @@
         <v>25</v>
       </c>
       <c r="R12" s="1" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="S12" s="1" t="n">
         <v>5</v>
       </c>
       <c r="T12" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="U12" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="V12" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="V12" s="1" t="n">
-        <v>13</v>
-      </c>
       <c r="W12" s="1" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="X12" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y12" s="1" t="n">
         <v>1</v>
       </c>
       <c r="Z12" s="1" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AA12" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AB12" s="1" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D13" s="1" t="n">
         <v>21</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G13" s="1" t="n">
         <v>27</v>
       </c>
       <c r="H13" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I13" s="1" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J13" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K13" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L13" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M13" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N13" s="1" t="n">
         <v>12</v>
       </c>
       <c r="O13" s="1" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="P13" s="1" t="n">
         <v>26</v>
@@ -3589,110 +3589,110 @@
         <v>25</v>
       </c>
       <c r="R13" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="S13" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T13" s="1" t="n">
         <v>20</v>
       </c>
       <c r="U13" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="V13" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="V13" s="1" t="n">
-        <v>11</v>
-      </c>
       <c r="W13" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="X13" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y13" s="1" t="n">
         <v>1</v>
       </c>
       <c r="Z13" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA13" s="1" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AB13" s="1" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="C14" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="C14" s="1" t="n">
-        <v>16</v>
-      </c>
       <c r="D14" s="1" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G14" s="1" t="n">
         <v>27</v>
       </c>
       <c r="H14" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I14" s="1" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J14" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K14" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M14" s="1" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N14" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="O14" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="P14" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q14" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="R14" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="S14" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="T14" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="U14" s="1" t="n">
         <v>13</v>
-      </c>
-      <c r="O14" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="P14" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="Q14" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="R14" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="S14" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="T14" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="U14" s="1" t="n">
-        <v>14</v>
       </c>
       <c r="V14" s="1" t="n">
         <v>11</v>
       </c>
       <c r="W14" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="X14" s="1" t="n">
         <v>3</v>
@@ -3701,29 +3701,29 @@
         <v>1</v>
       </c>
       <c r="Z14" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA14" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="AB14" s="1" t="n">
         <v>9</v>
-      </c>
-      <c r="AA14" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="AB14" s="1" t="n">
-        <v>10</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="C15" s="1" t="n">
         <v>16</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E15" s="1" t="n">
         <v>23</v>
@@ -3741,46 +3741,46 @@
         <v>7</v>
       </c>
       <c r="J15" s="1" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="K15" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L15" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M15" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N15" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O15" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="P15" s="1" t="n">
         <v>25</v>
-      </c>
-      <c r="P15" s="1" t="n">
-        <v>26</v>
       </c>
       <c r="Q15" s="1" t="n">
         <v>24</v>
       </c>
       <c r="R15" s="1" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="S15" s="1" t="n">
         <v>5</v>
       </c>
       <c r="T15" s="1" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="U15" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="V15" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="W15" s="1" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="X15" s="1" t="n">
         <v>3</v>
@@ -3789,10 +3789,10 @@
         <v>1</v>
       </c>
       <c r="Z15" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA15" s="1" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AB15" s="1" t="n">
         <v>10</v>
@@ -3801,59 +3801,59 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F16" s="1" t="n">
         <v>6</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H16" s="1" t="n">
         <v>4</v>
       </c>
       <c r="I16" s="1" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J16" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K16" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L16" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M16" s="1" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N16" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="O16" s="1" t="n">
         <v>25</v>
       </c>
       <c r="P16" s="1" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Q16" s="1" t="n">
         <v>24</v>
       </c>
       <c r="R16" s="1" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="S16" s="1" t="n">
         <v>5</v>
@@ -3865,10 +3865,10 @@
         <v>13</v>
       </c>
       <c r="V16" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="W16" s="1" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="X16" s="1" t="n">
         <v>3</v>
@@ -3877,35 +3877,35 @@
         <v>1</v>
       </c>
       <c r="Z16" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA16" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AB16" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="C17" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="C17" s="1" t="n">
-        <v>10</v>
-      </c>
       <c r="D17" s="1" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F17" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G17" s="1" t="n">
         <v>26</v>
@@ -3914,22 +3914,22 @@
         <v>4</v>
       </c>
       <c r="I17" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J17" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K17" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L17" s="1" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M17" s="1" t="n">
         <v>23</v>
       </c>
       <c r="N17" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O17" s="1" t="n">
         <v>25</v>
@@ -3941,22 +3941,22 @@
         <v>24</v>
       </c>
       <c r="R17" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="S17" s="1" t="n">
         <v>5</v>
       </c>
       <c r="T17" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="U17" s="1" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="V17" s="1" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="W17" s="1" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="X17" s="1" t="n">
         <v>3</v>
@@ -3968,32 +3968,32 @@
         <v>7</v>
       </c>
       <c r="AA17" s="1" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="AB17" s="1" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F18" s="1" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G18" s="1" t="n">
         <v>26</v>
@@ -4002,49 +4002,49 @@
         <v>4</v>
       </c>
       <c r="I18" s="1" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="J18" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K18" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L18" s="1" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="M18" s="1" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="N18" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O18" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="P18" s="1" t="n">
         <v>27</v>
       </c>
       <c r="Q18" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R18" s="1" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="S18" s="1" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T18" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="U18" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="V18" s="1" t="n">
         <v>18</v>
       </c>
       <c r="W18" s="1" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="X18" s="1" t="n">
         <v>3</v>
@@ -4053,19 +4053,19 @@
         <v>1</v>
       </c>
       <c r="Z18" s="1" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AA18" s="1" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AB18" s="1" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
@@ -4075,7 +4075,7 @@
         <v>11</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E19" s="1" t="n">
         <v>16</v>
@@ -4084,7 +4084,7 @@
         <v>6</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H19" s="1" t="n">
         <v>4</v>
@@ -4099,40 +4099,40 @@
         <v>2</v>
       </c>
       <c r="L19" s="1" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="M19" s="1" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="N19" s="1" t="n">
         <v>14</v>
       </c>
       <c r="O19" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P19" s="1" t="n">
         <v>27</v>
       </c>
       <c r="Q19" s="1" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="R19" s="1" t="n">
         <v>19</v>
       </c>
       <c r="S19" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T19" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="U19" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="V19" s="1" t="n">
         <v>18</v>
       </c>
       <c r="W19" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="X19" s="1" t="n">
         <v>3</v>
@@ -4141,10 +4141,10 @@
         <v>1</v>
       </c>
       <c r="Z19" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA19" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AB19" s="1" t="n">
         <v>7</v>
@@ -4153,29 +4153,29 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D20" s="1" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F20" s="1" t="n">
         <v>6</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H20" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I20" s="1" t="n">
         <v>5</v>
@@ -4187,16 +4187,16 @@
         <v>2</v>
       </c>
       <c r="L20" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M20" s="1" t="n">
         <v>22</v>
       </c>
       <c r="N20" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="O20" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="P20" s="1" t="n">
         <v>27</v>
@@ -4205,34 +4205,34 @@
         <v>26</v>
       </c>
       <c r="R20" s="1" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="S20" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T20" s="1" t="n">
         <v>21</v>
       </c>
       <c r="U20" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="V20" s="1" t="n">
         <v>18</v>
-      </c>
-      <c r="V20" s="1" t="n">
-        <v>15</v>
       </c>
       <c r="W20" s="1" t="n">
         <v>20</v>
       </c>
       <c r="X20" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y20" s="1" t="n">
         <v>1</v>
       </c>
       <c r="Z20" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA20" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AB20" s="1" t="n">
         <v>7</v>
@@ -4241,7 +4241,7 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
@@ -4251,22 +4251,22 @@
         <v>10</v>
       </c>
       <c r="D21" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F21" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="G21" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="H21" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="G21" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="H21" s="1" t="n">
+      <c r="I21" s="1" t="n">
         <v>5</v>
-      </c>
-      <c r="I21" s="1" t="n">
-        <v>6</v>
       </c>
       <c r="J21" s="1" t="n">
         <v>23</v>
@@ -4275,37 +4275,37 @@
         <v>2</v>
       </c>
       <c r="L21" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M21" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="N21" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="O21" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="P21" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q21" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="R21" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="S21" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="T21" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="N21" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="O21" s="1" t="n">
-        <v>27</v>
-      </c>
-      <c r="P21" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="Q21" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="R21" s="1" t="n">
+      <c r="U21" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="S21" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="T21" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="U21" s="1" t="n">
+      <c r="V21" s="1" t="n">
         <v>15</v>
-      </c>
-      <c r="V21" s="1" t="n">
-        <v>17</v>
       </c>
       <c r="W21" s="1" t="n">
         <v>20</v>
@@ -4317,7 +4317,7 @@
         <v>1</v>
       </c>
       <c r="Z21" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA21" s="1" t="n">
         <v>16</v>
@@ -4329,77 +4329,77 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D22" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="E22" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="E22" s="1" t="n">
-        <v>14</v>
-      </c>
       <c r="F22" s="1" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G22" s="1" t="n">
         <v>24</v>
       </c>
       <c r="H22" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I22" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J22" s="1" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="K22" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L22" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="M22" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="N22" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="O22" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="P22" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q22" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="R22" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="S22" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="T22" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="U22" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="V22" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="M22" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="N22" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="O22" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="P22" s="1" t="n">
-        <v>27</v>
-      </c>
-      <c r="Q22" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="R22" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="S22" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="T22" s="1" t="n">
-        <v>23</v>
-      </c>
-      <c r="U22" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="V22" s="1" t="n">
-        <v>16</v>
-      </c>
       <c r="W22" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="X22" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y22" s="1" t="n">
         <v>1</v>
@@ -4408,26 +4408,26 @@
         <v>8</v>
       </c>
       <c r="AA22" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AB22" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="C23" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="C23" s="1" t="n">
-        <v>10</v>
-      </c>
       <c r="D23" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E23" s="1" t="n">
         <v>14</v>
@@ -4445,34 +4445,34 @@
         <v>7</v>
       </c>
       <c r="J23" s="1" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K23" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L23" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M23" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N23" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="O23" s="1" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P23" s="1" t="n">
         <v>27</v>
       </c>
       <c r="Q23" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="R23" s="1" t="n">
         <v>19</v>
       </c>
       <c r="S23" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T23" s="1" t="n">
         <v>23</v>
@@ -4484,7 +4484,7 @@
         <v>16</v>
       </c>
       <c r="W23" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="X23" s="1" t="n">
         <v>3</v>
@@ -4493,47 +4493,47 @@
         <v>1</v>
       </c>
       <c r="Z23" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA23" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="AB23" s="1" t="n">
         <v>6</v>
-      </c>
-      <c r="AA23" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="AB23" s="1" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
         <v>11</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D24" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="E24" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="E24" s="1" t="n">
-        <v>12</v>
-      </c>
       <c r="F24" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G24" s="1" t="n">
         <v>24</v>
       </c>
       <c r="H24" s="1" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I24" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J24" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K24" s="1" t="n">
         <v>2</v>
@@ -4542,7 +4542,7 @@
         <v>15</v>
       </c>
       <c r="M24" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N24" s="1" t="n">
         <v>13</v>
@@ -4560,7 +4560,7 @@
         <v>19</v>
       </c>
       <c r="S24" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T24" s="1" t="n">
         <v>23</v>
@@ -4569,7 +4569,7 @@
         <v>18</v>
       </c>
       <c r="V24" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="W24" s="1" t="n">
         <v>20</v>
@@ -4581,32 +4581,32 @@
         <v>1</v>
       </c>
       <c r="Z24" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA24" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AB24" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C25" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="D25" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="E25" s="1" t="n">
         <v>12</v>
-      </c>
-      <c r="D25" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="E25" s="1" t="n">
-        <v>13</v>
       </c>
       <c r="F25" s="1" t="n">
         <v>4</v>
@@ -4615,10 +4615,10 @@
         <v>24</v>
       </c>
       <c r="H25" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I25" s="1" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J25" s="1" t="n">
         <v>21</v>
@@ -4627,40 +4627,40 @@
         <v>2</v>
       </c>
       <c r="L25" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="M25" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="N25" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="O25" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="P25" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q25" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="R25" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="S25" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="U25" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="M25" s="1" t="n">
+      <c r="V25" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="W25" s="1" t="n">
         <v>20</v>
-      </c>
-      <c r="N25" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="O25" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="P25" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="Q25" s="1" t="n">
-        <v>27</v>
-      </c>
-      <c r="R25" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="S25" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="T25" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="U25" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="V25" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="W25" s="1" t="n">
-        <v>23</v>
       </c>
       <c r="X25" s="1" t="n">
         <v>3</v>
@@ -4669,38 +4669,38 @@
         <v>1</v>
       </c>
       <c r="Z25" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA25" s="1" t="n">
         <v>16</v>
       </c>
       <c r="AB25" s="1" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C26" s="1" t="n">
         <v>12</v>
       </c>
       <c r="D26" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F26" s="1" t="n">
         <v>4</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H26" s="1" t="n">
         <v>7</v>
@@ -4709,7 +4709,7 @@
         <v>11</v>
       </c>
       <c r="J26" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K26" s="1" t="n">
         <v>2</v>
@@ -4718,25 +4718,25 @@
         <v>18</v>
       </c>
       <c r="M26" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="N26" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="O26" s="1" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="P26" s="1" t="n">
         <v>26</v>
       </c>
       <c r="Q26" s="1" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="R26" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="S26" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T26" s="1" t="n">
         <v>22</v>
@@ -4745,7 +4745,7 @@
         <v>19</v>
       </c>
       <c r="V26" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="W26" s="1" t="n">
         <v>23</v>
@@ -4760,7 +4760,7 @@
         <v>6</v>
       </c>
       <c r="AA26" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AB26" s="1" t="n">
         <v>5</v>
@@ -4769,47 +4769,47 @@
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C27" s="1" t="n">
         <v>12</v>
       </c>
       <c r="D27" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="E27" s="1" t="n">
         <v>15</v>
-      </c>
-      <c r="E27" s="1" t="n">
-        <v>10</v>
       </c>
       <c r="F27" s="1" t="n">
         <v>4</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H27" s="1" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I27" s="1" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J27" s="1" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K27" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L27" s="1" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M27" s="1" t="n">
         <v>21</v>
       </c>
       <c r="N27" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O27" s="1" t="n">
         <v>27</v>
@@ -4818,59 +4818,59 @@
         <v>26</v>
       </c>
       <c r="Q27" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R27" s="1" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="S27" s="1" t="n">
         <v>8</v>
       </c>
       <c r="T27" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="U27" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="V27" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="W27" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="U27" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="V27" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="W27" s="1" t="n">
+      <c r="X27" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y27" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="X27" s="1" t="n">
+      <c r="Z27" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA27" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="AB27" s="1" t="n">
         <v>5</v>
-      </c>
-      <c r="Y27" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z27" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA27" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="AB27" s="1" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
         <v>13</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D28" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F28" s="1" t="n">
         <v>4</v>
@@ -4879,13 +4879,13 @@
         <v>24</v>
       </c>
       <c r="H28" s="1" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I28" s="1" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="J28" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K28" s="1" t="n">
         <v>3</v>
@@ -4909,25 +4909,25 @@
         <v>25</v>
       </c>
       <c r="R28" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="S28" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="T28" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="U28" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="V28" s="1" t="n">
         <v>16</v>
-      </c>
-      <c r="S28" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="T28" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="U28" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="V28" s="1" t="n">
-        <v>15</v>
       </c>
       <c r="W28" s="1" t="n">
         <v>1</v>
       </c>
       <c r="X28" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y28" s="1" t="n">
         <v>2</v>
@@ -4936,26 +4936,26 @@
         <v>7</v>
       </c>
       <c r="AA28" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AB28" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D29" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E29" s="1" t="n">
         <v>9</v>
@@ -4964,22 +4964,22 @@
         <v>4</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H29" s="1" t="n">
         <v>12</v>
       </c>
       <c r="I29" s="1" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J29" s="1" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K29" s="1" t="n">
         <v>3</v>
       </c>
       <c r="L29" s="1" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="M29" s="1" t="n">
         <v>21</v>
@@ -4991,25 +4991,25 @@
         <v>27</v>
       </c>
       <c r="P29" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q29" s="1" t="n">
         <v>25</v>
-      </c>
-      <c r="Q29" s="1" t="n">
-        <v>24</v>
       </c>
       <c r="R29" s="1" t="n">
         <v>16</v>
       </c>
       <c r="S29" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T29" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="U29" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="V29" s="1" t="n">
         <v>15</v>
-      </c>
-      <c r="V29" s="1" t="n">
-        <v>14</v>
       </c>
       <c r="W29" s="1" t="n">
         <v>1</v>
@@ -5033,38 +5033,38 @@
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C30" s="1" t="n">
         <v>10</v>
       </c>
       <c r="D30" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E30" s="1" t="n">
         <v>9</v>
       </c>
       <c r="F30" s="1" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H30" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I30" s="1" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J30" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K30" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L30" s="1" t="n">
         <v>20</v>
@@ -5076,37 +5076,37 @@
         <v>11</v>
       </c>
       <c r="O30" s="1" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P30" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q30" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="Q30" s="1" t="n">
-        <v>25</v>
-      </c>
       <c r="R30" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="S30" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="T30" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="U30" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="V30" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="S30" s="1" t="n">
+      <c r="W30" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="X30" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="T30" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="U30" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="V30" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="W30" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="X30" s="1" t="n">
-        <v>8</v>
-      </c>
       <c r="Y30" s="1" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Z30" s="1" t="n">
         <v>7</v>
@@ -5121,20 +5121,20 @@
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="C31" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="C31" s="1" t="n">
-        <v>11</v>
-      </c>
       <c r="D31" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F31" s="1" t="n">
         <v>2</v>
@@ -5143,10 +5143,10 @@
         <v>27</v>
       </c>
       <c r="H31" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I31" s="1" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J31" s="1" t="n">
         <v>23</v>
@@ -5161,7 +5161,7 @@
         <v>21</v>
       </c>
       <c r="N31" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="O31" s="1" t="n">
         <v>26</v>
@@ -5173,10 +5173,10 @@
         <v>25</v>
       </c>
       <c r="R31" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S31" s="1" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T31" s="1" t="n">
         <v>22</v>
@@ -5185,13 +5185,13 @@
         <v>16</v>
       </c>
       <c r="V31" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="W31" s="1" t="n">
         <v>3</v>
       </c>
       <c r="X31" s="1" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y31" s="1" t="n">
         <v>4</v>
@@ -5209,38 +5209,38 @@
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D32" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="E32" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="F32" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G32" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="H32" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="I32" s="1" t="n">
         <v>19</v>
-      </c>
-      <c r="E32" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="F32" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="G32" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="H32" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="I32" s="1" t="n">
-        <v>18</v>
       </c>
       <c r="J32" s="1" t="n">
         <v>23</v>
       </c>
       <c r="K32" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L32" s="1" t="n">
         <v>20</v>
@@ -5249,10 +5249,10 @@
         <v>21</v>
       </c>
       <c r="N32" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="O32" s="1" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P32" s="1" t="n">
         <v>24</v>
@@ -5261,7 +5261,7 @@
         <v>25</v>
       </c>
       <c r="R32" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="S32" s="1" t="n">
         <v>9</v>
@@ -5270,25 +5270,25 @@
         <v>22</v>
       </c>
       <c r="U32" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="V32" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="W32" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X32" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y32" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="Y32" s="1" t="n">
-        <v>2</v>
-      </c>
       <c r="Z32" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA32" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AB32" s="1" t="n">
         <v>5</v>
@@ -5297,41 +5297,41 @@
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C33" s="1" t="n">
         <v>12</v>
       </c>
       <c r="D33" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F33" s="1" t="n">
         <v>7</v>
       </c>
       <c r="G33" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="H33" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="I33" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="J33" s="1" t="n">
         <v>23</v>
-      </c>
-      <c r="H33" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="I33" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="J33" s="1" t="n">
-        <v>24</v>
       </c>
       <c r="K33" s="1" t="n">
         <v>3</v>
       </c>
       <c r="L33" s="1" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M33" s="1" t="n">
         <v>21</v>
@@ -5343,25 +5343,25 @@
         <v>27</v>
       </c>
       <c r="P33" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q33" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="Q33" s="1" t="n">
-        <v>26</v>
-      </c>
       <c r="R33" s="1" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="S33" s="1" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="T33" s="1" t="n">
         <v>22</v>
       </c>
       <c r="U33" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="V33" s="1" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="W33" s="1" t="n">
         <v>1</v>
@@ -5376,50 +5376,50 @@
         <v>8</v>
       </c>
       <c r="AA33" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AB33" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="C34" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D34" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="E34" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="F34" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C34" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="D34" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="E34" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="F34" s="1" t="n">
-        <v>5</v>
-      </c>
       <c r="G34" s="1" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="H34" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I34" s="1" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J34" s="1" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K34" s="1" t="n">
         <v>3</v>
       </c>
       <c r="L34" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M34" s="1" t="n">
         <v>21</v>
@@ -5431,25 +5431,25 @@
         <v>27</v>
       </c>
       <c r="P34" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Q34" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="R34" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="S34" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="S34" s="1" t="n">
-        <v>19</v>
-      </c>
       <c r="T34" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="U34" s="1" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="V34" s="1" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="W34" s="1" t="n">
         <v>1</v>
@@ -5461,10 +5461,10 @@
         <v>2</v>
       </c>
       <c r="Z34" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA34" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AB34" s="1" t="n">
         <v>6</v>
@@ -5473,20 +5473,20 @@
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C35" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="D35" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="D35" s="1" t="n">
-        <v>20</v>
-      </c>
       <c r="E35" s="1" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F35" s="1" t="n">
         <v>5</v>
@@ -5495,10 +5495,10 @@
         <v>26</v>
       </c>
       <c r="H35" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I35" s="1" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J35" s="1" t="n">
         <v>22</v>
@@ -5507,34 +5507,34 @@
         <v>3</v>
       </c>
       <c r="L35" s="1" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M35" s="1" t="n">
         <v>21</v>
       </c>
       <c r="N35" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="O35" s="1" t="n">
         <v>27</v>
       </c>
       <c r="P35" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q35" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="Q35" s="1" t="n">
-        <v>24</v>
-      </c>
       <c r="R35" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="S35" s="1" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="T35" s="1" t="n">
         <v>23</v>
       </c>
       <c r="U35" s="1" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="V35" s="1" t="n">
         <v>17</v>
@@ -5549,10 +5549,10 @@
         <v>2</v>
       </c>
       <c r="Z35" s="1" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AA35" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AB35" s="1" t="n">
         <v>6</v>
@@ -5561,44 +5561,44 @@
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B36" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D36" s="1" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F36" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G36" s="1" t="n">
         <v>26</v>
       </c>
       <c r="H36" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I36" s="1" t="n">
         <v>10</v>
       </c>
       <c r="J36" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K36" s="1" t="n">
         <v>3</v>
       </c>
       <c r="L36" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M36" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N36" s="1" t="n">
         <v>11</v>
@@ -5613,10 +5613,10 @@
         <v>24</v>
       </c>
       <c r="R36" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="S36" s="1" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="T36" s="1" t="n">
         <v>23</v>
@@ -5625,13 +5625,13 @@
         <v>18</v>
       </c>
       <c r="V36" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="W36" s="1" t="n">
         <v>1</v>
       </c>
       <c r="X36" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y36" s="1" t="n">
         <v>2</v>
@@ -5640,7 +5640,7 @@
         <v>7</v>
       </c>
       <c r="AA36" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AB36" s="1" t="n">
         <v>6</v>
@@ -5649,38 +5649,38 @@
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B37" s="1" t="n">
         <v>9</v>
       </c>
       <c r="C37" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D37" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="E37" s="1" t="n">
         <v>13</v>
-      </c>
-      <c r="D37" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="E37" s="1" t="n">
-        <v>11</v>
       </c>
       <c r="F37" s="1" t="n">
         <v>4</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H37" s="1" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I37" s="1" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J37" s="1" t="n">
         <v>21</v>
       </c>
       <c r="K37" s="1" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="L37" s="1" t="n">
         <v>20</v>
@@ -5689,28 +5689,28 @@
         <v>22</v>
       </c>
       <c r="N37" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="O37" s="1" t="n">
         <v>27</v>
       </c>
       <c r="P37" s="1" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Q37" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R37" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="S37" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="T37" s="1" t="n">
         <v>23</v>
       </c>
       <c r="U37" s="1" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="V37" s="1" t="n">
         <v>15</v>
@@ -5725,10 +5725,10 @@
         <v>2</v>
       </c>
       <c r="Z37" s="1" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AA37" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AB37" s="1" t="n">
         <v>6</v>
@@ -5737,47 +5737,47 @@
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B38" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C38" s="1" t="n">
         <v>13</v>
       </c>
       <c r="D38" s="1" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="F38" s="1" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H38" s="1" t="n">
         <v>3</v>
       </c>
       <c r="I38" s="1" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J38" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="K38" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="L38" s="1" t="n">
         <v>20</v>
-      </c>
-      <c r="K38" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="L38" s="1" t="n">
-        <v>18</v>
       </c>
       <c r="M38" s="1" t="n">
         <v>22</v>
       </c>
       <c r="N38" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O38" s="1" t="n">
         <v>27</v>
@@ -5789,25 +5789,25 @@
         <v>25</v>
       </c>
       <c r="R38" s="1" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="S38" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="T38" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="U38" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="T38" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="U38" s="1" t="n">
-        <v>12</v>
-      </c>
       <c r="V38" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="W38" s="1" t="n">
         <v>1</v>
       </c>
       <c r="X38" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y38" s="1" t="n">
         <v>2</v>
@@ -5825,44 +5825,44 @@
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B39" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D39" s="1" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F39" s="1" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G39" s="1" t="n">
         <v>23</v>
       </c>
       <c r="H39" s="1" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I39" s="1" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J39" s="1" t="n">
         <v>20</v>
       </c>
       <c r="K39" s="1" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L39" s="1" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="M39" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N39" s="1" t="n">
         <v>11</v>
@@ -5874,86 +5874,86 @@
         <v>26</v>
       </c>
       <c r="Q39" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="R39" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="S39" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="T39" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="R39" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="S39" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="T39" s="1" t="n">
-        <v>25</v>
-      </c>
       <c r="U39" s="1" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="V39" s="1" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="W39" s="1" t="n">
         <v>1</v>
       </c>
       <c r="X39" s="1" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Y39" s="1" t="n">
         <v>2</v>
       </c>
       <c r="Z39" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA39" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AB39" s="1" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B40" s="1" t="n">
         <v>10</v>
       </c>
       <c r="C40" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="D40" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="D40" s="1" t="n">
-        <v>11</v>
-      </c>
       <c r="E40" s="1" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F40" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G40" s="1" t="n">
         <v>23</v>
       </c>
       <c r="H40" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="I40" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="J40" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="K40" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="I40" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="J40" s="1" t="n">
+      <c r="L40" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="M40" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="K40" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="L40" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="M40" s="1" t="n">
-        <v>22</v>
-      </c>
       <c r="N40" s="1" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="O40" s="1" t="n">
         <v>27</v>
@@ -5965,7 +5965,7 @@
         <v>24</v>
       </c>
       <c r="R40" s="1" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="S40" s="1" t="n">
         <v>19</v>
@@ -5974,16 +5974,16 @@
         <v>25</v>
       </c>
       <c r="U40" s="1" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="V40" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="W40" s="1" t="n">
         <v>1</v>
       </c>
       <c r="X40" s="1" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Y40" s="1" t="n">
         <v>2</v>
@@ -5992,23 +5992,23 @@
         <v>9</v>
       </c>
       <c r="AA40" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AB40" s="1" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B41" s="1" t="n">
         <v>10</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D41" s="1" t="n">
         <v>11</v>
@@ -6017,7 +6017,7 @@
         <v>20</v>
       </c>
       <c r="F41" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G41" s="1" t="n">
         <v>23</v>
@@ -6029,19 +6029,19 @@
         <v>7</v>
       </c>
       <c r="J41" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K41" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L41" s="1" t="n">
         <v>13</v>
       </c>
       <c r="M41" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N41" s="1" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="O41" s="1" t="n">
         <v>27</v>
@@ -6053,19 +6053,19 @@
         <v>24</v>
       </c>
       <c r="R41" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="S41" s="1" t="n">
         <v>19</v>
-      </c>
-      <c r="S41" s="1" t="n">
-        <v>18</v>
       </c>
       <c r="T41" s="1" t="n">
         <v>25</v>
       </c>
       <c r="U41" s="1" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="V41" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="W41" s="1" t="n">
         <v>1</v>
@@ -6080,7 +6080,7 @@
         <v>9</v>
       </c>
       <c r="AA41" s="1" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AB41" s="1" t="n">
         <v>8</v>
@@ -6089,44 +6089,44 @@
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B42" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="C42" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="C42" s="1" t="n">
-        <v>16</v>
-      </c>
       <c r="D42" s="1" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F42" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G42" s="1" t="n">
         <v>23</v>
       </c>
       <c r="H42" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I42" s="1" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J42" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="K42" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="L42" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="M42" s="1" t="n">
         <v>21</v>
-      </c>
-      <c r="K42" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="L42" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="M42" s="1" t="n">
-        <v>20</v>
       </c>
       <c r="N42" s="1" t="n">
         <v>12</v>
@@ -6150,19 +6150,19 @@
         <v>25</v>
       </c>
       <c r="U42" s="1" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="V42" s="1" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="W42" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="X42" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="X42" s="1" t="n">
-        <v>7</v>
-      </c>
       <c r="Y42" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Z42" s="1" t="n">
         <v>9</v>
@@ -6177,23 +6177,23 @@
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B43" s="1" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C43" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="D43" s="1" t="n">
         <v>14</v>
-      </c>
-      <c r="D43" s="1" t="n">
-        <v>13</v>
       </c>
       <c r="E43" s="1" t="n">
         <v>22</v>
       </c>
       <c r="F43" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G43" s="1" t="n">
         <v>23</v>
@@ -6205,16 +6205,16 @@
         <v>3</v>
       </c>
       <c r="J43" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K43" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L43" s="1" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="M43" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="N43" s="1" t="n">
         <v>12</v>
@@ -6229,47 +6229,47 @@
         <v>24</v>
       </c>
       <c r="R43" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="S43" s="1" t="n">
         <v>18</v>
-      </c>
-      <c r="S43" s="1" t="n">
-        <v>19</v>
       </c>
       <c r="T43" s="1" t="n">
         <v>25</v>
       </c>
       <c r="U43" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="V43" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="W43" s="1" t="n">
         <v>4</v>
       </c>
       <c r="X43" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y43" s="1" t="n">
         <v>5</v>
       </c>
       <c r="Z43" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA43" s="1" t="n">
         <v>17</v>
       </c>
       <c r="AB43" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B44" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C44" s="1" t="n">
         <v>14</v>
@@ -6278,31 +6278,31 @@
         <v>13</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F44" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G44" s="1" t="n">
         <v>23</v>
       </c>
       <c r="H44" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I44" s="1" t="n">
         <v>3</v>
       </c>
       <c r="J44" s="1" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K44" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L44" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M44" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N44" s="1" t="n">
         <v>12</v>
@@ -6317,19 +6317,19 @@
         <v>24</v>
       </c>
       <c r="R44" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="S44" s="1" t="n">
         <v>19</v>
-      </c>
-      <c r="S44" s="1" t="n">
-        <v>18</v>
       </c>
       <c r="T44" s="1" t="n">
         <v>25</v>
       </c>
       <c r="U44" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="V44" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="W44" s="1" t="n">
         <v>4</v>
@@ -6341,10 +6341,10 @@
         <v>5</v>
       </c>
       <c r="Z44" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA44" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AB44" s="1" t="n">
         <v>9</v>
@@ -6353,26 +6353,26 @@
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B45" s="1" t="n">
         <v>11</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D45" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F45" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H45" s="1" t="n">
         <v>2</v>
@@ -6381,13 +6381,13 @@
         <v>3</v>
       </c>
       <c r="J45" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K45" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L45" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M45" s="1" t="n">
         <v>20</v>
@@ -6402,16 +6402,16 @@
         <v>26</v>
       </c>
       <c r="Q45" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="R45" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="S45" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="T45" s="1" t="n">
         <v>25</v>
-      </c>
-      <c r="R45" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="S45" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="T45" s="1" t="n">
-        <v>24</v>
       </c>
       <c r="U45" s="1" t="n">
         <v>10</v>
@@ -6429,35 +6429,35 @@
         <v>5</v>
       </c>
       <c r="Z45" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA45" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="AB45" s="1" t="n">
         <v>9</v>
-      </c>
-      <c r="AA45" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="AB45" s="1" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B46" s="1" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D46" s="1" t="n">
         <v>14</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F46" s="1" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G46" s="1" t="n">
         <v>21</v>
@@ -6475,7 +6475,7 @@
         <v>1</v>
       </c>
       <c r="L46" s="1" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="M46" s="1" t="n">
         <v>20</v>
@@ -6487,56 +6487,56 @@
         <v>27</v>
       </c>
       <c r="P46" s="1" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="Q46" s="1" t="n">
         <v>25</v>
       </c>
       <c r="R46" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="S46" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="T46" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="U46" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="T46" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="U46" s="1" t="n">
+      <c r="V46" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="W46" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="V46" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="W46" s="1" t="n">
+      <c r="X46" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="X46" s="1" t="n">
-        <v>11</v>
-      </c>
       <c r="Y46" s="1" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Z46" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA46" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="AB46" s="1" t="n">
         <v>8</v>
-      </c>
-      <c r="AA46" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="AB46" s="1" t="n">
-        <v>9</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B47" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="C47" s="1" t="n">
         <v>17</v>
-      </c>
-      <c r="C47" s="1" t="n">
-        <v>15</v>
       </c>
       <c r="D47" s="1" t="n">
         <v>14</v>
@@ -6548,7 +6548,7 @@
         <v>5</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="H47" s="1" t="n">
         <v>2</v>
@@ -6557,25 +6557,25 @@
         <v>3</v>
       </c>
       <c r="J47" s="1" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K47" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L47" s="1" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="M47" s="1" t="n">
         <v>20</v>
       </c>
       <c r="N47" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="O47" s="1" t="n">
         <v>27</v>
       </c>
       <c r="P47" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q47" s="1" t="n">
         <v>25</v>
@@ -6584,47 +6584,47 @@
         <v>16</v>
       </c>
       <c r="S47" s="1" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T47" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="U47" s="1" t="n">
         <v>4</v>
       </c>
       <c r="V47" s="1" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="W47" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X47" s="1" t="n">
         <v>11</v>
       </c>
       <c r="Y47" s="1" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Z47" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA47" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="AB47" s="1" t="n">
         <v>9</v>
-      </c>
-      <c r="AA47" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="AB47" s="1" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B48" s="1" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D48" s="1" t="n">
         <v>14</v>
@@ -6645,34 +6645,34 @@
         <v>3</v>
       </c>
       <c r="J48" s="1" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K48" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L48" s="1" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M48" s="1" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="N48" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="O48" s="1" t="n">
         <v>27</v>
       </c>
       <c r="P48" s="1" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q48" s="1" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="R48" s="1" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="S48" s="1" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T48" s="1" t="n">
         <v>21</v>
@@ -6684,13 +6684,13 @@
         <v>12</v>
       </c>
       <c r="W48" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X48" s="1" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="Y48" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z48" s="1" t="n">
         <v>9</v>
@@ -6699,59 +6699,59 @@
         <v>19</v>
       </c>
       <c r="AB48" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B49" s="1" t="n">
         <v>25</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D49" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F49" s="1" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G49" s="1" t="n">
         <v>24</v>
       </c>
       <c r="H49" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I49" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="J49" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="K49" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="I49" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="J49" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="K49" s="1" t="n">
-        <v>3</v>
-      </c>
       <c r="L49" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M49" s="1" t="n">
         <v>18</v>
       </c>
       <c r="N49" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="O49" s="1" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P49" s="1" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="Q49" s="1" t="n">
         <v>23</v>
@@ -6760,56 +6760,56 @@
         <v>13</v>
       </c>
       <c r="S49" s="1" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T49" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="U49" s="1" t="n">
         <v>4</v>
       </c>
       <c r="V49" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="W49" s="1" t="n">
         <v>6</v>
       </c>
       <c r="X49" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Y49" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z49" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA49" s="1" t="n">
         <v>19</v>
       </c>
       <c r="AB49" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B50" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="C50" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="D50" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="E50" s="1" t="n">
         <v>27</v>
       </c>
-      <c r="C50" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="D50" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="E50" s="1" t="n">
-        <v>25</v>
-      </c>
       <c r="F50" s="1" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G50" s="1" t="n">
         <v>24</v>
@@ -6818,61 +6818,61 @@
         <v>1</v>
       </c>
       <c r="I50" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="J50" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="K50" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="J50" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="K50" s="1" t="n">
-        <v>2</v>
-      </c>
       <c r="L50" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M50" s="1" t="n">
         <v>18</v>
       </c>
       <c r="N50" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="O50" s="1" t="n">
         <v>26</v>
       </c>
       <c r="P50" s="1" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q50" s="1" t="n">
         <v>23</v>
       </c>
       <c r="R50" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="S50" s="1" t="n">
         <v>5</v>
       </c>
       <c r="T50" s="1" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="U50" s="1" t="n">
         <v>4</v>
       </c>
       <c r="V50" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="W50" s="1" t="n">
         <v>6</v>
       </c>
       <c r="X50" s="1" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="Y50" s="1" t="n">
         <v>7</v>
       </c>
       <c r="Z50" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA50" s="1" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AB50" s="1" t="n">
         <v>8</v>
@@ -6881,47 +6881,47 @@
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B51" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C51" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="D51" s="1" t="n">
         <v>13</v>
-      </c>
-      <c r="D51" s="1" t="n">
-        <v>6</v>
       </c>
       <c r="E51" s="1" t="n">
         <v>25</v>
       </c>
       <c r="F51" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H51" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I51" s="1" t="n">
         <v>3</v>
       </c>
       <c r="J51" s="1" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="K51" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L51" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M51" s="1" t="n">
         <v>18</v>
       </c>
       <c r="N51" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="O51" s="1" t="n">
         <v>26</v>
@@ -6939,53 +6939,53 @@
         <v>5</v>
       </c>
       <c r="T51" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="U51" s="1" t="n">
         <v>4</v>
       </c>
       <c r="V51" s="1" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="W51" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X51" s="1" t="n">
         <v>17</v>
       </c>
       <c r="Y51" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z51" s="1" t="n">
         <v>9</v>
       </c>
       <c r="AA51" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AB51" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B52" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C52" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="D52" s="1" t="n">
         <v>6</v>
-      </c>
-      <c r="D52" s="1" t="n">
-        <v>5</v>
       </c>
       <c r="E52" s="1" t="n">
         <v>25</v>
       </c>
       <c r="F52" s="1" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="G52" s="1" t="n">
         <v>22</v>
@@ -7009,22 +7009,22 @@
         <v>18</v>
       </c>
       <c r="N52" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="O52" s="1" t="n">
         <v>26</v>
       </c>
       <c r="P52" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Q52" s="1" t="n">
         <v>23</v>
       </c>
       <c r="R52" s="1" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="S52" s="1" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T52" s="1" t="n">
         <v>21</v>
@@ -7033,50 +7033,50 @@
         <v>4</v>
       </c>
       <c r="V52" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="W52" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X52" s="1" t="n">
         <v>17</v>
       </c>
       <c r="Y52" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z52" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="Z52" s="1" t="n">
+      <c r="AA52" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="AB52" s="1" t="n">
         <v>10</v>
-      </c>
-      <c r="AA52" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="AB52" s="1" t="n">
-        <v>11</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B53" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D53" s="1" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E53" s="1" t="n">
         <v>25</v>
       </c>
       <c r="F53" s="1" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H53" s="1" t="n">
         <v>2</v>
@@ -7094,7 +7094,7 @@
         <v>16</v>
       </c>
       <c r="M53" s="1" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N53" s="1" t="n">
         <v>14</v>
@@ -7103,68 +7103,68 @@
         <v>26</v>
       </c>
       <c r="P53" s="1" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="Q53" s="1" t="n">
         <v>23</v>
       </c>
       <c r="R53" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="S53" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="T53" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="U53" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="V53" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="W53" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="X53" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y53" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="S53" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="T53" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="U53" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="V53" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="W53" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="X53" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="Y53" s="1" t="n">
-        <v>5</v>
-      </c>
       <c r="Z53" s="1" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AA53" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AB53" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B54" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D54" s="1" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E54" s="1" t="n">
         <v>25</v>
       </c>
       <c r="F54" s="1" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H54" s="1" t="n">
         <v>2</v>
@@ -7173,25 +7173,25 @@
         <v>3</v>
       </c>
       <c r="J54" s="1" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K54" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L54" s="1" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="M54" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N54" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O54" s="1" t="n">
         <v>26</v>
       </c>
       <c r="P54" s="1" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="Q54" s="1" t="n">
         <v>23</v>
@@ -7200,31 +7200,31 @@
         <v>9</v>
       </c>
       <c r="S54" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="T54" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="U54" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="T54" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="U54" s="1" t="n">
-        <v>7</v>
-      </c>
       <c r="V54" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="W54" s="1" t="n">
         <v>4</v>
       </c>
       <c r="X54" s="1" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Y54" s="1" t="n">
         <v>5</v>
       </c>
       <c r="Z54" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA54" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AB54" s="1" t="n">
         <v>10</v>
@@ -7233,23 +7233,23 @@
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B55" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D55" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F55" s="1" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G55" s="1" t="n">
         <v>20</v>
@@ -7261,13 +7261,13 @@
         <v>3</v>
       </c>
       <c r="J55" s="1" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="K55" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L55" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="M55" s="1" t="n">
         <v>18</v>
@@ -7276,10 +7276,10 @@
         <v>15</v>
       </c>
       <c r="O55" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P55" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Q55" s="1" t="n">
         <v>23</v>
@@ -7294,25 +7294,25 @@
         <v>24</v>
       </c>
       <c r="U55" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V55" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="W55" s="1" t="n">
         <v>4</v>
       </c>
       <c r="X55" s="1" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Y55" s="1" t="n">
         <v>5</v>
       </c>
       <c r="Z55" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA55" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AB55" s="1" t="n">
         <v>10</v>
@@ -7321,26 +7321,26 @@
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B56" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C56" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="D56" s="1" t="n">
         <v>16</v>
-      </c>
-      <c r="D56" s="1" t="n">
-        <v>13</v>
       </c>
       <c r="E56" s="1" t="n">
         <v>26</v>
       </c>
       <c r="F56" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="G56" s="1" t="n">
         <v>20</v>
-      </c>
-      <c r="G56" s="1" t="n">
-        <v>22</v>
       </c>
       <c r="H56" s="1" t="n">
         <v>2</v>
@@ -7361,13 +7361,13 @@
         <v>18</v>
       </c>
       <c r="N56" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="O56" s="1" t="n">
         <v>25</v>
       </c>
       <c r="P56" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Q56" s="1" t="n">
         <v>23</v>
@@ -7385,7 +7385,7 @@
         <v>8</v>
       </c>
       <c r="V56" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="W56" s="1" t="n">
         <v>4</v>
@@ -7400,7 +7400,7 @@
         <v>7</v>
       </c>
       <c r="AA56" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AB56" s="1" t="n">
         <v>10</v>
@@ -7409,7 +7409,7 @@
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B57" s="1" t="n">
@@ -7419,16 +7419,16 @@
         <v>16</v>
       </c>
       <c r="D57" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F57" s="1" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H57" s="1" t="n">
         <v>2</v>
@@ -7446,22 +7446,22 @@
         <v>11</v>
       </c>
       <c r="M57" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="N57" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="N57" s="1" t="n">
-        <v>15</v>
-      </c>
       <c r="O57" s="1" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P57" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="Q57" s="1" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="R57" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="S57" s="1" t="n">
         <v>6</v>
@@ -7473,13 +7473,13 @@
         <v>8</v>
       </c>
       <c r="V57" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="W57" s="1" t="n">
         <v>4</v>
       </c>
       <c r="X57" s="1" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="Y57" s="1" t="n">
         <v>5</v>
@@ -7488,71 +7488,71 @@
         <v>7</v>
       </c>
       <c r="AA57" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AB57" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B58" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D58" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F58" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="G58" s="1" t="n">
         <v>20</v>
-      </c>
-      <c r="G58" s="1" t="n">
-        <v>17</v>
       </c>
       <c r="H58" s="1" t="n">
         <v>2</v>
       </c>
       <c r="I58" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J58" s="1" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K58" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L58" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="M58" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N58" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="O58" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="P58" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="O58" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="P58" s="1" t="n">
-        <v>11</v>
-      </c>
       <c r="Q58" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R58" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="S58" s="1" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T58" s="1" t="n">
         <v>24</v>
@@ -7564,132 +7564,132 @@
         <v>13</v>
       </c>
       <c r="W58" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="X58" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y58" s="1" t="n">
         <v>5</v>
-      </c>
-      <c r="X58" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="Y58" s="1" t="n">
-        <v>6</v>
       </c>
       <c r="Z58" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AA58" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AB58" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B59" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D59" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E59" s="1" t="n">
         <v>26</v>
       </c>
       <c r="F59" s="1" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H59" s="1" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I59" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J59" s="1" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="K59" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L59" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M59" s="1" t="n">
         <v>18</v>
       </c>
       <c r="N59" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O59" s="1" t="n">
         <v>25</v>
       </c>
       <c r="P59" s="1" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="Q59" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="R59" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="S59" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T59" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="U59" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V59" s="1" t="n">
         <v>13</v>
       </c>
       <c r="W59" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X59" s="1" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="Y59" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z59" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AA59" s="1" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AB59" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B60" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D60" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E60" s="1" t="n">
         <v>26</v>
       </c>
       <c r="F60" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G60" s="1" t="n">
         <v>20</v>
@@ -7698,7 +7698,7 @@
         <v>6</v>
       </c>
       <c r="I60" s="1" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J60" s="1" t="n">
         <v>19</v>
@@ -7719,10 +7719,10 @@
         <v>25</v>
       </c>
       <c r="P60" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Q60" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R60" s="1" t="n">
         <v>10</v>
@@ -7731,53 +7731,53 @@
         <v>2</v>
       </c>
       <c r="T60" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="U60" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="V60" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="W60" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="X60" s="1" t="n">
         <v>24</v>
-      </c>
-      <c r="U60" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="V60" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="W60" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="X60" s="1" t="n">
-        <v>23</v>
       </c>
       <c r="Y60" s="1" t="n">
         <v>5</v>
       </c>
       <c r="Z60" s="1" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AA60" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AB60" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B61" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D61" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E61" s="1" t="n">
         <v>26</v>
       </c>
       <c r="F61" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G61" s="1" t="n">
         <v>20</v>
@@ -7786,25 +7786,25 @@
         <v>6</v>
       </c>
       <c r="I61" s="1" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J61" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K61" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L61" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M61" s="1" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N61" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O61" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="P61" s="1" t="n">
         <v>17</v>
@@ -7813,31 +7813,31 @@
         <v>22</v>
       </c>
       <c r="R61" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="S61" s="1" t="n">
         <v>2</v>
       </c>
       <c r="T61" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="U61" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="V61" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="W61" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="X61" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="U61" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="V61" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="W61" s="1" t="n">
+      <c r="Y61" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z61" s="1" t="n">
         <v>4</v>
-      </c>
-      <c r="X61" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="Y61" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z61" s="1" t="n">
-        <v>5</v>
       </c>
       <c r="AA61" s="1" t="n">
         <v>21</v>
@@ -7849,32 +7849,32 @@
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B62" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D62" s="1" t="n">
         <v>11</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F62" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G62" s="1" t="n">
         <v>20</v>
       </c>
       <c r="H62" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="I62" s="1" t="n">
         <v>3</v>
-      </c>
-      <c r="I62" s="1" t="n">
-        <v>12</v>
       </c>
       <c r="J62" s="1" t="n">
         <v>18</v>
@@ -7883,13 +7883,13 @@
         <v>1</v>
       </c>
       <c r="L62" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M62" s="1" t="n">
         <v>19</v>
       </c>
       <c r="N62" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O62" s="1" t="n">
         <v>24</v>
@@ -7901,28 +7901,28 @@
         <v>22</v>
       </c>
       <c r="R62" s="1" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="S62" s="1" t="n">
         <v>2</v>
       </c>
       <c r="T62" s="1" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="U62" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V62" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="W62" s="1" t="n">
         <v>4</v>
       </c>
       <c r="X62" s="1" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Y62" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z62" s="1" t="n">
         <v>5</v>
@@ -7931,77 +7931,77 @@
         <v>21</v>
       </c>
       <c r="AB62" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B63" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C63" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="D63" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="D63" s="1" t="n">
-        <v>10</v>
-      </c>
       <c r="E63" s="1" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F63" s="1" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G63" s="1" t="n">
         <v>20</v>
       </c>
       <c r="H63" s="1" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="I63" s="1" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="J63" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K63" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L63" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M63" s="1" t="n">
         <v>19</v>
       </c>
       <c r="N63" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O63" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P63" s="1" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Q63" s="1" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="R63" s="1" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="S63" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T63" s="1" t="n">
         <v>26</v>
       </c>
       <c r="U63" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="V63" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="W63" s="1" t="n">
         <v>4</v>
@@ -8010,7 +8010,7 @@
         <v>23</v>
       </c>
       <c r="Y63" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z63" s="1" t="n">
         <v>5</v>
@@ -8019,62 +8019,62 @@
         <v>21</v>
       </c>
       <c r="AB63" s="1" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B64" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D64" s="1" t="n">
         <v>10</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F64" s="1" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="G64" s="1" t="n">
         <v>20</v>
       </c>
       <c r="H64" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I64" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J64" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K64" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L64" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M64" s="1" t="n">
         <v>19</v>
       </c>
       <c r="N64" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O64" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="P64" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q64" s="1" t="n">
         <v>24</v>
-      </c>
-      <c r="P64" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q64" s="1" t="n">
-        <v>21</v>
       </c>
       <c r="R64" s="1" t="n">
         <v>3</v>
@@ -8083,10 +8083,10 @@
         <v>1</v>
       </c>
       <c r="T64" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="U64" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V64" s="1" t="n">
         <v>12</v>
@@ -8095,7 +8095,7 @@
         <v>4</v>
       </c>
       <c r="X64" s="1" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="Y64" s="1" t="n">
         <v>6</v>
@@ -8104,50 +8104,50 @@
         <v>5</v>
       </c>
       <c r="AA64" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AB64" s="1" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B65" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D65" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F65" s="1" t="n">
         <v>18</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H65" s="1" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="I65" s="1" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="J65" s="1" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="K65" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L65" s="1" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="M65" s="1" t="n">
         <v>19</v>
@@ -8156,37 +8156,37 @@
         <v>17</v>
       </c>
       <c r="O65" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P65" s="1" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="Q65" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R65" s="1" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="S65" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T65" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="U65" s="1" t="n">
         <v>7</v>
       </c>
       <c r="V65" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="W65" s="1" t="n">
         <v>4</v>
       </c>
       <c r="X65" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Y65" s="1" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Z65" s="1" t="n">
         <v>5</v>
@@ -8201,7 +8201,7 @@
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B66" s="1" t="n">
@@ -8211,10 +8211,10 @@
         <v>16</v>
       </c>
       <c r="D66" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F66" s="1" t="n">
         <v>18</v>
@@ -8223,19 +8223,19 @@
         <v>21</v>
       </c>
       <c r="H66" s="1" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="I66" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J66" s="1" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K66" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L66" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M66" s="1" t="n">
         <v>19</v>
@@ -8253,13 +8253,13 @@
         <v>20</v>
       </c>
       <c r="R66" s="1" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="S66" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T66" s="1" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="U66" s="1" t="n">
         <v>7</v>
@@ -8268,101 +8268,101 @@
         <v>15</v>
       </c>
       <c r="W66" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X66" s="1" t="n">
         <v>25</v>
       </c>
       <c r="Y66" s="1" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="Z66" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA66" s="1" t="n">
         <v>22</v>
       </c>
       <c r="AB66" s="1" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B67" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D67" s="1" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E67" s="1" t="n">
         <v>24</v>
       </c>
       <c r="F67" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G67" s="1" t="n">
         <v>21</v>
       </c>
       <c r="H67" s="1" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I67" s="1" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="J67" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K67" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L67" s="1" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="M67" s="1" t="n">
         <v>19</v>
       </c>
       <c r="N67" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O67" s="1" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="P67" s="1" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="Q67" s="1" t="n">
         <v>20</v>
       </c>
       <c r="R67" s="1" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="S67" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T67" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="U67" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V67" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="W67" s="1" t="n">
         <v>3</v>
       </c>
       <c r="X67" s="1" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Y67" s="1" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="Z67" s="1" t="n">
         <v>4</v>

--- a/NSE_Sector_Monitor.xlsx
+++ b/NSE_Sector_Monitor.xlsx
@@ -568,22 +568,22 @@
         <v>0</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>13.92</v>
+        <v>13.68</v>
       </c>
       <c r="H2" s="1" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-1.79</v>
       </c>
       <c r="I2" s="1" t="n">
-        <v>-3.29</v>
+        <v>-5.75</v>
       </c>
       <c r="J2" s="1" t="n">
-        <v>0.49</v>
+        <v>-0.78</v>
       </c>
       <c r="K2" s="1" t="n">
-        <v>15.3</v>
+        <v>13.24</v>
       </c>
       <c r="L2" s="1" t="inlineStr">
         <is>
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="M2" s="1" t="n">
-        <v>-4.66</v>
+        <v>-5.75</v>
       </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
@@ -624,31 +624,31 @@
         <v>2</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>27.56</v>
+        <v>27.79</v>
       </c>
       <c r="H3" s="1" t="n">
-        <v>-0.86</v>
+        <v>0.83</v>
       </c>
       <c r="I3" s="1" t="n">
-        <v>2.08</v>
+        <v>3.55</v>
       </c>
       <c r="J3" s="1" t="n">
-        <v>5.07</v>
+        <v>6.84</v>
       </c>
       <c r="K3" s="1" t="n">
-        <v>10.08</v>
+        <v>11.04</v>
       </c>
       <c r="L3" s="1" t="inlineStr">
         <is>
@@ -660,7 +660,7 @@
       </c>
       <c r="N3" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O3" s="1" t="inlineStr">
@@ -682,38 +682,38 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Digital</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
         <v>3</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>84.53</v>
+        <v>30.8</v>
       </c>
       <c r="H4" s="1" t="n">
-        <v>-1.37</v>
+        <v>-1.6</v>
       </c>
       <c r="I4" s="1" t="n">
-        <v>-2.09</v>
+        <v>-0.01</v>
       </c>
       <c r="J4" s="1" t="n">
-        <v>-2.53</v>
+        <v>-4.78</v>
       </c>
       <c r="K4" s="1" t="n">
-        <v>9.300000000000001</v>
+        <v>9.75</v>
       </c>
       <c r="L4" s="1" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
         </is>
       </c>
       <c r="M4" s="1" t="n">
-        <v>-9.93</v>
+        <v>-25.19</v>
       </c>
       <c r="N4" s="1" t="inlineStr">
         <is>
@@ -747,46 +747,46 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Realty</t>
+          <t>Digital</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
         <v>4</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="D5" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="E5" s="2" t="n">
-        <v>-2</v>
-      </c>
       <c r="F5" s="2" t="n">
-        <v>-2</v>
+        <v>21</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>85.33</v>
+        <v>83.48999999999999</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>-2</v>
+        <v>-2.58</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>2.44</v>
+        <v>-2.81</v>
       </c>
       <c r="J5" s="1" t="n">
-        <v>-0.57</v>
+        <v>-2.97</v>
       </c>
       <c r="K5" s="1" t="n">
-        <v>8.1</v>
+        <v>9.34</v>
       </c>
       <c r="L5" s="1" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Down</t>
         </is>
       </c>
       <c r="M5" s="1" t="n">
-        <v>-5.85</v>
+        <v>-10.51</v>
       </c>
       <c r="N5" s="1" t="inlineStr">
         <is>
@@ -805,53 +805,53 @@
       </c>
       <c r="Q5" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Metal</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
         <v>5</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>31.23</v>
+        <v>13.02</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>-0.22</v>
+        <v>-1.21</v>
       </c>
       <c r="I6" s="1" t="n">
-        <v>-0.02</v>
+        <v>2.9</v>
       </c>
       <c r="J6" s="1" t="n">
-        <v>-4.75</v>
+        <v>3.64</v>
       </c>
       <c r="K6" s="1" t="n">
-        <v>7.62</v>
+        <v>7.86</v>
       </c>
       <c r="L6" s="1" t="inlineStr">
         <is>
-          <t>Down</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="M6" s="1" t="n">
-        <v>-24.59</v>
+        <v>-2.89</v>
       </c>
       <c r="N6" s="1" t="inlineStr">
         <is>
@@ -870,7 +870,7 @@
       </c>
       <c r="Q6" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -884,31 +884,31 @@
         <v>6</v>
       </c>
       <c r="C7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="2" t="n">
         <v>-2</v>
       </c>
-      <c r="D7" s="2" t="n">
+      <c r="E7" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="E7" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="F7" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>17.03</v>
+        <v>17.14</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>-0.82</v>
+        <v>-0.17</v>
       </c>
       <c r="I7" s="1" t="n">
-        <v>1.04</v>
+        <v>2.54</v>
       </c>
       <c r="J7" s="1" t="n">
-        <v>4.54</v>
+        <v>5.67</v>
       </c>
       <c r="K7" s="1" t="n">
-        <v>6.26</v>
+        <v>7.37</v>
       </c>
       <c r="L7" s="1" t="inlineStr">
         <is>
@@ -925,12 +925,12 @@
       </c>
       <c r="O7" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P7" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Q7" s="1" t="inlineStr">
@@ -942,46 +942,46 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Metal</t>
+          <t>Realty</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
         <v>7</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>3</v>
+        <v>-3</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>13</v>
+        <v>-5</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>12.91</v>
+        <v>84.51000000000001</v>
       </c>
       <c r="H8" s="1" t="n">
-        <v>-2.05</v>
+        <v>-2.94</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>1.72</v>
+        <v>1.26</v>
       </c>
       <c r="J8" s="1" t="n">
-        <v>0.76</v>
+        <v>-0.42</v>
       </c>
       <c r="K8" s="1" t="n">
-        <v>6.08</v>
+        <v>6.26</v>
       </c>
       <c r="L8" s="1" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Down</t>
         </is>
       </c>
       <c r="M8" s="1" t="n">
-        <v>-4.28</v>
+        <v>-6.2</v>
       </c>
       <c r="N8" s="1" t="inlineStr">
         <is>
@@ -1020,25 +1020,25 @@
         <v>1</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>-3</v>
+        <v>-5</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>10</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>274.3</v>
+        <v>272.72</v>
       </c>
       <c r="H9" s="1" t="n">
-        <v>-1.51</v>
+        <v>-2.08</v>
       </c>
       <c r="I9" s="1" t="n">
-        <v>0.28</v>
+        <v>0.41</v>
       </c>
       <c r="J9" s="1" t="n">
-        <v>-2.62</v>
+        <v>-3.15</v>
       </c>
       <c r="K9" s="1" t="n">
-        <v>4.06</v>
+        <v>3.92</v>
       </c>
       <c r="L9" s="1" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="M9" s="1" t="n">
-        <v>-4.84</v>
+        <v>-4.82</v>
       </c>
       <c r="N9" s="1" t="inlineStr">
         <is>
@@ -1079,31 +1079,31 @@
         <v>9</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>6</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>159.19</v>
+        <v>158.6</v>
       </c>
       <c r="H10" s="1" t="n">
-        <v>-1.46</v>
+        <v>-0.37</v>
       </c>
       <c r="I10" s="1" t="n">
-        <v>0.62</v>
+        <v>1.19</v>
       </c>
       <c r="J10" s="1" t="n">
-        <v>0.04</v>
+        <v>0.4</v>
       </c>
       <c r="K10" s="1" t="n">
-        <v>2.48</v>
+        <v>2.29</v>
       </c>
       <c r="L10" s="1" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="M10" s="1" t="n">
-        <v>-0.54</v>
+        <v>-0.32</v>
       </c>
       <c r="N10" s="1" t="inlineStr">
         <is>
@@ -1130,45 +1130,45 @@
       </c>
       <c r="Q10" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>EV &amp; New Age Auto</t>
+          <t>Consumption</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
         <v>10</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>-4</v>
+        <v>1</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-5</v>
+        <v>7</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>30.94</v>
+        <v>125.07</v>
       </c>
       <c r="H11" s="1" t="n">
-        <v>-1.56</v>
+        <v>-0.72</v>
       </c>
       <c r="I11" s="1" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.59</v>
       </c>
       <c r="J11" s="1" t="n">
-        <v>-1.9</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="K11" s="1" t="n">
-        <v>2.46</v>
+        <v>1.79</v>
       </c>
       <c r="L11" s="1" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         </is>
       </c>
       <c r="M11" s="1" t="n">
-        <v>-4.05</v>
+        <v>-4.82</v>
       </c>
       <c r="N11" s="1" t="inlineStr">
         <is>
@@ -1195,14 +1195,14 @@
       </c>
       <c r="Q11" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Consumption</t>
+          <t>EV &amp; New Age Auto</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
@@ -1212,36 +1212,36 @@
         <v>-2</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>2</v>
+        <v>-5</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>6</v>
+        <v>-2</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>125.98</v>
+        <v>30.28</v>
       </c>
       <c r="H12" s="1" t="n">
-        <v>-1.2</v>
+        <v>-3.66</v>
       </c>
       <c r="I12" s="1" t="n">
-        <v>0.8100000000000001</v>
+        <v>-0.57</v>
       </c>
       <c r="J12" s="1" t="n">
-        <v>0.5600000000000001</v>
+        <v>-3.78</v>
       </c>
       <c r="K12" s="1" t="n">
-        <v>2.11</v>
+        <v>1.76</v>
       </c>
       <c r="L12" s="1" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Down</t>
         </is>
       </c>
       <c r="M12" s="1" t="n">
-        <v>-4.7</v>
+        <v>-5.54</v>
       </c>
       <c r="N12" s="1" t="inlineStr">
         <is>
@@ -1274,31 +1274,31 @@
         <v>12</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>-7</v>
+        <v>-4</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>-11</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>101.45</v>
+        <v>101.29</v>
       </c>
       <c r="H13" s="1" t="n">
-        <v>-1.58</v>
+        <v>-1.74</v>
       </c>
       <c r="I13" s="1" t="n">
-        <v>1.01</v>
+        <v>0.63</v>
       </c>
       <c r="J13" s="1" t="n">
-        <v>0.48</v>
+        <v>0.83</v>
       </c>
       <c r="K13" s="1" t="n">
-        <v>1.81</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="L13" s="1" t="inlineStr">
         <is>
@@ -1306,7 +1306,7 @@
         </is>
       </c>
       <c r="M13" s="1" t="n">
-        <v>-3.9</v>
+        <v>-3.48</v>
       </c>
       <c r="N13" s="1" t="inlineStr">
         <is>
@@ -1332,46 +1332,46 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Oil &amp; Gas</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
         <v>13</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>-3</v>
+        <v>7</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-6</v>
+        <v>11</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>28.74</v>
+        <v>10.8</v>
       </c>
       <c r="H14" s="1" t="n">
-        <v>-2.38</v>
+        <v>-1.91</v>
       </c>
       <c r="I14" s="1" t="n">
-        <v>0.76</v>
+        <v>0.17</v>
       </c>
       <c r="J14" s="1" t="n">
-        <v>0.22</v>
+        <v>2.13</v>
       </c>
       <c r="K14" s="1" t="n">
-        <v>1.68</v>
+        <v>0.24</v>
       </c>
       <c r="L14" s="1" t="inlineStr">
         <is>
-          <t>Down</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="M14" s="1" t="n">
-        <v>0</v>
+        <v>-8.869999999999999</v>
       </c>
       <c r="N14" s="1" t="inlineStr">
         <is>
@@ -1397,46 +1397,46 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
         <v>14</v>
       </c>
       <c r="C15" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="E15" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D15" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="E15" s="2" t="n">
-        <v>9</v>
-      </c>
       <c r="F15" s="2" t="n">
-        <v>12</v>
+        <v>-7</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>10.85</v>
+        <v>28.5</v>
       </c>
       <c r="H15" s="1" t="n">
-        <v>-1.45</v>
+        <v>-3.19</v>
       </c>
       <c r="I15" s="1" t="n">
-        <v>-0.3</v>
+        <v>0.42</v>
       </c>
       <c r="J15" s="1" t="n">
-        <v>2.25</v>
+        <v>-1.14</v>
       </c>
       <c r="K15" s="1" t="n">
-        <v>0.31</v>
+        <v>0.15</v>
       </c>
       <c r="L15" s="1" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Down</t>
         </is>
       </c>
       <c r="M15" s="1" t="n">
-        <v>-8.98</v>
+        <v>0</v>
       </c>
       <c r="N15" s="1" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Tourism</t>
+          <t>Services</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
@@ -1472,36 +1472,36 @@
         <v>-1</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>-3</v>
+        <v>2</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>-7</v>
+        <v>1</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-11</v>
+        <v>7</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>75.95</v>
+        <v>29.32</v>
       </c>
       <c r="H16" s="1" t="n">
-        <v>-0.98</v>
+        <v>-1.68</v>
       </c>
       <c r="I16" s="1" t="n">
-        <v>0.11</v>
+        <v>0.13</v>
       </c>
       <c r="J16" s="1" t="n">
-        <v>2.13</v>
+        <v>0.32</v>
       </c>
       <c r="K16" s="1" t="n">
-        <v>-0.34</v>
+        <v>-0.36</v>
       </c>
       <c r="L16" s="1" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Down</t>
         </is>
       </c>
       <c r="M16" s="1" t="n">
-        <v>-11.88</v>
+        <v>0</v>
       </c>
       <c r="N16" s="1" t="inlineStr">
         <is>
@@ -1527,46 +1527,46 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>MNC</t>
+          <t>Commodities</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
         <v>16</v>
       </c>
       <c r="C17" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="F17" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="D17" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="E17" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="F17" s="2" t="n">
-        <v>-5</v>
-      </c>
       <c r="G17" s="1" t="n">
-        <v>31.93</v>
+        <v>95.27</v>
       </c>
       <c r="H17" s="1" t="n">
-        <v>-0.84</v>
+        <v>-0.13</v>
       </c>
       <c r="I17" s="1" t="n">
-        <v>0.77</v>
+        <v>0.6</v>
       </c>
       <c r="J17" s="1" t="n">
-        <v>-0.52</v>
+        <v>2.21</v>
       </c>
       <c r="K17" s="1" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.75</v>
       </c>
       <c r="L17" s="1" t="inlineStr">
         <is>
-          <t>Down</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="M17" s="1" t="n">
-        <v>-3.64</v>
+        <v>-7.92</v>
       </c>
       <c r="N17" s="1" t="inlineStr">
         <is>
@@ -1592,46 +1592,46 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>Commodities</t>
+          <t>MNC</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
         <v>17</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>3</v>
+        <v>-3</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>95.39</v>
+        <v>31.77</v>
       </c>
       <c r="H18" s="1" t="n">
-        <v>-1.62</v>
+        <v>-1.34</v>
       </c>
       <c r="I18" s="1" t="n">
-        <v>0.61</v>
+        <v>1.51</v>
       </c>
       <c r="J18" s="1" t="n">
-        <v>1.13</v>
+        <v>-0.53</v>
       </c>
       <c r="K18" s="1" t="n">
-        <v>-0.96</v>
+        <v>-1.09</v>
       </c>
       <c r="L18" s="1" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Down</t>
         </is>
       </c>
       <c r="M18" s="1" t="n">
-        <v>-8.35</v>
+        <v>-3.55</v>
       </c>
       <c r="N18" s="1" t="inlineStr">
         <is>
@@ -1657,46 +1657,46 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>PSE</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
         <v>18</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>-5</v>
+        <v>7</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>-3</v>
+        <v>3</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>-3</v>
+        <v>9</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>29.24</v>
+        <v>9.82</v>
       </c>
       <c r="H19" s="1" t="n">
-        <v>-1.95</v>
+        <v>-1.5</v>
       </c>
       <c r="I19" s="1" t="n">
-        <v>-1.2</v>
+        <v>1.28</v>
       </c>
       <c r="J19" s="1" t="n">
-        <v>-0.88</v>
+        <v>4.09</v>
       </c>
       <c r="K19" s="1" t="n">
-        <v>-1.57</v>
+        <v>-1.18</v>
       </c>
       <c r="L19" s="1" t="inlineStr">
         <is>
-          <t>Down</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="M19" s="1" t="n">
-        <v>0</v>
+        <v>-9.529999999999999</v>
       </c>
       <c r="N19" s="1" t="inlineStr">
         <is>
@@ -1722,46 +1722,46 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>Fin Services</t>
+          <t>Private Bank</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
         <v>19</v>
       </c>
       <c r="C20" s="2" t="n">
+        <v>-4</v>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E20" s="2" t="n">
         <v>-7</v>
-      </c>
-      <c r="D20" s="2" t="n">
-        <v>-8</v>
-      </c>
-      <c r="E20" s="2" t="n">
-        <v>-2</v>
       </c>
       <c r="F20" s="2" t="n">
         <v>-7</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>30.56</v>
+        <v>26.93</v>
       </c>
       <c r="H20" s="1" t="n">
-        <v>-1.74</v>
+        <v>-1.89</v>
       </c>
       <c r="I20" s="1" t="n">
-        <v>-2.38</v>
+        <v>-0.38</v>
       </c>
       <c r="J20" s="1" t="n">
-        <v>-2.76</v>
+        <v>1.11</v>
       </c>
       <c r="K20" s="1" t="n">
-        <v>-1.57</v>
+        <v>-1.2</v>
       </c>
       <c r="L20" s="1" t="inlineStr">
         <is>
-          <t>Down</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="M20" s="1" t="n">
-        <v>-3.93</v>
+        <v>-3.88</v>
       </c>
       <c r="N20" s="1" t="inlineStr">
         <is>
@@ -1787,38 +1787,38 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>Private Bank</t>
+          <t>Tourism</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
         <v>20</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>-2</v>
+        <v>-9</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>-2</v>
+        <v>-9</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>-7</v>
+        <v>-12</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>-7</v>
+        <v>-15</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>27.09</v>
+        <v>75.66</v>
       </c>
       <c r="H21" s="1" t="n">
-        <v>-1.31</v>
+        <v>-1.36</v>
       </c>
       <c r="I21" s="1" t="n">
-        <v>-0.05</v>
+        <v>-0.62</v>
       </c>
       <c r="J21" s="1" t="n">
-        <v>1.23</v>
+        <v>2.83</v>
       </c>
       <c r="K21" s="1" t="n">
-        <v>-1.7</v>
+        <v>-1.36</v>
       </c>
       <c r="L21" s="1" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         </is>
       </c>
       <c r="M21" s="1" t="n">
-        <v>-3.88</v>
+        <v>-11.69</v>
       </c>
       <c r="N21" s="1" t="inlineStr">
         <is>
@@ -1852,38 +1852,38 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>PSE</t>
+          <t>Bank</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
         <v>21</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>4</v>
+        <v>-11</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>2</v>
+        <v>-5</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>9.81</v>
+        <v>564.42</v>
       </c>
       <c r="H22" s="1" t="n">
-        <v>-1.6</v>
+        <v>-2.07</v>
       </c>
       <c r="I22" s="1" t="n">
-        <v>0.37</v>
+        <v>-0.24</v>
       </c>
       <c r="J22" s="1" t="n">
-        <v>2.59</v>
+        <v>0.55</v>
       </c>
       <c r="K22" s="1" t="n">
-        <v>-1.94</v>
+        <v>-1.53</v>
       </c>
       <c r="L22" s="1" t="inlineStr">
         <is>
@@ -1891,7 +1891,7 @@
         </is>
       </c>
       <c r="M22" s="1" t="n">
-        <v>-10.15</v>
+        <v>-5.61</v>
       </c>
       <c r="N22" s="1" t="inlineStr">
         <is>
@@ -1917,46 +1917,46 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>Bank</t>
+          <t>Capital Market</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
         <v>22</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>-6</v>
+        <v>0</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>-11</v>
+        <v>-2</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>-6</v>
+        <v>-18</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>565.3200000000001</v>
+        <v>51.55</v>
       </c>
       <c r="H23" s="1" t="n">
-        <v>-1.91</v>
+        <v>-2.68</v>
       </c>
       <c r="I23" s="1" t="n">
-        <v>-0.68</v>
+        <v>0.43</v>
       </c>
       <c r="J23" s="1" t="n">
-        <v>0.37</v>
+        <v>-0.06</v>
       </c>
       <c r="K23" s="1" t="n">
-        <v>-2.2</v>
+        <v>-1.82</v>
       </c>
       <c r="L23" s="1" t="inlineStr">
         <is>
-          <t>Down</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="M23" s="1" t="n">
-        <v>-6.02</v>
+        <v>0</v>
       </c>
       <c r="N23" s="1" t="inlineStr">
         <is>
@@ -1982,46 +1982,46 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Capital Market</t>
+          <t>PSU Bank</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
         <v>23</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D24" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>-2</v>
+        <v>-10</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>-20</v>
+        <v>3</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>51.77</v>
+        <v>89.70999999999999</v>
       </c>
       <c r="H24" s="1" t="n">
-        <v>-2.27</v>
+        <v>-2.86</v>
       </c>
       <c r="I24" s="1" t="n">
-        <v>0.57</v>
+        <v>0.41</v>
       </c>
       <c r="J24" s="1" t="n">
-        <v>-1.09</v>
+        <v>0.02</v>
       </c>
       <c r="K24" s="1" t="n">
-        <v>-2.27</v>
+        <v>-1.84</v>
       </c>
       <c r="L24" s="1" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Down</t>
         </is>
       </c>
       <c r="M24" s="1" t="n">
-        <v>0</v>
+        <v>-13.85</v>
       </c>
       <c r="N24" s="1" t="inlineStr">
         <is>
@@ -2047,38 +2047,38 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>PSU Bank</t>
+          <t>Fin Services</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
         <v>24</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>0</v>
+        <v>-11</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="E25" s="2" t="n">
         <v>-10</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>0</v>
+        <v>-11</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>89.92</v>
+        <v>30.42</v>
       </c>
       <c r="H25" s="1" t="n">
-        <v>-2.63</v>
+        <v>-2.19</v>
       </c>
       <c r="I25" s="1" t="n">
-        <v>-0.32</v>
+        <v>-1.96</v>
       </c>
       <c r="J25" s="1" t="n">
-        <v>-0.91</v>
+        <v>-2.16</v>
       </c>
       <c r="K25" s="1" t="n">
-        <v>-2.61</v>
+        <v>-2.04</v>
       </c>
       <c r="L25" s="1" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         </is>
       </c>
       <c r="M25" s="1" t="n">
-        <v>-14.16</v>
+        <v>-3.81</v>
       </c>
       <c r="N25" s="1" t="inlineStr">
         <is>
@@ -2119,39 +2119,39 @@
         <v>25</v>
       </c>
       <c r="C26" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E26" s="2" t="n">
         <v>-4</v>
-      </c>
-      <c r="D26" s="2" t="n">
-        <v>-3</v>
-      </c>
-      <c r="E26" s="2" t="n">
-        <v>-3</v>
       </c>
       <c r="F26" s="2" t="n">
         <v>-6</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>90.51000000000001</v>
+        <v>90.62</v>
       </c>
       <c r="H26" s="1" t="n">
-        <v>-2.08</v>
+        <v>0.12</v>
       </c>
       <c r="I26" s="1" t="n">
-        <v>-0.1</v>
+        <v>0.4</v>
       </c>
       <c r="J26" s="1" t="n">
-        <v>1.05</v>
+        <v>1.64</v>
       </c>
       <c r="K26" s="1" t="n">
-        <v>-3.13</v>
+        <v>-2.19</v>
       </c>
       <c r="L26" s="1" t="inlineStr">
         <is>
-          <t>Down</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="M26" s="1" t="n">
-        <v>-5</v>
+        <v>-4.32</v>
       </c>
       <c r="N26" s="1" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
@@ -2187,28 +2187,28 @@
         <v>0</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>-5</v>
+        <v>-20</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>48.76</v>
+        <v>36.92</v>
       </c>
       <c r="H27" s="1" t="n">
-        <v>-1.46</v>
+        <v>-1.91</v>
       </c>
       <c r="I27" s="1" t="n">
-        <v>1.08</v>
+        <v>0.44</v>
       </c>
       <c r="J27" s="1" t="n">
-        <v>2.51</v>
+        <v>3.2</v>
       </c>
       <c r="K27" s="1" t="n">
-        <v>-4.1</v>
+        <v>-3.67</v>
       </c>
       <c r="L27" s="1" t="inlineStr">
         <is>
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M27" s="1" t="n">
-        <v>-15.08</v>
+        <v>0</v>
       </c>
       <c r="N27" s="1" t="inlineStr">
         <is>
@@ -2242,7 +2242,7 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
@@ -2252,36 +2252,36 @@
         <v>0</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>-21</v>
+        <v>-6</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>37.05</v>
+        <v>48.35</v>
       </c>
       <c r="H28" s="1" t="n">
-        <v>-1.57</v>
+        <v>-0.84</v>
       </c>
       <c r="I28" s="1" t="n">
-        <v>0.28</v>
+        <v>1.38</v>
       </c>
       <c r="J28" s="1" t="n">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="K28" s="1" t="n">
-        <v>-4.37</v>
+        <v>-3.9</v>
       </c>
       <c r="L28" s="1" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Down</t>
         </is>
       </c>
       <c r="M28" s="1" t="n">
-        <v>0</v>
+        <v>-15.3</v>
       </c>
       <c r="N28" s="1" t="inlineStr">
         <is>
@@ -2569,26 +2569,26 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F2" s="1" t="n">
         <v>8</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H2" s="1" t="n">
         <v>2</v>
@@ -2597,80 +2597,80 @@
         <v>6</v>
       </c>
       <c r="J2" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="K2" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="K2" s="1" t="n">
-        <v>4</v>
-      </c>
       <c r="L2" s="1" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="M2" s="1" t="n">
         <v>25</v>
       </c>
       <c r="N2" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O2" s="1" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="P2" s="1" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Q2" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="R2" s="1" t="n">
         <v>17</v>
-      </c>
-      <c r="R2" s="1" t="n">
-        <v>16</v>
       </c>
       <c r="S2" s="1" t="n">
         <v>12</v>
       </c>
       <c r="T2" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="U2" s="1" t="n">
         <v>14</v>
-      </c>
-      <c r="U2" s="1" t="n">
-        <v>13</v>
       </c>
       <c r="V2" s="1" t="n">
         <v>9</v>
       </c>
       <c r="W2" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="X2" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y2" s="1" t="n">
         <v>1</v>
       </c>
       <c r="Z2" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="AA2" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="AA2" s="1" t="n">
-        <v>18</v>
-      </c>
       <c r="AB2" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C3" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="D3" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="D3" s="1" t="n">
-        <v>24</v>
-      </c>
       <c r="E3" s="1" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F3" s="1" t="n">
         <v>8</v>
@@ -2679,73 +2679,73 @@
         <v>27</v>
       </c>
       <c r="H3" s="1" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I3" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J3" s="1" t="n">
         <v>5</v>
       </c>
       <c r="K3" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L3" s="1" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="M3" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N3" s="1" t="n">
         <v>13</v>
       </c>
       <c r="O3" s="1" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="P3" s="1" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Q3" s="1" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="R3" s="1" t="n">
         <v>17</v>
       </c>
       <c r="S3" s="1" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T3" s="1" t="n">
         <v>14</v>
       </c>
       <c r="U3" s="1" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="V3" s="1" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="W3" s="1" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="X3" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y3" s="1" t="n">
         <v>1</v>
       </c>
       <c r="Z3" s="1" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="AA3" s="1" t="n">
         <v>16</v>
       </c>
       <c r="AB3" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
@@ -2779,7 +2779,7 @@
         <v>4</v>
       </c>
       <c r="L4" s="1" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="M4" s="1" t="n">
         <v>25</v>
@@ -2794,7 +2794,7 @@
         <v>26</v>
       </c>
       <c r="Q4" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="R4" s="1" t="n">
         <v>17</v>
@@ -2821,10 +2821,10 @@
         <v>1</v>
       </c>
       <c r="Z4" s="1" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AA4" s="1" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="AB4" s="1" t="n">
         <v>12</v>
@@ -2833,105 +2833,105 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="C5" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="F5" s="1" t="n">
         <v>8</v>
-      </c>
-      <c r="C5" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>23</v>
-      </c>
-      <c r="F5" s="1" t="n">
-        <v>7</v>
       </c>
       <c r="G5" s="1" t="n">
         <v>27</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I5" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="J5" s="1" t="n">
         <v>5</v>
-      </c>
-      <c r="J5" s="1" t="n">
-        <v>6</v>
       </c>
       <c r="K5" s="1" t="n">
         <v>4</v>
       </c>
       <c r="L5" s="1" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="M5" s="1" t="n">
         <v>25</v>
       </c>
       <c r="N5" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="O5" s="1" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="P5" s="1" t="n">
         <v>26</v>
       </c>
       <c r="Q5" s="1" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="R5" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="S5" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="T5" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="T5" s="1" t="n">
-        <v>19</v>
-      </c>
       <c r="U5" s="1" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="V5" s="1" t="n">
         <v>10</v>
       </c>
       <c r="W5" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="X5" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y5" s="1" t="n">
         <v>1</v>
       </c>
       <c r="Z5" s="1" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AA5" s="1" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="AB5" s="1" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E6" s="1" t="n">
         <v>23</v>
@@ -2946,49 +2946,49 @@
         <v>3</v>
       </c>
       <c r="I6" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="J6" s="1" t="n">
         <v>6</v>
-      </c>
-      <c r="J6" s="1" t="n">
-        <v>8</v>
       </c>
       <c r="K6" s="1" t="n">
         <v>4</v>
       </c>
       <c r="L6" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M6" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="N6" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="O6" s="1" t="n">
         <v>24</v>
-      </c>
-      <c r="N6" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="O6" s="1" t="n">
-        <v>25</v>
       </c>
       <c r="P6" s="1" t="n">
         <v>26</v>
       </c>
       <c r="Q6" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="R6" s="1" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="S6" s="1" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="T6" s="1" t="n">
         <v>19</v>
       </c>
       <c r="U6" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="V6" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="W6" s="1" t="n">
         <v>17</v>
-      </c>
-      <c r="V6" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="W6" s="1" t="n">
-        <v>22</v>
       </c>
       <c r="X6" s="1" t="n">
         <v>2</v>
@@ -2997,10 +2997,10 @@
         <v>1</v>
       </c>
       <c r="Z6" s="1" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="AA6" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AB6" s="1" t="n">
         <v>9</v>
@@ -3009,114 +3009,114 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F7" s="1" t="n">
         <v>7</v>
       </c>
       <c r="G7" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="H7" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="I7" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="J7" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="K7" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="L7" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="M7" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="N7" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="O7" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="P7" s="1" t="n">
         <v>26</v>
       </c>
-      <c r="H7" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="I7" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="J7" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="K7" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="L7" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="M7" s="1" t="n">
+      <c r="Q7" s="1" t="n">
         <v>21</v>
-      </c>
-      <c r="N7" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="O7" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="P7" s="1" t="n">
-        <v>27</v>
-      </c>
-      <c r="Q7" s="1" t="n">
-        <v>23</v>
       </c>
       <c r="R7" s="1" t="n">
         <v>20</v>
       </c>
       <c r="S7" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="T7" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="T7" s="1" t="n">
-        <v>15</v>
-      </c>
       <c r="U7" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="V7" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="W7" s="1" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="X7" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y7" s="1" t="n">
         <v>1</v>
       </c>
       <c r="Z7" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA7" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="AA7" s="1" t="n">
-        <v>13</v>
-      </c>
       <c r="AB7" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
         <v>6</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>7</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H8" s="1" t="n">
         <v>2</v>
@@ -3125,46 +3125,46 @@
         <v>4</v>
       </c>
       <c r="J8" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K8" s="1" t="n">
         <v>5</v>
       </c>
       <c r="L8" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="M8" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="N8" s="1" t="n">
         <v>9</v>
-      </c>
-      <c r="M8" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="N8" s="1" t="n">
-        <v>13</v>
       </c>
       <c r="O8" s="1" t="n">
         <v>22</v>
       </c>
       <c r="P8" s="1" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Q8" s="1" t="n">
         <v>23</v>
       </c>
       <c r="R8" s="1" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="S8" s="1" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="T8" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="U8" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="U8" s="1" t="n">
-        <v>15</v>
-      </c>
       <c r="V8" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="W8" s="1" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="X8" s="1" t="n">
         <v>3</v>
@@ -3173,10 +3173,10 @@
         <v>1</v>
       </c>
       <c r="Z8" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AA8" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AB8" s="1" t="n">
         <v>8</v>
@@ -3185,20 +3185,20 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
         <v>6</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F9" s="1" t="n">
         <v>7</v>
@@ -3213,43 +3213,43 @@
         <v>4</v>
       </c>
       <c r="J9" s="1" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K9" s="1" t="n">
         <v>5</v>
       </c>
       <c r="L9" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M9" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N9" s="1" t="n">
         <v>13</v>
       </c>
       <c r="O9" s="1" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="P9" s="1" t="n">
         <v>26</v>
       </c>
       <c r="Q9" s="1" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="R9" s="1" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="S9" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="T9" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="U9" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="T9" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="U9" s="1" t="n">
-        <v>18</v>
-      </c>
       <c r="V9" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="W9" s="1" t="n">
         <v>21</v>
@@ -3264,7 +3264,7 @@
         <v>12</v>
       </c>
       <c r="AA9" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AB9" s="1" t="n">
         <v>8</v>
@@ -3273,23 +3273,23 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E10" s="1" t="n">
         <v>24</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G10" s="1" t="n">
         <v>27</v>
@@ -3301,46 +3301,46 @@
         <v>4</v>
       </c>
       <c r="J10" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K10" s="1" t="n">
         <v>5</v>
       </c>
       <c r="L10" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="M10" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="N10" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="M10" s="1" t="n">
+      <c r="O10" s="1" t="n">
         <v>25</v>
-      </c>
-      <c r="N10" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="O10" s="1" t="n">
-        <v>21</v>
       </c>
       <c r="P10" s="1" t="n">
         <v>26</v>
       </c>
       <c r="Q10" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R10" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="S10" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="T10" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="S10" s="1" t="n">
+      <c r="U10" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="T10" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="U10" s="1" t="n">
-        <v>16</v>
-      </c>
       <c r="V10" s="1" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="W10" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="X10" s="1" t="n">
         <v>3</v>
@@ -3349,10 +3349,10 @@
         <v>1</v>
       </c>
       <c r="Z10" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AA10" s="1" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AB10" s="1" t="n">
         <v>8</v>
@@ -3361,23 +3361,23 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G11" s="1" t="n">
         <v>27</v>
@@ -3389,19 +3389,19 @@
         <v>4</v>
       </c>
       <c r="J11" s="1" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="K11" s="1" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M11" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="N11" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O11" s="1" t="n">
         <v>21</v>
@@ -3410,22 +3410,22 @@
         <v>26</v>
       </c>
       <c r="Q11" s="1" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="R11" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="S11" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="T11" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="S11" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="T11" s="1" t="n">
-        <v>20</v>
-      </c>
       <c r="U11" s="1" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="V11" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="W11" s="1" t="n">
         <v>22</v>
@@ -3437,23 +3437,23 @@
         <v>1</v>
       </c>
       <c r="Z11" s="1" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AA11" s="1" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="AB11" s="1" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C12" s="1" t="n">
         <v>16</v>
@@ -3462,7 +3462,7 @@
         <v>18</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F12" s="1" t="n">
         <v>9</v>
@@ -3474,22 +3474,22 @@
         <v>2</v>
       </c>
       <c r="I12" s="1" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J12" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="K12" s="1" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="M12" s="1" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="N12" s="1" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="O12" s="1" t="n">
         <v>21</v>
@@ -3501,22 +3501,22 @@
         <v>25</v>
       </c>
       <c r="R12" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="S12" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="T12" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="S12" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="T12" s="1" t="n">
-        <v>19</v>
-      </c>
       <c r="U12" s="1" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="V12" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="W12" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="X12" s="1" t="n">
         <v>3</v>
@@ -3525,62 +3525,62 @@
         <v>1</v>
       </c>
       <c r="Z12" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AA12" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AB12" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E13" s="1" t="n">
         <v>24</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G13" s="1" t="n">
         <v>27</v>
       </c>
       <c r="H13" s="1" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I13" s="1" t="n">
         <v>6</v>
       </c>
       <c r="J13" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K13" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L13" s="1" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="M13" s="1" t="n">
         <v>22</v>
       </c>
       <c r="N13" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O13" s="1" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="P13" s="1" t="n">
         <v>26</v>
@@ -3589,86 +3589,86 @@
         <v>25</v>
       </c>
       <c r="R13" s="1" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="S13" s="1" t="n">
         <v>5</v>
       </c>
       <c r="T13" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="U13" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="V13" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="V13" s="1" t="n">
-        <v>13</v>
-      </c>
       <c r="W13" s="1" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="X13" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y13" s="1" t="n">
         <v>1</v>
       </c>
       <c r="Z13" s="1" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AA13" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AB13" s="1" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D14" s="1" t="n">
         <v>21</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G14" s="1" t="n">
         <v>27</v>
       </c>
       <c r="H14" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I14" s="1" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J14" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K14" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M14" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N14" s="1" t="n">
         <v>12</v>
       </c>
       <c r="O14" s="1" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="P14" s="1" t="n">
         <v>26</v>
@@ -3677,110 +3677,110 @@
         <v>25</v>
       </c>
       <c r="R14" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="S14" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T14" s="1" t="n">
         <v>20</v>
       </c>
       <c r="U14" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="V14" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="V14" s="1" t="n">
-        <v>11</v>
-      </c>
       <c r="W14" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="X14" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y14" s="1" t="n">
         <v>1</v>
       </c>
       <c r="Z14" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA14" s="1" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AB14" s="1" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="C15" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="C15" s="1" t="n">
-        <v>16</v>
-      </c>
       <c r="D15" s="1" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G15" s="1" t="n">
         <v>27</v>
       </c>
       <c r="H15" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I15" s="1" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J15" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K15" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L15" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M15" s="1" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N15" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="O15" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="P15" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q15" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="R15" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="S15" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="T15" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="U15" s="1" t="n">
         <v>13</v>
-      </c>
-      <c r="O15" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="P15" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="Q15" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="R15" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="S15" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="T15" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="U15" s="1" t="n">
-        <v>14</v>
       </c>
       <c r="V15" s="1" t="n">
         <v>11</v>
       </c>
       <c r="W15" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="X15" s="1" t="n">
         <v>3</v>
@@ -3789,29 +3789,29 @@
         <v>1</v>
       </c>
       <c r="Z15" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA15" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="AB15" s="1" t="n">
         <v>9</v>
-      </c>
-      <c r="AA15" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="AB15" s="1" t="n">
-        <v>10</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="C16" s="1" t="n">
         <v>16</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E16" s="1" t="n">
         <v>23</v>
@@ -3829,46 +3829,46 @@
         <v>7</v>
       </c>
       <c r="J16" s="1" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="K16" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L16" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M16" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N16" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O16" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="P16" s="1" t="n">
         <v>25</v>
-      </c>
-      <c r="P16" s="1" t="n">
-        <v>26</v>
       </c>
       <c r="Q16" s="1" t="n">
         <v>24</v>
       </c>
       <c r="R16" s="1" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="S16" s="1" t="n">
         <v>5</v>
       </c>
       <c r="T16" s="1" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="U16" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="V16" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="W16" s="1" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="X16" s="1" t="n">
         <v>3</v>
@@ -3877,10 +3877,10 @@
         <v>1</v>
       </c>
       <c r="Z16" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA16" s="1" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AB16" s="1" t="n">
         <v>10</v>
@@ -3889,59 +3889,59 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F17" s="1" t="n">
         <v>6</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H17" s="1" t="n">
         <v>4</v>
       </c>
       <c r="I17" s="1" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J17" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K17" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L17" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M17" s="1" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N17" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="O17" s="1" t="n">
         <v>25</v>
       </c>
       <c r="P17" s="1" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Q17" s="1" t="n">
         <v>24</v>
       </c>
       <c r="R17" s="1" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="S17" s="1" t="n">
         <v>5</v>
@@ -3953,10 +3953,10 @@
         <v>13</v>
       </c>
       <c r="V17" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="W17" s="1" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="X17" s="1" t="n">
         <v>3</v>
@@ -3965,35 +3965,35 @@
         <v>1</v>
       </c>
       <c r="Z17" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA17" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AB17" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="C18" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="C18" s="1" t="n">
-        <v>10</v>
-      </c>
       <c r="D18" s="1" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F18" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G18" s="1" t="n">
         <v>26</v>
@@ -4002,22 +4002,22 @@
         <v>4</v>
       </c>
       <c r="I18" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J18" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K18" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L18" s="1" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M18" s="1" t="n">
         <v>23</v>
       </c>
       <c r="N18" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O18" s="1" t="n">
         <v>25</v>
@@ -4029,22 +4029,22 @@
         <v>24</v>
       </c>
       <c r="R18" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="S18" s="1" t="n">
         <v>5</v>
       </c>
       <c r="T18" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="U18" s="1" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="V18" s="1" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="W18" s="1" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="X18" s="1" t="n">
         <v>3</v>
@@ -4056,32 +4056,32 @@
         <v>7</v>
       </c>
       <c r="AA18" s="1" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="AB18" s="1" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F19" s="1" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G19" s="1" t="n">
         <v>26</v>
@@ -4090,49 +4090,49 @@
         <v>4</v>
       </c>
       <c r="I19" s="1" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="J19" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K19" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L19" s="1" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="M19" s="1" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="N19" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O19" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="P19" s="1" t="n">
         <v>27</v>
       </c>
       <c r="Q19" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R19" s="1" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="S19" s="1" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T19" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="U19" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="V19" s="1" t="n">
         <v>18</v>
       </c>
       <c r="W19" s="1" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="X19" s="1" t="n">
         <v>3</v>
@@ -4141,19 +4141,19 @@
         <v>1</v>
       </c>
       <c r="Z19" s="1" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AA19" s="1" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AB19" s="1" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
@@ -4163,7 +4163,7 @@
         <v>11</v>
       </c>
       <c r="D20" s="1" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E20" s="1" t="n">
         <v>16</v>
@@ -4172,7 +4172,7 @@
         <v>6</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H20" s="1" t="n">
         <v>4</v>
@@ -4187,40 +4187,40 @@
         <v>2</v>
       </c>
       <c r="L20" s="1" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="M20" s="1" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="N20" s="1" t="n">
         <v>14</v>
       </c>
       <c r="O20" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P20" s="1" t="n">
         <v>27</v>
       </c>
       <c r="Q20" s="1" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="R20" s="1" t="n">
         <v>19</v>
       </c>
       <c r="S20" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T20" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="U20" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="V20" s="1" t="n">
         <v>18</v>
       </c>
       <c r="W20" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="X20" s="1" t="n">
         <v>3</v>
@@ -4229,10 +4229,10 @@
         <v>1</v>
       </c>
       <c r="Z20" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA20" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AB20" s="1" t="n">
         <v>7</v>
@@ -4241,29 +4241,29 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D21" s="1" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F21" s="1" t="n">
         <v>6</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H21" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I21" s="1" t="n">
         <v>5</v>
@@ -4275,16 +4275,16 @@
         <v>2</v>
       </c>
       <c r="L21" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M21" s="1" t="n">
         <v>22</v>
       </c>
       <c r="N21" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="O21" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="P21" s="1" t="n">
         <v>27</v>
@@ -4293,34 +4293,34 @@
         <v>26</v>
       </c>
       <c r="R21" s="1" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="S21" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T21" s="1" t="n">
         <v>21</v>
       </c>
       <c r="U21" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="V21" s="1" t="n">
         <v>18</v>
-      </c>
-      <c r="V21" s="1" t="n">
-        <v>15</v>
       </c>
       <c r="W21" s="1" t="n">
         <v>20</v>
       </c>
       <c r="X21" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y21" s="1" t="n">
         <v>1</v>
       </c>
       <c r="Z21" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA21" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AB21" s="1" t="n">
         <v>7</v>
@@ -4329,7 +4329,7 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
@@ -4339,22 +4339,22 @@
         <v>10</v>
       </c>
       <c r="D22" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F22" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="G22" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="H22" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="G22" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="H22" s="1" t="n">
+      <c r="I22" s="1" t="n">
         <v>5</v>
-      </c>
-      <c r="I22" s="1" t="n">
-        <v>6</v>
       </c>
       <c r="J22" s="1" t="n">
         <v>23</v>
@@ -4363,37 +4363,37 @@
         <v>2</v>
       </c>
       <c r="L22" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M22" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="N22" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="O22" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="P22" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q22" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="R22" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="S22" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="T22" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="N22" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="O22" s="1" t="n">
-        <v>27</v>
-      </c>
-      <c r="P22" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="Q22" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="R22" s="1" t="n">
+      <c r="U22" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="S22" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="T22" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="U22" s="1" t="n">
+      <c r="V22" s="1" t="n">
         <v>15</v>
-      </c>
-      <c r="V22" s="1" t="n">
-        <v>17</v>
       </c>
       <c r="W22" s="1" t="n">
         <v>20</v>
@@ -4405,7 +4405,7 @@
         <v>1</v>
       </c>
       <c r="Z22" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA22" s="1" t="n">
         <v>16</v>
@@ -4417,77 +4417,77 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D23" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="E23" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="E23" s="1" t="n">
-        <v>14</v>
-      </c>
       <c r="F23" s="1" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G23" s="1" t="n">
         <v>24</v>
       </c>
       <c r="H23" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I23" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J23" s="1" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="K23" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L23" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="M23" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="N23" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="O23" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="P23" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q23" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="R23" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="S23" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="T23" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="U23" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="V23" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="M23" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="N23" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="O23" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="P23" s="1" t="n">
-        <v>27</v>
-      </c>
-      <c r="Q23" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="R23" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="S23" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="T23" s="1" t="n">
-        <v>23</v>
-      </c>
-      <c r="U23" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="V23" s="1" t="n">
-        <v>16</v>
-      </c>
       <c r="W23" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="X23" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y23" s="1" t="n">
         <v>1</v>
@@ -4496,26 +4496,26 @@
         <v>8</v>
       </c>
       <c r="AA23" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AB23" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="C24" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="C24" s="1" t="n">
-        <v>10</v>
-      </c>
       <c r="D24" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E24" s="1" t="n">
         <v>14</v>
@@ -4533,34 +4533,34 @@
         <v>7</v>
       </c>
       <c r="J24" s="1" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K24" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L24" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M24" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N24" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="O24" s="1" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P24" s="1" t="n">
         <v>27</v>
       </c>
       <c r="Q24" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="R24" s="1" t="n">
         <v>19</v>
       </c>
       <c r="S24" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T24" s="1" t="n">
         <v>23</v>
@@ -4572,7 +4572,7 @@
         <v>16</v>
       </c>
       <c r="W24" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="X24" s="1" t="n">
         <v>3</v>
@@ -4581,47 +4581,47 @@
         <v>1</v>
       </c>
       <c r="Z24" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA24" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="AB24" s="1" t="n">
         <v>6</v>
-      </c>
-      <c r="AA24" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="AB24" s="1" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
         <v>11</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D25" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="E25" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="E25" s="1" t="n">
-        <v>12</v>
-      </c>
       <c r="F25" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G25" s="1" t="n">
         <v>24</v>
       </c>
       <c r="H25" s="1" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I25" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J25" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K25" s="1" t="n">
         <v>2</v>
@@ -4630,7 +4630,7 @@
         <v>15</v>
       </c>
       <c r="M25" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N25" s="1" t="n">
         <v>13</v>
@@ -4648,7 +4648,7 @@
         <v>19</v>
       </c>
       <c r="S25" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T25" s="1" t="n">
         <v>23</v>
@@ -4657,7 +4657,7 @@
         <v>18</v>
       </c>
       <c r="V25" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="W25" s="1" t="n">
         <v>20</v>
@@ -4669,32 +4669,32 @@
         <v>1</v>
       </c>
       <c r="Z25" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA25" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AB25" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C26" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="D26" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="E26" s="1" t="n">
         <v>12</v>
-      </c>
-      <c r="D26" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="E26" s="1" t="n">
-        <v>13</v>
       </c>
       <c r="F26" s="1" t="n">
         <v>4</v>
@@ -4703,10 +4703,10 @@
         <v>24</v>
       </c>
       <c r="H26" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I26" s="1" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J26" s="1" t="n">
         <v>21</v>
@@ -4715,40 +4715,40 @@
         <v>2</v>
       </c>
       <c r="L26" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="M26" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="N26" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="O26" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="P26" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q26" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="R26" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="S26" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="U26" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="M26" s="1" t="n">
+      <c r="V26" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="W26" s="1" t="n">
         <v>20</v>
-      </c>
-      <c r="N26" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="O26" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="P26" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="Q26" s="1" t="n">
-        <v>27</v>
-      </c>
-      <c r="R26" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="S26" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="T26" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="U26" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="V26" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="W26" s="1" t="n">
-        <v>23</v>
       </c>
       <c r="X26" s="1" t="n">
         <v>3</v>
@@ -4757,38 +4757,38 @@
         <v>1</v>
       </c>
       <c r="Z26" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA26" s="1" t="n">
         <v>16</v>
       </c>
       <c r="AB26" s="1" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C27" s="1" t="n">
         <v>12</v>
       </c>
       <c r="D27" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F27" s="1" t="n">
         <v>4</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H27" s="1" t="n">
         <v>7</v>
@@ -4797,7 +4797,7 @@
         <v>11</v>
       </c>
       <c r="J27" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K27" s="1" t="n">
         <v>2</v>
@@ -4806,25 +4806,25 @@
         <v>18</v>
       </c>
       <c r="M27" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="N27" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="O27" s="1" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="P27" s="1" t="n">
         <v>26</v>
       </c>
       <c r="Q27" s="1" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="R27" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="S27" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T27" s="1" t="n">
         <v>22</v>
@@ -4833,7 +4833,7 @@
         <v>19</v>
       </c>
       <c r="V27" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="W27" s="1" t="n">
         <v>23</v>
@@ -4848,7 +4848,7 @@
         <v>6</v>
       </c>
       <c r="AA27" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AB27" s="1" t="n">
         <v>5</v>
@@ -4857,47 +4857,47 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C28" s="1" t="n">
         <v>12</v>
       </c>
       <c r="D28" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="E28" s="1" t="n">
         <v>15</v>
-      </c>
-      <c r="E28" s="1" t="n">
-        <v>10</v>
       </c>
       <c r="F28" s="1" t="n">
         <v>4</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H28" s="1" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I28" s="1" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J28" s="1" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K28" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L28" s="1" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M28" s="1" t="n">
         <v>21</v>
       </c>
       <c r="N28" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O28" s="1" t="n">
         <v>27</v>
@@ -4906,59 +4906,59 @@
         <v>26</v>
       </c>
       <c r="Q28" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R28" s="1" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="S28" s="1" t="n">
         <v>8</v>
       </c>
       <c r="T28" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="U28" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="V28" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="W28" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="U28" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="V28" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="W28" s="1" t="n">
+      <c r="X28" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y28" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="X28" s="1" t="n">
+      <c r="Z28" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA28" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="AB28" s="1" t="n">
         <v>5</v>
-      </c>
-      <c r="Y28" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z28" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA28" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="AB28" s="1" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
         <v>13</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D29" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F29" s="1" t="n">
         <v>4</v>
@@ -4967,13 +4967,13 @@
         <v>24</v>
       </c>
       <c r="H29" s="1" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I29" s="1" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="J29" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K29" s="1" t="n">
         <v>3</v>
@@ -4997,25 +4997,25 @@
         <v>25</v>
       </c>
       <c r="R29" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="S29" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="T29" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="U29" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="V29" s="1" t="n">
         <v>16</v>
-      </c>
-      <c r="S29" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="T29" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="U29" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="V29" s="1" t="n">
-        <v>15</v>
       </c>
       <c r="W29" s="1" t="n">
         <v>1</v>
       </c>
       <c r="X29" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y29" s="1" t="n">
         <v>2</v>
@@ -5024,26 +5024,26 @@
         <v>7</v>
       </c>
       <c r="AA29" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AB29" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D30" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E30" s="1" t="n">
         <v>9</v>
@@ -5052,22 +5052,22 @@
         <v>4</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H30" s="1" t="n">
         <v>12</v>
       </c>
       <c r="I30" s="1" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J30" s="1" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K30" s="1" t="n">
         <v>3</v>
       </c>
       <c r="L30" s="1" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="M30" s="1" t="n">
         <v>21</v>
@@ -5079,25 +5079,25 @@
         <v>27</v>
       </c>
       <c r="P30" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q30" s="1" t="n">
         <v>25</v>
-      </c>
-      <c r="Q30" s="1" t="n">
-        <v>24</v>
       </c>
       <c r="R30" s="1" t="n">
         <v>16</v>
       </c>
       <c r="S30" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T30" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="U30" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="V30" s="1" t="n">
         <v>15</v>
-      </c>
-      <c r="V30" s="1" t="n">
-        <v>14</v>
       </c>
       <c r="W30" s="1" t="n">
         <v>1</v>
@@ -5121,38 +5121,38 @@
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C31" s="1" t="n">
         <v>10</v>
       </c>
       <c r="D31" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E31" s="1" t="n">
         <v>9</v>
       </c>
       <c r="F31" s="1" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H31" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I31" s="1" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J31" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K31" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L31" s="1" t="n">
         <v>20</v>
@@ -5164,37 +5164,37 @@
         <v>11</v>
       </c>
       <c r="O31" s="1" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P31" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q31" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="Q31" s="1" t="n">
-        <v>25</v>
-      </c>
       <c r="R31" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="S31" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="T31" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="U31" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="V31" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="S31" s="1" t="n">
+      <c r="W31" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="X31" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="T31" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="U31" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="V31" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="W31" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="X31" s="1" t="n">
-        <v>8</v>
-      </c>
       <c r="Y31" s="1" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Z31" s="1" t="n">
         <v>7</v>
@@ -5209,20 +5209,20 @@
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="C32" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="C32" s="1" t="n">
-        <v>11</v>
-      </c>
       <c r="D32" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F32" s="1" t="n">
         <v>2</v>
@@ -5231,10 +5231,10 @@
         <v>27</v>
       </c>
       <c r="H32" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I32" s="1" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J32" s="1" t="n">
         <v>23</v>
@@ -5249,7 +5249,7 @@
         <v>21</v>
       </c>
       <c r="N32" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="O32" s="1" t="n">
         <v>26</v>
@@ -5261,10 +5261,10 @@
         <v>25</v>
       </c>
       <c r="R32" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S32" s="1" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T32" s="1" t="n">
         <v>22</v>
@@ -5273,13 +5273,13 @@
         <v>16</v>
       </c>
       <c r="V32" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="W32" s="1" t="n">
         <v>3</v>
       </c>
       <c r="X32" s="1" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y32" s="1" t="n">
         <v>4</v>
@@ -5297,38 +5297,38 @@
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D33" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="E33" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="F33" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G33" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="H33" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="I33" s="1" t="n">
         <v>19</v>
-      </c>
-      <c r="E33" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="F33" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="G33" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="H33" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="I33" s="1" t="n">
-        <v>18</v>
       </c>
       <c r="J33" s="1" t="n">
         <v>23</v>
       </c>
       <c r="K33" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L33" s="1" t="n">
         <v>20</v>
@@ -5337,10 +5337,10 @@
         <v>21</v>
       </c>
       <c r="N33" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="O33" s="1" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P33" s="1" t="n">
         <v>24</v>
@@ -5349,7 +5349,7 @@
         <v>25</v>
       </c>
       <c r="R33" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="S33" s="1" t="n">
         <v>9</v>
@@ -5358,25 +5358,25 @@
         <v>22</v>
       </c>
       <c r="U33" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="V33" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="W33" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X33" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y33" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="Y33" s="1" t="n">
-        <v>2</v>
-      </c>
       <c r="Z33" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA33" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AB33" s="1" t="n">
         <v>5</v>
@@ -5385,41 +5385,41 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C34" s="1" t="n">
         <v>12</v>
       </c>
       <c r="D34" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F34" s="1" t="n">
         <v>7</v>
       </c>
       <c r="G34" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="H34" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="I34" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="J34" s="1" t="n">
         <v>23</v>
-      </c>
-      <c r="H34" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="I34" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="J34" s="1" t="n">
-        <v>24</v>
       </c>
       <c r="K34" s="1" t="n">
         <v>3</v>
       </c>
       <c r="L34" s="1" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M34" s="1" t="n">
         <v>21</v>
@@ -5431,25 +5431,25 @@
         <v>27</v>
       </c>
       <c r="P34" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q34" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="Q34" s="1" t="n">
-        <v>26</v>
-      </c>
       <c r="R34" s="1" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="S34" s="1" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="T34" s="1" t="n">
         <v>22</v>
       </c>
       <c r="U34" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="V34" s="1" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="W34" s="1" t="n">
         <v>1</v>
@@ -5464,50 +5464,50 @@
         <v>8</v>
       </c>
       <c r="AA34" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AB34" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="C35" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D35" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="E35" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="F35" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C35" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="D35" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="E35" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="F35" s="1" t="n">
-        <v>5</v>
-      </c>
       <c r="G35" s="1" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="H35" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I35" s="1" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J35" s="1" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K35" s="1" t="n">
         <v>3</v>
       </c>
       <c r="L35" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M35" s="1" t="n">
         <v>21</v>
@@ -5519,25 +5519,25 @@
         <v>27</v>
       </c>
       <c r="P35" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Q35" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="R35" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="S35" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="S35" s="1" t="n">
-        <v>19</v>
-      </c>
       <c r="T35" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="U35" s="1" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="V35" s="1" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="W35" s="1" t="n">
         <v>1</v>
@@ -5549,10 +5549,10 @@
         <v>2</v>
       </c>
       <c r="Z35" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA35" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AB35" s="1" t="n">
         <v>6</v>
@@ -5561,20 +5561,20 @@
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B36" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C36" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="D36" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="D36" s="1" t="n">
-        <v>20</v>
-      </c>
       <c r="E36" s="1" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F36" s="1" t="n">
         <v>5</v>
@@ -5583,10 +5583,10 @@
         <v>26</v>
       </c>
       <c r="H36" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I36" s="1" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J36" s="1" t="n">
         <v>22</v>
@@ -5595,34 +5595,34 @@
         <v>3</v>
       </c>
       <c r="L36" s="1" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M36" s="1" t="n">
         <v>21</v>
       </c>
       <c r="N36" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="O36" s="1" t="n">
         <v>27</v>
       </c>
       <c r="P36" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q36" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="Q36" s="1" t="n">
-        <v>24</v>
-      </c>
       <c r="R36" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="S36" s="1" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="T36" s="1" t="n">
         <v>23</v>
       </c>
       <c r="U36" s="1" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="V36" s="1" t="n">
         <v>17</v>
@@ -5637,10 +5637,10 @@
         <v>2</v>
       </c>
       <c r="Z36" s="1" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AA36" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AB36" s="1" t="n">
         <v>6</v>
@@ -5649,44 +5649,44 @@
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B37" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D37" s="1" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F37" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G37" s="1" t="n">
         <v>26</v>
       </c>
       <c r="H37" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I37" s="1" t="n">
         <v>10</v>
       </c>
       <c r="J37" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K37" s="1" t="n">
         <v>3</v>
       </c>
       <c r="L37" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M37" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N37" s="1" t="n">
         <v>11</v>
@@ -5701,10 +5701,10 @@
         <v>24</v>
       </c>
       <c r="R37" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="S37" s="1" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="T37" s="1" t="n">
         <v>23</v>
@@ -5713,13 +5713,13 @@
         <v>18</v>
       </c>
       <c r="V37" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="W37" s="1" t="n">
         <v>1</v>
       </c>
       <c r="X37" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y37" s="1" t="n">
         <v>2</v>
@@ -5728,7 +5728,7 @@
         <v>7</v>
       </c>
       <c r="AA37" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AB37" s="1" t="n">
         <v>6</v>
@@ -5737,38 +5737,38 @@
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B38" s="1" t="n">
         <v>9</v>
       </c>
       <c r="C38" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D38" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="E38" s="1" t="n">
         <v>13</v>
-      </c>
-      <c r="D38" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="E38" s="1" t="n">
-        <v>11</v>
       </c>
       <c r="F38" s="1" t="n">
         <v>4</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H38" s="1" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I38" s="1" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J38" s="1" t="n">
         <v>21</v>
       </c>
       <c r="K38" s="1" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="L38" s="1" t="n">
         <v>20</v>
@@ -5777,28 +5777,28 @@
         <v>22</v>
       </c>
       <c r="N38" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="O38" s="1" t="n">
         <v>27</v>
       </c>
       <c r="P38" s="1" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Q38" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R38" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="S38" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="T38" s="1" t="n">
         <v>23</v>
       </c>
       <c r="U38" s="1" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="V38" s="1" t="n">
         <v>15</v>
@@ -5813,10 +5813,10 @@
         <v>2</v>
       </c>
       <c r="Z38" s="1" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AA38" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AB38" s="1" t="n">
         <v>6</v>
@@ -5825,47 +5825,47 @@
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B39" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C39" s="1" t="n">
         <v>13</v>
       </c>
       <c r="D39" s="1" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="F39" s="1" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H39" s="1" t="n">
         <v>3</v>
       </c>
       <c r="I39" s="1" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J39" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="K39" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="L39" s="1" t="n">
         <v>20</v>
-      </c>
-      <c r="K39" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="L39" s="1" t="n">
-        <v>18</v>
       </c>
       <c r="M39" s="1" t="n">
         <v>22</v>
       </c>
       <c r="N39" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O39" s="1" t="n">
         <v>27</v>
@@ -5877,25 +5877,25 @@
         <v>25</v>
       </c>
       <c r="R39" s="1" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="S39" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="T39" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="U39" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="T39" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="U39" s="1" t="n">
-        <v>12</v>
-      </c>
       <c r="V39" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="W39" s="1" t="n">
         <v>1</v>
       </c>
       <c r="X39" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y39" s="1" t="n">
         <v>2</v>
@@ -5913,44 +5913,44 @@
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B40" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D40" s="1" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F40" s="1" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G40" s="1" t="n">
         <v>23</v>
       </c>
       <c r="H40" s="1" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I40" s="1" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J40" s="1" t="n">
         <v>20</v>
       </c>
       <c r="K40" s="1" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L40" s="1" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="M40" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N40" s="1" t="n">
         <v>11</v>
@@ -5962,86 +5962,86 @@
         <v>26</v>
       </c>
       <c r="Q40" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="R40" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="S40" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="T40" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="R40" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="S40" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="T40" s="1" t="n">
-        <v>25</v>
-      </c>
       <c r="U40" s="1" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="V40" s="1" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="W40" s="1" t="n">
         <v>1</v>
       </c>
       <c r="X40" s="1" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Y40" s="1" t="n">
         <v>2</v>
       </c>
       <c r="Z40" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA40" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AB40" s="1" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B41" s="1" t="n">
         <v>10</v>
       </c>
       <c r="C41" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="D41" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="D41" s="1" t="n">
-        <v>11</v>
-      </c>
       <c r="E41" s="1" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F41" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G41" s="1" t="n">
         <v>23</v>
       </c>
       <c r="H41" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="I41" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="J41" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="K41" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="I41" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="J41" s="1" t="n">
+      <c r="L41" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="M41" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="K41" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="L41" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="M41" s="1" t="n">
-        <v>22</v>
-      </c>
       <c r="N41" s="1" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="O41" s="1" t="n">
         <v>27</v>
@@ -6053,7 +6053,7 @@
         <v>24</v>
       </c>
       <c r="R41" s="1" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="S41" s="1" t="n">
         <v>19</v>
@@ -6062,16 +6062,16 @@
         <v>25</v>
       </c>
       <c r="U41" s="1" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="V41" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="W41" s="1" t="n">
         <v>1</v>
       </c>
       <c r="X41" s="1" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Y41" s="1" t="n">
         <v>2</v>
@@ -6080,23 +6080,23 @@
         <v>9</v>
       </c>
       <c r="AA41" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AB41" s="1" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B42" s="1" t="n">
         <v>10</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D42" s="1" t="n">
         <v>11</v>
@@ -6105,7 +6105,7 @@
         <v>20</v>
       </c>
       <c r="F42" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G42" s="1" t="n">
         <v>23</v>
@@ -6117,19 +6117,19 @@
         <v>7</v>
       </c>
       <c r="J42" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K42" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L42" s="1" t="n">
         <v>13</v>
       </c>
       <c r="M42" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N42" s="1" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="O42" s="1" t="n">
         <v>27</v>
@@ -6141,19 +6141,19 @@
         <v>24</v>
       </c>
       <c r="R42" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="S42" s="1" t="n">
         <v>19</v>
-      </c>
-      <c r="S42" s="1" t="n">
-        <v>18</v>
       </c>
       <c r="T42" s="1" t="n">
         <v>25</v>
       </c>
       <c r="U42" s="1" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="V42" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="W42" s="1" t="n">
         <v>1</v>
@@ -6168,7 +6168,7 @@
         <v>9</v>
       </c>
       <c r="AA42" s="1" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AB42" s="1" t="n">
         <v>8</v>
@@ -6177,44 +6177,44 @@
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B43" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="C43" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="C43" s="1" t="n">
-        <v>16</v>
-      </c>
       <c r="D43" s="1" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F43" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G43" s="1" t="n">
         <v>23</v>
       </c>
       <c r="H43" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I43" s="1" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J43" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="K43" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="L43" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="M43" s="1" t="n">
         <v>21</v>
-      </c>
-      <c r="K43" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="L43" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="M43" s="1" t="n">
-        <v>20</v>
       </c>
       <c r="N43" s="1" t="n">
         <v>12</v>
@@ -6238,19 +6238,19 @@
         <v>25</v>
       </c>
       <c r="U43" s="1" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="V43" s="1" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="W43" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="X43" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="X43" s="1" t="n">
-        <v>7</v>
-      </c>
       <c r="Y43" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Z43" s="1" t="n">
         <v>9</v>
@@ -6265,23 +6265,23 @@
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B44" s="1" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C44" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="D44" s="1" t="n">
         <v>14</v>
-      </c>
-      <c r="D44" s="1" t="n">
-        <v>13</v>
       </c>
       <c r="E44" s="1" t="n">
         <v>22</v>
       </c>
       <c r="F44" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G44" s="1" t="n">
         <v>23</v>
@@ -6293,16 +6293,16 @@
         <v>3</v>
       </c>
       <c r="J44" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K44" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L44" s="1" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="M44" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="N44" s="1" t="n">
         <v>12</v>
@@ -6317,47 +6317,47 @@
         <v>24</v>
       </c>
       <c r="R44" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="S44" s="1" t="n">
         <v>18</v>
-      </c>
-      <c r="S44" s="1" t="n">
-        <v>19</v>
       </c>
       <c r="T44" s="1" t="n">
         <v>25</v>
       </c>
       <c r="U44" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="V44" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="W44" s="1" t="n">
         <v>4</v>
       </c>
       <c r="X44" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y44" s="1" t="n">
         <v>5</v>
       </c>
       <c r="Z44" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA44" s="1" t="n">
         <v>17</v>
       </c>
       <c r="AB44" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B45" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C45" s="1" t="n">
         <v>14</v>
@@ -6366,31 +6366,31 @@
         <v>13</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F45" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G45" s="1" t="n">
         <v>23</v>
       </c>
       <c r="H45" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I45" s="1" t="n">
         <v>3</v>
       </c>
       <c r="J45" s="1" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K45" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L45" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M45" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N45" s="1" t="n">
         <v>12</v>
@@ -6405,19 +6405,19 @@
         <v>24</v>
       </c>
       <c r="R45" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="S45" s="1" t="n">
         <v>19</v>
-      </c>
-      <c r="S45" s="1" t="n">
-        <v>18</v>
       </c>
       <c r="T45" s="1" t="n">
         <v>25</v>
       </c>
       <c r="U45" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="V45" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="W45" s="1" t="n">
         <v>4</v>
@@ -6429,10 +6429,10 @@
         <v>5</v>
       </c>
       <c r="Z45" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA45" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AB45" s="1" t="n">
         <v>9</v>
@@ -6441,26 +6441,26 @@
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B46" s="1" t="n">
         <v>11</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D46" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F46" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H46" s="1" t="n">
         <v>2</v>
@@ -6469,13 +6469,13 @@
         <v>3</v>
       </c>
       <c r="J46" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K46" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L46" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M46" s="1" t="n">
         <v>20</v>
@@ -6490,16 +6490,16 @@
         <v>26</v>
       </c>
       <c r="Q46" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="R46" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="S46" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="T46" s="1" t="n">
         <v>25</v>
-      </c>
-      <c r="R46" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="S46" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="T46" s="1" t="n">
-        <v>24</v>
       </c>
       <c r="U46" s="1" t="n">
         <v>10</v>
@@ -6517,35 +6517,35 @@
         <v>5</v>
       </c>
       <c r="Z46" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA46" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="AB46" s="1" t="n">
         <v>9</v>
-      </c>
-      <c r="AA46" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="AB46" s="1" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B47" s="1" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D47" s="1" t="n">
         <v>14</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F47" s="1" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G47" s="1" t="n">
         <v>21</v>
@@ -6563,7 +6563,7 @@
         <v>1</v>
       </c>
       <c r="L47" s="1" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="M47" s="1" t="n">
         <v>20</v>
@@ -6575,56 +6575,56 @@
         <v>27</v>
       </c>
       <c r="P47" s="1" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="Q47" s="1" t="n">
         <v>25</v>
       </c>
       <c r="R47" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="S47" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="T47" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="U47" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="T47" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="U47" s="1" t="n">
+      <c r="V47" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="W47" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="V47" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="W47" s="1" t="n">
+      <c r="X47" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="X47" s="1" t="n">
-        <v>11</v>
-      </c>
       <c r="Y47" s="1" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Z47" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA47" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="AB47" s="1" t="n">
         <v>8</v>
-      </c>
-      <c r="AA47" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="AB47" s="1" t="n">
-        <v>9</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B48" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="C48" s="1" t="n">
         <v>17</v>
-      </c>
-      <c r="C48" s="1" t="n">
-        <v>15</v>
       </c>
       <c r="D48" s="1" t="n">
         <v>14</v>
@@ -6636,7 +6636,7 @@
         <v>5</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="H48" s="1" t="n">
         <v>2</v>
@@ -6645,25 +6645,25 @@
         <v>3</v>
       </c>
       <c r="J48" s="1" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K48" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L48" s="1" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="M48" s="1" t="n">
         <v>20</v>
       </c>
       <c r="N48" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="O48" s="1" t="n">
         <v>27</v>
       </c>
       <c r="P48" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q48" s="1" t="n">
         <v>25</v>
@@ -6672,47 +6672,47 @@
         <v>16</v>
       </c>
       <c r="S48" s="1" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T48" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="U48" s="1" t="n">
         <v>4</v>
       </c>
       <c r="V48" s="1" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="W48" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X48" s="1" t="n">
         <v>11</v>
       </c>
       <c r="Y48" s="1" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Z48" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA48" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="AB48" s="1" t="n">
         <v>9</v>
-      </c>
-      <c r="AA48" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="AB48" s="1" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B49" s="1" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D49" s="1" t="n">
         <v>14</v>
@@ -6733,34 +6733,34 @@
         <v>3</v>
       </c>
       <c r="J49" s="1" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K49" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L49" s="1" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M49" s="1" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="N49" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="O49" s="1" t="n">
         <v>27</v>
       </c>
       <c r="P49" s="1" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q49" s="1" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="R49" s="1" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="S49" s="1" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T49" s="1" t="n">
         <v>21</v>
@@ -6772,13 +6772,13 @@
         <v>12</v>
       </c>
       <c r="W49" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X49" s="1" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="Y49" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z49" s="1" t="n">
         <v>9</v>
@@ -6787,59 +6787,59 @@
         <v>19</v>
       </c>
       <c r="AB49" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B50" s="1" t="n">
         <v>25</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D50" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F50" s="1" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G50" s="1" t="n">
         <v>24</v>
       </c>
       <c r="H50" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I50" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="J50" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="K50" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="I50" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="J50" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="K50" s="1" t="n">
-        <v>3</v>
-      </c>
       <c r="L50" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M50" s="1" t="n">
         <v>18</v>
       </c>
       <c r="N50" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="O50" s="1" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P50" s="1" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="Q50" s="1" t="n">
         <v>23</v>
@@ -6848,56 +6848,56 @@
         <v>13</v>
       </c>
       <c r="S50" s="1" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T50" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="U50" s="1" t="n">
         <v>4</v>
       </c>
       <c r="V50" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="W50" s="1" t="n">
         <v>6</v>
       </c>
       <c r="X50" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Y50" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z50" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA50" s="1" t="n">
         <v>19</v>
       </c>
       <c r="AB50" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B51" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="C51" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="D51" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="E51" s="1" t="n">
         <v>27</v>
       </c>
-      <c r="C51" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="D51" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="E51" s="1" t="n">
-        <v>25</v>
-      </c>
       <c r="F51" s="1" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G51" s="1" t="n">
         <v>24</v>
@@ -6906,61 +6906,61 @@
         <v>1</v>
       </c>
       <c r="I51" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="J51" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="K51" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="J51" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="K51" s="1" t="n">
-        <v>2</v>
-      </c>
       <c r="L51" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M51" s="1" t="n">
         <v>18</v>
       </c>
       <c r="N51" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="O51" s="1" t="n">
         <v>26</v>
       </c>
       <c r="P51" s="1" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q51" s="1" t="n">
         <v>23</v>
       </c>
       <c r="R51" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="S51" s="1" t="n">
         <v>5</v>
       </c>
       <c r="T51" s="1" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="U51" s="1" t="n">
         <v>4</v>
       </c>
       <c r="V51" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="W51" s="1" t="n">
         <v>6</v>
       </c>
       <c r="X51" s="1" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="Y51" s="1" t="n">
         <v>7</v>
       </c>
       <c r="Z51" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA51" s="1" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AB51" s="1" t="n">
         <v>8</v>
@@ -6969,47 +6969,47 @@
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B52" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C52" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="D52" s="1" t="n">
         <v>13</v>
-      </c>
-      <c r="D52" s="1" t="n">
-        <v>6</v>
       </c>
       <c r="E52" s="1" t="n">
         <v>25</v>
       </c>
       <c r="F52" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H52" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I52" s="1" t="n">
         <v>3</v>
       </c>
       <c r="J52" s="1" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="K52" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L52" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M52" s="1" t="n">
         <v>18</v>
       </c>
       <c r="N52" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="O52" s="1" t="n">
         <v>26</v>
@@ -7027,53 +7027,53 @@
         <v>5</v>
       </c>
       <c r="T52" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="U52" s="1" t="n">
         <v>4</v>
       </c>
       <c r="V52" s="1" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="W52" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X52" s="1" t="n">
         <v>17</v>
       </c>
       <c r="Y52" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z52" s="1" t="n">
         <v>9</v>
       </c>
       <c r="AA52" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AB52" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B53" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C53" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="D53" s="1" t="n">
         <v>6</v>
-      </c>
-      <c r="D53" s="1" t="n">
-        <v>5</v>
       </c>
       <c r="E53" s="1" t="n">
         <v>25</v>
       </c>
       <c r="F53" s="1" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="G53" s="1" t="n">
         <v>22</v>
@@ -7097,22 +7097,22 @@
         <v>18</v>
       </c>
       <c r="N53" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="O53" s="1" t="n">
         <v>26</v>
       </c>
       <c r="P53" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Q53" s="1" t="n">
         <v>23</v>
       </c>
       <c r="R53" s="1" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="S53" s="1" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T53" s="1" t="n">
         <v>21</v>
@@ -7121,50 +7121,50 @@
         <v>4</v>
       </c>
       <c r="V53" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="W53" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X53" s="1" t="n">
         <v>17</v>
       </c>
       <c r="Y53" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z53" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="Z53" s="1" t="n">
+      <c r="AA53" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="AB53" s="1" t="n">
         <v>10</v>
-      </c>
-      <c r="AA53" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="AB53" s="1" t="n">
-        <v>11</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B54" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D54" s="1" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E54" s="1" t="n">
         <v>25</v>
       </c>
       <c r="F54" s="1" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H54" s="1" t="n">
         <v>2</v>
@@ -7182,7 +7182,7 @@
         <v>16</v>
       </c>
       <c r="M54" s="1" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N54" s="1" t="n">
         <v>14</v>
@@ -7191,68 +7191,68 @@
         <v>26</v>
       </c>
       <c r="P54" s="1" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="Q54" s="1" t="n">
         <v>23</v>
       </c>
       <c r="R54" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="S54" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="T54" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="U54" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="V54" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="W54" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="X54" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y54" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="S54" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="T54" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="U54" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="V54" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="W54" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="X54" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="Y54" s="1" t="n">
-        <v>5</v>
-      </c>
       <c r="Z54" s="1" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AA54" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AB54" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B55" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D55" s="1" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E55" s="1" t="n">
         <v>25</v>
       </c>
       <c r="F55" s="1" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H55" s="1" t="n">
         <v>2</v>
@@ -7261,25 +7261,25 @@
         <v>3</v>
       </c>
       <c r="J55" s="1" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K55" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L55" s="1" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="M55" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N55" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O55" s="1" t="n">
         <v>26</v>
       </c>
       <c r="P55" s="1" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="Q55" s="1" t="n">
         <v>23</v>
@@ -7288,31 +7288,31 @@
         <v>9</v>
       </c>
       <c r="S55" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="T55" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="U55" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="T55" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="U55" s="1" t="n">
-        <v>7</v>
-      </c>
       <c r="V55" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="W55" s="1" t="n">
         <v>4</v>
       </c>
       <c r="X55" s="1" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Y55" s="1" t="n">
         <v>5</v>
       </c>
       <c r="Z55" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA55" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AB55" s="1" t="n">
         <v>10</v>
@@ -7321,23 +7321,23 @@
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B56" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D56" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F56" s="1" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G56" s="1" t="n">
         <v>20</v>
@@ -7349,13 +7349,13 @@
         <v>3</v>
       </c>
       <c r="J56" s="1" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="K56" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L56" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="M56" s="1" t="n">
         <v>18</v>
@@ -7364,10 +7364,10 @@
         <v>15</v>
       </c>
       <c r="O56" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P56" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Q56" s="1" t="n">
         <v>23</v>
@@ -7382,25 +7382,25 @@
         <v>24</v>
       </c>
       <c r="U56" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V56" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="W56" s="1" t="n">
         <v>4</v>
       </c>
       <c r="X56" s="1" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Y56" s="1" t="n">
         <v>5</v>
       </c>
       <c r="Z56" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA56" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AB56" s="1" t="n">
         <v>10</v>
@@ -7409,26 +7409,26 @@
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B57" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C57" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="D57" s="1" t="n">
         <v>16</v>
-      </c>
-      <c r="D57" s="1" t="n">
-        <v>13</v>
       </c>
       <c r="E57" s="1" t="n">
         <v>26</v>
       </c>
       <c r="F57" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="G57" s="1" t="n">
         <v>20</v>
-      </c>
-      <c r="G57" s="1" t="n">
-        <v>22</v>
       </c>
       <c r="H57" s="1" t="n">
         <v>2</v>
@@ -7449,13 +7449,13 @@
         <v>18</v>
       </c>
       <c r="N57" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="O57" s="1" t="n">
         <v>25</v>
       </c>
       <c r="P57" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Q57" s="1" t="n">
         <v>23</v>
@@ -7473,7 +7473,7 @@
         <v>8</v>
       </c>
       <c r="V57" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="W57" s="1" t="n">
         <v>4</v>
@@ -7488,7 +7488,7 @@
         <v>7</v>
       </c>
       <c r="AA57" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AB57" s="1" t="n">
         <v>10</v>
@@ -7497,7 +7497,7 @@
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B58" s="1" t="n">
@@ -7507,16 +7507,16 @@
         <v>16</v>
       </c>
       <c r="D58" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F58" s="1" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H58" s="1" t="n">
         <v>2</v>
@@ -7534,22 +7534,22 @@
         <v>11</v>
       </c>
       <c r="M58" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="N58" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="N58" s="1" t="n">
-        <v>15</v>
-      </c>
       <c r="O58" s="1" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P58" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="Q58" s="1" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="R58" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="S58" s="1" t="n">
         <v>6</v>
@@ -7561,13 +7561,13 @@
         <v>8</v>
       </c>
       <c r="V58" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="W58" s="1" t="n">
         <v>4</v>
       </c>
       <c r="X58" s="1" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="Y58" s="1" t="n">
         <v>5</v>
@@ -7576,71 +7576,71 @@
         <v>7</v>
       </c>
       <c r="AA58" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AB58" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B59" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D59" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F59" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="G59" s="1" t="n">
         <v>20</v>
-      </c>
-      <c r="G59" s="1" t="n">
-        <v>17</v>
       </c>
       <c r="H59" s="1" t="n">
         <v>2</v>
       </c>
       <c r="I59" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J59" s="1" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K59" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L59" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="M59" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N59" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="O59" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="P59" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="O59" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="P59" s="1" t="n">
-        <v>11</v>
-      </c>
       <c r="Q59" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R59" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="S59" s="1" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T59" s="1" t="n">
         <v>24</v>
@@ -7652,132 +7652,132 @@
         <v>13</v>
       </c>
       <c r="W59" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="X59" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y59" s="1" t="n">
         <v>5</v>
-      </c>
-      <c r="X59" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="Y59" s="1" t="n">
-        <v>6</v>
       </c>
       <c r="Z59" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AA59" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AB59" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B60" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D60" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E60" s="1" t="n">
         <v>26</v>
       </c>
       <c r="F60" s="1" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H60" s="1" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I60" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J60" s="1" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="K60" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L60" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M60" s="1" t="n">
         <v>18</v>
       </c>
       <c r="N60" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O60" s="1" t="n">
         <v>25</v>
       </c>
       <c r="P60" s="1" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="Q60" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="R60" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="S60" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T60" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="U60" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V60" s="1" t="n">
         <v>13</v>
       </c>
       <c r="W60" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X60" s="1" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="Y60" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z60" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AA60" s="1" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AB60" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B61" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D61" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E61" s="1" t="n">
         <v>26</v>
       </c>
       <c r="F61" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G61" s="1" t="n">
         <v>20</v>
@@ -7786,7 +7786,7 @@
         <v>6</v>
       </c>
       <c r="I61" s="1" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J61" s="1" t="n">
         <v>19</v>
@@ -7807,10 +7807,10 @@
         <v>25</v>
       </c>
       <c r="P61" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Q61" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R61" s="1" t="n">
         <v>10</v>
@@ -7819,53 +7819,53 @@
         <v>2</v>
       </c>
       <c r="T61" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="U61" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="V61" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="W61" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="X61" s="1" t="n">
         <v>24</v>
-      </c>
-      <c r="U61" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="V61" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="W61" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="X61" s="1" t="n">
-        <v>23</v>
       </c>
       <c r="Y61" s="1" t="n">
         <v>5</v>
       </c>
       <c r="Z61" s="1" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AA61" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AB61" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B62" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D62" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E62" s="1" t="n">
         <v>26</v>
       </c>
       <c r="F62" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G62" s="1" t="n">
         <v>20</v>
@@ -7874,25 +7874,25 @@
         <v>6</v>
       </c>
       <c r="I62" s="1" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J62" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K62" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L62" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M62" s="1" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N62" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O62" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="P62" s="1" t="n">
         <v>17</v>
@@ -7901,31 +7901,31 @@
         <v>22</v>
       </c>
       <c r="R62" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="S62" s="1" t="n">
         <v>2</v>
       </c>
       <c r="T62" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="U62" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="V62" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="W62" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="X62" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="U62" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="V62" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="W62" s="1" t="n">
+      <c r="Y62" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z62" s="1" t="n">
         <v>4</v>
-      </c>
-      <c r="X62" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="Y62" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z62" s="1" t="n">
-        <v>5</v>
       </c>
       <c r="AA62" s="1" t="n">
         <v>21</v>
@@ -7937,32 +7937,32 @@
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B63" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D63" s="1" t="n">
         <v>11</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F63" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G63" s="1" t="n">
         <v>20</v>
       </c>
       <c r="H63" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="I63" s="1" t="n">
         <v>3</v>
-      </c>
-      <c r="I63" s="1" t="n">
-        <v>12</v>
       </c>
       <c r="J63" s="1" t="n">
         <v>18</v>
@@ -7971,13 +7971,13 @@
         <v>1</v>
       </c>
       <c r="L63" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M63" s="1" t="n">
         <v>19</v>
       </c>
       <c r="N63" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O63" s="1" t="n">
         <v>24</v>
@@ -7989,28 +7989,28 @@
         <v>22</v>
       </c>
       <c r="R63" s="1" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="S63" s="1" t="n">
         <v>2</v>
       </c>
       <c r="T63" s="1" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="U63" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V63" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="W63" s="1" t="n">
         <v>4</v>
       </c>
       <c r="X63" s="1" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Y63" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z63" s="1" t="n">
         <v>5</v>
@@ -8019,77 +8019,77 @@
         <v>21</v>
       </c>
       <c r="AB63" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B64" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C64" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="D64" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="D64" s="1" t="n">
-        <v>10</v>
-      </c>
       <c r="E64" s="1" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F64" s="1" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G64" s="1" t="n">
         <v>20</v>
       </c>
       <c r="H64" s="1" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="I64" s="1" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="J64" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K64" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L64" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M64" s="1" t="n">
         <v>19</v>
       </c>
       <c r="N64" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O64" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P64" s="1" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Q64" s="1" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="R64" s="1" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="S64" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T64" s="1" t="n">
         <v>26</v>
       </c>
       <c r="U64" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="V64" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="W64" s="1" t="n">
         <v>4</v>
@@ -8098,7 +8098,7 @@
         <v>23</v>
       </c>
       <c r="Y64" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z64" s="1" t="n">
         <v>5</v>
@@ -8107,62 +8107,62 @@
         <v>21</v>
       </c>
       <c r="AB64" s="1" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B65" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D65" s="1" t="n">
         <v>10</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F65" s="1" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="G65" s="1" t="n">
         <v>20</v>
       </c>
       <c r="H65" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I65" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J65" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K65" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L65" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M65" s="1" t="n">
         <v>19</v>
       </c>
       <c r="N65" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O65" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="P65" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q65" s="1" t="n">
         <v>24</v>
-      </c>
-      <c r="P65" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q65" s="1" t="n">
-        <v>21</v>
       </c>
       <c r="R65" s="1" t="n">
         <v>3</v>
@@ -8171,10 +8171,10 @@
         <v>1</v>
       </c>
       <c r="T65" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="U65" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V65" s="1" t="n">
         <v>12</v>
@@ -8183,7 +8183,7 @@
         <v>4</v>
       </c>
       <c r="X65" s="1" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="Y65" s="1" t="n">
         <v>6</v>
@@ -8192,50 +8192,50 @@
         <v>5</v>
       </c>
       <c r="AA65" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AB65" s="1" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B66" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D66" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F66" s="1" t="n">
         <v>18</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H66" s="1" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="I66" s="1" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="J66" s="1" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="K66" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L66" s="1" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="M66" s="1" t="n">
         <v>19</v>
@@ -8244,37 +8244,37 @@
         <v>17</v>
       </c>
       <c r="O66" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P66" s="1" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="Q66" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R66" s="1" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="S66" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T66" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="U66" s="1" t="n">
         <v>7</v>
       </c>
       <c r="V66" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="W66" s="1" t="n">
         <v>4</v>
       </c>
       <c r="X66" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Y66" s="1" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Z66" s="1" t="n">
         <v>5</v>
@@ -8289,7 +8289,7 @@
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B67" s="1" t="n">
@@ -8299,10 +8299,10 @@
         <v>16</v>
       </c>
       <c r="D67" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F67" s="1" t="n">
         <v>18</v>
@@ -8311,19 +8311,19 @@
         <v>21</v>
       </c>
       <c r="H67" s="1" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="I67" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J67" s="1" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K67" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L67" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M67" s="1" t="n">
         <v>19</v>
@@ -8341,13 +8341,13 @@
         <v>20</v>
       </c>
       <c r="R67" s="1" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="S67" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T67" s="1" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="U67" s="1" t="n">
         <v>7</v>
@@ -8356,22 +8356,22 @@
         <v>15</v>
       </c>
       <c r="W67" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X67" s="1" t="n">
         <v>25</v>
       </c>
       <c r="Y67" s="1" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="Z67" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA67" s="1" t="n">
         <v>22</v>
       </c>
       <c r="AB67" s="1" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/NSE_Sector_Monitor.xlsx
+++ b/NSE_Sector_Monitor.xlsx
@@ -552,46 +552,46 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Internet</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="B2" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>13.68</v>
+        <v>30.86</v>
       </c>
       <c r="H2" s="1" t="n">
-        <v>-1.79</v>
+        <v>-1.18</v>
       </c>
       <c r="I2" s="1" t="n">
-        <v>-5.75</v>
+        <v>1.9</v>
       </c>
       <c r="J2" s="1" t="n">
-        <v>-0.78</v>
+        <v>-6.2</v>
       </c>
       <c r="K2" s="1" t="n">
-        <v>13.24</v>
+        <v>12.87</v>
       </c>
       <c r="L2" s="1" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Down</t>
         </is>
       </c>
       <c r="M2" s="1" t="n">
-        <v>-5.75</v>
+        <v>-24.95</v>
       </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
@@ -610,7 +610,7 @@
       </c>
       <c r="Q2" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -630,25 +630,25 @@
         <v>0</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>27.79</v>
+        <v>27.32</v>
       </c>
       <c r="H3" s="1" t="n">
-        <v>0.83</v>
+        <v>-1.69</v>
       </c>
       <c r="I3" s="1" t="n">
-        <v>3.55</v>
+        <v>1.79</v>
       </c>
       <c r="J3" s="1" t="n">
-        <v>6.84</v>
+        <v>4.94</v>
       </c>
       <c r="K3" s="1" t="n">
-        <v>11.04</v>
+        <v>10.75</v>
       </c>
       <c r="L3" s="1" t="inlineStr">
         <is>
@@ -656,16 +656,16 @@
         </is>
       </c>
       <c r="M3" s="1" t="n">
-        <v>0</v>
+        <v>-1.56</v>
       </c>
       <c r="N3" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O3" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P3" s="1" t="inlineStr">
@@ -682,38 +682,38 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Digital</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
         <v>3</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>30.8</v>
+        <v>82.98</v>
       </c>
       <c r="H4" s="1" t="n">
-        <v>-1.6</v>
+        <v>-1.83</v>
       </c>
       <c r="I4" s="1" t="n">
-        <v>-0.01</v>
+        <v>-2.9</v>
       </c>
       <c r="J4" s="1" t="n">
-        <v>-4.78</v>
+        <v>-4.14</v>
       </c>
       <c r="K4" s="1" t="n">
-        <v>9.75</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="L4" s="1" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
         </is>
       </c>
       <c r="M4" s="1" t="n">
-        <v>-25.19</v>
+        <v>-10.94</v>
       </c>
       <c r="N4" s="1" t="inlineStr">
         <is>
@@ -747,38 +747,38 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Digital</t>
+          <t>Internet</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
         <v>4</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>-1</v>
+        <v>-3</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>83.48999999999999</v>
+        <v>13.51</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>-2.58</v>
+        <v>-2.95</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>-2.81</v>
+        <v>-6.6</v>
       </c>
       <c r="J5" s="1" t="n">
-        <v>-2.97</v>
+        <v>-1.81</v>
       </c>
       <c r="K5" s="1" t="n">
-        <v>9.34</v>
+        <v>9.15</v>
       </c>
       <c r="L5" s="1" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="M5" s="1" t="n">
-        <v>-10.51</v>
+        <v>-6.8</v>
       </c>
       <c r="N5" s="1" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
       </c>
       <c r="Q5" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -819,31 +819,31 @@
         <v>5</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>18</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>13.02</v>
+        <v>12.89</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>-1.21</v>
+        <v>-0.15</v>
       </c>
       <c r="I6" s="1" t="n">
-        <v>2.9</v>
+        <v>0.4</v>
       </c>
       <c r="J6" s="1" t="n">
-        <v>3.64</v>
+        <v>3.03</v>
       </c>
       <c r="K6" s="1" t="n">
-        <v>7.86</v>
+        <v>8.58</v>
       </c>
       <c r="L6" s="1" t="inlineStr">
         <is>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="M6" s="1" t="n">
-        <v>-2.89</v>
+        <v>-3.73</v>
       </c>
       <c r="N6" s="1" t="inlineStr">
         <is>
@@ -884,31 +884,31 @@
         <v>6</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>-2</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>17.14</v>
+        <v>16.58</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>-0.17</v>
+        <v>-2.64</v>
       </c>
       <c r="I7" s="1" t="n">
-        <v>2.54</v>
+        <v>-0.76</v>
       </c>
       <c r="J7" s="1" t="n">
-        <v>5.67</v>
+        <v>2.35</v>
       </c>
       <c r="K7" s="1" t="n">
-        <v>7.37</v>
+        <v>5.09</v>
       </c>
       <c r="L7" s="1" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         </is>
       </c>
       <c r="M7" s="1" t="n">
-        <v>0</v>
+        <v>-2.51</v>
       </c>
       <c r="N7" s="1" t="inlineStr">
         <is>
@@ -925,12 +925,12 @@
       </c>
       <c r="O7" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P7" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Q7" s="1" t="inlineStr">
@@ -952,7 +952,7 @@
         <v>-3</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>-5</v>
@@ -961,27 +961,27 @@
         <v>-5</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>84.51000000000001</v>
+        <v>84.84999999999999</v>
       </c>
       <c r="H8" s="1" t="n">
-        <v>-2.94</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>1.26</v>
+        <v>1.06</v>
       </c>
       <c r="J8" s="1" t="n">
-        <v>-0.42</v>
+        <v>0.49</v>
       </c>
       <c r="K8" s="1" t="n">
-        <v>6.26</v>
+        <v>3.79</v>
       </c>
       <c r="L8" s="1" t="inlineStr">
         <is>
-          <t>Down</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="M8" s="1" t="n">
-        <v>-6.2</v>
+        <v>-5.7</v>
       </c>
       <c r="N8" s="1" t="inlineStr">
         <is>
@@ -1017,28 +1017,28 @@
         <v>-1</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>-5</v>
+        <v>-2</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>10</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>272.72</v>
+        <v>272.25</v>
       </c>
       <c r="H9" s="1" t="n">
-        <v>-2.08</v>
+        <v>-0.75</v>
       </c>
       <c r="I9" s="1" t="n">
-        <v>0.41</v>
+        <v>0.84</v>
       </c>
       <c r="J9" s="1" t="n">
-        <v>-3.15</v>
+        <v>-1.62</v>
       </c>
       <c r="K9" s="1" t="n">
-        <v>3.92</v>
+        <v>3.25</v>
       </c>
       <c r="L9" s="1" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="M9" s="1" t="n">
-        <v>-4.82</v>
+        <v>-4.86</v>
       </c>
       <c r="N9" s="1" t="inlineStr">
         <is>
@@ -1072,46 +1072,46 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Manufacturing</t>
+          <t>EV &amp; New Age Auto</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
         <v>9</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>4</v>
+        <v>-1</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>8</v>
+        <v>-2</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>158.6</v>
+        <v>30.59</v>
       </c>
       <c r="H10" s="1" t="n">
-        <v>-0.37</v>
+        <v>-1.13</v>
       </c>
       <c r="I10" s="1" t="n">
-        <v>1.19</v>
+        <v>0.91</v>
       </c>
       <c r="J10" s="1" t="n">
-        <v>0.4</v>
+        <v>-2.48</v>
       </c>
       <c r="K10" s="1" t="n">
-        <v>2.29</v>
+        <v>2.99</v>
       </c>
       <c r="L10" s="1" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Down</t>
         </is>
       </c>
       <c r="M10" s="1" t="n">
-        <v>-0.32</v>
+        <v>-4.45</v>
       </c>
       <c r="N10" s="1" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>Consumption</t>
+          <t>Manufacturing</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
@@ -1147,36 +1147,36 @@
         <v>0</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>125.07</v>
+        <v>157.7</v>
       </c>
       <c r="H11" s="1" t="n">
-        <v>-0.72</v>
+        <v>-0.57</v>
       </c>
       <c r="I11" s="1" t="n">
-        <v>0.59</v>
+        <v>0.53</v>
       </c>
       <c r="J11" s="1" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.18</v>
       </c>
       <c r="K11" s="1" t="n">
-        <v>1.79</v>
+        <v>2.19</v>
       </c>
       <c r="L11" s="1" t="inlineStr">
         <is>
-          <t>Down</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="M11" s="1" t="n">
-        <v>-4.82</v>
+        <v>-0.75</v>
       </c>
       <c r="N11" s="1" t="inlineStr">
         <is>
@@ -1202,46 +1202,46 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>EV &amp; New Age Auto</t>
+          <t>Defence</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
         <v>11</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>-2</v>
+        <v>3</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>-5</v>
+        <v>7</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-2</v>
+        <v>-10</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>30.28</v>
+        <v>101.86</v>
       </c>
       <c r="H12" s="1" t="n">
-        <v>-3.66</v>
+        <v>0.4</v>
       </c>
       <c r="I12" s="1" t="n">
-        <v>-0.57</v>
+        <v>2.01</v>
       </c>
       <c r="J12" s="1" t="n">
-        <v>-3.78</v>
+        <v>1.88</v>
       </c>
       <c r="K12" s="1" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="L12" s="1" t="inlineStr">
         <is>
-          <t>Down</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="M12" s="1" t="n">
-        <v>-5.54</v>
+        <v>-2.81</v>
       </c>
       <c r="N12" s="1" t="inlineStr">
         <is>
@@ -1260,45 +1260,45 @@
       </c>
       <c r="Q12" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>Defence</t>
+          <t>Services</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
         <v>12</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>-3</v>
+        <v>4</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-11</v>
+        <v>10</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>101.29</v>
+        <v>29.73</v>
       </c>
       <c r="H13" s="1" t="n">
-        <v>-1.74</v>
+        <v>1.68</v>
       </c>
       <c r="I13" s="1" t="n">
-        <v>0.63</v>
+        <v>1.69</v>
       </c>
       <c r="J13" s="1" t="n">
-        <v>0.83</v>
+        <v>2.17</v>
       </c>
       <c r="K13" s="1" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.15</v>
       </c>
       <c r="L13" s="1" t="inlineStr">
         <is>
@@ -1306,7 +1306,7 @@
         </is>
       </c>
       <c r="M13" s="1" t="n">
-        <v>-3.48</v>
+        <v>0</v>
       </c>
       <c r="N13" s="1" t="inlineStr">
         <is>
@@ -1325,53 +1325,53 @@
       </c>
       <c r="Q13" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
         <v>13</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>11</v>
+        <v>-6</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>10.8</v>
+        <v>28.37</v>
       </c>
       <c r="H14" s="1" t="n">
-        <v>-1.91</v>
+        <v>-1.29</v>
       </c>
       <c r="I14" s="1" t="n">
-        <v>0.17</v>
+        <v>-0.41</v>
       </c>
       <c r="J14" s="1" t="n">
-        <v>2.13</v>
+        <v>-0</v>
       </c>
       <c r="K14" s="1" t="n">
-        <v>0.24</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="L14" s="1" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Down</t>
         </is>
       </c>
       <c r="M14" s="1" t="n">
-        <v>-8.869999999999999</v>
+        <v>0</v>
       </c>
       <c r="N14" s="1" t="inlineStr">
         <is>
@@ -1397,46 +1397,46 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Oil &amp; Gas</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
         <v>14</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>-2</v>
+        <v>5</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-7</v>
+        <v>11</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>28.5</v>
+        <v>10.78</v>
       </c>
       <c r="H15" s="1" t="n">
-        <v>-3.19</v>
+        <v>-0.65</v>
       </c>
       <c r="I15" s="1" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="J15" s="1" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="K15" s="1" t="n">
         <v>0.42</v>
       </c>
-      <c r="J15" s="1" t="n">
-        <v>-1.14</v>
-      </c>
-      <c r="K15" s="1" t="n">
-        <v>0.15</v>
-      </c>
       <c r="L15" s="1" t="inlineStr">
         <is>
-          <t>Down</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="M15" s="1" t="n">
-        <v>0</v>
+        <v>-8.92</v>
       </c>
       <c r="N15" s="1" t="inlineStr">
         <is>
@@ -1462,46 +1462,46 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Commodities</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
         <v>15</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>29.32</v>
+        <v>95.31</v>
       </c>
       <c r="H16" s="1" t="n">
-        <v>-1.68</v>
+        <v>0.04</v>
       </c>
       <c r="I16" s="1" t="n">
-        <v>0.13</v>
+        <v>1.05</v>
       </c>
       <c r="J16" s="1" t="n">
-        <v>0.32</v>
+        <v>1.96</v>
       </c>
       <c r="K16" s="1" t="n">
-        <v>-0.36</v>
+        <v>0.3</v>
       </c>
       <c r="L16" s="1" t="inlineStr">
         <is>
-          <t>Down</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="M16" s="1" t="n">
-        <v>0</v>
+        <v>-7.76</v>
       </c>
       <c r="N16" s="1" t="inlineStr">
         <is>
@@ -1527,46 +1527,46 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>Commodities</t>
+          <t>Consumption</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
         <v>16</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>5</v>
+        <v>-5</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>9</v>
+        <v>-7</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>9</v>
+        <v>-4</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>95.27</v>
+        <v>123.68</v>
       </c>
       <c r="H17" s="1" t="n">
-        <v>-0.13</v>
+        <v>-1.11</v>
       </c>
       <c r="I17" s="1" t="n">
-        <v>0.6</v>
+        <v>-0.23</v>
       </c>
       <c r="J17" s="1" t="n">
-        <v>2.21</v>
+        <v>-0.51</v>
       </c>
       <c r="K17" s="1" t="n">
-        <v>-0.75</v>
+        <v>-0.22</v>
       </c>
       <c r="L17" s="1" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Down</t>
         </is>
       </c>
       <c r="M17" s="1" t="n">
-        <v>-7.92</v>
+        <v>-5.76</v>
       </c>
       <c r="N17" s="1" t="inlineStr">
         <is>
@@ -1592,46 +1592,46 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>MNC</t>
+          <t>Tourism</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
         <v>17</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>1</v>
+        <v>-8</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-3</v>
+        <v>-12</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>31.77</v>
+        <v>76.34999999999999</v>
       </c>
       <c r="H18" s="1" t="n">
-        <v>-1.34</v>
+        <v>0.53</v>
       </c>
       <c r="I18" s="1" t="n">
-        <v>1.51</v>
+        <v>1.28</v>
       </c>
       <c r="J18" s="1" t="n">
-        <v>-0.53</v>
+        <v>4.44</v>
       </c>
       <c r="K18" s="1" t="n">
-        <v>-1.09</v>
+        <v>-0.54</v>
       </c>
       <c r="L18" s="1" t="inlineStr">
         <is>
-          <t>Down</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="M18" s="1" t="n">
-        <v>-3.55</v>
+        <v>-10.39</v>
       </c>
       <c r="N18" s="1" t="inlineStr">
         <is>
@@ -1657,38 +1657,38 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>PSE</t>
+          <t>Private Bank</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
         <v>18</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>9</v>
+        <v>-7</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>5</v>
+        <v>-8</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>9.82</v>
+        <v>27.27</v>
       </c>
       <c r="H19" s="1" t="n">
-        <v>-1.5</v>
+        <v>0.66</v>
       </c>
       <c r="I19" s="1" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="J19" s="1" t="n">
-        <v>4.09</v>
+        <v>2.47</v>
       </c>
       <c r="K19" s="1" t="n">
-        <v>-1.18</v>
+        <v>-0.54</v>
       </c>
       <c r="L19" s="1" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         </is>
       </c>
       <c r="M19" s="1" t="n">
-        <v>-9.529999999999999</v>
+        <v>-2.54</v>
       </c>
       <c r="N19" s="1" t="inlineStr">
         <is>
@@ -1722,38 +1722,38 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>Private Bank</t>
+          <t>PSE</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
         <v>19</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>-4</v>
+        <v>5</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>-7</v>
+        <v>5</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>-7</v>
+        <v>5</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>26.93</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="H20" s="1" t="n">
-        <v>-1.89</v>
+        <v>-0.31</v>
       </c>
       <c r="I20" s="1" t="n">
-        <v>-0.38</v>
+        <v>1.42</v>
       </c>
       <c r="J20" s="1" t="n">
-        <v>1.11</v>
+        <v>2.9</v>
       </c>
       <c r="K20" s="1" t="n">
-        <v>-1.2</v>
+        <v>-1.15</v>
       </c>
       <c r="L20" s="1" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
         </is>
       </c>
       <c r="M20" s="1" t="n">
-        <v>-3.88</v>
+        <v>-9.779999999999999</v>
       </c>
       <c r="N20" s="1" t="inlineStr">
         <is>
@@ -1787,38 +1787,38 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>Tourism</t>
+          <t>Bank</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
         <v>20</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>-9</v>
+        <v>0</v>
       </c>
       <c r="D21" s="2" t="n">
         <v>-9</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>-12</v>
+        <v>-10</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>-15</v>
+        <v>-6</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>75.66</v>
+        <v>567.42</v>
       </c>
       <c r="H21" s="1" t="n">
-        <v>-1.36</v>
+        <v>0.37</v>
       </c>
       <c r="I21" s="1" t="n">
-        <v>-0.62</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="J21" s="1" t="n">
-        <v>2.83</v>
+        <v>1.05</v>
       </c>
       <c r="K21" s="1" t="n">
-        <v>-1.36</v>
+        <v>-1.23</v>
       </c>
       <c r="L21" s="1" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         </is>
       </c>
       <c r="M21" s="1" t="n">
-        <v>-11.69</v>
+        <v>-4.98</v>
       </c>
       <c r="N21" s="1" t="inlineStr">
         <is>
@@ -1852,38 +1852,38 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>Bank</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
         <v>21</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>-5</v>
+        <v>4</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>-5</v>
+        <v>4</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>-11</v>
+        <v>1</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>-5</v>
+        <v>-2</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>564.42</v>
+        <v>90.81</v>
       </c>
       <c r="H22" s="1" t="n">
-        <v>-2.07</v>
+        <v>0.21</v>
       </c>
       <c r="I22" s="1" t="n">
-        <v>-0.24</v>
+        <v>1.07</v>
       </c>
       <c r="J22" s="1" t="n">
-        <v>0.55</v>
+        <v>1.63</v>
       </c>
       <c r="K22" s="1" t="n">
-        <v>-1.53</v>
+        <v>-1.97</v>
       </c>
       <c r="L22" s="1" t="inlineStr">
         <is>
@@ -1891,7 +1891,7 @@
         </is>
       </c>
       <c r="M22" s="1" t="n">
-        <v>-5.61</v>
+        <v>-3.99</v>
       </c>
       <c r="N22" s="1" t="inlineStr">
         <is>
@@ -1917,46 +1917,46 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>Capital Market</t>
+          <t>PSU Bank</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
         <v>22</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>-2</v>
+        <v>-8</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>-18</v>
+        <v>1</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>51.55</v>
+        <v>89.59</v>
       </c>
       <c r="H23" s="1" t="n">
-        <v>-2.68</v>
+        <v>-0.37</v>
       </c>
       <c r="I23" s="1" t="n">
-        <v>0.43</v>
+        <v>-0.1</v>
       </c>
       <c r="J23" s="1" t="n">
-        <v>-0.06</v>
+        <v>0.09</v>
       </c>
       <c r="K23" s="1" t="n">
-        <v>-1.82</v>
+        <v>-2.26</v>
       </c>
       <c r="L23" s="1" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Down</t>
         </is>
       </c>
       <c r="M23" s="1" t="n">
-        <v>0</v>
+        <v>-13.86</v>
       </c>
       <c r="N23" s="1" t="inlineStr">
         <is>
@@ -1982,38 +1982,38 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>PSU Bank</t>
+          <t>MNC</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
         <v>23</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>-10</v>
+        <v>-6</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>3</v>
+        <v>-20</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>89.70999999999999</v>
+        <v>31.41</v>
       </c>
       <c r="H24" s="1" t="n">
-        <v>-2.86</v>
+        <v>-1.63</v>
       </c>
       <c r="I24" s="1" t="n">
-        <v>0.41</v>
+        <v>0.46</v>
       </c>
       <c r="J24" s="1" t="n">
-        <v>0.02</v>
+        <v>-1.35</v>
       </c>
       <c r="K24" s="1" t="n">
-        <v>-1.84</v>
+        <v>-2.69</v>
       </c>
       <c r="L24" s="1" t="inlineStr">
         <is>
@@ -2021,7 +2021,7 @@
         </is>
       </c>
       <c r="M24" s="1" t="n">
-        <v>-13.85</v>
+        <v>-4.52</v>
       </c>
       <c r="N24" s="1" t="inlineStr">
         <is>
@@ -2054,31 +2054,31 @@
         <v>24</v>
       </c>
       <c r="C25" s="2" t="n">
+        <v>-12</v>
+      </c>
+      <c r="D25" s="2" t="n">
         <v>-11</v>
       </c>
-      <c r="D25" s="2" t="n">
-        <v>-10</v>
-      </c>
       <c r="E25" s="2" t="n">
-        <v>-10</v>
+        <v>-11</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>-11</v>
+        <v>-16</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>30.42</v>
+        <v>30.25</v>
       </c>
       <c r="H25" s="1" t="n">
-        <v>-2.19</v>
+        <v>-1.01</v>
       </c>
       <c r="I25" s="1" t="n">
-        <v>-1.96</v>
+        <v>-2.9</v>
       </c>
       <c r="J25" s="1" t="n">
-        <v>-2.16</v>
+        <v>-2.03</v>
       </c>
       <c r="K25" s="1" t="n">
-        <v>-2.04</v>
+        <v>-3.11</v>
       </c>
       <c r="L25" s="1" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         </is>
       </c>
       <c r="M25" s="1" t="n">
-        <v>-3.81</v>
+        <v>-4.22</v>
       </c>
       <c r="N25" s="1" t="inlineStr">
         <is>
@@ -2112,38 +2112,38 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
         <v>25</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>-4</v>
+        <v>2</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>-6</v>
+        <v>-14</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>90.62</v>
+        <v>36.75</v>
       </c>
       <c r="H26" s="1" t="n">
-        <v>0.12</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="I26" s="1" t="n">
-        <v>0.4</v>
+        <v>0.44</v>
       </c>
       <c r="J26" s="1" t="n">
-        <v>1.64</v>
+        <v>2.51</v>
       </c>
       <c r="K26" s="1" t="n">
-        <v>-2.19</v>
+        <v>-3.34</v>
       </c>
       <c r="L26" s="1" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="M26" s="1" t="n">
-        <v>-4.32</v>
+        <v>0</v>
       </c>
       <c r="N26" s="1" t="inlineStr">
         <is>
@@ -2177,38 +2177,38 @@
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Capital Market</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
         <v>26</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>-20</v>
+        <v>-22</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>36.92</v>
+        <v>51.31</v>
       </c>
       <c r="H27" s="1" t="n">
-        <v>-1.91</v>
+        <v>-0.89</v>
       </c>
       <c r="I27" s="1" t="n">
-        <v>0.44</v>
+        <v>-1.05</v>
       </c>
       <c r="J27" s="1" t="n">
-        <v>3.2</v>
+        <v>0.61</v>
       </c>
       <c r="K27" s="1" t="n">
-        <v>-3.67</v>
+        <v>-3.54</v>
       </c>
       <c r="L27" s="1" t="inlineStr">
         <is>
@@ -2255,25 +2255,25 @@
         <v>0</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>48.35</v>
+        <v>47.92</v>
       </c>
       <c r="H28" s="1" t="n">
-        <v>-0.84</v>
+        <v>-0.89</v>
       </c>
       <c r="I28" s="1" t="n">
-        <v>1.38</v>
+        <v>0.17</v>
       </c>
       <c r="J28" s="1" t="n">
-        <v>2.4</v>
+        <v>1.79</v>
       </c>
       <c r="K28" s="1" t="n">
-        <v>-3.9</v>
+        <v>-5.97</v>
       </c>
       <c r="L28" s="1" t="inlineStr">
         <is>
@@ -2281,7 +2281,7 @@
         </is>
       </c>
       <c r="M28" s="1" t="n">
-        <v>-15.3</v>
+        <v>-15.5</v>
       </c>
       <c r="N28" s="1" t="inlineStr">
         <is>
@@ -2569,20 +2569,20 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F2" s="1" t="n">
         <v>8</v>
@@ -2606,71 +2606,71 @@
         <v>24</v>
       </c>
       <c r="M2" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="N2" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="O2" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="P2" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="N2" s="1" t="n">
+      <c r="Q2" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="R2" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="S2" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="T2" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="U2" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="V2" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="O2" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="P2" s="1" t="n">
+      <c r="W2" s="1" t="n">
         <v>26</v>
       </c>
-      <c r="Q2" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="R2" s="1" t="n">
+      <c r="X2" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y2" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z2" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="S2" s="1" t="n">
+      <c r="AA2" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="T2" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="U2" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="V2" s="1" t="n">
+      <c r="AB2" s="1" t="n">
         <v>9</v>
-      </c>
-      <c r="W2" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="X2" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y2" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z2" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="AA2" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="AB2" s="1" t="n">
-        <v>11</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C3" s="1" t="n">
         <v>21</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F3" s="1" t="n">
         <v>8</v>
@@ -2679,92 +2679,92 @@
         <v>27</v>
       </c>
       <c r="H3" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I3" s="1" t="n">
         <v>7</v>
       </c>
       <c r="J3" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="K3" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="K3" s="1" t="n">
-        <v>3</v>
-      </c>
       <c r="L3" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="M3" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="N3" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="O3" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="P3" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q3" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="M3" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="N3" s="1" t="n">
+      <c r="R3" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="S3" s="1" t="n">
         <v>13</v>
-      </c>
-      <c r="O3" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="P3" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="Q3" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="R3" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="S3" s="1" t="n">
-        <v>11</v>
       </c>
       <c r="T3" s="1" t="n">
         <v>14</v>
       </c>
       <c r="U3" s="1" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="V3" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="W3" s="1" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="X3" s="1" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y3" s="1" t="n">
         <v>1</v>
       </c>
       <c r="Z3" s="1" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="AA3" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AB3" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D4" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="E4" s="1" t="n">
         <v>24</v>
-      </c>
-      <c r="E4" s="1" t="n">
-        <v>22</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>8</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H4" s="1" t="n">
         <v>2</v>
@@ -2773,46 +2773,46 @@
         <v>6</v>
       </c>
       <c r="J4" s="1" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K4" s="1" t="n">
         <v>4</v>
       </c>
       <c r="L4" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M4" s="1" t="n">
         <v>25</v>
       </c>
       <c r="N4" s="1" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="O4" s="1" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="P4" s="1" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Q4" s="1" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="R4" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="S4" s="1" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T4" s="1" t="n">
         <v>14</v>
       </c>
       <c r="U4" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="V4" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W4" s="1" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="X4" s="1" t="n">
         <v>3</v>
@@ -2821,19 +2821,19 @@
         <v>1</v>
       </c>
       <c r="Z4" s="1" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="AA4" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AB4" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
@@ -2867,7 +2867,7 @@
         <v>4</v>
       </c>
       <c r="L5" s="1" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="M5" s="1" t="n">
         <v>25</v>
@@ -2882,7 +2882,7 @@
         <v>26</v>
       </c>
       <c r="Q5" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="R5" s="1" t="n">
         <v>17</v>
@@ -2909,10 +2909,10 @@
         <v>1</v>
       </c>
       <c r="Z5" s="1" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AA5" s="1" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="AB5" s="1" t="n">
         <v>12</v>
@@ -2921,105 +2921,105 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="C6" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="F6" s="1" t="n">
         <v>8</v>
-      </c>
-      <c r="C6" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>23</v>
-      </c>
-      <c r="F6" s="1" t="n">
-        <v>7</v>
       </c>
       <c r="G6" s="1" t="n">
         <v>27</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I6" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="J6" s="1" t="n">
         <v>5</v>
-      </c>
-      <c r="J6" s="1" t="n">
-        <v>6</v>
       </c>
       <c r="K6" s="1" t="n">
         <v>4</v>
       </c>
       <c r="L6" s="1" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="M6" s="1" t="n">
         <v>25</v>
       </c>
       <c r="N6" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="O6" s="1" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="P6" s="1" t="n">
         <v>26</v>
       </c>
       <c r="Q6" s="1" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="R6" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="S6" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="T6" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="T6" s="1" t="n">
-        <v>19</v>
-      </c>
       <c r="U6" s="1" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="V6" s="1" t="n">
         <v>10</v>
       </c>
       <c r="W6" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="X6" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y6" s="1" t="n">
         <v>1</v>
       </c>
       <c r="Z6" s="1" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AA6" s="1" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="AB6" s="1" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E7" s="1" t="n">
         <v>23</v>
@@ -3034,49 +3034,49 @@
         <v>3</v>
       </c>
       <c r="I7" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="J7" s="1" t="n">
         <v>6</v>
-      </c>
-      <c r="J7" s="1" t="n">
-        <v>8</v>
       </c>
       <c r="K7" s="1" t="n">
         <v>4</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M7" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="N7" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="O7" s="1" t="n">
         <v>24</v>
-      </c>
-      <c r="N7" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="O7" s="1" t="n">
-        <v>25</v>
       </c>
       <c r="P7" s="1" t="n">
         <v>26</v>
       </c>
       <c r="Q7" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="R7" s="1" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="S7" s="1" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="T7" s="1" t="n">
         <v>19</v>
       </c>
       <c r="U7" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="V7" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="W7" s="1" t="n">
         <v>17</v>
-      </c>
-      <c r="V7" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="W7" s="1" t="n">
-        <v>22</v>
       </c>
       <c r="X7" s="1" t="n">
         <v>2</v>
@@ -3085,10 +3085,10 @@
         <v>1</v>
       </c>
       <c r="Z7" s="1" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="AA7" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AB7" s="1" t="n">
         <v>9</v>
@@ -3097,114 +3097,114 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>7</v>
       </c>
       <c r="G8" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="H8" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="I8" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="J8" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="K8" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="L8" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="M8" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="N8" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="O8" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="P8" s="1" t="n">
         <v>26</v>
       </c>
-      <c r="H8" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="I8" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="J8" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="K8" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="L8" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="M8" s="1" t="n">
+      <c r="Q8" s="1" t="n">
         <v>21</v>
-      </c>
-      <c r="N8" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="O8" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="P8" s="1" t="n">
-        <v>27</v>
-      </c>
-      <c r="Q8" s="1" t="n">
-        <v>23</v>
       </c>
       <c r="R8" s="1" t="n">
         <v>20</v>
       </c>
       <c r="S8" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="T8" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="T8" s="1" t="n">
-        <v>15</v>
-      </c>
       <c r="U8" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="V8" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="W8" s="1" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="X8" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y8" s="1" t="n">
         <v>1</v>
       </c>
       <c r="Z8" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA8" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="AA8" s="1" t="n">
-        <v>13</v>
-      </c>
       <c r="AB8" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
         <v>6</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F9" s="1" t="n">
         <v>7</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H9" s="1" t="n">
         <v>2</v>
@@ -3213,46 +3213,46 @@
         <v>4</v>
       </c>
       <c r="J9" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K9" s="1" t="n">
         <v>5</v>
       </c>
       <c r="L9" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="M9" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="N9" s="1" t="n">
         <v>9</v>
-      </c>
-      <c r="M9" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="N9" s="1" t="n">
-        <v>13</v>
       </c>
       <c r="O9" s="1" t="n">
         <v>22</v>
       </c>
       <c r="P9" s="1" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Q9" s="1" t="n">
         <v>23</v>
       </c>
       <c r="R9" s="1" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="S9" s="1" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="T9" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="U9" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="U9" s="1" t="n">
-        <v>15</v>
-      </c>
       <c r="V9" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="W9" s="1" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="X9" s="1" t="n">
         <v>3</v>
@@ -3261,10 +3261,10 @@
         <v>1</v>
       </c>
       <c r="Z9" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AA9" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AB9" s="1" t="n">
         <v>8</v>
@@ -3273,20 +3273,20 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
         <v>6</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F10" s="1" t="n">
         <v>7</v>
@@ -3301,43 +3301,43 @@
         <v>4</v>
       </c>
       <c r="J10" s="1" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K10" s="1" t="n">
         <v>5</v>
       </c>
       <c r="L10" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M10" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N10" s="1" t="n">
         <v>13</v>
       </c>
       <c r="O10" s="1" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="P10" s="1" t="n">
         <v>26</v>
       </c>
       <c r="Q10" s="1" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="R10" s="1" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="S10" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="T10" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="U10" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="T10" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="U10" s="1" t="n">
-        <v>18</v>
-      </c>
       <c r="V10" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="W10" s="1" t="n">
         <v>21</v>
@@ -3352,7 +3352,7 @@
         <v>12</v>
       </c>
       <c r="AA10" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AB10" s="1" t="n">
         <v>8</v>
@@ -3361,23 +3361,23 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E11" s="1" t="n">
         <v>24</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G11" s="1" t="n">
         <v>27</v>
@@ -3389,46 +3389,46 @@
         <v>4</v>
       </c>
       <c r="J11" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K11" s="1" t="n">
         <v>5</v>
       </c>
       <c r="L11" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="M11" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="N11" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="M11" s="1" t="n">
+      <c r="O11" s="1" t="n">
         <v>25</v>
-      </c>
-      <c r="N11" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="O11" s="1" t="n">
-        <v>21</v>
       </c>
       <c r="P11" s="1" t="n">
         <v>26</v>
       </c>
       <c r="Q11" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R11" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="S11" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="T11" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="S11" s="1" t="n">
+      <c r="U11" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="T11" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="U11" s="1" t="n">
-        <v>16</v>
-      </c>
       <c r="V11" s="1" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="W11" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="X11" s="1" t="n">
         <v>3</v>
@@ -3437,10 +3437,10 @@
         <v>1</v>
       </c>
       <c r="Z11" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AA11" s="1" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AB11" s="1" t="n">
         <v>8</v>
@@ -3449,23 +3449,23 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G12" s="1" t="n">
         <v>27</v>
@@ -3477,19 +3477,19 @@
         <v>4</v>
       </c>
       <c r="J12" s="1" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="K12" s="1" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M12" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="N12" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O12" s="1" t="n">
         <v>21</v>
@@ -3498,22 +3498,22 @@
         <v>26</v>
       </c>
       <c r="Q12" s="1" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="R12" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="S12" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="T12" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="S12" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="T12" s="1" t="n">
-        <v>20</v>
-      </c>
       <c r="U12" s="1" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="V12" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="W12" s="1" t="n">
         <v>22</v>
@@ -3525,23 +3525,23 @@
         <v>1</v>
       </c>
       <c r="Z12" s="1" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AA12" s="1" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="AB12" s="1" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C13" s="1" t="n">
         <v>16</v>
@@ -3550,7 +3550,7 @@
         <v>18</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F13" s="1" t="n">
         <v>9</v>
@@ -3562,22 +3562,22 @@
         <v>2</v>
       </c>
       <c r="I13" s="1" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J13" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="K13" s="1" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L13" s="1" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="M13" s="1" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="N13" s="1" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="O13" s="1" t="n">
         <v>21</v>
@@ -3589,22 +3589,22 @@
         <v>25</v>
       </c>
       <c r="R13" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="S13" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="T13" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="S13" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="T13" s="1" t="n">
-        <v>19</v>
-      </c>
       <c r="U13" s="1" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="V13" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="W13" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="X13" s="1" t="n">
         <v>3</v>
@@ -3613,62 +3613,62 @@
         <v>1</v>
       </c>
       <c r="Z13" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AA13" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AB13" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E14" s="1" t="n">
         <v>24</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G14" s="1" t="n">
         <v>27</v>
       </c>
       <c r="H14" s="1" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I14" s="1" t="n">
         <v>6</v>
       </c>
       <c r="J14" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K14" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="M14" s="1" t="n">
         <v>22</v>
       </c>
       <c r="N14" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O14" s="1" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="P14" s="1" t="n">
         <v>26</v>
@@ -3677,86 +3677,86 @@
         <v>25</v>
       </c>
       <c r="R14" s="1" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="S14" s="1" t="n">
         <v>5</v>
       </c>
       <c r="T14" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="U14" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="V14" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="V14" s="1" t="n">
-        <v>13</v>
-      </c>
       <c r="W14" s="1" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="X14" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y14" s="1" t="n">
         <v>1</v>
       </c>
       <c r="Z14" s="1" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AA14" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AB14" s="1" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D15" s="1" t="n">
         <v>21</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G15" s="1" t="n">
         <v>27</v>
       </c>
       <c r="H15" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I15" s="1" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J15" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K15" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L15" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M15" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N15" s="1" t="n">
         <v>12</v>
       </c>
       <c r="O15" s="1" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="P15" s="1" t="n">
         <v>26</v>
@@ -3765,110 +3765,110 @@
         <v>25</v>
       </c>
       <c r="R15" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="S15" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T15" s="1" t="n">
         <v>20</v>
       </c>
       <c r="U15" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="V15" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="V15" s="1" t="n">
-        <v>11</v>
-      </c>
       <c r="W15" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="X15" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y15" s="1" t="n">
         <v>1</v>
       </c>
       <c r="Z15" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA15" s="1" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AB15" s="1" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="C16" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="C16" s="1" t="n">
-        <v>16</v>
-      </c>
       <c r="D16" s="1" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F16" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G16" s="1" t="n">
         <v>27</v>
       </c>
       <c r="H16" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I16" s="1" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J16" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K16" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L16" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M16" s="1" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N16" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="O16" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="P16" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q16" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="R16" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="S16" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="T16" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="U16" s="1" t="n">
         <v>13</v>
-      </c>
-      <c r="O16" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="P16" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="Q16" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="R16" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="S16" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="T16" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="U16" s="1" t="n">
-        <v>14</v>
       </c>
       <c r="V16" s="1" t="n">
         <v>11</v>
       </c>
       <c r="W16" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="X16" s="1" t="n">
         <v>3</v>
@@ -3877,29 +3877,29 @@
         <v>1</v>
       </c>
       <c r="Z16" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA16" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="AB16" s="1" t="n">
         <v>9</v>
-      </c>
-      <c r="AA16" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="AB16" s="1" t="n">
-        <v>10</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="C17" s="1" t="n">
         <v>16</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E17" s="1" t="n">
         <v>23</v>
@@ -3917,46 +3917,46 @@
         <v>7</v>
       </c>
       <c r="J17" s="1" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="K17" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L17" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M17" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N17" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O17" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="P17" s="1" t="n">
         <v>25</v>
-      </c>
-      <c r="P17" s="1" t="n">
-        <v>26</v>
       </c>
       <c r="Q17" s="1" t="n">
         <v>24</v>
       </c>
       <c r="R17" s="1" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="S17" s="1" t="n">
         <v>5</v>
       </c>
       <c r="T17" s="1" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="U17" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="V17" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="W17" s="1" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="X17" s="1" t="n">
         <v>3</v>
@@ -3965,10 +3965,10 @@
         <v>1</v>
       </c>
       <c r="Z17" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA17" s="1" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AB17" s="1" t="n">
         <v>10</v>
@@ -3977,59 +3977,59 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F18" s="1" t="n">
         <v>6</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H18" s="1" t="n">
         <v>4</v>
       </c>
       <c r="I18" s="1" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J18" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K18" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L18" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M18" s="1" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N18" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="O18" s="1" t="n">
         <v>25</v>
       </c>
       <c r="P18" s="1" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Q18" s="1" t="n">
         <v>24</v>
       </c>
       <c r="R18" s="1" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="S18" s="1" t="n">
         <v>5</v>
@@ -4041,10 +4041,10 @@
         <v>13</v>
       </c>
       <c r="V18" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="W18" s="1" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="X18" s="1" t="n">
         <v>3</v>
@@ -4053,35 +4053,35 @@
         <v>1</v>
       </c>
       <c r="Z18" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA18" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AB18" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="C19" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="C19" s="1" t="n">
-        <v>10</v>
-      </c>
       <c r="D19" s="1" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F19" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G19" s="1" t="n">
         <v>26</v>
@@ -4090,22 +4090,22 @@
         <v>4</v>
       </c>
       <c r="I19" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J19" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K19" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L19" s="1" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M19" s="1" t="n">
         <v>23</v>
       </c>
       <c r="N19" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O19" s="1" t="n">
         <v>25</v>
@@ -4117,22 +4117,22 @@
         <v>24</v>
       </c>
       <c r="R19" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="S19" s="1" t="n">
         <v>5</v>
       </c>
       <c r="T19" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="U19" s="1" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="V19" s="1" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="W19" s="1" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="X19" s="1" t="n">
         <v>3</v>
@@ -4144,32 +4144,32 @@
         <v>7</v>
       </c>
       <c r="AA19" s="1" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="AB19" s="1" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D20" s="1" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F20" s="1" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G20" s="1" t="n">
         <v>26</v>
@@ -4178,49 +4178,49 @@
         <v>4</v>
       </c>
       <c r="I20" s="1" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="J20" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K20" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L20" s="1" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="M20" s="1" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="N20" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O20" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="P20" s="1" t="n">
         <v>27</v>
       </c>
       <c r="Q20" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R20" s="1" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="S20" s="1" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T20" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="U20" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="V20" s="1" t="n">
         <v>18</v>
       </c>
       <c r="W20" s="1" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="X20" s="1" t="n">
         <v>3</v>
@@ -4229,19 +4229,19 @@
         <v>1</v>
       </c>
       <c r="Z20" s="1" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AA20" s="1" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AB20" s="1" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
@@ -4251,7 +4251,7 @@
         <v>11</v>
       </c>
       <c r="D21" s="1" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E21" s="1" t="n">
         <v>16</v>
@@ -4260,7 +4260,7 @@
         <v>6</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H21" s="1" t="n">
         <v>4</v>
@@ -4275,40 +4275,40 @@
         <v>2</v>
       </c>
       <c r="L21" s="1" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="M21" s="1" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="N21" s="1" t="n">
         <v>14</v>
       </c>
       <c r="O21" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P21" s="1" t="n">
         <v>27</v>
       </c>
       <c r="Q21" s="1" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="R21" s="1" t="n">
         <v>19</v>
       </c>
       <c r="S21" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T21" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="U21" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="V21" s="1" t="n">
         <v>18</v>
       </c>
       <c r="W21" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="X21" s="1" t="n">
         <v>3</v>
@@ -4317,10 +4317,10 @@
         <v>1</v>
       </c>
       <c r="Z21" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA21" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AB21" s="1" t="n">
         <v>7</v>
@@ -4329,29 +4329,29 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D22" s="1" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F22" s="1" t="n">
         <v>6</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H22" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I22" s="1" t="n">
         <v>5</v>
@@ -4363,16 +4363,16 @@
         <v>2</v>
       </c>
       <c r="L22" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M22" s="1" t="n">
         <v>22</v>
       </c>
       <c r="N22" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="O22" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="P22" s="1" t="n">
         <v>27</v>
@@ -4381,34 +4381,34 @@
         <v>26</v>
       </c>
       <c r="R22" s="1" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="S22" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T22" s="1" t="n">
         <v>21</v>
       </c>
       <c r="U22" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="V22" s="1" t="n">
         <v>18</v>
-      </c>
-      <c r="V22" s="1" t="n">
-        <v>15</v>
       </c>
       <c r="W22" s="1" t="n">
         <v>20</v>
       </c>
       <c r="X22" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y22" s="1" t="n">
         <v>1</v>
       </c>
       <c r="Z22" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA22" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AB22" s="1" t="n">
         <v>7</v>
@@ -4417,7 +4417,7 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
@@ -4427,22 +4427,22 @@
         <v>10</v>
       </c>
       <c r="D23" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F23" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="G23" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="H23" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="G23" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="H23" s="1" t="n">
+      <c r="I23" s="1" t="n">
         <v>5</v>
-      </c>
-      <c r="I23" s="1" t="n">
-        <v>6</v>
       </c>
       <c r="J23" s="1" t="n">
         <v>23</v>
@@ -4451,37 +4451,37 @@
         <v>2</v>
       </c>
       <c r="L23" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M23" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="N23" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="O23" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="P23" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q23" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="R23" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="S23" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="T23" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="N23" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="O23" s="1" t="n">
-        <v>27</v>
-      </c>
-      <c r="P23" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="Q23" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="R23" s="1" t="n">
+      <c r="U23" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="S23" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="T23" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="U23" s="1" t="n">
+      <c r="V23" s="1" t="n">
         <v>15</v>
-      </c>
-      <c r="V23" s="1" t="n">
-        <v>17</v>
       </c>
       <c r="W23" s="1" t="n">
         <v>20</v>
@@ -4493,7 +4493,7 @@
         <v>1</v>
       </c>
       <c r="Z23" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA23" s="1" t="n">
         <v>16</v>
@@ -4505,77 +4505,77 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D24" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="E24" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="E24" s="1" t="n">
-        <v>14</v>
-      </c>
       <c r="F24" s="1" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G24" s="1" t="n">
         <v>24</v>
       </c>
       <c r="H24" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I24" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J24" s="1" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="K24" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L24" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="M24" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="N24" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="O24" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="P24" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q24" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="R24" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="S24" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="T24" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="U24" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="V24" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="M24" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="N24" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="O24" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="P24" s="1" t="n">
-        <v>27</v>
-      </c>
-      <c r="Q24" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="R24" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="S24" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="T24" s="1" t="n">
-        <v>23</v>
-      </c>
-      <c r="U24" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="V24" s="1" t="n">
-        <v>16</v>
-      </c>
       <c r="W24" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="X24" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y24" s="1" t="n">
         <v>1</v>
@@ -4584,26 +4584,26 @@
         <v>8</v>
       </c>
       <c r="AA24" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AB24" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="C25" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="C25" s="1" t="n">
-        <v>10</v>
-      </c>
       <c r="D25" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E25" s="1" t="n">
         <v>14</v>
@@ -4621,34 +4621,34 @@
         <v>7</v>
       </c>
       <c r="J25" s="1" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K25" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L25" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M25" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N25" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="O25" s="1" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P25" s="1" t="n">
         <v>27</v>
       </c>
       <c r="Q25" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="R25" s="1" t="n">
         <v>19</v>
       </c>
       <c r="S25" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T25" s="1" t="n">
         <v>23</v>
@@ -4660,7 +4660,7 @@
         <v>16</v>
       </c>
       <c r="W25" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="X25" s="1" t="n">
         <v>3</v>
@@ -4669,47 +4669,47 @@
         <v>1</v>
       </c>
       <c r="Z25" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA25" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="AB25" s="1" t="n">
         <v>6</v>
-      </c>
-      <c r="AA25" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="AB25" s="1" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
         <v>11</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D26" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="E26" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="E26" s="1" t="n">
-        <v>12</v>
-      </c>
       <c r="F26" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G26" s="1" t="n">
         <v>24</v>
       </c>
       <c r="H26" s="1" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I26" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J26" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K26" s="1" t="n">
         <v>2</v>
@@ -4718,7 +4718,7 @@
         <v>15</v>
       </c>
       <c r="M26" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N26" s="1" t="n">
         <v>13</v>
@@ -4736,7 +4736,7 @@
         <v>19</v>
       </c>
       <c r="S26" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T26" s="1" t="n">
         <v>23</v>
@@ -4745,7 +4745,7 @@
         <v>18</v>
       </c>
       <c r="V26" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="W26" s="1" t="n">
         <v>20</v>
@@ -4757,32 +4757,32 @@
         <v>1</v>
       </c>
       <c r="Z26" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA26" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AB26" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C27" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="D27" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="E27" s="1" t="n">
         <v>12</v>
-      </c>
-      <c r="D27" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="E27" s="1" t="n">
-        <v>13</v>
       </c>
       <c r="F27" s="1" t="n">
         <v>4</v>
@@ -4791,10 +4791,10 @@
         <v>24</v>
       </c>
       <c r="H27" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I27" s="1" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J27" s="1" t="n">
         <v>21</v>
@@ -4803,40 +4803,40 @@
         <v>2</v>
       </c>
       <c r="L27" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="M27" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="N27" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="O27" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="P27" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q27" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="R27" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="S27" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="U27" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="M27" s="1" t="n">
+      <c r="V27" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="W27" s="1" t="n">
         <v>20</v>
-      </c>
-      <c r="N27" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="O27" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="P27" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="Q27" s="1" t="n">
-        <v>27</v>
-      </c>
-      <c r="R27" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="S27" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="T27" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="U27" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="V27" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="W27" s="1" t="n">
-        <v>23</v>
       </c>
       <c r="X27" s="1" t="n">
         <v>3</v>
@@ -4845,38 +4845,38 @@
         <v>1</v>
       </c>
       <c r="Z27" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA27" s="1" t="n">
         <v>16</v>
       </c>
       <c r="AB27" s="1" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C28" s="1" t="n">
         <v>12</v>
       </c>
       <c r="D28" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F28" s="1" t="n">
         <v>4</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H28" s="1" t="n">
         <v>7</v>
@@ -4885,7 +4885,7 @@
         <v>11</v>
       </c>
       <c r="J28" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K28" s="1" t="n">
         <v>2</v>
@@ -4894,25 +4894,25 @@
         <v>18</v>
       </c>
       <c r="M28" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="N28" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="O28" s="1" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="P28" s="1" t="n">
         <v>26</v>
       </c>
       <c r="Q28" s="1" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="R28" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="S28" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T28" s="1" t="n">
         <v>22</v>
@@ -4921,7 +4921,7 @@
         <v>19</v>
       </c>
       <c r="V28" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="W28" s="1" t="n">
         <v>23</v>
@@ -4936,7 +4936,7 @@
         <v>6</v>
       </c>
       <c r="AA28" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AB28" s="1" t="n">
         <v>5</v>
@@ -4945,47 +4945,47 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C29" s="1" t="n">
         <v>12</v>
       </c>
       <c r="D29" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="E29" s="1" t="n">
         <v>15</v>
-      </c>
-      <c r="E29" s="1" t="n">
-        <v>10</v>
       </c>
       <c r="F29" s="1" t="n">
         <v>4</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H29" s="1" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I29" s="1" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J29" s="1" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K29" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L29" s="1" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M29" s="1" t="n">
         <v>21</v>
       </c>
       <c r="N29" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O29" s="1" t="n">
         <v>27</v>
@@ -4994,59 +4994,59 @@
         <v>26</v>
       </c>
       <c r="Q29" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R29" s="1" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="S29" s="1" t="n">
         <v>8</v>
       </c>
       <c r="T29" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="U29" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="V29" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="W29" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="U29" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="V29" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="W29" s="1" t="n">
+      <c r="X29" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y29" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="X29" s="1" t="n">
+      <c r="Z29" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA29" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="AB29" s="1" t="n">
         <v>5</v>
-      </c>
-      <c r="Y29" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z29" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA29" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="AB29" s="1" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
         <v>13</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D30" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F30" s="1" t="n">
         <v>4</v>
@@ -5055,13 +5055,13 @@
         <v>24</v>
       </c>
       <c r="H30" s="1" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I30" s="1" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="J30" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K30" s="1" t="n">
         <v>3</v>
@@ -5085,25 +5085,25 @@
         <v>25</v>
       </c>
       <c r="R30" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="S30" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="T30" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="U30" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="V30" s="1" t="n">
         <v>16</v>
-      </c>
-      <c r="S30" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="T30" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="U30" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="V30" s="1" t="n">
-        <v>15</v>
       </c>
       <c r="W30" s="1" t="n">
         <v>1</v>
       </c>
       <c r="X30" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y30" s="1" t="n">
         <v>2</v>
@@ -5112,26 +5112,26 @@
         <v>7</v>
       </c>
       <c r="AA30" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AB30" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
   